--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,186 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6362.psd</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0003.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6361.psd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tamilpsd-0004.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6360.psd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0005.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6359.psd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tamilpsd-0006.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6358.psd</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0007.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6357.psd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tamilpsd-0008.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6356.psd</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0009.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6355.psd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>tamilpsd-0010.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6354.psd</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0011.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6353.psd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>tamilpsd-0012.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6352.psd</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0013.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6351.psd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>tamilpsd-0014.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6350.psd</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0015.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6349.psd</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tamilpsd-0016.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6348.psd</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0017.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -654,6 +654,1206 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6347.psd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>tamilpsd-0018.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>6346.psd</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0019.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6345.psd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>tamilpsd-0020.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>6342.psd</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0021.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6341.psd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>tamilpsd-0022.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>6340.psd</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0023.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6339.psd</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>tamilpsd-0024.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>6338.psd</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0025.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6337.psd</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>tamilpsd-0026.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>6336.psd</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0027.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6335.psd</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>tamilpsd-0028.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>6334.psd</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0029.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6333.psd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>tamilpsd-0030.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>6332.psd</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0031.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6331.psd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>tamilpsd-0032.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>6330.psd</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0033.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6329.psd</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>tamilpsd-0034.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>6328.psd</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0035.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6327.psd</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>tamilpsd-0036.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>6326.psd</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0037.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6325.psd</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>tamilpsd-0038.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>6324.psd</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0039.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>6323.psd</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>tamilpsd-0040.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>6322.psd</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0041.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6321.psd</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>tamilpsd-0042.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>6320.psd</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0043.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6319.psd</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tamilpsd-0044.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>6318.psd</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0045.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6317.psd</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tamilpsd-0046.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>6316.psd</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0047.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>6315.psd</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tamilpsd-0048.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>6314.psd</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0049.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6313.psd</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>tamilpsd-0050.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>6312.psd</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0051.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>6311.psd</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>tamilpsd-0052.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>6310.psd</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0053.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>6309.psd</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>tamilpsd-0054.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>6307.psd</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0055.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6306.psd</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>tamilpsd-0056.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>6305.psd</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0057.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6304.psd</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>tamilpsd-0058.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>6303.psd</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0059.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6302 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>tamilpsd-0060.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>6301 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0061.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6300 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>tamilpsd-0062.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>6299 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0063.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>6298 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>tamilpsd-0064.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>6297 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0065.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>6296 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>tamilpsd-0066.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>6295 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0067.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>6294 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>tamilpsd-0068.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>6293 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0069.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>6292 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>tamilpsd-0070.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>6291 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0071.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>6290 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>tamilpsd-0072.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>6289 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0073.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6288 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>tamilpsd-0074.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>6287 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0075.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>6286 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>tamilpsd-0076.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>6285 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0077.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6284 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>tamilpsd-0078.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>6283 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0079.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>6282 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>tamilpsd-0080.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>6281 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0081.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>6280 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>tamilpsd-0082.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>6279 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0083.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>6278 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>tamilpsd-0084.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>6277 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0085.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6276 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>tamilpsd-0086.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>6275 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0087.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>6274 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>tamilpsd-0088.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>6273 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0089.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>6272.psd</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>tamilpsd-0090.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>6271.psd</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0091.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>6270.psd</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>tamilpsd-0092.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>6269.psd</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0093.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>6268.psd</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>tamilpsd-0094.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>6267.psd</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0095.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>6266.psd</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>tamilpsd-0096.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>6265.psd</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0097.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>6264.psd</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>tamilpsd-0098.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>6263.psd</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0099.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>6262.psd</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>tamilpsd-0100.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>6261.psd</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0101.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>6260.psd</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>tamilpsd-0102.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>6259.psd</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0103.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>6258.psd</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>tamilpsd-0104.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>6257.psd</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0105.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>6256.psd</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>tamilpsd-0106.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>6255.psd</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0107.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>6254.psd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>tamilpsd-0108.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>6253.psd</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0109.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>6252.psd</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>tamilpsd-0110.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>6251.psd</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0111.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>6250.psd</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>tamilpsd-0112.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>6249.psd</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0113.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>6248.psd</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>tamilpsd-0114.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>6247.psd</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0115.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>6246.psd</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>tamilpsd-0116.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>6245.psd</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0117.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1854,6 +1854,30 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>6244.psd</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>tamilpsd-0118.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>6243.psd</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0119.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1878,6 +1878,1578 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>6242.psd</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>tamilpsd-0120.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>6241.psd</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0121.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>6240.psd</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>tamilpsd-0122.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>6239.psd</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0123.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>6238.psd</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>tamilpsd-0124.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>6237.psd</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0125.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>6236.psd</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>tamilpsd-0126.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>6235.psd</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0127.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>6234.psd</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>tamilpsd-0128.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>6233.psd</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0129.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>6232.psd</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>tamilpsd-0130.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>6231.psd</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0131.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>6230.psd</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>tamilpsd-0132.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>6229.psd</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0133.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>6228.psd</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>tamilpsd-0134.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>6227.psd</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0135.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>6226.psd</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>tamilpsd-0136.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>6225.psd</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0137.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>6224.psd</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>tamilpsd-0138.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>6223.psd</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0139.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>6222.psd</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>tamilpsd-0140.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>6221.psd</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0141.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>6220.psd</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>tamilpsd-0142.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>6219.psd</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0143.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>6218.psd</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>tamilpsd-0144.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>6217.psd</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0145.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>6216.psd</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>tamilpsd-0146.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>6215.psd</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0147.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>6214.psd</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>tamilpsd-0148.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>6213.psd</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0149.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>6212.psd</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>tamilpsd-0150.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>6211.psd</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0151.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>6210.psd</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>tamilpsd-0152.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>6209.psd</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0153.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>6208.psd</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>tamilpsd-0154.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>6207.psd</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0155.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>6206.psd</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>tamilpsd-0156.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>6205.psd</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0157.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>6203.psd</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>tamilpsd-0158.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>6202.psd</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0159.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>6201.psd</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>tamilpsd-0160.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>6200.psd</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0161.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>6199.psd</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>tamilpsd-0162.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>6198.psd</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0163.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>6197.psd</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>tamilpsd-0164.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>6196.psd</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0165.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>6195.psd</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>tamilpsd-0166.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>6194.psd</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0167.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>6193.psd</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>tamilpsd-0168.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>6192  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0169.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>6188  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>tamilpsd-0170.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>6187  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0171.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>6185  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>tamilpsd-0172.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>6184  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0173.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>6183 This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>tamilpsd-0174.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>6240  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0175.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>6344.psd</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>tamilpsd-0176.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>6343.psd</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0177.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>6308.psd</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>tamilpsd-0178.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>6302.psd</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0179.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>6301.psd</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>tamilpsd-0180.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>6299.psd</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0181.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>6298.psd</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>tamilpsd-0182.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>6297.psd</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0183.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>6296.psd</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>tamilpsd-0184.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>6295.psd</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0185.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>6294.psd</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>tamilpsd-0186.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>6293.psd</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0187.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>6292.psd</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>tamilpsd-0188.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>6291.psd</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0189.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>6290.psd</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>tamilpsd-0190.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>6289.psd</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0191.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>6288.psd</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>tamilpsd-0192.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>6287.psd</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0193.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>6286.psd</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>tamilpsd-0194.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>6285.psd</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0195.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>6284.psd</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>tamilpsd-0196.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>6283.psd</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0197.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>6282.psd</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>tamilpsd-0198.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>6281.psd</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0199.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>6280.psd</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>tamilpsd-0200.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>6279.psd</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0201.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>6278.psd</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>tamilpsd-0202.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>6277.psd</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0203.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>6205a.psd</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>tamilpsd-0204.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>6191.psd</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0205.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>6190.psd</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>tamilpsd-0206.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>6189.psd</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0207.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>6186.psd</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>tamilpsd-0208.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>6198 This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0209.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>6182.psd</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>tamilpsd-0210.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>6181.psd</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0211.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>6180.psd</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>tamilpsd-0212.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>6179.psd</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0213.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>6178.psd</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>tamilpsd-0214.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>6177.psd</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0215.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>6176.psd</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>tamilpsd-0216.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>6175.psd</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0217.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>6174.psd</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>tamilpsd-0218.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>6173.psd</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0219.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>6172.psd</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>tamilpsd-0220.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>6171.psd</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0221.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>6170.psd</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>tamilpsd-0222.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>6169.psd</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0223.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>6168.psd</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>tamilpsd-0224.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>6167.psd</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0225.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>6166.psd</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>tamilpsd-0226.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>6165.psd</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0227.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>6164.psd</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>tamilpsd-0228.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>6163.psd</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0229.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>6162.psd</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>tamilpsd-0230.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>6161.psd</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0231.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>6160.psd</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>tamilpsd-0232.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>6159.psd</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0233.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>6158.psd</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>tamilpsd-0234.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>6157.psd</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0235.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>6156.psd</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>tamilpsd-0236.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>6155.psd</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0237.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>6154.psd</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>tamilpsd-0238.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>6153.psd</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0239.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>6142.psd</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>tamilpsd-0240.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>6141.psd</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0241.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>6140.psd</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>tamilpsd-0242.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>6139.psd</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0243.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>6138.psd</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>tamilpsd-0244.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>6137.psd</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0245.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>6136.psd</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>tamilpsd-0246.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>6135.psd</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0247.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>6134.psd</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>tamilpsd-0248.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>6133.psd</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0249.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>6132.psd</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>tamilpsd-0250.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3450,6 +3450,1206 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>6131.psd</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0252.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>6130.psd</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>tamilpsd-0253.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>6129.psd</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0254.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>6128.psd</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>tamilpsd-0255.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>6127.psd</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0256.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>6126.psd</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>tamilpsd-0257.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>6125.psd</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0258.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>6124.psd</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>tamilpsd-0259.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>6123.psd</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0260.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>6122.psd</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>tamilpsd-0261.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>6121.psd</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0262.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>6120.psd</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>tamilpsd-0263.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>6119.psd</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0264.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>6118.psd</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>tamilpsd-0265.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>6117.psd</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0266.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>6107.psd</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>tamilpsd-0267.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>6106.psd</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0268.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>6105.psd</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>tamilpsd-0269.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>6104.psd</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0270.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>6103.psd</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>tamilpsd-0271.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>6102.psd</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0272.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>6101.psd</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>tamilpsd-0273.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>6100.psd</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0274.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>6099.psd</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>tamilpsd-0275.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>6098.psd</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0276.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>6097.psd</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>tamilpsd-0277.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>6096.psd</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0278.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>6095.psd</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>tamilpsd-0279.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>6094.psd</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0280.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>6093.psd</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>tamilpsd-0281.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>6092.psd</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0282.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>6091.psd</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>tamilpsd-0283.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>6090.psd</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0284.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>6089.psd</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>tamilpsd-0285.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>6088.psd</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0286.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>6087.psd</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>tamilpsd-0287.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>6086.psd</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0288.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>6085.psd</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>tamilpsd-0289.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>6084.psd</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0290.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>6083.psd</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>tamilpsd-0291.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>6082.psd</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0292.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>6081.psd</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>tamilpsd-0293.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>6080.psd</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0294.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>6079.psd</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>tamilpsd-0295.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>6078.psd</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0296.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>6077.psd</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>tamilpsd-0297.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>6076.psd</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0298.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>6075.psd</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>tamilpsd-0299.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>6074.psd</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0300.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>6073.psd</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>tamilpsd-0301.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>6072.psd</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0302.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>6071.psd</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>tamilpsd-0303.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>6070.psd</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0304.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>6069.psd</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>tamilpsd-0305.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>6068.psd</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0306.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>6067.psd</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>tamilpsd-0307.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>6066.psd</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0308.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>6065.psd</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>tamilpsd-0309.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>6064.psd</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0310.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>6063.psd</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>tamilpsd-0311.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>6062.psd</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0312.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>6060.psd</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>tamilpsd-0313.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>6061.psd</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0314.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>6059.psd</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>tamilpsd-0315.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>6058.psd</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0316.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>6057.psd</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>tamilpsd-0317.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>6056.psd</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0318.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>6055.psd</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>tamilpsd-0319.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>6054.psd</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0320.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>6053.psd</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>tamilpsd-0321.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>6052.psd</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0322.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>6051.psd</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>tamilpsd-0323.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>6050.psd</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0324.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>6049.psd</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>tamilpsd-0325.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>6048.psd</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0326.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>6047.psd</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>tamilpsd-0327.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>6046.psd</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0328.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>6045.psd</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>tamilpsd-0329.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>6044.psd</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0330.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>6043.psd</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>tamilpsd-0331.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>6042.psd</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0332.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>6041.psd</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>tamilpsd-0333.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>6040.psd</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0334.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>6039.psd</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>tamilpsd-0335.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>6038.psd</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0336.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>6037.psd</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>tamilpsd-0337.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>6036.psd</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0338.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>6035.psd</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>tamilpsd-0339.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>6034.psd</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0340.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>6033.psd</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>tamilpsd-0341.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>6032.psd</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0342.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>6031.psd</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>tamilpsd-0343.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>6030.psd</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0344.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>6029.psd</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>tamilpsd-0345.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>6028.psd</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0346.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>6027.psd</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>tamilpsd-0347.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>6026.psd</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0348.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>6025.psd</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>tamilpsd-0349.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>6024.psd</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0350.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>6023.psd</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>tamilpsd-0351.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,30 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6362.psd</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0402.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6361.psd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tamilpsd-0403.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,126 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6360.psd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0404.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6359.psd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tamilpsd-0405.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6358.psd</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0406.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6357.psd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tamilpsd-0407.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6356.psd</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0408.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6355.psd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>tamilpsd-0409.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6354.psd</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0410.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6353.psd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>tamilpsd-0411.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6352.psd</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0412.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6351.psd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>tamilpsd-0413.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,30 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6350.psd</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0414.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6349.psd</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tamilpsd-0415.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -642,6 +642,234 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6348.psd</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0815.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6347.psd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>tamilpsd-0816.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>6346.psd</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0817.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6345.psd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>tamilpsd-0818.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>6342.psd</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0819.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6341.psd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>tamilpsd-0820.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>6340.psd</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0821.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6339.psd</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>tamilpsd-0822.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>6338.psd</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0823.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6337.psd</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>tamilpsd-0824.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>6336.psd</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0825.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6335.psd</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>tamilpsd-0826.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>6334.psd</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0827.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6333.psd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>tamilpsd-0828.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>6332.psd</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0829.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6331.psd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>tamilpsd-0830.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>6330.psd</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0831.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6329.psd</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>tamilpsd-0832.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>6328.psd</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>tamilpsd-0833.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -1,55 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guru - 1\Downloads\backend-sample-main\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED35C7D7-3DB3-488C-9625-8B6104CA600A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rename Log" sheetId="1" r:id="rId1"/>
+    <sheet name="Rename Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>Original File Name</t>
-  </si>
-  <si>
-    <t>Renamed File Name</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -62,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,26 +66,86 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -384,93 +433,1301 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B136"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Original File Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Renamed File Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6327.psd</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>tamilpsd-0001.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>6326.psd</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0002.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6325.psd</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>tamilpsd-0003.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>6324.psd</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0004.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>6323.psd</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>tamilpsd-0005.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>6322.psd</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0006.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6321.psd</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>tamilpsd-0007.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>6320.psd</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0008.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6319.psd</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tamilpsd-0009.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>6318.psd</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0010.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6317.psd</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tamilpsd-0011.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>6316.psd</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0012.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>6315.psd</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tamilpsd-0013.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>6314.psd</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0014.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6313.psd</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>tamilpsd-0015.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>6312.psd</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0016.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>6311.psd</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>tamilpsd-0017.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>6310.psd</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0018.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>6309.psd</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>tamilpsd-0019.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>6307.psd</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0020.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6306.psd</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>tamilpsd-0021.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>6305.psd</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0022.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6304.psd</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>tamilpsd-0023.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>6303.psd</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0024.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6302 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>tamilpsd-0025.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>6301 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0026.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6300 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>tamilpsd-0027.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>6299 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0028.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>6298 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>tamilpsd-0029.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>6297 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0030.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>6296 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>tamilpsd-0031.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>6295 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0032.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>6294 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>tamilpsd-0033.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>6293 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0034.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>6292 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>tamilpsd-0035.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>6291 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0036.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>6290 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>tamilpsd-0037.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>6289 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0038.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6288 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>tamilpsd-0039.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>6287 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0040.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>6286 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>tamilpsd-0041.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>6285 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0042.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6284 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>tamilpsd-0043.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>6283 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0044.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>6282 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>tamilpsd-0045.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>6281 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0046.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>6280 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>tamilpsd-0047.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>6279 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0048.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>6278 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>tamilpsd-0049.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>6277 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0050.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6276 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>tamilpsd-0051.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>6275 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0052.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>6274 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>tamilpsd-0053.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>6273 - this file not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0054.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>6272.psd</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>tamilpsd-0055.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>6271.psd</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0056.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>6270.psd</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>tamilpsd-0057.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>6269.psd</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0058.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>6268.psd</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>tamilpsd-0059.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>6267.psd</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0060.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>6266.psd</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>tamilpsd-0061.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>6265.psd</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0062.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>6264.psd</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>tamilpsd-0063.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>6263.psd</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0064.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>6262.psd</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>tamilpsd-0065.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>6261.psd</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0066.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>6260.psd</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>tamilpsd-0067.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>6259.psd</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0068.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>6258.psd</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>tamilpsd-0069.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>6257.psd</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0070.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>6256.psd</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>tamilpsd-0071.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>6255.psd</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0072.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>6254.psd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>tamilpsd-0073.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>6253.psd</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0074.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>6252.psd</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>tamilpsd-0075.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>6251.psd</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0076.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>6250.psd</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>tamilpsd-0077.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>6249.psd</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0078.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>6248.psd</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>tamilpsd-0079.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>6247.psd</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0080.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>6246.psd</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>tamilpsd-0081.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>6245.psd</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0082.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>6244.psd</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>tamilpsd-0083.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>6243.psd</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0084.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>6242.psd</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>tamilpsd-0085.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>6241.psd</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0086.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>6240.psd</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>tamilpsd-0087.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>6239.psd</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0088.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>6238.psd</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>tamilpsd-0089.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>6237.psd</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0090.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>6236.psd</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>tamilpsd-0091.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>6235.psd</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0092.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>6234.psd</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>tamilpsd-0093.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>6233.psd</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0094.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>6232.psd</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>tamilpsd-0095.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>6231.psd</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0096.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>6230.psd</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>tamilpsd-0097.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>6229.psd</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0098.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>6228.psd</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>tamilpsd-0099.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>6227.psd</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0100.psd</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1729,6 +1729,4974 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>6226.psd</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>tamilpsd-0101.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>6225.psd</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0102.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>6224.psd</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>tamilpsd-0103.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>6223.psd</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0104.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>6222.psd</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>tamilpsd-0105.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>6221.psd</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0106.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>6220.psd</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>tamilpsd-0107.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>6219.psd</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0108.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>6218.psd</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>tamilpsd-0109.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>6217.psd</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0110.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>6216.psd</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>tamilpsd-0111.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>6215.psd</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0112.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>6214.psd</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>tamilpsd-0113.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>6213.psd</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0114.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>6212.psd</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>tamilpsd-0115.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>6211.psd</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0116.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>6210.psd</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>tamilpsd-0117.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>6209.psd</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0118.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>6208.psd</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>tamilpsd-0119.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>6207.psd</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0120.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>6206.psd</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>tamilpsd-0121.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>6205.psd</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0122.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>6203.psd</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>tamilpsd-0123.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>6202.psd</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0124.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>6201.psd</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>tamilpsd-0125.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>6200.psd</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0126.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>6199.psd</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>tamilpsd-0127.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>6198.psd</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0128.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>6197.psd</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>tamilpsd-0129.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>6196.psd</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0130.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>6195.psd</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>tamilpsd-0131.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>6194.psd</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0132.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>6193.psd</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>tamilpsd-0133.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>6192  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0134.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>6188  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>tamilpsd-0135.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>6187  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0136.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>6185  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>tamilpsd-0137.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>6184  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0138.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>6183 This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>tamilpsd-0139.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>6240  This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0140.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>6346.psd</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>tamilpsd-0141.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>6345.psd</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0142.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>6344.psd</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>tamilpsd-0143.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>6343.psd</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0144.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>6342.psd</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>tamilpsd-0145.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>6341.psd</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0146.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>6340.psd</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>tamilpsd-0147.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>6339.psd</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0148.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>6338.psd</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>tamilpsd-0149.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>6337.psd</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0150.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>6336.psd</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>tamilpsd-0151.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>6335.psd</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0152.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>6334.psd</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>tamilpsd-0153.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>6333.psd</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0154.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>6332.psd</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>tamilpsd-0155.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>6331.psd</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0156.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>6330.psd</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>tamilpsd-0157.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>6329.psd</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0158.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>6328.psd</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>tamilpsd-0159.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>6308.psd</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0160.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>6302.psd</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>tamilpsd-0161.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>6301.psd</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0162.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>6299.psd</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>tamilpsd-0163.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>6298.psd</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0164.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>6297.psd</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>tamilpsd-0165.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>6296.psd</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0166.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>6295.psd</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>tamilpsd-0167.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>6294.psd</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0168.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>6293.psd</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>tamilpsd-0169.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>6292.psd</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0170.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>6291.psd</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>tamilpsd-0171.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>6290.psd</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0172.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>6289.psd</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>tamilpsd-0173.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>6288.psd</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0174.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>6287.psd</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>tamilpsd-0175.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>6286.psd</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0176.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>6285.psd</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>tamilpsd-0177.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>6284.psd</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0178.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>6283.psd</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>tamilpsd-0179.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>6282.psd</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0180.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>6281.psd</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>tamilpsd-0181.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>6280.psd</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0182.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>6279.psd</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>tamilpsd-0183.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>6278.psd</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0184.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>6277.psd</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>tamilpsd-0185.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>6205a.psd</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0186.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>6191.psd</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>tamilpsd-0187.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>6190.psd</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0188.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>6189.psd</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>tamilpsd-0189.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>6186.psd</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0190.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>6198 This file is not suitable for photoshop 7.0 and cs3.psd</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>tamilpsd-0191.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>6182.psd</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0192.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>6181.psd</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>tamilpsd-0193.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>6180.psd</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0194.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>6179.psd</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>tamilpsd-0195.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>6178.psd</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0196.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>6177.psd</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>tamilpsd-0197.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>6176.psd</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0198.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>6175.psd</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>tamilpsd-0199.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>6174.psd</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0200.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>6173.psd</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>tamilpsd-0201.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>6172.psd</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0202.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>6171.psd</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>tamilpsd-0203.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>6170.psd</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0204.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>6169.psd</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>tamilpsd-0205.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>6168.psd</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0206.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>6167.psd</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>tamilpsd-0207.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>6166.psd</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0208.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>6165.psd</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>tamilpsd-0209.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>6164.psd</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0210.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>6163.psd</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>tamilpsd-0211.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>6162.psd</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0212.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>6161.psd</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>tamilpsd-0213.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>6160.psd</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0214.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>6159.psd</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>tamilpsd-0215.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>6158.psd</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0216.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>6157.psd</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>tamilpsd-0217.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>6156.psd</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0218.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>6155.psd</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>tamilpsd-0219.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>6154.psd</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0220.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>6153.psd</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>tamilpsd-0221.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>6142.psd</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0222.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>6141.psd</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>tamilpsd-0223.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>6140.psd</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0224.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>6139.psd</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>tamilpsd-0225.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>6138.psd</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0226.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>6137.psd</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>tamilpsd-0227.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>6136.psd</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0228.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>6135.psd</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>tamilpsd-0229.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>6134.psd</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0230.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>6133.psd</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>tamilpsd-0231.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>6132.psd</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0232.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>6131.psd</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>tamilpsd-0233.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>6130.psd</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0234.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>6129.psd</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>tamilpsd-0235.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>6128.psd</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0236.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>6127.psd</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>tamilpsd-0237.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>6126.psd</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0238.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>6125.psd</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>tamilpsd-0239.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>6124.psd</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0240.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>6123.psd</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>tamilpsd-0241.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>6122.psd</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0242.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>6121.psd</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>tamilpsd-0243.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>6120.psd</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0244.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>6119.psd</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>tamilpsd-0245.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>6118.psd</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0246.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>6117.psd</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>tamilpsd-0247.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>6107.psd</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0248.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>6106.psd</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>tamilpsd-0249.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>6105.psd</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0250.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>6104.psd</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>tamilpsd-0251.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>6103.psd</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0252.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>6102.psd</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>tamilpsd-0253.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>6101.psd</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0254.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>6100.psd</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>tamilpsd-0255.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>6099.psd</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0256.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>6098.psd</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>tamilpsd-0257.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>6097.psd</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0258.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>6096.psd</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>tamilpsd-0259.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>6095.psd</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0260.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>6094.psd</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>tamilpsd-0261.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>6093.psd</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0262.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>6092.psd</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>tamilpsd-0263.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>6091.psd</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0264.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>6090.psd</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>tamilpsd-0265.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>6089.psd</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0266.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>6088.psd</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>tamilpsd-0267.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>6087.psd</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0268.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>6086.psd</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>tamilpsd-0269.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>6085.psd</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0270.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>6084.psd</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>tamilpsd-0271.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>6083.psd</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0272.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>6082.psd</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>tamilpsd-0273.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>6081.psd</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0274.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>6080.psd</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>tamilpsd-0275.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>6079.psd</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0276.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>6078.psd</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>tamilpsd-0277.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>6077.psd</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0278.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>6076.psd</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>tamilpsd-0279.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>6075.psd</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0280.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>6074.psd</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>tamilpsd-0281.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>6073.psd</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0282.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>6072.psd</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>tamilpsd-0283.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>6071.psd</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0284.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>6070.psd</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>tamilpsd-0285.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>6069.psd</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0286.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>6068.psd</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>tamilpsd-0287.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>6067.psd</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0288.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>6066.psd</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>tamilpsd-0289.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>6065.psd</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0290.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>6064.psd</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>tamilpsd-0291.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>6063.psd</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0292.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>6062.psd</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>tamilpsd-0293.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>6060.psd</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0294.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>6061.psd</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>tamilpsd-0295.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>6059.psd</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0296.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>6058.psd</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>tamilpsd-0297.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>6057.psd</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0298.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>6056.psd</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>tamilpsd-0299.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>6055.psd</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0300.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>6054.psd</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>tamilpsd-0301.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>6053.psd</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0302.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>6052.psd</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>tamilpsd-0303.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>6051.psd</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0304.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>6050.psd</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>tamilpsd-0305.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>6049.psd</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0306.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>6048.psd</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>tamilpsd-0307.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>6047.psd</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0308.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>6046.psd</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>tamilpsd-0309.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>6045.psd</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0310.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>6044.psd</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>tamilpsd-0311.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>6043.psd</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0312.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>6042.psd</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>tamilpsd-0313.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>6041.psd</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0314.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>6040.psd</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>tamilpsd-0315.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>6039.psd</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0316.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>6038.psd</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>tamilpsd-0317.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>6037.psd</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0318.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>6036.psd</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>tamilpsd-0319.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>6035.psd</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0320.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>6034.psd</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>tamilpsd-0321.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>6033.psd</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0322.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>6032.psd</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>tamilpsd-0323.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>6031.psd</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0324.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>6030.psd</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>tamilpsd-0325.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>6029.psd</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0326.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>6028.psd</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>tamilpsd-0327.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>6027.psd</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0328.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>6026.psd</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>tamilpsd-0329.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>6025.psd</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0330.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>6024.psd</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>tamilpsd-0331.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>6023.psd</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0332.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>6022.psd</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>tamilpsd-0333.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t>6021.psd</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0334.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>6020.psd</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>tamilpsd-0335.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>6019.psd</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0336.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>6018.psd</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>tamilpsd-0337.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="3" t="inlineStr">
+        <is>
+          <t>6017.psd</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0338.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>6016.psd</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>tamilpsd-0339.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="3" t="inlineStr">
+        <is>
+          <t>6015.psd</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0340.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>6014.psd</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>tamilpsd-0341.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="3" t="inlineStr">
+        <is>
+          <t>6013.psd</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0342.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>6012.psd</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>tamilpsd-0343.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="3" t="inlineStr">
+        <is>
+          <t>6011.psd</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0344.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>6010.psd</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>tamilpsd-0345.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="3" t="inlineStr">
+        <is>
+          <t>6009.psd</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0346.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>6008.psd</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>tamilpsd-0347.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="3" t="inlineStr">
+        <is>
+          <t>6007.psd</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0348.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>6006.psd</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>tamilpsd-0349.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t>6005.psd</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0350.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>6004.psd</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>tamilpsd-0351.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>6003.psd</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0352.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>6002.psd</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>tamilpsd-0353.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t>6001.psd</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0354.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>6000.psd</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>tamilpsd-0355.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="inlineStr">
+        <is>
+          <t>5999.psd</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0356.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>5997.psd</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>tamilpsd-0357.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="3" t="inlineStr">
+        <is>
+          <t>5996.psd</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0358.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>5995.psd</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>tamilpsd-0359.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="3" t="inlineStr">
+        <is>
+          <t>5994.psd</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0360.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>5993.psd</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>tamilpsd-0361.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="inlineStr">
+        <is>
+          <t>5992.psd</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0362.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>5991.psd</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>tamilpsd-0363.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="3" t="inlineStr">
+        <is>
+          <t>5990.psd</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0364.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>5989.psd</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>tamilpsd-0365.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>5988.psd</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0366.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>5987.psd</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>tamilpsd-0367.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>5986.psd</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0368.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>5985.psd</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>tamilpsd-0369.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t>5983.psd</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0370.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>5982.psd</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>tamilpsd-0371.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t>5981.psd</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0372.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>5980.psd</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>tamilpsd-0373.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="3" t="inlineStr">
+        <is>
+          <t>5979.psd</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0374.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>5978.psd</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>tamilpsd-0375.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t>5977.psd</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0376.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>5976.psd</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>tamilpsd-0377.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="3" t="inlineStr">
+        <is>
+          <t>5975.psd</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0378.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>5974.psd</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>tamilpsd-0379.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="3" t="inlineStr">
+        <is>
+          <t>5973.psd</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0380.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>5972.psd</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>tamilpsd-0381.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="3" t="inlineStr">
+        <is>
+          <t>5971.psd</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0382.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>5970.psd</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>tamilpsd-0383.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="3" t="inlineStr">
+        <is>
+          <t>5969.psd</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0384.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>5968.psd</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>tamilpsd-0385.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="3" t="inlineStr">
+        <is>
+          <t>5967.psd</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0386.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>5966.psd</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>tamilpsd-0387.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="3" t="inlineStr">
+        <is>
+          <t>5965.psd</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0388.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>5964.psd</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>tamilpsd-0389.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="3" t="inlineStr">
+        <is>
+          <t>5963.psd</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0390.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>5962.psd</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>tamilpsd-0391.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="3" t="inlineStr">
+        <is>
+          <t>5961.psd</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0392.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>5960.psd</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>tamilpsd-0393.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="3" t="inlineStr">
+        <is>
+          <t>5959.psd</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0394.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>5958.psd</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>tamilpsd-0395.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="3" t="inlineStr">
+        <is>
+          <t>5957.psd</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0396.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>5956.psd</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>tamilpsd-0397.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="3" t="inlineStr">
+        <is>
+          <t>5955.psd</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0398.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>5954.psd</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>tamilpsd-0399.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>5953.psd</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0400.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>5952.psd</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>tamilpsd-0401.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="3" t="inlineStr">
+        <is>
+          <t>5951.psd</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0402.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>5950.psd</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>tamilpsd-0403.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="3" t="inlineStr">
+        <is>
+          <t>5949.psd</t>
+        </is>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0404.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>5948.psd</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>tamilpsd-0405.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="3" t="inlineStr">
+        <is>
+          <t>5947.psd</t>
+        </is>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0406.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>5945.psd</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>tamilpsd-0407.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="3" t="inlineStr">
+        <is>
+          <t>5944.psd</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0408.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>5943.psd</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>tamilpsd-0409.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="3" t="inlineStr">
+        <is>
+          <t>5942.psd</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0410.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>5941.psd</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>tamilpsd-0411.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="3" t="inlineStr">
+        <is>
+          <t>5940.psd</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0412.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>5939.psd</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>tamilpsd-0413.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="3" t="inlineStr">
+        <is>
+          <t>5938.psd</t>
+        </is>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0414.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>5937.psd</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>tamilpsd-0415.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="3" t="inlineStr">
+        <is>
+          <t>5936.psd</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0416.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>5935.psd</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>tamilpsd-0417.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="3" t="inlineStr">
+        <is>
+          <t>5934.psd</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0418.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>5933.psd</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>tamilpsd-0419.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="3" t="inlineStr">
+        <is>
+          <t>5932.psd</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0420.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>5930.psd</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>tamilpsd-0421.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="3" t="inlineStr">
+        <is>
+          <t>5931.psd</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0422.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>5929.psd</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>tamilpsd-0423.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="3" t="inlineStr">
+        <is>
+          <t>5927.psd</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0424.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>5928.psd</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>tamilpsd-0425.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="3" t="inlineStr">
+        <is>
+          <t>5924.psd</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0426.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>5925.psd</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>tamilpsd-0427.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="3" t="inlineStr">
+        <is>
+          <t>5926.psd</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0428.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>5922.psd</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>tamilpsd-0429.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="3" t="inlineStr">
+        <is>
+          <t>5923.psd</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0430.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>5921.psd</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>tamilpsd-0431.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="3" t="inlineStr">
+        <is>
+          <t>5920.psd</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0432.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>5919.psd</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>tamilpsd-0433.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="3" t="inlineStr">
+        <is>
+          <t>5918.psd</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0434.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>5917.psd</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>tamilpsd-0435.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="3" t="inlineStr">
+        <is>
+          <t>5916.psd</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0436.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>5915.psd</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>tamilpsd-0437.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="3" t="inlineStr">
+        <is>
+          <t>5914.psd</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0438.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>5912.psd</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>tamilpsd-0439.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="3" t="inlineStr">
+        <is>
+          <t>5911.psd</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0440.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>5910.psd</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>tamilpsd-0441.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="3" t="inlineStr">
+        <is>
+          <t>5913.psd</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0442.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>5907.psd</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>tamilpsd-0443.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="3" t="inlineStr">
+        <is>
+          <t>5908.psd</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0444.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>5909.psd</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>tamilpsd-0445.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="3" t="inlineStr">
+        <is>
+          <t>5904.psd</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0446.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>5906.psd</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>tamilpsd-0447.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="3" t="inlineStr">
+        <is>
+          <t>5905.psd</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0448.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>5903.psd</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>tamilpsd-0449.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="3" t="inlineStr">
+        <is>
+          <t>5902.psd</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0450.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>5901.psd</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>tamilpsd-0451.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="3" t="inlineStr">
+        <is>
+          <t>5900.psd</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0452.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>5899.psd</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>tamilpsd-0453.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="3" t="inlineStr">
+        <is>
+          <t>5897.psd</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0454.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>5898.psd</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>tamilpsd-0455.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="3" t="inlineStr">
+        <is>
+          <t>5896.psd</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0456.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>5894.psd</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>tamilpsd-0457.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="3" t="inlineStr">
+        <is>
+          <t>5895.psd</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0458.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>5893.psd</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>tamilpsd-0459.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="3" t="inlineStr">
+        <is>
+          <t>5891.psd</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0460.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>5892.psd</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>tamilpsd-0461.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="3" t="inlineStr">
+        <is>
+          <t>5890.psd</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0462.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>5888.psd</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>tamilpsd-0463.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="3" t="inlineStr">
+        <is>
+          <t>5889.psd</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0464.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>5886.psd</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>tamilpsd-0465.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="3" t="inlineStr">
+        <is>
+          <t>5887.psd</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0466.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>5882.psd</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>tamilpsd-0467.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="3" t="inlineStr">
+        <is>
+          <t>5885.psd</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0468.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>5883.psd</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>tamilpsd-0469.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="3" t="inlineStr">
+        <is>
+          <t>5884.psd</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0470.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>5876.psd</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>tamilpsd-0471.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="3" t="inlineStr">
+        <is>
+          <t>5881.psd</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0472.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>5880.psd</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>tamilpsd-0473.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="3" t="inlineStr">
+        <is>
+          <t>5879.psd</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0474.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>5878.psd</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>tamilpsd-0475.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="3" t="inlineStr">
+        <is>
+          <t>5877.psd</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0476.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>5874.psd</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>tamilpsd-0477.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="3" t="inlineStr">
+        <is>
+          <t>5873.psd</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0478.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>5875.psd</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>tamilpsd-0479.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="3" t="inlineStr">
+        <is>
+          <t>5872.psd</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0480.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>5863.psd</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>tamilpsd-0481.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="3" t="inlineStr">
+        <is>
+          <t>5866.psd</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0482.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>5864.psd</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>tamilpsd-0483.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="3" t="inlineStr">
+        <is>
+          <t>5871.psd</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0484.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>5870.psd</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>tamilpsd-0485.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="3" t="inlineStr">
+        <is>
+          <t>5868.psd</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0486.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>5867.psd</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>tamilpsd-0487.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="3" t="inlineStr">
+        <is>
+          <t>5865.psd</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0488.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>5869.psd</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>tamilpsd-0489.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="3" t="inlineStr">
+        <is>
+          <t>5857.psd</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0490.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>5859.psd</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>tamilpsd-0491.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="3" t="inlineStr">
+        <is>
+          <t>5862.psd</t>
+        </is>
+      </c>
+      <c r="B528" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0492.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>5861.psd</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>tamilpsd-0493.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="3" t="inlineStr">
+        <is>
+          <t>5860.psd</t>
+        </is>
+      </c>
+      <c r="B530" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0494.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>5858.psd</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>tamilpsd-0495.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="3" t="inlineStr">
+        <is>
+          <t>5851.psd</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0496.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>5852.psd</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>tamilpsd-0497.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="3" t="inlineStr">
+        <is>
+          <t>5853.psd</t>
+        </is>
+      </c>
+      <c r="B534" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0498.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>5850.psd</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>tamilpsd-0499.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="3" t="inlineStr">
+        <is>
+          <t>5854.psd</t>
+        </is>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0500.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>5855.psd</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>tamilpsd-0501.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="3" t="inlineStr">
+        <is>
+          <t>5856.psd</t>
+        </is>
+      </c>
+      <c r="B538" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0502.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>5848.psd</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>tamilpsd-0503.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="3" t="inlineStr">
+        <is>
+          <t>5849.psd</t>
+        </is>
+      </c>
+      <c r="B540" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0504.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>5846.psd</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>tamilpsd-0505.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="3" t="inlineStr">
+        <is>
+          <t>5847.psd</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0506.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>5845.psd</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>tamilpsd-0507.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="3" t="inlineStr">
+        <is>
+          <t>5843.psd</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0508.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>5842.psd</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>tamilpsd-0509.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="3" t="inlineStr">
+        <is>
+          <t>5840.psd</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0510.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>5838.psd</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>tamilpsd-0511.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="3" t="inlineStr">
+        <is>
+          <t>5839.psd</t>
+        </is>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0512.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>5837.psd</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>tamilpsd-0513.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="3" t="inlineStr">
+        <is>
+          <t>5841.psd</t>
+        </is>
+      </c>
+      <c r="B550" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0514.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B550"/>
+  <dimension ref="A1:B1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6697,6 +6697,6378 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>5836.psd</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>tamilpsd-0515.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="3" t="inlineStr">
+        <is>
+          <t>5835.psd</t>
+        </is>
+      </c>
+      <c r="B552" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0516.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>5833.psd</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>tamilpsd-0517.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="3" t="inlineStr">
+        <is>
+          <t>5829.psd</t>
+        </is>
+      </c>
+      <c r="B554" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0518.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>5831.psd</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>tamilpsd-0519.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="3" t="inlineStr">
+        <is>
+          <t>5830.psd</t>
+        </is>
+      </c>
+      <c r="B556" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0520.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>5832.psd</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>tamilpsd-0521.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="3" t="inlineStr">
+        <is>
+          <t>5828.psd</t>
+        </is>
+      </c>
+      <c r="B558" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0522.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>5827.psd</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>tamilpsd-0523.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="3" t="inlineStr">
+        <is>
+          <t>5826.psd</t>
+        </is>
+      </c>
+      <c r="B560" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0524.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>5824.psd</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>tamilpsd-0525.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="3" t="inlineStr">
+        <is>
+          <t>5825.psd</t>
+        </is>
+      </c>
+      <c r="B562" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0526.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>5823.psd</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>tamilpsd-0527.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="3" t="inlineStr">
+        <is>
+          <t>5821.psd</t>
+        </is>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0528.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>5822.psd</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>tamilpsd-0529.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="3" t="inlineStr">
+        <is>
+          <t>5818.psd</t>
+        </is>
+      </c>
+      <c r="B566" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0530.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>5817.psd</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>tamilpsd-0531.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="3" t="inlineStr">
+        <is>
+          <t>5819.psd</t>
+        </is>
+      </c>
+      <c r="B568" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0532.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>5815.psd</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>tamilpsd-0533.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="3" t="inlineStr">
+        <is>
+          <t>5816.psd</t>
+        </is>
+      </c>
+      <c r="B570" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0534.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>5814.psd</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>tamilpsd-0535.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="3" t="inlineStr">
+        <is>
+          <t>5813.psd</t>
+        </is>
+      </c>
+      <c r="B572" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0536.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>5812.psd</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>tamilpsd-0537.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="3" t="inlineStr">
+        <is>
+          <t>5810.psd</t>
+        </is>
+      </c>
+      <c r="B574" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0538.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>5808.psd</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>tamilpsd-0539.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="3" t="inlineStr">
+        <is>
+          <t>5809.psd</t>
+        </is>
+      </c>
+      <c r="B576" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0540.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>5807.psd</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>tamilpsd-0541.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="3" t="inlineStr">
+        <is>
+          <t>5811.psd</t>
+        </is>
+      </c>
+      <c r="B578" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0542.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>5801.psd</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>tamilpsd-0543.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="3" t="inlineStr">
+        <is>
+          <t>5805.psd</t>
+        </is>
+      </c>
+      <c r="B580" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0544.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>5802.psd</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>tamilpsd-0545.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="3" t="inlineStr">
+        <is>
+          <t>5803.psd</t>
+        </is>
+      </c>
+      <c r="B582" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0546.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>5806.psd</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>tamilpsd-0547.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="3" t="inlineStr">
+        <is>
+          <t>5804.psd</t>
+        </is>
+      </c>
+      <c r="B584" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0548.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>5800.psd</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>tamilpsd-0549.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="3" t="inlineStr">
+        <is>
+          <t>5798.psd</t>
+        </is>
+      </c>
+      <c r="B586" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0550.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>5799.psd</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>tamilpsd-0551.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="3" t="inlineStr">
+        <is>
+          <t>5797.psd</t>
+        </is>
+      </c>
+      <c r="B588" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0552.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>5796.psd</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>tamilpsd-0553.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="3" t="inlineStr">
+        <is>
+          <t>5793.psd</t>
+        </is>
+      </c>
+      <c r="B590" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0554.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>5795.psd</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>tamilpsd-0555.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="3" t="inlineStr">
+        <is>
+          <t>5794.psd</t>
+        </is>
+      </c>
+      <c r="B592" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0556.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>5792.psd</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>tamilpsd-0557.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="3" t="inlineStr">
+        <is>
+          <t>5791.psd</t>
+        </is>
+      </c>
+      <c r="B594" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0558.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>5790.psd</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>tamilpsd-0559.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="3" t="inlineStr">
+        <is>
+          <t>5946.psd</t>
+        </is>
+      </c>
+      <c r="B596" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0560.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>5789.psd</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>tamilpsd-0561.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="3" t="inlineStr">
+        <is>
+          <t>5788.psd</t>
+        </is>
+      </c>
+      <c r="B598" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0562.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>5787.psd</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>tamilpsd-0563.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="3" t="inlineStr">
+        <is>
+          <t>5786.psd</t>
+        </is>
+      </c>
+      <c r="B600" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0564.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>5785.psd</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>tamilpsd-0565.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="3" t="inlineStr">
+        <is>
+          <t>5784.psd</t>
+        </is>
+      </c>
+      <c r="B602" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0566.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>5783.psd</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>tamilpsd-0567.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="3" t="inlineStr">
+        <is>
+          <t>5782.psd</t>
+        </is>
+      </c>
+      <c r="B604" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0568.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>5781.psd</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>tamilpsd-0569.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="3" t="inlineStr">
+        <is>
+          <t>5780.psd</t>
+        </is>
+      </c>
+      <c r="B606" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0570.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>5778.psd</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>tamilpsd-0571.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="3" t="inlineStr">
+        <is>
+          <t>5777.psd</t>
+        </is>
+      </c>
+      <c r="B608" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0572.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>5776.psd</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>tamilpsd-0573.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="3" t="inlineStr">
+        <is>
+          <t>5775.psd</t>
+        </is>
+      </c>
+      <c r="B610" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0574.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>5774.psd</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>tamilpsd-0575.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="3" t="inlineStr">
+        <is>
+          <t>5773.psd</t>
+        </is>
+      </c>
+      <c r="B612" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0576.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>5772.psd</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>tamilpsd-0577.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="3" t="inlineStr">
+        <is>
+          <t>5771.psd</t>
+        </is>
+      </c>
+      <c r="B614" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0578.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>5770.psd</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>tamilpsd-0579.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="3" t="inlineStr">
+        <is>
+          <t>5769.psd</t>
+        </is>
+      </c>
+      <c r="B616" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0580.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>5768.psd</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>tamilpsd-0581.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="3" t="inlineStr">
+        <is>
+          <t>5767.PSD</t>
+        </is>
+      </c>
+      <c r="B618" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0582.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>5766.psd</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>tamilpsd-0583.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="3" t="inlineStr">
+        <is>
+          <t>5765.psd</t>
+        </is>
+      </c>
+      <c r="B620" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0584.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>5764.psd</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>tamilpsd-0585.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="3" t="inlineStr">
+        <is>
+          <t>5763.psd</t>
+        </is>
+      </c>
+      <c r="B622" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0586.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>5762.psd</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>tamilpsd-0587.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="3" t="inlineStr">
+        <is>
+          <t>5761.psd</t>
+        </is>
+      </c>
+      <c r="B624" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0588.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>5760.psd</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>tamilpsd-0589.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="3" t="inlineStr">
+        <is>
+          <t>5759.psd</t>
+        </is>
+      </c>
+      <c r="B626" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0590.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>5758.psd</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>tamilpsd-0591.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="3" t="inlineStr">
+        <is>
+          <t>5757.psd</t>
+        </is>
+      </c>
+      <c r="B628" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0592.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>5756.psd</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>tamilpsd-0593.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="3" t="inlineStr">
+        <is>
+          <t>5755.psd</t>
+        </is>
+      </c>
+      <c r="B630" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0594.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>5754.psd</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>tamilpsd-0595.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="3" t="inlineStr">
+        <is>
+          <t>5753.psd</t>
+        </is>
+      </c>
+      <c r="B632" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0596.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>5752.psd</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>tamilpsd-0597.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="3" t="inlineStr">
+        <is>
+          <t>5751.psd</t>
+        </is>
+      </c>
+      <c r="B634" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0598.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>5750.psd</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>tamilpsd-0599.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="3" t="inlineStr">
+        <is>
+          <t>5749.psd</t>
+        </is>
+      </c>
+      <c r="B636" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0600.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>5748.psd</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>tamilpsd-0601.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="3" t="inlineStr">
+        <is>
+          <t>5747.psd</t>
+        </is>
+      </c>
+      <c r="B638" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0602.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>5746.psd</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>tamilpsd-0603.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="3" t="inlineStr">
+        <is>
+          <t>5744.psd</t>
+        </is>
+      </c>
+      <c r="B640" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0604.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>5743.psd</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>tamilpsd-0605.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="3" t="inlineStr">
+        <is>
+          <t>5742.psd</t>
+        </is>
+      </c>
+      <c r="B642" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0606.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>5741.psd</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>tamilpsd-0607.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="3" t="inlineStr">
+        <is>
+          <t>5779.psd</t>
+        </is>
+      </c>
+      <c r="B644" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0608.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>5740.psd</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>tamilpsd-0609.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="3" t="inlineStr">
+        <is>
+          <t>5739.psd</t>
+        </is>
+      </c>
+      <c r="B646" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0610.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>5704.psd</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>tamilpsd-0611.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="3" t="inlineStr">
+        <is>
+          <t>5703.psd</t>
+        </is>
+      </c>
+      <c r="B648" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0612.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>5701.psd</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>tamilpsd-0613.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="3" t="inlineStr">
+        <is>
+          <t>5724.psd</t>
+        </is>
+      </c>
+      <c r="B650" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0614.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>5707.psd</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>tamilpsd-0615.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="3" t="inlineStr">
+        <is>
+          <t>5730.psd</t>
+        </is>
+      </c>
+      <c r="B652" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0616.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>5731.psd</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>tamilpsd-0617.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="3" t="inlineStr">
+        <is>
+          <t>5709.psd</t>
+        </is>
+      </c>
+      <c r="B654" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0618.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>5702.psd</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>tamilpsd-0619.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="3" t="inlineStr">
+        <is>
+          <t>5719.psd</t>
+        </is>
+      </c>
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0620.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>5732.psd</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>tamilpsd-0621.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="3" t="inlineStr">
+        <is>
+          <t>5728.psd</t>
+        </is>
+      </c>
+      <c r="B658" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0622.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>5718.psd</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>tamilpsd-0623.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="3" t="inlineStr">
+        <is>
+          <t>5706.psd</t>
+        </is>
+      </c>
+      <c r="B660" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0624.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>5717.psd</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>tamilpsd-0625.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="3" t="inlineStr">
+        <is>
+          <t>5727.psd</t>
+        </is>
+      </c>
+      <c r="B662" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0626.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>5705.psd</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>tamilpsd-0627.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="3" t="inlineStr">
+        <is>
+          <t>5726.psd</t>
+        </is>
+      </c>
+      <c r="B664" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0628.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>5712.psd</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>tamilpsd-0629.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="3" t="inlineStr">
+        <is>
+          <t>5737.psd</t>
+        </is>
+      </c>
+      <c r="B666" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0630.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>5738.psd</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>tamilpsd-0631.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="3" t="inlineStr">
+        <is>
+          <t>5725.psd</t>
+        </is>
+      </c>
+      <c r="B668" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0632.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>5710.psd</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>tamilpsd-0633.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="3" t="inlineStr">
+        <is>
+          <t>5733.psd</t>
+        </is>
+      </c>
+      <c r="B670" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0634.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>5729.psd</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>tamilpsd-0635.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="3" t="inlineStr">
+        <is>
+          <t>5735.psd</t>
+        </is>
+      </c>
+      <c r="B672" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0636.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>5723.psd</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>tamilpsd-0637.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="3" t="inlineStr">
+        <is>
+          <t>5714.psd</t>
+        </is>
+      </c>
+      <c r="B674" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0638.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>5716.psd</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>tamilpsd-0639.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="3" t="inlineStr">
+        <is>
+          <t>5708.psd</t>
+        </is>
+      </c>
+      <c r="B676" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0640.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>5734.psd</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>tamilpsd-0641.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="3" t="inlineStr">
+        <is>
+          <t>5715.psd</t>
+        </is>
+      </c>
+      <c r="B678" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0642.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>5722.psd</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>tamilpsd-0643.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="3" t="inlineStr">
+        <is>
+          <t>5736.psd</t>
+        </is>
+      </c>
+      <c r="B680" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0644.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>5700.psd</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>tamilpsd-0645.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="3" t="inlineStr">
+        <is>
+          <t>5713.psd</t>
+        </is>
+      </c>
+      <c r="B682" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0646.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>5720.psd</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>tamilpsd-0647.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="3" t="inlineStr">
+        <is>
+          <t>5721.psd</t>
+        </is>
+      </c>
+      <c r="B684" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0648.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>5684.psd</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>tamilpsd-0649.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="3" t="inlineStr">
+        <is>
+          <t>5691.psd</t>
+        </is>
+      </c>
+      <c r="B686" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0650.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>5689.psd</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>tamilpsd-0651.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="3" t="inlineStr">
+        <is>
+          <t>5686.psd</t>
+        </is>
+      </c>
+      <c r="B688" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0652.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>5672.psd</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>tamilpsd-0653.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="3" t="inlineStr">
+        <is>
+          <t>5692.psd</t>
+        </is>
+      </c>
+      <c r="B690" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0654.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>5678.psd</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>tamilpsd-0655.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="3" t="inlineStr">
+        <is>
+          <t>5696.psd</t>
+        </is>
+      </c>
+      <c r="B692" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0656.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>5681.psd</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>tamilpsd-0657.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="3" t="inlineStr">
+        <is>
+          <t>5697.psd</t>
+        </is>
+      </c>
+      <c r="B694" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0658.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>5677.psd</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>tamilpsd-0659.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="3" t="inlineStr">
+        <is>
+          <t>5682.psd</t>
+        </is>
+      </c>
+      <c r="B696" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0660.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>5698.psd</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>tamilpsd-0661.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="3" t="inlineStr">
+        <is>
+          <t>5694.psd</t>
+        </is>
+      </c>
+      <c r="B698" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0662.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>5695.psd</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>tamilpsd-0663.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="3" t="inlineStr">
+        <is>
+          <t>5687.psd</t>
+        </is>
+      </c>
+      <c r="B700" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0664.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>5685.psd</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>tamilpsd-0665.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="3" t="inlineStr">
+        <is>
+          <t>5675.psd</t>
+        </is>
+      </c>
+      <c r="B702" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0666.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>5693.psd</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>tamilpsd-0667.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="3" t="inlineStr">
+        <is>
+          <t>5680.psd</t>
+        </is>
+      </c>
+      <c r="B704" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0668.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>5688.psd</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>tamilpsd-0669.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="3" t="inlineStr">
+        <is>
+          <t>5674.psd</t>
+        </is>
+      </c>
+      <c r="B706" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0670.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>5690.psd</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>tamilpsd-0671.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="3" t="inlineStr">
+        <is>
+          <t>5673.psd</t>
+        </is>
+      </c>
+      <c r="B708" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0672.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>5683.psd</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>tamilpsd-0673.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="3" t="inlineStr">
+        <is>
+          <t>5699.psd</t>
+        </is>
+      </c>
+      <c r="B710" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0674.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>5676.psd</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>tamilpsd-0675.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="3" t="inlineStr">
+        <is>
+          <t>5671.psd</t>
+        </is>
+      </c>
+      <c r="B712" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0676.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>5679.psd</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>tamilpsd-0677.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="3" t="inlineStr">
+        <is>
+          <t>5657.psd</t>
+        </is>
+      </c>
+      <c r="B714" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0678.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>5663.psd</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>tamilpsd-0679.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="3" t="inlineStr">
+        <is>
+          <t>5661.psd</t>
+        </is>
+      </c>
+      <c r="B716" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0680.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>5652.psd</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>tamilpsd-0681.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="3" t="inlineStr">
+        <is>
+          <t>5665.psd</t>
+        </is>
+      </c>
+      <c r="B718" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0682.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>5659.psd</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>tamilpsd-0683.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="3" t="inlineStr">
+        <is>
+          <t>5668.psd</t>
+        </is>
+      </c>
+      <c r="B720" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0684.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>5666.psd</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>tamilpsd-0685.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="3" t="inlineStr">
+        <is>
+          <t>5664.psd</t>
+        </is>
+      </c>
+      <c r="B722" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0686.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>5655.psd</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>tamilpsd-0687.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="3" t="inlineStr">
+        <is>
+          <t>5653.psd</t>
+        </is>
+      </c>
+      <c r="B724" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0688.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>5670.psd</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>tamilpsd-0689.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="3" t="inlineStr">
+        <is>
+          <t>5669.psd</t>
+        </is>
+      </c>
+      <c r="B726" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0690.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>5654.psd</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>tamilpsd-0691.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="3" t="inlineStr">
+        <is>
+          <t>5662.psd</t>
+        </is>
+      </c>
+      <c r="B728" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0692.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>5667.psd</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>tamilpsd-0693.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="3" t="inlineStr">
+        <is>
+          <t>5656.psd</t>
+        </is>
+      </c>
+      <c r="B730" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0694.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>5658.psd</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>tamilpsd-0695.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="3" t="inlineStr">
+        <is>
+          <t>5660.psd</t>
+        </is>
+      </c>
+      <c r="B732" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0696.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>5651.psd</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>tamilpsd-0697.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="3" t="inlineStr">
+        <is>
+          <t>01 a copy.psd</t>
+        </is>
+      </c>
+      <c r="B734" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0698.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>01 copy.psd</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>tamilpsd-0699.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="3" t="inlineStr">
+        <is>
+          <t>01 a.psd</t>
+        </is>
+      </c>
+      <c r="B736" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0700.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>01.psd</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>tamilpsd-0702.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="3" t="inlineStr">
+        <is>
+          <t>02.psd</t>
+        </is>
+      </c>
+      <c r="B738" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0703.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>01a.psd</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>tamilpsd-0705.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="3" t="inlineStr">
+        <is>
+          <t>A4__Invi__Aaa.psd</t>
+        </is>
+      </c>
+      <c r="B740" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0706.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>A4__Invi__B.psd</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>tamilpsd-0707.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="3" t="inlineStr">
+        <is>
+          <t>B.psd</t>
+        </is>
+      </c>
+      <c r="B742" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0708.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>V.psd</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>tamilpsd-0709.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="3" t="inlineStr">
+        <is>
+          <t>Cover___A.psd</t>
+        </is>
+      </c>
+      <c r="B744" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0710.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Invi___A321.psd</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>tamilpsd-0711.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="3" t="inlineStr">
+        <is>
+          <t>Invi___B654.psd</t>
+        </is>
+      </c>
+      <c r="B746" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0712.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Invi__Bv.psd</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>tamilpsd-0713.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="3" t="inlineStr">
+        <is>
+          <t>invi___Av.psd</t>
+        </is>
+      </c>
+      <c r="B748" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0714.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>invi__A.psd</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>tamilpsd-0715.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="3" t="inlineStr">
+        <is>
+          <t>invi__B.psd</t>
+        </is>
+      </c>
+      <c r="B750" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0716.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>invi___A.psd</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>tamilpsd-0717.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="3" t="inlineStr">
+        <is>
+          <t>invi___B.psd</t>
+        </is>
+      </c>
+      <c r="B752" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0718.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Grown __Invi__BB.psd</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>tamilpsd-0719.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="3" t="inlineStr">
+        <is>
+          <t>Grown __Invi___AA.psd</t>
+        </is>
+      </c>
+      <c r="B754" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0720.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Crown__Invitation___300 GSM___Glossy Lamination___A copy.psd</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>tamilpsd-0721.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="3" t="inlineStr">
+        <is>
+          <t>Crown__Invitation___300 GSM___Glossy Lamination___B.psd</t>
+        </is>
+      </c>
+      <c r="B756" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0722.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>A4__Inviation___AA copy.psd</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>tamilpsd-0723.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="3" t="inlineStr">
+        <is>
+          <t>A4__Inviation___BBa.psd</t>
+        </is>
+      </c>
+      <c r="B758" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0724.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>A4__Inviation___AA.psd</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>tamilpsd-0725.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="3" t="inlineStr">
+        <is>
+          <t>A4__Inviation___BB.psd</t>
+        </is>
+      </c>
+      <c r="B760" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0726.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>A4__Inviation___A copyaa.psd</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>tamilpsd-0727.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="3" t="inlineStr">
+        <is>
+          <t>A4__Inviation___BA copy.psd</t>
+        </is>
+      </c>
+      <c r="B762" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0728.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>A4__Inviation___A copy.psd</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>tamilpsd-0729.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="3" t="inlineStr">
+        <is>
+          <t>A4__Inviation___BA.psd</t>
+        </is>
+      </c>
+      <c r="B764" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0730.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>A4__Invi__300 GSM__Glossy Lamination___800 Copies___A.psd</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>tamilpsd-0731.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="3" t="inlineStr">
+        <is>
+          <t>A4__Invi__300 GSM__Glossy Lamination___800 Copies___B.psd</t>
+        </is>
+      </c>
+      <c r="B766" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0732.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>A4__Invi - Copy.psd</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>tamilpsd-0733.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="3" t="inlineStr">
+        <is>
+          <t>A4__Invi__Bbb.psd</t>
+        </is>
+      </c>
+      <c r="B768" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0734.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>A4___A.psd</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>tamilpsd-0735.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="3" t="inlineStr">
+        <is>
+          <t>A4___B.psd</t>
+        </is>
+      </c>
+      <c r="B770" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0736.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>A3__Invi__300 GSM__Matt Lamination__1500 Copies___F&amp;B___A.psd</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>tamilpsd-0737.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="3" t="inlineStr">
+        <is>
+          <t>A3__Invi__300 GSM__Matt Lamination__1500 Copies___F&amp;B___B.psd</t>
+        </is>
+      </c>
+      <c r="B772" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0738.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>A3__Invi___AA copyAA.psd</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>tamilpsd-0739.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="3" t="inlineStr">
+        <is>
+          <t>A3__Invi___AA copyBB.psd</t>
+        </is>
+      </c>
+      <c r="B774" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0740.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>A4__Cover__Back Side___A.psd</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>tamilpsd-0741.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="3" t="inlineStr">
+        <is>
+          <t>A4__Cover___B.psd</t>
+        </is>
+      </c>
+      <c r="B776" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0742.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>A3___Invi___Af.psd</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>tamilpsd-0743.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi___Bf.psd</t>
+        </is>
+      </c>
+      <c r="B778" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0744.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>A3___Invi___aaa.psd</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>tamilpsd-0745.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi___Baaa.psd</t>
+        </is>
+      </c>
+      <c r="B780" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0746.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>A3___Invi___A.psd</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>tamilpsd-0747.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi___B.psd</t>
+        </is>
+      </c>
+      <c r="B782" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0748.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>A3___Invi___a copya.psd</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>tamilpsd-0749.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi___Bava.psd</t>
+        </is>
+      </c>
+      <c r="B784" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0750.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>A3___Invi___300  GSM___A.psd</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>tamilpsd-0751.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi___300  GSM___B.psd</t>
+        </is>
+      </c>
+      <c r="B786" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0752.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>A3___Invi____Glossy Lamination___300 GSM____500 Copies___A.psd</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>tamilpsd-0753.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi____Glossy Lamination___300 GSM____500 Copies___B.psd</t>
+        </is>
+      </c>
+      <c r="B788" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0754.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>A3___Invi____Ap.psd</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>tamilpsd-0755.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi____Bp.psd</t>
+        </is>
+      </c>
+      <c r="B790" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0756.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>A3___Invi____AAAAA.psd</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>tamilpsd-0757.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi____BBBB.psd</t>
+        </is>
+      </c>
+      <c r="B792" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0758.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>A3___Invi____A.psd</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>tamilpsd-0759.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="3" t="inlineStr">
+        <is>
+          <t>A3___Invi____B.psd</t>
+        </is>
+      </c>
+      <c r="B794" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0760.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>6544.psd</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>tamilpsd-0761.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="3" t="inlineStr">
+        <is>
+          <t>987.psd</t>
+        </is>
+      </c>
+      <c r="B796" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0762.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>0102.psd</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>tamilpsd-0763.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="3" t="inlineStr">
+        <is>
+          <t>0234.psd</t>
+        </is>
+      </c>
+      <c r="B798" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0764.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>54.psd</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>tamilpsd-0765.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="3" t="inlineStr">
+        <is>
+          <t>55.psd</t>
+        </is>
+      </c>
+      <c r="B800" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0766.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>22x8.5__Invi___Matt Lamination__300 GSM___A.psd</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>tamilpsd-0767.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="3" t="inlineStr">
+        <is>
+          <t>22x8.5__Invi___Matt Lamination__300 GSM___B.psd</t>
+        </is>
+      </c>
+      <c r="B802" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0768.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>22x8.5__Invi___300 GSM___Matt Lamination___700 Copies___F&amp;B___A.psd</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>tamilpsd-0769.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="3" t="inlineStr">
+        <is>
+          <t>22x8.5__Invi___300 GSM___Matt Lamination___700 Copies___F&amp;B___B.psd</t>
+        </is>
+      </c>
+      <c r="B804" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0770.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>22x8.5___Invi___Al.psd</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>tamilpsd-0771.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="3" t="inlineStr">
+        <is>
+          <t>22x8.5___Invi___Bl.psd</t>
+        </is>
+      </c>
+      <c r="B806" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0772.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>19x7___Grown Size___300 GSM___Matt Lamination___1000 Copies___F&amp;B___B.psd</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>tamilpsd-0773.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="3" t="inlineStr">
+        <is>
+          <t>19x7___invi Grown Size___300 GSM___Matt Lamination___1000 Copies___F&amp;B___A.psd</t>
+        </is>
+      </c>
+      <c r="B808" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0774.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>11x17__B.psd</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>tamilpsd-0775.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="3" t="inlineStr">
+        <is>
+          <t>11x17___A.psd</t>
+        </is>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0776.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>11x8.5___Ar.psd</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>tamilpsd-0777.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="3" t="inlineStr">
+        <is>
+          <t>11x8.5___B.psd</t>
+        </is>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0778.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>22x8.5a.psd</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>tamilpsd-0779.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="3" t="inlineStr">
+        <is>
+          <t>22x8.5b.psd</t>
+        </is>
+      </c>
+      <c r="B814" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0780.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>22x8.5 a (1).psd</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>tamilpsd-0781.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="3" t="inlineStr">
+        <is>
+          <t>22x8.5 a (2).psd</t>
+        </is>
+      </c>
+      <c r="B816" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0782.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>22x8.5 a.psd</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>tamilpsd-0783.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="3" t="inlineStr">
+        <is>
+          <t>22x8.5 b.psd</t>
+        </is>
+      </c>
+      <c r="B818" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0784.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>1x8___Al.psd</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>tamilpsd-0785.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="3" t="inlineStr">
+        <is>
+          <t>1x8___BA.psd</t>
+        </is>
+      </c>
+      <c r="B820" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0786.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>1x8___Aaal.psd</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>tamilpsd-0787.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="3" t="inlineStr">
+        <is>
+          <t>1x8___B.psd</t>
+        </is>
+      </c>
+      <c r="B822" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0788.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>8.5x5.5 a.psd</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>tamilpsd-0789.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="3" t="inlineStr">
+        <is>
+          <t>8.5x5.5 b.psd</t>
+        </is>
+      </c>
+      <c r="B824" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0790.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>8.5x5.5 Cover.psd</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>tamilpsd-0791.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="3" t="inlineStr">
+        <is>
+          <t>4668.psd</t>
+        </is>
+      </c>
+      <c r="B826" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0792.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>4667.psd</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>tamilpsd-0793.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="3" t="inlineStr">
+        <is>
+          <t>4666.psd</t>
+        </is>
+      </c>
+      <c r="B828" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0794.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>4665.psd</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>tamilpsd-0795.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="3" t="inlineStr">
+        <is>
+          <t>4664.psd</t>
+        </is>
+      </c>
+      <c r="B830" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0796.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>4663.psd</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>tamilpsd-0797.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="3" t="inlineStr">
+        <is>
+          <t>4662.psd</t>
+        </is>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0798.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>4661.psd</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>tamilpsd-0799.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="3" t="inlineStr">
+        <is>
+          <t>4660.psd</t>
+        </is>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0800.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>4659.psd</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>tamilpsd-0801.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="3" t="inlineStr">
+        <is>
+          <t>4658.psd</t>
+        </is>
+      </c>
+      <c r="B836" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0802.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>4657.psd</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>tamilpsd-0803.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="3" t="inlineStr">
+        <is>
+          <t>4656.psd</t>
+        </is>
+      </c>
+      <c r="B838" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0804.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>4655.psd</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>tamilpsd-0805.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="3" t="inlineStr">
+        <is>
+          <t>4654.psd</t>
+        </is>
+      </c>
+      <c r="B840" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0806.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>4653.psd</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>tamilpsd-0807.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="3" t="inlineStr">
+        <is>
+          <t>4652.psd</t>
+        </is>
+      </c>
+      <c r="B842" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0808.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>4651.psd</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>tamilpsd-0809.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="3" t="inlineStr">
+        <is>
+          <t>4650.psd</t>
+        </is>
+      </c>
+      <c r="B844" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0810.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>4649.psd</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>tamilpsd-0811.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="3" t="inlineStr">
+        <is>
+          <t>4648.psd</t>
+        </is>
+      </c>
+      <c r="B846" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0812.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>4647.psd</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>tamilpsd-0813.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="3" t="inlineStr">
+        <is>
+          <t>4646.psd</t>
+        </is>
+      </c>
+      <c r="B848" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0814.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>4645.psd</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>tamilpsd-0815.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="3" t="inlineStr">
+        <is>
+          <t>4640.psd</t>
+        </is>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0816.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>4639.psd</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>tamilpsd-0817.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="3" t="inlineStr">
+        <is>
+          <t>4641.psd</t>
+        </is>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0818.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>4643.psd</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>tamilpsd-0819.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="3" t="inlineStr">
+        <is>
+          <t>4642.psd</t>
+        </is>
+      </c>
+      <c r="B854" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0820.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>4644.psd</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>tamilpsd-0821.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="3" t="inlineStr">
+        <is>
+          <t>4638.psd</t>
+        </is>
+      </c>
+      <c r="B856" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0822.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>4634.psd</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>tamilpsd-0823.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="3" t="inlineStr">
+        <is>
+          <t>4635.psd</t>
+        </is>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0824.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>4633.psd</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>tamilpsd-0825.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="3" t="inlineStr">
+        <is>
+          <t>4632.psd</t>
+        </is>
+      </c>
+      <c r="B860" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0826.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>4637.psd</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>tamilpsd-0827.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="3" t="inlineStr">
+        <is>
+          <t>4636.psd</t>
+        </is>
+      </c>
+      <c r="B862" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0828.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>4631.psd</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>tamilpsd-0829.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="3" t="inlineStr">
+        <is>
+          <t>4630.psd</t>
+        </is>
+      </c>
+      <c r="B864" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0830.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>4628.psd</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>tamilpsd-0831.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="3" t="inlineStr">
+        <is>
+          <t>4623.psd</t>
+        </is>
+      </c>
+      <c r="B866" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0832.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>4626.psd</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>tamilpsd-0833.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="3" t="inlineStr">
+        <is>
+          <t>4629.psd</t>
+        </is>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0834.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>4625.psd</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>tamilpsd-0835.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="3" t="inlineStr">
+        <is>
+          <t>4627.psd</t>
+        </is>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0836.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>4624.psd</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>tamilpsd-0837.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="3" t="inlineStr">
+        <is>
+          <t>4622.psd</t>
+        </is>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0838.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>4621.psd</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>tamilpsd-0839.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="3" t="inlineStr">
+        <is>
+          <t>4620.psd</t>
+        </is>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0840.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>4619.psd</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>tamilpsd-0841.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="3" t="inlineStr">
+        <is>
+          <t>4618.psd</t>
+        </is>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0842.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>4617.psd</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>tamilpsd-0843.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="3" t="inlineStr">
+        <is>
+          <t>4616.psd</t>
+        </is>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0844.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>4615.psd</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>tamilpsd-0845.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="3" t="inlineStr">
+        <is>
+          <t>4613.psd</t>
+        </is>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0846.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>4614.psd</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>tamilpsd-0847.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="3" t="inlineStr">
+        <is>
+          <t>4612.psd</t>
+        </is>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0848.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>4610.psd</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>tamilpsd-0849.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="3" t="inlineStr">
+        <is>
+          <t>4611.psd</t>
+        </is>
+      </c>
+      <c r="B884" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0850.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>4609.psd</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>tamilpsd-0851.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="3" t="inlineStr">
+        <is>
+          <t>4607.psd</t>
+        </is>
+      </c>
+      <c r="B886" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0852.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>4608.psd</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>tamilpsd-0853.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="3" t="inlineStr">
+        <is>
+          <t>4605.psd</t>
+        </is>
+      </c>
+      <c r="B888" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0854.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>4606.psd</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>tamilpsd-0855.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="3" t="inlineStr">
+        <is>
+          <t>4604.psd</t>
+        </is>
+      </c>
+      <c r="B890" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0856.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>4601.psd</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>tamilpsd-0857.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="3" t="inlineStr">
+        <is>
+          <t>4603.psd</t>
+        </is>
+      </c>
+      <c r="B892" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0858.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>4602.psd</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>tamilpsd-0859.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="3" t="inlineStr">
+        <is>
+          <t>4599.psd</t>
+        </is>
+      </c>
+      <c r="B894" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0860.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>4600.psd</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>tamilpsd-0861.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="3" t="inlineStr">
+        <is>
+          <t>4597.psd</t>
+        </is>
+      </c>
+      <c r="B896" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0862.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>4598.psd</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>tamilpsd-0863.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="3" t="inlineStr">
+        <is>
+          <t>4596.psd</t>
+        </is>
+      </c>
+      <c r="B898" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0864.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>4590.psd</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>tamilpsd-0865.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="3" t="inlineStr">
+        <is>
+          <t>4592.psd</t>
+        </is>
+      </c>
+      <c r="B900" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0866.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>4594.psd</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>tamilpsd-0867.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="3" t="inlineStr">
+        <is>
+          <t>4595.psd</t>
+        </is>
+      </c>
+      <c r="B902" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0868.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>4593.psd</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>tamilpsd-0869.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="3" t="inlineStr">
+        <is>
+          <t>4588.psd</t>
+        </is>
+      </c>
+      <c r="B904" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0870.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>4591.psd</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>tamilpsd-0871.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="3" t="inlineStr">
+        <is>
+          <t>4589.psd</t>
+        </is>
+      </c>
+      <c r="B906" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0872.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>4587.psd</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>tamilpsd-0873.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="3" t="inlineStr">
+        <is>
+          <t>4585.psd</t>
+        </is>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0874.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>4586.psd</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>tamilpsd-0875.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="3" t="inlineStr">
+        <is>
+          <t>4584.psd</t>
+        </is>
+      </c>
+      <c r="B910" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0876.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>4581.psd</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>tamilpsd-0877.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="3" t="inlineStr">
+        <is>
+          <t>4583.psd</t>
+        </is>
+      </c>
+      <c r="B912" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0878.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>4582.psd</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>tamilpsd-0879.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="3" t="inlineStr">
+        <is>
+          <t>4579.psd</t>
+        </is>
+      </c>
+      <c r="B914" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0880.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>4580.psd</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>tamilpsd-0881.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="3" t="inlineStr">
+        <is>
+          <t>4578.psd</t>
+        </is>
+      </c>
+      <c r="B916" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0882.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>4575.psd</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>tamilpsd-0883.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="3" t="inlineStr">
+        <is>
+          <t>4574.psd</t>
+        </is>
+      </c>
+      <c r="B918" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0884.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>4576.psd</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>tamilpsd-0885.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="3" t="inlineStr">
+        <is>
+          <t>4577.psd</t>
+        </is>
+      </c>
+      <c r="B920" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0886.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>4572.psd</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>tamilpsd-0887.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="3" t="inlineStr">
+        <is>
+          <t>4573.psd</t>
+        </is>
+      </c>
+      <c r="B922" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0888.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>4571.psd</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>tamilpsd-0889.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="3" t="inlineStr">
+        <is>
+          <t>4570.psd</t>
+        </is>
+      </c>
+      <c r="B924" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0890.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>4566.psd</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>tamilpsd-0891.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="3" t="inlineStr">
+        <is>
+          <t>4568.psd</t>
+        </is>
+      </c>
+      <c r="B926" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0892.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>4567.psd</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>tamilpsd-0893.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="3" t="inlineStr">
+        <is>
+          <t>4569.psd</t>
+        </is>
+      </c>
+      <c r="B928" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0894.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>4564.psd</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>tamilpsd-0895.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="3" t="inlineStr">
+        <is>
+          <t>4562.psd</t>
+        </is>
+      </c>
+      <c r="B930" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0896.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>4563.psd</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>tamilpsd-0897.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="3" t="inlineStr">
+        <is>
+          <t>4560.psd</t>
+        </is>
+      </c>
+      <c r="B932" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0898.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>4565.psd</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>tamilpsd-0899.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="3" t="inlineStr">
+        <is>
+          <t>4561.psd</t>
+        </is>
+      </c>
+      <c r="B934" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0900.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>4559.psd</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>tamilpsd-0901.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="3" t="inlineStr">
+        <is>
+          <t>4558.psd</t>
+        </is>
+      </c>
+      <c r="B936" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0902.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>4557.psd</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>tamilpsd-0903.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="3" t="inlineStr">
+        <is>
+          <t>4556.psd</t>
+        </is>
+      </c>
+      <c r="B938" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0904.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>4555.psd</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>tamilpsd-0905.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="3" t="inlineStr">
+        <is>
+          <t>4541.psd</t>
+        </is>
+      </c>
+      <c r="B940" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0906.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>4543.psd</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>tamilpsd-0907.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="3" t="inlineStr">
+        <is>
+          <t>4542.psd</t>
+        </is>
+      </c>
+      <c r="B942" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0908.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>4544.psd</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>tamilpsd-0909.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="3" t="inlineStr">
+        <is>
+          <t>4539.psd</t>
+        </is>
+      </c>
+      <c r="B944" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0910.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>4540.psd</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>tamilpsd-0911.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="3" t="inlineStr">
+        <is>
+          <t>4536.psd</t>
+        </is>
+      </c>
+      <c r="B946" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0912.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>4538.psd</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>tamilpsd-0913.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="3" t="inlineStr">
+        <is>
+          <t>4535.psd</t>
+        </is>
+      </c>
+      <c r="B948" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0914.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>4533.psd</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>tamilpsd-0915.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="3" t="inlineStr">
+        <is>
+          <t>4537.psd</t>
+        </is>
+      </c>
+      <c r="B950" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0916.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>4532.psd</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>tamilpsd-0917.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="3" t="inlineStr">
+        <is>
+          <t>4529.psd</t>
+        </is>
+      </c>
+      <c r="B952" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0918.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>4527.psd</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>tamilpsd-0919.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="3" t="inlineStr">
+        <is>
+          <t>4530.psd</t>
+        </is>
+      </c>
+      <c r="B954" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0920.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>4528.psd</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>tamilpsd-0921.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="3" t="inlineStr">
+        <is>
+          <t>4531.psd</t>
+        </is>
+      </c>
+      <c r="B956" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0922.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>4526.psd</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>tamilpsd-0923.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="3" t="inlineStr">
+        <is>
+          <t>4523.psd</t>
+        </is>
+      </c>
+      <c r="B958" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0924.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>4525.psd</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>tamilpsd-0925.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="3" t="inlineStr">
+        <is>
+          <t>4524.psd</t>
+        </is>
+      </c>
+      <c r="B960" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0926.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>4520.psd</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>tamilpsd-0927.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="3" t="inlineStr">
+        <is>
+          <t>4522.psd</t>
+        </is>
+      </c>
+      <c r="B962" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0928.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>4521.psd</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>tamilpsd-0929.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="3" t="inlineStr">
+        <is>
+          <t>4519.psd</t>
+        </is>
+      </c>
+      <c r="B964" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0930.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>4518.psd</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>tamilpsd-0931.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="3" t="inlineStr">
+        <is>
+          <t>4517.psd</t>
+        </is>
+      </c>
+      <c r="B966" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0932.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>4516.psd</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>tamilpsd-0933.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="3" t="inlineStr">
+        <is>
+          <t>4515.psd</t>
+        </is>
+      </c>
+      <c r="B968" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0934.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>4514.psd</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>tamilpsd-0935.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="3" t="inlineStr">
+        <is>
+          <t>4513.psd</t>
+        </is>
+      </c>
+      <c r="B970" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0936.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>4512.psd</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>tamilpsd-0937.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="3" t="inlineStr">
+        <is>
+          <t>4511.psd</t>
+        </is>
+      </c>
+      <c r="B972" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0938.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>4510.psd</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>tamilpsd-0939.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="3" t="inlineStr">
+        <is>
+          <t>4509.psd</t>
+        </is>
+      </c>
+      <c r="B974" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0940.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>4508.psd</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>tamilpsd-0941.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="3" t="inlineStr">
+        <is>
+          <t>4507.psd</t>
+        </is>
+      </c>
+      <c r="B976" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0942.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>4506.psd</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>tamilpsd-0943.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="3" t="inlineStr">
+        <is>
+          <t>4505.psd</t>
+        </is>
+      </c>
+      <c r="B978" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0944.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>4504.psd</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>tamilpsd-0945.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="3" t="inlineStr">
+        <is>
+          <t>4503.psd</t>
+        </is>
+      </c>
+      <c r="B980" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0946.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>4502.psd</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>tamilpsd-0947.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="3" t="inlineStr">
+        <is>
+          <t>4501.psd</t>
+        </is>
+      </c>
+      <c r="B982" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0948.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>4500.psd</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>tamilpsd-0949.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="3" t="inlineStr">
+        <is>
+          <t>4499.psd</t>
+        </is>
+      </c>
+      <c r="B984" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0950.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>4498.psd</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>tamilpsd-0951.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="3" t="inlineStr">
+        <is>
+          <t>4497.psd</t>
+        </is>
+      </c>
+      <c r="B986" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0952.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>4496.psd</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>tamilpsd-0953.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="3" t="inlineStr">
+        <is>
+          <t>4495.psd</t>
+        </is>
+      </c>
+      <c r="B988" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0954.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>4494.psd</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>tamilpsd-0955.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="3" t="inlineStr">
+        <is>
+          <t>4492.psd</t>
+        </is>
+      </c>
+      <c r="B990" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0956.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>4493.psd</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>tamilpsd-0957.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="3" t="inlineStr">
+        <is>
+          <t>4488.psd</t>
+        </is>
+      </c>
+      <c r="B992" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0958.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>4486.psd</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>tamilpsd-0959.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="3" t="inlineStr">
+        <is>
+          <t>4487.psd</t>
+        </is>
+      </c>
+      <c r="B994" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0960.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>4485.psd</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>tamilpsd-0961.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="3" t="inlineStr">
+        <is>
+          <t>4491.psd</t>
+        </is>
+      </c>
+      <c r="B996" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0962.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>4489.psd</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>tamilpsd-0963.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="3" t="inlineStr">
+        <is>
+          <t>4490.psd</t>
+        </is>
+      </c>
+      <c r="B998" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0964.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>4484.psd</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>tamilpsd-0965.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="3" t="inlineStr">
+        <is>
+          <t>4481.psd</t>
+        </is>
+      </c>
+      <c r="B1000" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0966.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>4482.psd</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>tamilpsd-0967.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="3" t="inlineStr">
+        <is>
+          <t>4480.psd</t>
+        </is>
+      </c>
+      <c r="B1002" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0968.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>4483.psd</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>tamilpsd-0969.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="3" t="inlineStr">
+        <is>
+          <t>4479.psd</t>
+        </is>
+      </c>
+      <c r="B1004" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0970.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>4478.psd</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>tamilpsd-0971.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="3" t="inlineStr">
+        <is>
+          <t>4474.psd</t>
+        </is>
+      </c>
+      <c r="B1006" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0972.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>4476.psd</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>tamilpsd-0973.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="3" t="inlineStr">
+        <is>
+          <t>4475.psd</t>
+        </is>
+      </c>
+      <c r="B1008" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0974.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>4477.psd</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>tamilpsd-0975.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="3" t="inlineStr">
+        <is>
+          <t>4473.psd</t>
+        </is>
+      </c>
+      <c r="B1010" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0976.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>4472.psd</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>tamilpsd-0977.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="3" t="inlineStr">
+        <is>
+          <t>4471.psd</t>
+        </is>
+      </c>
+      <c r="B1012" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0978.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>4469.psd</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>tamilpsd-0979.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="3" t="inlineStr">
+        <is>
+          <t>4470.psd</t>
+        </is>
+      </c>
+      <c r="B1014" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0980.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>4468.psd</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>tamilpsd-0981.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="3" t="inlineStr">
+        <is>
+          <t>4467.psd</t>
+        </is>
+      </c>
+      <c r="B1016" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0982.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>4465.psd</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>tamilpsd-0983.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="3" t="inlineStr">
+        <is>
+          <t>4466.psd</t>
+        </is>
+      </c>
+      <c r="B1018" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0984.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>4464.psd</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>tamilpsd-0985.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="3" t="inlineStr">
+        <is>
+          <t>4462.psd</t>
+        </is>
+      </c>
+      <c r="B1020" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0986.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>4463.psd</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>tamilpsd-0987.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="3" t="inlineStr">
+        <is>
+          <t>4459.psd</t>
+        </is>
+      </c>
+      <c r="B1022" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0988.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>4460.psd</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>tamilpsd-0989.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="3" t="inlineStr">
+        <is>
+          <t>4458.psd</t>
+        </is>
+      </c>
+      <c r="B1024" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0990.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>4455.psd</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>tamilpsd-0991.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="3" t="inlineStr">
+        <is>
+          <t>4456.psd</t>
+        </is>
+      </c>
+      <c r="B1026" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0992.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>4457.psd</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>tamilpsd-0993.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="3" t="inlineStr">
+        <is>
+          <t>4454.psd</t>
+        </is>
+      </c>
+      <c r="B1028" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0994.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>4453.psd</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>tamilpsd-0995.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="3" t="inlineStr">
+        <is>
+          <t>4452.psd</t>
+        </is>
+      </c>
+      <c r="B1030" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0996.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>4451.psd</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>tamilpsd-0997.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="3" t="inlineStr">
+        <is>
+          <t>4450.psd</t>
+        </is>
+      </c>
+      <c r="B1032" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-0998.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>4448.psd</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>tamilpsd-0999.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="3" t="inlineStr">
+        <is>
+          <t>4449.psd</t>
+        </is>
+      </c>
+      <c r="B1034" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1000.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>4446.psd</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>tamilpsd-1001.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="3" t="inlineStr">
+        <is>
+          <t>4447.psd</t>
+        </is>
+      </c>
+      <c r="B1036" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1002.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>4445.psd</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>tamilpsd-1003.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="3" t="inlineStr">
+        <is>
+          <t>4443.psd</t>
+        </is>
+      </c>
+      <c r="B1038" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1004.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>4444.psd</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>tamilpsd-1005.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="3" t="inlineStr">
+        <is>
+          <t>4442.psd</t>
+        </is>
+      </c>
+      <c r="B1040" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1006.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>4441.psd</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>tamilpsd-1007.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="3" t="inlineStr">
+        <is>
+          <t>4440.psd</t>
+        </is>
+      </c>
+      <c r="B1042" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1008.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>4439.psd</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>tamilpsd-1009.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="3" t="inlineStr">
+        <is>
+          <t>4438.psd</t>
+        </is>
+      </c>
+      <c r="B1044" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1010.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>4437.psd</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>tamilpsd-1011.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="3" t="inlineStr">
+        <is>
+          <t>4436.psd</t>
+        </is>
+      </c>
+      <c r="B1046" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1012.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>4435.psd</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>tamilpsd-1013.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="3" t="inlineStr">
+        <is>
+          <t>4434.psd</t>
+        </is>
+      </c>
+      <c r="B1048" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1014.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>4432.psd</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>tamilpsd-1015.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="3" t="inlineStr">
+        <is>
+          <t>4433.psd</t>
+        </is>
+      </c>
+      <c r="B1050" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1016.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>4430 letters.psd</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>tamilpsd-1017.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="3" t="inlineStr">
+        <is>
+          <t>4431.psd</t>
+        </is>
+      </c>
+      <c r="B1052" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1018.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>4424.psd</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>tamilpsd-1019.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="3" t="inlineStr">
+        <is>
+          <t>4425 letters.psd</t>
+        </is>
+      </c>
+      <c r="B1054" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1020.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>4427 letters.psd</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>tamilpsd-1021.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="3" t="inlineStr">
+        <is>
+          <t>4428 letters.psd</t>
+        </is>
+      </c>
+      <c r="B1056" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1022.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>4426 letters.psd</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>tamilpsd-1023.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="3" t="inlineStr">
+        <is>
+          <t>4423.psd</t>
+        </is>
+      </c>
+      <c r="B1058" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1024.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>4422.psd</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>tamilpsd-1025.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="3" t="inlineStr">
+        <is>
+          <t>4421.psd</t>
+        </is>
+      </c>
+      <c r="B1060" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1026.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>4420.psd</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>tamilpsd-1027.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="3" t="inlineStr">
+        <is>
+          <t>4419.psd</t>
+        </is>
+      </c>
+      <c r="B1062" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1028.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>4418.psd</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>tamilpsd-1029.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="3" t="inlineStr">
+        <is>
+          <t>4417.psd</t>
+        </is>
+      </c>
+      <c r="B1064" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1030.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>4416.psd</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>tamilpsd-1031.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="3" t="inlineStr">
+        <is>
+          <t>4415.psd</t>
+        </is>
+      </c>
+      <c r="B1066" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1032.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>4414.psd</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>tamilpsd-1033.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="3" t="inlineStr">
+        <is>
+          <t>4413.psd</t>
+        </is>
+      </c>
+      <c r="B1068" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1034.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>4412.psd</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>tamilpsd-1035.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="3" t="inlineStr">
+        <is>
+          <t>4411.psd</t>
+        </is>
+      </c>
+      <c r="B1070" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1036.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>4410.psd</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>tamilpsd-1037.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="3" t="inlineStr">
+        <is>
+          <t>4409.psd</t>
+        </is>
+      </c>
+      <c r="B1072" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1038.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>4408.psd</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>tamilpsd-1039.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="3" t="inlineStr">
+        <is>
+          <t>4407.psd</t>
+        </is>
+      </c>
+      <c r="B1074" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1040.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>4406.psd</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>tamilpsd-1041.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="3" t="inlineStr">
+        <is>
+          <t>4405.psd</t>
+        </is>
+      </c>
+      <c r="B1076" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1042.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>4404.psd</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>tamilpsd-1043.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="3" t="inlineStr">
+        <is>
+          <t>4403.psd</t>
+        </is>
+      </c>
+      <c r="B1078" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1044.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>4402.psd</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>tamilpsd-1045.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="3" t="inlineStr">
+        <is>
+          <t>4401.psd</t>
+        </is>
+      </c>
+      <c r="B1080" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-1046.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>4400.psd</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>tamilpsd-1047.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2049"/>
+  <dimension ref="A1:B2325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -24685,6 +24685,3318 @@
         </is>
       </c>
     </row>
+    <row r="2050">
+      <c r="A2050" s="3" t="inlineStr">
+        <is>
+          <t>5406.psd</t>
+        </is>
+      </c>
+      <c r="B2050" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2017.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>4950.psd</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>tamilpsd-2018.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="3" t="inlineStr">
+        <is>
+          <t>4803.psd</t>
+        </is>
+      </c>
+      <c r="B2052" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2019.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>4802.psd</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>tamilpsd-2020.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="3" t="inlineStr">
+        <is>
+          <t>4801.PSD</t>
+        </is>
+      </c>
+      <c r="B2054" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2021.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>4800.psd</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>tamilpsd-2022.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="3" t="inlineStr">
+        <is>
+          <t>4799.psd</t>
+        </is>
+      </c>
+      <c r="B2056" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2023.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>4798.psd</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>tamilpsd-2024.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="3" t="inlineStr">
+        <is>
+          <t>4797.PSD</t>
+        </is>
+      </c>
+      <c r="B2058" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2025.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>4796.psd</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>tamilpsd-2026.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="3" t="inlineStr">
+        <is>
+          <t>4795.psd</t>
+        </is>
+      </c>
+      <c r="B2060" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2027.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>4794.psd</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>tamilpsd-2028.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="3" t="inlineStr">
+        <is>
+          <t>4793.psd</t>
+        </is>
+      </c>
+      <c r="B2062" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2029.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>4792.psd</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>tamilpsd-2030.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="3" t="inlineStr">
+        <is>
+          <t>4791.psd</t>
+        </is>
+      </c>
+      <c r="B2064" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2031.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>4790.psd</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>tamilpsd-2032.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="3" t="inlineStr">
+        <is>
+          <t>4789.psd</t>
+        </is>
+      </c>
+      <c r="B2066" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2033.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>4788.PSD</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>tamilpsd-2034.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="3" t="inlineStr">
+        <is>
+          <t>4787.PSD</t>
+        </is>
+      </c>
+      <c r="B2068" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2035.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>4786.psd</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>tamilpsd-2036.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="3" t="inlineStr">
+        <is>
+          <t>4785.psd</t>
+        </is>
+      </c>
+      <c r="B2070" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2037.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>4784.psd</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>tamilpsd-2038.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="3" t="inlineStr">
+        <is>
+          <t>4783.psd</t>
+        </is>
+      </c>
+      <c r="B2072" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2039.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>4782.psd</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>tamilpsd-2040.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="3" t="inlineStr">
+        <is>
+          <t>4763.psd</t>
+        </is>
+      </c>
+      <c r="B2074" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2041.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>4762.psd</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>tamilpsd-2042.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="3" t="inlineStr">
+        <is>
+          <t>4761.psd</t>
+        </is>
+      </c>
+      <c r="B2076" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2043.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>4760.psd</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>tamilpsd-2044.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="3" t="inlineStr">
+        <is>
+          <t>4759.psd</t>
+        </is>
+      </c>
+      <c r="B2078" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2045.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>4758.psd</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>tamilpsd-2046.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="3" t="inlineStr">
+        <is>
+          <t>4757.psd</t>
+        </is>
+      </c>
+      <c r="B2080" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2047.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>4756.psd</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>tamilpsd-2048.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="3" t="inlineStr">
+        <is>
+          <t>4755.psd</t>
+        </is>
+      </c>
+      <c r="B2082" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2049.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>4754.psd</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>tamilpsd-2050.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="3" t="inlineStr">
+        <is>
+          <t>4753.psd</t>
+        </is>
+      </c>
+      <c r="B2084" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2051.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>4752.psd</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>tamilpsd-2052.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="3" t="inlineStr">
+        <is>
+          <t>4751.psd</t>
+        </is>
+      </c>
+      <c r="B2086" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2053.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>4750.psd</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>tamilpsd-2054.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="3" t="inlineStr">
+        <is>
+          <t>4749.psd</t>
+        </is>
+      </c>
+      <c r="B2088" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2055.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>4748.psd</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>tamilpsd-2056.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="3" t="inlineStr">
+        <is>
+          <t>4747.psd</t>
+        </is>
+      </c>
+      <c r="B2090" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2057.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>4746.psd</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>tamilpsd-2058.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="3" t="inlineStr">
+        <is>
+          <t>4745.psd</t>
+        </is>
+      </c>
+      <c r="B2092" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2059.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>4744.psd</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>tamilpsd-2060.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="3" t="inlineStr">
+        <is>
+          <t>4743.psd</t>
+        </is>
+      </c>
+      <c r="B2094" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2061.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>4742.psd</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>tamilpsd-2062.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="3" t="inlineStr">
+        <is>
+          <t>4741.psd</t>
+        </is>
+      </c>
+      <c r="B2096" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2063.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>4740.psd</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>tamilpsd-2064.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="3" t="inlineStr">
+        <is>
+          <t>4739.psd</t>
+        </is>
+      </c>
+      <c r="B2098" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2065.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>4738.psd</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>tamilpsd-2066.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="3" t="inlineStr">
+        <is>
+          <t>4737.psd</t>
+        </is>
+      </c>
+      <c r="B2100" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2067.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>4736.psd</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>tamilpsd-2068.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="3" t="inlineStr">
+        <is>
+          <t>4735.psd</t>
+        </is>
+      </c>
+      <c r="B2102" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2069.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>4734.psd</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>tamilpsd-2070.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="3" t="inlineStr">
+        <is>
+          <t>4733.psd</t>
+        </is>
+      </c>
+      <c r="B2104" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2071.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>4732.psd</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>tamilpsd-2072.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="3" t="inlineStr">
+        <is>
+          <t>4731.psd</t>
+        </is>
+      </c>
+      <c r="B2106" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2073.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>4730.psd</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>tamilpsd-2074.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="3" t="inlineStr">
+        <is>
+          <t>4729.psd</t>
+        </is>
+      </c>
+      <c r="B2108" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2075.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>4728.psd</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>tamilpsd-2076.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="3" t="inlineStr">
+        <is>
+          <t>4727.psd</t>
+        </is>
+      </c>
+      <c r="B2110" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2077.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>4726.psd</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>tamilpsd-2078.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="3" t="inlineStr">
+        <is>
+          <t>4725.psd</t>
+        </is>
+      </c>
+      <c r="B2112" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2079.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>4724.psd</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>tamilpsd-2080.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="3" t="inlineStr">
+        <is>
+          <t>4723.psd</t>
+        </is>
+      </c>
+      <c r="B2114" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2081.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>4722.psd</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>tamilpsd-2082.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="3" t="inlineStr">
+        <is>
+          <t>4721.psd</t>
+        </is>
+      </c>
+      <c r="B2116" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2083.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>4720.psd</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>tamilpsd-2084.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="3" t="inlineStr">
+        <is>
+          <t>4719.psd</t>
+        </is>
+      </c>
+      <c r="B2118" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2085.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>4718.psd</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>tamilpsd-2086.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="3" t="inlineStr">
+        <is>
+          <t>4717.psd</t>
+        </is>
+      </c>
+      <c r="B2120" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2087.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>4716.psd</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>tamilpsd-2088.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="3" t="inlineStr">
+        <is>
+          <t>4715.psd</t>
+        </is>
+      </c>
+      <c r="B2122" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2089.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>4714.psd</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>tamilpsd-2090.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="3" t="inlineStr">
+        <is>
+          <t>4713.psd</t>
+        </is>
+      </c>
+      <c r="B2124" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2091.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>4712.psd</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>tamilpsd-2092.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="3" t="inlineStr">
+        <is>
+          <t>4711.psd</t>
+        </is>
+      </c>
+      <c r="B2126" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2093.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>4710.psd</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>tamilpsd-2094.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="3" t="inlineStr">
+        <is>
+          <t>4709.psd</t>
+        </is>
+      </c>
+      <c r="B2128" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2095.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>4708.psd</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>tamilpsd-2096.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="3" t="inlineStr">
+        <is>
+          <t>4707.psd</t>
+        </is>
+      </c>
+      <c r="B2130" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2097.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>4706.psd</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>tamilpsd-2098.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="3" t="inlineStr">
+        <is>
+          <t>4705.psd</t>
+        </is>
+      </c>
+      <c r="B2132" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2099.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>4704.psd</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>tamilpsd-2100.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="3" t="inlineStr">
+        <is>
+          <t>4703.psd</t>
+        </is>
+      </c>
+      <c r="B2134" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2101.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>4702.psd</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>tamilpsd-2102.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="3" t="inlineStr">
+        <is>
+          <t>4701.psd</t>
+        </is>
+      </c>
+      <c r="B2136" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2103.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>4700.psd</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>tamilpsd-2104.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="3" t="inlineStr">
+        <is>
+          <t>4699.psd</t>
+        </is>
+      </c>
+      <c r="B2138" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2105.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>4698.psd</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>tamilpsd-2106.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="3" t="inlineStr">
+        <is>
+          <t>4697.psd</t>
+        </is>
+      </c>
+      <c r="B2140" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2107.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>4696.psd</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>tamilpsd-2108.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="3" t="inlineStr">
+        <is>
+          <t>4695.psd</t>
+        </is>
+      </c>
+      <c r="B2142" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2109.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>4694.psd</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>tamilpsd-2110.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="3" t="inlineStr">
+        <is>
+          <t>4693.psd</t>
+        </is>
+      </c>
+      <c r="B2144" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2111.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>4692.psd</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>tamilpsd-2112.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="3" t="inlineStr">
+        <is>
+          <t>4691.psd</t>
+        </is>
+      </c>
+      <c r="B2146" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2113.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>4690.psd</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>tamilpsd-2114.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="3" t="inlineStr">
+        <is>
+          <t>4689.psd</t>
+        </is>
+      </c>
+      <c r="B2148" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2115.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>4688.psd</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>tamilpsd-2116.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="3" t="inlineStr">
+        <is>
+          <t>4687.psd</t>
+        </is>
+      </c>
+      <c r="B2150" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2117.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>4686.psd</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>tamilpsd-2118.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="3" t="inlineStr">
+        <is>
+          <t>4685.psd</t>
+        </is>
+      </c>
+      <c r="B2152" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2119.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>4684.psd</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>tamilpsd-2120.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="3" t="inlineStr">
+        <is>
+          <t>4683.psd</t>
+        </is>
+      </c>
+      <c r="B2154" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2121.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>4682.psd</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>tamilpsd-2122.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="3" t="inlineStr">
+        <is>
+          <t>4681.psd</t>
+        </is>
+      </c>
+      <c r="B2156" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2123.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>4680.psd</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>tamilpsd-2124.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="3" t="inlineStr">
+        <is>
+          <t>4679.psd</t>
+        </is>
+      </c>
+      <c r="B2158" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2125.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>4678.psd</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>tamilpsd-2126.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" s="3" t="inlineStr">
+        <is>
+          <t>4677.psd</t>
+        </is>
+      </c>
+      <c r="B2160" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2127.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>4676.psd</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>tamilpsd-2128.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="3" t="inlineStr">
+        <is>
+          <t>4675.psd</t>
+        </is>
+      </c>
+      <c r="B2162" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2129.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>4674.psd</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>tamilpsd-2130.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="3" t="inlineStr">
+        <is>
+          <t>4673.psd</t>
+        </is>
+      </c>
+      <c r="B2164" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2131.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>4672.psd</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>tamilpsd-2132.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="3" t="inlineStr">
+        <is>
+          <t>4671.psd</t>
+        </is>
+      </c>
+      <c r="B2166" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2133.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>4670.psd</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>tamilpsd-2134.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="3" t="inlineStr">
+        <is>
+          <t>4780.psd</t>
+        </is>
+      </c>
+      <c r="B2168" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2135.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>4778.psd</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>tamilpsd-2136.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="3" t="inlineStr">
+        <is>
+          <t>4779.psd</t>
+        </is>
+      </c>
+      <c r="B2170" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2137.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>4777.psd</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>tamilpsd-2138.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="3" t="inlineStr">
+        <is>
+          <t>4776.psd</t>
+        </is>
+      </c>
+      <c r="B2172" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2139.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>4775.psd</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>tamilpsd-2140.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="3" t="inlineStr">
+        <is>
+          <t>4774.psd</t>
+        </is>
+      </c>
+      <c r="B2174" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2141.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>4773.psd</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>tamilpsd-2142.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="3" t="inlineStr">
+        <is>
+          <t>4772.psd</t>
+        </is>
+      </c>
+      <c r="B2176" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2143.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>4771.psd</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>tamilpsd-2144.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="3" t="inlineStr">
+        <is>
+          <t>4770.psd</t>
+        </is>
+      </c>
+      <c r="B2178" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2145.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>4769.psd</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>tamilpsd-2146.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="3" t="inlineStr">
+        <is>
+          <t>4768.psd</t>
+        </is>
+      </c>
+      <c r="B2180" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2147.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>4767.psd</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>tamilpsd-2148.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="3" t="inlineStr">
+        <is>
+          <t>4766.psd</t>
+        </is>
+      </c>
+      <c r="B2182" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2149.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>4765.psd</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>tamilpsd-2150.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="3" t="inlineStr">
+        <is>
+          <t>4764.psd</t>
+        </is>
+      </c>
+      <c r="B2184" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2151.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>4461.psd</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>tamilpsd-2152.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="3" t="inlineStr">
+        <is>
+          <t>017.psd</t>
+        </is>
+      </c>
+      <c r="B2186" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2153.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>018.psd</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>tamilpsd-2154.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="3" t="inlineStr">
+        <is>
+          <t>019.psd</t>
+        </is>
+      </c>
+      <c r="B2188" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2155.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>020.psd</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>tamilpsd-2156.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="3" t="inlineStr">
+        <is>
+          <t>021.psd</t>
+        </is>
+      </c>
+      <c r="B2190" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2157.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>022.psd</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>tamilpsd-2158.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="3" t="inlineStr">
+        <is>
+          <t>023.psd</t>
+        </is>
+      </c>
+      <c r="B2192" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2159.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>024.psd</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>tamilpsd-2160.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="3" t="inlineStr">
+        <is>
+          <t>025.psd</t>
+        </is>
+      </c>
+      <c r="B2194" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2161.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>009.psd</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>tamilpsd-2162.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="3" t="inlineStr">
+        <is>
+          <t>010.psd</t>
+        </is>
+      </c>
+      <c r="B2196" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2163.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>011.psd</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>tamilpsd-2164.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="3" t="inlineStr">
+        <is>
+          <t>012.psd</t>
+        </is>
+      </c>
+      <c r="B2198" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2165.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>013.psd</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>tamilpsd-2166.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="3" t="inlineStr">
+        <is>
+          <t>014.psd</t>
+        </is>
+      </c>
+      <c r="B2200" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2167.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>015.psd</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>tamilpsd-2168.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="3" t="inlineStr">
+        <is>
+          <t>016.psd</t>
+        </is>
+      </c>
+      <c r="B2202" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2169.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (31).psd</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>tamilpsd-2170.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (32).psd</t>
+        </is>
+      </c>
+      <c r="B2204" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2171.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (33).psd</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>tamilpsd-2172.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (34).psd</t>
+        </is>
+      </c>
+      <c r="B2206" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2173.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (35).psd</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>tamilpsd-2174.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (36).psd</t>
+        </is>
+      </c>
+      <c r="B2208" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2175.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (37).psd</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>tamilpsd-2176.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (38).psd</t>
+        </is>
+      </c>
+      <c r="B2210" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2177.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (39).psd</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>tamilpsd-2178.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (40).psd</t>
+        </is>
+      </c>
+      <c r="B2212" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2179.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (26).psd</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>tamilpsd-2185.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (27).psd</t>
+        </is>
+      </c>
+      <c r="B2214" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2186.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (28).psd</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>tamilpsd-2187.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (29).psd</t>
+        </is>
+      </c>
+      <c r="B2216" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2188.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (30).psd</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>tamilpsd-2189.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12 x 36 (1).psd</t>
+        </is>
+      </c>
+      <c r="B2218" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2190.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>RC Design 12 x 36 (2).psd</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>tamilpsd-2191.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12 x 36 (3).psd</t>
+        </is>
+      </c>
+      <c r="B2220" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2192.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>RC Design 12 x 36 (4).psd</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>tamilpsd-2193.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12 x 36 (5).psd</t>
+        </is>
+      </c>
+      <c r="B2222" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2194.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>RC Design 12 x 36 (6).psd</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>tamilpsd-2195.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (1).psd</t>
+        </is>
+      </c>
+      <c r="B2224" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2196.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (2).psd</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>tamilpsd-2197.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (3).psd</t>
+        </is>
+      </c>
+      <c r="B2226" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2198.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (4).psd</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>tamilpsd-2199.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (5).psd</t>
+        </is>
+      </c>
+      <c r="B2228" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2200.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (6).psd</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>tamilpsd-2201.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (7).psd</t>
+        </is>
+      </c>
+      <c r="B2230" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2202.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (10).psd</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>tamilpsd-2203.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (11).psd</t>
+        </is>
+      </c>
+      <c r="B2232" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2204.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (12).psd</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>tamilpsd-2205.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (13).psd</t>
+        </is>
+      </c>
+      <c r="B2234" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2206.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (14).psd</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>tamilpsd-2207.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (8).psd</t>
+        </is>
+      </c>
+      <c r="B2236" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2208.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (9).psd</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>tamilpsd-2209.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (1).psd</t>
+        </is>
+      </c>
+      <c r="B2238" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2210.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (2).psd</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>tamilpsd-2211.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (3).psd</t>
+        </is>
+      </c>
+      <c r="B2240" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2212.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (4).psd</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>tamilpsd-2213.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (5).psd</t>
+        </is>
+      </c>
+      <c r="B2242" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2214.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (6).psd</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>tamilpsd-2215.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (7).psd</t>
+        </is>
+      </c>
+      <c r="B2244" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2216.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (10).psd</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>tamilpsd-2217.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (11).psd</t>
+        </is>
+      </c>
+      <c r="B2246" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2218.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (12).psd</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>tamilpsd-2219.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (13).psd</t>
+        </is>
+      </c>
+      <c r="B2248" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2220.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (14).psd</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>tamilpsd-2221.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (8).psd</t>
+        </is>
+      </c>
+      <c r="B2250" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2222.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (9).psd</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>tamilpsd-2223.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12 X 36 (8).psd</t>
+        </is>
+      </c>
+      <c r="B2252" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2227.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>RC Design 12 X 36 (9).psd</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>tamilpsd-2228.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12 X 36 (10).psd</t>
+        </is>
+      </c>
+      <c r="B2254" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2229.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>RC Design 12 X 36 (7).psd</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>tamilpsd-2233.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" s="3" t="inlineStr">
+        <is>
+          <t>4551.psd</t>
+        </is>
+      </c>
+      <c r="B2256" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2234.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>4550.psd</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>tamilpsd-2235.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="3" t="inlineStr">
+        <is>
+          <t>4552.psd</t>
+        </is>
+      </c>
+      <c r="B2258" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2236.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>4548.psd</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>tamilpsd-2237.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="3" t="inlineStr">
+        <is>
+          <t>4546.psd</t>
+        </is>
+      </c>
+      <c r="B2260" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2238.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>4534.psd</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>tamilpsd-2239.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="3" t="inlineStr">
+        <is>
+          <t>4359.psd</t>
+        </is>
+      </c>
+      <c r="B2262" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2240.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>4358.psd</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>tamilpsd-2241.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="3" t="inlineStr">
+        <is>
+          <t>4357.psd</t>
+        </is>
+      </c>
+      <c r="B2264" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2242.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>4356.psd</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>tamilpsd-2243.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" s="3" t="inlineStr">
+        <is>
+          <t>4355.psd</t>
+        </is>
+      </c>
+      <c r="B2266" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2244.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>4354.psd</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>tamilpsd-2245.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="3" t="inlineStr">
+        <is>
+          <t>4353.psd</t>
+        </is>
+      </c>
+      <c r="B2268" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2246.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>4352.psd</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>tamilpsd-2247.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="3" t="inlineStr">
+        <is>
+          <t>4350.psd</t>
+        </is>
+      </c>
+      <c r="B2270" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2248.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>4351.psd</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>tamilpsd-2249.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="3" t="inlineStr">
+        <is>
+          <t>4349.psd</t>
+        </is>
+      </c>
+      <c r="B2272" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2250.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>4348.psd</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>tamilpsd-2251.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="3" t="inlineStr">
+        <is>
+          <t>4345.psd</t>
+        </is>
+      </c>
+      <c r="B2274" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2252.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>4347.psd</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>tamilpsd-2253.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="3" t="inlineStr">
+        <is>
+          <t>4344.psd</t>
+        </is>
+      </c>
+      <c r="B2276" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2254.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>4342.psd</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>tamilpsd-2255.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="3" t="inlineStr">
+        <is>
+          <t>4343.psd</t>
+        </is>
+      </c>
+      <c r="B2278" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2256.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>4341.psd</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>tamilpsd-2257.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="3" t="inlineStr">
+        <is>
+          <t>4340.psd</t>
+        </is>
+      </c>
+      <c r="B2280" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2258.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>4338.psd</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>tamilpsd-2259.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="3" t="inlineStr">
+        <is>
+          <t>4339.psd</t>
+        </is>
+      </c>
+      <c r="B2282" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2260.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>4337.psd</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>tamilpsd-2261.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="3" t="inlineStr">
+        <is>
+          <t>4336.PSD</t>
+        </is>
+      </c>
+      <c r="B2284" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2262.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>4335.psd</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>tamilpsd-2263.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="3" t="inlineStr">
+        <is>
+          <t>4334.psd</t>
+        </is>
+      </c>
+      <c r="B2286" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2264.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>4333.psd</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>tamilpsd-2265.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="3" t="inlineStr">
+        <is>
+          <t>4332.psd</t>
+        </is>
+      </c>
+      <c r="B2288" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2266.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>4331.psd</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>tamilpsd-2267.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="3" t="inlineStr">
+        <is>
+          <t>4330.psd</t>
+        </is>
+      </c>
+      <c r="B2290" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2268.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>4329.psd</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>tamilpsd-2269.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="3" t="inlineStr">
+        <is>
+          <t>4328.psd</t>
+        </is>
+      </c>
+      <c r="B2292" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2270.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>4327.psd</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>tamilpsd-2271.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="3" t="inlineStr">
+        <is>
+          <t>4326.psd</t>
+        </is>
+      </c>
+      <c r="B2294" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2272.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>4325.psd</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>tamilpsd-2273.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="3" t="inlineStr">
+        <is>
+          <t>4324.psd</t>
+        </is>
+      </c>
+      <c r="B2296" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2274.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>4323.psd</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>tamilpsd-2275.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="3" t="inlineStr">
+        <is>
+          <t>4322.psd</t>
+        </is>
+      </c>
+      <c r="B2298" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2276.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>4321.psd</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>tamilpsd-2277.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="3" t="inlineStr">
+        <is>
+          <t>Rc Design 12x30 (2)25.psd</t>
+        </is>
+      </c>
+      <c r="B2300" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2278.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (4)12.psd</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>tamilpsd-2279.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (4)22.psd</t>
+        </is>
+      </c>
+      <c r="B2302" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2280.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (5)13.psd</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>tamilpsd-2281.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (5)23.psd</t>
+        </is>
+      </c>
+      <c r="B2304" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2282.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>Rc Design 12x36 (5)8.psd</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>tamilpsd-2283.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (2)10.psd</t>
+        </is>
+      </c>
+      <c r="B2306" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2284.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (2)20.psd</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>tamilpsd-2285.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (3)11.psd</t>
+        </is>
+      </c>
+      <c r="B2308" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2286.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (3)21.psd</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>tamilpsd-2287.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (3)3.psd</t>
+        </is>
+      </c>
+      <c r="B2310" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2288.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>Rc Design 12x36 (3)6.psd</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>tamilpsd-2289.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="3" t="inlineStr">
+        <is>
+          <t>Rc Design 12x36 (4)7.psd</t>
+        </is>
+      </c>
+      <c r="B2312" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2290.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>Rc Design 12x30 (3)26.psd</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>tamilpsd-2291.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (1)1.psd</t>
+        </is>
+      </c>
+      <c r="B2314" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2292.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (1)19.psd</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>tamilpsd-2293.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" s="3" t="inlineStr">
+        <is>
+          <t>Rc Design 12x36 (1)4.psd</t>
+        </is>
+      </c>
+      <c r="B2316" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2294.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (1)9.psd</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>tamilpsd-2295.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (2)2.psd</t>
+        </is>
+      </c>
+      <c r="B2318" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2296.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>Rc Design 12x36 (2)5.psd</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>tamilpsd-2297.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" s="3" t="inlineStr">
+        <is>
+          <t>RC Desgin 12x36 (1)14.psd</t>
+        </is>
+      </c>
+      <c r="B2320" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2298.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>RC Desgin 12x36 (2)15.psd</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>tamilpsd-2299.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" s="3" t="inlineStr">
+        <is>
+          <t>RC Desgin 12x36 (3)16.psd</t>
+        </is>
+      </c>
+      <c r="B2322" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2300.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>RC Desgin 12x36 (4)17.psd</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>tamilpsd-2301.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" s="3" t="inlineStr">
+        <is>
+          <t>RC Desgin 12x36 (5)18.psd</t>
+        </is>
+      </c>
+      <c r="B2324" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2302.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>Rc Design 12x30 (1)24.psd</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>tamilpsd-2303.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2325"/>
+  <dimension ref="A1:B2634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -27997,6 +27997,3714 @@
         </is>
       </c>
     </row>
+    <row r="2326">
+      <c r="A2326" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (41).psd</t>
+        </is>
+      </c>
+      <c r="B2326" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2830.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (42).psd</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>tamilpsd-2831.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (43).psd</t>
+        </is>
+      </c>
+      <c r="B2328" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2832.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (44).psd</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>tamilpsd-2833.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (45).psd</t>
+        </is>
+      </c>
+      <c r="B2330" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2834.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (46).psd</t>
+        </is>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>tamilpsd-2835.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (47).psd</t>
+        </is>
+      </c>
+      <c r="B2332" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2836.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (48).psd</t>
+        </is>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>tamilpsd-2837.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (49).psd</t>
+        </is>
+      </c>
+      <c r="B2334" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2838.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 (50).psd</t>
+        </is>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>tamilpsd-2839.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 1.psd</t>
+        </is>
+      </c>
+      <c r="B2336" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2845.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 2.psd</t>
+        </is>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>tamilpsd-2846.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 3.psd</t>
+        </is>
+      </c>
+      <c r="B2338" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2847.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 4.psd</t>
+        </is>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>tamilpsd-2848.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (15).psd</t>
+        </is>
+      </c>
+      <c r="B2340" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2849.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (16).psd</t>
+        </is>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>tamilpsd-2850.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (17).psd</t>
+        </is>
+      </c>
+      <c r="B2342" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2851.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (18).psd</t>
+        </is>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>tamilpsd-2852.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (19).psd</t>
+        </is>
+      </c>
+      <c r="B2344" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2853.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (20).psd</t>
+        </is>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>tamilpsd-2854.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (21).psd</t>
+        </is>
+      </c>
+      <c r="B2346" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2855.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOL 242 (22).psd</t>
+        </is>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>tamilpsd-2856.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVE VOl245 (10).psd</t>
+        </is>
+      </c>
+      <c r="B2348" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2857.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>DMAX LIVEVOL-99 (10).psd</t>
+        </is>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>tamilpsd-2858.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVEVOL-99 (12).psd</t>
+        </is>
+      </c>
+      <c r="B2350" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2859.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>DMAX LIVEVOL-99 (18).psd</t>
+        </is>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>tamilpsd-2860.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" s="3" t="inlineStr">
+        <is>
+          <t>DMAX LIVEVOL-99 (19).psd</t>
+        </is>
+      </c>
+      <c r="B2352" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2861.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>SOORIYA 001.psd</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>tamilpsd-2862.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA 002.psd</t>
+        </is>
+      </c>
+      <c r="B2354" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2863.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>SOORIYA 003.psd</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>tamilpsd-2864.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA 004.psd</t>
+        </is>
+      </c>
+      <c r="B2356" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2865.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>SOORIYA 005.psd</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>tamilpsd-2866.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA 006.psd</t>
+        </is>
+      </c>
+      <c r="B2358" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2867.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>SOORIYA 007.psd</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>tamilpsd-2868.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA 008.psd</t>
+        </is>
+      </c>
+      <c r="B2360" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2869.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>SOORIYA 009.psd</t>
+        </is>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>tamilpsd-2870.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA 010.psd</t>
+        </is>
+      </c>
+      <c r="B2362" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2871.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>SOORIYA 018.psd</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>tamilpsd-2872.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA 025.psd</t>
+        </is>
+      </c>
+      <c r="B2364" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2873.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>SOORIYA 027.psd</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>tamilpsd-2874.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA001.psd</t>
+        </is>
+      </c>
+      <c r="B2366" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2875.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>SOORIYA002.psd</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>tamilpsd-2876.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA003.psd</t>
+        </is>
+      </c>
+      <c r="B2368" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2877.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>SOORIYA004.psd</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>tamilpsd-2878.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA005.psd</t>
+        </is>
+      </c>
+      <c r="B2370" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2879.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>SOORIYA006.psd</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>tamilpsd-2880.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA007.psd</t>
+        </is>
+      </c>
+      <c r="B2372" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2881.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>SOORIYA008.psd</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>tamilpsd-2882.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" s="3" t="inlineStr">
+        <is>
+          <t>SOORIYA009.psd</t>
+        </is>
+      </c>
+      <c r="B2374" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2883.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>SOORIYA010.psd</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>tamilpsd-2884.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (15).psd</t>
+        </is>
+      </c>
+      <c r="B2376" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2885.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (16).psd</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>tamilpsd-2886.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (17).psd</t>
+        </is>
+      </c>
+      <c r="B2378" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2887.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (18).psd</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>tamilpsd-2888.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (19).psd</t>
+        </is>
+      </c>
+      <c r="B2380" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2889.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (20).psd</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>tamilpsd-2890.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (21).psd</t>
+        </is>
+      </c>
+      <c r="B2382" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2891.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (22).psd</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>tamilpsd-2892.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (23).psd</t>
+        </is>
+      </c>
+      <c r="B2384" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2893.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (24).psd</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>tamilpsd-2894.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" s="3" t="inlineStr">
+        <is>
+          <t>RC Desing 12x36 (25).psd</t>
+        </is>
+      </c>
+      <c r="B2386" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2895.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 5.psd</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>tamilpsd-2896.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 a.psd</t>
+        </is>
+      </c>
+      <c r="B2388" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2897.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 b.psd</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>tamilpsd-2898.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 c.psd</t>
+        </is>
+      </c>
+      <c r="B2390" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2899.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 d.psd</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>tamilpsd-2900.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" s="3" t="inlineStr">
+        <is>
+          <t>RC Design 12x36 e.psd</t>
+        </is>
+      </c>
+      <c r="B2392" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2901.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>4267.psd</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>tamilpsd-2902.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" s="3" t="inlineStr">
+        <is>
+          <t>4266.psd</t>
+        </is>
+      </c>
+      <c r="B2394" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2903.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>4265.psd</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>tamilpsd-2904.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" s="3" t="inlineStr">
+        <is>
+          <t>4264.psd</t>
+        </is>
+      </c>
+      <c r="B2396" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2905.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>4262.psd</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>tamilpsd-2906.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" s="3" t="inlineStr">
+        <is>
+          <t>4261.psd</t>
+        </is>
+      </c>
+      <c r="B2398" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2907.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>4260.psd</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>tamilpsd-2908.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" s="3" t="inlineStr">
+        <is>
+          <t>4259.psd</t>
+        </is>
+      </c>
+      <c r="B2400" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2909.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>4258.psd</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>tamilpsd-2910.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" s="3" t="inlineStr">
+        <is>
+          <t>4257.psd</t>
+        </is>
+      </c>
+      <c r="B2402" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2911.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>4256.psd</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>tamilpsd-2912.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" s="3" t="inlineStr">
+        <is>
+          <t>4255.psd</t>
+        </is>
+      </c>
+      <c r="B2404" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2913.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>4254.psd</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>tamilpsd-2914.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" s="3" t="inlineStr">
+        <is>
+          <t>4253.psd</t>
+        </is>
+      </c>
+      <c r="B2406" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2915.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>4252.psd</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>tamilpsd-2916.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" s="3" t="inlineStr">
+        <is>
+          <t>4251.psd</t>
+        </is>
+      </c>
+      <c r="B2408" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2917.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>4250.psd</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>tamilpsd-2918.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" s="3" t="inlineStr">
+        <is>
+          <t>4249.psd</t>
+        </is>
+      </c>
+      <c r="B2410" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2919.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>4248.psd</t>
+        </is>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>tamilpsd-2920.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" s="3" t="inlineStr">
+        <is>
+          <t>4247.psd</t>
+        </is>
+      </c>
+      <c r="B2412" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2921.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>4246.psd</t>
+        </is>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>tamilpsd-2922.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" s="3" t="inlineStr">
+        <is>
+          <t>4245.psd</t>
+        </is>
+      </c>
+      <c r="B2414" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2923.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>4244.psd</t>
+        </is>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>tamilpsd-2924.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" s="3" t="inlineStr">
+        <is>
+          <t>4268.psd</t>
+        </is>
+      </c>
+      <c r="B2416" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2925.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>4242.psd</t>
+        </is>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>tamilpsd-2926.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" s="3" t="inlineStr">
+        <is>
+          <t>4241.psd</t>
+        </is>
+      </c>
+      <c r="B2418" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2927.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>4240.psd</t>
+        </is>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>tamilpsd-2928.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" s="3" t="inlineStr">
+        <is>
+          <t>4238.psd</t>
+        </is>
+      </c>
+      <c r="B2420" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2929.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>4239.psd</t>
+        </is>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>tamilpsd-2930.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" s="3" t="inlineStr">
+        <is>
+          <t>4237.psd</t>
+        </is>
+      </c>
+      <c r="B2422" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2931.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>4236.psd</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>tamilpsd-2932.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" s="3" t="inlineStr">
+        <is>
+          <t>4235.psd</t>
+        </is>
+      </c>
+      <c r="B2424" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2933.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>4234.psd</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>tamilpsd-2934.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" s="3" t="inlineStr">
+        <is>
+          <t>4233.psd</t>
+        </is>
+      </c>
+      <c r="B2426" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2935.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>4232.psd</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>tamilpsd-2936.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" s="3" t="inlineStr">
+        <is>
+          <t>4231.psd</t>
+        </is>
+      </c>
+      <c r="B2428" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2937.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>4230.psd</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>tamilpsd-2938.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" s="3" t="inlineStr">
+        <is>
+          <t>4229.psd</t>
+        </is>
+      </c>
+      <c r="B2430" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2939.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>4228.psd</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>tamilpsd-2940.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" s="3" t="inlineStr">
+        <is>
+          <t>4227.psd</t>
+        </is>
+      </c>
+      <c r="B2432" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2941.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>4226.psd</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>tamilpsd-2942.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" s="3" t="inlineStr">
+        <is>
+          <t>4225.psd</t>
+        </is>
+      </c>
+      <c r="B2434" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2943.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>4224.psd</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>tamilpsd-2944.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" s="3" t="inlineStr">
+        <is>
+          <t>4223.psd</t>
+        </is>
+      </c>
+      <c r="B2436" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2945.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>4222.psd</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>tamilpsd-2946.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" s="3" t="inlineStr">
+        <is>
+          <t>4221.psd</t>
+        </is>
+      </c>
+      <c r="B2438" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2947.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>4220.psd</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>tamilpsd-2948.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" s="3" t="inlineStr">
+        <is>
+          <t>4219.psd</t>
+        </is>
+      </c>
+      <c r="B2440" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2949.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>4218.psd</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>tamilpsd-2950.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" s="3" t="inlineStr">
+        <is>
+          <t>4217.psd</t>
+        </is>
+      </c>
+      <c r="B2442" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2951.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>4216.psd</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>tamilpsd-2952.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" s="3" t="inlineStr">
+        <is>
+          <t>4215.psd</t>
+        </is>
+      </c>
+      <c r="B2444" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2953.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>4214.psd</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>tamilpsd-2954.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" s="3" t="inlineStr">
+        <is>
+          <t>4213.psd</t>
+        </is>
+      </c>
+      <c r="B2446" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2955.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>4212.psd</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>tamilpsd-2956.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" s="3" t="inlineStr">
+        <is>
+          <t>4211.psd</t>
+        </is>
+      </c>
+      <c r="B2448" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2957.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>4210.psd</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>tamilpsd-2958.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" s="3" t="inlineStr">
+        <is>
+          <t>4209.psd</t>
+        </is>
+      </c>
+      <c r="B2450" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2959.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>4208.psd</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>tamilpsd-2960.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" s="3" t="inlineStr">
+        <is>
+          <t>4207.psd</t>
+        </is>
+      </c>
+      <c r="B2452" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2961.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>4206.psd</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>tamilpsd-2962.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" s="3" t="inlineStr">
+        <is>
+          <t>4205.psd</t>
+        </is>
+      </c>
+      <c r="B2454" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2963.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>4204.psd</t>
+        </is>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>tamilpsd-2964.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" s="3" t="inlineStr">
+        <is>
+          <t>4203.psd</t>
+        </is>
+      </c>
+      <c r="B2456" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2965.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>4202.psd</t>
+        </is>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>tamilpsd-2966.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" s="3" t="inlineStr">
+        <is>
+          <t>4201.psd</t>
+        </is>
+      </c>
+      <c r="B2458" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2967.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>4200.psd</t>
+        </is>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>tamilpsd-2968.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" s="3" t="inlineStr">
+        <is>
+          <t>4199.psd</t>
+        </is>
+      </c>
+      <c r="B2460" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2969.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>4198.psd</t>
+        </is>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>tamilpsd-2970.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" s="3" t="inlineStr">
+        <is>
+          <t>4197.psd</t>
+        </is>
+      </c>
+      <c r="B2462" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2971.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>4196.psd</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>tamilpsd-2972.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" s="3" t="inlineStr">
+        <is>
+          <t>4195.psd</t>
+        </is>
+      </c>
+      <c r="B2464" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2973.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>4194.psd</t>
+        </is>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>tamilpsd-2974.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" s="3" t="inlineStr">
+        <is>
+          <t>4193.psd</t>
+        </is>
+      </c>
+      <c r="B2466" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2975.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>4192.psd</t>
+        </is>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>tamilpsd-2976.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" s="3" t="inlineStr">
+        <is>
+          <t>4191.psd</t>
+        </is>
+      </c>
+      <c r="B2468" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2977.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>4190.psd</t>
+        </is>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>tamilpsd-2978.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" s="3" t="inlineStr">
+        <is>
+          <t>4189.psd</t>
+        </is>
+      </c>
+      <c r="B2470" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2979.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>4243.psd</t>
+        </is>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>tamilpsd-2980.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" s="3" t="inlineStr">
+        <is>
+          <t>4167.psd</t>
+        </is>
+      </c>
+      <c r="B2472" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2981.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>4166.psd</t>
+        </is>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>tamilpsd-2982.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" s="3" t="inlineStr">
+        <is>
+          <t>4165.psd</t>
+        </is>
+      </c>
+      <c r="B2474" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2983.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>4164.psd</t>
+        </is>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>tamilpsd-2984.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" s="3" t="inlineStr">
+        <is>
+          <t>4163.psd</t>
+        </is>
+      </c>
+      <c r="B2476" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2985.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>4162.psd</t>
+        </is>
+      </c>
+      <c r="B2477" t="inlineStr">
+        <is>
+          <t>tamilpsd-2986.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" s="3" t="inlineStr">
+        <is>
+          <t>4161.psd</t>
+        </is>
+      </c>
+      <c r="B2478" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2987.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>4160.psd</t>
+        </is>
+      </c>
+      <c r="B2479" t="inlineStr">
+        <is>
+          <t>tamilpsd-2988.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" s="3" t="inlineStr">
+        <is>
+          <t>4159.psd</t>
+        </is>
+      </c>
+      <c r="B2480" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2989.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>4158.psd</t>
+        </is>
+      </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>tamilpsd-2990.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" s="3" t="inlineStr">
+        <is>
+          <t>4157.psd</t>
+        </is>
+      </c>
+      <c r="B2482" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2991.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>4156.psd</t>
+        </is>
+      </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>tamilpsd-2992.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" s="3" t="inlineStr">
+        <is>
+          <t>4175.psd</t>
+        </is>
+      </c>
+      <c r="B2484" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2993.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>4174.psd</t>
+        </is>
+      </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>tamilpsd-2994.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" s="3" t="inlineStr">
+        <is>
+          <t>4173.psd</t>
+        </is>
+      </c>
+      <c r="B2486" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2995.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>4172.psd</t>
+        </is>
+      </c>
+      <c r="B2487" t="inlineStr">
+        <is>
+          <t>tamilpsd-2996.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="3" t="inlineStr">
+        <is>
+          <t>4171.psd</t>
+        </is>
+      </c>
+      <c r="B2488" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2997.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>4170.psd</t>
+        </is>
+      </c>
+      <c r="B2489" t="inlineStr">
+        <is>
+          <t>tamilpsd-2998.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="3" t="inlineStr">
+        <is>
+          <t>4169.psd</t>
+        </is>
+      </c>
+      <c r="B2490" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-2999.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>4168.psd</t>
+        </is>
+      </c>
+      <c r="B2491" t="inlineStr">
+        <is>
+          <t>tamilpsd-3000.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="3" t="inlineStr">
+        <is>
+          <t>4154.psd</t>
+        </is>
+      </c>
+      <c r="B2492" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3001.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>4153.psd</t>
+        </is>
+      </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>tamilpsd-3002.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="3" t="inlineStr">
+        <is>
+          <t>4152.psd</t>
+        </is>
+      </c>
+      <c r="B2494" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3003.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>4151.psd</t>
+        </is>
+      </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>tamilpsd-3004.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="3" t="inlineStr">
+        <is>
+          <t>4150.psd</t>
+        </is>
+      </c>
+      <c r="B2496" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3005.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>4149.psd</t>
+        </is>
+      </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>tamilpsd-3006.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="3" t="inlineStr">
+        <is>
+          <t>4148.psd</t>
+        </is>
+      </c>
+      <c r="B2498" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3007.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>4147.psd</t>
+        </is>
+      </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>tamilpsd-3008.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="3" t="inlineStr">
+        <is>
+          <t>4146.psd</t>
+        </is>
+      </c>
+      <c r="B2500" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3009.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>4145.psd</t>
+        </is>
+      </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>tamilpsd-3010.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="3" t="inlineStr">
+        <is>
+          <t>4144.psd</t>
+        </is>
+      </c>
+      <c r="B2502" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3011.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>4143.psd</t>
+        </is>
+      </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>tamilpsd-3012.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="3" t="inlineStr">
+        <is>
+          <t>4142.psd</t>
+        </is>
+      </c>
+      <c r="B2504" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3013.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>4141.psd</t>
+        </is>
+      </c>
+      <c r="B2505" t="inlineStr">
+        <is>
+          <t>tamilpsd-3014.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="3" t="inlineStr">
+        <is>
+          <t>4140.psd</t>
+        </is>
+      </c>
+      <c r="B2506" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3015.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>4139.psd</t>
+        </is>
+      </c>
+      <c r="B2507" t="inlineStr">
+        <is>
+          <t>tamilpsd-3016.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="3" t="inlineStr">
+        <is>
+          <t>4138.psd</t>
+        </is>
+      </c>
+      <c r="B2508" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3017.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>4137.psd</t>
+        </is>
+      </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>tamilpsd-3018.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="3" t="inlineStr">
+        <is>
+          <t>4136.psd</t>
+        </is>
+      </c>
+      <c r="B2510" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3019.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>4155.psd</t>
+        </is>
+      </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>tamilpsd-3020.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="3" t="inlineStr">
+        <is>
+          <t>4134.psd</t>
+        </is>
+      </c>
+      <c r="B2512" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3021.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>4133.psd</t>
+        </is>
+      </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>tamilpsd-3022.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="3" t="inlineStr">
+        <is>
+          <t>4132.psd</t>
+        </is>
+      </c>
+      <c r="B2514" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3023.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>4131.psd</t>
+        </is>
+      </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>tamilpsd-3024.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="3" t="inlineStr">
+        <is>
+          <t>4130.psd</t>
+        </is>
+      </c>
+      <c r="B2516" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3025.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>4129.psd</t>
+        </is>
+      </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>tamilpsd-3026.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="3" t="inlineStr">
+        <is>
+          <t>4128.psd</t>
+        </is>
+      </c>
+      <c r="B2518" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3027.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>4127.PSD</t>
+        </is>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>tamilpsd-3028.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="3" t="inlineStr">
+        <is>
+          <t>4126.psd</t>
+        </is>
+      </c>
+      <c r="B2520" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3029.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>4125.psd</t>
+        </is>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>tamilpsd-3030.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="3" t="inlineStr">
+        <is>
+          <t>4124.psd</t>
+        </is>
+      </c>
+      <c r="B2522" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3031.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>4123.psd</t>
+        </is>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>tamilpsd-3032.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="3" t="inlineStr">
+        <is>
+          <t>4122.psd</t>
+        </is>
+      </c>
+      <c r="B2524" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3033.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>4121.psd</t>
+        </is>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>tamilpsd-3034.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="3" t="inlineStr">
+        <is>
+          <t>4120.psd</t>
+        </is>
+      </c>
+      <c r="B2526" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3035.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>4119.psd</t>
+        </is>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>tamilpsd-3036.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="3" t="inlineStr">
+        <is>
+          <t>4118.psd</t>
+        </is>
+      </c>
+      <c r="B2528" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3037.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>4117.psd</t>
+        </is>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>tamilpsd-3038.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="3" t="inlineStr">
+        <is>
+          <t>4116.psd</t>
+        </is>
+      </c>
+      <c r="B2530" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3039.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>4115.psd</t>
+        </is>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>tamilpsd-3040.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="3" t="inlineStr">
+        <is>
+          <t>4114.psd</t>
+        </is>
+      </c>
+      <c r="B2532" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3041.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>4113.psd</t>
+        </is>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>tamilpsd-3042.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="3" t="inlineStr">
+        <is>
+          <t>4112.psd</t>
+        </is>
+      </c>
+      <c r="B2534" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3043.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>4111.psd</t>
+        </is>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>tamilpsd-3044.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="3" t="inlineStr">
+        <is>
+          <t>4110.psd</t>
+        </is>
+      </c>
+      <c r="B2536" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3045.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>4109.psd</t>
+        </is>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>tamilpsd-3046.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="3" t="inlineStr">
+        <is>
+          <t>4108.psd</t>
+        </is>
+      </c>
+      <c r="B2538" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3047.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>4107.psd</t>
+        </is>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>tamilpsd-3048.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" s="3" t="inlineStr">
+        <is>
+          <t>4106.psd</t>
+        </is>
+      </c>
+      <c r="B2540" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3049.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>4105.psd</t>
+        </is>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>tamilpsd-3050.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" s="3" t="inlineStr">
+        <is>
+          <t>4104.psd</t>
+        </is>
+      </c>
+      <c r="B2542" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3051.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>4103.psd</t>
+        </is>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>tamilpsd-3052.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="3" t="inlineStr">
+        <is>
+          <t>4102.psd</t>
+        </is>
+      </c>
+      <c r="B2544" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3053.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>4101.psd</t>
+        </is>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>tamilpsd-3054.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" s="3" t="inlineStr">
+        <is>
+          <t>4100.psd</t>
+        </is>
+      </c>
+      <c r="B2546" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3055.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>4099.psd</t>
+        </is>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>tamilpsd-3056.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" s="3" t="inlineStr">
+        <is>
+          <t>4098.psd</t>
+        </is>
+      </c>
+      <c r="B2548" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3057.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>4097.psd</t>
+        </is>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>tamilpsd-3058.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="3" t="inlineStr">
+        <is>
+          <t>4096.psd</t>
+        </is>
+      </c>
+      <c r="B2550" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3059.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="inlineStr">
+        <is>
+          <t>4095.psd</t>
+        </is>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>tamilpsd-3060.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" s="3" t="inlineStr">
+        <is>
+          <t>4094.psd</t>
+        </is>
+      </c>
+      <c r="B2552" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3061.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="inlineStr">
+        <is>
+          <t>4093.psd</t>
+        </is>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>tamilpsd-3062.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="3" t="inlineStr">
+        <is>
+          <t>4092.psd</t>
+        </is>
+      </c>
+      <c r="B2554" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3063.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="inlineStr">
+        <is>
+          <t>4091.psd</t>
+        </is>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>tamilpsd-3064.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" s="3" t="inlineStr">
+        <is>
+          <t>4090.psd</t>
+        </is>
+      </c>
+      <c r="B2556" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3065.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="inlineStr">
+        <is>
+          <t>4089.psd</t>
+        </is>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>tamilpsd-3066.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" s="3" t="inlineStr">
+        <is>
+          <t>4088.psd</t>
+        </is>
+      </c>
+      <c r="B2558" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3067.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="inlineStr">
+        <is>
+          <t>4087.psd</t>
+        </is>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>tamilpsd-3068.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="3" t="inlineStr">
+        <is>
+          <t>4086.psd</t>
+        </is>
+      </c>
+      <c r="B2560" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3069.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="inlineStr">
+        <is>
+          <t>4085.psd</t>
+        </is>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>tamilpsd-3070.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" s="3" t="inlineStr">
+        <is>
+          <t>4083.psd</t>
+        </is>
+      </c>
+      <c r="B2562" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3071.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="inlineStr">
+        <is>
+          <t>4084.psd</t>
+        </is>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>tamilpsd-3072.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="3" t="inlineStr">
+        <is>
+          <t>4082.psd</t>
+        </is>
+      </c>
+      <c r="B2564" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3073.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="inlineStr">
+        <is>
+          <t>4081.psd</t>
+        </is>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>tamilpsd-3074.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" s="3" t="inlineStr">
+        <is>
+          <t>4080.psd</t>
+        </is>
+      </c>
+      <c r="B2566" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3075.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="inlineStr">
+        <is>
+          <t>4079.psd</t>
+        </is>
+      </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>tamilpsd-3076.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="3" t="inlineStr">
+        <is>
+          <t>4078.psd</t>
+        </is>
+      </c>
+      <c r="B2568" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3077.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" t="inlineStr">
+        <is>
+          <t>4077.psd</t>
+        </is>
+      </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>tamilpsd-3078.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" s="3" t="inlineStr">
+        <is>
+          <t>4076.psd</t>
+        </is>
+      </c>
+      <c r="B2570" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3079.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="inlineStr">
+        <is>
+          <t>4075.psd</t>
+        </is>
+      </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>tamilpsd-3080.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" s="3" t="inlineStr">
+        <is>
+          <t>4074.psd</t>
+        </is>
+      </c>
+      <c r="B2572" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3081.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="inlineStr">
+        <is>
+          <t>4073.psd</t>
+        </is>
+      </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>tamilpsd-3082.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" s="3" t="inlineStr">
+        <is>
+          <t>4072.psd</t>
+        </is>
+      </c>
+      <c r="B2574" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3083.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="inlineStr">
+        <is>
+          <t>4135.psd</t>
+        </is>
+      </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>tamilpsd-3084.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" s="3" t="inlineStr">
+        <is>
+          <t>4070.psd</t>
+        </is>
+      </c>
+      <c r="B2576" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3085.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="inlineStr">
+        <is>
+          <t>4069.psd</t>
+        </is>
+      </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>tamilpsd-3086.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" s="3" t="inlineStr">
+        <is>
+          <t>4068.psd</t>
+        </is>
+      </c>
+      <c r="B2578" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3087.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="inlineStr">
+        <is>
+          <t>4067.psd</t>
+        </is>
+      </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>tamilpsd-3088.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" s="3" t="inlineStr">
+        <is>
+          <t>4066.psd</t>
+        </is>
+      </c>
+      <c r="B2580" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3089.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" t="inlineStr">
+        <is>
+          <t>4065.psd</t>
+        </is>
+      </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>tamilpsd-3090.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" s="3" t="inlineStr">
+        <is>
+          <t>4064.psd</t>
+        </is>
+      </c>
+      <c r="B2582" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3091.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" t="inlineStr">
+        <is>
+          <t>4063.psd</t>
+        </is>
+      </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>tamilpsd-3092.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" s="3" t="inlineStr">
+        <is>
+          <t>4062.psd</t>
+        </is>
+      </c>
+      <c r="B2584" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3093.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" t="inlineStr">
+        <is>
+          <t>4061.psd</t>
+        </is>
+      </c>
+      <c r="B2585" t="inlineStr">
+        <is>
+          <t>tamilpsd-3094.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" s="3" t="inlineStr">
+        <is>
+          <t>4060.psd</t>
+        </is>
+      </c>
+      <c r="B2586" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3095.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" t="inlineStr">
+        <is>
+          <t>4059.psd</t>
+        </is>
+      </c>
+      <c r="B2587" t="inlineStr">
+        <is>
+          <t>tamilpsd-3096.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" s="3" t="inlineStr">
+        <is>
+          <t>4058.psd</t>
+        </is>
+      </c>
+      <c r="B2588" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3097.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" t="inlineStr">
+        <is>
+          <t>4057.psd</t>
+        </is>
+      </c>
+      <c r="B2589" t="inlineStr">
+        <is>
+          <t>tamilpsd-3098.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" s="3" t="inlineStr">
+        <is>
+          <t>4056.psd</t>
+        </is>
+      </c>
+      <c r="B2590" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3099.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" t="inlineStr">
+        <is>
+          <t>4055.psd</t>
+        </is>
+      </c>
+      <c r="B2591" t="inlineStr">
+        <is>
+          <t>tamilpsd-3100.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" s="3" t="inlineStr">
+        <is>
+          <t>4054.psd</t>
+        </is>
+      </c>
+      <c r="B2592" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3101.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" t="inlineStr">
+        <is>
+          <t>4053.psd</t>
+        </is>
+      </c>
+      <c r="B2593" t="inlineStr">
+        <is>
+          <t>tamilpsd-3102.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" s="3" t="inlineStr">
+        <is>
+          <t>4052.psd</t>
+        </is>
+      </c>
+      <c r="B2594" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3103.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" t="inlineStr">
+        <is>
+          <t>4051.psd</t>
+        </is>
+      </c>
+      <c r="B2595" t="inlineStr">
+        <is>
+          <t>tamilpsd-3104.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" s="3" t="inlineStr">
+        <is>
+          <t>4050.psd</t>
+        </is>
+      </c>
+      <c r="B2596" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3105.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" t="inlineStr">
+        <is>
+          <t>4049.psd</t>
+        </is>
+      </c>
+      <c r="B2597" t="inlineStr">
+        <is>
+          <t>tamilpsd-3106.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" s="3" t="inlineStr">
+        <is>
+          <t>4048.psd</t>
+        </is>
+      </c>
+      <c r="B2598" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3107.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" t="inlineStr">
+        <is>
+          <t>4047.psd</t>
+        </is>
+      </c>
+      <c r="B2599" t="inlineStr">
+        <is>
+          <t>tamilpsd-3108.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" s="3" t="inlineStr">
+        <is>
+          <t>4071.psd</t>
+        </is>
+      </c>
+      <c r="B2600" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3109.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" t="inlineStr">
+        <is>
+          <t>4044.psd</t>
+        </is>
+      </c>
+      <c r="B2601" t="inlineStr">
+        <is>
+          <t>tamilpsd-3110.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" s="3" t="inlineStr">
+        <is>
+          <t>4043.psd</t>
+        </is>
+      </c>
+      <c r="B2602" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3111.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2603">
+      <c r="A2603" t="inlineStr">
+        <is>
+          <t>4042.psd</t>
+        </is>
+      </c>
+      <c r="B2603" t="inlineStr">
+        <is>
+          <t>tamilpsd-3112.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2604">
+      <c r="A2604" s="3" t="inlineStr">
+        <is>
+          <t>4041.psd</t>
+        </is>
+      </c>
+      <c r="B2604" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3113.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="inlineStr">
+        <is>
+          <t>4040.psd</t>
+        </is>
+      </c>
+      <c r="B2605" t="inlineStr">
+        <is>
+          <t>tamilpsd-3114.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" s="3" t="inlineStr">
+        <is>
+          <t>4039.psd</t>
+        </is>
+      </c>
+      <c r="B2606" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3115.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2607">
+      <c r="A2607" t="inlineStr">
+        <is>
+          <t>4038.psd</t>
+        </is>
+      </c>
+      <c r="B2607" t="inlineStr">
+        <is>
+          <t>tamilpsd-3116.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" s="3" t="inlineStr">
+        <is>
+          <t>4037.psd</t>
+        </is>
+      </c>
+      <c r="B2608" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3117.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="inlineStr">
+        <is>
+          <t>4036.psd</t>
+        </is>
+      </c>
+      <c r="B2609" t="inlineStr">
+        <is>
+          <t>tamilpsd-3118.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2610">
+      <c r="A2610" s="3" t="inlineStr">
+        <is>
+          <t>4035.psd</t>
+        </is>
+      </c>
+      <c r="B2610" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3119.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2611">
+      <c r="A2611" t="inlineStr">
+        <is>
+          <t>4034.psd</t>
+        </is>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>tamilpsd-3120.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2612">
+      <c r="A2612" s="3" t="inlineStr">
+        <is>
+          <t>4033.psd</t>
+        </is>
+      </c>
+      <c r="B2612" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3121.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2613">
+      <c r="A2613" t="inlineStr">
+        <is>
+          <t>4032.psd</t>
+        </is>
+      </c>
+      <c r="B2613" t="inlineStr">
+        <is>
+          <t>tamilpsd-3122.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2614">
+      <c r="A2614" s="3" t="inlineStr">
+        <is>
+          <t>4031.psd</t>
+        </is>
+      </c>
+      <c r="B2614" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3123.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2615">
+      <c r="A2615" t="inlineStr">
+        <is>
+          <t>4030.psd</t>
+        </is>
+      </c>
+      <c r="B2615" t="inlineStr">
+        <is>
+          <t>tamilpsd-3124.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" s="3" t="inlineStr">
+        <is>
+          <t>4029.psd</t>
+        </is>
+      </c>
+      <c r="B2616" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3125.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" t="inlineStr">
+        <is>
+          <t>4028.psd</t>
+        </is>
+      </c>
+      <c r="B2617" t="inlineStr">
+        <is>
+          <t>tamilpsd-3126.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2618">
+      <c r="A2618" s="3" t="inlineStr">
+        <is>
+          <t>4027.psd</t>
+        </is>
+      </c>
+      <c r="B2618" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3127.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2619">
+      <c r="A2619" t="inlineStr">
+        <is>
+          <t>4026.psd</t>
+        </is>
+      </c>
+      <c r="B2619" t="inlineStr">
+        <is>
+          <t>tamilpsd-3128.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2620">
+      <c r="A2620" s="3" t="inlineStr">
+        <is>
+          <t>4025.psd</t>
+        </is>
+      </c>
+      <c r="B2620" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3129.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2621">
+      <c r="A2621" t="inlineStr">
+        <is>
+          <t>4024.psd</t>
+        </is>
+      </c>
+      <c r="B2621" t="inlineStr">
+        <is>
+          <t>tamilpsd-3130.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2622">
+      <c r="A2622" s="3" t="inlineStr">
+        <is>
+          <t>4023.psd</t>
+        </is>
+      </c>
+      <c r="B2622" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3131.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2623">
+      <c r="A2623" t="inlineStr">
+        <is>
+          <t>4022.psd</t>
+        </is>
+      </c>
+      <c r="B2623" t="inlineStr">
+        <is>
+          <t>tamilpsd-3132.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2624">
+      <c r="A2624" s="3" t="inlineStr">
+        <is>
+          <t>4021.psd</t>
+        </is>
+      </c>
+      <c r="B2624" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3133.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2625">
+      <c r="A2625" t="inlineStr">
+        <is>
+          <t>4020.psd</t>
+        </is>
+      </c>
+      <c r="B2625" t="inlineStr">
+        <is>
+          <t>tamilpsd-3134.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" s="3" t="inlineStr">
+        <is>
+          <t>4019.psd</t>
+        </is>
+      </c>
+      <c r="B2626" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3135.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2627">
+      <c r="A2627" t="inlineStr">
+        <is>
+          <t>4018.psd</t>
+        </is>
+      </c>
+      <c r="B2627" t="inlineStr">
+        <is>
+          <t>tamilpsd-3136.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2628">
+      <c r="A2628" s="3" t="inlineStr">
+        <is>
+          <t>4017.psd</t>
+        </is>
+      </c>
+      <c r="B2628" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3137.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2629">
+      <c r="A2629" t="inlineStr">
+        <is>
+          <t>4016.psd</t>
+        </is>
+      </c>
+      <c r="B2629" t="inlineStr">
+        <is>
+          <t>tamilpsd-3138.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2630">
+      <c r="A2630" s="3" t="inlineStr">
+        <is>
+          <t>4015.psd</t>
+        </is>
+      </c>
+      <c r="B2630" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3139.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2631">
+      <c r="A2631" t="inlineStr">
+        <is>
+          <t>4014.psd</t>
+        </is>
+      </c>
+      <c r="B2631" t="inlineStr">
+        <is>
+          <t>tamilpsd-3140.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" s="3" t="inlineStr">
+        <is>
+          <t>4013.psd</t>
+        </is>
+      </c>
+      <c r="B2632" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3141.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2633">
+      <c r="A2633" t="inlineStr">
+        <is>
+          <t>4012.psd</t>
+        </is>
+      </c>
+      <c r="B2633" t="inlineStr">
+        <is>
+          <t>tamilpsd-3142.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2634">
+      <c r="A2634" s="3" t="inlineStr">
+        <is>
+          <t>4011.psd</t>
+        </is>
+      </c>
+      <c r="B2634" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-3143.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2634"/>
+  <dimension ref="A1:B2961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -31705,6 +31705,3930 @@
         </is>
       </c>
     </row>
+    <row r="2635">
+      <c r="A2635" t="inlineStr">
+        <is>
+          <t>4554.psd</t>
+        </is>
+      </c>
+      <c r="B2635" t="inlineStr">
+        <is>
+          <t>tamilpsd-5452.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2636">
+      <c r="A2636" s="3" t="inlineStr">
+        <is>
+          <t>4010.psd</t>
+        </is>
+      </c>
+      <c r="B2636" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5453.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2637">
+      <c r="A2637" t="inlineStr">
+        <is>
+          <t>4009.psd</t>
+        </is>
+      </c>
+      <c r="B2637" t="inlineStr">
+        <is>
+          <t>tamilpsd-5454.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2638">
+      <c r="A2638" s="3" t="inlineStr">
+        <is>
+          <t>4008.psd</t>
+        </is>
+      </c>
+      <c r="B2638" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5455.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2639">
+      <c r="A2639" t="inlineStr">
+        <is>
+          <t>4007.psd</t>
+        </is>
+      </c>
+      <c r="B2639" t="inlineStr">
+        <is>
+          <t>tamilpsd-5456.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2640">
+      <c r="A2640" s="3" t="inlineStr">
+        <is>
+          <t>4006.psd</t>
+        </is>
+      </c>
+      <c r="B2640" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5457.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2641">
+      <c r="A2641" t="inlineStr">
+        <is>
+          <t>4005.psd</t>
+        </is>
+      </c>
+      <c r="B2641" t="inlineStr">
+        <is>
+          <t>tamilpsd-5458.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2642">
+      <c r="A2642" s="3" t="inlineStr">
+        <is>
+          <t>4004.psd</t>
+        </is>
+      </c>
+      <c r="B2642" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5459.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" t="inlineStr">
+        <is>
+          <t>4003.psd</t>
+        </is>
+      </c>
+      <c r="B2643" t="inlineStr">
+        <is>
+          <t>tamilpsd-5460.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" s="3" t="inlineStr">
+        <is>
+          <t>4002.psd</t>
+        </is>
+      </c>
+      <c r="B2644" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5461.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2645">
+      <c r="A2645" t="inlineStr">
+        <is>
+          <t>4001.psd</t>
+        </is>
+      </c>
+      <c r="B2645" t="inlineStr">
+        <is>
+          <t>tamilpsd-5462.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" s="3" t="inlineStr">
+        <is>
+          <t>4000.psd</t>
+        </is>
+      </c>
+      <c r="B2646" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5463.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" t="inlineStr">
+        <is>
+          <t>3999.psd</t>
+        </is>
+      </c>
+      <c r="B2647" t="inlineStr">
+        <is>
+          <t>tamilpsd-5464.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2648">
+      <c r="A2648" s="3" t="inlineStr">
+        <is>
+          <t>3998.psd</t>
+        </is>
+      </c>
+      <c r="B2648" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5465.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" t="inlineStr">
+        <is>
+          <t>3997.psd</t>
+        </is>
+      </c>
+      <c r="B2649" t="inlineStr">
+        <is>
+          <t>tamilpsd-5466.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" s="3" t="inlineStr">
+        <is>
+          <t>4046.psd</t>
+        </is>
+      </c>
+      <c r="B2650" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5467.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2651">
+      <c r="A2651" t="inlineStr">
+        <is>
+          <t>3996.psd</t>
+        </is>
+      </c>
+      <c r="B2651" t="inlineStr">
+        <is>
+          <t>tamilpsd-5468.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" s="3" t="inlineStr">
+        <is>
+          <t>3995.psd</t>
+        </is>
+      </c>
+      <c r="B2652" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5469.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" t="inlineStr">
+        <is>
+          <t>3994.psd</t>
+        </is>
+      </c>
+      <c r="B2653" t="inlineStr">
+        <is>
+          <t>tamilpsd-5470.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" s="3" t="inlineStr">
+        <is>
+          <t>3993.psd</t>
+        </is>
+      </c>
+      <c r="B2654" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5471.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" t="inlineStr">
+        <is>
+          <t>3992.psd</t>
+        </is>
+      </c>
+      <c r="B2655" t="inlineStr">
+        <is>
+          <t>tamilpsd-5472.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" s="3" t="inlineStr">
+        <is>
+          <t>3991.psd</t>
+        </is>
+      </c>
+      <c r="B2656" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5473.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2657">
+      <c r="A2657" t="inlineStr">
+        <is>
+          <t>3990.psd</t>
+        </is>
+      </c>
+      <c r="B2657" t="inlineStr">
+        <is>
+          <t>tamilpsd-5474.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2658">
+      <c r="A2658" s="3" t="inlineStr">
+        <is>
+          <t>3989.psd</t>
+        </is>
+      </c>
+      <c r="B2658" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5475.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2659">
+      <c r="A2659" t="inlineStr">
+        <is>
+          <t>3988.psd</t>
+        </is>
+      </c>
+      <c r="B2659" t="inlineStr">
+        <is>
+          <t>tamilpsd-5476.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2660">
+      <c r="A2660" s="3" t="inlineStr">
+        <is>
+          <t>3987.psd</t>
+        </is>
+      </c>
+      <c r="B2660" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5477.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" t="inlineStr">
+        <is>
+          <t>3986.psd</t>
+        </is>
+      </c>
+      <c r="B2661" t="inlineStr">
+        <is>
+          <t>tamilpsd-5478.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2662">
+      <c r="A2662" s="3" t="inlineStr">
+        <is>
+          <t>3985.psd</t>
+        </is>
+      </c>
+      <c r="B2662" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5479.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="inlineStr">
+        <is>
+          <t>3984.psd</t>
+        </is>
+      </c>
+      <c r="B2663" t="inlineStr">
+        <is>
+          <t>tamilpsd-5480.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2664">
+      <c r="A2664" s="3" t="inlineStr">
+        <is>
+          <t>3983.psd</t>
+        </is>
+      </c>
+      <c r="B2664" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5481.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2665">
+      <c r="A2665" t="inlineStr">
+        <is>
+          <t>3982.PSD</t>
+        </is>
+      </c>
+      <c r="B2665" t="inlineStr">
+        <is>
+          <t>tamilpsd-5482.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2666">
+      <c r="A2666" s="3" t="inlineStr">
+        <is>
+          <t>3981.psd</t>
+        </is>
+      </c>
+      <c r="B2666" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5483.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2667">
+      <c r="A2667" t="inlineStr">
+        <is>
+          <t>3980.psd</t>
+        </is>
+      </c>
+      <c r="B2667" t="inlineStr">
+        <is>
+          <t>tamilpsd-5484.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" s="3" t="inlineStr">
+        <is>
+          <t>3979.psd</t>
+        </is>
+      </c>
+      <c r="B2668" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5485.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2669">
+      <c r="A2669" t="inlineStr">
+        <is>
+          <t>3978.psd</t>
+        </is>
+      </c>
+      <c r="B2669" t="inlineStr">
+        <is>
+          <t>tamilpsd-5486.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2670">
+      <c r="A2670" s="3" t="inlineStr">
+        <is>
+          <t>3977.psd</t>
+        </is>
+      </c>
+      <c r="B2670" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5487.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" t="inlineStr">
+        <is>
+          <t>3976.psd</t>
+        </is>
+      </c>
+      <c r="B2671" t="inlineStr">
+        <is>
+          <t>tamilpsd-5488.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" s="3" t="inlineStr">
+        <is>
+          <t>3975.psd</t>
+        </is>
+      </c>
+      <c r="B2672" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5489.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2673">
+      <c r="A2673" t="inlineStr">
+        <is>
+          <t>3974.psd</t>
+        </is>
+      </c>
+      <c r="B2673" t="inlineStr">
+        <is>
+          <t>tamilpsd-5490.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" s="3" t="inlineStr">
+        <is>
+          <t>3973.psd</t>
+        </is>
+      </c>
+      <c r="B2674" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5491.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2675">
+      <c r="A2675" t="inlineStr">
+        <is>
+          <t>3972.psd</t>
+        </is>
+      </c>
+      <c r="B2675" t="inlineStr">
+        <is>
+          <t>tamilpsd-5492.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2676">
+      <c r="A2676" s="3" t="inlineStr">
+        <is>
+          <t>3971.psd</t>
+        </is>
+      </c>
+      <c r="B2676" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5493.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2677">
+      <c r="A2677" t="inlineStr">
+        <is>
+          <t>3970.psd</t>
+        </is>
+      </c>
+      <c r="B2677" t="inlineStr">
+        <is>
+          <t>tamilpsd-5494.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2678">
+      <c r="A2678" s="3" t="inlineStr">
+        <is>
+          <t>3969.psd</t>
+        </is>
+      </c>
+      <c r="B2678" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5495.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" t="inlineStr">
+        <is>
+          <t>3968.psd</t>
+        </is>
+      </c>
+      <c r="B2679" t="inlineStr">
+        <is>
+          <t>tamilpsd-5496.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2680">
+      <c r="A2680" s="3" t="inlineStr">
+        <is>
+          <t>3967.psd</t>
+        </is>
+      </c>
+      <c r="B2680" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5497.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2681">
+      <c r="A2681" t="inlineStr">
+        <is>
+          <t>3966.psd</t>
+        </is>
+      </c>
+      <c r="B2681" t="inlineStr">
+        <is>
+          <t>tamilpsd-5498.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" s="3" t="inlineStr">
+        <is>
+          <t>3965.psd</t>
+        </is>
+      </c>
+      <c r="B2682" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5499.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2683">
+      <c r="A2683" t="inlineStr">
+        <is>
+          <t>3964.psd</t>
+        </is>
+      </c>
+      <c r="B2683" t="inlineStr">
+        <is>
+          <t>tamilpsd-5500.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" s="3" t="inlineStr">
+        <is>
+          <t>3963.psd</t>
+        </is>
+      </c>
+      <c r="B2684" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5501.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" t="inlineStr">
+        <is>
+          <t>3962.psd</t>
+        </is>
+      </c>
+      <c r="B2685" t="inlineStr">
+        <is>
+          <t>tamilpsd-5502.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" s="3" t="inlineStr">
+        <is>
+          <t>3961.psd</t>
+        </is>
+      </c>
+      <c r="B2686" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5503.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2687">
+      <c r="A2687" t="inlineStr">
+        <is>
+          <t>3960.psd</t>
+        </is>
+      </c>
+      <c r="B2687" t="inlineStr">
+        <is>
+          <t>tamilpsd-5504.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2688">
+      <c r="A2688" s="3" t="inlineStr">
+        <is>
+          <t>3959.psd</t>
+        </is>
+      </c>
+      <c r="B2688" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5505.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" t="inlineStr">
+        <is>
+          <t>3958.psd</t>
+        </is>
+      </c>
+      <c r="B2689" t="inlineStr">
+        <is>
+          <t>tamilpsd-5506.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" s="3" t="inlineStr">
+        <is>
+          <t>3957.psd</t>
+        </is>
+      </c>
+      <c r="B2690" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5507.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" t="inlineStr">
+        <is>
+          <t>3956.psd</t>
+        </is>
+      </c>
+      <c r="B2691" t="inlineStr">
+        <is>
+          <t>tamilpsd-5508.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" s="3" t="inlineStr">
+        <is>
+          <t>3955.psd</t>
+        </is>
+      </c>
+      <c r="B2692" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5509.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" t="inlineStr">
+        <is>
+          <t>3954.psd</t>
+        </is>
+      </c>
+      <c r="B2693" t="inlineStr">
+        <is>
+          <t>tamilpsd-5510.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" s="3" t="inlineStr">
+        <is>
+          <t>3953.psd</t>
+        </is>
+      </c>
+      <c r="B2694" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5511.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" t="inlineStr">
+        <is>
+          <t>3952.psd</t>
+        </is>
+      </c>
+      <c r="B2695" t="inlineStr">
+        <is>
+          <t>tamilpsd-5512.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" s="3" t="inlineStr">
+        <is>
+          <t>3951.psd</t>
+        </is>
+      </c>
+      <c r="B2696" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5513.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" t="inlineStr">
+        <is>
+          <t>3950.psd</t>
+        </is>
+      </c>
+      <c r="B2697" t="inlineStr">
+        <is>
+          <t>tamilpsd-5514.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2698">
+      <c r="A2698" s="3" t="inlineStr">
+        <is>
+          <t>3949.psd</t>
+        </is>
+      </c>
+      <c r="B2698" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5515.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" t="inlineStr">
+        <is>
+          <t>3948.psd</t>
+        </is>
+      </c>
+      <c r="B2699" t="inlineStr">
+        <is>
+          <t>tamilpsd-5516.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" s="3" t="inlineStr">
+        <is>
+          <t>3947.PSD</t>
+        </is>
+      </c>
+      <c r="B2700" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5517.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" t="inlineStr">
+        <is>
+          <t>3465.psd</t>
+        </is>
+      </c>
+      <c r="B2701" t="inlineStr">
+        <is>
+          <t>tamilpsd-5518.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" s="3" t="inlineStr">
+        <is>
+          <t>3463.psd</t>
+        </is>
+      </c>
+      <c r="B2702" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5519.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2703">
+      <c r="A2703" t="inlineStr">
+        <is>
+          <t>3462.psd</t>
+        </is>
+      </c>
+      <c r="B2703" t="inlineStr">
+        <is>
+          <t>tamilpsd-5520.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" s="3" t="inlineStr">
+        <is>
+          <t>3461.psd</t>
+        </is>
+      </c>
+      <c r="B2704" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5521.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" t="inlineStr">
+        <is>
+          <t>3460.psd</t>
+        </is>
+      </c>
+      <c r="B2705" t="inlineStr">
+        <is>
+          <t>tamilpsd-5522.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" s="3" t="inlineStr">
+        <is>
+          <t>3459.psd</t>
+        </is>
+      </c>
+      <c r="B2706" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5523.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" t="inlineStr">
+        <is>
+          <t>3458.psd</t>
+        </is>
+      </c>
+      <c r="B2707" t="inlineStr">
+        <is>
+          <t>tamilpsd-5524.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" s="3" t="inlineStr">
+        <is>
+          <t>3456.psd</t>
+        </is>
+      </c>
+      <c r="B2708" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5525.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" t="inlineStr">
+        <is>
+          <t>3454.psd</t>
+        </is>
+      </c>
+      <c r="B2709" t="inlineStr">
+        <is>
+          <t>tamilpsd-5526.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" s="3" t="inlineStr">
+        <is>
+          <t>3453.psd</t>
+        </is>
+      </c>
+      <c r="B2710" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5527.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2711">
+      <c r="A2711" t="inlineStr">
+        <is>
+          <t>3452.psd</t>
+        </is>
+      </c>
+      <c r="B2711" t="inlineStr">
+        <is>
+          <t>tamilpsd-5528.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="A2712" s="3" t="inlineStr">
+        <is>
+          <t>3451.psd</t>
+        </is>
+      </c>
+      <c r="B2712" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5529.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2713">
+      <c r="A2713" t="inlineStr">
+        <is>
+          <t>3450.psd</t>
+        </is>
+      </c>
+      <c r="B2713" t="inlineStr">
+        <is>
+          <t>tamilpsd-5530.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="A2714" s="3" t="inlineStr">
+        <is>
+          <t>3449.psd</t>
+        </is>
+      </c>
+      <c r="B2714" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5531.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2715">
+      <c r="A2715" t="inlineStr">
+        <is>
+          <t>3447.psd</t>
+        </is>
+      </c>
+      <c r="B2715" t="inlineStr">
+        <is>
+          <t>tamilpsd-5532.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="A2716" s="3" t="inlineStr">
+        <is>
+          <t>3446.psd</t>
+        </is>
+      </c>
+      <c r="B2716" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5533.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="inlineStr">
+        <is>
+          <t>3445.psd</t>
+        </is>
+      </c>
+      <c r="B2717" t="inlineStr">
+        <is>
+          <t>tamilpsd-5534.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" s="3" t="inlineStr">
+        <is>
+          <t>3443.psd</t>
+        </is>
+      </c>
+      <c r="B2718" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5535.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="inlineStr">
+        <is>
+          <t>3442.psd</t>
+        </is>
+      </c>
+      <c r="B2719" t="inlineStr">
+        <is>
+          <t>tamilpsd-5536.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="3" t="inlineStr">
+        <is>
+          <t>3441.psd</t>
+        </is>
+      </c>
+      <c r="B2720" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5537.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="inlineStr">
+        <is>
+          <t>3440.psd</t>
+        </is>
+      </c>
+      <c r="B2721" t="inlineStr">
+        <is>
+          <t>tamilpsd-5538.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="3" t="inlineStr">
+        <is>
+          <t>3439.psd</t>
+        </is>
+      </c>
+      <c r="B2722" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5539.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="inlineStr">
+        <is>
+          <t>3438.psd</t>
+        </is>
+      </c>
+      <c r="B2723" t="inlineStr">
+        <is>
+          <t>tamilpsd-5540.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="3" t="inlineStr">
+        <is>
+          <t>3437.psd</t>
+        </is>
+      </c>
+      <c r="B2724" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5541.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="A2725" t="inlineStr">
+        <is>
+          <t>3436.psd</t>
+        </is>
+      </c>
+      <c r="B2725" t="inlineStr">
+        <is>
+          <t>tamilpsd-5542.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="3" t="inlineStr">
+        <is>
+          <t>3435.psd</t>
+        </is>
+      </c>
+      <c r="B2726" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5543.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" t="inlineStr">
+        <is>
+          <t>3434.psd</t>
+        </is>
+      </c>
+      <c r="B2727" t="inlineStr">
+        <is>
+          <t>tamilpsd-5544.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="3" t="inlineStr">
+        <is>
+          <t>3433.psd</t>
+        </is>
+      </c>
+      <c r="B2728" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5545.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" t="inlineStr">
+        <is>
+          <t>3432.psd</t>
+        </is>
+      </c>
+      <c r="B2729" t="inlineStr">
+        <is>
+          <t>tamilpsd-5546.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" s="3" t="inlineStr">
+        <is>
+          <t>3431.psd</t>
+        </is>
+      </c>
+      <c r="B2730" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5547.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" t="inlineStr">
+        <is>
+          <t>3430.psd</t>
+        </is>
+      </c>
+      <c r="B2731" t="inlineStr">
+        <is>
+          <t>tamilpsd-5548.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="3" t="inlineStr">
+        <is>
+          <t>3429.psd</t>
+        </is>
+      </c>
+      <c r="B2732" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5549.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" t="inlineStr">
+        <is>
+          <t>3428.psd</t>
+        </is>
+      </c>
+      <c r="B2733" t="inlineStr">
+        <is>
+          <t>tamilpsd-5550.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" s="3" t="inlineStr">
+        <is>
+          <t>3427.psd</t>
+        </is>
+      </c>
+      <c r="B2734" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5551.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" t="inlineStr">
+        <is>
+          <t>3426.psd</t>
+        </is>
+      </c>
+      <c r="B2735" t="inlineStr">
+        <is>
+          <t>tamilpsd-5552.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="3" t="inlineStr">
+        <is>
+          <t>3425.psd</t>
+        </is>
+      </c>
+      <c r="B2736" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5553.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" t="inlineStr">
+        <is>
+          <t>3423.psd</t>
+        </is>
+      </c>
+      <c r="B2737" t="inlineStr">
+        <is>
+          <t>tamilpsd-5554.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="3" t="inlineStr">
+        <is>
+          <t>3422.psd</t>
+        </is>
+      </c>
+      <c r="B2738" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5555.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" t="inlineStr">
+        <is>
+          <t>3421.psd</t>
+        </is>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>tamilpsd-5556.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" s="3" t="inlineStr">
+        <is>
+          <t>3420.psd</t>
+        </is>
+      </c>
+      <c r="B2740" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5557.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" t="inlineStr">
+        <is>
+          <t>3419.psd</t>
+        </is>
+      </c>
+      <c r="B2741" t="inlineStr">
+        <is>
+          <t>tamilpsd-5558.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" s="3" t="inlineStr">
+        <is>
+          <t>3418.psd</t>
+        </is>
+      </c>
+      <c r="B2742" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5559.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" t="inlineStr">
+        <is>
+          <t>3417.psd</t>
+        </is>
+      </c>
+      <c r="B2743" t="inlineStr">
+        <is>
+          <t>tamilpsd-5560.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="3" t="inlineStr">
+        <is>
+          <t>3416.psd</t>
+        </is>
+      </c>
+      <c r="B2744" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5561.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="inlineStr">
+        <is>
+          <t>3415.psd</t>
+        </is>
+      </c>
+      <c r="B2745" t="inlineStr">
+        <is>
+          <t>tamilpsd-5562.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" s="3" t="inlineStr">
+        <is>
+          <t>3414.psd</t>
+        </is>
+      </c>
+      <c r="B2746" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5563.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="inlineStr">
+        <is>
+          <t>3413.psd</t>
+        </is>
+      </c>
+      <c r="B2747" t="inlineStr">
+        <is>
+          <t>tamilpsd-5564.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" s="3" t="inlineStr">
+        <is>
+          <t>3412.psd</t>
+        </is>
+      </c>
+      <c r="B2748" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5565.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="inlineStr">
+        <is>
+          <t>3411.psd</t>
+        </is>
+      </c>
+      <c r="B2749" t="inlineStr">
+        <is>
+          <t>tamilpsd-5566.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" s="3" t="inlineStr">
+        <is>
+          <t>3410.psd</t>
+        </is>
+      </c>
+      <c r="B2750" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5567.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>3409.psd</t>
+        </is>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>tamilpsd-5568.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" s="3" t="inlineStr">
+        <is>
+          <t>3408.psd</t>
+        </is>
+      </c>
+      <c r="B2752" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5569.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>3407.psd</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>tamilpsd-5570.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" s="3" t="inlineStr">
+        <is>
+          <t>3405.psd</t>
+        </is>
+      </c>
+      <c r="B2754" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5571.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>3404.psd</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>tamilpsd-5572.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" s="3" t="inlineStr">
+        <is>
+          <t>3403.psd</t>
+        </is>
+      </c>
+      <c r="B2756" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5573.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>3402.psd</t>
+        </is>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>tamilpsd-5574.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2758">
+      <c r="A2758" s="3" t="inlineStr">
+        <is>
+          <t>3401.psd</t>
+        </is>
+      </c>
+      <c r="B2758" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5575.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>3400.psd</t>
+        </is>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>tamilpsd-5576.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2760">
+      <c r="A2760" s="3" t="inlineStr">
+        <is>
+          <t>3399.psd</t>
+        </is>
+      </c>
+      <c r="B2760" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5577.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>3398.psd</t>
+        </is>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>tamilpsd-5578.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="A2762" s="3" t="inlineStr">
+        <is>
+          <t>3397.psd</t>
+        </is>
+      </c>
+      <c r="B2762" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5579.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>3945.PSD</t>
+        </is>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>tamilpsd-5580.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="A2764" s="3" t="inlineStr">
+        <is>
+          <t>3944.psd</t>
+        </is>
+      </c>
+      <c r="B2764" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5581.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>3943.psd</t>
+        </is>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>tamilpsd-5582.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="A2766" s="3" t="inlineStr">
+        <is>
+          <t>3942.psd</t>
+        </is>
+      </c>
+      <c r="B2766" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5583.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>3941.psd</t>
+        </is>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>tamilpsd-5584.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="A2768" s="3" t="inlineStr">
+        <is>
+          <t>3940.psd</t>
+        </is>
+      </c>
+      <c r="B2768" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5585.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="inlineStr">
+        <is>
+          <t>3939.psd</t>
+        </is>
+      </c>
+      <c r="B2769" t="inlineStr">
+        <is>
+          <t>tamilpsd-5586.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="A2770" s="3" t="inlineStr">
+        <is>
+          <t>3938.psd</t>
+        </is>
+      </c>
+      <c r="B2770" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5587.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="inlineStr">
+        <is>
+          <t>3937.psd</t>
+        </is>
+      </c>
+      <c r="B2771" t="inlineStr">
+        <is>
+          <t>tamilpsd-5588.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" s="3" t="inlineStr">
+        <is>
+          <t>3935.psd</t>
+        </is>
+      </c>
+      <c r="B2772" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5589.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>3936.psd</t>
+        </is>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>tamilpsd-5590.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" s="3" t="inlineStr">
+        <is>
+          <t>3934.psd</t>
+        </is>
+      </c>
+      <c r="B2774" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5591.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>3933.psd</t>
+        </is>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>tamilpsd-5592.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" s="3" t="inlineStr">
+        <is>
+          <t>3932.psd</t>
+        </is>
+      </c>
+      <c r="B2776" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5593.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="inlineStr">
+        <is>
+          <t>3931.psd</t>
+        </is>
+      </c>
+      <c r="B2777" t="inlineStr">
+        <is>
+          <t>tamilpsd-5594.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" s="3" t="inlineStr">
+        <is>
+          <t>3930.psd</t>
+        </is>
+      </c>
+      <c r="B2778" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5595.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="inlineStr">
+        <is>
+          <t>3929.psd</t>
+        </is>
+      </c>
+      <c r="B2779" t="inlineStr">
+        <is>
+          <t>tamilpsd-5596.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" s="3" t="inlineStr">
+        <is>
+          <t>3928.psd</t>
+        </is>
+      </c>
+      <c r="B2780" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5597.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="inlineStr">
+        <is>
+          <t>3927.psd</t>
+        </is>
+      </c>
+      <c r="B2781" t="inlineStr">
+        <is>
+          <t>tamilpsd-5598.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" s="3" t="inlineStr">
+        <is>
+          <t>3926.psd</t>
+        </is>
+      </c>
+      <c r="B2782" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5599.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="inlineStr">
+        <is>
+          <t>3925.psd</t>
+        </is>
+      </c>
+      <c r="B2783" t="inlineStr">
+        <is>
+          <t>tamilpsd-5600.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" s="3" t="inlineStr">
+        <is>
+          <t>3946.PSD</t>
+        </is>
+      </c>
+      <c r="B2784" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5601.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="inlineStr">
+        <is>
+          <t>3923.psd</t>
+        </is>
+      </c>
+      <c r="B2785" t="inlineStr">
+        <is>
+          <t>tamilpsd-5602.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" s="3" t="inlineStr">
+        <is>
+          <t>3922.psd</t>
+        </is>
+      </c>
+      <c r="B2786" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5603.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="inlineStr">
+        <is>
+          <t>3921.psd</t>
+        </is>
+      </c>
+      <c r="B2787" t="inlineStr">
+        <is>
+          <t>tamilpsd-5604.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" s="3" t="inlineStr">
+        <is>
+          <t>3920.psd</t>
+        </is>
+      </c>
+      <c r="B2788" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5605.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="inlineStr">
+        <is>
+          <t>3919.psd</t>
+        </is>
+      </c>
+      <c r="B2789" t="inlineStr">
+        <is>
+          <t>tamilpsd-5606.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" s="3" t="inlineStr">
+        <is>
+          <t>3918.psd</t>
+        </is>
+      </c>
+      <c r="B2790" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5607.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="inlineStr">
+        <is>
+          <t>3917.psd</t>
+        </is>
+      </c>
+      <c r="B2791" t="inlineStr">
+        <is>
+          <t>tamilpsd-5608.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" s="3" t="inlineStr">
+        <is>
+          <t>3916.psd</t>
+        </is>
+      </c>
+      <c r="B2792" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5609.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="inlineStr">
+        <is>
+          <t>3915.psd</t>
+        </is>
+      </c>
+      <c r="B2793" t="inlineStr">
+        <is>
+          <t>tamilpsd-5610.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" s="3" t="inlineStr">
+        <is>
+          <t>3914.psd</t>
+        </is>
+      </c>
+      <c r="B2794" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5611.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="inlineStr">
+        <is>
+          <t>3913.psd</t>
+        </is>
+      </c>
+      <c r="B2795" t="inlineStr">
+        <is>
+          <t>tamilpsd-5612.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" s="3" t="inlineStr">
+        <is>
+          <t>3912.psd</t>
+        </is>
+      </c>
+      <c r="B2796" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5613.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="inlineStr">
+        <is>
+          <t>3911.psd</t>
+        </is>
+      </c>
+      <c r="B2797" t="inlineStr">
+        <is>
+          <t>tamilpsd-5614.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" s="3" t="inlineStr">
+        <is>
+          <t>3910.psd</t>
+        </is>
+      </c>
+      <c r="B2798" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5615.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="inlineStr">
+        <is>
+          <t>3908.psd</t>
+        </is>
+      </c>
+      <c r="B2799" t="inlineStr">
+        <is>
+          <t>tamilpsd-5616.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" s="3" t="inlineStr">
+        <is>
+          <t>3907.psd</t>
+        </is>
+      </c>
+      <c r="B2800" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5617.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="inlineStr">
+        <is>
+          <t>3906.psd</t>
+        </is>
+      </c>
+      <c r="B2801" t="inlineStr">
+        <is>
+          <t>tamilpsd-5618.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" s="3" t="inlineStr">
+        <is>
+          <t>3905.psd</t>
+        </is>
+      </c>
+      <c r="B2802" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5619.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="inlineStr">
+        <is>
+          <t>3924.psd</t>
+        </is>
+      </c>
+      <c r="B2803" t="inlineStr">
+        <is>
+          <t>tamilpsd-5620.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" s="3" t="inlineStr">
+        <is>
+          <t>49.psd</t>
+        </is>
+      </c>
+      <c r="B2804" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5621.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" t="inlineStr">
+        <is>
+          <t>50.psd</t>
+        </is>
+      </c>
+      <c r="B2805" t="inlineStr">
+        <is>
+          <t>tamilpsd-5622.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" s="3" t="inlineStr">
+        <is>
+          <t>34.psd</t>
+        </is>
+      </c>
+      <c r="B2806" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5623.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="inlineStr">
+        <is>
+          <t>44.psd</t>
+        </is>
+      </c>
+      <c r="B2807" t="inlineStr">
+        <is>
+          <t>tamilpsd-5624.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" s="3" t="inlineStr">
+        <is>
+          <t>43.psd</t>
+        </is>
+      </c>
+      <c r="B2808" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5625.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" t="inlineStr">
+        <is>
+          <t>57.psd</t>
+        </is>
+      </c>
+      <c r="B2809" t="inlineStr">
+        <is>
+          <t>tamilpsd-5626.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="A2810" s="3" t="inlineStr">
+        <is>
+          <t>58.psd</t>
+        </is>
+      </c>
+      <c r="B2810" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5627.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2811">
+      <c r="A2811" t="inlineStr">
+        <is>
+          <t>62.psd</t>
+        </is>
+      </c>
+      <c r="B2811" t="inlineStr">
+        <is>
+          <t>tamilpsd-5628.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="A2812" s="3" t="inlineStr">
+        <is>
+          <t>67.psd</t>
+        </is>
+      </c>
+      <c r="B2812" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5629.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" t="inlineStr">
+        <is>
+          <t>64.psd</t>
+        </is>
+      </c>
+      <c r="B2813" t="inlineStr">
+        <is>
+          <t>tamilpsd-5630.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="A2814" s="3" t="inlineStr">
+        <is>
+          <t>65.psd</t>
+        </is>
+      </c>
+      <c r="B2814" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5631.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="A2815" t="inlineStr">
+        <is>
+          <t>66.psd</t>
+        </is>
+      </c>
+      <c r="B2815" t="inlineStr">
+        <is>
+          <t>tamilpsd-5632.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" s="3" t="inlineStr">
+        <is>
+          <t>73.psd</t>
+        </is>
+      </c>
+      <c r="B2816" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5633.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" t="inlineStr">
+        <is>
+          <t>72.psd</t>
+        </is>
+      </c>
+      <c r="B2817" t="inlineStr">
+        <is>
+          <t>tamilpsd-5634.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="A2818" s="3" t="inlineStr">
+        <is>
+          <t>74.psd</t>
+        </is>
+      </c>
+      <c r="B2818" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5635.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="A2819" t="inlineStr">
+        <is>
+          <t>80.psd</t>
+        </is>
+      </c>
+      <c r="B2819" t="inlineStr">
+        <is>
+          <t>tamilpsd-5636.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="A2820" s="3" t="inlineStr">
+        <is>
+          <t>70.psd</t>
+        </is>
+      </c>
+      <c r="B2820" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5637.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" t="inlineStr">
+        <is>
+          <t>71.psd</t>
+        </is>
+      </c>
+      <c r="B2821" t="inlineStr">
+        <is>
+          <t>tamilpsd-5638.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="A2822" s="3" t="inlineStr">
+        <is>
+          <t>56.psd</t>
+        </is>
+      </c>
+      <c r="B2822" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5639.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="A2823" t="inlineStr">
+        <is>
+          <t>31.psd</t>
+        </is>
+      </c>
+      <c r="B2823" t="inlineStr">
+        <is>
+          <t>tamilpsd-5640.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="A2824" s="3" t="inlineStr">
+        <is>
+          <t>16.psd</t>
+        </is>
+      </c>
+      <c r="B2824" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5642.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="A2825" t="inlineStr">
+        <is>
+          <t>19.psd</t>
+        </is>
+      </c>
+      <c r="B2825" t="inlineStr">
+        <is>
+          <t>tamilpsd-5643.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" s="3" t="inlineStr">
+        <is>
+          <t>21.psd</t>
+        </is>
+      </c>
+      <c r="B2826" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5644.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="A2827" t="inlineStr">
+        <is>
+          <t>15.psd</t>
+        </is>
+      </c>
+      <c r="B2827" t="inlineStr">
+        <is>
+          <t>tamilpsd-5646.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" s="3" t="inlineStr">
+        <is>
+          <t>00.psd</t>
+        </is>
+      </c>
+      <c r="B2828" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5647.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="A2829" t="inlineStr">
+        <is>
+          <t>00a.psd</t>
+        </is>
+      </c>
+      <c r="B2829" t="inlineStr">
+        <is>
+          <t>tamilpsd-5648.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="A2830" s="3" t="inlineStr">
+        <is>
+          <t>3877.psd</t>
+        </is>
+      </c>
+      <c r="B2830" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5649.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" t="inlineStr">
+        <is>
+          <t>3876.psd</t>
+        </is>
+      </c>
+      <c r="B2831" t="inlineStr">
+        <is>
+          <t>tamilpsd-5650.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" s="3" t="inlineStr">
+        <is>
+          <t>3875.psd</t>
+        </is>
+      </c>
+      <c r="B2832" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5651.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="A2833" t="inlineStr">
+        <is>
+          <t>3874.psd</t>
+        </is>
+      </c>
+      <c r="B2833" t="inlineStr">
+        <is>
+          <t>tamilpsd-5652.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" s="3" t="inlineStr">
+        <is>
+          <t>3873.psd</t>
+        </is>
+      </c>
+      <c r="B2834" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5653.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="A2835" t="inlineStr">
+        <is>
+          <t>3872.psd</t>
+        </is>
+      </c>
+      <c r="B2835" t="inlineStr">
+        <is>
+          <t>tamilpsd-5654.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" s="3" t="inlineStr">
+        <is>
+          <t>3871.psd</t>
+        </is>
+      </c>
+      <c r="B2836" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5655.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="A2837" t="inlineStr">
+        <is>
+          <t>3870.psd</t>
+        </is>
+      </c>
+      <c r="B2837" t="inlineStr">
+        <is>
+          <t>tamilpsd-5656.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" s="3" t="inlineStr">
+        <is>
+          <t>3869.psd</t>
+        </is>
+      </c>
+      <c r="B2838" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5657.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="A2839" t="inlineStr">
+        <is>
+          <t>3868.psd</t>
+        </is>
+      </c>
+      <c r="B2839" t="inlineStr">
+        <is>
+          <t>tamilpsd-5658.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="A2840" s="3" t="inlineStr">
+        <is>
+          <t>3867.psd</t>
+        </is>
+      </c>
+      <c r="B2840" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5659.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="A2841" t="inlineStr">
+        <is>
+          <t>3866.psd</t>
+        </is>
+      </c>
+      <c r="B2841" t="inlineStr">
+        <is>
+          <t>tamilpsd-5660.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="A2842" s="3" t="inlineStr">
+        <is>
+          <t>3865.psd</t>
+        </is>
+      </c>
+      <c r="B2842" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5661.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" t="inlineStr">
+        <is>
+          <t>3864.psd</t>
+        </is>
+      </c>
+      <c r="B2843" t="inlineStr">
+        <is>
+          <t>tamilpsd-5662.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="A2844" s="3" t="inlineStr">
+        <is>
+          <t>3863.psd</t>
+        </is>
+      </c>
+      <c r="B2844" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5663.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" t="inlineStr">
+        <is>
+          <t>3862.psd</t>
+        </is>
+      </c>
+      <c r="B2845" t="inlineStr">
+        <is>
+          <t>tamilpsd-5664.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="A2846" s="3" t="inlineStr">
+        <is>
+          <t>3861.psd</t>
+        </is>
+      </c>
+      <c r="B2846" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5665.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="A2847" t="inlineStr">
+        <is>
+          <t>3860.psd</t>
+        </is>
+      </c>
+      <c r="B2847" t="inlineStr">
+        <is>
+          <t>tamilpsd-5666.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" s="3" t="inlineStr">
+        <is>
+          <t>3859.psd</t>
+        </is>
+      </c>
+      <c r="B2848" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5667.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="A2849" t="inlineStr">
+        <is>
+          <t>3878.psd</t>
+        </is>
+      </c>
+      <c r="B2849" t="inlineStr">
+        <is>
+          <t>tamilpsd-5668.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="A2850" s="3" t="inlineStr">
+        <is>
+          <t>3857.psd</t>
+        </is>
+      </c>
+      <c r="B2850" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5669.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" t="inlineStr">
+        <is>
+          <t>3856.psd</t>
+        </is>
+      </c>
+      <c r="B2851" t="inlineStr">
+        <is>
+          <t>tamilpsd-5670.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2852">
+      <c r="A2852" s="3" t="inlineStr">
+        <is>
+          <t>3855.psd</t>
+        </is>
+      </c>
+      <c r="B2852" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5671.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" t="inlineStr">
+        <is>
+          <t>3854.psd</t>
+        </is>
+      </c>
+      <c r="B2853" t="inlineStr">
+        <is>
+          <t>tamilpsd-5672.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="A2854" s="3" t="inlineStr">
+        <is>
+          <t>3853.psd</t>
+        </is>
+      </c>
+      <c r="B2854" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5673.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="A2855" t="inlineStr">
+        <is>
+          <t>3852.psd</t>
+        </is>
+      </c>
+      <c r="B2855" t="inlineStr">
+        <is>
+          <t>tamilpsd-5674.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="A2856" s="3" t="inlineStr">
+        <is>
+          <t>3851.psd</t>
+        </is>
+      </c>
+      <c r="B2856" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5675.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="A2857" t="inlineStr">
+        <is>
+          <t>3850.psd</t>
+        </is>
+      </c>
+      <c r="B2857" t="inlineStr">
+        <is>
+          <t>tamilpsd-5676.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" s="3" t="inlineStr">
+        <is>
+          <t>3849.psd</t>
+        </is>
+      </c>
+      <c r="B2858" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5677.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2859">
+      <c r="A2859" t="inlineStr">
+        <is>
+          <t>3848.psd</t>
+        </is>
+      </c>
+      <c r="B2859" t="inlineStr">
+        <is>
+          <t>tamilpsd-5678.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="A2860" s="3" t="inlineStr">
+        <is>
+          <t>3847.psd</t>
+        </is>
+      </c>
+      <c r="B2860" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5679.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="A2861" t="inlineStr">
+        <is>
+          <t>3846.psd</t>
+        </is>
+      </c>
+      <c r="B2861" t="inlineStr">
+        <is>
+          <t>tamilpsd-5680.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="A2862" s="3" t="inlineStr">
+        <is>
+          <t>3845.psd</t>
+        </is>
+      </c>
+      <c r="B2862" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5681.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="A2863" t="inlineStr">
+        <is>
+          <t>3844.psd</t>
+        </is>
+      </c>
+      <c r="B2863" t="inlineStr">
+        <is>
+          <t>tamilpsd-5682.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" s="3" t="inlineStr">
+        <is>
+          <t>3843.psd</t>
+        </is>
+      </c>
+      <c r="B2864" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5683.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" t="inlineStr">
+        <is>
+          <t>3842.psd</t>
+        </is>
+      </c>
+      <c r="B2865" t="inlineStr">
+        <is>
+          <t>tamilpsd-5684.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" s="3" t="inlineStr">
+        <is>
+          <t>3841.psd</t>
+        </is>
+      </c>
+      <c r="B2866" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5685.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" t="inlineStr">
+        <is>
+          <t>3840.psd</t>
+        </is>
+      </c>
+      <c r="B2867" t="inlineStr">
+        <is>
+          <t>tamilpsd-5686.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" s="3" t="inlineStr">
+        <is>
+          <t>3839.psd</t>
+        </is>
+      </c>
+      <c r="B2868" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5687.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" t="inlineStr">
+        <is>
+          <t>3838.psd</t>
+        </is>
+      </c>
+      <c r="B2869" t="inlineStr">
+        <is>
+          <t>tamilpsd-5688.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" s="3" t="inlineStr">
+        <is>
+          <t>3837.psd</t>
+        </is>
+      </c>
+      <c r="B2870" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5689.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" t="inlineStr">
+        <is>
+          <t>3836.psd</t>
+        </is>
+      </c>
+      <c r="B2871" t="inlineStr">
+        <is>
+          <t>tamilpsd-5690.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" s="3" t="inlineStr">
+        <is>
+          <t>3835.psd</t>
+        </is>
+      </c>
+      <c r="B2872" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5691.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" t="inlineStr">
+        <is>
+          <t>3834.psd</t>
+        </is>
+      </c>
+      <c r="B2873" t="inlineStr">
+        <is>
+          <t>tamilpsd-5692.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" s="3" t="inlineStr">
+        <is>
+          <t>3833.psd</t>
+        </is>
+      </c>
+      <c r="B2874" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5693.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" t="inlineStr">
+        <is>
+          <t>3832.psd</t>
+        </is>
+      </c>
+      <c r="B2875" t="inlineStr">
+        <is>
+          <t>tamilpsd-5694.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" s="3" t="inlineStr">
+        <is>
+          <t>3831.psd</t>
+        </is>
+      </c>
+      <c r="B2876" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5695.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" t="inlineStr">
+        <is>
+          <t>3858.psd</t>
+        </is>
+      </c>
+      <c r="B2877" t="inlineStr">
+        <is>
+          <t>tamilpsd-5696.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" s="3" t="inlineStr">
+        <is>
+          <t>28.psd</t>
+        </is>
+      </c>
+      <c r="B2878" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5697.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" t="inlineStr">
+        <is>
+          <t>29.psd</t>
+        </is>
+      </c>
+      <c r="B2879" t="inlineStr">
+        <is>
+          <t>tamilpsd-5698.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" s="3" t="inlineStr">
+        <is>
+          <t>30.psd</t>
+        </is>
+      </c>
+      <c r="B2880" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5699.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" t="inlineStr">
+        <is>
+          <t>48.psd</t>
+        </is>
+      </c>
+      <c r="B2881" t="inlineStr">
+        <is>
+          <t>tamilpsd-5700.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" s="3" t="inlineStr">
+        <is>
+          <t>32.psd</t>
+        </is>
+      </c>
+      <c r="B2882" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5705.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" t="inlineStr">
+        <is>
+          <t>12.psd</t>
+        </is>
+      </c>
+      <c r="B2883" t="inlineStr">
+        <is>
+          <t>tamilpsd-5706.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" s="3" t="inlineStr">
+        <is>
+          <t>13.psd</t>
+        </is>
+      </c>
+      <c r="B2884" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5707.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" t="inlineStr">
+        <is>
+          <t>59.psd</t>
+        </is>
+      </c>
+      <c r="B2885" t="inlineStr">
+        <is>
+          <t>tamilpsd-5708.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" s="3" t="inlineStr">
+        <is>
+          <t>60.psd</t>
+        </is>
+      </c>
+      <c r="B2886" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5709.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" t="inlineStr">
+        <is>
+          <t>61.psd</t>
+        </is>
+      </c>
+      <c r="B2887" t="inlineStr">
+        <is>
+          <t>tamilpsd-5710.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" s="3" t="inlineStr">
+        <is>
+          <t>25.psd</t>
+        </is>
+      </c>
+      <c r="B2888" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5711.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" t="inlineStr">
+        <is>
+          <t>26.psd</t>
+        </is>
+      </c>
+      <c r="B2889" t="inlineStr">
+        <is>
+          <t>tamilpsd-5712.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2890">
+      <c r="A2890" s="3" t="inlineStr">
+        <is>
+          <t>27.psd</t>
+        </is>
+      </c>
+      <c r="B2890" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5713.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2891">
+      <c r="A2891" t="inlineStr">
+        <is>
+          <t>51.psd</t>
+        </is>
+      </c>
+      <c r="B2891" t="inlineStr">
+        <is>
+          <t>tamilpsd-5714.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="A2892" s="3" t="inlineStr">
+        <is>
+          <t>52.psd</t>
+        </is>
+      </c>
+      <c r="B2892" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5715.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" t="inlineStr">
+        <is>
+          <t>53.psd</t>
+        </is>
+      </c>
+      <c r="B2893" t="inlineStr">
+        <is>
+          <t>tamilpsd-5716.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="A2894" s="3" t="inlineStr">
+        <is>
+          <t>46.psd</t>
+        </is>
+      </c>
+      <c r="B2894" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5717.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="A2895" t="inlineStr">
+        <is>
+          <t>47.psd</t>
+        </is>
+      </c>
+      <c r="B2895" t="inlineStr">
+        <is>
+          <t>tamilpsd-5718.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="A2896" s="3" t="inlineStr">
+        <is>
+          <t>45.psd</t>
+        </is>
+      </c>
+      <c r="B2896" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5721.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="A2897" t="inlineStr">
+        <is>
+          <t>39.psd</t>
+        </is>
+      </c>
+      <c r="B2897" t="inlineStr">
+        <is>
+          <t>tamilpsd-5722.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="A2898" s="3" t="inlineStr">
+        <is>
+          <t>40.psd</t>
+        </is>
+      </c>
+      <c r="B2898" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5723.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2899">
+      <c r="A2899" t="inlineStr">
+        <is>
+          <t>41.psd</t>
+        </is>
+      </c>
+      <c r="B2899" t="inlineStr">
+        <is>
+          <t>tamilpsd-5724.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="A2900" s="3" t="inlineStr">
+        <is>
+          <t>42.psd</t>
+        </is>
+      </c>
+      <c r="B2900" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5725.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="A2901" t="inlineStr">
+        <is>
+          <t>33.psd</t>
+        </is>
+      </c>
+      <c r="B2901" t="inlineStr">
+        <is>
+          <t>tamilpsd-5726.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" s="3" t="inlineStr">
+        <is>
+          <t>35.psd</t>
+        </is>
+      </c>
+      <c r="B2902" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5728.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2903">
+      <c r="A2903" t="inlineStr">
+        <is>
+          <t>36.psd</t>
+        </is>
+      </c>
+      <c r="B2903" t="inlineStr">
+        <is>
+          <t>tamilpsd-5729.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2904">
+      <c r="A2904" s="3" t="inlineStr">
+        <is>
+          <t>37.psd</t>
+        </is>
+      </c>
+      <c r="B2904" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5730.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2905">
+      <c r="A2905" t="inlineStr">
+        <is>
+          <t>38.psd</t>
+        </is>
+      </c>
+      <c r="B2905" t="inlineStr">
+        <is>
+          <t>tamilpsd-5731.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2906">
+      <c r="A2906" s="3" t="inlineStr">
+        <is>
+          <t>17.psd</t>
+        </is>
+      </c>
+      <c r="B2906" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5733.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2907">
+      <c r="A2907" t="inlineStr">
+        <is>
+          <t>18.psd</t>
+        </is>
+      </c>
+      <c r="B2907" t="inlineStr">
+        <is>
+          <t>tamilpsd-5734.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2908">
+      <c r="A2908" s="3" t="inlineStr">
+        <is>
+          <t>20.psd</t>
+        </is>
+      </c>
+      <c r="B2908" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5736.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2909">
+      <c r="A2909" t="inlineStr">
+        <is>
+          <t>22.psd</t>
+        </is>
+      </c>
+      <c r="B2909" t="inlineStr">
+        <is>
+          <t>tamilpsd-5738.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2910">
+      <c r="A2910" s="3" t="inlineStr">
+        <is>
+          <t>23.psd</t>
+        </is>
+      </c>
+      <c r="B2910" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5739.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2911">
+      <c r="A2911" t="inlineStr">
+        <is>
+          <t>3811.psd</t>
+        </is>
+      </c>
+      <c r="B2911" t="inlineStr">
+        <is>
+          <t>tamilpsd-5740.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2912">
+      <c r="A2912" s="3" t="inlineStr">
+        <is>
+          <t>3810.psd</t>
+        </is>
+      </c>
+      <c r="B2912" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5741.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2913">
+      <c r="A2913" t="inlineStr">
+        <is>
+          <t>3809.psd</t>
+        </is>
+      </c>
+      <c r="B2913" t="inlineStr">
+        <is>
+          <t>tamilpsd-5742.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2914">
+      <c r="A2914" s="3" t="inlineStr">
+        <is>
+          <t>3808.psd</t>
+        </is>
+      </c>
+      <c r="B2914" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5743.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2915">
+      <c r="A2915" t="inlineStr">
+        <is>
+          <t>3807.psd</t>
+        </is>
+      </c>
+      <c r="B2915" t="inlineStr">
+        <is>
+          <t>tamilpsd-5744.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2916">
+      <c r="A2916" s="3" t="inlineStr">
+        <is>
+          <t>3806.psd</t>
+        </is>
+      </c>
+      <c r="B2916" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5745.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2917">
+      <c r="A2917" t="inlineStr">
+        <is>
+          <t>3805.psd</t>
+        </is>
+      </c>
+      <c r="B2917" t="inlineStr">
+        <is>
+          <t>tamilpsd-5746.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2918">
+      <c r="A2918" s="3" t="inlineStr">
+        <is>
+          <t>3804.psd</t>
+        </is>
+      </c>
+      <c r="B2918" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5747.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2919">
+      <c r="A2919" t="inlineStr">
+        <is>
+          <t>3803.psd</t>
+        </is>
+      </c>
+      <c r="B2919" t="inlineStr">
+        <is>
+          <t>tamilpsd-5748.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2920">
+      <c r="A2920" s="3" t="inlineStr">
+        <is>
+          <t>3802.psd</t>
+        </is>
+      </c>
+      <c r="B2920" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5749.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2921">
+      <c r="A2921" t="inlineStr">
+        <is>
+          <t>3801.psd</t>
+        </is>
+      </c>
+      <c r="B2921" t="inlineStr">
+        <is>
+          <t>tamilpsd-5750.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2922">
+      <c r="A2922" s="3" t="inlineStr">
+        <is>
+          <t>3800.psd</t>
+        </is>
+      </c>
+      <c r="B2922" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5751.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2923">
+      <c r="A2923" t="inlineStr">
+        <is>
+          <t>3799.psd</t>
+        </is>
+      </c>
+      <c r="B2923" t="inlineStr">
+        <is>
+          <t>tamilpsd-5752.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="A2924" s="3" t="inlineStr">
+        <is>
+          <t>3798.psd</t>
+        </is>
+      </c>
+      <c r="B2924" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5753.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2925">
+      <c r="A2925" t="inlineStr">
+        <is>
+          <t>3797.psd</t>
+        </is>
+      </c>
+      <c r="B2925" t="inlineStr">
+        <is>
+          <t>tamilpsd-5754.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2926">
+      <c r="A2926" s="3" t="inlineStr">
+        <is>
+          <t>3796.psd</t>
+        </is>
+      </c>
+      <c r="B2926" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5755.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2927">
+      <c r="A2927" t="inlineStr">
+        <is>
+          <t>3795.psd</t>
+        </is>
+      </c>
+      <c r="B2927" t="inlineStr">
+        <is>
+          <t>tamilpsd-5756.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2928">
+      <c r="A2928" s="3" t="inlineStr">
+        <is>
+          <t>3794.psd</t>
+        </is>
+      </c>
+      <c r="B2928" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5757.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2929">
+      <c r="A2929" t="inlineStr">
+        <is>
+          <t>3793.psd</t>
+        </is>
+      </c>
+      <c r="B2929" t="inlineStr">
+        <is>
+          <t>tamilpsd-5758.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2930">
+      <c r="A2930" s="3" t="inlineStr">
+        <is>
+          <t>3792.psd</t>
+        </is>
+      </c>
+      <c r="B2930" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5759.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2931">
+      <c r="A2931" t="inlineStr">
+        <is>
+          <t>3791.psd</t>
+        </is>
+      </c>
+      <c r="B2931" t="inlineStr">
+        <is>
+          <t>tamilpsd-5760.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2932">
+      <c r="A2932" s="3" t="inlineStr">
+        <is>
+          <t>3790.psd</t>
+        </is>
+      </c>
+      <c r="B2932" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5761.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2933">
+      <c r="A2933" t="inlineStr">
+        <is>
+          <t>3789.psd</t>
+        </is>
+      </c>
+      <c r="B2933" t="inlineStr">
+        <is>
+          <t>tamilpsd-5762.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2934">
+      <c r="A2934" s="3" t="inlineStr">
+        <is>
+          <t>3788.psd</t>
+        </is>
+      </c>
+      <c r="B2934" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5763.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2935">
+      <c r="A2935" t="inlineStr">
+        <is>
+          <t>3787.psd</t>
+        </is>
+      </c>
+      <c r="B2935" t="inlineStr">
+        <is>
+          <t>tamilpsd-5764.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2936">
+      <c r="A2936" s="3" t="inlineStr">
+        <is>
+          <t>3786.psd</t>
+        </is>
+      </c>
+      <c r="B2936" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5765.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2937">
+      <c r="A2937" t="inlineStr">
+        <is>
+          <t>3785.psd</t>
+        </is>
+      </c>
+      <c r="B2937" t="inlineStr">
+        <is>
+          <t>tamilpsd-5766.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2938">
+      <c r="A2938" s="3" t="inlineStr">
+        <is>
+          <t>3784.psd</t>
+        </is>
+      </c>
+      <c r="B2938" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5767.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2939">
+      <c r="A2939" t="inlineStr">
+        <is>
+          <t>3783.psd</t>
+        </is>
+      </c>
+      <c r="B2939" t="inlineStr">
+        <is>
+          <t>tamilpsd-5768.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2940">
+      <c r="A2940" s="3" t="inlineStr">
+        <is>
+          <t>3781.psd</t>
+        </is>
+      </c>
+      <c r="B2940" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5769.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2941">
+      <c r="A2941" t="inlineStr">
+        <is>
+          <t>3782.psd</t>
+        </is>
+      </c>
+      <c r="B2941" t="inlineStr">
+        <is>
+          <t>tamilpsd-5770.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2942">
+      <c r="A2942" s="3" t="inlineStr">
+        <is>
+          <t>3780.psd</t>
+        </is>
+      </c>
+      <c r="B2942" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5771.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2943">
+      <c r="A2943" t="inlineStr">
+        <is>
+          <t>3779.psd</t>
+        </is>
+      </c>
+      <c r="B2943" t="inlineStr">
+        <is>
+          <t>tamilpsd-5772.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2944">
+      <c r="A2944" s="3" t="inlineStr">
+        <is>
+          <t>3778.psd</t>
+        </is>
+      </c>
+      <c r="B2944" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5773.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2945">
+      <c r="A2945" t="inlineStr">
+        <is>
+          <t>3776.psd</t>
+        </is>
+      </c>
+      <c r="B2945" t="inlineStr">
+        <is>
+          <t>tamilpsd-5774.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2946">
+      <c r="A2946" s="3" t="inlineStr">
+        <is>
+          <t>3777.psd</t>
+        </is>
+      </c>
+      <c r="B2946" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5775.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2947">
+      <c r="A2947" t="inlineStr">
+        <is>
+          <t>3775.psd</t>
+        </is>
+      </c>
+      <c r="B2947" t="inlineStr">
+        <is>
+          <t>tamilpsd-5776.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2948">
+      <c r="A2948" s="3" t="inlineStr">
+        <is>
+          <t>3774.psd</t>
+        </is>
+      </c>
+      <c r="B2948" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5777.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2949">
+      <c r="A2949" t="inlineStr">
+        <is>
+          <t>3773.psd</t>
+        </is>
+      </c>
+      <c r="B2949" t="inlineStr">
+        <is>
+          <t>tamilpsd-5778.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2950">
+      <c r="A2950" s="3" t="inlineStr">
+        <is>
+          <t>3772.psd</t>
+        </is>
+      </c>
+      <c r="B2950" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5779.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2951">
+      <c r="A2951" t="inlineStr">
+        <is>
+          <t>3771.psd</t>
+        </is>
+      </c>
+      <c r="B2951" t="inlineStr">
+        <is>
+          <t>tamilpsd-5780.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2952">
+      <c r="A2952" s="3" t="inlineStr">
+        <is>
+          <t>3770.psd</t>
+        </is>
+      </c>
+      <c r="B2952" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5781.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2953">
+      <c r="A2953" t="inlineStr">
+        <is>
+          <t>3769.psd</t>
+        </is>
+      </c>
+      <c r="B2953" t="inlineStr">
+        <is>
+          <t>tamilpsd-5782.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2954">
+      <c r="A2954" s="3" t="inlineStr">
+        <is>
+          <t>3768.psd</t>
+        </is>
+      </c>
+      <c r="B2954" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5783.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2955">
+      <c r="A2955" t="inlineStr">
+        <is>
+          <t>3767.psd</t>
+        </is>
+      </c>
+      <c r="B2955" t="inlineStr">
+        <is>
+          <t>tamilpsd-5784.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2956">
+      <c r="A2956" s="3" t="inlineStr">
+        <is>
+          <t>3766.psd</t>
+        </is>
+      </c>
+      <c r="B2956" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5785.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2957">
+      <c r="A2957" t="inlineStr">
+        <is>
+          <t>3765.psd</t>
+        </is>
+      </c>
+      <c r="B2957" t="inlineStr">
+        <is>
+          <t>tamilpsd-5786.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2958">
+      <c r="A2958" s="3" t="inlineStr">
+        <is>
+          <t>3764.psd</t>
+        </is>
+      </c>
+      <c r="B2958" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5787.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2959">
+      <c r="A2959" t="inlineStr">
+        <is>
+          <t>3763.psd</t>
+        </is>
+      </c>
+      <c r="B2959" t="inlineStr">
+        <is>
+          <t>tamilpsd-5788.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2960">
+      <c r="A2960" s="3" t="inlineStr">
+        <is>
+          <t>3762.psd</t>
+        </is>
+      </c>
+      <c r="B2960" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-5789.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2961">
+      <c r="A2961" t="inlineStr">
+        <is>
+          <t>3761.psd</t>
+        </is>
+      </c>
+      <c r="B2961" t="inlineStr">
+        <is>
+          <t>tamilpsd-5790.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4258"/>
+  <dimension ref="A1:B4259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -51193,6 +51193,18 @@
         </is>
       </c>
     </row>
+    <row r="4259">
+      <c r="A4259" t="inlineStr">
+        <is>
+          <t>3246.psd</t>
+        </is>
+      </c>
+      <c r="B4259" t="inlineStr">
+        <is>
+          <t>tamilpsd-7754.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4259"/>
+  <dimension ref="A1:B4269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -51205,6 +51205,126 @@
         </is>
       </c>
     </row>
+    <row r="4260">
+      <c r="A4260" s="3" t="inlineStr">
+        <is>
+          <t>6152.png</t>
+        </is>
+      </c>
+      <c r="B4260" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-7756.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4261">
+      <c r="A4261" t="inlineStr">
+        <is>
+          <t>6151.png</t>
+        </is>
+      </c>
+      <c r="B4261" t="inlineStr">
+        <is>
+          <t>tamilpsd-7757.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4262">
+      <c r="A4262" s="3" t="inlineStr">
+        <is>
+          <t>6150.png</t>
+        </is>
+      </c>
+      <c r="B4262" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-7758.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4263">
+      <c r="A4263" t="inlineStr">
+        <is>
+          <t>6149.png</t>
+        </is>
+      </c>
+      <c r="B4263" t="inlineStr">
+        <is>
+          <t>tamilpsd-7759.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4264">
+      <c r="A4264" s="3" t="inlineStr">
+        <is>
+          <t>6148.png</t>
+        </is>
+      </c>
+      <c r="B4264" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-7760.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4265">
+      <c r="A4265" t="inlineStr">
+        <is>
+          <t>6147.png</t>
+        </is>
+      </c>
+      <c r="B4265" t="inlineStr">
+        <is>
+          <t>tamilpsd-7761.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4266">
+      <c r="A4266" s="3" t="inlineStr">
+        <is>
+          <t>6146.png</t>
+        </is>
+      </c>
+      <c r="B4266" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-7762.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4267">
+      <c r="A4267" t="inlineStr">
+        <is>
+          <t>6145.png</t>
+        </is>
+      </c>
+      <c r="B4267" t="inlineStr">
+        <is>
+          <t>tamilpsd-7763.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4268">
+      <c r="A4268" s="3" t="inlineStr">
+        <is>
+          <t>6144.png</t>
+        </is>
+      </c>
+      <c r="B4268" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-7764.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4269">
+      <c r="A4269" t="inlineStr">
+        <is>
+          <t>6143.png</t>
+        </is>
+      </c>
+      <c r="B4269" t="inlineStr">
+        <is>
+          <t>tamilpsd-7765.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4269"/>
+  <dimension ref="A1:B4738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -51325,6 +51325,5634 @@
         </is>
       </c>
     </row>
+    <row r="4270">
+      <c r="A4270" s="3" t="inlineStr">
+        <is>
+          <t>2200.psd</t>
+        </is>
+      </c>
+      <c r="B4270" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10167.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4271">
+      <c r="A4271" t="inlineStr">
+        <is>
+          <t>2199.psd</t>
+        </is>
+      </c>
+      <c r="B4271" t="inlineStr">
+        <is>
+          <t>tamilpsd-10168.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4272">
+      <c r="A4272" s="3" t="inlineStr">
+        <is>
+          <t>2198.psd</t>
+        </is>
+      </c>
+      <c r="B4272" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10169.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4273">
+      <c r="A4273" t="inlineStr">
+        <is>
+          <t>2197.psd</t>
+        </is>
+      </c>
+      <c r="B4273" t="inlineStr">
+        <is>
+          <t>tamilpsd-10170.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" s="3" t="inlineStr">
+        <is>
+          <t>2196.psd</t>
+        </is>
+      </c>
+      <c r="B4274" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10171.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" t="inlineStr">
+        <is>
+          <t>2195.psd</t>
+        </is>
+      </c>
+      <c r="B4275" t="inlineStr">
+        <is>
+          <t>tamilpsd-10172.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" s="3" t="inlineStr">
+        <is>
+          <t>2194.psd</t>
+        </is>
+      </c>
+      <c r="B4276" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10173.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" t="inlineStr">
+        <is>
+          <t>2193.psd</t>
+        </is>
+      </c>
+      <c r="B4277" t="inlineStr">
+        <is>
+          <t>tamilpsd-10174.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" s="3" t="inlineStr">
+        <is>
+          <t>2192.psd</t>
+        </is>
+      </c>
+      <c r="B4278" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10175.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" t="inlineStr">
+        <is>
+          <t>2191.psd</t>
+        </is>
+      </c>
+      <c r="B4279" t="inlineStr">
+        <is>
+          <t>tamilpsd-10176.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" s="3" t="inlineStr">
+        <is>
+          <t>2190.psd</t>
+        </is>
+      </c>
+      <c r="B4280" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10177.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4281">
+      <c r="A4281" t="inlineStr">
+        <is>
+          <t>2189.psd</t>
+        </is>
+      </c>
+      <c r="B4281" t="inlineStr">
+        <is>
+          <t>tamilpsd-10178.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4282">
+      <c r="A4282" s="3" t="inlineStr">
+        <is>
+          <t>2188.psd</t>
+        </is>
+      </c>
+      <c r="B4282" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10179.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" t="inlineStr">
+        <is>
+          <t>2187.psd</t>
+        </is>
+      </c>
+      <c r="B4283" t="inlineStr">
+        <is>
+          <t>tamilpsd-10180.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4284">
+      <c r="A4284" s="3" t="inlineStr">
+        <is>
+          <t>2186.psd</t>
+        </is>
+      </c>
+      <c r="B4284" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10181.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" t="inlineStr">
+        <is>
+          <t>2185.psd</t>
+        </is>
+      </c>
+      <c r="B4285" t="inlineStr">
+        <is>
+          <t>tamilpsd-10182.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4286">
+      <c r="A4286" s="3" t="inlineStr">
+        <is>
+          <t>2184.psd</t>
+        </is>
+      </c>
+      <c r="B4286" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10183.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" t="inlineStr">
+        <is>
+          <t>2183.psd</t>
+        </is>
+      </c>
+      <c r="B4287" t="inlineStr">
+        <is>
+          <t>tamilpsd-10184.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" s="3" t="inlineStr">
+        <is>
+          <t>2182.psd</t>
+        </is>
+      </c>
+      <c r="B4288" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10185.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" t="inlineStr">
+        <is>
+          <t>2181.psd</t>
+        </is>
+      </c>
+      <c r="B4289" t="inlineStr">
+        <is>
+          <t>tamilpsd-10186.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4290">
+      <c r="A4290" s="3" t="inlineStr">
+        <is>
+          <t>2180.psd</t>
+        </is>
+      </c>
+      <c r="B4290" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10187.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4291">
+      <c r="A4291" t="inlineStr">
+        <is>
+          <t>2280.psd</t>
+        </is>
+      </c>
+      <c r="B4291" t="inlineStr">
+        <is>
+          <t>tamilpsd-10188.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4292">
+      <c r="A4292" s="3" t="inlineStr">
+        <is>
+          <t>2178.psd</t>
+        </is>
+      </c>
+      <c r="B4292" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10189.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4293">
+      <c r="A4293" t="inlineStr">
+        <is>
+          <t>2177.psd</t>
+        </is>
+      </c>
+      <c r="B4293" t="inlineStr">
+        <is>
+          <t>tamilpsd-10190.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4294">
+      <c r="A4294" s="3" t="inlineStr">
+        <is>
+          <t>2176.psd</t>
+        </is>
+      </c>
+      <c r="B4294" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10191.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4295">
+      <c r="A4295" t="inlineStr">
+        <is>
+          <t>2175.psd</t>
+        </is>
+      </c>
+      <c r="B4295" t="inlineStr">
+        <is>
+          <t>tamilpsd-10192.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4296">
+      <c r="A4296" s="3" t="inlineStr">
+        <is>
+          <t>2174.psd</t>
+        </is>
+      </c>
+      <c r="B4296" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10193.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4297">
+      <c r="A4297" t="inlineStr">
+        <is>
+          <t>2173.psd</t>
+        </is>
+      </c>
+      <c r="B4297" t="inlineStr">
+        <is>
+          <t>tamilpsd-10194.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4298">
+      <c r="A4298" s="3" t="inlineStr">
+        <is>
+          <t>2172.psd</t>
+        </is>
+      </c>
+      <c r="B4298" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10195.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4299">
+      <c r="A4299" t="inlineStr">
+        <is>
+          <t>2171.psd</t>
+        </is>
+      </c>
+      <c r="B4299" t="inlineStr">
+        <is>
+          <t>tamilpsd-10196.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4300">
+      <c r="A4300" s="3" t="inlineStr">
+        <is>
+          <t>2170.psd</t>
+        </is>
+      </c>
+      <c r="B4300" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10197.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4301">
+      <c r="A4301" t="inlineStr">
+        <is>
+          <t>2169.psd</t>
+        </is>
+      </c>
+      <c r="B4301" t="inlineStr">
+        <is>
+          <t>tamilpsd-10198.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4302">
+      <c r="A4302" s="3" t="inlineStr">
+        <is>
+          <t>2168.psd</t>
+        </is>
+      </c>
+      <c r="B4302" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10199.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" t="inlineStr">
+        <is>
+          <t>2167.psd</t>
+        </is>
+      </c>
+      <c r="B4303" t="inlineStr">
+        <is>
+          <t>tamilpsd-10200.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" s="3" t="inlineStr">
+        <is>
+          <t>2166.psd</t>
+        </is>
+      </c>
+      <c r="B4304" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10201.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" t="inlineStr">
+        <is>
+          <t>2165.psd</t>
+        </is>
+      </c>
+      <c r="B4305" t="inlineStr">
+        <is>
+          <t>tamilpsd-10202.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" s="3" t="inlineStr">
+        <is>
+          <t>2164.psd</t>
+        </is>
+      </c>
+      <c r="B4306" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10203.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4307">
+      <c r="A4307" t="inlineStr">
+        <is>
+          <t>2163.psd</t>
+        </is>
+      </c>
+      <c r="B4307" t="inlineStr">
+        <is>
+          <t>tamilpsd-10204.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" s="3" t="inlineStr">
+        <is>
+          <t>2162.psd</t>
+        </is>
+      </c>
+      <c r="B4308" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10205.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" t="inlineStr">
+        <is>
+          <t>2161.psd</t>
+        </is>
+      </c>
+      <c r="B4309" t="inlineStr">
+        <is>
+          <t>tamilpsd-10206.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4310">
+      <c r="A4310" s="3" t="inlineStr">
+        <is>
+          <t>2160.psd</t>
+        </is>
+      </c>
+      <c r="B4310" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10207.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4311">
+      <c r="A4311" t="inlineStr">
+        <is>
+          <t>2159.psd</t>
+        </is>
+      </c>
+      <c r="B4311" t="inlineStr">
+        <is>
+          <t>tamilpsd-10208.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4312">
+      <c r="A4312" s="3" t="inlineStr">
+        <is>
+          <t>2158.psd</t>
+        </is>
+      </c>
+      <c r="B4312" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10209.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4313">
+      <c r="A4313" t="inlineStr">
+        <is>
+          <t>2157.psd</t>
+        </is>
+      </c>
+      <c r="B4313" t="inlineStr">
+        <is>
+          <t>tamilpsd-10210.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4314">
+      <c r="A4314" s="3" t="inlineStr">
+        <is>
+          <t>2156.psd</t>
+        </is>
+      </c>
+      <c r="B4314" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10211.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4315">
+      <c r="A4315" t="inlineStr">
+        <is>
+          <t>2155.psd</t>
+        </is>
+      </c>
+      <c r="B4315" t="inlineStr">
+        <is>
+          <t>tamilpsd-10212.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" s="3" t="inlineStr">
+        <is>
+          <t>2154.psd</t>
+        </is>
+      </c>
+      <c r="B4316" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10213.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4317">
+      <c r="A4317" t="inlineStr">
+        <is>
+          <t>2153.psd</t>
+        </is>
+      </c>
+      <c r="B4317" t="inlineStr">
+        <is>
+          <t>tamilpsd-10214.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" s="3" t="inlineStr">
+        <is>
+          <t>2152.psd</t>
+        </is>
+      </c>
+      <c r="B4318" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10215.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" t="inlineStr">
+        <is>
+          <t>2151.psd</t>
+        </is>
+      </c>
+      <c r="B4319" t="inlineStr">
+        <is>
+          <t>tamilpsd-10216.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4320">
+      <c r="A4320" s="3" t="inlineStr">
+        <is>
+          <t>2150.psd</t>
+        </is>
+      </c>
+      <c r="B4320" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10217.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4321">
+      <c r="A4321" t="inlineStr">
+        <is>
+          <t>2149.psd</t>
+        </is>
+      </c>
+      <c r="B4321" t="inlineStr">
+        <is>
+          <t>tamilpsd-10218.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4322">
+      <c r="A4322" s="3" t="inlineStr">
+        <is>
+          <t>2148.psd</t>
+        </is>
+      </c>
+      <c r="B4322" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10219.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4323">
+      <c r="A4323" t="inlineStr">
+        <is>
+          <t>2147.psd</t>
+        </is>
+      </c>
+      <c r="B4323" t="inlineStr">
+        <is>
+          <t>tamilpsd-10220.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4324">
+      <c r="A4324" s="3" t="inlineStr">
+        <is>
+          <t>2146.psd</t>
+        </is>
+      </c>
+      <c r="B4324" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10221.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4325">
+      <c r="A4325" t="inlineStr">
+        <is>
+          <t>2145.psd</t>
+        </is>
+      </c>
+      <c r="B4325" t="inlineStr">
+        <is>
+          <t>tamilpsd-10222.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4326">
+      <c r="A4326" s="3" t="inlineStr">
+        <is>
+          <t>2144.psd</t>
+        </is>
+      </c>
+      <c r="B4326" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10223.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4327">
+      <c r="A4327" t="inlineStr">
+        <is>
+          <t>2143.psd</t>
+        </is>
+      </c>
+      <c r="B4327" t="inlineStr">
+        <is>
+          <t>tamilpsd-10224.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4328">
+      <c r="A4328" s="3" t="inlineStr">
+        <is>
+          <t>2142.psd</t>
+        </is>
+      </c>
+      <c r="B4328" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10225.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4329">
+      <c r="A4329" t="inlineStr">
+        <is>
+          <t>2141.psd</t>
+        </is>
+      </c>
+      <c r="B4329" t="inlineStr">
+        <is>
+          <t>tamilpsd-10226.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4330">
+      <c r="A4330" s="3" t="inlineStr">
+        <is>
+          <t>2140.psd</t>
+        </is>
+      </c>
+      <c r="B4330" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10227.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4331">
+      <c r="A4331" t="inlineStr">
+        <is>
+          <t>2139.psd</t>
+        </is>
+      </c>
+      <c r="B4331" t="inlineStr">
+        <is>
+          <t>tamilpsd-10228.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4332">
+      <c r="A4332" s="3" t="inlineStr">
+        <is>
+          <t>2138.psd</t>
+        </is>
+      </c>
+      <c r="B4332" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10229.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4333">
+      <c r="A4333" t="inlineStr">
+        <is>
+          <t>2137.psd</t>
+        </is>
+      </c>
+      <c r="B4333" t="inlineStr">
+        <is>
+          <t>tamilpsd-10230.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4334">
+      <c r="A4334" s="3" t="inlineStr">
+        <is>
+          <t>2136.psd</t>
+        </is>
+      </c>
+      <c r="B4334" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10231.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4335">
+      <c r="A4335" t="inlineStr">
+        <is>
+          <t>2135.psd</t>
+        </is>
+      </c>
+      <c r="B4335" t="inlineStr">
+        <is>
+          <t>tamilpsd-10232.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4336">
+      <c r="A4336" s="3" t="inlineStr">
+        <is>
+          <t>2134.psd</t>
+        </is>
+      </c>
+      <c r="B4336" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10233.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4337">
+      <c r="A4337" t="inlineStr">
+        <is>
+          <t>2133.psd</t>
+        </is>
+      </c>
+      <c r="B4337" t="inlineStr">
+        <is>
+          <t>tamilpsd-10234.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4338">
+      <c r="A4338" s="3" t="inlineStr">
+        <is>
+          <t>2132.psd</t>
+        </is>
+      </c>
+      <c r="B4338" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10235.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4339">
+      <c r="A4339" t="inlineStr">
+        <is>
+          <t>2131.psd</t>
+        </is>
+      </c>
+      <c r="B4339" t="inlineStr">
+        <is>
+          <t>tamilpsd-10236.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4340">
+      <c r="A4340" s="3" t="inlineStr">
+        <is>
+          <t>2130.psd</t>
+        </is>
+      </c>
+      <c r="B4340" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10237.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4341">
+      <c r="A4341" t="inlineStr">
+        <is>
+          <t>2129.psd</t>
+        </is>
+      </c>
+      <c r="B4341" t="inlineStr">
+        <is>
+          <t>tamilpsd-10238.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4342">
+      <c r="A4342" s="3" t="inlineStr">
+        <is>
+          <t>2128.psd</t>
+        </is>
+      </c>
+      <c r="B4342" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10239.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4343">
+      <c r="A4343" t="inlineStr">
+        <is>
+          <t>2127.psd</t>
+        </is>
+      </c>
+      <c r="B4343" t="inlineStr">
+        <is>
+          <t>tamilpsd-10240.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4344">
+      <c r="A4344" s="3" t="inlineStr">
+        <is>
+          <t>2126.psd</t>
+        </is>
+      </c>
+      <c r="B4344" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10241.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4345">
+      <c r="A4345" t="inlineStr">
+        <is>
+          <t>2125.psd</t>
+        </is>
+      </c>
+      <c r="B4345" t="inlineStr">
+        <is>
+          <t>tamilpsd-10242.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4346">
+      <c r="A4346" s="3" t="inlineStr">
+        <is>
+          <t>2124.psd</t>
+        </is>
+      </c>
+      <c r="B4346" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10243.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4347">
+      <c r="A4347" t="inlineStr">
+        <is>
+          <t>2123.psd</t>
+        </is>
+      </c>
+      <c r="B4347" t="inlineStr">
+        <is>
+          <t>tamilpsd-10244.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4348">
+      <c r="A4348" s="3" t="inlineStr">
+        <is>
+          <t>2122.psd</t>
+        </is>
+      </c>
+      <c r="B4348" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10245.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4349">
+      <c r="A4349" t="inlineStr">
+        <is>
+          <t>2121.psd</t>
+        </is>
+      </c>
+      <c r="B4349" t="inlineStr">
+        <is>
+          <t>tamilpsd-10246.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4350">
+      <c r="A4350" s="3" t="inlineStr">
+        <is>
+          <t>2120.psd</t>
+        </is>
+      </c>
+      <c r="B4350" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10247.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4351">
+      <c r="A4351" t="inlineStr">
+        <is>
+          <t>2119.psd</t>
+        </is>
+      </c>
+      <c r="B4351" t="inlineStr">
+        <is>
+          <t>tamilpsd-10248.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4352">
+      <c r="A4352" s="3" t="inlineStr">
+        <is>
+          <t>2118.psd</t>
+        </is>
+      </c>
+      <c r="B4352" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10249.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4353">
+      <c r="A4353" t="inlineStr">
+        <is>
+          <t>2117.psd</t>
+        </is>
+      </c>
+      <c r="B4353" t="inlineStr">
+        <is>
+          <t>tamilpsd-10250.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4354">
+      <c r="A4354" s="3" t="inlineStr">
+        <is>
+          <t>2116.psd</t>
+        </is>
+      </c>
+      <c r="B4354" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10251.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4355">
+      <c r="A4355" t="inlineStr">
+        <is>
+          <t>2115.psd</t>
+        </is>
+      </c>
+      <c r="B4355" t="inlineStr">
+        <is>
+          <t>tamilpsd-10252.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4356">
+      <c r="A4356" s="3" t="inlineStr">
+        <is>
+          <t>2114.psd</t>
+        </is>
+      </c>
+      <c r="B4356" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10253.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4357">
+      <c r="A4357" t="inlineStr">
+        <is>
+          <t>2113.psd</t>
+        </is>
+      </c>
+      <c r="B4357" t="inlineStr">
+        <is>
+          <t>tamilpsd-10254.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4358">
+      <c r="A4358" s="3" t="inlineStr">
+        <is>
+          <t>2112.psd</t>
+        </is>
+      </c>
+      <c r="B4358" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10255.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4359">
+      <c r="A4359" t="inlineStr">
+        <is>
+          <t>2111.psd</t>
+        </is>
+      </c>
+      <c r="B4359" t="inlineStr">
+        <is>
+          <t>tamilpsd-10256.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4360">
+      <c r="A4360" s="3" t="inlineStr">
+        <is>
+          <t>2110.psd</t>
+        </is>
+      </c>
+      <c r="B4360" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10257.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4361">
+      <c r="A4361" t="inlineStr">
+        <is>
+          <t>2109.psd</t>
+        </is>
+      </c>
+      <c r="B4361" t="inlineStr">
+        <is>
+          <t>tamilpsd-10258.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4362">
+      <c r="A4362" s="3" t="inlineStr">
+        <is>
+          <t>2108.psd</t>
+        </is>
+      </c>
+      <c r="B4362" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10259.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4363">
+      <c r="A4363" t="inlineStr">
+        <is>
+          <t>2107.psd</t>
+        </is>
+      </c>
+      <c r="B4363" t="inlineStr">
+        <is>
+          <t>tamilpsd-10260.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4364">
+      <c r="A4364" s="3" t="inlineStr">
+        <is>
+          <t>2106.psd</t>
+        </is>
+      </c>
+      <c r="B4364" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10261.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4365">
+      <c r="A4365" t="inlineStr">
+        <is>
+          <t>2105.psd</t>
+        </is>
+      </c>
+      <c r="B4365" t="inlineStr">
+        <is>
+          <t>tamilpsd-10262.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4366">
+      <c r="A4366" s="3" t="inlineStr">
+        <is>
+          <t>2104.psd</t>
+        </is>
+      </c>
+      <c r="B4366" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10263.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4367">
+      <c r="A4367" t="inlineStr">
+        <is>
+          <t>2103.psd</t>
+        </is>
+      </c>
+      <c r="B4367" t="inlineStr">
+        <is>
+          <t>tamilpsd-10264.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4368">
+      <c r="A4368" s="3" t="inlineStr">
+        <is>
+          <t>2102.psd</t>
+        </is>
+      </c>
+      <c r="B4368" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10265.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4369">
+      <c r="A4369" t="inlineStr">
+        <is>
+          <t>2101.psd</t>
+        </is>
+      </c>
+      <c r="B4369" t="inlineStr">
+        <is>
+          <t>tamilpsd-10266.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4370">
+      <c r="A4370" s="3" t="inlineStr">
+        <is>
+          <t>2100.psd</t>
+        </is>
+      </c>
+      <c r="B4370" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10267.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4371">
+      <c r="A4371" t="inlineStr">
+        <is>
+          <t>2099.psd</t>
+        </is>
+      </c>
+      <c r="B4371" t="inlineStr">
+        <is>
+          <t>tamilpsd-10268.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4372">
+      <c r="A4372" s="3" t="inlineStr">
+        <is>
+          <t>2098.psd</t>
+        </is>
+      </c>
+      <c r="B4372" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10269.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4373">
+      <c r="A4373" t="inlineStr">
+        <is>
+          <t>2097.psd</t>
+        </is>
+      </c>
+      <c r="B4373" t="inlineStr">
+        <is>
+          <t>tamilpsd-10270.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4374">
+      <c r="A4374" s="3" t="inlineStr">
+        <is>
+          <t>2096.psd</t>
+        </is>
+      </c>
+      <c r="B4374" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10271.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4375">
+      <c r="A4375" t="inlineStr">
+        <is>
+          <t>2095.psd</t>
+        </is>
+      </c>
+      <c r="B4375" t="inlineStr">
+        <is>
+          <t>tamilpsd-10272.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4376">
+      <c r="A4376" s="3" t="inlineStr">
+        <is>
+          <t>2094.psd</t>
+        </is>
+      </c>
+      <c r="B4376" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10273.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4377">
+      <c r="A4377" t="inlineStr">
+        <is>
+          <t>2093.psd</t>
+        </is>
+      </c>
+      <c r="B4377" t="inlineStr">
+        <is>
+          <t>tamilpsd-10274.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4378">
+      <c r="A4378" s="3" t="inlineStr">
+        <is>
+          <t>2092.psd</t>
+        </is>
+      </c>
+      <c r="B4378" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10275.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4379">
+      <c r="A4379" t="inlineStr">
+        <is>
+          <t>2091.psd</t>
+        </is>
+      </c>
+      <c r="B4379" t="inlineStr">
+        <is>
+          <t>tamilpsd-10276.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4380">
+      <c r="A4380" s="3" t="inlineStr">
+        <is>
+          <t>2090.psd</t>
+        </is>
+      </c>
+      <c r="B4380" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10277.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4381">
+      <c r="A4381" t="inlineStr">
+        <is>
+          <t>2089.psd</t>
+        </is>
+      </c>
+      <c r="B4381" t="inlineStr">
+        <is>
+          <t>tamilpsd-10278.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4382">
+      <c r="A4382" s="3" t="inlineStr">
+        <is>
+          <t>2088.psd</t>
+        </is>
+      </c>
+      <c r="B4382" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10279.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4383">
+      <c r="A4383" t="inlineStr">
+        <is>
+          <t>2087.psd</t>
+        </is>
+      </c>
+      <c r="B4383" t="inlineStr">
+        <is>
+          <t>tamilpsd-10280.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4384">
+      <c r="A4384" s="3" t="inlineStr">
+        <is>
+          <t>2086.psd</t>
+        </is>
+      </c>
+      <c r="B4384" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10281.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4385">
+      <c r="A4385" t="inlineStr">
+        <is>
+          <t>2179.psd</t>
+        </is>
+      </c>
+      <c r="B4385" t="inlineStr">
+        <is>
+          <t>tamilpsd-10282.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4386">
+      <c r="A4386" s="3" t="inlineStr">
+        <is>
+          <t>1658.psd</t>
+        </is>
+      </c>
+      <c r="B4386" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10283.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4387">
+      <c r="A4387" t="inlineStr">
+        <is>
+          <t>1657.psd</t>
+        </is>
+      </c>
+      <c r="B4387" t="inlineStr">
+        <is>
+          <t>tamilpsd-10284.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4388">
+      <c r="A4388" s="3" t="inlineStr">
+        <is>
+          <t>1656.psd</t>
+        </is>
+      </c>
+      <c r="B4388" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10285.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4389">
+      <c r="A4389" t="inlineStr">
+        <is>
+          <t>1655.psd</t>
+        </is>
+      </c>
+      <c r="B4389" t="inlineStr">
+        <is>
+          <t>tamilpsd-10286.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4390">
+      <c r="A4390" s="3" t="inlineStr">
+        <is>
+          <t>1654.psd</t>
+        </is>
+      </c>
+      <c r="B4390" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10287.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4391">
+      <c r="A4391" t="inlineStr">
+        <is>
+          <t>1653.psd</t>
+        </is>
+      </c>
+      <c r="B4391" t="inlineStr">
+        <is>
+          <t>tamilpsd-10288.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4392">
+      <c r="A4392" s="3" t="inlineStr">
+        <is>
+          <t>1652.psd</t>
+        </is>
+      </c>
+      <c r="B4392" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10289.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4393">
+      <c r="A4393" t="inlineStr">
+        <is>
+          <t>1651.psd</t>
+        </is>
+      </c>
+      <c r="B4393" t="inlineStr">
+        <is>
+          <t>tamilpsd-10290.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4394">
+      <c r="A4394" s="3" t="inlineStr">
+        <is>
+          <t>1650.psd</t>
+        </is>
+      </c>
+      <c r="B4394" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10291.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4395">
+      <c r="A4395" t="inlineStr">
+        <is>
+          <t>1649.psd</t>
+        </is>
+      </c>
+      <c r="B4395" t="inlineStr">
+        <is>
+          <t>tamilpsd-10292.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4396">
+      <c r="A4396" s="3" t="inlineStr">
+        <is>
+          <t>1648.psd</t>
+        </is>
+      </c>
+      <c r="B4396" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10293.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4397">
+      <c r="A4397" t="inlineStr">
+        <is>
+          <t>1647.psd</t>
+        </is>
+      </c>
+      <c r="B4397" t="inlineStr">
+        <is>
+          <t>tamilpsd-10294.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4398">
+      <c r="A4398" s="3" t="inlineStr">
+        <is>
+          <t>1646.psd</t>
+        </is>
+      </c>
+      <c r="B4398" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10295.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4399">
+      <c r="A4399" t="inlineStr">
+        <is>
+          <t>1645.psd</t>
+        </is>
+      </c>
+      <c r="B4399" t="inlineStr">
+        <is>
+          <t>tamilpsd-10296.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4400">
+      <c r="A4400" s="3" t="inlineStr">
+        <is>
+          <t>1644.psd</t>
+        </is>
+      </c>
+      <c r="B4400" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10297.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4401">
+      <c r="A4401" t="inlineStr">
+        <is>
+          <t>1643.psd</t>
+        </is>
+      </c>
+      <c r="B4401" t="inlineStr">
+        <is>
+          <t>tamilpsd-10298.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4402">
+      <c r="A4402" s="3" t="inlineStr">
+        <is>
+          <t>1642.psd</t>
+        </is>
+      </c>
+      <c r="B4402" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10299.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4403">
+      <c r="A4403" t="inlineStr">
+        <is>
+          <t>1641.psd</t>
+        </is>
+      </c>
+      <c r="B4403" t="inlineStr">
+        <is>
+          <t>tamilpsd-10300.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4404">
+      <c r="A4404" s="3" t="inlineStr">
+        <is>
+          <t>1640.psd</t>
+        </is>
+      </c>
+      <c r="B4404" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10301.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4405">
+      <c r="A4405" t="inlineStr">
+        <is>
+          <t>1639.psd</t>
+        </is>
+      </c>
+      <c r="B4405" t="inlineStr">
+        <is>
+          <t>tamilpsd-10302.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4406">
+      <c r="A4406" s="3" t="inlineStr">
+        <is>
+          <t>1637.psd</t>
+        </is>
+      </c>
+      <c r="B4406" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10303.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4407">
+      <c r="A4407" t="inlineStr">
+        <is>
+          <t>1636.psd</t>
+        </is>
+      </c>
+      <c r="B4407" t="inlineStr">
+        <is>
+          <t>tamilpsd-10304.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4408">
+      <c r="A4408" s="3" t="inlineStr">
+        <is>
+          <t>1635.psd</t>
+        </is>
+      </c>
+      <c r="B4408" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10305.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4409">
+      <c r="A4409" t="inlineStr">
+        <is>
+          <t>2084.psd</t>
+        </is>
+      </c>
+      <c r="B4409" t="inlineStr">
+        <is>
+          <t>tamilpsd-10306.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4410">
+      <c r="A4410" s="3" t="inlineStr">
+        <is>
+          <t>2083.PSD</t>
+        </is>
+      </c>
+      <c r="B4410" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10307.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4411">
+      <c r="A4411" t="inlineStr">
+        <is>
+          <t>2082.psd</t>
+        </is>
+      </c>
+      <c r="B4411" t="inlineStr">
+        <is>
+          <t>tamilpsd-10308.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4412">
+      <c r="A4412" s="3" t="inlineStr">
+        <is>
+          <t>2081.psd</t>
+        </is>
+      </c>
+      <c r="B4412" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10309.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4413">
+      <c r="A4413" t="inlineStr">
+        <is>
+          <t>2080.psd</t>
+        </is>
+      </c>
+      <c r="B4413" t="inlineStr">
+        <is>
+          <t>tamilpsd-10310.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4414">
+      <c r="A4414" s="3" t="inlineStr">
+        <is>
+          <t>2079.psd</t>
+        </is>
+      </c>
+      <c r="B4414" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10311.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4415">
+      <c r="A4415" t="inlineStr">
+        <is>
+          <t>2078.psd</t>
+        </is>
+      </c>
+      <c r="B4415" t="inlineStr">
+        <is>
+          <t>tamilpsd-10312.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4416">
+      <c r="A4416" s="3" t="inlineStr">
+        <is>
+          <t>2077.PSD</t>
+        </is>
+      </c>
+      <c r="B4416" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10313.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4417">
+      <c r="A4417" t="inlineStr">
+        <is>
+          <t>2076.psd</t>
+        </is>
+      </c>
+      <c r="B4417" t="inlineStr">
+        <is>
+          <t>tamilpsd-10314.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4418">
+      <c r="A4418" s="3" t="inlineStr">
+        <is>
+          <t>2075.psd</t>
+        </is>
+      </c>
+      <c r="B4418" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10315.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4419">
+      <c r="A4419" t="inlineStr">
+        <is>
+          <t>2074.psd</t>
+        </is>
+      </c>
+      <c r="B4419" t="inlineStr">
+        <is>
+          <t>tamilpsd-10316.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4420">
+      <c r="A4420" s="3" t="inlineStr">
+        <is>
+          <t>2073.PSD</t>
+        </is>
+      </c>
+      <c r="B4420" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10317.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4421">
+      <c r="A4421" t="inlineStr">
+        <is>
+          <t>2072.PSD</t>
+        </is>
+      </c>
+      <c r="B4421" t="inlineStr">
+        <is>
+          <t>tamilpsd-10318.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4422">
+      <c r="A4422" s="3" t="inlineStr">
+        <is>
+          <t>2071.psd</t>
+        </is>
+      </c>
+      <c r="B4422" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10319.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4423">
+      <c r="A4423" t="inlineStr">
+        <is>
+          <t>2070.psd</t>
+        </is>
+      </c>
+      <c r="B4423" t="inlineStr">
+        <is>
+          <t>tamilpsd-10320.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4424">
+      <c r="A4424" s="3" t="inlineStr">
+        <is>
+          <t>2069.psd</t>
+        </is>
+      </c>
+      <c r="B4424" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10321.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4425">
+      <c r="A4425" t="inlineStr">
+        <is>
+          <t>2068.psd</t>
+        </is>
+      </c>
+      <c r="B4425" t="inlineStr">
+        <is>
+          <t>tamilpsd-10322.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4426">
+      <c r="A4426" s="3" t="inlineStr">
+        <is>
+          <t>2067.psd</t>
+        </is>
+      </c>
+      <c r="B4426" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10323.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4427">
+      <c r="A4427" t="inlineStr">
+        <is>
+          <t>2066.psd</t>
+        </is>
+      </c>
+      <c r="B4427" t="inlineStr">
+        <is>
+          <t>tamilpsd-10324.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4428">
+      <c r="A4428" s="3" t="inlineStr">
+        <is>
+          <t>2065.PSD</t>
+        </is>
+      </c>
+      <c r="B4428" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10325.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4429">
+      <c r="A4429" t="inlineStr">
+        <is>
+          <t>2064.PSD</t>
+        </is>
+      </c>
+      <c r="B4429" t="inlineStr">
+        <is>
+          <t>tamilpsd-10326.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4430">
+      <c r="A4430" s="3" t="inlineStr">
+        <is>
+          <t>2063.psd</t>
+        </is>
+      </c>
+      <c r="B4430" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10327.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4431">
+      <c r="A4431" t="inlineStr">
+        <is>
+          <t>2062.PSD</t>
+        </is>
+      </c>
+      <c r="B4431" t="inlineStr">
+        <is>
+          <t>tamilpsd-10328.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4432">
+      <c r="A4432" s="3" t="inlineStr">
+        <is>
+          <t>2061.PSD</t>
+        </is>
+      </c>
+      <c r="B4432" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10329.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4433">
+      <c r="A4433" t="inlineStr">
+        <is>
+          <t>2060.psd</t>
+        </is>
+      </c>
+      <c r="B4433" t="inlineStr">
+        <is>
+          <t>tamilpsd-10330.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4434">
+      <c r="A4434" s="3" t="inlineStr">
+        <is>
+          <t>2059.psd</t>
+        </is>
+      </c>
+      <c r="B4434" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10331.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4435">
+      <c r="A4435" t="inlineStr">
+        <is>
+          <t>2058.PSD</t>
+        </is>
+      </c>
+      <c r="B4435" t="inlineStr">
+        <is>
+          <t>tamilpsd-10332.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4436">
+      <c r="A4436" s="3" t="inlineStr">
+        <is>
+          <t>2057.PSD</t>
+        </is>
+      </c>
+      <c r="B4436" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10333.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4437">
+      <c r="A4437" t="inlineStr">
+        <is>
+          <t>2056.PSD</t>
+        </is>
+      </c>
+      <c r="B4437" t="inlineStr">
+        <is>
+          <t>tamilpsd-10334.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4438">
+      <c r="A4438" s="3" t="inlineStr">
+        <is>
+          <t>2055.psd</t>
+        </is>
+      </c>
+      <c r="B4438" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10335.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4439">
+      <c r="A4439" t="inlineStr">
+        <is>
+          <t>2054.psd</t>
+        </is>
+      </c>
+      <c r="B4439" t="inlineStr">
+        <is>
+          <t>tamilpsd-10336.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4440">
+      <c r="A4440" s="3" t="inlineStr">
+        <is>
+          <t>2053.psd</t>
+        </is>
+      </c>
+      <c r="B4440" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10337.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4441">
+      <c r="A4441" t="inlineStr">
+        <is>
+          <t>2052.psd</t>
+        </is>
+      </c>
+      <c r="B4441" t="inlineStr">
+        <is>
+          <t>tamilpsd-10338.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4442">
+      <c r="A4442" s="3" t="inlineStr">
+        <is>
+          <t>2051.psd</t>
+        </is>
+      </c>
+      <c r="B4442" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10339.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4443">
+      <c r="A4443" t="inlineStr">
+        <is>
+          <t>2050.psd</t>
+        </is>
+      </c>
+      <c r="B4443" t="inlineStr">
+        <is>
+          <t>tamilpsd-10340.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4444">
+      <c r="A4444" s="3" t="inlineStr">
+        <is>
+          <t>2049.psd</t>
+        </is>
+      </c>
+      <c r="B4444" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10341.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4445">
+      <c r="A4445" t="inlineStr">
+        <is>
+          <t>2048.PSD</t>
+        </is>
+      </c>
+      <c r="B4445" t="inlineStr">
+        <is>
+          <t>tamilpsd-10342.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4446">
+      <c r="A4446" s="3" t="inlineStr">
+        <is>
+          <t>2047.PSD</t>
+        </is>
+      </c>
+      <c r="B4446" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10343.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4447">
+      <c r="A4447" t="inlineStr">
+        <is>
+          <t>2046.psd</t>
+        </is>
+      </c>
+      <c r="B4447" t="inlineStr">
+        <is>
+          <t>tamilpsd-10344.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4448">
+      <c r="A4448" s="3" t="inlineStr">
+        <is>
+          <t>2045.psd</t>
+        </is>
+      </c>
+      <c r="B4448" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10345.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4449">
+      <c r="A4449" t="inlineStr">
+        <is>
+          <t>2044.PSD</t>
+        </is>
+      </c>
+      <c r="B4449" t="inlineStr">
+        <is>
+          <t>tamilpsd-10346.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4450">
+      <c r="A4450" s="3" t="inlineStr">
+        <is>
+          <t>2043.PSD</t>
+        </is>
+      </c>
+      <c r="B4450" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10347.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4451">
+      <c r="A4451" t="inlineStr">
+        <is>
+          <t>2042.PSD</t>
+        </is>
+      </c>
+      <c r="B4451" t="inlineStr">
+        <is>
+          <t>tamilpsd-10348.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4452">
+      <c r="A4452" s="3" t="inlineStr">
+        <is>
+          <t>2041.psd</t>
+        </is>
+      </c>
+      <c r="B4452" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10349.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4453">
+      <c r="A4453" t="inlineStr">
+        <is>
+          <t>2040.PSD</t>
+        </is>
+      </c>
+      <c r="B4453" t="inlineStr">
+        <is>
+          <t>tamilpsd-10350.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4454">
+      <c r="A4454" s="3" t="inlineStr">
+        <is>
+          <t>2039.PSD</t>
+        </is>
+      </c>
+      <c r="B4454" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10351.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4455">
+      <c r="A4455" t="inlineStr">
+        <is>
+          <t>2038.PSD</t>
+        </is>
+      </c>
+      <c r="B4455" t="inlineStr">
+        <is>
+          <t>tamilpsd-10352.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4456">
+      <c r="A4456" s="3" t="inlineStr">
+        <is>
+          <t>2037.PSD</t>
+        </is>
+      </c>
+      <c r="B4456" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10353.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4457">
+      <c r="A4457" t="inlineStr">
+        <is>
+          <t>2036.psd</t>
+        </is>
+      </c>
+      <c r="B4457" t="inlineStr">
+        <is>
+          <t>tamilpsd-10354.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4458">
+      <c r="A4458" s="3" t="inlineStr">
+        <is>
+          <t>2035.psd</t>
+        </is>
+      </c>
+      <c r="B4458" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10355.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4459">
+      <c r="A4459" t="inlineStr">
+        <is>
+          <t>2034.psd</t>
+        </is>
+      </c>
+      <c r="B4459" t="inlineStr">
+        <is>
+          <t>tamilpsd-10356.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4460">
+      <c r="A4460" s="3" t="inlineStr">
+        <is>
+          <t>2033.psd</t>
+        </is>
+      </c>
+      <c r="B4460" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10357.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4461">
+      <c r="A4461" t="inlineStr">
+        <is>
+          <t>2032.psd</t>
+        </is>
+      </c>
+      <c r="B4461" t="inlineStr">
+        <is>
+          <t>tamilpsd-10358.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4462">
+      <c r="A4462" s="3" t="inlineStr">
+        <is>
+          <t>2031.psd</t>
+        </is>
+      </c>
+      <c r="B4462" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10359.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4463">
+      <c r="A4463" t="inlineStr">
+        <is>
+          <t>2030.psd</t>
+        </is>
+      </c>
+      <c r="B4463" t="inlineStr">
+        <is>
+          <t>tamilpsd-10360.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4464">
+      <c r="A4464" s="3" t="inlineStr">
+        <is>
+          <t>2029.psd</t>
+        </is>
+      </c>
+      <c r="B4464" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10361.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4465">
+      <c r="A4465" t="inlineStr">
+        <is>
+          <t>2028.psd</t>
+        </is>
+      </c>
+      <c r="B4465" t="inlineStr">
+        <is>
+          <t>tamilpsd-10362.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4466">
+      <c r="A4466" s="3" t="inlineStr">
+        <is>
+          <t>2027.psd</t>
+        </is>
+      </c>
+      <c r="B4466" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10363.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4467">
+      <c r="A4467" t="inlineStr">
+        <is>
+          <t>2026.psd</t>
+        </is>
+      </c>
+      <c r="B4467" t="inlineStr">
+        <is>
+          <t>tamilpsd-10364.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4468">
+      <c r="A4468" s="3" t="inlineStr">
+        <is>
+          <t>2025.PSD</t>
+        </is>
+      </c>
+      <c r="B4468" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10365.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4469">
+      <c r="A4469" t="inlineStr">
+        <is>
+          <t>2024.psd</t>
+        </is>
+      </c>
+      <c r="B4469" t="inlineStr">
+        <is>
+          <t>tamilpsd-10366.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4470">
+      <c r="A4470" s="3" t="inlineStr">
+        <is>
+          <t>2023.psd</t>
+        </is>
+      </c>
+      <c r="B4470" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10367.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4471">
+      <c r="A4471" t="inlineStr">
+        <is>
+          <t>2022.psd</t>
+        </is>
+      </c>
+      <c r="B4471" t="inlineStr">
+        <is>
+          <t>tamilpsd-10368.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4472">
+      <c r="A4472" s="3" t="inlineStr">
+        <is>
+          <t>2021.psd</t>
+        </is>
+      </c>
+      <c r="B4472" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10369.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4473">
+      <c r="A4473" t="inlineStr">
+        <is>
+          <t>2020.PSD</t>
+        </is>
+      </c>
+      <c r="B4473" t="inlineStr">
+        <is>
+          <t>tamilpsd-10370.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4474">
+      <c r="A4474" s="3" t="inlineStr">
+        <is>
+          <t>2019.psd</t>
+        </is>
+      </c>
+      <c r="B4474" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10371.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4475">
+      <c r="A4475" t="inlineStr">
+        <is>
+          <t>2018.PSD</t>
+        </is>
+      </c>
+      <c r="B4475" t="inlineStr">
+        <is>
+          <t>tamilpsd-10372.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4476">
+      <c r="A4476" s="3" t="inlineStr">
+        <is>
+          <t>2017.PSD</t>
+        </is>
+      </c>
+      <c r="B4476" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10373.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4477">
+      <c r="A4477" t="inlineStr">
+        <is>
+          <t>2016.PSD</t>
+        </is>
+      </c>
+      <c r="B4477" t="inlineStr">
+        <is>
+          <t>tamilpsd-10374.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4478">
+      <c r="A4478" s="3" t="inlineStr">
+        <is>
+          <t>2015.psd</t>
+        </is>
+      </c>
+      <c r="B4478" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10375.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4479">
+      <c r="A4479" t="inlineStr">
+        <is>
+          <t>2014.psd</t>
+        </is>
+      </c>
+      <c r="B4479" t="inlineStr">
+        <is>
+          <t>tamilpsd-10376.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4480">
+      <c r="A4480" s="3" t="inlineStr">
+        <is>
+          <t>2013.PSD</t>
+        </is>
+      </c>
+      <c r="B4480" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10377.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4481">
+      <c r="A4481" t="inlineStr">
+        <is>
+          <t>2012.psd</t>
+        </is>
+      </c>
+      <c r="B4481" t="inlineStr">
+        <is>
+          <t>tamilpsd-10378.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4482">
+      <c r="A4482" s="3" t="inlineStr">
+        <is>
+          <t>2011.PSD</t>
+        </is>
+      </c>
+      <c r="B4482" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10379.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4483">
+      <c r="A4483" t="inlineStr">
+        <is>
+          <t>2010.PSD</t>
+        </is>
+      </c>
+      <c r="B4483" t="inlineStr">
+        <is>
+          <t>tamilpsd-10380.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4484">
+      <c r="A4484" s="3" t="inlineStr">
+        <is>
+          <t>2009.PSD</t>
+        </is>
+      </c>
+      <c r="B4484" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10381.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4485">
+      <c r="A4485" t="inlineStr">
+        <is>
+          <t>2008.psd</t>
+        </is>
+      </c>
+      <c r="B4485" t="inlineStr">
+        <is>
+          <t>tamilpsd-10382.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4486">
+      <c r="A4486" s="3" t="inlineStr">
+        <is>
+          <t>2007.PSD</t>
+        </is>
+      </c>
+      <c r="B4486" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10383.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4487">
+      <c r="A4487" t="inlineStr">
+        <is>
+          <t>2006.PSD</t>
+        </is>
+      </c>
+      <c r="B4487" t="inlineStr">
+        <is>
+          <t>tamilpsd-10384.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4488">
+      <c r="A4488" s="3" t="inlineStr">
+        <is>
+          <t>2005.PSD</t>
+        </is>
+      </c>
+      <c r="B4488" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10385.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4489">
+      <c r="A4489" t="inlineStr">
+        <is>
+          <t>2004.PSD</t>
+        </is>
+      </c>
+      <c r="B4489" t="inlineStr">
+        <is>
+          <t>tamilpsd-10386.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4490">
+      <c r="A4490" s="3" t="inlineStr">
+        <is>
+          <t>2003.PSD</t>
+        </is>
+      </c>
+      <c r="B4490" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10387.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4491">
+      <c r="A4491" t="inlineStr">
+        <is>
+          <t>2002.PSD</t>
+        </is>
+      </c>
+      <c r="B4491" t="inlineStr">
+        <is>
+          <t>tamilpsd-10388.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4492">
+      <c r="A4492" s="3" t="inlineStr">
+        <is>
+          <t>2001.psd</t>
+        </is>
+      </c>
+      <c r="B4492" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10389.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4493">
+      <c r="A4493" t="inlineStr">
+        <is>
+          <t>2000.PSD</t>
+        </is>
+      </c>
+      <c r="B4493" t="inlineStr">
+        <is>
+          <t>tamilpsd-10390.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4494">
+      <c r="A4494" s="3" t="inlineStr">
+        <is>
+          <t>1999.psd</t>
+        </is>
+      </c>
+      <c r="B4494" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10391.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4495">
+      <c r="A4495" t="inlineStr">
+        <is>
+          <t>1998.psd</t>
+        </is>
+      </c>
+      <c r="B4495" t="inlineStr">
+        <is>
+          <t>tamilpsd-10392.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4496">
+      <c r="A4496" s="3" t="inlineStr">
+        <is>
+          <t>1997.PSD</t>
+        </is>
+      </c>
+      <c r="B4496" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10393.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4497">
+      <c r="A4497" t="inlineStr">
+        <is>
+          <t>1996.psd</t>
+        </is>
+      </c>
+      <c r="B4497" t="inlineStr">
+        <is>
+          <t>tamilpsd-10394.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4498">
+      <c r="A4498" s="3" t="inlineStr">
+        <is>
+          <t>1995.PSD</t>
+        </is>
+      </c>
+      <c r="B4498" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10395.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4499">
+      <c r="A4499" t="inlineStr">
+        <is>
+          <t>1994.PSD</t>
+        </is>
+      </c>
+      <c r="B4499" t="inlineStr">
+        <is>
+          <t>tamilpsd-10396.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4500">
+      <c r="A4500" s="3" t="inlineStr">
+        <is>
+          <t>1993.PSD</t>
+        </is>
+      </c>
+      <c r="B4500" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10397.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4501">
+      <c r="A4501" t="inlineStr">
+        <is>
+          <t>1992.psd</t>
+        </is>
+      </c>
+      <c r="B4501" t="inlineStr">
+        <is>
+          <t>tamilpsd-10398.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4502">
+      <c r="A4502" s="3" t="inlineStr">
+        <is>
+          <t>1991.psd</t>
+        </is>
+      </c>
+      <c r="B4502" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10399.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4503">
+      <c r="A4503" t="inlineStr">
+        <is>
+          <t>1990.psd</t>
+        </is>
+      </c>
+      <c r="B4503" t="inlineStr">
+        <is>
+          <t>tamilpsd-10400.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4504">
+      <c r="A4504" s="3" t="inlineStr">
+        <is>
+          <t>1989.PSD</t>
+        </is>
+      </c>
+      <c r="B4504" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10401.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4505">
+      <c r="A4505" t="inlineStr">
+        <is>
+          <t>1988.psd</t>
+        </is>
+      </c>
+      <c r="B4505" t="inlineStr">
+        <is>
+          <t>tamilpsd-10402.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4506">
+      <c r="A4506" s="3" t="inlineStr">
+        <is>
+          <t>1987.PSD</t>
+        </is>
+      </c>
+      <c r="B4506" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10403.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4507">
+      <c r="A4507" t="inlineStr">
+        <is>
+          <t>1986.psd</t>
+        </is>
+      </c>
+      <c r="B4507" t="inlineStr">
+        <is>
+          <t>tamilpsd-10404.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4508">
+      <c r="A4508" s="3" t="inlineStr">
+        <is>
+          <t>2085.psd</t>
+        </is>
+      </c>
+      <c r="B4508" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10405.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4509">
+      <c r="A4509" t="inlineStr">
+        <is>
+          <t>1984.psd</t>
+        </is>
+      </c>
+      <c r="B4509" t="inlineStr">
+        <is>
+          <t>tamilpsd-10406.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4510">
+      <c r="A4510" s="3" t="inlineStr">
+        <is>
+          <t>1983.psd</t>
+        </is>
+      </c>
+      <c r="B4510" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10407.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4511">
+      <c r="A4511" t="inlineStr">
+        <is>
+          <t>1982.psd</t>
+        </is>
+      </c>
+      <c r="B4511" t="inlineStr">
+        <is>
+          <t>tamilpsd-10408.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4512">
+      <c r="A4512" s="3" t="inlineStr">
+        <is>
+          <t>1981.psd</t>
+        </is>
+      </c>
+      <c r="B4512" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10409.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4513">
+      <c r="A4513" t="inlineStr">
+        <is>
+          <t>1980.psd</t>
+        </is>
+      </c>
+      <c r="B4513" t="inlineStr">
+        <is>
+          <t>tamilpsd-10410.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4514">
+      <c r="A4514" s="3" t="inlineStr">
+        <is>
+          <t>1979.psd</t>
+        </is>
+      </c>
+      <c r="B4514" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10411.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4515">
+      <c r="A4515" t="inlineStr">
+        <is>
+          <t>1978.psd</t>
+        </is>
+      </c>
+      <c r="B4515" t="inlineStr">
+        <is>
+          <t>tamilpsd-10412.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4516">
+      <c r="A4516" s="3" t="inlineStr">
+        <is>
+          <t>1977.psd</t>
+        </is>
+      </c>
+      <c r="B4516" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10413.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4517">
+      <c r="A4517" t="inlineStr">
+        <is>
+          <t>1976.psd</t>
+        </is>
+      </c>
+      <c r="B4517" t="inlineStr">
+        <is>
+          <t>tamilpsd-10414.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4518">
+      <c r="A4518" s="3" t="inlineStr">
+        <is>
+          <t>1975.psd</t>
+        </is>
+      </c>
+      <c r="B4518" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10415.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4519">
+      <c r="A4519" t="inlineStr">
+        <is>
+          <t>1974.psd</t>
+        </is>
+      </c>
+      <c r="B4519" t="inlineStr">
+        <is>
+          <t>tamilpsd-10416.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4520">
+      <c r="A4520" s="3" t="inlineStr">
+        <is>
+          <t>1973.psd</t>
+        </is>
+      </c>
+      <c r="B4520" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10417.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4521">
+      <c r="A4521" t="inlineStr">
+        <is>
+          <t>1972.psd</t>
+        </is>
+      </c>
+      <c r="B4521" t="inlineStr">
+        <is>
+          <t>tamilpsd-10418.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4522">
+      <c r="A4522" s="3" t="inlineStr">
+        <is>
+          <t>1971.psd</t>
+        </is>
+      </c>
+      <c r="B4522" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10419.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4523">
+      <c r="A4523" t="inlineStr">
+        <is>
+          <t>1970.psd</t>
+        </is>
+      </c>
+      <c r="B4523" t="inlineStr">
+        <is>
+          <t>tamilpsd-10420.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4524">
+      <c r="A4524" s="3" t="inlineStr">
+        <is>
+          <t>1969.psd</t>
+        </is>
+      </c>
+      <c r="B4524" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10421.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4525">
+      <c r="A4525" t="inlineStr">
+        <is>
+          <t>1968.psd</t>
+        </is>
+      </c>
+      <c r="B4525" t="inlineStr">
+        <is>
+          <t>tamilpsd-10422.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4526">
+      <c r="A4526" s="3" t="inlineStr">
+        <is>
+          <t>1967.psd</t>
+        </is>
+      </c>
+      <c r="B4526" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10423.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4527">
+      <c r="A4527" t="inlineStr">
+        <is>
+          <t>1966.psd</t>
+        </is>
+      </c>
+      <c r="B4527" t="inlineStr">
+        <is>
+          <t>tamilpsd-10424.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4528">
+      <c r="A4528" s="3" t="inlineStr">
+        <is>
+          <t>1965.psd</t>
+        </is>
+      </c>
+      <c r="B4528" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10425.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4529">
+      <c r="A4529" t="inlineStr">
+        <is>
+          <t>1964.psd</t>
+        </is>
+      </c>
+      <c r="B4529" t="inlineStr">
+        <is>
+          <t>tamilpsd-10426.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4530">
+      <c r="A4530" s="3" t="inlineStr">
+        <is>
+          <t>1963.psd</t>
+        </is>
+      </c>
+      <c r="B4530" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10427.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4531">
+      <c r="A4531" t="inlineStr">
+        <is>
+          <t>1962.psd</t>
+        </is>
+      </c>
+      <c r="B4531" t="inlineStr">
+        <is>
+          <t>tamilpsd-10428.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4532">
+      <c r="A4532" s="3" t="inlineStr">
+        <is>
+          <t>1961.psd</t>
+        </is>
+      </c>
+      <c r="B4532" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10429.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4533">
+      <c r="A4533" t="inlineStr">
+        <is>
+          <t>1960.psd</t>
+        </is>
+      </c>
+      <c r="B4533" t="inlineStr">
+        <is>
+          <t>tamilpsd-10430.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4534">
+      <c r="A4534" s="3" t="inlineStr">
+        <is>
+          <t>1959.psd</t>
+        </is>
+      </c>
+      <c r="B4534" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10431.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4535">
+      <c r="A4535" t="inlineStr">
+        <is>
+          <t>1958.psd</t>
+        </is>
+      </c>
+      <c r="B4535" t="inlineStr">
+        <is>
+          <t>tamilpsd-10432.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4536">
+      <c r="A4536" s="3" t="inlineStr">
+        <is>
+          <t>1957.psd</t>
+        </is>
+      </c>
+      <c r="B4536" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10433.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4537">
+      <c r="A4537" t="inlineStr">
+        <is>
+          <t>1956.psd</t>
+        </is>
+      </c>
+      <c r="B4537" t="inlineStr">
+        <is>
+          <t>tamilpsd-10434.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4538">
+      <c r="A4538" s="3" t="inlineStr">
+        <is>
+          <t>1955.psd</t>
+        </is>
+      </c>
+      <c r="B4538" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10435.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4539">
+      <c r="A4539" t="inlineStr">
+        <is>
+          <t>1954.psd</t>
+        </is>
+      </c>
+      <c r="B4539" t="inlineStr">
+        <is>
+          <t>tamilpsd-10436.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4540">
+      <c r="A4540" s="3" t="inlineStr">
+        <is>
+          <t>1953.psd</t>
+        </is>
+      </c>
+      <c r="B4540" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10437.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4541">
+      <c r="A4541" t="inlineStr">
+        <is>
+          <t>1952.psd</t>
+        </is>
+      </c>
+      <c r="B4541" t="inlineStr">
+        <is>
+          <t>tamilpsd-10438.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4542">
+      <c r="A4542" s="3" t="inlineStr">
+        <is>
+          <t>1951.psd</t>
+        </is>
+      </c>
+      <c r="B4542" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10439.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4543">
+      <c r="A4543" t="inlineStr">
+        <is>
+          <t>1950.psd</t>
+        </is>
+      </c>
+      <c r="B4543" t="inlineStr">
+        <is>
+          <t>tamilpsd-10440.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4544">
+      <c r="A4544" s="3" t="inlineStr">
+        <is>
+          <t>1949.psd</t>
+        </is>
+      </c>
+      <c r="B4544" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10441.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4545">
+      <c r="A4545" t="inlineStr">
+        <is>
+          <t>1948.psd</t>
+        </is>
+      </c>
+      <c r="B4545" t="inlineStr">
+        <is>
+          <t>tamilpsd-10442.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4546">
+      <c r="A4546" s="3" t="inlineStr">
+        <is>
+          <t>1947.psd</t>
+        </is>
+      </c>
+      <c r="B4546" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10443.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4547">
+      <c r="A4547" t="inlineStr">
+        <is>
+          <t>1946.psd</t>
+        </is>
+      </c>
+      <c r="B4547" t="inlineStr">
+        <is>
+          <t>tamilpsd-10444.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4548">
+      <c r="A4548" s="3" t="inlineStr">
+        <is>
+          <t>1945.psd</t>
+        </is>
+      </c>
+      <c r="B4548" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10445.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4549">
+      <c r="A4549" t="inlineStr">
+        <is>
+          <t>1944.psd</t>
+        </is>
+      </c>
+      <c r="B4549" t="inlineStr">
+        <is>
+          <t>tamilpsd-10446.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4550">
+      <c r="A4550" s="3" t="inlineStr">
+        <is>
+          <t>1943.psd</t>
+        </is>
+      </c>
+      <c r="B4550" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10447.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4551">
+      <c r="A4551" t="inlineStr">
+        <is>
+          <t>1942.psd</t>
+        </is>
+      </c>
+      <c r="B4551" t="inlineStr">
+        <is>
+          <t>tamilpsd-10448.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4552">
+      <c r="A4552" s="3" t="inlineStr">
+        <is>
+          <t>1941.psd</t>
+        </is>
+      </c>
+      <c r="B4552" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10449.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4553">
+      <c r="A4553" t="inlineStr">
+        <is>
+          <t>1940.psd</t>
+        </is>
+      </c>
+      <c r="B4553" t="inlineStr">
+        <is>
+          <t>tamilpsd-10450.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4554">
+      <c r="A4554" s="3" t="inlineStr">
+        <is>
+          <t>1939.psd</t>
+        </is>
+      </c>
+      <c r="B4554" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10451.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4555">
+      <c r="A4555" t="inlineStr">
+        <is>
+          <t>1938.psd</t>
+        </is>
+      </c>
+      <c r="B4555" t="inlineStr">
+        <is>
+          <t>tamilpsd-10452.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4556">
+      <c r="A4556" s="3" t="inlineStr">
+        <is>
+          <t>1937.psd</t>
+        </is>
+      </c>
+      <c r="B4556" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10453.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4557">
+      <c r="A4557" t="inlineStr">
+        <is>
+          <t>1936.psd</t>
+        </is>
+      </c>
+      <c r="B4557" t="inlineStr">
+        <is>
+          <t>tamilpsd-10454.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4558">
+      <c r="A4558" s="3" t="inlineStr">
+        <is>
+          <t>1935.psd</t>
+        </is>
+      </c>
+      <c r="B4558" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10455.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4559">
+      <c r="A4559" t="inlineStr">
+        <is>
+          <t>1934.psd</t>
+        </is>
+      </c>
+      <c r="B4559" t="inlineStr">
+        <is>
+          <t>tamilpsd-10456.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4560">
+      <c r="A4560" s="3" t="inlineStr">
+        <is>
+          <t>1933.psd</t>
+        </is>
+      </c>
+      <c r="B4560" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10457.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4561">
+      <c r="A4561" t="inlineStr">
+        <is>
+          <t>1932.psd</t>
+        </is>
+      </c>
+      <c r="B4561" t="inlineStr">
+        <is>
+          <t>tamilpsd-10458.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4562">
+      <c r="A4562" s="3" t="inlineStr">
+        <is>
+          <t>1931.psd</t>
+        </is>
+      </c>
+      <c r="B4562" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10459.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4563">
+      <c r="A4563" t="inlineStr">
+        <is>
+          <t>1930.psd</t>
+        </is>
+      </c>
+      <c r="B4563" t="inlineStr">
+        <is>
+          <t>tamilpsd-10460.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4564">
+      <c r="A4564" s="3" t="inlineStr">
+        <is>
+          <t>1929.psd</t>
+        </is>
+      </c>
+      <c r="B4564" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10461.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4565">
+      <c r="A4565" t="inlineStr">
+        <is>
+          <t>1928.psd</t>
+        </is>
+      </c>
+      <c r="B4565" t="inlineStr">
+        <is>
+          <t>tamilpsd-10462.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4566">
+      <c r="A4566" s="3" t="inlineStr">
+        <is>
+          <t>1927.psd</t>
+        </is>
+      </c>
+      <c r="B4566" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10463.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4567">
+      <c r="A4567" t="inlineStr">
+        <is>
+          <t>1926.psd</t>
+        </is>
+      </c>
+      <c r="B4567" t="inlineStr">
+        <is>
+          <t>tamilpsd-10464.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4568">
+      <c r="A4568" s="3" t="inlineStr">
+        <is>
+          <t>1925.psd</t>
+        </is>
+      </c>
+      <c r="B4568" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10465.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4569">
+      <c r="A4569" t="inlineStr">
+        <is>
+          <t>1924.psd</t>
+        </is>
+      </c>
+      <c r="B4569" t="inlineStr">
+        <is>
+          <t>tamilpsd-10466.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4570">
+      <c r="A4570" s="3" t="inlineStr">
+        <is>
+          <t>1923.psd</t>
+        </is>
+      </c>
+      <c r="B4570" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10467.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4571">
+      <c r="A4571" t="inlineStr">
+        <is>
+          <t>1922.psd</t>
+        </is>
+      </c>
+      <c r="B4571" t="inlineStr">
+        <is>
+          <t>tamilpsd-10468.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4572">
+      <c r="A4572" s="3" t="inlineStr">
+        <is>
+          <t>1921.psd</t>
+        </is>
+      </c>
+      <c r="B4572" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10469.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4573">
+      <c r="A4573" t="inlineStr">
+        <is>
+          <t>1920.psd</t>
+        </is>
+      </c>
+      <c r="B4573" t="inlineStr">
+        <is>
+          <t>tamilpsd-10470.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4574">
+      <c r="A4574" s="3" t="inlineStr">
+        <is>
+          <t>1919.psd</t>
+        </is>
+      </c>
+      <c r="B4574" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10471.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4575">
+      <c r="A4575" t="inlineStr">
+        <is>
+          <t>1918.psd</t>
+        </is>
+      </c>
+      <c r="B4575" t="inlineStr">
+        <is>
+          <t>tamilpsd-10472.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4576">
+      <c r="A4576" s="3" t="inlineStr">
+        <is>
+          <t>1917.psd</t>
+        </is>
+      </c>
+      <c r="B4576" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10473.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4577">
+      <c r="A4577" t="inlineStr">
+        <is>
+          <t>1916.psd</t>
+        </is>
+      </c>
+      <c r="B4577" t="inlineStr">
+        <is>
+          <t>tamilpsd-10474.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4578">
+      <c r="A4578" s="3" t="inlineStr">
+        <is>
+          <t>1985.psd</t>
+        </is>
+      </c>
+      <c r="B4578" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10475.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4579">
+      <c r="A4579" t="inlineStr">
+        <is>
+          <t>1913.psd</t>
+        </is>
+      </c>
+      <c r="B4579" t="inlineStr">
+        <is>
+          <t>tamilpsd-10476.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4580">
+      <c r="A4580" s="3" t="inlineStr">
+        <is>
+          <t>1912.psd</t>
+        </is>
+      </c>
+      <c r="B4580" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10477.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4581">
+      <c r="A4581" t="inlineStr">
+        <is>
+          <t>1911.psd</t>
+        </is>
+      </c>
+      <c r="B4581" t="inlineStr">
+        <is>
+          <t>tamilpsd-10478.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4582">
+      <c r="A4582" s="3" t="inlineStr">
+        <is>
+          <t>1910.psd</t>
+        </is>
+      </c>
+      <c r="B4582" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10479.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4583">
+      <c r="A4583" t="inlineStr">
+        <is>
+          <t>1909.psd</t>
+        </is>
+      </c>
+      <c r="B4583" t="inlineStr">
+        <is>
+          <t>tamilpsd-10480.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4584">
+      <c r="A4584" s="3" t="inlineStr">
+        <is>
+          <t>1908.psd</t>
+        </is>
+      </c>
+      <c r="B4584" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10481.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4585">
+      <c r="A4585" t="inlineStr">
+        <is>
+          <t>1907.psd</t>
+        </is>
+      </c>
+      <c r="B4585" t="inlineStr">
+        <is>
+          <t>tamilpsd-10482.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4586">
+      <c r="A4586" s="3" t="inlineStr">
+        <is>
+          <t>1906.psd</t>
+        </is>
+      </c>
+      <c r="B4586" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10483.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4587">
+      <c r="A4587" t="inlineStr">
+        <is>
+          <t>1905.psd</t>
+        </is>
+      </c>
+      <c r="B4587" t="inlineStr">
+        <is>
+          <t>tamilpsd-10484.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4588">
+      <c r="A4588" s="3" t="inlineStr">
+        <is>
+          <t>1904.psd</t>
+        </is>
+      </c>
+      <c r="B4588" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10485.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4589">
+      <c r="A4589" t="inlineStr">
+        <is>
+          <t>1903.psd</t>
+        </is>
+      </c>
+      <c r="B4589" t="inlineStr">
+        <is>
+          <t>tamilpsd-10486.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4590">
+      <c r="A4590" s="3" t="inlineStr">
+        <is>
+          <t>1902.psd</t>
+        </is>
+      </c>
+      <c r="B4590" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10487.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4591">
+      <c r="A4591" t="inlineStr">
+        <is>
+          <t>1901.psd</t>
+        </is>
+      </c>
+      <c r="B4591" t="inlineStr">
+        <is>
+          <t>tamilpsd-10488.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4592">
+      <c r="A4592" s="3" t="inlineStr">
+        <is>
+          <t>1900.psd</t>
+        </is>
+      </c>
+      <c r="B4592" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10489.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4593">
+      <c r="A4593" t="inlineStr">
+        <is>
+          <t>1899.psd</t>
+        </is>
+      </c>
+      <c r="B4593" t="inlineStr">
+        <is>
+          <t>tamilpsd-10490.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4594">
+      <c r="A4594" s="3" t="inlineStr">
+        <is>
+          <t>1898.psd</t>
+        </is>
+      </c>
+      <c r="B4594" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10491.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4595">
+      <c r="A4595" t="inlineStr">
+        <is>
+          <t>1897.psd</t>
+        </is>
+      </c>
+      <c r="B4595" t="inlineStr">
+        <is>
+          <t>tamilpsd-10492.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4596">
+      <c r="A4596" s="3" t="inlineStr">
+        <is>
+          <t>1896.psd</t>
+        </is>
+      </c>
+      <c r="B4596" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10493.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4597">
+      <c r="A4597" t="inlineStr">
+        <is>
+          <t>1895.psd</t>
+        </is>
+      </c>
+      <c r="B4597" t="inlineStr">
+        <is>
+          <t>tamilpsd-10494.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4598">
+      <c r="A4598" s="3" t="inlineStr">
+        <is>
+          <t>1894.psd</t>
+        </is>
+      </c>
+      <c r="B4598" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10495.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4599">
+      <c r="A4599" t="inlineStr">
+        <is>
+          <t>1893.psd</t>
+        </is>
+      </c>
+      <c r="B4599" t="inlineStr">
+        <is>
+          <t>tamilpsd-10496.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4600">
+      <c r="A4600" s="3" t="inlineStr">
+        <is>
+          <t>1892.psd</t>
+        </is>
+      </c>
+      <c r="B4600" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10497.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4601">
+      <c r="A4601" t="inlineStr">
+        <is>
+          <t>1891.psd</t>
+        </is>
+      </c>
+      <c r="B4601" t="inlineStr">
+        <is>
+          <t>tamilpsd-10498.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4602">
+      <c r="A4602" s="3" t="inlineStr">
+        <is>
+          <t>1890.psd</t>
+        </is>
+      </c>
+      <c r="B4602" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10499.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4603">
+      <c r="A4603" t="inlineStr">
+        <is>
+          <t>1889.psd</t>
+        </is>
+      </c>
+      <c r="B4603" t="inlineStr">
+        <is>
+          <t>tamilpsd-10500.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4604">
+      <c r="A4604" s="3" t="inlineStr">
+        <is>
+          <t>1888.psd</t>
+        </is>
+      </c>
+      <c r="B4604" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10501.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4605">
+      <c r="A4605" t="inlineStr">
+        <is>
+          <t>1887.psd</t>
+        </is>
+      </c>
+      <c r="B4605" t="inlineStr">
+        <is>
+          <t>tamilpsd-10502.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4606">
+      <c r="A4606" s="3" t="inlineStr">
+        <is>
+          <t>1886.psd</t>
+        </is>
+      </c>
+      <c r="B4606" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10503.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4607">
+      <c r="A4607" t="inlineStr">
+        <is>
+          <t>1885.psd</t>
+        </is>
+      </c>
+      <c r="B4607" t="inlineStr">
+        <is>
+          <t>tamilpsd-10504.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4608">
+      <c r="A4608" s="3" t="inlineStr">
+        <is>
+          <t>1884.psd</t>
+        </is>
+      </c>
+      <c r="B4608" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10505.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4609">
+      <c r="A4609" t="inlineStr">
+        <is>
+          <t>1883.psd</t>
+        </is>
+      </c>
+      <c r="B4609" t="inlineStr">
+        <is>
+          <t>tamilpsd-10506.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4610">
+      <c r="A4610" s="3" t="inlineStr">
+        <is>
+          <t>1882.psd</t>
+        </is>
+      </c>
+      <c r="B4610" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10507.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4611">
+      <c r="A4611" t="inlineStr">
+        <is>
+          <t>1881.psd</t>
+        </is>
+      </c>
+      <c r="B4611" t="inlineStr">
+        <is>
+          <t>tamilpsd-10508.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4612">
+      <c r="A4612" s="3" t="inlineStr">
+        <is>
+          <t>1915.psd</t>
+        </is>
+      </c>
+      <c r="B4612" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10509.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4613">
+      <c r="A4613" t="inlineStr">
+        <is>
+          <t>91.psd</t>
+        </is>
+      </c>
+      <c r="B4613" t="inlineStr">
+        <is>
+          <t>tamilpsd-10510.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4614">
+      <c r="A4614" s="3" t="inlineStr">
+        <is>
+          <t>92.psd</t>
+        </is>
+      </c>
+      <c r="B4614" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10511.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4615">
+      <c r="A4615" t="inlineStr">
+        <is>
+          <t>90.psd</t>
+        </is>
+      </c>
+      <c r="B4615" t="inlineStr">
+        <is>
+          <t>tamilpsd-10515.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4616">
+      <c r="A4616" s="3" t="inlineStr">
+        <is>
+          <t>82.psd</t>
+        </is>
+      </c>
+      <c r="B4616" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10516.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4617">
+      <c r="A4617" t="inlineStr">
+        <is>
+          <t>83.psd</t>
+        </is>
+      </c>
+      <c r="B4617" t="inlineStr">
+        <is>
+          <t>tamilpsd-10517.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4618">
+      <c r="A4618" s="3" t="inlineStr">
+        <is>
+          <t>84.psd</t>
+        </is>
+      </c>
+      <c r="B4618" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10518.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4619">
+      <c r="A4619" t="inlineStr">
+        <is>
+          <t>79.psd</t>
+        </is>
+      </c>
+      <c r="B4619" t="inlineStr">
+        <is>
+          <t>tamilpsd-10519.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4620">
+      <c r="A4620" s="3" t="inlineStr">
+        <is>
+          <t>81.psd</t>
+        </is>
+      </c>
+      <c r="B4620" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10521.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4621">
+      <c r="A4621" t="inlineStr">
+        <is>
+          <t>76.psd</t>
+        </is>
+      </c>
+      <c r="B4621" t="inlineStr">
+        <is>
+          <t>tamilpsd-10522.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4622">
+      <c r="A4622" s="3" t="inlineStr">
+        <is>
+          <t>68.psd</t>
+        </is>
+      </c>
+      <c r="B4622" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10526.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4623">
+      <c r="A4623" t="inlineStr">
+        <is>
+          <t>69.psd</t>
+        </is>
+      </c>
+      <c r="B4623" t="inlineStr">
+        <is>
+          <t>tamilpsd-10527.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4624">
+      <c r="A4624" s="3" t="inlineStr">
+        <is>
+          <t>63.psd</t>
+        </is>
+      </c>
+      <c r="B4624" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10530.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4625">
+      <c r="A4625" t="inlineStr">
+        <is>
+          <t>1847.psd</t>
+        </is>
+      </c>
+      <c r="B4625" t="inlineStr">
+        <is>
+          <t>tamilpsd-10531.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4626">
+      <c r="A4626" s="3" t="inlineStr">
+        <is>
+          <t>1846.psd</t>
+        </is>
+      </c>
+      <c r="B4626" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10532.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4627">
+      <c r="A4627" t="inlineStr">
+        <is>
+          <t>1845.psd</t>
+        </is>
+      </c>
+      <c r="B4627" t="inlineStr">
+        <is>
+          <t>tamilpsd-10533.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4628">
+      <c r="A4628" s="3" t="inlineStr">
+        <is>
+          <t>1844.psd</t>
+        </is>
+      </c>
+      <c r="B4628" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10534.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4629">
+      <c r="A4629" t="inlineStr">
+        <is>
+          <t>1843.psd</t>
+        </is>
+      </c>
+      <c r="B4629" t="inlineStr">
+        <is>
+          <t>tamilpsd-10535.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4630">
+      <c r="A4630" s="3" t="inlineStr">
+        <is>
+          <t>1842.psd</t>
+        </is>
+      </c>
+      <c r="B4630" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10536.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4631">
+      <c r="A4631" t="inlineStr">
+        <is>
+          <t>1841.psd</t>
+        </is>
+      </c>
+      <c r="B4631" t="inlineStr">
+        <is>
+          <t>tamilpsd-10537.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4632">
+      <c r="A4632" s="3" t="inlineStr">
+        <is>
+          <t>1840.psd</t>
+        </is>
+      </c>
+      <c r="B4632" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10538.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4633">
+      <c r="A4633" t="inlineStr">
+        <is>
+          <t>1839.psd</t>
+        </is>
+      </c>
+      <c r="B4633" t="inlineStr">
+        <is>
+          <t>tamilpsd-10539.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4634">
+      <c r="A4634" s="3" t="inlineStr">
+        <is>
+          <t>1838.psd</t>
+        </is>
+      </c>
+      <c r="B4634" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10540.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4635">
+      <c r="A4635" t="inlineStr">
+        <is>
+          <t>1837.psd</t>
+        </is>
+      </c>
+      <c r="B4635" t="inlineStr">
+        <is>
+          <t>tamilpsd-10541.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4636">
+      <c r="A4636" s="3" t="inlineStr">
+        <is>
+          <t>1836.psd</t>
+        </is>
+      </c>
+      <c r="B4636" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10542.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4637">
+      <c r="A4637" t="inlineStr">
+        <is>
+          <t>1835.psd</t>
+        </is>
+      </c>
+      <c r="B4637" t="inlineStr">
+        <is>
+          <t>tamilpsd-10543.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4638">
+      <c r="A4638" s="3" t="inlineStr">
+        <is>
+          <t>1834.psd</t>
+        </is>
+      </c>
+      <c r="B4638" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10544.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4639">
+      <c r="A4639" t="inlineStr">
+        <is>
+          <t>1833.psd</t>
+        </is>
+      </c>
+      <c r="B4639" t="inlineStr">
+        <is>
+          <t>tamilpsd-10545.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4640">
+      <c r="A4640" s="3" t="inlineStr">
+        <is>
+          <t>1832.psd</t>
+        </is>
+      </c>
+      <c r="B4640" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10546.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4641">
+      <c r="A4641" t="inlineStr">
+        <is>
+          <t>1831.psd</t>
+        </is>
+      </c>
+      <c r="B4641" t="inlineStr">
+        <is>
+          <t>tamilpsd-10547.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4642">
+      <c r="A4642" s="3" t="inlineStr">
+        <is>
+          <t>1830.psd</t>
+        </is>
+      </c>
+      <c r="B4642" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10548.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4643">
+      <c r="A4643" t="inlineStr">
+        <is>
+          <t>1829.psd</t>
+        </is>
+      </c>
+      <c r="B4643" t="inlineStr">
+        <is>
+          <t>tamilpsd-10549.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4644">
+      <c r="A4644" s="3" t="inlineStr">
+        <is>
+          <t>1828.psd</t>
+        </is>
+      </c>
+      <c r="B4644" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10550.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4645">
+      <c r="A4645" t="inlineStr">
+        <is>
+          <t>1827.psd</t>
+        </is>
+      </c>
+      <c r="B4645" t="inlineStr">
+        <is>
+          <t>tamilpsd-10551.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4646">
+      <c r="A4646" s="3" t="inlineStr">
+        <is>
+          <t>1826.psd</t>
+        </is>
+      </c>
+      <c r="B4646" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10552.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4647">
+      <c r="A4647" t="inlineStr">
+        <is>
+          <t>1825.psd</t>
+        </is>
+      </c>
+      <c r="B4647" t="inlineStr">
+        <is>
+          <t>tamilpsd-10553.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4648">
+      <c r="A4648" s="3" t="inlineStr">
+        <is>
+          <t>1824.psd</t>
+        </is>
+      </c>
+      <c r="B4648" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10554.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4649">
+      <c r="A4649" t="inlineStr">
+        <is>
+          <t>1823.psd</t>
+        </is>
+      </c>
+      <c r="B4649" t="inlineStr">
+        <is>
+          <t>tamilpsd-10555.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4650">
+      <c r="A4650" s="3" t="inlineStr">
+        <is>
+          <t>1822.psd</t>
+        </is>
+      </c>
+      <c r="B4650" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10556.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4651">
+      <c r="A4651" t="inlineStr">
+        <is>
+          <t>1821.psd</t>
+        </is>
+      </c>
+      <c r="B4651" t="inlineStr">
+        <is>
+          <t>tamilpsd-10557.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4652">
+      <c r="A4652" s="3" t="inlineStr">
+        <is>
+          <t>1820.psd</t>
+        </is>
+      </c>
+      <c r="B4652" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10558.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4653">
+      <c r="A4653" t="inlineStr">
+        <is>
+          <t>1819.psd</t>
+        </is>
+      </c>
+      <c r="B4653" t="inlineStr">
+        <is>
+          <t>tamilpsd-10559.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4654">
+      <c r="A4654" s="3" t="inlineStr">
+        <is>
+          <t>1818.psd</t>
+        </is>
+      </c>
+      <c r="B4654" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10560.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4655">
+      <c r="A4655" t="inlineStr">
+        <is>
+          <t>1817.psd</t>
+        </is>
+      </c>
+      <c r="B4655" t="inlineStr">
+        <is>
+          <t>tamilpsd-10561.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4656">
+      <c r="A4656" s="3" t="inlineStr">
+        <is>
+          <t>1816.psd</t>
+        </is>
+      </c>
+      <c r="B4656" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10562.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4657">
+      <c r="A4657" t="inlineStr">
+        <is>
+          <t>1815.psd</t>
+        </is>
+      </c>
+      <c r="B4657" t="inlineStr">
+        <is>
+          <t>tamilpsd-10563.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4658">
+      <c r="A4658" s="3" t="inlineStr">
+        <is>
+          <t>1814.psd</t>
+        </is>
+      </c>
+      <c r="B4658" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10564.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4659">
+      <c r="A4659" t="inlineStr">
+        <is>
+          <t>1813.psd</t>
+        </is>
+      </c>
+      <c r="B4659" t="inlineStr">
+        <is>
+          <t>tamilpsd-10565.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4660">
+      <c r="A4660" s="3" t="inlineStr">
+        <is>
+          <t>1812.psd</t>
+        </is>
+      </c>
+      <c r="B4660" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10566.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4661">
+      <c r="A4661" t="inlineStr">
+        <is>
+          <t>1811.psd</t>
+        </is>
+      </c>
+      <c r="B4661" t="inlineStr">
+        <is>
+          <t>tamilpsd-10567.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4662">
+      <c r="A4662" s="3" t="inlineStr">
+        <is>
+          <t>1810.psd</t>
+        </is>
+      </c>
+      <c r="B4662" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10568.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4663">
+      <c r="A4663" t="inlineStr">
+        <is>
+          <t>1809.psd</t>
+        </is>
+      </c>
+      <c r="B4663" t="inlineStr">
+        <is>
+          <t>tamilpsd-10569.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4664">
+      <c r="A4664" s="3" t="inlineStr">
+        <is>
+          <t>1808.psd</t>
+        </is>
+      </c>
+      <c r="B4664" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10570.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4665">
+      <c r="A4665" t="inlineStr">
+        <is>
+          <t>1807.psd</t>
+        </is>
+      </c>
+      <c r="B4665" t="inlineStr">
+        <is>
+          <t>tamilpsd-10571.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4666">
+      <c r="A4666" s="3" t="inlineStr">
+        <is>
+          <t>1805.psd</t>
+        </is>
+      </c>
+      <c r="B4666" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10572.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4667">
+      <c r="A4667" t="inlineStr">
+        <is>
+          <t>1804.psd</t>
+        </is>
+      </c>
+      <c r="B4667" t="inlineStr">
+        <is>
+          <t>tamilpsd-10573.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4668">
+      <c r="A4668" s="3" t="inlineStr">
+        <is>
+          <t>1803.psd</t>
+        </is>
+      </c>
+      <c r="B4668" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10574.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4669">
+      <c r="A4669" t="inlineStr">
+        <is>
+          <t>1802.psd</t>
+        </is>
+      </c>
+      <c r="B4669" t="inlineStr">
+        <is>
+          <t>tamilpsd-10575.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4670">
+      <c r="A4670" s="3" t="inlineStr">
+        <is>
+          <t>1801.psd</t>
+        </is>
+      </c>
+      <c r="B4670" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10576.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4671">
+      <c r="A4671" t="inlineStr">
+        <is>
+          <t>1800.psd</t>
+        </is>
+      </c>
+      <c r="B4671" t="inlineStr">
+        <is>
+          <t>tamilpsd-10577.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4672">
+      <c r="A4672" s="3" t="inlineStr">
+        <is>
+          <t>1799.psd</t>
+        </is>
+      </c>
+      <c r="B4672" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10578.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4673">
+      <c r="A4673" t="inlineStr">
+        <is>
+          <t>1848.psd</t>
+        </is>
+      </c>
+      <c r="B4673" t="inlineStr">
+        <is>
+          <t>tamilpsd-10579.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4674">
+      <c r="A4674" s="3" t="inlineStr">
+        <is>
+          <t>1634.psd</t>
+        </is>
+      </c>
+      <c r="B4674" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10580.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4675">
+      <c r="A4675" t="inlineStr">
+        <is>
+          <t>1633.psd</t>
+        </is>
+      </c>
+      <c r="B4675" t="inlineStr">
+        <is>
+          <t>tamilpsd-10581.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4676">
+      <c r="A4676" s="3" t="inlineStr">
+        <is>
+          <t>1632.psd</t>
+        </is>
+      </c>
+      <c r="B4676" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10582.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4677">
+      <c r="A4677" t="inlineStr">
+        <is>
+          <t>1660.psd</t>
+        </is>
+      </c>
+      <c r="B4677" t="inlineStr">
+        <is>
+          <t>tamilpsd-10583.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4678">
+      <c r="A4678" s="3" t="inlineStr">
+        <is>
+          <t>1798.psd</t>
+        </is>
+      </c>
+      <c r="B4678" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10584.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4679">
+      <c r="A4679" t="inlineStr">
+        <is>
+          <t>1797.psd</t>
+        </is>
+      </c>
+      <c r="B4679" t="inlineStr">
+        <is>
+          <t>tamilpsd-10585.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4680">
+      <c r="A4680" s="3" t="inlineStr">
+        <is>
+          <t>1796.psd</t>
+        </is>
+      </c>
+      <c r="B4680" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10586.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4681">
+      <c r="A4681" t="inlineStr">
+        <is>
+          <t>1795.psd</t>
+        </is>
+      </c>
+      <c r="B4681" t="inlineStr">
+        <is>
+          <t>tamilpsd-10587.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4682">
+      <c r="A4682" s="3" t="inlineStr">
+        <is>
+          <t>1794.psd</t>
+        </is>
+      </c>
+      <c r="B4682" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10588.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4683">
+      <c r="A4683" t="inlineStr">
+        <is>
+          <t>1631.psd</t>
+        </is>
+      </c>
+      <c r="B4683" t="inlineStr">
+        <is>
+          <t>tamilpsd-10589.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4684">
+      <c r="A4684" s="3" t="inlineStr">
+        <is>
+          <t>1793.psd</t>
+        </is>
+      </c>
+      <c r="B4684" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10590.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4685">
+      <c r="A4685" t="inlineStr">
+        <is>
+          <t>1792.psd</t>
+        </is>
+      </c>
+      <c r="B4685" t="inlineStr">
+        <is>
+          <t>tamilpsd-10591.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4686">
+      <c r="A4686" s="3" t="inlineStr">
+        <is>
+          <t>1791.psd</t>
+        </is>
+      </c>
+      <c r="B4686" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10592.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4687">
+      <c r="A4687" t="inlineStr">
+        <is>
+          <t>1790.psd</t>
+        </is>
+      </c>
+      <c r="B4687" t="inlineStr">
+        <is>
+          <t>tamilpsd-10593.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4688">
+      <c r="A4688" s="3" t="inlineStr">
+        <is>
+          <t>1789.psd</t>
+        </is>
+      </c>
+      <c r="B4688" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10594.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4689">
+      <c r="A4689" t="inlineStr">
+        <is>
+          <t>1630.psd</t>
+        </is>
+      </c>
+      <c r="B4689" t="inlineStr">
+        <is>
+          <t>tamilpsd-10595.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4690">
+      <c r="A4690" s="3" t="inlineStr">
+        <is>
+          <t>1788.psd</t>
+        </is>
+      </c>
+      <c r="B4690" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10596.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4691">
+      <c r="A4691" t="inlineStr">
+        <is>
+          <t>1787.psd</t>
+        </is>
+      </c>
+      <c r="B4691" t="inlineStr">
+        <is>
+          <t>tamilpsd-10597.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4692">
+      <c r="A4692" s="3" t="inlineStr">
+        <is>
+          <t>1786.psd</t>
+        </is>
+      </c>
+      <c r="B4692" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10598.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4693">
+      <c r="A4693" t="inlineStr">
+        <is>
+          <t>1629.psd</t>
+        </is>
+      </c>
+      <c r="B4693" t="inlineStr">
+        <is>
+          <t>tamilpsd-10599.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4694">
+      <c r="A4694" s="3" t="inlineStr">
+        <is>
+          <t>1785.psd</t>
+        </is>
+      </c>
+      <c r="B4694" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10600.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4695">
+      <c r="A4695" t="inlineStr">
+        <is>
+          <t>1784.psd</t>
+        </is>
+      </c>
+      <c r="B4695" t="inlineStr">
+        <is>
+          <t>tamilpsd-10601.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4696">
+      <c r="A4696" s="3" t="inlineStr">
+        <is>
+          <t>1783.psd</t>
+        </is>
+      </c>
+      <c r="B4696" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10602.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4697">
+      <c r="A4697" t="inlineStr">
+        <is>
+          <t>1628.psd</t>
+        </is>
+      </c>
+      <c r="B4697" t="inlineStr">
+        <is>
+          <t>tamilpsd-10603.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4698">
+      <c r="A4698" s="3" t="inlineStr">
+        <is>
+          <t>1782.psd</t>
+        </is>
+      </c>
+      <c r="B4698" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10604.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4699">
+      <c r="A4699" t="inlineStr">
+        <is>
+          <t>1627.psd</t>
+        </is>
+      </c>
+      <c r="B4699" t="inlineStr">
+        <is>
+          <t>tamilpsd-10605.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4700">
+      <c r="A4700" s="3" t="inlineStr">
+        <is>
+          <t>1781.psd</t>
+        </is>
+      </c>
+      <c r="B4700" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10606.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4701">
+      <c r="A4701" t="inlineStr">
+        <is>
+          <t>1780.psd</t>
+        </is>
+      </c>
+      <c r="B4701" t="inlineStr">
+        <is>
+          <t>tamilpsd-10607.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4702">
+      <c r="A4702" s="3" t="inlineStr">
+        <is>
+          <t>1779.psd</t>
+        </is>
+      </c>
+      <c r="B4702" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10608.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4703">
+      <c r="A4703" t="inlineStr">
+        <is>
+          <t>1626.psd</t>
+        </is>
+      </c>
+      <c r="B4703" t="inlineStr">
+        <is>
+          <t>tamilpsd-10609.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4704">
+      <c r="A4704" s="3" t="inlineStr">
+        <is>
+          <t>1778.psd</t>
+        </is>
+      </c>
+      <c r="B4704" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10610.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4705">
+      <c r="A4705" t="inlineStr">
+        <is>
+          <t>1777.psd</t>
+        </is>
+      </c>
+      <c r="B4705" t="inlineStr">
+        <is>
+          <t>tamilpsd-10611.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4706">
+      <c r="A4706" s="3" t="inlineStr">
+        <is>
+          <t>1776.psd</t>
+        </is>
+      </c>
+      <c r="B4706" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10612.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4707">
+      <c r="A4707" t="inlineStr">
+        <is>
+          <t>1775.psd</t>
+        </is>
+      </c>
+      <c r="B4707" t="inlineStr">
+        <is>
+          <t>tamilpsd-10613.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4708">
+      <c r="A4708" s="3" t="inlineStr">
+        <is>
+          <t>1774.psd</t>
+        </is>
+      </c>
+      <c r="B4708" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10614.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4709">
+      <c r="A4709" t="inlineStr">
+        <is>
+          <t>1625.psd</t>
+        </is>
+      </c>
+      <c r="B4709" t="inlineStr">
+        <is>
+          <t>tamilpsd-10615.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4710">
+      <c r="A4710" s="3" t="inlineStr">
+        <is>
+          <t>1624.psd</t>
+        </is>
+      </c>
+      <c r="B4710" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10616.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4711">
+      <c r="A4711" t="inlineStr">
+        <is>
+          <t>1623.psd</t>
+        </is>
+      </c>
+      <c r="B4711" t="inlineStr">
+        <is>
+          <t>tamilpsd-10617.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4712">
+      <c r="A4712" s="3" t="inlineStr">
+        <is>
+          <t>1622.psd</t>
+        </is>
+      </c>
+      <c r="B4712" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10618.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4713">
+      <c r="A4713" t="inlineStr">
+        <is>
+          <t>1621.psd</t>
+        </is>
+      </c>
+      <c r="B4713" t="inlineStr">
+        <is>
+          <t>tamilpsd-10619.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4714">
+      <c r="A4714" s="3" t="inlineStr">
+        <is>
+          <t>1620.psd</t>
+        </is>
+      </c>
+      <c r="B4714" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10620.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4715">
+      <c r="A4715" t="inlineStr">
+        <is>
+          <t>1619.psd</t>
+        </is>
+      </c>
+      <c r="B4715" t="inlineStr">
+        <is>
+          <t>tamilpsd-10621.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4716">
+      <c r="A4716" s="3" t="inlineStr">
+        <is>
+          <t>1618.psd</t>
+        </is>
+      </c>
+      <c r="B4716" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10622.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4717">
+      <c r="A4717" t="inlineStr">
+        <is>
+          <t>1617.psd</t>
+        </is>
+      </c>
+      <c r="B4717" t="inlineStr">
+        <is>
+          <t>tamilpsd-10623.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4718">
+      <c r="A4718" s="3" t="inlineStr">
+        <is>
+          <t>1616.psd</t>
+        </is>
+      </c>
+      <c r="B4718" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10624.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4719">
+      <c r="A4719" t="inlineStr">
+        <is>
+          <t>1615.psd</t>
+        </is>
+      </c>
+      <c r="B4719" t="inlineStr">
+        <is>
+          <t>tamilpsd-10625.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4720">
+      <c r="A4720" s="3" t="inlineStr">
+        <is>
+          <t>1773.psd</t>
+        </is>
+      </c>
+      <c r="B4720" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10626.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4721">
+      <c r="A4721" t="inlineStr">
+        <is>
+          <t>1772.psd</t>
+        </is>
+      </c>
+      <c r="B4721" t="inlineStr">
+        <is>
+          <t>tamilpsd-10627.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4722">
+      <c r="A4722" s="3" t="inlineStr">
+        <is>
+          <t>1614.psd</t>
+        </is>
+      </c>
+      <c r="B4722" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10628.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4723">
+      <c r="A4723" t="inlineStr">
+        <is>
+          <t>1771.psd</t>
+        </is>
+      </c>
+      <c r="B4723" t="inlineStr">
+        <is>
+          <t>tamilpsd-10629.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4724">
+      <c r="A4724" s="3" t="inlineStr">
+        <is>
+          <t>1770.psd</t>
+        </is>
+      </c>
+      <c r="B4724" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10630.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4725">
+      <c r="A4725" t="inlineStr">
+        <is>
+          <t>1769.psd</t>
+        </is>
+      </c>
+      <c r="B4725" t="inlineStr">
+        <is>
+          <t>tamilpsd-10631.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4726">
+      <c r="A4726" s="3" t="inlineStr">
+        <is>
+          <t>1768.psd</t>
+        </is>
+      </c>
+      <c r="B4726" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10632.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4727">
+      <c r="A4727" t="inlineStr">
+        <is>
+          <t>1613.psd</t>
+        </is>
+      </c>
+      <c r="B4727" t="inlineStr">
+        <is>
+          <t>tamilpsd-10633.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4728">
+      <c r="A4728" s="3" t="inlineStr">
+        <is>
+          <t>1767.PSD</t>
+        </is>
+      </c>
+      <c r="B4728" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10634.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4729">
+      <c r="A4729" t="inlineStr">
+        <is>
+          <t>1766.psd</t>
+        </is>
+      </c>
+      <c r="B4729" t="inlineStr">
+        <is>
+          <t>tamilpsd-10635.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4730">
+      <c r="A4730" s="3" t="inlineStr">
+        <is>
+          <t>1765.psd</t>
+        </is>
+      </c>
+      <c r="B4730" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10636.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4731">
+      <c r="A4731" t="inlineStr">
+        <is>
+          <t>1764.psd</t>
+        </is>
+      </c>
+      <c r="B4731" t="inlineStr">
+        <is>
+          <t>tamilpsd-10637.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4732">
+      <c r="A4732" s="3" t="inlineStr">
+        <is>
+          <t>1763.psd</t>
+        </is>
+      </c>
+      <c r="B4732" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10638.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4733">
+      <c r="A4733" t="inlineStr">
+        <is>
+          <t>1612.psd</t>
+        </is>
+      </c>
+      <c r="B4733" t="inlineStr">
+        <is>
+          <t>tamilpsd-10639.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4734">
+      <c r="A4734" s="3" t="inlineStr">
+        <is>
+          <t>1762.psd</t>
+        </is>
+      </c>
+      <c r="B4734" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10640.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4735">
+      <c r="A4735" t="inlineStr">
+        <is>
+          <t>1761.psd</t>
+        </is>
+      </c>
+      <c r="B4735" t="inlineStr">
+        <is>
+          <t>tamilpsd-10641.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4736">
+      <c r="A4736" s="3" t="inlineStr">
+        <is>
+          <t>1611.psd</t>
+        </is>
+      </c>
+      <c r="B4736" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10642.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4737">
+      <c r="A4737" t="inlineStr">
+        <is>
+          <t>1760.psd</t>
+        </is>
+      </c>
+      <c r="B4737" t="inlineStr">
+        <is>
+          <t>tamilpsd-10643.psd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4738">
+      <c r="A4738" s="3" t="inlineStr">
+        <is>
+          <t>1758.psd</t>
+        </is>
+      </c>
+      <c r="B4738" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10644.psd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4738"/>
+  <dimension ref="A1:B4746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -56953,6 +56953,102 @@
         </is>
       </c>
     </row>
+    <row r="4739">
+      <c r="A4739" t="inlineStr">
+        <is>
+          <t>6116.png</t>
+        </is>
+      </c>
+      <c r="B4739" t="inlineStr">
+        <is>
+          <t>tamilpsd-10645.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4740">
+      <c r="A4740" s="3" t="inlineStr">
+        <is>
+          <t>6115.png</t>
+        </is>
+      </c>
+      <c r="B4740" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10646.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4741">
+      <c r="A4741" t="inlineStr">
+        <is>
+          <t>6114.png</t>
+        </is>
+      </c>
+      <c r="B4741" t="inlineStr">
+        <is>
+          <t>tamilpsd-10647.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4742">
+      <c r="A4742" s="3" t="inlineStr">
+        <is>
+          <t>6113.png</t>
+        </is>
+      </c>
+      <c r="B4742" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10648.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4743">
+      <c r="A4743" t="inlineStr">
+        <is>
+          <t>6112.png</t>
+        </is>
+      </c>
+      <c r="B4743" t="inlineStr">
+        <is>
+          <t>tamilpsd-10649.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4744">
+      <c r="A4744" s="3" t="inlineStr">
+        <is>
+          <t>6111.png</t>
+        </is>
+      </c>
+      <c r="B4744" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10650.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4745">
+      <c r="A4745" t="inlineStr">
+        <is>
+          <t>6110.png</t>
+        </is>
+      </c>
+      <c r="B4745" t="inlineStr">
+        <is>
+          <t>tamilpsd-10651.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4746">
+      <c r="A4746" s="3" t="inlineStr">
+        <is>
+          <t>6109.png</t>
+        </is>
+      </c>
+      <c r="B4746" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10652.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4746"/>
+  <dimension ref="A1:C4796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -57049,6 +57049,856 @@
         </is>
       </c>
     </row>
+    <row r="4747">
+      <c r="A4747" t="inlineStr">
+        <is>
+          <t>6108.png</t>
+        </is>
+      </c>
+      <c r="B4747" t="inlineStr">
+        <is>
+          <t>tamilpsd-10654.png</t>
+        </is>
+      </c>
+      <c r="C4747" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhUZ2tZQUxpWWhMb2hwUk1XdGJrSVE9PSIsInZhbHVlIjoiUURHWlNxYlJpSEpzUm9yM0cwOTc5dz09IiwibWFjIjoiM2RhZjlmNDhmNGI0YjdlMDJkYWNhMDkxNWRkMDA3NzJmNzgwNTUyNGZkZjEzMTc2N2Q1MTk1ZTY3YmM3NWE4MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4748">
+      <c r="A4748" s="3" t="inlineStr">
+        <is>
+          <t>5496.png</t>
+        </is>
+      </c>
+      <c r="B4748" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10655.png</t>
+        </is>
+      </c>
+      <c r="C4748" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im13L1hSS0M1NzB2bGlGcE53YVJRWmc9PSIsInZhbHVlIjoiRHVCMHlTRGZubStzQVZnZzRyS1oxdz09IiwibWFjIjoiZTg0MGZkYzExOTBkY2JkMDkxMzkzMDgzOGJmYTFhMTAxOTI5ZDJmYTc2MjI0MmE3ZDlmNmMyYzc0NjVkYzA5YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4749">
+      <c r="A4749" t="inlineStr">
+        <is>
+          <t>5491.png</t>
+        </is>
+      </c>
+      <c r="B4749" t="inlineStr">
+        <is>
+          <t>tamilpsd-10656.png</t>
+        </is>
+      </c>
+      <c r="C4749" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklQZXVQeVhIN3MveUkwOVFiSGxDcHc9PSIsInZhbHVlIjoiTXNuZjR5MGk3b1BISjZRSEgvYzV5QT09IiwibWFjIjoiZDk4ZTBmNzljMGQ0NTA3YWM5YzliNTFlNzg4OWVmNDA3OWNjMWUxMzBjM2RlNzA5YzZiZmY4MWZlM2RlYTFkNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4750">
+      <c r="A4750" s="3" t="inlineStr">
+        <is>
+          <t>5493.png</t>
+        </is>
+      </c>
+      <c r="B4750" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10657.png</t>
+        </is>
+      </c>
+      <c r="C4750" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNjWkVvQWhUUk1tMjVhbHkyVVorMWc9PSIsInZhbHVlIjoiT2Jub1F0OXJ1RUsvaFRJbFo4bVNWdz09IiwibWFjIjoiNmNkYmRiZjdlOTlhM2YyYTE4NGE0ZmE1MTAzYzE5MDJlOWM4YmNjYzNiNzY1ZmVlM2U2NjE4ZmNmNWY1MmE2MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4751">
+      <c r="A4751" t="inlineStr">
+        <is>
+          <t>5495.png</t>
+        </is>
+      </c>
+      <c r="B4751" t="inlineStr">
+        <is>
+          <t>tamilpsd-10658.png</t>
+        </is>
+      </c>
+      <c r="C4751" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilg0UjBjemd0bFJsWDR5NUpUeHg4Tmc9PSIsInZhbHVlIjoiSDVtU1o1OUtKMWlLV0szVi9iYW1qdz09IiwibWFjIjoiYjlhYjM3YTJjY2UwZTBmYTFiYWQwMGM1ZDBkYTEyOGRiM2I1ZmE4NmIyNGNjYmMzNmM5NmJjYzVlZmY2MDRhZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4752">
+      <c r="A4752" s="3" t="inlineStr">
+        <is>
+          <t>5497.png</t>
+        </is>
+      </c>
+      <c r="B4752" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10659.png</t>
+        </is>
+      </c>
+      <c r="C4752" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InRzWjd0SUZVNjQ3ekpFU1l1dmhwNkE9PSIsInZhbHVlIjoiTk1iQzVtS2ZQVUo5NVRDeXNHUGVJdz09IiwibWFjIjoiNTU1NWFjYjFlZmFjYmUwMDVmM2ZhMmRhZjdjYTQzYjQxN2QxODM5MTBjNWI5NDg4Y2ZiZDEyNzg1NmVmNzdmYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4753">
+      <c r="A4753" t="inlineStr">
+        <is>
+          <t>5034.png</t>
+        </is>
+      </c>
+      <c r="B4753" t="inlineStr">
+        <is>
+          <t>tamilpsd-10660.png</t>
+        </is>
+      </c>
+      <c r="C4753" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpLMGM1bk9OYXhIeS8xTmYwTU9ERHc9PSIsInZhbHVlIjoicU1hM0xjaHA1OTRmdlNZeW5zUnRYZz09IiwibWFjIjoiODI0ODM4YzE3Y2RlNjMyM2YxZjc0ODY4M2M4ZTU0MDU1Yzc4ZTlhNjE4ZWE3ZDA3NWU1MDNiZTg4M2MxODRhMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4754">
+      <c r="A4754" s="3" t="inlineStr">
+        <is>
+          <t>5032.png</t>
+        </is>
+      </c>
+      <c r="B4754" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10661.png</t>
+        </is>
+      </c>
+      <c r="C4754" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikp5NThDQnY3SDRNZEl1aVlxMHFNU1E9PSIsInZhbHVlIjoiUGJjZ2ROYVJydmhaaUpobnMwZ1F5dz09IiwibWFjIjoiNDMyNmEwMjUyOWMyNGI4MDBmNzEyNDNmNGIwMjkxMjkxMzhkM2FlY2JhYWJhNzE1NGFiZmRiZmQ2YzY2MWM1NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4755">
+      <c r="A4755" t="inlineStr">
+        <is>
+          <t>5035.png</t>
+        </is>
+      </c>
+      <c r="B4755" t="inlineStr">
+        <is>
+          <t>tamilpsd-10662.png</t>
+        </is>
+      </c>
+      <c r="C4755" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpSc05vWWFKMkMyUDdYTXpvck5Ganc9PSIsInZhbHVlIjoiYWpQT1M4U1V1WmdZRnR0RHhxN2tpUT09IiwibWFjIjoiYjFmODI0YzA4NmM1NGU2NmNiYTFlZDNhMTk5ZTAxMDE0MDU3YWE4M2Y1YjAyNzYyMDBhMDk3Mjk2ZTA0YzBjNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4756">
+      <c r="A4756" s="3" t="inlineStr">
+        <is>
+          <t>5033.png</t>
+        </is>
+      </c>
+      <c r="B4756" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10663.png</t>
+        </is>
+      </c>
+      <c r="C4756" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxDeXRsVWxCdmhBNUY4R1IvTXZBcnc9PSIsInZhbHVlIjoiR3BSVmtEQzdZNVVQcENqQ3RxNE9YUT09IiwibWFjIjoiZjVkYjg1OWI5ZjMzOWUwZGY0NTgyZWFlNDc0MTc0ZmMxMjk0NmZkMjU0MDU0YTFjYzdmMDMxYTNmM2QxZGJjZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4757">
+      <c r="A4757" t="inlineStr">
+        <is>
+          <t>5028.png</t>
+        </is>
+      </c>
+      <c r="B4757" t="inlineStr">
+        <is>
+          <t>tamilpsd-10664.png</t>
+        </is>
+      </c>
+      <c r="C4757" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InN4OW9zQzI2WW5yazYrRUdqYWd0Y3c9PSIsInZhbHVlIjoiMFJVMk5HdjVibk13UXlmUnoyV2pzZz09IiwibWFjIjoiMTgxMWFhNDZjYTZhYTkxOWMyNTM5OTI5MGViZDZjNTVhMmM4ZGE5ZTRkOWQ4NWYxMTZjMTBkYjJjMmIzODIxYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4758">
+      <c r="A4758" s="3" t="inlineStr">
+        <is>
+          <t>5027.png</t>
+        </is>
+      </c>
+      <c r="B4758" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10665.png</t>
+        </is>
+      </c>
+      <c r="C4758" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBuZExEakMwNnM1dUs0bEt6Yy8rbXc9PSIsInZhbHVlIjoiS09VWFZ4dE9ta2FhS1JHajZVR2ZCZz09IiwibWFjIjoiYTI0YWRlNjljOTg2OGE4Mjk3ZTBhNmZmODk1M2VjNjc3NzViMDEzMzdmYjhkMWUwNjQ4MTdlZGEwMGIzOTI3YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4759">
+      <c r="A4759" t="inlineStr">
+        <is>
+          <t>5026.png</t>
+        </is>
+      </c>
+      <c r="B4759" t="inlineStr">
+        <is>
+          <t>tamilpsd-10666.png</t>
+        </is>
+      </c>
+      <c r="C4759" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFQUDRlekhLamh2WU9oeFc2UmVzM0E9PSIsInZhbHVlIjoiTWJtK05uUWoxaDNDaUtrc1NYNHkxUT09IiwibWFjIjoiNjdjZmU2YWVmYzI4Njk0N2ZlNmUxNTJmZWE3MTU2ZmQ5NDlmNWNkODYyNDg2YWNmNGJmN2Q3MjU1MTE3ZDJiZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4760">
+      <c r="A4760" s="3" t="inlineStr">
+        <is>
+          <t>5029.png</t>
+        </is>
+      </c>
+      <c r="B4760" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10667.png</t>
+        </is>
+      </c>
+      <c r="C4760" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFsRTdnWVc5dVAxaDdOY2p5OTJCclE9PSIsInZhbHVlIjoiSTV2Y3lDd1YvSkVzaVhSQzN3MzZ4QT09IiwibWFjIjoiMjk3YjZkZWM2NmIxNTEwMjcxYjk2NDZhZTI0NTc5YTJkYTNlOWFlZTlkYTg5YjI3ZWYwZWI1NDMyOTlmNDc0NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4761">
+      <c r="A4761" t="inlineStr">
+        <is>
+          <t>5031.png</t>
+        </is>
+      </c>
+      <c r="B4761" t="inlineStr">
+        <is>
+          <t>tamilpsd-10668.png</t>
+        </is>
+      </c>
+      <c r="C4761" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZFZE54aGtEWUluOEtCZDRCZE5TbkE9PSIsInZhbHVlIjoiQmFlSGJVcTBXN3FCQUwzbVd0MlJxUT09IiwibWFjIjoiOGFmZTgyZTAxOTkyNzE0ZDdjZTVjZTg3OWY3NThmZjFmNTg3NGUzMjAxYTEzNjg3YmI5ODM0MTY4MTFjOGE1ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4762">
+      <c r="A4762" s="3" t="inlineStr">
+        <is>
+          <t>5030.png</t>
+        </is>
+      </c>
+      <c r="B4762" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10669.png</t>
+        </is>
+      </c>
+      <c r="C4762" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklvRUk2SW1WZEgwMVpLcEw1cjhkZnc9PSIsInZhbHVlIjoiVkhORnQwK1BLRUs3R0NYTlJQUkJJQT09IiwibWFjIjoiMzY4YWRkMWI2ZjVjYmRmNzdlMThmY2JkZjQ4ZWU2MzdlMGMzNjVlMTc4MTBmMmRiNDFhZWQxZDIwZGVlZWQxZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4763">
+      <c r="A4763" t="inlineStr">
+        <is>
+          <t>5025.png</t>
+        </is>
+      </c>
+      <c r="B4763" t="inlineStr">
+        <is>
+          <t>tamilpsd-10670.png</t>
+        </is>
+      </c>
+      <c r="C4763" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNseVdHUjk1bGsvbitBckRCYlp6Z1E9PSIsInZhbHVlIjoiSTRkbWZmUXFsQm5hblpWZlc2WDhYQT09IiwibWFjIjoiZThhMjc2MDA3ZGNhZTZkNGQxNTBjZjE1NjIyYTQ2ODcyZDE2YjQyYzFiMGY3OTUyNjE2YWFjN2Y5Y2VmMjAyZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4764">
+      <c r="A4764" s="3" t="inlineStr">
+        <is>
+          <t>5024.png</t>
+        </is>
+      </c>
+      <c r="B4764" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10671.png</t>
+        </is>
+      </c>
+      <c r="C4764" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNBcW1vcmN1Q1YzYnpYMzZUSWM2L3c9PSIsInZhbHVlIjoiM0FwaEFjVEFyZklUM1Y1VzZGWjhXZz09IiwibWFjIjoiOTIzODM1MzlhNzc0ODE2MWNjYTM0Zjg2YzI2YjA4OTllMWI4Y2FiZTdkMjMxNWQ2ZDAyOGQwMmMwN2U3MjZjMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4765">
+      <c r="A4765" t="inlineStr">
+        <is>
+          <t>5021.png</t>
+        </is>
+      </c>
+      <c r="B4765" t="inlineStr">
+        <is>
+          <t>tamilpsd-10672.png</t>
+        </is>
+      </c>
+      <c r="C4765" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InM4WWpGRWhtRnhjdzcveCt1b2piYXc9PSIsInZhbHVlIjoiRDBwSmhMb1VLaG82d25OQUhLR3dIQT09IiwibWFjIjoiMDI2Njg1N2MxMmVlY2E5ZjY4YmIzZDdlYzU5OTdlNzJkZTBjY2I4MmUzNmVmZTE0MzYxNDhhOGFkY2M1OTQxYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4766">
+      <c r="A4766" s="3" t="inlineStr">
+        <is>
+          <t>5023.png</t>
+        </is>
+      </c>
+      <c r="B4766" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10673.png</t>
+        </is>
+      </c>
+      <c r="C4766" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlUyRUpRWG9SZ3lLVHE4cFZicVoxUHc9PSIsInZhbHVlIjoidVpDaHgwM1Zjajl5QnRWMDNVc2o3Zz09IiwibWFjIjoiNzFiMWE1YzE1OWQ0OTljNTJhN2RlZTkzZWE3ZDQ1MmRiMzhmNDE4ZmQ5ZjVmZDA1M2ZkMjc0MGQ4NDJmNzYyOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4767">
+      <c r="A4767" t="inlineStr">
+        <is>
+          <t>5020.png</t>
+        </is>
+      </c>
+      <c r="B4767" t="inlineStr">
+        <is>
+          <t>tamilpsd-10674.png</t>
+        </is>
+      </c>
+      <c r="C4767" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlluNEhGTmduZFh0Ykw2anpyNFdyRnc9PSIsInZhbHVlIjoiVzg5MGl6aEl0OGtSS0kyRWRFRExGQT09IiwibWFjIjoiZDViOWQ5MDYwYjc2YjkwNjgwODdmZmIxNjY4NjJhNGM0MGQxMzMzYWM5MmRiMmQ2YjU0NzRlYmI2NGU4NDc5YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4768">
+      <c r="A4768" s="3" t="inlineStr">
+        <is>
+          <t>5019.png</t>
+        </is>
+      </c>
+      <c r="B4768" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10675.png</t>
+        </is>
+      </c>
+      <c r="C4768" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijk3YnVVSkNieUpWY3BQREg2cHZvZWc9PSIsInZhbHVlIjoiQk13ekFnODVYb1VhZTNISThDcUI2Zz09IiwibWFjIjoiNGY4Yzk4NGUxNjc4NDAxZWFmMWU5NjllZTM2OWMxMzk0MzVhNGFjYzIxMTYzMDYxY2UzMWQ0NjQ0MzU3MmE3NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4769">
+      <c r="A4769" t="inlineStr">
+        <is>
+          <t>5022.png</t>
+        </is>
+      </c>
+      <c r="B4769" t="inlineStr">
+        <is>
+          <t>tamilpsd-10676.png</t>
+        </is>
+      </c>
+      <c r="C4769" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im02YmlnMW5MWmRVV1JLMmt1c2xiNUE9PSIsInZhbHVlIjoiS1FTdnVXdHRaTWplRDExUWFNNWFrUT09IiwibWFjIjoiMmIzODZhOTU2ZWU4OTVhYjM3ZTdhMjNiMDEwNmFjMGVmYmJiOTg4N2QxNWU1NDdmNGZiMDgwYTUzNzcwOWM5MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4770">
+      <c r="A4770" s="3" t="inlineStr">
+        <is>
+          <t>5018.png</t>
+        </is>
+      </c>
+      <c r="B4770" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10677.png</t>
+        </is>
+      </c>
+      <c r="C4770" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJUSGFkdTRQdVVWSGt6UXN4OGZvMEE9PSIsInZhbHVlIjoiK3hGSkFsVjExN1dReXFPQmFGQUxkQT09IiwibWFjIjoiMzQ0NzIzZjU5NjdjZWNhZjU2Zjg3YjcwZDRhYjMyNTlhMWIwZmU2Nzk5NDk2MjgzY2NiMDA1Yjk0MzEwYjczOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4771">
+      <c r="A4771" t="inlineStr">
+        <is>
+          <t>5016.png</t>
+        </is>
+      </c>
+      <c r="B4771" t="inlineStr">
+        <is>
+          <t>tamilpsd-10678.png</t>
+        </is>
+      </c>
+      <c r="C4771" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBMZ214bnk5VWl0alJZSWdqcXU1OHc9PSIsInZhbHVlIjoiT1dOWTJHWlU5ci9oa0gxOC96cGVuQT09IiwibWFjIjoiN2FiMWY3YjI1ZGJhNDllMjdmMWY1YTUyZjZiMmQ3YWEyMDgzOWMxNmNkOGUyODA3ZGQwY2E4MThhZWFmMzZlNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4772">
+      <c r="A4772" s="3" t="inlineStr">
+        <is>
+          <t>5017.png</t>
+        </is>
+      </c>
+      <c r="B4772" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10679.png</t>
+        </is>
+      </c>
+      <c r="C4772" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNmTzQ1UC9BWk5oQnpXWVNmdis1OEE9PSIsInZhbHVlIjoiL0QrNUxlSDM5M1lnZFNESHI2cHhjdz09IiwibWFjIjoiYzMzY2RhMTE4YTJkMGQ5NTY5NDQ3ODBiYTZjOWU5NGVlZGNhZTRkZTY5YTc3M2VmMDUxYTk4YzM2OTU1ZjcxNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4773">
+      <c r="A4773" t="inlineStr">
+        <is>
+          <t>5013.png</t>
+        </is>
+      </c>
+      <c r="B4773" t="inlineStr">
+        <is>
+          <t>tamilpsd-10680.png</t>
+        </is>
+      </c>
+      <c r="C4773" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjN1Ly90UEpCUU5yOXppRHcyZU5hdWc9PSIsInZhbHVlIjoiWGtSSGZ4bjRXVUFqeTZ5WGFWN0x0UT09IiwibWFjIjoiM2I5MzFhNjQ3ZmYxYzAzMGYwMzZkZDVlMGY0NjBlMDQ4NjZiYzU2NzY4Y2M0MTFmZTA3Yjc2NGMyZWRlZDRhZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4774">
+      <c r="A4774" s="3" t="inlineStr">
+        <is>
+          <t>5015.png</t>
+        </is>
+      </c>
+      <c r="B4774" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10681.png</t>
+        </is>
+      </c>
+      <c r="C4774" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpOeGtaSjd0VkdIRk1MajcwUHZUdkE9PSIsInZhbHVlIjoiS2ZSNloxamROcXNFY0tnWnhkN0o5UT09IiwibWFjIjoiYWE3Mjg4MDdkZGUyNDBhYjk5MzcyMGY2NGJmNWM4OGY5ZTEzZmYwMjdkZjg1NDQ2NTJlYjlmNTY2OTlhMWU2MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4775">
+      <c r="A4775" t="inlineStr">
+        <is>
+          <t>5014.png</t>
+        </is>
+      </c>
+      <c r="B4775" t="inlineStr">
+        <is>
+          <t>tamilpsd-10682.png</t>
+        </is>
+      </c>
+      <c r="C4775" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVYaExydlN6ZE12dEJJQ3pBYVRzRXc9PSIsInZhbHVlIjoielQ4NjR5Tyt5ajBOeWVJSzNpRDJqdz09IiwibWFjIjoiMDc2ZTdjNTkxN2RiNmQ3ZTZkOWFmYjJmYzljZjgzOTdkM2I0ODk2ZWRiZjk2MmM1MjI0YjZlZTQzZWU3YzVjOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4776">
+      <c r="A4776" s="3" t="inlineStr">
+        <is>
+          <t>5012.png</t>
+        </is>
+      </c>
+      <c r="B4776" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10683.png</t>
+        </is>
+      </c>
+      <c r="C4776" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImFLTlEwM0ZQd0NCWmRLaVExTDhWQnc9PSIsInZhbHVlIjoid045R2lOeUR6WldTUlVhalpkTDNxZz09IiwibWFjIjoiNzZiNjNlMTA4MWUxZTk5ZDdkYWUwZTBmMjM5ZTczNGY4NWJhMDBlMWJmNjVlZWVjZWM5NDZmYzY1NzZkY2YxZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4777">
+      <c r="A4777" t="inlineStr">
+        <is>
+          <t>5011.png</t>
+        </is>
+      </c>
+      <c r="B4777" t="inlineStr">
+        <is>
+          <t>tamilpsd-10684.png</t>
+        </is>
+      </c>
+      <c r="C4777" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5SVTFMQ25MZkJrS1ZVdFFLcTczSEE9PSIsInZhbHVlIjoibkhXdUt0cUFQYUpxR2ZvZ2oxY3J0UT09IiwibWFjIjoiOWRhNjhiZGU3Mzk3MWMzNDMxOGI4ODQ0ZDNhMzEyNTYzMGYyYTcxY2EyZmQ5NzU3NmI4NzEyN2VmZDQ0YWJiMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4778">
+      <c r="A4778" s="3" t="inlineStr">
+        <is>
+          <t>4994.png</t>
+        </is>
+      </c>
+      <c r="B4778" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10685.png</t>
+        </is>
+      </c>
+      <c r="C4778" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBIeVhIcjErQUpzSElwaFhhZ00zYnc9PSIsInZhbHVlIjoiZHdzR0lYZUV5THhXMjR1eWNPbE9odz09IiwibWFjIjoiMTVmOGUyMGI1MjJmNWMxZTNkMjVmY2IzODJkMDBlYWE5ZGEwOGRlYWM2Zjc1NzlkNTFiNGY5ZjlhYjlhZGJmNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4779">
+      <c r="A4779" t="inlineStr">
+        <is>
+          <t>4995.png</t>
+        </is>
+      </c>
+      <c r="B4779" t="inlineStr">
+        <is>
+          <t>tamilpsd-10686.png</t>
+        </is>
+      </c>
+      <c r="C4779" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVpRFNBS3dmNGN2TEhmdlpsRVBzdEE9PSIsInZhbHVlIjoiZDBvUlhhdzdxV2F6ZEVtTGVuZ1NWZz09IiwibWFjIjoiZjVlM2QyZGY2NGUwNzRiZjkzZGI2OGQ0MDY2MGUzMDJmNGM3OTQxMWVkMzg2ZTlkOTAxMmFmOTU4ZDFmOTE2NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4780">
+      <c r="A4780" s="3" t="inlineStr">
+        <is>
+          <t>4992.png</t>
+        </is>
+      </c>
+      <c r="B4780" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10687.png</t>
+        </is>
+      </c>
+      <c r="C4780" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFrbHJ5ckpaVUdpaVFBcWlWbVhIYXc9PSIsInZhbHVlIjoiMTd3VVI0OGE0TDZGMnNDOWFOL1Y1Zz09IiwibWFjIjoiZmRkYThkYTIzNDNlYzVkMWI1OGM1ZjM4Y2UyMjQyYjM1ZjZmNmUxM2NkMWUzYmIwOWY5YTY0OTE0YTI1OWZjMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4781">
+      <c r="A4781" t="inlineStr">
+        <is>
+          <t>4991.png</t>
+        </is>
+      </c>
+      <c r="B4781" t="inlineStr">
+        <is>
+          <t>tamilpsd-10688.png</t>
+        </is>
+      </c>
+      <c r="C4781" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZIZnU4bmJoVEczZ1hQSXd0T3NRMnc9PSIsInZhbHVlIjoiLytvZmNKQ1NDUG43eTROcXZGY1hoZz09IiwibWFjIjoiZWRmNmFmOGIwYzZhYzc1MWY4NDNiNjE5OGM2YTdjZjM5ZTU5MGEyNDhmZjBkZWVlNGE4NTUzZDNmYzgyNzhhNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4782">
+      <c r="A4782" s="3" t="inlineStr">
+        <is>
+          <t>4993.png</t>
+        </is>
+      </c>
+      <c r="B4782" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10689.png</t>
+        </is>
+      </c>
+      <c r="C4782" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJaeE5sNHV5SWtSM09OQjlaUGJCWVE9PSIsInZhbHVlIjoiQm1sMzMraDVrR1lLOEluZlk3MDJ2Zz09IiwibWFjIjoiYjBlYWM4YjY2ZDhiMmI1MDlkNTQwYWFhMWQ1MDQ0NzdjZTc3N2MyODMxNDA4M2Q3NDI4YzFhNmE3MTk4NGM4MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4783">
+      <c r="A4783" t="inlineStr">
+        <is>
+          <t>5036.png</t>
+        </is>
+      </c>
+      <c r="B4783" t="inlineStr">
+        <is>
+          <t>tamilpsd-10690.png</t>
+        </is>
+      </c>
+      <c r="C4783" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRjbFZ2ekFySjVHN3ZiVG52NjkzVGc9PSIsInZhbHVlIjoiQXJoZXoyVlRuOXdZQ1FtUFJlVWRUUT09IiwibWFjIjoiMmQ4YjUwMGQzMGMzNWNhYWUyNWExODI3NDM2MjA4OTgxODUzYzBiZjM5ZDc2ODA5YmRkY2UyYzM2MDhkYmFkYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4784">
+      <c r="A4784" s="3" t="inlineStr">
+        <is>
+          <t>4990.png</t>
+        </is>
+      </c>
+      <c r="B4784" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10691.png</t>
+        </is>
+      </c>
+      <c r="C4784" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNpaTBzNjRuYzhxWDZrY2txcWRqbkE9PSIsInZhbHVlIjoiYXRYZlV1SkwvaFJYdWpGZHdzZUFXUT09IiwibWFjIjoiNjY1ZWY0MWFiZTg5NjBmYWVhN2JjNjY0NjYwZGYxZDZlODNiZWM5ODU0YTFmMTRlNGIwODUyODA0NjUyZWVhNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4785">
+      <c r="A4785" t="inlineStr">
+        <is>
+          <t>4985.png</t>
+        </is>
+      </c>
+      <c r="B4785" t="inlineStr">
+        <is>
+          <t>tamilpsd-10692.png</t>
+        </is>
+      </c>
+      <c r="C4785" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9wcDZ4QXMrZE1UZm45TCs0c2tFOEE9PSIsInZhbHVlIjoiVkhRSTJxR2QwQWloVEtoaHM0R2svUT09IiwibWFjIjoiNDU2YTBiZGI2NDk2ZGZlODM1MGM2YzI4YzhjZmViMmQ5MzViYjJmNGUxMmZkMDEyYWE4ZmUxMzY2OTEzMTVlMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4786">
+      <c r="A4786" s="3" t="inlineStr">
+        <is>
+          <t>4984.png</t>
+        </is>
+      </c>
+      <c r="B4786" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10693.png</t>
+        </is>
+      </c>
+      <c r="C4786" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilk0T3kwZ2pOT0Fnb3NHck5uYlZQQ2c9PSIsInZhbHVlIjoiYVF6MHBqWDliRkZ1WVpBUTJaQ2dyUT09IiwibWFjIjoiOGU0YTAwZTlmZTgyN2Y4OWQ0ZmNjMjRhMWRiMTMyMGZkMjM3MmE0MDNmZDUwOGU5ZTZhNjBiYTg5MjNmNmI4YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4787">
+      <c r="A4787" t="inlineStr">
+        <is>
+          <t>4980.png</t>
+        </is>
+      </c>
+      <c r="B4787" t="inlineStr">
+        <is>
+          <t>tamilpsd-10694.png</t>
+        </is>
+      </c>
+      <c r="C4787" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllORSszbEpnN3BQYzB5MG45SGRNMnc9PSIsInZhbHVlIjoiSXFqY1lwMmtQUTViU2I3UDhKQjZLQT09IiwibWFjIjoiNzZhOTEwMzNhY2U2MDg3M2E3ODJjNWVlNWMzMTUyNmE4ZWIwOWQ3OGE5Y2FlYWM5NGEyNDllYmIwM2NmMjEzMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4788">
+      <c r="A4788" s="3" t="inlineStr">
+        <is>
+          <t>4983.png</t>
+        </is>
+      </c>
+      <c r="B4788" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10695.png</t>
+        </is>
+      </c>
+      <c r="C4788" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZhUzVuZmtXWVhmVWpnWG81Z1ZCcGc9PSIsInZhbHVlIjoicU1aR0J4ZHZjdm9tUndOR1F1bDdCZz09IiwibWFjIjoiNzI0ZTY0NzVkYjExMjRhMjVhYTQwNjdhYjRiNzM2ODExYTAwZmJlMzRiYTg5NWNlMzc4Mzg5MGI0NzM1ZTI5NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4789">
+      <c r="A4789" t="inlineStr">
+        <is>
+          <t>4981.png</t>
+        </is>
+      </c>
+      <c r="B4789" t="inlineStr">
+        <is>
+          <t>tamilpsd-10696.png</t>
+        </is>
+      </c>
+      <c r="C4789" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZzeUQ4a1pxVVArdzljSys4VGR6Vmc9PSIsInZhbHVlIjoibWs5dzJYWVFWcU1hU041MXRwa0cxZz09IiwibWFjIjoiOTI2MjhhZDVhZGQyMGI4OTRhMDdlM2M0OWNiMGRkMWJjYTdmNDAxZWY4NjE5YjY0NDg4NmMzZjIzZGY1NjVjZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4790">
+      <c r="A4790" s="3" t="inlineStr">
+        <is>
+          <t>4978.png</t>
+        </is>
+      </c>
+      <c r="B4790" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10697.png</t>
+        </is>
+      </c>
+      <c r="C4790" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlwV05FR2VNQUNsS1lNekY1bWlEblE9PSIsInZhbHVlIjoiVmtsYU1aME8wZjhhVmQrTkJKN3VIZz09IiwibWFjIjoiZGJmMzMwMDdmZjJlZGJlODM3YjUzNmJhZTcyYzllNTAzOTQ1ODMxM2IwMzc3Y2M0OTBhNjk2MGI2Yzg4ZjhlMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4791">
+      <c r="A4791" t="inlineStr">
+        <is>
+          <t>4977.png</t>
+        </is>
+      </c>
+      <c r="B4791" t="inlineStr">
+        <is>
+          <t>tamilpsd-10698.png</t>
+        </is>
+      </c>
+      <c r="C4791" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilo4RWdUWTlsTDFtT2cxTG8yL29CVlE9PSIsInZhbHVlIjoiVDVNeFh5Y3gySFBFZnpZWlllRDQwdz09IiwibWFjIjoiZGY5Yzc0MjQ2NTY0YWM3Mjc2ZDJlZjg5ZWE5NDUyOGY3ZjQ5OGI1ZDI4YTFhZThmYWE5NjEyZDI5NzA4YjYwNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4792">
+      <c r="A4792" s="3" t="inlineStr">
+        <is>
+          <t>4974.png</t>
+        </is>
+      </c>
+      <c r="B4792" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10699.png</t>
+        </is>
+      </c>
+      <c r="C4792" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJHdVgzS29mMjY0ck1XaU1kbDVHcGc9PSIsInZhbHVlIjoiR3RMM3BCTEdReEVBMENtRkowck9Ndz09IiwibWFjIjoiMmFlN2JkNmFiZDg5ZjNhMGEyNjMwZWY4MDQyYmZkYmQ4YjE2ZDkxNTFiMDIyYmM0NjU4ZDQzNmNiMDAyM2U2YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4793">
+      <c r="A4793" t="inlineStr">
+        <is>
+          <t>4975.png</t>
+        </is>
+      </c>
+      <c r="B4793" t="inlineStr">
+        <is>
+          <t>tamilpsd-10700.png</t>
+        </is>
+      </c>
+      <c r="C4793" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkYybnhMTFBMN2g3R1BVcGJidkVsclE9PSIsInZhbHVlIjoiNUpFYUhqT3R2ZE5rRmNtZytqNkFsUT09IiwibWFjIjoiNDA5YmU2YmFkMGNmYWQyNTAwNDllM2VjZGY1YTA5ZjYzM2RiNmNjYzhjOGY0OGU1YTNjMzQ1MmM5ZTQ5NTZlOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4794">
+      <c r="A4794" s="3" t="inlineStr">
+        <is>
+          <t>4973.png</t>
+        </is>
+      </c>
+      <c r="B4794" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10701.png</t>
+        </is>
+      </c>
+      <c r="C4794" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVWQ1lSMjdtb0FDWXp0TUtrRUhsdnc9PSIsInZhbHVlIjoieXhmbWxMT3JQMTVJWHZ4VXFqVFE0dz09IiwibWFjIjoiYmU5M2I4ZTM2MDBlMmUxOGRjY2FjYjFjYWZiN2ZmMDcwNGEwYzkzMzllYWMzMDM0MmE3YmM3ZTg2NGQyNDVmMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4795">
+      <c r="A4795" t="inlineStr">
+        <is>
+          <t>4976.png</t>
+        </is>
+      </c>
+      <c r="B4795" t="inlineStr">
+        <is>
+          <t>tamilpsd-10702.png</t>
+        </is>
+      </c>
+      <c r="C4795" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklmZEJ2bGVRYzRGbzM0cE5FQTFxNWc9PSIsInZhbHVlIjoiekY4V2puSHdGM2lOZUlVZmlYeGw3Zz09IiwibWFjIjoiN2Y0OTE4ZjQyYjJlN2U5M2FkZmY1NjVjMGM5ZjVhMTQ1NjQ0MzlkZmNkOTQ1YWQ1ZTUwNGY1OGZkMGY1YzNlNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4796">
+      <c r="A4796" s="3" t="inlineStr">
+        <is>
+          <t>4972.png</t>
+        </is>
+      </c>
+      <c r="B4796" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10703.png</t>
+        </is>
+      </c>
+      <c r="C4796" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNDU3N2ZTc4ZGVJKzNKQ3V3OFVxRUE9PSIsInZhbHVlIjoiM1AwQU41ckZPQ3dKYUVCNXFRcGppQT09IiwibWFjIjoiNDQ5MDQzMjg1ZTA5M2M5YzA2OWQ4YzQ1Y2JlOWExZjRmODY3ZTUyMjg1ZGQ4ODhjZDJkZGI4Yzg0MGY4MzQ4MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4796"/>
+  <dimension ref="A1:C4845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -57899,6 +57899,839 @@
         </is>
       </c>
     </row>
+    <row r="4797">
+      <c r="A4797" t="inlineStr">
+        <is>
+          <t>4989.png</t>
+        </is>
+      </c>
+      <c r="B4797" t="inlineStr">
+        <is>
+          <t>tamilpsd-10704.png</t>
+        </is>
+      </c>
+      <c r="C4797" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVYTUZHYlRmOHMrUU80UkVIMWFleVE9PSIsInZhbHVlIjoiWWMwSE5NVGh3bWNmUVpXcTBFOVpIZz09IiwibWFjIjoiNGMxYmYxYzkxZmViMTE2YTg2MzcxMGYxNzQyODQyM2NiYzFhMDQ2ODRjMTc2ZWZkMTA1ZjlhYjBmZWQzZGYxZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4798">
+      <c r="A4798" s="3" t="inlineStr">
+        <is>
+          <t>4988.png</t>
+        </is>
+      </c>
+      <c r="B4798" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10705.png</t>
+        </is>
+      </c>
+      <c r="C4798" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InY2a2tYaU9sRVNaNHFKdmM0UE13SEE9PSIsInZhbHVlIjoiT1hIMk56Ukc1dFJreS9jbUtSdi9Mdz09IiwibWFjIjoiNTJkZDJkNGMyMmIzMWNkMTQ5MGY0M2U1M2YwODMxZDVkZmU1YmVhZWVmM2NiMmI0YzEyMWYyNjY2OTY5NzBhYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4799">
+      <c r="A4799" t="inlineStr">
+        <is>
+          <t>4987.png</t>
+        </is>
+      </c>
+      <c r="B4799" t="inlineStr">
+        <is>
+          <t>tamilpsd-10706.png</t>
+        </is>
+      </c>
+      <c r="C4799" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtBaUl1cC9EK2xMaVJTbVlRanJFUlE9PSIsInZhbHVlIjoibDl3Mk5hdkVYTXltSW4vaXpUYzJhUT09IiwibWFjIjoiYjU2ZjcyODIzNjQzZmU0YWM2ZTk0MDRmOWFhOWNiZGZkODc0YmY0OTZiOWI1MzMyNWFjYjljNWQ1MjcwOWVlNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4800">
+      <c r="A4800" s="3" t="inlineStr">
+        <is>
+          <t>4986.png</t>
+        </is>
+      </c>
+      <c r="B4800" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10707.png</t>
+        </is>
+      </c>
+      <c r="C4800" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBuYlhiMExBNnlySktuZGZuTG5SUFE9PSIsInZhbHVlIjoiZldSMUN6S2hOczU3MGNpbUxHcXJMQT09IiwibWFjIjoiNzA1NzNhYjZjZThmMzk1MWZkNWQwZWUzYzc0N2M0YjliYzg5M2M2MGMxN2Y2ZmFjMzk2YzEyYzA5ZjhhOWRjMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4801">
+      <c r="A4801" t="inlineStr">
+        <is>
+          <t>4889.png</t>
+        </is>
+      </c>
+      <c r="B4801" t="inlineStr">
+        <is>
+          <t>tamilpsd-10708.png</t>
+        </is>
+      </c>
+      <c r="C4801" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNWNjF6NjIralAwa2RldWpZWFU0bFE9PSIsInZhbHVlIjoiMkwzSzlmWDRxQkZwMVgvVHBCZ1J4dz09IiwibWFjIjoiZGVlMjNjYmU5M2YxZjI3MDIyZmUwYWZlNzM5NDQyY2I2ZTljMzZlYjFhNjgyNGFmYmM3MTE0Y2ZiM2M5M2E0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4802">
+      <c r="A4802" s="3" t="inlineStr">
+        <is>
+          <t>4888.png</t>
+        </is>
+      </c>
+      <c r="B4802" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10709.png</t>
+        </is>
+      </c>
+      <c r="C4802" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhUYTdTMWc0eXQwNUpZWG5TREttS0E9PSIsInZhbHVlIjoidEkxTVFFQWM0V1hEWThXNmtmNmZxUT09IiwibWFjIjoiNDE1ODkxZTQ1MmJjY2NiZmE4ZmU5NDViM2ZmMzQ1MTIxMWNlYjA0ODc4YjMzNDcwZjg2OTJiNjI1MmRiNTIwNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4803">
+      <c r="A4803" t="inlineStr">
+        <is>
+          <t>4887.png</t>
+        </is>
+      </c>
+      <c r="B4803" t="inlineStr">
+        <is>
+          <t>tamilpsd-10710.png</t>
+        </is>
+      </c>
+      <c r="C4803" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxuOUNVQzFtTE9jZkNZZXltZ0tmQVE9PSIsInZhbHVlIjoiQVI0OW9xd2ZIeVBranBSRWVYSmdBZz09IiwibWFjIjoiNGNjNTZjMmRhNmYyMTRhZDUwN2UyMmE5OGY3ODlmOTI4MTQ1ODZjNzJkOThhYmZiZmM2YzlhN2IxYmIxY2UwNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4804">
+      <c r="A4804" s="3" t="inlineStr">
+        <is>
+          <t>4886.png</t>
+        </is>
+      </c>
+      <c r="B4804" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10711.png</t>
+        </is>
+      </c>
+      <c r="C4804" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFwUnN4OURIMFhmSjdpMDFQRHYyMGc9PSIsInZhbHVlIjoiei85WmFxeDk1TTkzTE8wdHZPN0tTdz09IiwibWFjIjoiNTViZTNmODM4MjFjMjdkY2I1ZWIzMjU1Y2UzNDU5YmMxNDY2NDI0Mzc4NGI4ZDZkNzBkYjdlMTk5NWY4MzA2ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4805">
+      <c r="A4805" t="inlineStr">
+        <is>
+          <t>4885.png</t>
+        </is>
+      </c>
+      <c r="B4805" t="inlineStr">
+        <is>
+          <t>tamilpsd-10712.png</t>
+        </is>
+      </c>
+      <c r="C4805" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9WcmREQlg5aCs5VlIrbGVHZ2J4NGc9PSIsInZhbHVlIjoiLzBBK3I1NFVQeUF4ZW9DUDVndXlKQT09IiwibWFjIjoiNzRiZTZjNDExNDBhNDc1OGFmOTUyNmNhMjY4Mjc5YmNjYTc2NzE0MmE0OTc2ZjVkMDAzM2Q1ZTljMmQ0NWE4YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4806">
+      <c r="A4806" s="3" t="inlineStr">
+        <is>
+          <t>4884.png</t>
+        </is>
+      </c>
+      <c r="B4806" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10713.png</t>
+        </is>
+      </c>
+      <c r="C4806" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpadkJONGFxMmpGdUZKYysvUGx5cWc9PSIsInZhbHVlIjoiYUd6MVFCNzcxcklqSXUzbHB0OWwrQT09IiwibWFjIjoiNTcyOGE2NjQyMjExZDEyOGI5ZWM2ZGJmY2EyYzMwMGQ1NmY3ODc2MjI4YTQ3NWEzYTkzYzgzYjVjOWVmZDZlZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4807">
+      <c r="A4807" t="inlineStr">
+        <is>
+          <t>4883.png</t>
+        </is>
+      </c>
+      <c r="B4807" t="inlineStr">
+        <is>
+          <t>tamilpsd-10714.png</t>
+        </is>
+      </c>
+      <c r="C4807" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkdNdjB3VVEwaEhDbHlnZ2RhVkQ2ZWc9PSIsInZhbHVlIjoiNm9iUkZzVUVFUldnYXBOZFZjSGJWQT09IiwibWFjIjoiZjNiNjU4NWFiMzM0YjlhYjkwMjgyMDVkOGFmZDY5MDRiYWFlZGE1YmMxMjI3OGFiMmQzYjMzNGQ0NTc4MGUxNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4808">
+      <c r="A4808" s="3" t="inlineStr">
+        <is>
+          <t>4882.png</t>
+        </is>
+      </c>
+      <c r="B4808" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10715.png</t>
+        </is>
+      </c>
+      <c r="C4808" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJ3QTNHais3UE9sbE96N085OHBXOHc9PSIsInZhbHVlIjoid0w4OTBTZGNxU3NoRTVpbWMrQW11dz09IiwibWFjIjoiMTI3ZDc2Mjk4NTc4MTNlNGZhYTliMjU0ZDZhMGM1ZWRiODcwZjQ3ZjgxMGY0MjFhMzUwMjQ1YTgyNzkwM2EzOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4809">
+      <c r="A4809" t="inlineStr">
+        <is>
+          <t>4881.png</t>
+        </is>
+      </c>
+      <c r="B4809" t="inlineStr">
+        <is>
+          <t>tamilpsd-10716.png</t>
+        </is>
+      </c>
+      <c r="C4809" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVpZVZqKy94eUtSZVVjZ1BNOW11NUE9PSIsInZhbHVlIjoiVDdvV1QrODhncVFEcWNBODRNODk3UT09IiwibWFjIjoiODlhMWQxNTk3OTkzMjE0NWVhYzFlZjg0Y2I1NTEwYWZjZTc2MGY2ODhkMmYyNDgwNTFjMjExN2VhYjc4OTBiNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4810">
+      <c r="A4810" s="3" t="inlineStr">
+        <is>
+          <t>4880.png</t>
+        </is>
+      </c>
+      <c r="B4810" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10717.png</t>
+        </is>
+      </c>
+      <c r="C4810" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InIwSGJZREdibDErc214WGVOZ3duTnc9PSIsInZhbHVlIjoiL05Ndk1XQzdYYWFqdVIwZUNTeHBuZz09IiwibWFjIjoiYzBhNzY0Mjk5NDk1NDFhODAyMTUxODcxZGU3Mjg4NmRlMGE3YjdkODFlM2U2OGRlMjM2MzJmOGVhY2I1NTU4NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4811">
+      <c r="A4811" t="inlineStr">
+        <is>
+          <t>4879.png</t>
+        </is>
+      </c>
+      <c r="B4811" t="inlineStr">
+        <is>
+          <t>tamilpsd-10718.png</t>
+        </is>
+      </c>
+      <c r="C4811" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5ZamlUL3UzenNhQzNKVTV0VXhoVkE9PSIsInZhbHVlIjoiSEpEcVF0Q2xCTzBiQzNKUVlsMDVjZz09IiwibWFjIjoiNDUxNjc3MDNmZGIxZWI0YzBjYTQyYWQyMjQ1YjcyMmZlODI3ZTk3NWY2NDc3YmE2Y2NlMGUxMmJiMGQ5Y2Q5MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4812">
+      <c r="A4812" s="3" t="inlineStr">
+        <is>
+          <t>4878.png</t>
+        </is>
+      </c>
+      <c r="B4812" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10719.png</t>
+        </is>
+      </c>
+      <c r="C4812" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRKL2Q0RkZIWXM3alhGUGcydks2bnc9PSIsInZhbHVlIjoiZDR5ZkhsQUJ0RUluT2NaVU4yNEhCdz09IiwibWFjIjoiZWI0NjVkYWUyZjgxODhlYjFhMWQ4M2VkMTFlMTkwMDJkY2FiNDgwMjFmNTgwNTVjYWNjNDI4MTNhZWY4NGJiYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4813">
+      <c r="A4813" t="inlineStr">
+        <is>
+          <t>4877.png</t>
+        </is>
+      </c>
+      <c r="B4813" t="inlineStr">
+        <is>
+          <t>tamilpsd-10720.png</t>
+        </is>
+      </c>
+      <c r="C4813" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtHWVBqZ3Bvd1VrY0lNTFh2M250SXc9PSIsInZhbHVlIjoibnNBaUFUcGpUUDc5Yk5jamdrejFKZz09IiwibWFjIjoiZGIzNTkyM2Y0ZjI5MWJjYjYyNjViNjBiYjMyNTVkNDU4MDdlMzQxNmE1NmQ3YjU4ODg4NjczYzJmYTVjMzc4MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4814">
+      <c r="A4814" s="3" t="inlineStr">
+        <is>
+          <t>4876.png</t>
+        </is>
+      </c>
+      <c r="B4814" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10721.png</t>
+        </is>
+      </c>
+      <c r="C4814" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijd2SnpVaThKT2xYb2IwenRKekxxK0E9PSIsInZhbHVlIjoib3YrVzlHNmJ5Q2FvMTNXRzVyNUQwZz09IiwibWFjIjoiNTdmNTFhNGJhMmVjODIzNTZjZWExNmJmMjRiOWVmNzdiMDhmMjkyOGY5NmRhMzFmYzViNThiMWVmODVlYmFjMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4815">
+      <c r="A4815" t="inlineStr">
+        <is>
+          <t>4875.png</t>
+        </is>
+      </c>
+      <c r="B4815" t="inlineStr">
+        <is>
+          <t>tamilpsd-10722.png</t>
+        </is>
+      </c>
+      <c r="C4815" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjQzSVVtOUp0enlXZllBVHpPN0ZTTVE9PSIsInZhbHVlIjoiTnpZYjE4R0pmZmppMlhNMXEyVWQwdz09IiwibWFjIjoiNTU3ZmU1YWViYjVjYWY3NTdiMGRlMzU5NzhkN2NmZDRlNjUxNTkyYzU5NzAwZTI4YzNkYTBjODdmZWRhMDU5OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4816">
+      <c r="A4816" s="3" t="inlineStr">
+        <is>
+          <t>4874.png</t>
+        </is>
+      </c>
+      <c r="B4816" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10723.png</t>
+        </is>
+      </c>
+      <c r="C4816" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhRekNyQzJxeDNLb1NMQU53S0p4TFE9PSIsInZhbHVlIjoiT0s4RGEvaWoxR2g2Q2J4Ui92T1NIQT09IiwibWFjIjoiNTMzZTIxMDg0MjQxMWRjZWIzNDQzMzBiNTc5ZWM1NzdiNmFmZjlhYjVmMGJkY2IxZjNiMTA4ZjFlNzgwYTU0MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4817">
+      <c r="A4817" t="inlineStr">
+        <is>
+          <t>4873.png</t>
+        </is>
+      </c>
+      <c r="B4817" t="inlineStr">
+        <is>
+          <t>tamilpsd-10724.png</t>
+        </is>
+      </c>
+      <c r="C4817" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJQTDJ3NWxNd2x1enRKejZiZVdZVmc9PSIsInZhbHVlIjoiV3E0YmhBSEtTVHNyMFNkaEVvcDJyUT09IiwibWFjIjoiNDJjZjQzY2UxMTJlMDQ3YjYyZmQwZGU3M2Y4NzdlZWZiOGI1NTdjOWVlYmMxODc4OWRhMjk3Mjg3NTdmYjkyMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4818">
+      <c r="A4818" s="3" t="inlineStr">
+        <is>
+          <t>4872.png</t>
+        </is>
+      </c>
+      <c r="B4818" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10725.png</t>
+        </is>
+      </c>
+      <c r="C4818" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImI3N3YwQlc5SW9tUkx2UktlZ0tzVXc9PSIsInZhbHVlIjoiUWl6YmFubmo5L3R0OFB6WFE5Sjd0dz09IiwibWFjIjoiNGFiN2Q4YjA3MzNjMGIzYWYyNmI1MGIxYzNlZTBhMTZjYzAwYzc3NDliNWQzYjk0Y2YxYzFlNmNlYzljYTQzMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4819">
+      <c r="A4819" t="inlineStr">
+        <is>
+          <t>4871.png</t>
+        </is>
+      </c>
+      <c r="B4819" t="inlineStr">
+        <is>
+          <t>tamilpsd-10726.png</t>
+        </is>
+      </c>
+      <c r="C4819" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVOQ0xxcFlncThzWW11WWZmMjh4bXc9PSIsInZhbHVlIjoiZFRLQWhnNW55S2gvdnhEb3RtaW1YQT09IiwibWFjIjoiNzk5YjVhYmNjOTgzYTViM2JkNTdlMGI1NWUwMDk5NTEwZGIyMTVhMzNhYTc5OGJkZDgyYmI1OTdlMmRmZmFmOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4820">
+      <c r="A4820" s="3" t="inlineStr">
+        <is>
+          <t>4870.png</t>
+        </is>
+      </c>
+      <c r="B4820" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10727.png</t>
+        </is>
+      </c>
+      <c r="C4820" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilg0RnhKTW1zeGVxVGh3YllXdm9SUmc9PSIsInZhbHVlIjoiZ2RuQTNzeHM4S2U0YndDVEluMmRmUT09IiwibWFjIjoiZGY3OGRlOWMxZWNmY2FiNzk0YzVjZDIzODgyNTMzZjg1ZTI1ZDliMTJhMWY0NTg4MWI2MDdjNTUyOTk2MTY4NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4821">
+      <c r="A4821" t="inlineStr">
+        <is>
+          <t>4919.png</t>
+        </is>
+      </c>
+      <c r="B4821" t="inlineStr">
+        <is>
+          <t>tamilpsd-10728.png</t>
+        </is>
+      </c>
+      <c r="C4821" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhHaTk2VTdjbmE2N0k1b0xSRWxEN2c9PSIsInZhbHVlIjoiekNkaFUxVDc2TFhseHlhYTVTMmZGdz09IiwibWFjIjoiMGZiYWJhZjRjMmQzOTcwZDMwZWVkZDZjMjFhOWM2YmE1ZDRkZTg4NGZhZDRlZGZlMjViMmZjYjQ3MDdhZmUzMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4822">
+      <c r="A4822" s="3" t="inlineStr">
+        <is>
+          <t>4918.png</t>
+        </is>
+      </c>
+      <c r="B4822" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10729.png</t>
+        </is>
+      </c>
+      <c r="C4822" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkVXR0VtdmxBR1NHSGhKcEExVmxHV1E9PSIsInZhbHVlIjoiWW9BVzBua1h6L3BjemI4QzZ2YXVzZz09IiwibWFjIjoiMGUyM2FlNjhmOTYxZWU0NDM2ZDQ4ODgyNTU4NGFkMTBkYWE4MTNmMWFhZmI2NTM3OTFlOTRhZjRlNTE1NDk4MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4823">
+      <c r="A4823" t="inlineStr">
+        <is>
+          <t>4917.png</t>
+        </is>
+      </c>
+      <c r="B4823" t="inlineStr">
+        <is>
+          <t>tamilpsd-10730.png</t>
+        </is>
+      </c>
+      <c r="C4823" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikl0WTBsTTBxRmxveXd0L3NvSmZQU0E9PSIsInZhbHVlIjoiNlZsUEdRU1cxTzZtTlh2alQ3M2dJZz09IiwibWFjIjoiMjViZWI2Y2ViY2NiMWM2ZDhmOWM4M2Y2MmUyYjk0ODQxZWEzODJmMjQ1ZDYwMjAxMGVhMWRhYWQwYTBhMzViOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4824">
+      <c r="A4824" s="3" t="inlineStr">
+        <is>
+          <t>4916.png</t>
+        </is>
+      </c>
+      <c r="B4824" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10731.png</t>
+        </is>
+      </c>
+      <c r="C4824" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkYrM2krR2hGenFEdDE3TVRlM0ppNVE9PSIsInZhbHVlIjoic1VYb1hGcHJrd3VudXhBT3dJTmZSdz09IiwibWFjIjoiM2JiNDU1YjMwMGMwYmQ3ZmUxMmNiZTliNGQ1NzBjMDgxNTg0YzI4NTg5MTNhYjg5OTIyYTQ0NzA0MTY4M2QwMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4825">
+      <c r="A4825" t="inlineStr">
+        <is>
+          <t>4915.png</t>
+        </is>
+      </c>
+      <c r="B4825" t="inlineStr">
+        <is>
+          <t>tamilpsd-10732.png</t>
+        </is>
+      </c>
+      <c r="C4825" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik8vaHd0bUU4eFdIb1VWZnRMdzJWdEE9PSIsInZhbHVlIjoiVmQvenVEMTNERjRjYmF6ME9FcUFZQT09IiwibWFjIjoiMzhiNGZkZWRlM2QwZWI1MDY0NWU3MzQzMTFkNWZiMDkzN2FjOWRiODFjOGU2OTk0NmI3ODFkNjUwZTA4MTliZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4826">
+      <c r="A4826" s="3" t="inlineStr">
+        <is>
+          <t>4914.png</t>
+        </is>
+      </c>
+      <c r="B4826" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10733.png</t>
+        </is>
+      </c>
+      <c r="C4826" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imk3UnZuWTFWRWoyWUhwUXJrbFA0R0E9PSIsInZhbHVlIjoiQ1pyR05jMzlHWWJUazFQbStNSEdDUT09IiwibWFjIjoiMTU2YjgyMTRiNDQyMzg4YzhiMDQ5OWFhYWEyYzBhOTk4MzI1MWQ1ZDU5NzI5YzA1YzZiM2E4YmM3YTcyYzhiYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4827">
+      <c r="A4827" t="inlineStr">
+        <is>
+          <t>4913.png</t>
+        </is>
+      </c>
+      <c r="B4827" t="inlineStr">
+        <is>
+          <t>tamilpsd-10734.png</t>
+        </is>
+      </c>
+      <c r="C4827" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImkyVG0wLy9jTnFHWkVHeDRsb1FyZlE9PSIsInZhbHVlIjoiWWhiS1MwdHV6aEVKcWkyTjJQdTlRZz09IiwibWFjIjoiNjE0NTBlMGMzMGUxYTdkNmQ3YTEwYTc0NTM0YTM1Yjk1MTRlMjVhZDcxMmNlZjRlMjA4Mjk1MWY3YWZhOTBjMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4828">
+      <c r="A4828" s="3" t="inlineStr">
+        <is>
+          <t>4912.png</t>
+        </is>
+      </c>
+      <c r="B4828" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10735.png</t>
+        </is>
+      </c>
+      <c r="C4828" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJ6aVRUcDVwR3RaRklvZ3E2WmI2d3c9PSIsInZhbHVlIjoiVkdwVHhxQmpwbVZna214ZklpVmFsQT09IiwibWFjIjoiYTlhMTBhMmU4NjMwYjhjMjAzOGVlZjRiOTA4ZWYzZWJlZTVlMzYxMWI4MTA5ZjY0NzUxYTIxNGQ0NzYwM2YyYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4829">
+      <c r="A4829" t="inlineStr">
+        <is>
+          <t>4910.png</t>
+        </is>
+      </c>
+      <c r="B4829" t="inlineStr">
+        <is>
+          <t>tamilpsd-10736.png</t>
+        </is>
+      </c>
+      <c r="C4829" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImttQ0FhU1JxSEJ6WUc0MmVRT05lUnc9PSIsInZhbHVlIjoiOVQwUFFMdi8zSXBwNkJtVWExdmlHQT09IiwibWFjIjoiNTk0NzcyZjJiMGRkMzE5OTNiZDRkOWJiY2JjNjQ2ODVjYmIyMDNmMjdiODY3ZDAxNjI0NjYzZDM4ODIxYzM3MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4830">
+      <c r="A4830" s="3" t="inlineStr">
+        <is>
+          <t>4911.png</t>
+        </is>
+      </c>
+      <c r="B4830" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10737.png</t>
+        </is>
+      </c>
+      <c r="C4830" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9jcW9oMFhoWHZNV2czVWNxdnhGMmc9PSIsInZhbHVlIjoiZVZrSGVhaXJ4N0gyVjR0QjVwQ3BmQT09IiwibWFjIjoiYzhhMjMzMzUzZjA1NzhmY2ZiNDgyMGQ3YmY4ZDM5ODA5OTZhNGRhNGNiOTUzOTc5N2YzZDc3MTlhZGNjN2VlOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4831">
+      <c r="A4831" t="inlineStr">
+        <is>
+          <t>4909.png</t>
+        </is>
+      </c>
+      <c r="B4831" t="inlineStr">
+        <is>
+          <t>tamilpsd-10738.png</t>
+        </is>
+      </c>
+      <c r="C4831" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imx0OXAxanh3MU5EZDEvVXZiRHlGTWc9PSIsInZhbHVlIjoiSEc4L283dXRxSU9Tai9BNkgrNGNuUT09IiwibWFjIjoiMmRiODE1M2ZhM2JlMzc4Y2I0ODdhZjg3NzMzY2I2ZGExY2M3ODkyYjg2OGRlMmQ4Y2MzY2QzYTFjMzIyZjZiMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4832">
+      <c r="A4832" s="3" t="inlineStr">
+        <is>
+          <t>4908.png</t>
+        </is>
+      </c>
+      <c r="B4832" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10739.png</t>
+        </is>
+      </c>
+      <c r="C4832" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxEMTRESFgxcktiZzF3NjU2dFBubUE9PSIsInZhbHVlIjoiQzdERmZIMHR0V3lRZndRRzdzemNwQT09IiwibWFjIjoiYmE2OWNiN2YzNDhiZmRmNGE4OTU4MmJkMjNlZTc2MWRjMjJlNDYzZmFkNzBlODZkYjZhNjQzM2QxYzVlOWE0ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4833">
+      <c r="A4833" t="inlineStr">
+        <is>
+          <t>4906.png</t>
+        </is>
+      </c>
+      <c r="B4833" t="inlineStr">
+        <is>
+          <t>tamilpsd-10740.png</t>
+        </is>
+      </c>
+      <c r="C4833" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpURHVTWi8wQWtSaWJLUkljdXozbVE9PSIsInZhbHVlIjoiYlBQY2xEMlpJMVpYbzlsVjVZb2VXZz09IiwibWFjIjoiODRiM2UwOWU3MWU5ZjU1YzQ3NTBmZDJhNTNlMDBlN2M3YjI3MDZkODY0YjFiNGM0ZDg2ZWM2YzIwYWRjZTE2OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4834">
+      <c r="A4834" s="3" t="inlineStr">
+        <is>
+          <t>4907.png</t>
+        </is>
+      </c>
+      <c r="B4834" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10741.png</t>
+        </is>
+      </c>
+      <c r="C4834" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Inhta0U4YWNKZFZxeVBoY1VmUGNLU1E9PSIsInZhbHVlIjoiK1dUdENhZ0M2Qnc3VGtWQUZrNG5TUT09IiwibWFjIjoiYmMzNWFhN2Y5ZjkzMWEzZDQyY2E2ZjNmNWFjMmExNGIzYzQ0ZmY0ZWU4ODMwZjY0NTZhMjYzMzRlNjlkMTVlYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4835">
+      <c r="A4835" t="inlineStr">
+        <is>
+          <t>4905.png</t>
+        </is>
+      </c>
+      <c r="B4835" t="inlineStr">
+        <is>
+          <t>tamilpsd-10742.png</t>
+        </is>
+      </c>
+      <c r="C4835" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImROTFZBeHFwZnpmcnM3Wk53d1JDOGc9PSIsInZhbHVlIjoic3NONWNjemtIZ1ZKZzhRSkRqWkw5QT09IiwibWFjIjoiYThiNWZkNzM2ZmExYjNmZjJmOWRiNGJkNDQ4OTVkMzZhMzYyNGNmMjc1ZGJmYmE2MjQ3ZGJjYzIwZjYxNjZkZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4836">
+      <c r="A4836" s="3" t="inlineStr">
+        <is>
+          <t>4903.png</t>
+        </is>
+      </c>
+      <c r="B4836" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10743.png</t>
+        </is>
+      </c>
+      <c r="C4836" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iks0dGwvNStIczNCcFNBL3YyZkVJU0E9PSIsInZhbHVlIjoiNXgvU1orMjNnY1JDdDU3Z2FURnh6dz09IiwibWFjIjoiYTlmNDE5ODc2ZWJkYzQ4MTVmYmVjOWYzODUwZjJjNWM5ZDdiNjIwZmMzNGVkNTI0NzA0NGNjZTYxZTRkZDAwOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4837">
+      <c r="A4837" t="inlineStr">
+        <is>
+          <t>4904.png</t>
+        </is>
+      </c>
+      <c r="B4837" t="inlineStr">
+        <is>
+          <t>tamilpsd-10744.png</t>
+        </is>
+      </c>
+      <c r="C4837" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjM3ZzNZRm0zRSt2Wk05ejdsMGI3MUE9PSIsInZhbHVlIjoiZ0tBYWxnNHp5cTBnc3JxUml6aklLUT09IiwibWFjIjoiZDMzY2Q2YjdkMDJmNTYyN2JiNDM2NGRmOTkyZDZjMjdhMTlkMzM3YzY1NTg3YjQ4MjkzNmExOTI0N2EyZmIyZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4838">
+      <c r="A4838" s="3" t="inlineStr">
+        <is>
+          <t>4902.png</t>
+        </is>
+      </c>
+      <c r="B4838" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10745.png</t>
+        </is>
+      </c>
+      <c r="C4838" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNiWWp2Q09memJTOHZoR0xNelRZd1E9PSIsInZhbHVlIjoiTzlRNFQwV1ROTWJtbEtaWmNvTFpsZz09IiwibWFjIjoiYjAxNmQ2NGIzZDE5NTYxMjcyZGUyNTNjNjlhZTMyOTQ2MzVkZTM2YmY1YTAzMjFkNmU2YzBjNDMyNjMwZTZkMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4839">
+      <c r="A4839" t="inlineStr">
+        <is>
+          <t>4901.png</t>
+        </is>
+      </c>
+      <c r="B4839" t="inlineStr">
+        <is>
+          <t>tamilpsd-10746.png</t>
+        </is>
+      </c>
+      <c r="C4839" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkVkVlpscDNMSDNjSnMwRTkzSHEvS1E9PSIsInZhbHVlIjoiVS9QZFdVdHNaVU9HZytPOHhGRk1Ldz09IiwibWFjIjoiZTI0YTJjZGVjNDkzYTNmY2VhZDMxMTk4ZDYyNjlmMjU0ODVkZDk5MzYyZmY4YjFkMjc5OTkzNDA4NzhhMDM4OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4840">
+      <c r="A4840" s="3" t="inlineStr">
+        <is>
+          <t>4900.png</t>
+        </is>
+      </c>
+      <c r="B4840" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10747.png</t>
+        </is>
+      </c>
+      <c r="C4840" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxLV0xaMWwwb1ZPYmprcjV6UjFGa2c9PSIsInZhbHVlIjoiNDhuVklmSDRoV21oeFZNZTFVQWdlZz09IiwibWFjIjoiZGNkNmIyNTc5ZDg1YzVhNmJlMWUxZTZhY2NkMTQyNDRlYWEzOTY5YzczZWFlYTJiNmYyODU1ZmUzMTQzNmU4OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4841">
+      <c r="A4841" t="inlineStr">
+        <is>
+          <t>4899.png</t>
+        </is>
+      </c>
+      <c r="B4841" t="inlineStr">
+        <is>
+          <t>tamilpsd-10748.png</t>
+        </is>
+      </c>
+      <c r="C4841" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFpWkZ3ZUNLM3lnVklWeVZYZDZWZVE9PSIsInZhbHVlIjoiK2xCYnJWelk0dkNZcmhTOW9uVG9LUT09IiwibWFjIjoiYjIxZTBiMTE5MTQ5YjRhYzBmODgyZDQwMDg5ZmJiNWU5NTQzZDAwYmM0YTU0YjZmN2MwY2EyZGVmZGIwYzc5NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4842">
+      <c r="A4842" s="3" t="inlineStr">
+        <is>
+          <t>4898.png</t>
+        </is>
+      </c>
+      <c r="B4842" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10749.png</t>
+        </is>
+      </c>
+      <c r="C4842" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNUK0NNZFRTbjNMVm5KMm45Y2t0bWc9PSIsInZhbHVlIjoidUx0eTE5RFc1aFNvRWQxY2R3bUMvUT09IiwibWFjIjoiYzFiMjExYTBlMjA3MGJjY2U3MGU1NTU4NDBiNjE2ODAzOTAxMTRhZjM3YWE4YjQ1YWEyMmFlYzEzNDcwNTc4MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4843">
+      <c r="A4843" t="inlineStr">
+        <is>
+          <t>4896.png</t>
+        </is>
+      </c>
+      <c r="B4843" t="inlineStr">
+        <is>
+          <t>tamilpsd-10750.png</t>
+        </is>
+      </c>
+      <c r="C4843" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBWcVI3WUJIbFdSSEdDRUNqQzZEQlE9PSIsInZhbHVlIjoiSGwrU3k3aTdocEp4a0EyVGZ6TnNGdz09IiwibWFjIjoiYzI1MWFjOTQ4ZDkzNjYxYWU4Y2ZhNzEzNDY3NmRkMDRlMTQ2ZTZhZGY0MzlkZDA2OTc0MTIyYTU0OGE4YzI3ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4844">
+      <c r="A4844" s="3" t="inlineStr">
+        <is>
+          <t>4897.png</t>
+        </is>
+      </c>
+      <c r="B4844" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10751.png</t>
+        </is>
+      </c>
+      <c r="C4844" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJPbXVZQlc4Rk9DVXNEWUxaZ01UK0E9PSIsInZhbHVlIjoibTVXVHhmbVZoTGxsMXNRdUxNSU5wZz09IiwibWFjIjoiYWRmOGYzMGVjYWFkNmE0MDQxZDk0MWUxOTVmZWQzMTE1YzEzMTY1ZjE1YjI1OWQyMzkyNjYwNWQ1MzJlMDJhZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4845">
+      <c r="A4845" t="inlineStr">
+        <is>
+          <t>4895.png</t>
+        </is>
+      </c>
+      <c r="B4845" t="inlineStr">
+        <is>
+          <t>tamilpsd-10752.png</t>
+        </is>
+      </c>
+      <c r="C4845" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iks0WEZOVzRjeEtPb3ZIMHZNTmNtZ3c9PSIsInZhbHVlIjoiQ2pFNnJVT3JxUE9RZzYrUld0cFlPUT09IiwibWFjIjoiN2MxZTI3N2NmMDM2NWUzNTM5YjIyMTQzMDdkZjc2OWYyMTUxMzgwMmZkZDgxNzQ0NDVlMGYyMTM2ZTM4MGU1MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4845"/>
+  <dimension ref="A1:C5339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -58732,6 +58732,8404 @@
         </is>
       </c>
     </row>
+    <row r="4846">
+      <c r="A4846" s="3" t="inlineStr">
+        <is>
+          <t>4894.png</t>
+        </is>
+      </c>
+      <c r="B4846" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10753.png</t>
+        </is>
+      </c>
+      <c r="C4846" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhQTEo2aG1vbmZvMTBZalBlN1FaMUE9PSIsInZhbHVlIjoiTm5Sa0REbUhyb0RmVTJkREkzeXhtdz09IiwibWFjIjoiNzBmMDYyYzdkYWNhYzUxNDQzZjkzZjA5ZGY0Mzc5ZjhlMzRmNWM3Y2QzZGFhNTRjN2RmMDE0NGRhM2QzZmM3ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4847">
+      <c r="A4847" t="inlineStr">
+        <is>
+          <t>4893.png</t>
+        </is>
+      </c>
+      <c r="B4847" t="inlineStr">
+        <is>
+          <t>tamilpsd-10754.png</t>
+        </is>
+      </c>
+      <c r="C4847" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZOSjZoQXNLVG9FSUtjSjE0WkZYbHc9PSIsInZhbHVlIjoidzdLbmRpVHFHbldrNVhHT0dya2REQT09IiwibWFjIjoiZmE0NDZkNGNhZWUzMDNjMTQzYjE3NmI3MzcxN2U5YTQzMWYwMDM2YTEzOGYyYzRjNGU2NjA1OTBmN2RiOGZkNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4848">
+      <c r="A4848" s="3" t="inlineStr">
+        <is>
+          <t>4891.png</t>
+        </is>
+      </c>
+      <c r="B4848" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10755.png</t>
+        </is>
+      </c>
+      <c r="C4848" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InloajlFOHc3N096TG1nMzNHVGVvdGc9PSIsInZhbHVlIjoiR0d1R3dBMGxWc1JMVzdORTVNRThNZz09IiwibWFjIjoiN2IxZGEwZTYzZmFjMjZjZTBmMjRkYjIwYTNiZWRiNGQxMTQxNWU1YjhmZTMyZDk1ZjI4OTJlODBjNWMwOGVmZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4849">
+      <c r="A4849" t="inlineStr">
+        <is>
+          <t>4890.png</t>
+        </is>
+      </c>
+      <c r="B4849" t="inlineStr">
+        <is>
+          <t>tamilpsd-10756.png</t>
+        </is>
+      </c>
+      <c r="C4849" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxjWm1VVlAycXV1aFM0UFQ3WW9Da2c9PSIsInZhbHVlIjoiOGtnOUJHUTNJK05RMldKNWhLNkpkUT09IiwibWFjIjoiYWEyM2VjNzJkN2QzMmZjODQ3MGQwMDY1YzhhNzFlM2JkODQxNjM2M2Q1Y2M5YWZlZDQ5ZTg1MjYxYjAzODhjYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4850">
+      <c r="A4850" s="3" t="inlineStr">
+        <is>
+          <t>4892.png</t>
+        </is>
+      </c>
+      <c r="B4850" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10757.png</t>
+        </is>
+      </c>
+      <c r="C4850" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkEySEkyaTV6aHBkS1MxUVBkOXErbkE9PSIsInZhbHVlIjoiV3lsNDNkNW9nRVdVNWVDakZva1Axdz09IiwibWFjIjoiYTc4ZGE3ZTFiZGFjZjc2NTllZTgwYjYwZDU3ZWE3NmZkMjllNWNkZjBiYzc3ZjMzZjEzZjg4OGY5N2VlZWU0MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4851">
+      <c r="A4851" t="inlineStr">
+        <is>
+          <t>4365.png</t>
+        </is>
+      </c>
+      <c r="B4851" t="inlineStr">
+        <is>
+          <t>tamilpsd-10758.png</t>
+        </is>
+      </c>
+      <c r="C4851" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndQVVk4UVVIbExaRnlvZGxxSDREU2c9PSIsInZhbHVlIjoiUFBxdTl1ZjczclNKd3k4OG1sWmtYZz09IiwibWFjIjoiYzU5NGMwMzcyOTcyMjY4MDc2YjU4NTZiZTE2MjExM2NmOTM2NTMzOWYwZGFjMjYzMzNiNzE2ZGNkYjk2YjgxZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4852">
+      <c r="A4852" s="3" t="inlineStr">
+        <is>
+          <t>4364.png</t>
+        </is>
+      </c>
+      <c r="B4852" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10759.png</t>
+        </is>
+      </c>
+      <c r="C4852" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZxaENUcW8xNzM4OUJsM21zcGo3blE9PSIsInZhbHVlIjoiL0tOa2xWM2VycUFqcXJnbFhsRDIwdz09IiwibWFjIjoiZGQ2NzBmNDUwMTEzNjNlN2VjYzc4NTQ3MzhhZDA2OWY2MGM4YjYwZDgxZDYyOTc3Zjk4NTNiMWQxMzlkZWFmMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4853">
+      <c r="A4853" t="inlineStr">
+        <is>
+          <t>4362.png</t>
+        </is>
+      </c>
+      <c r="B4853" t="inlineStr">
+        <is>
+          <t>tamilpsd-10760.png</t>
+        </is>
+      </c>
+      <c r="C4853" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5lVkc5S0pUdjB1M3lRcFBRSWFJWUE9PSIsInZhbHVlIjoiRUNiaGNzUytxVmh6bEwxR2xxNzM2QT09IiwibWFjIjoiN2Y1ODkzZmE2YTA5NDE4NDhmMTBhMjhkYWJhNTM3OGFkMmE5ZmE4YzkyNjg0MTBlZjNjMDU2ODEzN2Y1YjE4ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4854">
+      <c r="A4854" s="3" t="inlineStr">
+        <is>
+          <t>4363.png</t>
+        </is>
+      </c>
+      <c r="B4854" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10761.png</t>
+        </is>
+      </c>
+      <c r="C4854" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllZVTN2aUF1QVBZUTI4NnBJYnIrR1E9PSIsInZhbHVlIjoibVNvRHNVQ3JKa3d2QU5OeUVoeU9BQT09IiwibWFjIjoiOTFlM2NjOTFjMmEyNzJjZWQ4ZjYyOGQ0Y2UyMGEyMzJlZGVmMTNiYTMxMzk1MDYyYWQ5ZTI1MzZhMmNlZDRkNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4855">
+      <c r="A4855" t="inlineStr">
+        <is>
+          <t>4367.png</t>
+        </is>
+      </c>
+      <c r="B4855" t="inlineStr">
+        <is>
+          <t>tamilpsd-10762.png</t>
+        </is>
+      </c>
+      <c r="C4855" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJmTE5NZ240bEpKQkVtWFdPem1tdnc9PSIsInZhbHVlIjoiMTdmbmh0SlcyRWxqV0h1djUrWDl4UT09IiwibWFjIjoiYjI2NzU3YzBhYWE3YjYxNmI1MTI4MzU2OThmMmVkNmQzNWFlYjk1MGQ3NjIyZGVkODYzNTFhYWMxZjcwMTkyYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4856">
+      <c r="A4856" s="3" t="inlineStr">
+        <is>
+          <t>4369.png</t>
+        </is>
+      </c>
+      <c r="B4856" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10763.png</t>
+        </is>
+      </c>
+      <c r="C4856" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im42ZVNtb25CRTR0dkdRWVpIYWRseUE9PSIsInZhbHVlIjoiOVcyaU9NamV3T3gyaGUrVEg5WWkvUT09IiwibWFjIjoiYmI4YmE1OGY5NzEwODVjMmFkMzc3ZTViOWE4NmRhNmNmN2E5MjUzMWUyZmM0MjkzYjJlNDNiMDMwNWE4ZjAyZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4857">
+      <c r="A4857" t="inlineStr">
+        <is>
+          <t>4368.png</t>
+        </is>
+      </c>
+      <c r="B4857" t="inlineStr">
+        <is>
+          <t>tamilpsd-10764.png</t>
+        </is>
+      </c>
+      <c r="C4857" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlUNjJmY3RraW9oYzVLbWZ3dW1RclE9PSIsInZhbHVlIjoiT1l3MGNYRUtCdEdVbHFMbEhQWGkwdz09IiwibWFjIjoiNGU3OTQzMDBlZTczNTQ1YzQ0ODQxMzM3MWM4YWEwOTc5YjcwNGE5Zjg4MDkxNGY3ZjIzZTY1Zjc3ODY0N2Y0OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4858">
+      <c r="A4858" s="3" t="inlineStr">
+        <is>
+          <t>4366.png</t>
+        </is>
+      </c>
+      <c r="B4858" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10765.png</t>
+        </is>
+      </c>
+      <c r="C4858" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxJa0FmeDc1VHgyQlZSbzZEOEcvaFE9PSIsInZhbHVlIjoiOS9zQ2dmOVVLbThPeEIxcG9UYUFrUT09IiwibWFjIjoiNDM0MzBiMjMyM2YwMjExODE0Y2I0NTUyYjlkOWNjMDAyYWYwYTEyM2IxMzExMmFiODIxYjM3Y2JhYzMxMDJiZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4859">
+      <c r="A4859" t="inlineStr">
+        <is>
+          <t>4360.PNG</t>
+        </is>
+      </c>
+      <c r="B4859" t="inlineStr">
+        <is>
+          <t>tamilpsd-10766.png</t>
+        </is>
+      </c>
+      <c r="C4859" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkF3LzFiQjlSNTBmVXRDanZJbThRY2c9PSIsInZhbHVlIjoiZG1zUnFESWIyNlJsL2RVU1RlVUwyUT09IiwibWFjIjoiZGFhNjFmZDUxYWNlMzczODQ3MWRlNjAwYTk4MGZlNjAwYzVmN2FhMmMwMTQ5NjQyY2NhZjY2YTY2YzJjMmMwNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4860">
+      <c r="A4860" s="3" t="inlineStr">
+        <is>
+          <t>4361.png</t>
+        </is>
+      </c>
+      <c r="B4860" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10767.png</t>
+        </is>
+      </c>
+      <c r="C4860" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVuNkF2QnR2c29jazV0RWpaRjJpWVE9PSIsInZhbHVlIjoiZ3FCNTRsK1loVHE3YUlucmxCL0EvUT09IiwibWFjIjoiMjY4ZWQxYjYxMzJhMzgwZDE2YmE5Yjg3MzhmNzJkNjcyOTUwM2RmNDEzYTFhNTdmNzhhN2QwNzY5ZjBmOWNkZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4861">
+      <c r="A4861" t="inlineStr">
+        <is>
+          <t>4188.png</t>
+        </is>
+      </c>
+      <c r="B4861" t="inlineStr">
+        <is>
+          <t>tamilpsd-10768.png</t>
+        </is>
+      </c>
+      <c r="C4861" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImM1QWcwUjg5Rlg2ZUg0SzdHK1JmVWc9PSIsInZhbHVlIjoiOTZXcDM1UzFWVGZSOHVqcm5YQnRlQT09IiwibWFjIjoiM2I0ZmVhMTI0OThlYWRlZjgwZWM4OTEwOTU3MWU3Zjc4MjI5NGZmNzc5ZWQ3ZjNiMjc1NzljZTU0Y2Y1OWYyMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4862">
+      <c r="A4862" s="3" t="inlineStr">
+        <is>
+          <t>4187.png</t>
+        </is>
+      </c>
+      <c r="B4862" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10769.png</t>
+        </is>
+      </c>
+      <c r="C4862" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1pQXdlZmJhcDhVV3l3ellDZFhyOHc9PSIsInZhbHVlIjoibTlyUXdRd2NYdFRpSEFsWFBWR2FCQT09IiwibWFjIjoiMDgzYmM3NGEwMTk0NWUyYjc5NTUyNmNjNzMzNWJkZTFhNmIzMDY3YTgxNDk0M2E3NDcxNmU1NmMxNDAxNDAyZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4863">
+      <c r="A4863" t="inlineStr">
+        <is>
+          <t>4186.png</t>
+        </is>
+      </c>
+      <c r="B4863" t="inlineStr">
+        <is>
+          <t>tamilpsd-10770.png</t>
+        </is>
+      </c>
+      <c r="C4863" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkYrSmN4bGNlWjF3akRVVVVJbVo3RGc9PSIsInZhbHVlIjoibzgzd0NCMHMxWUhiYzJXTVppc3YzQT09IiwibWFjIjoiMWQwN2NmMTg5Y2JmYjU0NTViYjc3MDI2ZTZiMWUyNjg5YWRlMmQ2YzNkMzQ0Y2Q4ODcxZWJlMTFmZWE0MjQyNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4864">
+      <c r="A4864" s="3" t="inlineStr">
+        <is>
+          <t>4185.png</t>
+        </is>
+      </c>
+      <c r="B4864" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10771.png</t>
+        </is>
+      </c>
+      <c r="C4864" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNVbCt0NDBqaTdBL01UUGFtV0VNcVE9PSIsInZhbHVlIjoiR3JVNUFaZmxKcjFNd0t5M2hLSDZwUT09IiwibWFjIjoiNjgwMWIxOTJhNWE1YjU5M2EwOTEzNWFlNGI1YjBiMGVmOWY2ZGRhMjhjYjMxOTk2NWE2OTA3ZWJjYmZlOGQ5NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4865">
+      <c r="A4865" t="inlineStr">
+        <is>
+          <t>4184.png</t>
+        </is>
+      </c>
+      <c r="B4865" t="inlineStr">
+        <is>
+          <t>tamilpsd-10772.png</t>
+        </is>
+      </c>
+      <c r="C4865" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikl0TEl4S21yN29XeTdxVktJTVZZSEE9PSIsInZhbHVlIjoiVTdJZzNqTFlCdkdoUWJoc25pTSttUT09IiwibWFjIjoiNjg0ZjBiZDlhMDZjMmY0MzUyYzdiMWViMTljOWQzNWIzOGY4MWNhMDY0MzNiNTA0YTFhNjI3YWQzMWIyNzc2ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4866">
+      <c r="A4866" s="3" t="inlineStr">
+        <is>
+          <t>4183.png</t>
+        </is>
+      </c>
+      <c r="B4866" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10773.png</t>
+        </is>
+      </c>
+      <c r="C4866" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ino2azdqMmx6UGNiTWdiNFBwREpWSVE9PSIsInZhbHVlIjoiTUdWenAyWWtWS0J5OGUrSUVUN2E3Zz09IiwibWFjIjoiMjFjMDExODkyN2FhNDdjNWNkNjQ5MDEyNTlmZWJmNjkwMzRjOGI2YzMwNjQ3NzliMmZjODk5NTg1OGExYmFhMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4867">
+      <c r="A4867" t="inlineStr">
+        <is>
+          <t>4182.png</t>
+        </is>
+      </c>
+      <c r="B4867" t="inlineStr">
+        <is>
+          <t>tamilpsd-10774.png</t>
+        </is>
+      </c>
+      <c r="C4867" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1sK3daRGNmY0dmdzRsN0ppbkFaQnc9PSIsInZhbHVlIjoic1pPUTFYT05TazJpbXIwc3BzR3U3dz09IiwibWFjIjoiMjBjYzdiNDllNzJkMmEzZjE1NjBiOTdjMGE3MzlkZDM2NWUxNmUxYWFmNDdjNGVkYmFjMGRhOWJhYzNkNWE1NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4868">
+      <c r="A4868" s="3" t="inlineStr">
+        <is>
+          <t>4181.png</t>
+        </is>
+      </c>
+      <c r="B4868" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10775.png</t>
+        </is>
+      </c>
+      <c r="C4868" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imc5TGRwVUp1aDBOV2ZIc3lCZ1JpMmc9PSIsInZhbHVlIjoiaFNvYjVQUzVLb2JQc0xSd1k4RUZGQT09IiwibWFjIjoiMjE1YTFhNTg0Njg3ZTI2YWZhNGZjY2ZiM2QzOGYxNDI2NmMxN2ZhMTZhZDhkYjdiODZhMjk0NGZmYjQ3YzE0YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4869">
+      <c r="A4869" t="inlineStr">
+        <is>
+          <t>4180.png</t>
+        </is>
+      </c>
+      <c r="B4869" t="inlineStr">
+        <is>
+          <t>tamilpsd-10776.png</t>
+        </is>
+      </c>
+      <c r="C4869" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRrYncrY0dpNUZJaTVsWWZWT0U2YWc9PSIsInZhbHVlIjoiWjJxczA0c2xnL3Jrc0JvbkZ1ODlqUT09IiwibWFjIjoiYmM5NzQ4YjJiY2YzMDRlYjUxZmU2ZmY2MWVkMzg2MWIzMmFmNjM5MzA0NjgwNTlmZDU5NWVmOWMwMzc3MmYxZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4870">
+      <c r="A4870" s="3" t="inlineStr">
+        <is>
+          <t>4179.png</t>
+        </is>
+      </c>
+      <c r="B4870" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10777.png</t>
+        </is>
+      </c>
+      <c r="C4870" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhSS1diYVpobHZudmx4enZPWG81ZEE9PSIsInZhbHVlIjoieEQ4Mnc3eTQ0dU5vWGZqQjArUlRNUT09IiwibWFjIjoiMDFmNGU4NWRlZDM0NzZiODBlMzk2NzcyZmZkM2NmNTQzNjYyMjA1OGE1YTA4ZTlmMmVkMDkwNGFhY2NjZjJmMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4871">
+      <c r="A4871" t="inlineStr">
+        <is>
+          <t>4178.png</t>
+        </is>
+      </c>
+      <c r="B4871" t="inlineStr">
+        <is>
+          <t>tamilpsd-10778.png</t>
+        </is>
+      </c>
+      <c r="C4871" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhJY1hVclJLNGNRMUhuWm85cHBYZlE9PSIsInZhbHVlIjoiNWU4cmdNN1ZpZVloSExjTXgvSWNpUT09IiwibWFjIjoiNWU5NGI5ZjU0NTY1YTViYzExYjA3OWM3YzQwZTcwMWRmZDQ1NDkxOGE2NjdlNjEwMTY0Zjk3ZWRlZGIxNzY3NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4872">
+      <c r="A4872" s="3" t="inlineStr">
+        <is>
+          <t>4177.png</t>
+        </is>
+      </c>
+      <c r="B4872" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10779.png</t>
+        </is>
+      </c>
+      <c r="C4872" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlI3SE1hVWowTFYvVXNNSzJnY3BxRkE9PSIsInZhbHVlIjoidkw0OVdCM3g2UmlpWnd4dHpiY2pwQT09IiwibWFjIjoiMWQ0NjkzOGRmZGMwN2U0MzhmN2Q5OTEzNjQwYjMyZmM0YzZmOWI2NTZlMjUyNWNjYzU5ZWRhYWRkYmE2ZDUxMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4873">
+      <c r="A4873" t="inlineStr">
+        <is>
+          <t>4176.png</t>
+        </is>
+      </c>
+      <c r="B4873" t="inlineStr">
+        <is>
+          <t>tamilpsd-10780.png</t>
+        </is>
+      </c>
+      <c r="C4873" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1aS2cwalViak5WS1BQdjBURDRRb0E9PSIsInZhbHVlIjoiMFJtSGhjTG5kT09JMzFTSzg2TFZxQT09IiwibWFjIjoiZGUzYzM0NTNjZjM3YmUzOTIxMjRjNWRhY2RkODdjNWUyZDg4MGFiYTAxMmRlZTA0ZGRkNGNjNmRmYTcyNDEwMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4874">
+      <c r="A4874" s="3" t="inlineStr">
+        <is>
+          <t>3760.psd</t>
+        </is>
+      </c>
+      <c r="B4874" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10781.psd</t>
+        </is>
+      </c>
+      <c r="C4874" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImE2WUtDMW4rSGc3RDFMd21mRVoyUlE9PSIsInZhbHVlIjoid29UYU90ZWlYREdQT0V3ZmlUU1p4QT09IiwibWFjIjoiNThiNzFiZTc5OWMyNDI1YmU4MTg5ZWUwNmVlMWY2ZWM4MzI3ZGVmZTgzNWM3YTU3YjMxOWQ2OGMwZDlhMzNjYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4875">
+      <c r="A4875" t="inlineStr">
+        <is>
+          <t>3020.psd</t>
+        </is>
+      </c>
+      <c r="B4875" t="inlineStr">
+        <is>
+          <t>tamilpsd-10782.psd</t>
+        </is>
+      </c>
+      <c r="C4875" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZuckRoT0FDcU1sd1Y3aVFqcXNzZkE9PSIsInZhbHVlIjoiVzRDeGlwRUZwYXlhTUxKbGp2MjI3Zz09IiwibWFjIjoiM2IzZDcyNDM0ODI1YjA1NTRiMTQ5NWU2MmVjYzkwYWYxODRhZmRjOTNlNTRmZjgwMWE2ZTcyY2NkZGVmNDFjYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4876">
+      <c r="A4876" s="3" t="inlineStr">
+        <is>
+          <t>2791.psd</t>
+        </is>
+      </c>
+      <c r="B4876" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10783.psd</t>
+        </is>
+      </c>
+      <c r="C4876" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFVaFp3WlBkZ1FVNGxXdXFxWEt2L1E9PSIsInZhbHVlIjoiVk5oQ3hQTEswN0lkL09zNzhtc1JxQT09IiwibWFjIjoiYzVkZTAzYzc2ZmQ4NDI3ZWM4NTU2Y2UzNTY3ZTZjZTc0NjA4MGE4NDlhNjJhYzhjZWNjYWNiMjIxMTFmOGJlNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4877">
+      <c r="A4877" t="inlineStr">
+        <is>
+          <t>2543.psd</t>
+        </is>
+      </c>
+      <c r="B4877" t="inlineStr">
+        <is>
+          <t>tamilpsd-10784.psd</t>
+        </is>
+      </c>
+      <c r="C4877" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZIWXhCeWxVVjc4VlhHaTZQbDR4YUE9PSIsInZhbHVlIjoiOVFPTXJyUTRsbXIyU25SOXpjUTJ2Zz09IiwibWFjIjoiYjViMWU4ODI3OTJkZWVkOGU2N2IzYzU1ZWJmYzQ5MzA2MTliYzYxZmZmMTdmMGExNTlkNzY1OTk5MTljNzI5ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4878">
+      <c r="A4878" s="3" t="inlineStr">
+        <is>
+          <t>2317.psd</t>
+        </is>
+      </c>
+      <c r="B4878" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10785.psd</t>
+        </is>
+      </c>
+      <c r="C4878" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRUcGJ2aDdvUHNvVXJKS1kvVHNFZmc9PSIsInZhbHVlIjoiUE4xK3RNZndoMXVFdElQN2Q2d0FMZz09IiwibWFjIjoiYzNjNGRlMDI5ZWY5OTEwY2IzOTc4YWEwMzY2MzBiMjNjMGY2MGEwOGE4OGI3ZmZiMGYwOWU1OTNhNmVmMzMyYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4879">
+      <c r="A4879" t="inlineStr">
+        <is>
+          <t>2316.psd</t>
+        </is>
+      </c>
+      <c r="B4879" t="inlineStr">
+        <is>
+          <t>tamilpsd-10786.psd</t>
+        </is>
+      </c>
+      <c r="C4879" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndvMTNva3E0N3ZoOTJYd3hnVmdoL0E9PSIsInZhbHVlIjoibUs2dVRBaGNOV0NjRE90VE1xQ2Mrdz09IiwibWFjIjoiYmY5NmJiMDc1NzIyNTM0NzMwOTY5MzE2MmUyNmNlODJiZjgzZjFmMjUwMzhmZGMwYzRhZGIxNjQzMDc2ZmJkNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4880">
+      <c r="A4880" s="3" t="inlineStr">
+        <is>
+          <t>2315.psd</t>
+        </is>
+      </c>
+      <c r="B4880" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10787.psd</t>
+        </is>
+      </c>
+      <c r="C4880" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkEyK1VtYXFuMm5lbGVWS0wzVXFLR1E9PSIsInZhbHVlIjoiazkvMnJUTFVtdTZNNnl3MU1Vcys1QT09IiwibWFjIjoiOGQ3ZTg3ODhjN2VhZmZmMWQyYmM3NGJjYjg1MmNjN2I4ZWExZmM3OGIxZmU1NWY1NzEwZGE2YzIwYWYwMjgzMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4881">
+      <c r="A4881" t="inlineStr">
+        <is>
+          <t>2314.psd</t>
+        </is>
+      </c>
+      <c r="B4881" t="inlineStr">
+        <is>
+          <t>tamilpsd-10788.psd</t>
+        </is>
+      </c>
+      <c r="C4881" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJTMHc5ellUU1JZcU5mWit0WkNNSEE9PSIsInZhbHVlIjoiTllaNlpuVEdWdjI5cDQ1MzFlRGtRUT09IiwibWFjIjoiOTI3YTQ2NWRjZmU1ZjJkMjk3OGE3ZTlkZWY1ZWRlMDBkYWQ1OWFjOWY4YTc4Y2NkOWY0ODY4YzJmNTE4MGI2ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4882">
+      <c r="A4882" s="3" t="inlineStr">
+        <is>
+          <t>2313.psd</t>
+        </is>
+      </c>
+      <c r="B4882" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10789.psd</t>
+        </is>
+      </c>
+      <c r="C4882" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJjRzA1aGVLa0VVOGdaZjVUU3ZJZGc9PSIsInZhbHVlIjoiTTZVRkh4dGN2d2tkYVNwSzg4NGlkdz09IiwibWFjIjoiNGVlZTE0NGM1ODExNDRhNDgxZTVkNmMxNWIxNzY0NTE0NTZjNmIzNjgyNDM1ZGZjYTU5Nzk5MGI0YWZhZTFiMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4883">
+      <c r="A4883" t="inlineStr">
+        <is>
+          <t>2312.psd</t>
+        </is>
+      </c>
+      <c r="B4883" t="inlineStr">
+        <is>
+          <t>tamilpsd-10790.psd</t>
+        </is>
+      </c>
+      <c r="C4883" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFITGozVFd2VXhMSXQ1T1BncmM1bmc9PSIsInZhbHVlIjoib0tTZzEwYUZvWTE4YUZoKytCRytJdz09IiwibWFjIjoiN2RkZTQyN2FlMjU0YTRjYzgzZTZiMTRhNmUxYjBiOWY4ZGE3ZTM3MmMwY2NhZDM4YzJhNGZmNzIzNjc1OTIwNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4884">
+      <c r="A4884" s="3" t="inlineStr">
+        <is>
+          <t>2311.psd</t>
+        </is>
+      </c>
+      <c r="B4884" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10791.psd</t>
+        </is>
+      </c>
+      <c r="C4884" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkdrN3k3ZW1pWEpZVHdJN1pmcHBUdkE9PSIsInZhbHVlIjoia2FJNkV0bERBNHB0MnlqNGE5dGNqQT09IiwibWFjIjoiNGQyYWZkYjM5NGQ0YzQ1MmYxYjFkZGYyNTUxNzZhMjY3YWMxOGIxODJlNGVkYmE4ZTNmZGE2MDUxNGJjYmEzOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4885">
+      <c r="A4885" t="inlineStr">
+        <is>
+          <t>2310.psd</t>
+        </is>
+      </c>
+      <c r="B4885" t="inlineStr">
+        <is>
+          <t>tamilpsd-10792.psd</t>
+        </is>
+      </c>
+      <c r="C4885" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjZrc0NLZ1JUK1Z5ZlEzUUJQQnFlTVE9PSIsInZhbHVlIjoibjVqT25ET2dSdlhOTEhCaTEvNlhDZz09IiwibWFjIjoiYjUxMzExZGZjNzYxMDBiOGM0MWNlYzg2MTM2YjhlYWIzYzNjMWVlNTJmM2I5YjQ1YTJkNTQwMTlhYjZhNGJjZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4886">
+      <c r="A4886" s="3" t="inlineStr">
+        <is>
+          <t>2309.psd</t>
+        </is>
+      </c>
+      <c r="B4886" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10793.psd</t>
+        </is>
+      </c>
+      <c r="C4886" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImEyZVJTQzdoTUdiMXJGU0VoUy9CN1E9PSIsInZhbHVlIjoiUjliZ2NJQVZ4VmV6QkQ2UmNrelhMUT09IiwibWFjIjoiMzAxYmZkNWY3NjQ1MTE1N2EyMDVmNzM2NjcyMDIyMThkMGY5YzkxYWQwZTU5YzQwNDM0ODVmYTRhYjg5ZTYwOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4887">
+      <c r="A4887" t="inlineStr">
+        <is>
+          <t>2308.psd</t>
+        </is>
+      </c>
+      <c r="B4887" t="inlineStr">
+        <is>
+          <t>tamilpsd-10794.psd</t>
+        </is>
+      </c>
+      <c r="C4887" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik81TGxxcUNHVUU2dTl6MWplbU5aYVE9PSIsInZhbHVlIjoia0g1RDVhbG1CTGR0STAxVHRMUFIrdz09IiwibWFjIjoiNGY3MWU0OWU1Mjk1YTkwM2Y2ODFkMTMyYzQ1M2U4NjNlY2U0ZjE0M2EwMmJhNWVlMzdkZmQxOWRkOTRmZDg5NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4888">
+      <c r="A4888" s="3" t="inlineStr">
+        <is>
+          <t>2307.psd</t>
+        </is>
+      </c>
+      <c r="B4888" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10795.psd</t>
+        </is>
+      </c>
+      <c r="C4888" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFEOXlac0N6b0U0TTJkM1AzV0t6Z3c9PSIsInZhbHVlIjoid0lWSmVyRlM1M25zWGVOQ2x1SHU1dz09IiwibWFjIjoiOTEwODZjNTZjZDczYjlmNzE5M2Q2OWY3NWY2ZjAwYTNkMjYyNDdiOGM2ZWU4MzAzOTA2ZTQ4NDg5MzFmZmJjZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4889">
+      <c r="A4889" t="inlineStr">
+        <is>
+          <t>2306.psd</t>
+        </is>
+      </c>
+      <c r="B4889" t="inlineStr">
+        <is>
+          <t>tamilpsd-10796.psd</t>
+        </is>
+      </c>
+      <c r="C4889" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik92T1NwZTAybkI5cFVKNzgvQVZXb1E9PSIsInZhbHVlIjoiQWVMRzI0cDVlUjQwNjZUaFlLdXV2dz09IiwibWFjIjoiOTMxM2ZmNzc3NzhlNzUwZTI2NThkN2I1ODdiNWI3M2RkNTA2OTc5NGNlZmJlNjI4YWNjNWJjNjFiZmNiNmFjYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4890">
+      <c r="A4890" s="3" t="inlineStr">
+        <is>
+          <t>2305.psd</t>
+        </is>
+      </c>
+      <c r="B4890" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10797.psd</t>
+        </is>
+      </c>
+      <c r="C4890" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9MaFB5WWVkZWhSaWl6WkwzTWkzd0E9PSIsInZhbHVlIjoiUjBQUUJsOE5XUFVrT3pIUVB2djY3UT09IiwibWFjIjoiMzA5ZTg5YWQ0N2UwZDVlYzJiNzg0NDRhYTA5M2RlNmUxOWI4NTViMDcxNjQwYTExM2I4NTIzYWU5YWFkNTFkYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4891">
+      <c r="A4891" t="inlineStr">
+        <is>
+          <t>2304.psd</t>
+        </is>
+      </c>
+      <c r="B4891" t="inlineStr">
+        <is>
+          <t>tamilpsd-10798.psd</t>
+        </is>
+      </c>
+      <c r="C4891" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhqU2ZxZVJ6bFRUZ0JkcjJUcFVnNEE9PSIsInZhbHVlIjoiZlZEVDNyRmhNOURXY1pQdTZtTEJ4dz09IiwibWFjIjoiY2RiMmNkZTZlMjEyNDViYjE1M2M1ZTMyMGFlZWQ1MmNhYzI5NjE4NTdlMWRiNWVkNWZjOWVlZjQ0MWNmOGU2MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4892">
+      <c r="A4892" s="3" t="inlineStr">
+        <is>
+          <t>2303.psd</t>
+        </is>
+      </c>
+      <c r="B4892" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10799.psd</t>
+        </is>
+      </c>
+      <c r="C4892" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjdLOWFSZTI5NDkvNnB2c0dvbzM4YXc9PSIsInZhbHVlIjoiaHBhTTJWc2xSV25mSEhla1BrZnQxQT09IiwibWFjIjoiZTdkMTEyYzc0ODQ5NzUwYTJkZTY0Mjk5YjBiNjFiYTRkN2FhOTJmZDkzNmViODk0ZjA1ODBmOTdmZmFlMGFiYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4893">
+      <c r="A4893" t="inlineStr">
+        <is>
+          <t>2302.psd</t>
+        </is>
+      </c>
+      <c r="B4893" t="inlineStr">
+        <is>
+          <t>tamilpsd-10800.psd</t>
+        </is>
+      </c>
+      <c r="C4893" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InMzZTMvcDE2eE9CZVViN1hjcko3QWc9PSIsInZhbHVlIjoiTTNmdnZUZkZrY0dlVnVsR0FkZWNVQT09IiwibWFjIjoiM2RjMmJlZDM5YTljNGY5ZjQ3NzlkM2IxMjFhNGVmNWQ4MjQ0MjJmOTgzMmEzNmIyZThkYzQ0NTNjNDk4Mjg2ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4894">
+      <c r="A4894" s="3" t="inlineStr">
+        <is>
+          <t>2301.psd</t>
+        </is>
+      </c>
+      <c r="B4894" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10801.psd</t>
+        </is>
+      </c>
+      <c r="C4894" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5YUEsxYm5ZOXpvUTgyWDdNM2hUMnc9PSIsInZhbHVlIjoiajM5c0Faak1JdzRQbnIrRFE0Mzd0QT09IiwibWFjIjoiNThlOWIzZGFkNTJjNzhmZTQ2NWJkYThlMWQ5OGEwYTZkMWYwYjg4ZTdhYWJlOTAxZDZjMGZiOTgyYmFhM2E0YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4895">
+      <c r="A4895" t="inlineStr">
+        <is>
+          <t>2300.psd</t>
+        </is>
+      </c>
+      <c r="B4895" t="inlineStr">
+        <is>
+          <t>tamilpsd-10802.psd</t>
+        </is>
+      </c>
+      <c r="C4895" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZMclgvNC9ONnBFWGgwSWVnQUJLVHc9PSIsInZhbHVlIjoiU0pINVZ6aXBzZG1sMEQ4V29EYkc0Zz09IiwibWFjIjoiNTM1ZjMzZTI3MDBmOGFjNmY3M2FjMDIxZmQ1YmE0ZDc5MTNmMTNkY2YwMTUyYmY3NjM4NGJjNDQ4YmM5MGRjYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4896">
+      <c r="A4896" s="3" t="inlineStr">
+        <is>
+          <t>2299.psd</t>
+        </is>
+      </c>
+      <c r="B4896" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10803.psd</t>
+        </is>
+      </c>
+      <c r="C4896" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlrcGZERXRWNDRaanlVOTdabk4yQ1E9PSIsInZhbHVlIjoiZjR0akZjZnowNWtlVkVHeEJNZXBJdz09IiwibWFjIjoiMzYzYWE3YzkzM2RiYjYzMzQzYjY5MzQ2ZjBhYTk4MTgyYjJkYjdmYjFlNDIxY2ZiMzJmNzBhYzljMWZmMjBjYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4897">
+      <c r="A4897" t="inlineStr">
+        <is>
+          <t>2298.psd</t>
+        </is>
+      </c>
+      <c r="B4897" t="inlineStr">
+        <is>
+          <t>tamilpsd-10804.psd</t>
+        </is>
+      </c>
+      <c r="C4897" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZCY29TYnVvRWpnMEE3MjB5dlVRUnc9PSIsInZhbHVlIjoiekozVjJ5citBb1UyNzVnNTZkd25ZZz09IiwibWFjIjoiYmQ5YjViYzg4N2JkN2ZlNjRiOTdjZjdlYzZjY2NkNjhjNTg4ZGE5Zjc0MTJhYTIwNTE4ODg5YzNmODk3YTMzYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4898">
+      <c r="A4898" s="3" t="inlineStr">
+        <is>
+          <t>2297.psd</t>
+        </is>
+      </c>
+      <c r="B4898" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10805.psd</t>
+        </is>
+      </c>
+      <c r="C4898" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlU3VTVGVkg0Qk1GRU15d0xYRm1XNHc9PSIsInZhbHVlIjoiYk1zUU9HSlJ6YlRpcnVYUDUvNFVwUT09IiwibWFjIjoiYmE0MGFjZjdiMTcyODMzMTZiNGE0ZGFkZDc4NjU4ZGJjNmQxNGM2ZTVhMzYwZmFjOTgxNTlmYTZmM2Y1YzVmYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4899">
+      <c r="A4899" t="inlineStr">
+        <is>
+          <t>2296.psd</t>
+        </is>
+      </c>
+      <c r="B4899" t="inlineStr">
+        <is>
+          <t>tamilpsd-10806.psd</t>
+        </is>
+      </c>
+      <c r="C4899" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktQSlhIejVua3RKTGVTeEI3aHJSSHc9PSIsInZhbHVlIjoiNG1HUWhWbjIvekVQSFdjVTYxRythdz09IiwibWFjIjoiZGRkZmRiYjI5NjM2NWRkNGZhOTJhNTkwM2E5YTRkN2E4YjE5YmYzMzBhYjczMmUyNjA4YTc0OTMzZTY3Zjg2MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4900">
+      <c r="A4900" s="3" t="inlineStr">
+        <is>
+          <t>2295.psd</t>
+        </is>
+      </c>
+      <c r="B4900" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10807.psd</t>
+        </is>
+      </c>
+      <c r="C4900" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjQzRzdReFBxSXBib2FrQm5rcXh6aGc9PSIsInZhbHVlIjoiVlFqMWtMQ1FqNFNHTGZDaTcreTl6QT09IiwibWFjIjoiMDQ4Y2E2NDcyNWZkYmMzNjY5OTFhNTFiOWVlMDNlMjNiZWFiZjRhMmVhZjA2YTk1Y2U1OWU3N2VhNGU5YmU3MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4901">
+      <c r="A4901" t="inlineStr">
+        <is>
+          <t>2294.psd</t>
+        </is>
+      </c>
+      <c r="B4901" t="inlineStr">
+        <is>
+          <t>tamilpsd-10808.psd</t>
+        </is>
+      </c>
+      <c r="C4901" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Inh0bVA0QVM5bHBlZnFseEVaUGxycGc9PSIsInZhbHVlIjoiaHU0cmNRMk85L3g0RjZzUHBBV1dZUT09IiwibWFjIjoiYjQ1Y2RjY2MwYzkzNDFiZDY5ZGQ5ZDg4YjU2ZWE2NzI5ZGRhNzQwYjgwOGNlMWQ1M2FjMDRjMTQ0NzlmZTcwYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4902">
+      <c r="A4902" s="3" t="inlineStr">
+        <is>
+          <t>2293.psd</t>
+        </is>
+      </c>
+      <c r="B4902" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10809.psd</t>
+        </is>
+      </c>
+      <c r="C4902" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkhGUllCSGtHc001eFlkL3RDZVNpWHc9PSIsInZhbHVlIjoicGljcklUbUVjRVQ3ZHRyTllLQXkrZz09IiwibWFjIjoiNTExNjg2Yzk5NGFlY2JiNWFkNDMzYjk4YjBmZmUxOGYwNzk2NmIyOGE5NzQ0YmE5MzI0ZTgzMzliNTkwMzAwMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4903">
+      <c r="A4903" t="inlineStr">
+        <is>
+          <t>2292.psd</t>
+        </is>
+      </c>
+      <c r="B4903" t="inlineStr">
+        <is>
+          <t>tamilpsd-10810.psd</t>
+        </is>
+      </c>
+      <c r="C4903" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndLdDl6TWNveVAzN09VUEx6Wmp0dnc9PSIsInZhbHVlIjoiKzJYQVMvbDhRcEh0K2cxNmEzKzdPZz09IiwibWFjIjoiOGVhY2JjOWM3NTUxYTJkMDY0YTYwNjhiZDIyOTgwMTM5ZjcwODI0MGM3NzZhMjQ0N2Y5MzFlYzYyMTZmZDYyMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4904">
+      <c r="A4904" s="3" t="inlineStr">
+        <is>
+          <t>2291.psd</t>
+        </is>
+      </c>
+      <c r="B4904" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10811.psd</t>
+        </is>
+      </c>
+      <c r="C4904" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik9WUnduQ1MrQUJUZTFsVDRPaU1GNnc9PSIsInZhbHVlIjoibElrSkVLSXBxNjd4c2d1d0NHNC9SZz09IiwibWFjIjoiMDEwMDI0Mzc3MjRkM2Y5YjIzOWNkNmVlMTY0MmZjOTMyYmE4YjRlMTA2ZmIwYjkwODcyMzM5ODI0NzczNDZjNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4905">
+      <c r="A4905" t="inlineStr">
+        <is>
+          <t>2290.psd</t>
+        </is>
+      </c>
+      <c r="B4905" t="inlineStr">
+        <is>
+          <t>tamilpsd-10812.psd</t>
+        </is>
+      </c>
+      <c r="C4905" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllEQy82NmZ0SVVXQkhPN1dGRVpYT3c9PSIsInZhbHVlIjoiQy92dGNnUXpHTVNVeFUybUc1NWlIdz09IiwibWFjIjoiZTgxZTI0Y2E4ODI1NmM4YjNhODVmYzQxZmNkMjQ2ZjM2OTBmOThiMzBmYTExOGFhZmU4MjAyZThiNzY4ZTYwYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4906">
+      <c r="A4906" s="3" t="inlineStr">
+        <is>
+          <t>2289.psd</t>
+        </is>
+      </c>
+      <c r="B4906" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10813.psd</t>
+        </is>
+      </c>
+      <c r="C4906" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZ6Q0NiWnBNZ2lSL3dqLzRXQ0N1UEE9PSIsInZhbHVlIjoiMG5taURRbkM4alV1NXZsbThpQUdsZz09IiwibWFjIjoiNzQzMDQ0YmJlNDNiNjI4NjVmNjlhNTllMzc5ODY0YzI0ZWU5NDAwNmIwNzQ0ZWJmMjRlNTg2MjJkZWI5NjYzOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4907">
+      <c r="A4907" t="inlineStr">
+        <is>
+          <t>2288.psd</t>
+        </is>
+      </c>
+      <c r="B4907" t="inlineStr">
+        <is>
+          <t>tamilpsd-10814.psd</t>
+        </is>
+      </c>
+      <c r="C4907" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhHN1hiVGlGeExuM0lVOTQ5Q2g3U0E9PSIsInZhbHVlIjoiQXZzTU84MEdLaDlEUzRycGdTWDNRdz09IiwibWFjIjoiMmFmZDJiMTE4MDA3N2YyN2ZmNzgwNWEwMWE5MjJkMDJhYmE3NTU3MGUzNWFjZjY0OWQ0ZTVkNDU5NmNiOWFlZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4908">
+      <c r="A4908" s="3" t="inlineStr">
+        <is>
+          <t>2287.PSD</t>
+        </is>
+      </c>
+      <c r="B4908" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10815.psd</t>
+        </is>
+      </c>
+      <c r="C4908" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRtVEdTMmZOVXZiMGU3Ym82eVBXWUE9PSIsInZhbHVlIjoiRGZTUm5yRHZ6QStBa0l3UUs2a29yZz09IiwibWFjIjoiYTYxOTljOWM5MGIwZDM2YjJiMmU4MjFmMjQyNTAzNjU4ZWJiYWU2MzI3M2ViZWZjZDAyYzkzNDNmZDI5Yzg1YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4909">
+      <c r="A4909" t="inlineStr">
+        <is>
+          <t>2286.PSD</t>
+        </is>
+      </c>
+      <c r="B4909" t="inlineStr">
+        <is>
+          <t>tamilpsd-10816.psd</t>
+        </is>
+      </c>
+      <c r="C4909" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImYzZ3VZTnJlNGxjbnNoSFlRZERlUFE9PSIsInZhbHVlIjoiWWV2YWJQZXAyejhNanp3bys3RWR0UT09IiwibWFjIjoiMjlmMzM4MmQ5ODYwNTMyMDI2MjJmOGQzZjhiYzNlZWMzZjc2YjA0ZjI1MDVjMWExNWIyYjNlZDUzMDE3YmFhOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4910">
+      <c r="A4910" s="3" t="inlineStr">
+        <is>
+          <t>2285.PSD</t>
+        </is>
+      </c>
+      <c r="B4910" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10817.psd</t>
+        </is>
+      </c>
+      <c r="C4910" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IitQcVRwbCtYa01malZ4VXFwTy95UUE9PSIsInZhbHVlIjoiMlZuQWsrakdsUG5ldUYzdkpmNUU3dz09IiwibWFjIjoiNzcyMTY3MmVlOWMxNDUxZWYwNzc2ZDRkMmM4Y2U4ZDZkYjM2ODEyYTkyY2RmYThkMjJlMDJiN2MwM2FkZDlhNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4911">
+      <c r="A4911" t="inlineStr">
+        <is>
+          <t>2284.PSD</t>
+        </is>
+      </c>
+      <c r="B4911" t="inlineStr">
+        <is>
+          <t>tamilpsd-10818.psd</t>
+        </is>
+      </c>
+      <c r="C4911" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNVc3o1Rmc5SWdIVUd4SGtRSTBHSEE9PSIsInZhbHVlIjoiM3ZYc3UwNkljanJiQld0TWp5eWJhQT09IiwibWFjIjoiNGZlYWMwYzlhNTAzODY4YTUxNTBiMWY2ZjE2M2EzMTEyMDRlNTRmZTQxOTVlMWQ4M2Y3NmQ4MDk0MmZhMDYyMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4912">
+      <c r="A4912" s="3" t="inlineStr">
+        <is>
+          <t>2283.PSD</t>
+        </is>
+      </c>
+      <c r="B4912" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10819.psd</t>
+        </is>
+      </c>
+      <c r="C4912" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllDSmVOR25xVlp0WFVmUDZkZzBCd0E9PSIsInZhbHVlIjoiUjQrMU5oZnZxL1dEZi95VEU4ay9Rdz09IiwibWFjIjoiYmNmYjI2MDgyZWFhYmRjOTJiMGYxYzdkOWEyYjc2ZmQ3OTQ5ZmEyMjJlOTIxYjRjNWYwNzUyMzE4ZWQ5MjQyNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4913">
+      <c r="A4913" t="inlineStr">
+        <is>
+          <t>2282.psd</t>
+        </is>
+      </c>
+      <c r="B4913" t="inlineStr">
+        <is>
+          <t>tamilpsd-10820.psd</t>
+        </is>
+      </c>
+      <c r="C4913" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFmd2xIM3BJcnpuUTdjZ0hpRCtrZ3c9PSIsInZhbHVlIjoiekdheFcxamYzRXZnK0tuVU9xZk4yUT09IiwibWFjIjoiN2QwYWI1MTYyM2MzZjkxMGVjMDNiMjcwMTE0MWJhNjQwYzE5YzZmZjUzOWE5MmFkNzhiOTg3ZDQyZmFjYWQ4YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4914">
+      <c r="A4914" s="3" t="inlineStr">
+        <is>
+          <t>2281.PSD</t>
+        </is>
+      </c>
+      <c r="B4914" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10821.psd</t>
+        </is>
+      </c>
+      <c r="C4914" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IldyU1hzYm5INDdNVEZLNkxObU1Id3c9PSIsInZhbHVlIjoiNENtYmJDM2lHNHh5WnZtclpJWEhKZz09IiwibWFjIjoiZWIxNzFjNDJkZGJjZmY1YmU4OTMzMjNhNzA5Yzk2MjFiOWJkMjZiZjljMTZmNzBmMDhlNmU3MWEyODRkNzM0ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4915">
+      <c r="A4915" t="inlineStr">
+        <is>
+          <t>2334.PSD</t>
+        </is>
+      </c>
+      <c r="B4915" t="inlineStr">
+        <is>
+          <t>tamilpsd-10822.psd</t>
+        </is>
+      </c>
+      <c r="C4915" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJpNUtwVXh5WFEwOHJCSFhOUUFnSlE9PSIsInZhbHVlIjoiQ2NWL0ZYNFJaTStSNUljRms2RzVOQT09IiwibWFjIjoiMGE2MTE4MzUyYWIyZTI3NmQ5ZTA3Nzk2YjM3MTVhMjdhMmFkNDMyZDdlNDdmNTg5MWY2Y2I5YWNiMDIwNjI1OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4916">
+      <c r="A4916" s="3" t="inlineStr">
+        <is>
+          <t>2279.psd</t>
+        </is>
+      </c>
+      <c r="B4916" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10823.psd</t>
+        </is>
+      </c>
+      <c r="C4916" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5WaFhBM0l6dkpBZXFPQUloR0Ztd2c9PSIsInZhbHVlIjoiY3NhRlBLd0ltdDdTNnZkVkFxMmV3UT09IiwibWFjIjoiMTIyMThjMmJkNDFkZDA0YjUzZDcyN2ZiNzM4YzQyMDIxZmRlOWRjYTRlNjdlZjQxN2U4NTkyMDI2NzhlMjIzNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4917">
+      <c r="A4917" t="inlineStr">
+        <is>
+          <t>2278.psd</t>
+        </is>
+      </c>
+      <c r="B4917" t="inlineStr">
+        <is>
+          <t>tamilpsd-10824.psd</t>
+        </is>
+      </c>
+      <c r="C4917" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imhmd1RuSHIzMTR6MktZT3M5R1lVcEE9PSIsInZhbHVlIjoiWGdiQnJCTkhHUWdRSzNjUVBEMzFqdz09IiwibWFjIjoiZTQ5MDY1MzQwMWQ3NWQ1MmFkYWRkYWI3ZDYwYzQ1OWI2NWFlMjM0MTFlZGVmMmI0NDFhZGEzNmFmMzgzMGEwOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4918">
+      <c r="A4918" s="3" t="inlineStr">
+        <is>
+          <t>2277.psd</t>
+        </is>
+      </c>
+      <c r="B4918" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10825.psd</t>
+        </is>
+      </c>
+      <c r="C4918" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1GWTJpRGFERWRXT081ZTRTK25UalE9PSIsInZhbHVlIjoicVRmZkVIN1RGQ20wdHNyYlJrQU56Zz09IiwibWFjIjoiNzgyMzlkNDI1OTExZjZjNWYyNzZmMTA4NmYyNmJkN2ZkNGJkM2QxOGY4OTM0NWEyZGMxN2U2MWNlZmMxNGI1ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4919">
+      <c r="A4919" t="inlineStr">
+        <is>
+          <t>2276.psd</t>
+        </is>
+      </c>
+      <c r="B4919" t="inlineStr">
+        <is>
+          <t>tamilpsd-10826.psd</t>
+        </is>
+      </c>
+      <c r="C4919" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InJIdWlteHQ5YnlpZElaRWJUVnVNdlE9PSIsInZhbHVlIjoiUDEwb01hVGk2NTZxU0R0aVBvUlV1dz09IiwibWFjIjoiODBmNGVmZDY5YjA1MWIyYjI0ZDU2MGE1MmZlNjY1MWMyMmI1ZDJlNWQ4YWRlNzQ5ZGQ4MzU1Y2YwZjE1YmJiOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4920">
+      <c r="A4920" s="3" t="inlineStr">
+        <is>
+          <t>2275.psd</t>
+        </is>
+      </c>
+      <c r="B4920" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10827.psd</t>
+        </is>
+      </c>
+      <c r="C4920" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndDemdvb3BjR0dYVkUxaFk5SUVIVWc9PSIsInZhbHVlIjoiSTJyWC9sbXZ6S1lFSFdEREZ5eVZRQT09IiwibWFjIjoiNWM1YjcxOGMwMmEyODE5ODE1MWVjYzQxOWU1ZWM1MTcwMDY4MGU2N2RkNmJjYWMxMzJkNDQzNTgxYjk1OTg3YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4921">
+      <c r="A4921" t="inlineStr">
+        <is>
+          <t>2274.psd</t>
+        </is>
+      </c>
+      <c r="B4921" t="inlineStr">
+        <is>
+          <t>tamilpsd-10828.psd</t>
+        </is>
+      </c>
+      <c r="C4921" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhNVlljaEdITTlSU2JkMW16dEZQdXc9PSIsInZhbHVlIjoiQUxUOVBDK2w4NlE4bnV4dzJhSmxKQT09IiwibWFjIjoiZjI4NTdiZmIyNTQyMDBjZWRkZjE5MTk1ZDRmZmVhZmI2MTk2MzQxMDc4NzMxZjJhNmY2MTMwNWU5N2Q5ZmRlMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4922">
+      <c r="A4922" s="3" t="inlineStr">
+        <is>
+          <t>2273.psd</t>
+        </is>
+      </c>
+      <c r="B4922" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10829.psd</t>
+        </is>
+      </c>
+      <c r="C4922" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpoellidS9SWUhXSm5nWFcwQzhzYXc9PSIsInZhbHVlIjoiMXJoK1E0Rkc5dC9HS3kzQzUxU2RoQT09IiwibWFjIjoiNmQwYjRkMDE5ODRmNTE4ZmQ5MWExMTZkMzNkYjE4OTdiOGZjMDA0MDQ1NTliNDBlYzExOWZlYzQ1MDJkOTViYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4923">
+      <c r="A4923" t="inlineStr">
+        <is>
+          <t>2272.psd</t>
+        </is>
+      </c>
+      <c r="B4923" t="inlineStr">
+        <is>
+          <t>tamilpsd-10830.psd</t>
+        </is>
+      </c>
+      <c r="C4923" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjE4VkRXRnVjdDBHampLbkIyV1BrTlE9PSIsInZhbHVlIjoiTi9NdGFMeFp2VWdrY3JDY0kvL1pDQT09IiwibWFjIjoiMjJmYWJhNjc3NjU4MGVkNDA1YjdhY2U0NDJiZDc2YTQ2Mjk4MDJiMzZjZWYzNmE1ZDVjNTMyN2M3NWFlODI4NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4924">
+      <c r="A4924" s="3" t="inlineStr">
+        <is>
+          <t>2271.psd</t>
+        </is>
+      </c>
+      <c r="B4924" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10831.psd</t>
+        </is>
+      </c>
+      <c r="C4924" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNvTWFab09UK25HMlg1cnNTOVVKS0E9PSIsInZhbHVlIjoiK3A5SHBiK0cva1AwRitQZ1ppOVgrUT09IiwibWFjIjoiNjcyMTliNmE4MzM0NDQzNDZkMDkwMjRhNjZlMjVjYzRjNTMxMWEwZWFhZjM1NjgzZmNkMGJhMjdjMWJiYmRmZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4925">
+      <c r="A4925" t="inlineStr">
+        <is>
+          <t>2270.psd</t>
+        </is>
+      </c>
+      <c r="B4925" t="inlineStr">
+        <is>
+          <t>tamilpsd-10832.psd</t>
+        </is>
+      </c>
+      <c r="C4925" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtLL3JGVVZIclhGZG1mY2d2SWJQZmc9PSIsInZhbHVlIjoiZlk2WDFHa1c5SzRlQ1N2QTJuUy9JQT09IiwibWFjIjoiZjQ5MzQwZDY5N2U1MjVhZTQyZmE0ZmI4Nzc4YjljZjVhODdlNWZmY2FhMjcyZjdiZWRjOGJjMzBkNmQ2MTIxMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4926">
+      <c r="A4926" s="3" t="inlineStr">
+        <is>
+          <t>2269.psd</t>
+        </is>
+      </c>
+      <c r="B4926" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10833.psd</t>
+        </is>
+      </c>
+      <c r="C4926" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJuWnRTTHFzTldmSjZ0REpkYnVvSVE9PSIsInZhbHVlIjoiNVNLVStBVGw5VDZMRkdjdkR3bDBXUT09IiwibWFjIjoiOTk5ZDI4NTJhNzQ4NTRjYjlkMjQ0M2JiODdhNWEyMTVjZWYzYTY3MGE1NTFhOTQzZDM5ZDUwYmRhZWRjMTgyMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4927">
+      <c r="A4927" t="inlineStr">
+        <is>
+          <t>2268.psd</t>
+        </is>
+      </c>
+      <c r="B4927" t="inlineStr">
+        <is>
+          <t>tamilpsd-10834.psd</t>
+        </is>
+      </c>
+      <c r="C4927" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iks0VHlhT2pOaCtyYVM5QXg0R2FubGc9PSIsInZhbHVlIjoiMXBUa2REVGZneGovVWcwcGhZSUc4QT09IiwibWFjIjoiYjVhNjFmYjVhZmY4ZjYyNWMzY2M0YzliY2U1NGQ0NTEzMDQzY2ZhYzgxZDQ1NGYwOGRjZTU0YWJhZmYwZDJmOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4928">
+      <c r="A4928" s="3" t="inlineStr">
+        <is>
+          <t>2267.psd</t>
+        </is>
+      </c>
+      <c r="B4928" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10835.psd</t>
+        </is>
+      </c>
+      <c r="C4928" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRkK0x3RTVJS0VNc3J2VTgrdHp5dFE9PSIsInZhbHVlIjoiVlNnZkEyRHlBc1p6eG0wZnlZeHgxZz09IiwibWFjIjoiMjQwOGRlMzUxNmZlMmY4YmI4NWMxNTFkNmI5YzIwNTQ3MzJlOWRiMTJlNDhiYzc2ODQ0ZTYxNTNjMjVmOWNjNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4929">
+      <c r="A4929" t="inlineStr">
+        <is>
+          <t>2266.psd</t>
+        </is>
+      </c>
+      <c r="B4929" t="inlineStr">
+        <is>
+          <t>tamilpsd-10836.psd</t>
+        </is>
+      </c>
+      <c r="C4929" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlF6MnVXUUNwSC8yemxFWmZ2M01qZXc9PSIsInZhbHVlIjoidkhBcTdmaEFoeDlYU2V0UGJVT2Mrdz09IiwibWFjIjoiYzkxMzMwOTJhNjA4YmJkZmQ5MTViZDhlYmMwZDg1ZDE0NDQzNTczMTZjYjE0YTFlYWE1YmQzNDUyNDM2ODliOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4930">
+      <c r="A4930" s="3" t="inlineStr">
+        <is>
+          <t>2265.psd</t>
+        </is>
+      </c>
+      <c r="B4930" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10837.psd</t>
+        </is>
+      </c>
+      <c r="C4930" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImF4bGFPSi9SZXF0bzh4ejhUVzY1VWc9PSIsInZhbHVlIjoiRndoUXhKNmNhMDVmUSswSDZhdkM2QT09IiwibWFjIjoiODU1ZGU5MzVhYjVjNzcxMDQ5MzJlMmUyNTg5MDI1MzE5ZWQ0OTRlNzFiNjcwZGQzMzdjN2NhODgwNWY3NGVlMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4931">
+      <c r="A4931" t="inlineStr">
+        <is>
+          <t>2264.psd</t>
+        </is>
+      </c>
+      <c r="B4931" t="inlineStr">
+        <is>
+          <t>tamilpsd-10838.psd</t>
+        </is>
+      </c>
+      <c r="C4931" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVPc3ZyUXFDV0FBbk5hQ01RNWNTVUE9PSIsInZhbHVlIjoiZ2kxWGFQWkJWVVNyN2p3eTZoWXFFZz09IiwibWFjIjoiZmEyNjk1MjA0MzQ2OWFjMTQyNTE0YTUzNDc2OTE4MjA0YmQzNDRkMWY2Yjc4Njk1NWViMDllYmJiZmE2NTI3ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4932">
+      <c r="A4932" s="3" t="inlineStr">
+        <is>
+          <t>2263.psd</t>
+        </is>
+      </c>
+      <c r="B4932" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10839.psd</t>
+        </is>
+      </c>
+      <c r="C4932" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJ2ajI2RUJCNVJXbnV6MFBNQ0hXeGc9PSIsInZhbHVlIjoiOXRyRXA1TXl3dUxMVE1iRUpvS3B4Zz09IiwibWFjIjoiMjZhZjUzZWFiNTI2M2EyOTI5Y2Y2ZTJmNzFiNjQzMTBjNzkzZDY3ODUwNDJmMzcxNzlkZTM1YjE0MGY2MGEyYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4933">
+      <c r="A4933" t="inlineStr">
+        <is>
+          <t>2262.psd</t>
+        </is>
+      </c>
+      <c r="B4933" t="inlineStr">
+        <is>
+          <t>tamilpsd-10840.psd</t>
+        </is>
+      </c>
+      <c r="C4933" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFVdjdUWTFNVnJwR0YxMmdiS29kSFE9PSIsInZhbHVlIjoicVIwUlRvSnhBaktjZ2U0d1IrbXplQT09IiwibWFjIjoiOWViNzRhNzk2NWUwNDM4YWFkOGZkYTIyMDRiYTI0NGZiMmMyMGJkYWMwMjMzYjRmZDM2NjgzYzliODQyODhjMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4934">
+      <c r="A4934" s="3" t="inlineStr">
+        <is>
+          <t>2261.psd</t>
+        </is>
+      </c>
+      <c r="B4934" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10841.psd</t>
+        </is>
+      </c>
+      <c r="C4934" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlU0NVZYTGRkVE1qMU1BZVVXY2RrQnc9PSIsInZhbHVlIjoibWFjTUVKaEdXVEt0cGVXcWQyQkNKUT09IiwibWFjIjoiZjQ5MDUxZTBiNGFkYjVlNmQ1MzU2YzM1N2ZmNDc0YzlmNDAyMjVmNzA5MWU5MzkwYzIxYmZlYmU4MWQ3ZGFlNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4935">
+      <c r="A4935" t="inlineStr">
+        <is>
+          <t>2260.psd</t>
+        </is>
+      </c>
+      <c r="B4935" t="inlineStr">
+        <is>
+          <t>tamilpsd-10842.psd</t>
+        </is>
+      </c>
+      <c r="C4935" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlaeEtHYllqditSWTloMFZXRWlSZ2c9PSIsInZhbHVlIjoieW1abVA3T0RrZ3ZaM3E5ZEdmNDA1Zz09IiwibWFjIjoiOTlmM2E5ZTBiNjFmZjM3ZmUxODM4ZjNmYmMxNGFhMzZkMDhjNzQyMmNiOTY0ODU5M2M5NGM5ODQyMDU2YTNiOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4936">
+      <c r="A4936" s="3" t="inlineStr">
+        <is>
+          <t>2259.psd</t>
+        </is>
+      </c>
+      <c r="B4936" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10843.psd</t>
+        </is>
+      </c>
+      <c r="C4936" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikp6RnNxejFtc1NGWkVvazZYQy9YU3c9PSIsInZhbHVlIjoibDVGdzlXR1YwSE5yUkVvL1dhbG5CZz09IiwibWFjIjoiYTVmOGMyOTQxNjY3ZjY2NmJjMmQ1MjQwYWMzN2M3YmNhZGE2ZGQ2NjBmZjdjMTJmNjUyMTQ1M2NkYzBhNzM3ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4937">
+      <c r="A4937" t="inlineStr">
+        <is>
+          <t>2258.psd</t>
+        </is>
+      </c>
+      <c r="B4937" t="inlineStr">
+        <is>
+          <t>tamilpsd-10844.psd</t>
+        </is>
+      </c>
+      <c r="C4937" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxoWjl2b3pZWldzU1FYUS8zTmFYSlE9PSIsInZhbHVlIjoiSnl3R2Q2a3NZd2JoUElVdlYvSWQ3dz09IiwibWFjIjoiNmQ4NTUyNTU3MjRmYWZjOTViYmI4ZTI1YjU4ODM4MzM4ZjA5ZTllZTljNDYwOGIwMTFiNGQ4ZWJhZTNiYWRkZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4938">
+      <c r="A4938" s="3" t="inlineStr">
+        <is>
+          <t>2257.psd</t>
+        </is>
+      </c>
+      <c r="B4938" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10845.psd</t>
+        </is>
+      </c>
+      <c r="C4938" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik51NWtwSlRDRHNvamRFdXRLWXZ3SGc9PSIsInZhbHVlIjoicE1FdHNWS3V5dTVEdS9COGhVdHJvZz09IiwibWFjIjoiNTI2MTZkMjU3NDE3ZjkyMWE3ZjYwMjhlNmNkMzJlMjNmMmZjZDdhMzQ2ZTgwMWEzYzQ2OGVhMDJhMTllZDQ1ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4939">
+      <c r="A4939" t="inlineStr">
+        <is>
+          <t>2256.psd</t>
+        </is>
+      </c>
+      <c r="B4939" t="inlineStr">
+        <is>
+          <t>tamilpsd-10846.psd</t>
+        </is>
+      </c>
+      <c r="C4939" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1DSmJKamFEakpjWVlQbVFvMDlHMVE9PSIsInZhbHVlIjoiYVBydnkzK0JNTlpLb0paN0p2SjkyQT09IiwibWFjIjoiNGQ4NjEwZTAzYTliOGI3NWU2OGU3M2RiNTY0NTEwMmMxNjZjNjljZjY5MzRhNGQ0Mzc0YzYxNjk1OTBkZDJjZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4940">
+      <c r="A4940" s="3" t="inlineStr">
+        <is>
+          <t>2255.psd</t>
+        </is>
+      </c>
+      <c r="B4940" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10847.psd</t>
+        </is>
+      </c>
+      <c r="C4940" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZPQ2xBcWZaOXE0ZUVlMGI4Rks3ZUE9PSIsInZhbHVlIjoic0JkVVZwdXh6N0ZtNVh2VUhjNXNJQT09IiwibWFjIjoiZWVhMWM5MmZiY2ZhMWVmOGEyOTYzMmEyZmQ2ZjliZGFhNGNjYWZmZDRiYmEwYzU5NGJjNTI3Y2E1MWU0ZDVjNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4941">
+      <c r="A4941" t="inlineStr">
+        <is>
+          <t>2254.psd</t>
+        </is>
+      </c>
+      <c r="B4941" t="inlineStr">
+        <is>
+          <t>tamilpsd-10848.psd</t>
+        </is>
+      </c>
+      <c r="C4941" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iml4VHNZOGhIdUhrQnZkSXhPU3M1MVE9PSIsInZhbHVlIjoiYlNVTXN6WVZ2Z0c1bkhlUWVMV0dPdz09IiwibWFjIjoiZTIwMThkMThlMTY0ODhhOTU0MGU3YWNmN2U0NDhiN2Y5YzZlYmRjZTQzNDUwMmVhNTM1MGU0OWU5YTg5NWExYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4942">
+      <c r="A4942" s="3" t="inlineStr">
+        <is>
+          <t>2252.psd</t>
+        </is>
+      </c>
+      <c r="B4942" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10849.psd</t>
+        </is>
+      </c>
+      <c r="C4942" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IldpbmtuQm9nRHQ2aEo2NlBCeXBnRmc9PSIsInZhbHVlIjoiVXA0L1d5ejRwU3RkWlpPa0IrWS9OUT09IiwibWFjIjoiMTE0ZGRlNzYyMWY2MmQ4OGVjY2QwMzJlOTBiN2ZjMTc1YjcyMGE3ZTc2MzdhYTFlY2NkZTQ4NTZjYzUwYjAwOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4943">
+      <c r="A4943" t="inlineStr">
+        <is>
+          <t>2251.psd</t>
+        </is>
+      </c>
+      <c r="B4943" t="inlineStr">
+        <is>
+          <t>tamilpsd-10850.psd</t>
+        </is>
+      </c>
+      <c r="C4943" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFxTGRKT0ZjMGlBdm9CTUd5QmE5OXc9PSIsInZhbHVlIjoiM3JsRkk2c1VBK0pHSWpoaXF3TXNLZz09IiwibWFjIjoiYjI1ZWM0MTdiNDIyYWEzZjQyYjlmMWYwNzZlNDY5YjViYzA0YTJkNjYzZGVlMGI3ZWNjNDMxZWFlMzY4ZjNkNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4944">
+      <c r="A4944" s="3" t="inlineStr">
+        <is>
+          <t>2250.psd</t>
+        </is>
+      </c>
+      <c r="B4944" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10851.psd</t>
+        </is>
+      </c>
+      <c r="C4944" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InBySDEvbnZPV21idEFZbXJRRVdXblE9PSIsInZhbHVlIjoiWWlLUVhQMEpmT0syWmU0MEwvWllHZz09IiwibWFjIjoiYWYyYjczNjczZDI5MTc3MGU5Nzk4MTk0Mjc3YjA5M2NmYmU3NzA1MGQ4MTE5Njc1YTZlYjJhYWQ3MDY2NDBlYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4945">
+      <c r="A4945" t="inlineStr">
+        <is>
+          <t>2249.psd</t>
+        </is>
+      </c>
+      <c r="B4945" t="inlineStr">
+        <is>
+          <t>tamilpsd-10852.psd</t>
+        </is>
+      </c>
+      <c r="C4945" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImExK1Z5TzEzRnRiVzFobEdtZ21xZHc9PSIsInZhbHVlIjoiNUZROTJ3WHduZ0JIS1c5YU0xNWxtZz09IiwibWFjIjoiYzIwOTg0NWI0YjY3YTc5YTY1MDI1YjFmNjkwMTA0ODk1ZDU2YzZmZmI1ODViZmU5NjI3ODYyZWYwNWY1Y2MwZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4946">
+      <c r="A4946" s="3" t="inlineStr">
+        <is>
+          <t>2248.psd</t>
+        </is>
+      </c>
+      <c r="B4946" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10853.psd</t>
+        </is>
+      </c>
+      <c r="C4946" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9uTlgwLzY5SzZ4WUQzUUdjZ0tlbVE9PSIsInZhbHVlIjoiMVpmWEx1OTY1QkZwTkZWa28xMVZuUT09IiwibWFjIjoiY2MyMjkxNmY2ZjhhYjZjZGNlMzVlOTMyMDExNWEwNDAyNWY0ODJjMzYzODg2MjY2NGVjMzJmZDJmNWJjODgwOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4947">
+      <c r="A4947" t="inlineStr">
+        <is>
+          <t>2247.psd</t>
+        </is>
+      </c>
+      <c r="B4947" t="inlineStr">
+        <is>
+          <t>tamilpsd-10854.psd</t>
+        </is>
+      </c>
+      <c r="C4947" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBlUTI1TFNCakJ0YjZtRzYvdXY2cXc9PSIsInZhbHVlIjoiLytVc1ZjRGVGdXBMQ2FtVjV6ajBJdz09IiwibWFjIjoiZjcyNDg1MDQ4NjhiZjdiMWUxZGY0NWQ5NzcxZDY0MDdlOTRjNjdjMmRiMWZlNDJmOTU5ZWU1YWY1ZjRjNzNjOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4948">
+      <c r="A4948" s="3" t="inlineStr">
+        <is>
+          <t>2246.psd</t>
+        </is>
+      </c>
+      <c r="B4948" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10855.psd</t>
+        </is>
+      </c>
+      <c r="C4948" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhZWGVaQ0RsTmJXYllubGpERlVEZWc9PSIsInZhbHVlIjoiTFRCZnVqeGplbDNIMks3NVl6MVFoZz09IiwibWFjIjoiMWMyZmU4YzgwZjY2NWNkOWUzNzI1Njc0OTlhOTY5OWM3YzhhNDVmMmMzYTQwYjlkNDIxZGUzNzkwODFmNjM5NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4949">
+      <c r="A4949" t="inlineStr">
+        <is>
+          <t>2245.psd</t>
+        </is>
+      </c>
+      <c r="B4949" t="inlineStr">
+        <is>
+          <t>tamilpsd-10856.psd</t>
+        </is>
+      </c>
+      <c r="C4949" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkhpbU9SN1JWNzdjd0NnUUd1ZEY2bmc9PSIsInZhbHVlIjoiNjNQbUo5OEo5OU1OYzBIZC9JUm5ZUT09IiwibWFjIjoiZTMwNzVmYTk4ZDQ2NWZkNTY4Zjc0ZTRmYjRjNTRjNTI3ZTUxYzgwZmZkNzY3Mjg3MTRmZGE3YjljYzY5MDBmYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4950">
+      <c r="A4950" s="3" t="inlineStr">
+        <is>
+          <t>2244.psd</t>
+        </is>
+      </c>
+      <c r="B4950" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10857.psd</t>
+        </is>
+      </c>
+      <c r="C4950" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklkYnE1ZStYUDM1TnZHdGlYQjV5NGc9PSIsInZhbHVlIjoiblpHUTZjT2FPZVVaT0lSWSszZ2U5UT09IiwibWFjIjoiZDJjYTljNGVmNTk3OGI2ZGFmNWQ0ZTdhOTRjYTkzNzQ4NjFkYzYwMDg2ZDAxNmU1ZTA2MGVmY2M1Y2U1OWRkMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4951">
+      <c r="A4951" t="inlineStr">
+        <is>
+          <t>2243.psd</t>
+        </is>
+      </c>
+      <c r="B4951" t="inlineStr">
+        <is>
+          <t>tamilpsd-10858.psd</t>
+        </is>
+      </c>
+      <c r="C4951" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZ2UEdFZ3dRSExpSXJBbjJwRDBycEE9PSIsInZhbHVlIjoiY0xSRmc4R1BPTXpUOGIwYng3ZWhEUT09IiwibWFjIjoiMzBkYjdhMzQxYjNhZGVhMzkxZWY3YjU5YzA0MzcwY2I2MmI5MWVmM2NmOTVjNzFjMGE2MzI5NGI0Y2MwODQ2NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4952">
+      <c r="A4952" s="3" t="inlineStr">
+        <is>
+          <t>2241.psd</t>
+        </is>
+      </c>
+      <c r="B4952" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10859.psd</t>
+        </is>
+      </c>
+      <c r="C4952" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZnVFNMc1JRd242akZ4ZE1RTkRnOEE9PSIsInZhbHVlIjoiZ25iWkVlc09taHFvR3MvYndiWEpyUT09IiwibWFjIjoiOTMxNzM0NDQyYmQ2ZWYxYTljMjM4MjgxZTRjNWQ3MjEwZDUzODNmNGU2MzYxMjNkZDUyMDQyOGU3NGU3NjY3MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4953">
+      <c r="A4953" t="inlineStr">
+        <is>
+          <t>2240.psd</t>
+        </is>
+      </c>
+      <c r="B4953" t="inlineStr">
+        <is>
+          <t>tamilpsd-10860.psd</t>
+        </is>
+      </c>
+      <c r="C4953" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlodXVpRUhadkxkTExPUDdOWkxnaHc9PSIsInZhbHVlIjoiQkN5Q2MrekdWOWZrMEdkaG9rTFZjUT09IiwibWFjIjoiY2JkMmM4ODFjMTdmOGEwYjk4MWU1ZDJlNjYzNzU2NzlkMDgzNGFhNTcwY2M2MzcxNGY5ODBjZDJhMDAwMzljZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4954">
+      <c r="A4954" s="3" t="inlineStr">
+        <is>
+          <t>2239.psd</t>
+        </is>
+      </c>
+      <c r="B4954" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10861.psd</t>
+        </is>
+      </c>
+      <c r="C4954" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZYdVNLQlFmZ20rUXN2bWpjajRjRVE9PSIsInZhbHVlIjoiZmdITTdEVUExd0N2aEtueEtHTXhHUT09IiwibWFjIjoiMzI1YjRlMDk3YTk1NDMyZGI3ZGRmM2YzNjI0NGEyZTEzYTJiZTlkMTU5YTI2ODkwOWMyNmIzM2NkNThjN2Q4ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4955">
+      <c r="A4955" t="inlineStr">
+        <is>
+          <t>2238.psd</t>
+        </is>
+      </c>
+      <c r="B4955" t="inlineStr">
+        <is>
+          <t>tamilpsd-10862.psd</t>
+        </is>
+      </c>
+      <c r="C4955" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ims4MUp4SVhkekZzTUVqcnF2azltbmc9PSIsInZhbHVlIjoiVTVlU0UvYzBNbVZtb2dYUHlqUzVjZz09IiwibWFjIjoiM2FjNjY3MWVjOTAyNmQ0OTc3NzFhMTBhOTJjNGRkOGNhMmFiN2IwNDViN2I5OWU5MGViN2Q3MGMzM2Q3YTExNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4956">
+      <c r="A4956" s="3" t="inlineStr">
+        <is>
+          <t>2237.psd</t>
+        </is>
+      </c>
+      <c r="B4956" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10863.psd</t>
+        </is>
+      </c>
+      <c r="C4956" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikh5cnhTcXp4M1F5V2QwZU5zejFIOUE9PSIsInZhbHVlIjoiSUJNSDN3SGZRMEZtVzVBamNjMy8yZz09IiwibWFjIjoiYjI2OTNhZjkwMDliNzBmNGRmZGVjYTI0OTAxN2RkZDRiZmRjZTFhNDY2OWYyNzYzODUyNjE4N2I2YzNjYmRiNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4957">
+      <c r="A4957" t="inlineStr">
+        <is>
+          <t>2236.psd</t>
+        </is>
+      </c>
+      <c r="B4957" t="inlineStr">
+        <is>
+          <t>tamilpsd-10864.psd</t>
+        </is>
+      </c>
+      <c r="C4957" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhCVlBNQVRaVzVrcWp2UmxlWUhqVlE9PSIsInZhbHVlIjoiT09rN2QreGZ4UjdPQXg3SXR3dVF2Zz09IiwibWFjIjoiODI1ODI2NmIwNjVmNzQwMWFhZTg1OTNjNTIyNjRjMjU3YzRmNDcyM2M5ODAzODA5ZTFlZTVmYjdjM2E4NjljNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4958">
+      <c r="A4958" s="3" t="inlineStr">
+        <is>
+          <t>2235.psd</t>
+        </is>
+      </c>
+      <c r="B4958" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10865.psd</t>
+        </is>
+      </c>
+      <c r="C4958" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFSeGRKZ2hiODRiMVoxTFNFZ2hMQmc9PSIsInZhbHVlIjoiNU5wNWZYQjJneWwzV2JkcEdTVHlOUT09IiwibWFjIjoiMzllNjI3YTEyMzQ0ZTg2NGFmYTc4YzBhMzgwMDQzMjQ3OGI2YzVmOTg5MDRhNDMyZDJjNzRjNmUyMGFjNTBjNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4959">
+      <c r="A4959" t="inlineStr">
+        <is>
+          <t>2234.psd</t>
+        </is>
+      </c>
+      <c r="B4959" t="inlineStr">
+        <is>
+          <t>tamilpsd-10866.psd</t>
+        </is>
+      </c>
+      <c r="C4959" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBjYWozV05JdFJLZXpMS0hIN2VQVnc9PSIsInZhbHVlIjoiK2pHbk1oTEVUSTZuK0dZUTd0aGxSZz09IiwibWFjIjoiNjk5NzczNGUxOTllYmZlOGYzNmQ2OWI2ODJiYjkyOTg5M2FlNGMxZmQzZmVlYmY1MzFlYWY4ZGRmYjY4MTM4NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4960">
+      <c r="A4960" s="3" t="inlineStr">
+        <is>
+          <t>2233.psd</t>
+        </is>
+      </c>
+      <c r="B4960" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10867.psd</t>
+        </is>
+      </c>
+      <c r="C4960" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVOQ3pqOTBNbVlxZ01ZM2FBcTBNWVE9PSIsInZhbHVlIjoiajBWZjhKeTVCRHdGK0dHalFXeTFXdz09IiwibWFjIjoiMjNjMzQ4NDdjYmFmYzNhMmI4NjFlMDhkNTAxMzgzNmM5MzRjYWM5MzQxNGQ2NzBlZTE3Y2M1Y2JiNjRhMWQwZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4961">
+      <c r="A4961" t="inlineStr">
+        <is>
+          <t>2232.psd</t>
+        </is>
+      </c>
+      <c r="B4961" t="inlineStr">
+        <is>
+          <t>tamilpsd-10868.psd</t>
+        </is>
+      </c>
+      <c r="C4961" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkUzS2RFdk04N2pkRVFIK1cwN05TSmc9PSIsInZhbHVlIjoiek53U25RVU5qZmIzSzZ4cmhGajh1QT09IiwibWFjIjoiZGQ4ODk0NmU1YjMzM2QyOWE1MzBjNTJhYzBmOWMxODFjNmExYTk5Mjc4NDEyNTA3ZGIxMDI3YjllMzQ4NDY3NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4962">
+      <c r="A4962" s="3" t="inlineStr">
+        <is>
+          <t>2231.psd</t>
+        </is>
+      </c>
+      <c r="B4962" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10869.psd</t>
+        </is>
+      </c>
+      <c r="C4962" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBRbmFSZ0k1T1A4NmVaWU1HRkFPS2c9PSIsInZhbHVlIjoiQjk0OUVCcXBmYVcxMVM4MUt5eWdrdz09IiwibWFjIjoiOWRlMzVkYTRhYjQwZjQ0YzcxMDZjNWQ3Y2M0YjcyMzEzNmMyYTY1ZDc2MDgzOWQ5OGY5MWYwMzYxYjgwYWNiNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4963">
+      <c r="A4963" t="inlineStr">
+        <is>
+          <t>2230.psd</t>
+        </is>
+      </c>
+      <c r="B4963" t="inlineStr">
+        <is>
+          <t>tamilpsd-10870.psd</t>
+        </is>
+      </c>
+      <c r="C4963" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpxU2Q2MzFFZWNZQTFRZ214YmZVUEE9PSIsInZhbHVlIjoicnI1M2UyZ2FTSFVPT3RmRG5rSkljZz09IiwibWFjIjoiMTdlYTZiNDY5MTVhMWI2YTUzYzBlMTUyMjE4NWQ3Y2NlZjUxNzA5ZDk0NTRmNzJlMmY3MDc2YTU4MjA1YjVlNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4964">
+      <c r="A4964" s="3" t="inlineStr">
+        <is>
+          <t>2229.psd</t>
+        </is>
+      </c>
+      <c r="B4964" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10871.psd</t>
+        </is>
+      </c>
+      <c r="C4964" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikg0cmFCK21lVi90WmxBR2RuNTZEdXc9PSIsInZhbHVlIjoiTGJyanA0NUU0R3V2MmNyaHVtRHNhdz09IiwibWFjIjoiZjQ4MDY4NmUwYmNlZjQxYmE3YjY0MWI0NWZjYzQ4YTRhNjY4ODJhOWZhYzIzZTAyNjJlZDQyYjA1YTI4NGUxOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4965">
+      <c r="A4965" t="inlineStr">
+        <is>
+          <t>2228.psd</t>
+        </is>
+      </c>
+      <c r="B4965" t="inlineStr">
+        <is>
+          <t>tamilpsd-10872.psd</t>
+        </is>
+      </c>
+      <c r="C4965" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkY2U2J0b2k5bVJxL2hkZXhNV3d1Z1E9PSIsInZhbHVlIjoid2Rta09NYlI1bzZ5SG5KRXVaNFA2QT09IiwibWFjIjoiMjY5ODc1M2FjZDU4YzllYmNiMWIxMTY0Y2UzY2YxNzVlNjUzOWVmZWE2Y2JjMTE5ZjM5YTg5MzkxNjExYTVhMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4966">
+      <c r="A4966" s="3" t="inlineStr">
+        <is>
+          <t>2227.psd</t>
+        </is>
+      </c>
+      <c r="B4966" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10873.psd</t>
+        </is>
+      </c>
+      <c r="C4966" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijh3bXNITG40ZUJUM0t0YnEvVXFnMnc9PSIsInZhbHVlIjoiVVo3L01Rdks1MURtb09rekVndzAzUT09IiwibWFjIjoiNTEyZjQ0MzM1YzI4YjU1YTRmMmU0NTgxNmM1MzIyMzg0MWYyNmNiYThkOTY1MmViMzk0NmQwYTZkYTcyNjNkNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4967">
+      <c r="A4967" t="inlineStr">
+        <is>
+          <t>2226.psd</t>
+        </is>
+      </c>
+      <c r="B4967" t="inlineStr">
+        <is>
+          <t>tamilpsd-10874.psd</t>
+        </is>
+      </c>
+      <c r="C4967" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InBoaFJnd0hoL2V4cmVnRk5Xc2dYdEE9PSIsInZhbHVlIjoic09rcHR6YUtEeHU5M25nRW8xM1RQUT09IiwibWFjIjoiMjIwOGE3Y2M2ZGU4NDYwMTVkMWY2MWI0NTVmZTVmMjgxNTZiYTMzYWY3ZmY0N2JhYjM2MjlhYjFmMWZlMDQ5MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4968">
+      <c r="A4968" s="3" t="inlineStr">
+        <is>
+          <t>2225.psd</t>
+        </is>
+      </c>
+      <c r="B4968" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10875.psd</t>
+        </is>
+      </c>
+      <c r="C4968" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFqaEMybnQwTXdiak9uanhmNUR4VlE9PSIsInZhbHVlIjoiWktubXphd0FlWWQzaWlNMkhuMVpOQT09IiwibWFjIjoiM2ZjMzE2MjJiOTRlMjRiM2NjN2U4MDNiY2Q1NDBiOTQ3YjRlYzk3NTU0NWU0N2Y0Yzg1NDQ0ZGU5NjdhMzhiMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4969">
+      <c r="A4969" t="inlineStr">
+        <is>
+          <t>2224.psd</t>
+        </is>
+      </c>
+      <c r="B4969" t="inlineStr">
+        <is>
+          <t>tamilpsd-10876.psd</t>
+        </is>
+      </c>
+      <c r="C4969" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVjMGdxazd3WGZyeVloSXJMM3ZWTVE9PSIsInZhbHVlIjoiMWhHZkVxOSttRnZTbWErcDlwY0Y0QT09IiwibWFjIjoiZGY3YTIyNjA1YzA2NGEwMWFiYTg5NWJmODJmNGViZDVjODQzYWM0NDcxOGE4NzBkYjkyMzQ1OTBmNjY2N2EwNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4970">
+      <c r="A4970" s="3" t="inlineStr">
+        <is>
+          <t>2223.psd</t>
+        </is>
+      </c>
+      <c r="B4970" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10877.psd</t>
+        </is>
+      </c>
+      <c r="C4970" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhabVRVWVYvUldBandoeTc4UExrTEE9PSIsInZhbHVlIjoiVVQybktzSUJEZ0xWZlVvSnAyb2Z1QT09IiwibWFjIjoiZmU2OWUyYzZiMjkyMjE5NTQ2OTdkNWY2MzVlZTEwNDJkMjk0YWIwOWViZTUzNGE3NmYxNWY0ZmIyMTU4YzBkNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4971">
+      <c r="A4971" t="inlineStr">
+        <is>
+          <t>2222.psd</t>
+        </is>
+      </c>
+      <c r="B4971" t="inlineStr">
+        <is>
+          <t>tamilpsd-10878.psd</t>
+        </is>
+      </c>
+      <c r="C4971" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imhia0NwUTNSRG5mRzZpOWc3U0xhL1E9PSIsInZhbHVlIjoiMWxSUnNSd2h1RTBJY2hnV0ZPNG9PZz09IiwibWFjIjoiYzgwMjc2YmQyMDk2ZmFmMDM4YTRmYjM3NjViMTRhN2QzOTY3OTg5OGQzYWE5ZGEzZjY1NzRhMGY3MDQxM2ZmZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4972">
+      <c r="A4972" s="3" t="inlineStr">
+        <is>
+          <t>2221.psd</t>
+        </is>
+      </c>
+      <c r="B4972" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10879.psd</t>
+        </is>
+      </c>
+      <c r="C4972" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhyNURzdzc3RE9JZTlJNnNYVzVHRXc9PSIsInZhbHVlIjoiNTZYRVMwa3pQTHh4aDhSQnZCVHAwQT09IiwibWFjIjoiMmI4MTk0MWQ5MTM3NTFlMGNiMWU4OTZmMTVjOWJiM2U3MDRmY2UwNGY1ZjczM2JiNThjOWNmODM5ZTA5MTNiMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4973">
+      <c r="A4973" t="inlineStr">
+        <is>
+          <t>2220.psd</t>
+        </is>
+      </c>
+      <c r="B4973" t="inlineStr">
+        <is>
+          <t>tamilpsd-10880.psd</t>
+        </is>
+      </c>
+      <c r="C4973" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFvK0I0dHRXbk52akZlTkFoMlFKT2c9PSIsInZhbHVlIjoiaUZMVGwvRWtCUE9IZlV0blpJWWliQT09IiwibWFjIjoiYjQzMmNmYjNlZDRlZGUyNmE0MDNkM2RhODM3N2VmYmQzMDE0NGEzZGJjMTQ5MDgxYjY0MDMzZGMzNzRlMWUyNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4974">
+      <c r="A4974" s="3" t="inlineStr">
+        <is>
+          <t>2219.psd</t>
+        </is>
+      </c>
+      <c r="B4974" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10881.psd</t>
+        </is>
+      </c>
+      <c r="C4974" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdLS0ZuQXNlMTdZa29kUitIVUVRMVE9PSIsInZhbHVlIjoicFBNSm9kVlNUYkVLeW8weWhzYU1BQT09IiwibWFjIjoiNDBiNWIwYjI4MmYzNGYwNjQxM2QwZDQ3ODFkZGUxYWMwNTAxNmQ5ZjhjNjcxOTQyMDBkODkyOTg1MjQ0ZjJkNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4975">
+      <c r="A4975" t="inlineStr">
+        <is>
+          <t>2218.psd</t>
+        </is>
+      </c>
+      <c r="B4975" t="inlineStr">
+        <is>
+          <t>tamilpsd-10882.psd</t>
+        </is>
+      </c>
+      <c r="C4975" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Img4c2xqNXdieTRZUTFGOFJ6ZHltWUE9PSIsInZhbHVlIjoiL3I5SG5iVXJXeWZrL25IYlBjeFkvdz09IiwibWFjIjoiNzYyODA1NmI2NTNhMzRjNDgxZTU4ZWQxNDQ5ZWZjYjJhZGE4ZTc1NjA2ZWU2ZTk5ZGMzOTczNzM0MWY3ODc2NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4976">
+      <c r="A4976" s="3" t="inlineStr">
+        <is>
+          <t>2217.psd</t>
+        </is>
+      </c>
+      <c r="B4976" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10883.psd</t>
+        </is>
+      </c>
+      <c r="C4976" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik45YVdlMmtrczljK3VpWXZmc3hKSFE9PSIsInZhbHVlIjoiN2ZVNVNDRFROYW1UOWsyRzF0b2t5dz09IiwibWFjIjoiM2I3NDIzNWM1OTUxNjM3YTgwYWU1MzAzNTE2MzkxNDBiMjNkOWJkNWEzNzA4NzNmMTQwZmYzM2ZlYzY5M2EwZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4977">
+      <c r="A4977" t="inlineStr">
+        <is>
+          <t>2216.psd</t>
+        </is>
+      </c>
+      <c r="B4977" t="inlineStr">
+        <is>
+          <t>tamilpsd-10884.psd</t>
+        </is>
+      </c>
+      <c r="C4977" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImsvZURBS0I2YzlnQUpGUHpKRktDVmc9PSIsInZhbHVlIjoiUnpNRS9kS3BSSnpYaDRiaCtLTEJwdz09IiwibWFjIjoiZTI0MjRiMjBjYzhmMGRkYTgzMDc0Njk4NzM0NTgxZGYyMjgwMDk2NWEzOWNjMzIxNDAzNGEzYTg5ZjQ5N2IyNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4978">
+      <c r="A4978" s="3" t="inlineStr">
+        <is>
+          <t>2215.psd</t>
+        </is>
+      </c>
+      <c r="B4978" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10885.psd</t>
+        </is>
+      </c>
+      <c r="C4978" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Inpxc0QvVWp1QXBidUdpK0R6UEh1VkE9PSIsInZhbHVlIjoiQStiWFE4UlpVODBwWEpLd090OXJ4Zz09IiwibWFjIjoiYmVmYTRhZTQ2YWIwZTRlZWY1NTk4NGQ3OGQ5YmQ5YTZhNTg3NzYyNmRlMzdiMmUzNzY1NzJlMTEyY2UyMTQ1ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4979">
+      <c r="A4979" t="inlineStr">
+        <is>
+          <t>2214.psd</t>
+        </is>
+      </c>
+      <c r="B4979" t="inlineStr">
+        <is>
+          <t>tamilpsd-10886.psd</t>
+        </is>
+      </c>
+      <c r="C4979" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFqRnRieSt1YUxnc2hYY0R3SXBqN3c9PSIsInZhbHVlIjoieTVUSjFuMXFQdHV0Z05ETm54eE1pUT09IiwibWFjIjoiMmNhZDA1MmNjYTA3YTEwNzUzNTc5YzllMmQwM2FhNmE5YjE0ODRlMzhkNjY5MmI3NjllZjZlMDc3ODEwNzJiYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4980">
+      <c r="A4980" s="3" t="inlineStr">
+        <is>
+          <t>2213.psd</t>
+        </is>
+      </c>
+      <c r="B4980" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10887.psd</t>
+        </is>
+      </c>
+      <c r="C4980" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkN5MDNCdzY2eExmcWFEbkZkUURrVlE9PSIsInZhbHVlIjoiOUEzMXVKSEQzZ1FSMXUxdzN4cnkxdz09IiwibWFjIjoiMTNjYjFjYjcyZDAwNTZhNDdjNjk1MWYyOTE5NzZhZDI5OTEzZjU5YzI0NTllYThiNjg3YTY3MzA0M2U5NGRkNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4981">
+      <c r="A4981" t="inlineStr">
+        <is>
+          <t>2212.psd</t>
+        </is>
+      </c>
+      <c r="B4981" t="inlineStr">
+        <is>
+          <t>tamilpsd-10888.psd</t>
+        </is>
+      </c>
+      <c r="C4981" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZZc3kwR3llZXZadGdvS2E0SG9reUE9PSIsInZhbHVlIjoiN21ucUQ2UnY4MFVIS2JINFoxNmFydz09IiwibWFjIjoiM2JkN2Y5ODc0ZjkzNDFlYWUxZTFhNmQ2NzU2YzA0YzA2YzM3OWYyYjhjMjhiZTFjNWJmN2Q0NTI4MTlhNzcyMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4982">
+      <c r="A4982" s="3" t="inlineStr">
+        <is>
+          <t>2211.psd</t>
+        </is>
+      </c>
+      <c r="B4982" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10889.psd</t>
+        </is>
+      </c>
+      <c r="C4982" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJiWjF2R0psOWtLcnYzS0NQRGxuVGc9PSIsInZhbHVlIjoiM05ZL0xacEp1MkJLazFFcSs4NXJDUT09IiwibWFjIjoiOWRiZDEzNzVhNGE4MmZkYzg4OTZhY2U5OWEyNzI2NDU3MmEwODRjZTc5ZDllMTI2NzgyN2VjYzBiMjUwNDk5MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4983">
+      <c r="A4983" t="inlineStr">
+        <is>
+          <t>2210.psd</t>
+        </is>
+      </c>
+      <c r="B4983" t="inlineStr">
+        <is>
+          <t>tamilpsd-10890.psd</t>
+        </is>
+      </c>
+      <c r="C4983" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVBMFd0VlR1dFNvUDdkcGxTSzlhTGc9PSIsInZhbHVlIjoiZkhPZ1ZBUDVvcCtCL3ErTVljcFdiUT09IiwibWFjIjoiYTgwMzRiNTNmZWY1MDQ3MWNhNDhiNWJhYjE1YTIwMTkwYWQwMmQzMTYyMmQ1MzAwNDhkZjYwOTZhYjRiOGZjMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4984">
+      <c r="A4984" s="3" t="inlineStr">
+        <is>
+          <t>2209.psd</t>
+        </is>
+      </c>
+      <c r="B4984" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10891.psd</t>
+        </is>
+      </c>
+      <c r="C4984" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhQYnBzR3luMm9NM2RFQmh6amVLb2c9PSIsInZhbHVlIjoicWttd1R6WW52OGdIWHhnYktydDF3Zz09IiwibWFjIjoiMGY1MDI4ZmZlNGQ0YzA4ZGZlZDAwN2I2Y2E5YWE0ZjVlZDQwMjk2MGFiYmI0M2I5OWFlN2FkNWE0ZjJmZDhhOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4985">
+      <c r="A4985" t="inlineStr">
+        <is>
+          <t>2208.psd</t>
+        </is>
+      </c>
+      <c r="B4985" t="inlineStr">
+        <is>
+          <t>tamilpsd-10892.psd</t>
+        </is>
+      </c>
+      <c r="C4985" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZIUHRKZjV5YTRId3ltTkN4R0U4RFE9PSIsInZhbHVlIjoic0IvUlpWNnlxcGlwelZ0ZjY4MnI2dz09IiwibWFjIjoiMjlmNmFmYWI0YjgzYTA0NGVhN2MxMGVmYTkyZGQwMTZjYzEwMWMyYzMyZDlkMmExMTlkMTgzY2Q1Yjk4ZjQxMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4986">
+      <c r="A4986" s="3" t="inlineStr">
+        <is>
+          <t>2207.psd</t>
+        </is>
+      </c>
+      <c r="B4986" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10893.psd</t>
+        </is>
+      </c>
+      <c r="C4986" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkE5b3FqdzZrQm5vNHJWR0F3NjZpVkE9PSIsInZhbHVlIjoiM0xZMG9vRjZpV1EyRkpCSzhnTFcrZz09IiwibWFjIjoiYjA4YWY4Y2IwYWYxYzg4NzYyZTg3NTUwYjM5NzlmYjExZGI4Y2ZjZjIxMDI1YTUzNjUwZTliZGVlNjExOTY4NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4987">
+      <c r="A4987" t="inlineStr">
+        <is>
+          <t>2206.psd</t>
+        </is>
+      </c>
+      <c r="B4987" t="inlineStr">
+        <is>
+          <t>tamilpsd-10894.psd</t>
+        </is>
+      </c>
+      <c r="C4987" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjI1Tk1BUlk2ZWMzMTFLakpwTEFsdmc9PSIsInZhbHVlIjoib2UzODlwcUszcDJsUVFxVllRK2lQdz09IiwibWFjIjoiOWI1Y2E3M2ZkYWEzODQ0NGNhMGFiY2YzM2QxZDAyNjYxZGM3M2IzN2U1ODgwODRhN2JjZDZkMjk1N2NiMDQzYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4988">
+      <c r="A4988" s="3" t="inlineStr">
+        <is>
+          <t>2205.psd</t>
+        </is>
+      </c>
+      <c r="B4988" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10895.psd</t>
+        </is>
+      </c>
+      <c r="C4988" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhYeUdVelpxVEZYbGdEcEY3dnkxenc9PSIsInZhbHVlIjoiSEYwbTl3L1hmMWhOUWYwZktEU3Eydz09IiwibWFjIjoiMDQwMjk1ZmVlNWZiMTg1ZjBhZjRhMGI2ZTQ5NGMzOWQ4ZTc0YWI3YWNlNjE4NWExNDJiNzNjODg4NWVkZmVkOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4989">
+      <c r="A4989" t="inlineStr">
+        <is>
+          <t>2204.psd</t>
+        </is>
+      </c>
+      <c r="B4989" t="inlineStr">
+        <is>
+          <t>tamilpsd-10896.psd</t>
+        </is>
+      </c>
+      <c r="C4989" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVJcnZmTFc1N3IrcHVQdC9kRkU1Vnc9PSIsInZhbHVlIjoicCtvUXBhdG1TS3M1Z3V1SWMrOUVLdz09IiwibWFjIjoiZDhiMjVkMDIzZThmZjk2NWE4ZTQzZWY4OTAxODQ1ZTUzMDVmYTNmNGU5ODFiN2M4Y2MwZWI5YjIwMTcyODc5YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4990">
+      <c r="A4990" s="3" t="inlineStr">
+        <is>
+          <t>2203.psd</t>
+        </is>
+      </c>
+      <c r="B4990" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10897.psd</t>
+        </is>
+      </c>
+      <c r="C4990" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZwNTRwc0V0T1RGZ2hsR2J6T3FucFE9PSIsInZhbHVlIjoiNEU4K2pXakpFbXdacHR2c0ErdEdwZz09IiwibWFjIjoiMjYzNzdjZWZhNGRlODJlYTM2ZGVmOWUwNzFiZGY2ZWI4M2RmNWRjODRhMDU1YTUyYjgwMDczMTc5ZTcyNWFhNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4991">
+      <c r="A4991" t="inlineStr">
+        <is>
+          <t>2202.psd</t>
+        </is>
+      </c>
+      <c r="B4991" t="inlineStr">
+        <is>
+          <t>tamilpsd-10898.psd</t>
+        </is>
+      </c>
+      <c r="C4991" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkordnJSM0V6Ull3Sk1pWG5YQ2ZUMFE9PSIsInZhbHVlIjoiVWR6TDROY0xuYU5WYkcxZEFEajBudz09IiwibWFjIjoiMGJjMTkwM2EwMDZlN2EzZjJjNmE5NzkxNTMwOWY3YzA3MjMyNDM5NGEyYzRhM2U5ZWExYjUxNmY5NTk2M2M1ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4992">
+      <c r="A4992" s="3" t="inlineStr">
+        <is>
+          <t>2201.psd</t>
+        </is>
+      </c>
+      <c r="B4992" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10899.psd</t>
+        </is>
+      </c>
+      <c r="C4992" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlsSHdFRkM0enNNVS9UY3BPZm0raXc9PSIsInZhbHVlIjoidldWMTBFdXNUUk9kd2xSbmVqT0wzQT09IiwibWFjIjoiZDY1Mzc0ZDA0ZGExNjBjODYzMGVlNjQ2Y2Y5ZTY0ZjhjYTMwOTNlNDM3ZjA3N2E1NjVlNzZlODRkMTYzMGEzMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4993">
+      <c r="A4993" t="inlineStr">
+        <is>
+          <t>1914.psd</t>
+        </is>
+      </c>
+      <c r="B4993" t="inlineStr">
+        <is>
+          <t>tamilpsd-10900.psd</t>
+        </is>
+      </c>
+      <c r="C4993" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFiQWJBWFNwT0FNa1dLcXFhdi8zVmc9PSIsInZhbHVlIjoiOE5Jc0Q2ZzE3VHNub2w2amhmSkFHQT09IiwibWFjIjoiOGJhNjk2N2U0NGYyMjNlNDE1NzYwOTA0MzlhZTFlYjU0NmMxZmZiYWY5MjhhYWEwOTcxMzA4MjljYjFkM2MzNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4994">
+      <c r="A4994" s="3" t="inlineStr">
+        <is>
+          <t>1806.psd</t>
+        </is>
+      </c>
+      <c r="B4994" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10901.psd</t>
+        </is>
+      </c>
+      <c r="C4994" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBpblNyQlF6bGhlWUhTcUZkRDlEdGc9PSIsInZhbHVlIjoiMld0QzM5d1R3SUNXemZ4WTU1MllJZz09IiwibWFjIjoiN2RkZmQ1OGVmMzg2NjZhMjNjYjBiZGFjOWM0YWU2MTFhZjRiMTk3ZGE0ODA2MGJhMGUyZGI3ZmI4NDgzMDRmYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4995">
+      <c r="A4995" t="inlineStr">
+        <is>
+          <t>1759.psd</t>
+        </is>
+      </c>
+      <c r="B4995" t="inlineStr">
+        <is>
+          <t>tamilpsd-10902.psd</t>
+        </is>
+      </c>
+      <c r="C4995" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlvcHQzanJsYTNaS3crc0svb3JLR0E9PSIsInZhbHVlIjoiOHMxRVVITDh1ek5MZDZRQ3RiZVZaZz09IiwibWFjIjoiN2YyNzJmZTVlMTI3ZDJmNzU2ZWQyNmFmZDYyZGRiNWU5OGE5YmMyOTI1NWUwMGIyZjYwMGFlMjFmMWI1NGY0MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4996">
+      <c r="A4996" s="3" t="inlineStr">
+        <is>
+          <t>1609.psd</t>
+        </is>
+      </c>
+      <c r="B4996" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10903.psd</t>
+        </is>
+      </c>
+      <c r="C4996" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlLbXhiY2lmaVM4aDRCTXJXSmRDeVE9PSIsInZhbHVlIjoiZC9DWmV6VzNYQmNIeUlKYm5GYmlwUT09IiwibWFjIjoiNmFiODc0MjJjODBjN2RjYWVhZTI4ZjBlODBiNjI4Y2JhNTU0ZjUwMWIwMzIzZmVmMmFhYWEwYjE1NjlmNzY3OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4997">
+      <c r="A4997" t="inlineStr">
+        <is>
+          <t>1757.psd</t>
+        </is>
+      </c>
+      <c r="B4997" t="inlineStr">
+        <is>
+          <t>tamilpsd-10904.psd</t>
+        </is>
+      </c>
+      <c r="C4997" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJtYS9ZOXE3T0tyYThKYS9mMkU0VUE9PSIsInZhbHVlIjoidHFFZVZYcUNYQkhlQ3hoNGFKQnNjQT09IiwibWFjIjoiMTQzY2JmM2FkZTkwMDJiZDlmOTIxMGZkMDQ3M2RmZDBiMWI2ZWM0YmUzMGRmODc0M2I5YmRjZjE1MzcxMzc3MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4998">
+      <c r="A4998" s="3" t="inlineStr">
+        <is>
+          <t>1756.psd</t>
+        </is>
+      </c>
+      <c r="B4998" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10905.psd</t>
+        </is>
+      </c>
+      <c r="C4998" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllsRFlMOVhBRDNoYVVPbEhVcG5nMEE9PSIsInZhbHVlIjoib29lQ2t1SjA4ZFNlRms3NDAxUDk0UT09IiwibWFjIjoiNGY4MTA2YjdiZDY1OGY0ZjdiOGRlZDQ4YTZiMTA5MWExZGU5ZGM4MDMzNTdmODBmY2M5MzkwZTkzZWVjOThmYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4999">
+      <c r="A4999" t="inlineStr">
+        <is>
+          <t>1754.psd</t>
+        </is>
+      </c>
+      <c r="B4999" t="inlineStr">
+        <is>
+          <t>tamilpsd-10906.psd</t>
+        </is>
+      </c>
+      <c r="C4999" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdLc3lVUjYreHFZS2dRNC9NdUw3S3c9PSIsInZhbHVlIjoiYWhFSGpFNklXQks4aWsyQzl4KzVWUT09IiwibWFjIjoiZmRjODI5OTZmZDVhOGU5MTliODQ1MTFjYzI3MzFmOTg0NjFhMDAyMTM2MWM2MDcyZTMzOTk1MmMxYzlhYjhhMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5000">
+      <c r="A5000" s="3" t="inlineStr">
+        <is>
+          <t>1755.psd</t>
+        </is>
+      </c>
+      <c r="B5000" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10907.psd</t>
+        </is>
+      </c>
+      <c r="C5000" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkE3VEMvUEh6cytLU2ZwVnNSTGplRUE9PSIsInZhbHVlIjoiTFVGQkw3T2lyYnlnMzRvK1BXNUkvdz09IiwibWFjIjoiMTExNzM0ZGY2OWEzZGQ4NTNhMWJhNWI2ZTk3Nzc4MmJlNzllMTg0ZWU4ZjMzNWRlNjExOWUxMTMyOWQxMjYzMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5001">
+      <c r="A5001" t="inlineStr">
+        <is>
+          <t>1753.psd</t>
+        </is>
+      </c>
+      <c r="B5001" t="inlineStr">
+        <is>
+          <t>tamilpsd-10908.psd</t>
+        </is>
+      </c>
+      <c r="C5001" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1NYWpFSHVrcjMyWG9KWmp5Qno1UHc9PSIsInZhbHVlIjoiM1N3c1lrM1RQVTJQRERDK0ZudmlSZz09IiwibWFjIjoiNzJiM2UyZDIzOWM5ZjAzMTE5MTk5ODA0Y2ZkY2E1ZTA0YmM3NjRlMWRlZmQxMjdlNmEyZThiYThiNTYxMmY4ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5002">
+      <c r="A5002" s="3" t="inlineStr">
+        <is>
+          <t>1752.psd</t>
+        </is>
+      </c>
+      <c r="B5002" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10909.psd</t>
+        </is>
+      </c>
+      <c r="C5002" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5uaUZ0cUlzYkxvSU54dFUrbUt6ZGc9PSIsInZhbHVlIjoiTyt2dS9ZTFV5dDZCbFNRRkE1b3lRdz09IiwibWFjIjoiZDIyZWJhYTlmNjE3ZmRlOWFlYWNlNDlmYjk5YzRmYTUzMGVmMDIyODg3OTg1MGY2Yjg0MmUzNWFlYTE0OGQyYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5003">
+      <c r="A5003" t="inlineStr">
+        <is>
+          <t>1751.psd</t>
+        </is>
+      </c>
+      <c r="B5003" t="inlineStr">
+        <is>
+          <t>tamilpsd-10910.psd</t>
+        </is>
+      </c>
+      <c r="C5003" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJzbTBpaU9GVVk0ZGNNc0U2ZVdLWFE9PSIsInZhbHVlIjoiN0MyTjBZYnFXVEQyMmp0d0tFNW4wUT09IiwibWFjIjoiMTdkNzA1NzcxYTk1MjdkNDRiMzI0ODMyMDgxNjFhZGQzYjk2NmMzNjdjMTRmNmI5Zjc4Yjg1ODYyMGNkMjRkMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5004">
+      <c r="A5004" s="3" t="inlineStr">
+        <is>
+          <t>1749.psd</t>
+        </is>
+      </c>
+      <c r="B5004" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10911.psd</t>
+        </is>
+      </c>
+      <c r="C5004" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9nbXh2WXUxQ0hheTNkMWxyanVmK1E9PSIsInZhbHVlIjoiZkp2SlcxSGk1SysvUW8wdFpqK2ZiZz09IiwibWFjIjoiMWI0ZWNiNTRjMzM3Yjg1NTkzYWRhNTM5ZTk3NDg0ZWY0MDM1MTI3ZTgwZjZjNTlhNWRlYzk5MDYxOGZjNDllMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5005">
+      <c r="A5005" t="inlineStr">
+        <is>
+          <t>1750.psd</t>
+        </is>
+      </c>
+      <c r="B5005" t="inlineStr">
+        <is>
+          <t>tamilpsd-10912.psd</t>
+        </is>
+      </c>
+      <c r="C5005" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhaaFJmdFNSVWtPSXhkQ01MYllKb0E9PSIsInZhbHVlIjoiT2dCT2Fzbk14RUZoY0tBN2tnOTNHUT09IiwibWFjIjoiYTQwNGJmZWQ0NGEwYTgzMjJiZjk4ZDdmMGYwN2Q3YjNiYjkwY2U4NGUyYjkyMjZiNTA4YTFiODU3MzEwMzRmOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5006">
+      <c r="A5006" s="3" t="inlineStr">
+        <is>
+          <t>1608.psd</t>
+        </is>
+      </c>
+      <c r="B5006" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10913.psd</t>
+        </is>
+      </c>
+      <c r="C5006" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im44djYvdmt4RkFybXJXQ2U2MjVnRnc9PSIsInZhbHVlIjoiQnR6cHBVWTlxUkEwbnJ0dnc1SkVDdz09IiwibWFjIjoiYmYwMjUzNzBkZDEwY2EwY2FkMWZkNmY4ZmEwY2RlOWYwYzgwZjAzYTIzOTllMWI5OTE0N2RhZjlhZWMwMjgwMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5007">
+      <c r="A5007" t="inlineStr">
+        <is>
+          <t>1748.psd</t>
+        </is>
+      </c>
+      <c r="B5007" t="inlineStr">
+        <is>
+          <t>tamilpsd-10914.psd</t>
+        </is>
+      </c>
+      <c r="C5007" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilg1VjlrVFlGbmQ1alh2Rk51YzlxZGc9PSIsInZhbHVlIjoiR2ZCcGJEd0hhaHRIeWczTGYvV2NDZz09IiwibWFjIjoiZjVmYWJlNzVlYTRkMDJjMWE4OGUxNjljNWZmNjgwOGZhMTMxZTQ3Mjk2MTU4NDNiYzA0ZWI0OTJhODZjODdmNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5008">
+      <c r="A5008" s="3" t="inlineStr">
+        <is>
+          <t>1747.psd</t>
+        </is>
+      </c>
+      <c r="B5008" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10915.psd</t>
+        </is>
+      </c>
+      <c r="C5008" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxxWTdQS3IxTXprU2NXakMwbUIwMWc9PSIsInZhbHVlIjoiaHk4L2M4VUpTa3N6OHdlRjRYbXA4Zz09IiwibWFjIjoiMzI1ZjU1YWE2ZTJmM2JkYzZmN2VkMGJjMmVmYzMyMTI0NjY1NTc1MzA5YTlmZjVlNTY2ZmIwZTRlNWJiY2NmNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5009">
+      <c r="A5009" t="inlineStr">
+        <is>
+          <t>1745.psd</t>
+        </is>
+      </c>
+      <c r="B5009" t="inlineStr">
+        <is>
+          <t>tamilpsd-10916.psd</t>
+        </is>
+      </c>
+      <c r="C5009" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ino3akc3TmVqR0pRYSsxU2IzbzFvRlE9PSIsInZhbHVlIjoiRzhiKzJoV0lvQy85VlEyd1R2NGVtUT09IiwibWFjIjoiNWVlYjhiOWZmYzliNzM1OGI5MDE4ZmY1Mzg3ZWI5NTc3MzUzZTAxZWM1YzIxMTFmODVlYWIwNzQxZjAzMWQ5ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5010">
+      <c r="A5010" s="3" t="inlineStr">
+        <is>
+          <t>1746.psd</t>
+        </is>
+      </c>
+      <c r="B5010" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10917.psd</t>
+        </is>
+      </c>
+      <c r="C5010" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNrNWEra29lZURqZ2dpQXB0TWpmS2c9PSIsInZhbHVlIjoiWDkwQ2lkYWM4aWorQlRNSXF1ZVVuZz09IiwibWFjIjoiOGZmYzgyZjViNGY0OGUzNWFjZWVjNzM3YTM2ODJiZDYyNzE3Njc1YjJjNjlkZjVhMzAyMWNiZmRiYjYwZjAzZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5011">
+      <c r="A5011" t="inlineStr">
+        <is>
+          <t>1744.psd</t>
+        </is>
+      </c>
+      <c r="B5011" t="inlineStr">
+        <is>
+          <t>tamilpsd-10918.psd</t>
+        </is>
+      </c>
+      <c r="C5011" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImE3Vk55cjFVZHpJVEx5UXRaY3UzV3c9PSIsInZhbHVlIjoiMndnUWVkV1Y1TDJVbFBxenZzRGVaUT09IiwibWFjIjoiMTQ4ZDM2YjEyZjU1YWU4MDk4ZGUxNmVhOGQ5M2NkMWM2ZTI1YmRjN2NlYzAwZDU3ZDI4OWM0MWM5N2RiZTExMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5012">
+      <c r="A5012" s="3" t="inlineStr">
+        <is>
+          <t>1607.psd</t>
+        </is>
+      </c>
+      <c r="B5012" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10919.psd</t>
+        </is>
+      </c>
+      <c r="C5012" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVJTWNIRHBQQjJ5R1UxdEk3Ykw5WkE9PSIsInZhbHVlIjoiWFRWRXd6Q1YxK3dBeVZleGpGL2dpUT09IiwibWFjIjoiNDFhMTkzMDljOTBhYzE4ZjUyMjliZDJlOGM1YzRjMmVhZWRjNDg3ZGNmNGYxZmY4NzJhOTk3Y2EyNjE2MDhlZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5013">
+      <c r="A5013" t="inlineStr">
+        <is>
+          <t>1742.psd</t>
+        </is>
+      </c>
+      <c r="B5013" t="inlineStr">
+        <is>
+          <t>tamilpsd-10920.psd</t>
+        </is>
+      </c>
+      <c r="C5013" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJSU05pTWp2UWtRTDVjSTRWQ3Bsc0E9PSIsInZhbHVlIjoidm1IVHJmQ3FTbmNoWmtCZGxyaHBvQT09IiwibWFjIjoiY2RjMDE4ZDVmMDNhZGQyNGJmZDhlMjE1NzcyMGMzNjQzZDEyNjI3MjMzMWZlN2MyMGNjYmUxNTQ0OWQ1OWIxZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5014">
+      <c r="A5014" s="3" t="inlineStr">
+        <is>
+          <t>1743.psd</t>
+        </is>
+      </c>
+      <c r="B5014" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10921.psd</t>
+        </is>
+      </c>
+      <c r="C5014" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBiWnhhdXlqdmtwTnVqY3Z4a3dsY3c9PSIsInZhbHVlIjoia01WWm5kL0JKeUU1N09YbEdEVjBIdz09IiwibWFjIjoiMTBiNjE5MzI0MDc0ODFmMGQ3YjU4NWRmMmNjM2YwOGVjYWVmZTYyNTc1NDBjYzg0MzhlYTdhMjZlN2FlZWNkMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5015">
+      <c r="A5015" t="inlineStr">
+        <is>
+          <t>1741.psd</t>
+        </is>
+      </c>
+      <c r="B5015" t="inlineStr">
+        <is>
+          <t>tamilpsd-10922.psd</t>
+        </is>
+      </c>
+      <c r="C5015" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjN0RG1IT01MaVltLytsOGNIenVQclE9PSIsInZhbHVlIjoiR3JRamVaWmlISmU4QXJyMVhYQnFkdz09IiwibWFjIjoiZTZmMmI1YjQzYmU1NDkwNWNlYjc5OWY1MzlkNTdkOTM5ZjM3ODRmNjY4MjczZmYwNzkxOWUzMzYwYjEzOWU1YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5016">
+      <c r="A5016" s="3" t="inlineStr">
+        <is>
+          <t>1740.psd</t>
+        </is>
+      </c>
+      <c r="B5016" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10923.psd</t>
+        </is>
+      </c>
+      <c r="C5016" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InBTM0h2ajZPRzRLTGVxdTVldUJ3dEE9PSIsInZhbHVlIjoiSVFQK3lNTU9PaFhTUXJQRkpDcFNPZz09IiwibWFjIjoiNzFlOTBiNTU0YjYzMGNhZjExNWUxOTAxNDllNzc0ZWIyMjY5MTdlMjNiNDBmMTExOGViYzYwOGYwOTNjYTUyZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5017">
+      <c r="A5017" t="inlineStr">
+        <is>
+          <t>1606.psd</t>
+        </is>
+      </c>
+      <c r="B5017" t="inlineStr">
+        <is>
+          <t>tamilpsd-10924.psd</t>
+        </is>
+      </c>
+      <c r="C5017" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9qakh4alFKQ1JyMmFtWjAvODJxdGc9PSIsInZhbHVlIjoiak5ub0RHSGNna29TaXFCME1Hbndvdz09IiwibWFjIjoiZjJiNmIwMTkwYjVlMTdhMDM4NDRhZjY3YTU1YTZmMjFmNjJlZGE0Mzc5ZDJkOGFhNjU0YzQ5NDgwNmNjMzIwNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5018">
+      <c r="A5018" s="3" t="inlineStr">
+        <is>
+          <t>1739.psd</t>
+        </is>
+      </c>
+      <c r="B5018" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10925.psd</t>
+        </is>
+      </c>
+      <c r="C5018" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IngwbHRJSUorbTRVTUVqc2R1c2xNeHc9PSIsInZhbHVlIjoiSWpLTm1vcWJyK0gwelJOcTRraXVhQT09IiwibWFjIjoiMWRkZDdiNDMwNWU5MWU3NGZhZmRmZGE1Yzg2YzkzZDQ1ZTRiODRjNDJlY2EwZWI5MTgxOTU0ZTUzZGRlMTE0YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5019">
+      <c r="A5019" t="inlineStr">
+        <is>
+          <t>1738.psd</t>
+        </is>
+      </c>
+      <c r="B5019" t="inlineStr">
+        <is>
+          <t>tamilpsd-10926.psd</t>
+        </is>
+      </c>
+      <c r="C5019" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikw1VmxUTkU5RUpWYzhYMTZFcVhaUVE9PSIsInZhbHVlIjoiM2pZdUtUOTBickI1UnduVlRDMUxtZz09IiwibWFjIjoiNzEyMGZmMzMyMzk5ODFlYmNmYmU0MzRjZGJiYThmNzg3NDJmZTZjOTM0NmM0OGUyNGE0ZjI1YzE1MjhlMGZlOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5020">
+      <c r="A5020" s="3" t="inlineStr">
+        <is>
+          <t>1737.psd</t>
+        </is>
+      </c>
+      <c r="B5020" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10927.psd</t>
+        </is>
+      </c>
+      <c r="C5020" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilo3WWRZZHlOTy9STnFlbkdTWFpETlE9PSIsInZhbHVlIjoiaFMyNGNON0U0cGRKZ3F2VE5KWGFyUT09IiwibWFjIjoiZTc2ZjdkYTAwYzAxMTU4NmFjOWU0NDhjMGFiNTYzMTYwZTlmN2I0NmIyZDIzZDI0ZGI2Y2JjYWNmMWEwMTQzYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5021">
+      <c r="A5021" t="inlineStr">
+        <is>
+          <t>1736.psd</t>
+        </is>
+      </c>
+      <c r="B5021" t="inlineStr">
+        <is>
+          <t>tamilpsd-10928.psd</t>
+        </is>
+      </c>
+      <c r="C5021" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik9TcVQxbEIwSWpKbkl5U1IrZmxJbmc9PSIsInZhbHVlIjoiODVMVG5LQ0xiSjl5azA2VmNDL0ZKQT09IiwibWFjIjoiM2Y0NThmOGU3YTM1MzUwYmUwZmRhNTZhODgxNWRjZDE3N2QzZWU0ODIzNWE1N2ZjZTBiYjNiNmFiOWExNWQyNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5022">
+      <c r="A5022" s="3" t="inlineStr">
+        <is>
+          <t>1605.psd</t>
+        </is>
+      </c>
+      <c r="B5022" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10929.psd</t>
+        </is>
+      </c>
+      <c r="C5022" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9qOEdJKzBhSDUrYjJlVkdkd0t2b2c9PSIsInZhbHVlIjoianc1UDhIaXpZWFJiUEpaTXdyeVYrUT09IiwibWFjIjoiZjA1ZGRlOGFkMzJiOWVhMGNmNWZjNDVhODZlZWQyNTA2MjhjMzAxMTU4NTExYjkwMjA0YmEwYzIwMmQ0YTYxYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5023">
+      <c r="A5023" t="inlineStr">
+        <is>
+          <t>1735.psd</t>
+        </is>
+      </c>
+      <c r="B5023" t="inlineStr">
+        <is>
+          <t>tamilpsd-10930.psd</t>
+        </is>
+      </c>
+      <c r="C5023" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InR2UGRGYWlLT1A3cHdEb3c1WjJOS1E9PSIsInZhbHVlIjoieTczZEM4dWt1VU5OUG01VHB0Witldz09IiwibWFjIjoiOWJlNjU3NjYxODdlODE5YTdjMGQ3YTI4MDU2ZTAyZWM5MzI0ZTliYmU2ODQwNDY2Mzc5MzJiMzQwYzIzNWNmNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5024">
+      <c r="A5024" s="3" t="inlineStr">
+        <is>
+          <t>1734.psd</t>
+        </is>
+      </c>
+      <c r="B5024" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10931.psd</t>
+        </is>
+      </c>
+      <c r="C5024" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlMzeHpIaTJldTA5WnJaRFoxdlhuTWc9PSIsInZhbHVlIjoiaGVxQ1cwZC85cWF5VjBYTmVPRVdjQT09IiwibWFjIjoiM2M3OTE0OTZjZGVlNDI4ZmU2MDUwN2JmMTQxOTQ2OGRkY2U0ODM4MTRkMmZjYTdlOWQzOTJiMzQzOWQ2NWUyNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5025">
+      <c r="A5025" t="inlineStr">
+        <is>
+          <t>1733.psd</t>
+        </is>
+      </c>
+      <c r="B5025" t="inlineStr">
+        <is>
+          <t>tamilpsd-10932.psd</t>
+        </is>
+      </c>
+      <c r="C5025" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxObUJ4SFM1NGphRSszQXZQbk9SUGc9PSIsInZhbHVlIjoiSWZ2eGE4YnhMQTlIKzM3TDFWNlE4QT09IiwibWFjIjoiMjZlZGU2ZTM3Y2RiMTg3MGQ5YjFiNzhmZDQzOGFlYjFhNmUyMmNmZDU0NzYzMWFkNjgwZmNjYWE2OWRkYWM1YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5026">
+      <c r="A5026" s="3" t="inlineStr">
+        <is>
+          <t>1732.psd</t>
+        </is>
+      </c>
+      <c r="B5026" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10933.psd</t>
+        </is>
+      </c>
+      <c r="C5026" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNlZGZwN2lUc0tRaGE3TWNBUmNkcUE9PSIsInZhbHVlIjoiVkYvZGZzTE1QbW5JcDR1QzVGSXdUQT09IiwibWFjIjoiNGEzMDUxMzU3ZWYxZDY5ZjBiYmRkZjE1Y2U2ZmUyMGQwNjA1MDc5NmE5ZmJlMzczOTMzY2ViMDRmY2M0ZjAwMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5027">
+      <c r="A5027" t="inlineStr">
+        <is>
+          <t>1731.psd</t>
+        </is>
+      </c>
+      <c r="B5027" t="inlineStr">
+        <is>
+          <t>tamilpsd-10934.psd</t>
+        </is>
+      </c>
+      <c r="C5027" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5aeko3VXdXZW9wZXFBS2pOU0dYRlE9PSIsInZhbHVlIjoiWGFLOUhZWEI3c2hWVmtVWDZnMERQZz09IiwibWFjIjoiYzU2YTM3ZGMxZTZiOTVlNGYzMjMxMmJkM2U3MmJlZjVhODRlYTQ2Yjc5MjE5ZjdhM2NhZGE2OTczMWMxNWExYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5028">
+      <c r="A5028" s="3" t="inlineStr">
+        <is>
+          <t>1604.psd</t>
+        </is>
+      </c>
+      <c r="B5028" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10935.psd</t>
+        </is>
+      </c>
+      <c r="C5028" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InN5alNDL2QwbGNEQ3crOEpPaTMwWXc9PSIsInZhbHVlIjoiZVNxblRSS0xMam5zODRrNWFqNlRZdz09IiwibWFjIjoiZDI1MDY1NDgzYjg2OWY1MzdmMzhhZTVlZDcwNjkyOTczZjk1Y2MzN2M0M2YyNmJhZmMyNjk0YjMzY2I4ZjRkZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5029">
+      <c r="A5029" t="inlineStr">
+        <is>
+          <t>1730.psd</t>
+        </is>
+      </c>
+      <c r="B5029" t="inlineStr">
+        <is>
+          <t>tamilpsd-10936.psd</t>
+        </is>
+      </c>
+      <c r="C5029" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5HcE8rL092Y0Qwa3JPT3VCMkw2V0E9PSIsInZhbHVlIjoiVWxDbGEyQ2dGYU4xRlhvM3BoVElTZz09IiwibWFjIjoiMTk1YzM2NDI3MTIyYWQ5YmRhOGMxNTg0OTdhZTI0N2VmNTgzNTRlMjA5NDAwM2RkMGYzMjVhODBjMGFmNTljYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5030">
+      <c r="A5030" s="3" t="inlineStr">
+        <is>
+          <t>1729.psd</t>
+        </is>
+      </c>
+      <c r="B5030" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10937.psd</t>
+        </is>
+      </c>
+      <c r="C5030" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijl0bmIrOTVxRW5mNDcyZnRGN2xWb2c9PSIsInZhbHVlIjoiVWRHL2ZBT2pLNHY1L1lXRlQ2R1c0UT09IiwibWFjIjoiODRlZDc3ZTU0NDM3NmJhM2I1NGQ5ZDRjZWY5MGJmNDE2YmYzY2QxMjU0YjVmYzU2MDc4YjZjNWFhNmYxYmMwYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5031">
+      <c r="A5031" t="inlineStr">
+        <is>
+          <t>1728.psd</t>
+        </is>
+      </c>
+      <c r="B5031" t="inlineStr">
+        <is>
+          <t>tamilpsd-10938.psd</t>
+        </is>
+      </c>
+      <c r="C5031" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InpsMnlXYzYzQ2pUakVVQk4rY3Z4WUE9PSIsInZhbHVlIjoibVZYaHYxdERaVzNUYXNSdVUxRyt4QT09IiwibWFjIjoiMDZkNzFjYTQwY2JkOGRhYjgwNzUwYjI3OTc1MTMwYWYzZGZjYjE3ZjU2ZDkzZGE4YjgwZDgwYzIyYTU0Yzc0OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5032">
+      <c r="A5032" s="3" t="inlineStr">
+        <is>
+          <t>1603.psd</t>
+        </is>
+      </c>
+      <c r="B5032" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10939.psd</t>
+        </is>
+      </c>
+      <c r="C5032" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhhYTluWkZnT1cxU1pyT3B0UTVkQUE9PSIsInZhbHVlIjoiemtDalBsMENVYnlWZWxVSjNkTGF0QT09IiwibWFjIjoiZTk1MzU3OTZhYTZjZWU1NDVlYTRjODk5OTRmMzhkM2U4MmEzOTZiYmExYWQzYjUxNjNmYzViYzQyNGM1Y2I0YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5033">
+      <c r="A5033" t="inlineStr">
+        <is>
+          <t>1727.psd</t>
+        </is>
+      </c>
+      <c r="B5033" t="inlineStr">
+        <is>
+          <t>tamilpsd-10940.psd</t>
+        </is>
+      </c>
+      <c r="C5033" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik8yNWhHd0tvQ3BWazM4RFlYb1REWGc9PSIsInZhbHVlIjoiNlJRZWM4UmNKTTZnUFkrT05Gamt1Zz09IiwibWFjIjoiZWY2NjlkYjJmZjhmNWJmZjM0MjliMDhkNDM5OTYzZGNjNjJlNzU3ZmEwMDgxNDQ4MzBkZGM0Y2E5MjkwNjZlOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5034">
+      <c r="A5034" s="3" t="inlineStr">
+        <is>
+          <t>1726.psd</t>
+        </is>
+      </c>
+      <c r="B5034" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10941.psd</t>
+        </is>
+      </c>
+      <c r="C5034" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik16S2ExSklPYkpmZlRSV09ENm9nb1E9PSIsInZhbHVlIjoiRytmV1ptdFRQQzA3YzVwMXdKaW5KQT09IiwibWFjIjoiODRkODU4N2U1MmU1NWExNjJmZDVlNGQxMzAyNjlmNTQzNGJiYWQ1Y2JkYTdkMDM3MGIxZjIxMGYwNWY4OWVmMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5035">
+      <c r="A5035" t="inlineStr">
+        <is>
+          <t>1725.psd</t>
+        </is>
+      </c>
+      <c r="B5035" t="inlineStr">
+        <is>
+          <t>tamilpsd-10942.psd</t>
+        </is>
+      </c>
+      <c r="C5035" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFMa3p2d2Q0V1NmSmRFakRTc1lkaFE9PSIsInZhbHVlIjoiRm5pOXU1YzMvdEdlTGMwcDdjL1VkUT09IiwibWFjIjoiNGUwMDAxZTE2OGQ1YTlmYjY0YzhlMzRlMjU0MDI3MTQzYTFlZTM3OWMxNGY0NDY0ZDZiMDM4MTczOGM5NzE1OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5036">
+      <c r="A5036" s="3" t="inlineStr">
+        <is>
+          <t>1724.psd</t>
+        </is>
+      </c>
+      <c r="B5036" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10943.psd</t>
+        </is>
+      </c>
+      <c r="C5036" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNiOEVENEpVRVFxQTNMRE1NQW51a3c9PSIsInZhbHVlIjoiWkNGYjRvMTlhdXdJb2VtSXNjbEt6Zz09IiwibWFjIjoiNDdmNGEwZmJiMjI5MmJlYjZlNGViMDM2ZTFhZWQ4NzJiOGI0YzUzZGRlNzE5YzE2ODAyZDUxNTM5NjEyYzBjNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5037">
+      <c r="A5037" t="inlineStr">
+        <is>
+          <t>1723.psd</t>
+        </is>
+      </c>
+      <c r="B5037" t="inlineStr">
+        <is>
+          <t>tamilpsd-10944.psd</t>
+        </is>
+      </c>
+      <c r="C5037" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNmYmc3MjJ2TE1hMnE1b09FQkYyWGc9PSIsInZhbHVlIjoiYUhVbnF4eEJ3QXJtQ1FvVkhvTFVZZz09IiwibWFjIjoiMDRmNmZlMjU3YmE4MTYyYTgwZDJjYzhiZGY1ZmRlMmU3MWFkOWQ3ZDI4MmFlZmI5Zjc5NjRmNmZhOTBhYWQ1MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5038">
+      <c r="A5038" s="3" t="inlineStr">
+        <is>
+          <t>1722.psd</t>
+        </is>
+      </c>
+      <c r="B5038" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10945.psd</t>
+        </is>
+      </c>
+      <c r="C5038" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpWSkNLcFNwSVpJc1lxZm91amVvMlE9PSIsInZhbHVlIjoiejg0ZG1sQmJDeGRvYzhxOVhqbjZkdz09IiwibWFjIjoiNGJiZTgzYjExYjY2OWE3OTM3YWY5NGNmNDIwYjAwYjVkZGNlNGVmNWI0YzVlOGVjMTBmMWZiY2FjYzI2OTQyNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5039">
+      <c r="A5039" t="inlineStr">
+        <is>
+          <t>1721.psd</t>
+        </is>
+      </c>
+      <c r="B5039" t="inlineStr">
+        <is>
+          <t>tamilpsd-10946.psd</t>
+        </is>
+      </c>
+      <c r="C5039" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjdQSVpEU0I5UUZueWx4ZzYxNVNvUlE9PSIsInZhbHVlIjoiaHFPcm1lWVZyM2g4TXlNNk1KRVlqUT09IiwibWFjIjoiYzE1NmI4Y2ExNzNkOTU4ODZmZGJjNDcyMjk0MmQzY2U0MzYxMjFhZjM3OTM1ZTg3M2Q0MTM2NmJiZjk1NmJhOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5040">
+      <c r="A5040" s="3" t="inlineStr">
+        <is>
+          <t>1720.psd</t>
+        </is>
+      </c>
+      <c r="B5040" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10947.psd</t>
+        </is>
+      </c>
+      <c r="C5040" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjV3dUlGMzcvYy9TMTFMSnJYT2c4U3c9PSIsInZhbHVlIjoiTmk4N0k2a0J1RVlpUUpLREpUM3NMdz09IiwibWFjIjoiMmNlZDUyNTBmNmQ0NTIyZGQ0NmY2NmUwZjBmMjMzOWE2ZTlmNzQxMmFlYzcxNTA5NjEyNjU5MTIyODAxMDdhMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5041">
+      <c r="A5041" t="inlineStr">
+        <is>
+          <t>1719.psd</t>
+        </is>
+      </c>
+      <c r="B5041" t="inlineStr">
+        <is>
+          <t>tamilpsd-10948.psd</t>
+        </is>
+      </c>
+      <c r="C5041" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNndkZnbmxpVTJ6ZzR4bm54S00wNWc9PSIsInZhbHVlIjoieDEzNUZRN0ZYU3JpcVh0SytEcUpnZz09IiwibWFjIjoiZTM5NjU4NmExZjc4NzA5OWRlODMwYjFmZGZhYjgzN2I0OTlmMWVhN2M2YmQ4ZmFlNzQxNmExZDg3ZmM2MjE3ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5042">
+      <c r="A5042" s="3" t="inlineStr">
+        <is>
+          <t>1718.psd</t>
+        </is>
+      </c>
+      <c r="B5042" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10949.psd</t>
+        </is>
+      </c>
+      <c r="C5042" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InUvd1FPUWhyL040N0JBcU50djFrd3c9PSIsInZhbHVlIjoiMklaeitRWTFHSWdqY2ZnY2F0c0hMdz09IiwibWFjIjoiMWUxYmQ1ZTFkOGE4NWUzNDJhNzk3NzRiMzEyZjgzNTVkMjIxNzE0ZDJhNjc2MjE2NDZlZDUzMjE5ZTg1NzBlZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5043">
+      <c r="A5043" t="inlineStr">
+        <is>
+          <t>1717.psd</t>
+        </is>
+      </c>
+      <c r="B5043" t="inlineStr">
+        <is>
+          <t>tamilpsd-10950.psd</t>
+        </is>
+      </c>
+      <c r="C5043" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlE3T2lVODNqejlyUDZVZVZQaGNDUXc9PSIsInZhbHVlIjoiVHExMnRITWNDblJwRDlRckNqQ1hXZz09IiwibWFjIjoiNGUxZDAwYTRiMTUyODhiZDY3N2ZkNTMwOWQyMTBmYTc0YWY1YjNjY2VhYzc5NWJjNGUxMDk3ZTY1NDMzNjhhYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5044">
+      <c r="A5044" s="3" t="inlineStr">
+        <is>
+          <t>1716.psd</t>
+        </is>
+      </c>
+      <c r="B5044" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10951.psd</t>
+        </is>
+      </c>
+      <c r="C5044" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5WVE1VK1Y4US9tU3BvRTJTWkd4dlE9PSIsInZhbHVlIjoiZjAvVG1ubTlhczRqSHpKSVU5SjBxdz09IiwibWFjIjoiYzM3YWFmYmE0Zjk1MDgwNDRkMjFhMTYyZmQxZjhkNjMwNzMyNDcxMDJjOTI0MGMzZWVmZGU5M2QyYmQ4Yzk5MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5045">
+      <c r="A5045" t="inlineStr">
+        <is>
+          <t>1715.psd</t>
+        </is>
+      </c>
+      <c r="B5045" t="inlineStr">
+        <is>
+          <t>tamilpsd-10952.psd</t>
+        </is>
+      </c>
+      <c r="C5045" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjkzSXNQU0RFMjVHME9yMG1sWlVtQnc9PSIsInZhbHVlIjoiSmU1TzNHT2JFSS91U1hSelhwTHp0UT09IiwibWFjIjoiOTkyMjFkOTM4MzU1YzBjNzBjZWEyODZmZmQwY2I1MzRkYzUwOWI0M2U0MjI3MzVlOWE5MTNiNGNjN2VlYjhjYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5046">
+      <c r="A5046" s="3" t="inlineStr">
+        <is>
+          <t>1602.psd</t>
+        </is>
+      </c>
+      <c r="B5046" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10953.psd</t>
+        </is>
+      </c>
+      <c r="C5046" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZoRWZWenhLWlN2eEpDQXhpbXZ6Q2c9PSIsInZhbHVlIjoiaXFGbTVKUW5yKzN2RXJGakVDMTN3QT09IiwibWFjIjoiZjMxZDJlM2JmYjY3ZmJlYmZjZGE5NTZmMDhiYTVmODBkNmNkNTYwZjlmMTJlMzllMTRlNjg0ZWI2MzY5NmY2OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5047">
+      <c r="A5047" t="inlineStr">
+        <is>
+          <t>1714.PSD</t>
+        </is>
+      </c>
+      <c r="B5047" t="inlineStr">
+        <is>
+          <t>tamilpsd-10954.psd</t>
+        </is>
+      </c>
+      <c r="C5047" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9wTUM1dklWVHp4bHYvTy9IN3JYelE9PSIsInZhbHVlIjoiL2svMGlXRDBKYXRVZGlSZFgzd3Z3dz09IiwibWFjIjoiOTYzMWMzMjY0Y2VjNmJlMWZjM2RhYTVjM2Y5M2RlMjEwYzk1NzBlMTg3ZjVjNDEwMjJkOGQyMDZmYjE1M2FlMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5048">
+      <c r="A5048" s="3" t="inlineStr">
+        <is>
+          <t>1713.PSD</t>
+        </is>
+      </c>
+      <c r="B5048" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10955.psd</t>
+        </is>
+      </c>
+      <c r="C5048" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktoeXI0K1lVU2hYdjM5WWZML0JNdkE9PSIsInZhbHVlIjoiZ3ZQNjRYWG9MT00zR0Z3b1o4OFc0dz09IiwibWFjIjoiMTI1Y2U4MTFhY2IxMjEyZDMwMDE3NjEwNzIxYTY5MTMzNTkyN2Y5NjY4ODQ4OWE2ZmIzYjE0MmUwY2E3MThjNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5049">
+      <c r="A5049" t="inlineStr">
+        <is>
+          <t>1601.psd</t>
+        </is>
+      </c>
+      <c r="B5049" t="inlineStr">
+        <is>
+          <t>tamilpsd-10956.psd</t>
+        </is>
+      </c>
+      <c r="C5049" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRadzdTQUUyd2RrRk5TNEpaRTB1R2c9PSIsInZhbHVlIjoiY2RkajJrMVRJUnNlTy9KaXAzVW1vQT09IiwibWFjIjoiZGE2ZjRmYmQyODAxNGQ3Yjg2M2NiOGE5ODIyNjVlZDEwYTA4ZGNmMTkzNTkzZDYwYTA3N2ZhYWI1NTg2ZDZkOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5050">
+      <c r="A5050" s="3" t="inlineStr">
+        <is>
+          <t>1712.PSD</t>
+        </is>
+      </c>
+      <c r="B5050" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10957.psd</t>
+        </is>
+      </c>
+      <c r="C5050" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRnaGljU0pNSlZ0RXN0eXdSeThTRFE9PSIsInZhbHVlIjoiZWVVUjRoQ2hVZVZrVGw2dDBQaGFQUT09IiwibWFjIjoiZTQzNTNlNDMzYzY2MmUyMjAxNDZiYmIyZWRkMGJhNmRhYTViZGM0NTcyODViZWU4MmM3MTEzMDM0YzBiYThjZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5051">
+      <c r="A5051" t="inlineStr">
+        <is>
+          <t>1711.psd</t>
+        </is>
+      </c>
+      <c r="B5051" t="inlineStr">
+        <is>
+          <t>tamilpsd-10958.psd</t>
+        </is>
+      </c>
+      <c r="C5051" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktJVE1iOUdsRHgzRHpSNEw2THJuWkE9PSIsInZhbHVlIjoiYXdqL1dFM2lucTB1eHlGdU5RNThCUT09IiwibWFjIjoiZjE5NjFkZmNmYzI3YzQxMWZmOGM0ZmY1ODBlNzgyMzJiOGZmZDY3YWQzYTYwYTgxYWNjNTM4MTVhNWJiYzVjZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5052">
+      <c r="A5052" s="3" t="inlineStr">
+        <is>
+          <t>1710.psd</t>
+        </is>
+      </c>
+      <c r="B5052" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10959.psd</t>
+        </is>
+      </c>
+      <c r="C5052" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhwbklxR29lcGNua2VjalFLN2U1S3c9PSIsInZhbHVlIjoiTVFFTDJsblFwSDkveEVUVFdVU3FwZz09IiwibWFjIjoiOTdlZWYyNmExODJhYWE2NTNjNzA2MzlmMTIyMTk3MjE0ZjFjMTQ3OTQ1NTllMTQ0YjRhZGYzM2RkNWE4YmZlYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5053">
+      <c r="A5053" t="inlineStr">
+        <is>
+          <t>1709.PSD</t>
+        </is>
+      </c>
+      <c r="B5053" t="inlineStr">
+        <is>
+          <t>tamilpsd-10960.psd</t>
+        </is>
+      </c>
+      <c r="C5053" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InBhWWw4V3ZvYllnWkhNaXZmN3FDZ3c9PSIsInZhbHVlIjoiVUN0eVp0ck9IcUhPVnRBTW1MZG9XQT09IiwibWFjIjoiMzcyZWMyNjhmNDZlODg0ZmEzYWVhNjFkZjNkMTdjY2Y1NDYzNTZkNDY3ZGI3Njc0NzhmMTNkZDY4MjJlMjA4ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5054">
+      <c r="A5054" s="3" t="inlineStr">
+        <is>
+          <t>1600.psd</t>
+        </is>
+      </c>
+      <c r="B5054" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10961.psd</t>
+        </is>
+      </c>
+      <c r="C5054" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJJYWd5clhoZHo5NkdYblNZZ2RFZXc9PSIsInZhbHVlIjoiYUJyNGcrbHVLNklBeTNZZjJGWkpOdz09IiwibWFjIjoiMjNjYmFiMzg3YWE0OWE3ODRjNjU1ZTExNmViOWY0YWYyMjlhMzBiMzI4ODI5YjlhYzQzN2U5ZGVhNGUyNzdhNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5055">
+      <c r="A5055" t="inlineStr">
+        <is>
+          <t>1708.psd</t>
+        </is>
+      </c>
+      <c r="B5055" t="inlineStr">
+        <is>
+          <t>tamilpsd-10962.psd</t>
+        </is>
+      </c>
+      <c r="C5055" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNSSnNxVFJMKytMUEhqS0lmaCtvd2c9PSIsInZhbHVlIjoiYm16ZWp6RWFSTTUxOVl2aVAvSjRFdz09IiwibWFjIjoiYzRjNDdjYjFiNzI2YWE5ZDlhNGY4NzY0OGUwMThhYWE1ZGY2OTc2ZTU2MzkzNmYwYTkxMTExNTdjNzZlZWQwMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5056">
+      <c r="A5056" s="3" t="inlineStr">
+        <is>
+          <t>1707.PSD</t>
+        </is>
+      </c>
+      <c r="B5056" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10963.psd</t>
+        </is>
+      </c>
+      <c r="C5056" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdYaTRXYTBxZ0xxSGZaRFFyT1RkTUE9PSIsInZhbHVlIjoicU9ONDU4bmRJTEEzR3BWbTAvYkZRUT09IiwibWFjIjoiOGY4OTRmZDk3M2IzZGUyYTk0YTE5YWEzOTAyODc0ZjE1MTQxNzAxZjc5NjQzNDM0YTJiYWMzNDk1OTQzN2ExNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5057">
+      <c r="A5057" t="inlineStr">
+        <is>
+          <t>1659.psd</t>
+        </is>
+      </c>
+      <c r="B5057" t="inlineStr">
+        <is>
+          <t>tamilpsd-10964.psd</t>
+        </is>
+      </c>
+      <c r="C5057" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii84U3RVTlFLaEF2S3lWeWRaTjNvWmc9PSIsInZhbHVlIjoiT3JKSWRYaHMvajFMV3JLdVlXUGpjdz09IiwibWFjIjoiMTEyNzk3OTg3MTU2OGUzZTNiZTVlZGY2ZTdiMDcyM2Y4NmMzYTRlNWIyZGEzYWI1ZjRkZTY2MTk1ZDFhNjg2MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5058">
+      <c r="A5058" s="3" t="inlineStr">
+        <is>
+          <t>1706.psd</t>
+        </is>
+      </c>
+      <c r="B5058" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10965.psd</t>
+        </is>
+      </c>
+      <c r="C5058" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhsR2paSnptRitKV1Mva3RWYzVsY2c9PSIsInZhbHVlIjoiTGFWNTYvRVJBVURzRVhXM2VlNkRNUT09IiwibWFjIjoiYWUwNzA5Y2YzNDk0M2MyNDRhZTk4NWFmMDg3NDFmZjFjNDg2MDg3NGUyMjJlMDNiYjZkZTU4Y2FmMmMxMzNlZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5059">
+      <c r="A5059" t="inlineStr">
+        <is>
+          <t>1705.psd</t>
+        </is>
+      </c>
+      <c r="B5059" t="inlineStr">
+        <is>
+          <t>tamilpsd-10966.psd</t>
+        </is>
+      </c>
+      <c r="C5059" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFUWTNvdHc5ZHg3c2JrbU5rUURDZEE9PSIsInZhbHVlIjoieTYrMzFWVVFrajkzNmFlem5ZWjM3Zz09IiwibWFjIjoiNTVjMjY0YmQ0NTgzYzFjM2UwYjA3OTgzZGQ4MGMzOGI4Y2ZmOGIzNGMwYmZmNmQ0NzE2MDFjOTNmZTI3Y2E2NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5060">
+      <c r="A5060" s="3" t="inlineStr">
+        <is>
+          <t>1704.psd</t>
+        </is>
+      </c>
+      <c r="B5060" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10967.psd</t>
+        </is>
+      </c>
+      <c r="C5060" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik9wekU0MGJNQ2hZQ1RVVGhPWFpoSkE9PSIsInZhbHVlIjoiVlIveXNEK3paM2tUSVlxSGRYTmZLZz09IiwibWFjIjoiMDdlMDJiMWFiOTEyNTcwMDViNGYwNGVkNTMwMTE3YjAyYWMwOGE0NjBlODA1Yzc2YTZiN2VjNjA3MzhhNzczNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5061">
+      <c r="A5061" t="inlineStr">
+        <is>
+          <t>1703.PSD</t>
+        </is>
+      </c>
+      <c r="B5061" t="inlineStr">
+        <is>
+          <t>tamilpsd-10968.psd</t>
+        </is>
+      </c>
+      <c r="C5061" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IitxbjY0d2UwN0VIVml6clUvWUZ4RGc9PSIsInZhbHVlIjoiVnZ0MG04WWppRldnWEh1bWtnOW9IQT09IiwibWFjIjoiZmY2ZTJjMzQwNzJkZGI5YWNlNDEyOTJjYjk3NGExNjRlNTlkNzY2M2ZmNTk3MjhhOTIwZGY2NjNlNGUzNzZkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5062">
+      <c r="A5062" s="3" t="inlineStr">
+        <is>
+          <t>1702.psd</t>
+        </is>
+      </c>
+      <c r="B5062" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10969.psd</t>
+        </is>
+      </c>
+      <c r="C5062" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVrNC9BK1pzRDhCSElzK0I0TEROUHc9PSIsInZhbHVlIjoiSDUzVFFjajROUTNyYjVKT21vWnpUdz09IiwibWFjIjoiNTA4Njk2NDZkNDIzMThkZWM5NzI5ZWVhNDYzYjE5NGI3YjE3OWY1YTYyM2RjYTliNjkwYzQ1YmM4MWExYjNiYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5063">
+      <c r="A5063" t="inlineStr">
+        <is>
+          <t>1701.psd</t>
+        </is>
+      </c>
+      <c r="B5063" t="inlineStr">
+        <is>
+          <t>tamilpsd-10970.psd</t>
+        </is>
+      </c>
+      <c r="C5063" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVvQjU4Y3N5VUlEd1h1QW5WZUZQSWc9PSIsInZhbHVlIjoiWDdHMVNWVW9IQ1YvOEloTzl6VGhpQT09IiwibWFjIjoiNjdjYjczZjhlNWNlZWM1NTQxMjE1OWM1YzM4YWIyZWM0NzU1OGVhMTY0ZmZjZjU5NzA0ZDdlYzQ1NmE0MzY0NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5064">
+      <c r="A5064" s="3" t="inlineStr">
+        <is>
+          <t>1700.psd</t>
+        </is>
+      </c>
+      <c r="B5064" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10971.psd</t>
+        </is>
+      </c>
+      <c r="C5064" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZud0l0ak5mZ1lTRXZoMjZ5OVZKamc9PSIsInZhbHVlIjoia09nNFZYVitTTDYxVHVWV3ZRdVkrdz09IiwibWFjIjoiMTAyMjhhN2YyMDgwNjcyMDZkNTVkZDFmYjRkM2M3OWE3MTRiMzk4MTIwODA5NTJkN2QyYzY4YTc0MDlmOGI2MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5065">
+      <c r="A5065" t="inlineStr">
+        <is>
+          <t>1699.PSD</t>
+        </is>
+      </c>
+      <c r="B5065" t="inlineStr">
+        <is>
+          <t>tamilpsd-10972.psd</t>
+        </is>
+      </c>
+      <c r="C5065" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJkSnExVUR5K0FjbngwRUNxdGdzZFE9PSIsInZhbHVlIjoiNkN0cVJ2S0FsUStXNGUvS2R2OHhodz09IiwibWFjIjoiMDBiNjcyZDM4NWIwYTVhNzg4NmFlNjI5MjYxYTc2OGQwNGMxM2EzMTY2ZDZjZjhlN2Y0MzcwMWQ2YjlkODNmMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5066">
+      <c r="A5066" s="3" t="inlineStr">
+        <is>
+          <t>1698.psd</t>
+        </is>
+      </c>
+      <c r="B5066" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10973.psd</t>
+        </is>
+      </c>
+      <c r="C5066" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkI4eUxsT0JmeHE1ZnIrclBTcU5xa1E9PSIsInZhbHVlIjoiTzNLSnVxMmVIeWhCZnoyZjNTUG0wUT09IiwibWFjIjoiMGI0Mzc5OThjMjAzZDE1MTJiM2UyZDFjNTk3ODhhMTgwOWNlMTU5OTYzNjYxMmVmNTYxMjViNjI5ZjMzMGNkMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5067">
+      <c r="A5067" t="inlineStr">
+        <is>
+          <t>1697.psd</t>
+        </is>
+      </c>
+      <c r="B5067" t="inlineStr">
+        <is>
+          <t>tamilpsd-10974.psd</t>
+        </is>
+      </c>
+      <c r="C5067" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkdjMzBIYU9GbUMzN3BISGRDSjZ5MEE9PSIsInZhbHVlIjoiT09EUmlIbkcvbjJsNWUvL0pvaWdLQT09IiwibWFjIjoiOWFhNTcwZTI2NGM2MDY4NzA1OTQ0Y2NmYzFkZDZlMzNlMTRmYzQ3OTdlZDI1MjVjZTA1NGIxYmExYzNjODlkNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5068">
+      <c r="A5068" s="3" t="inlineStr">
+        <is>
+          <t>1696.psd</t>
+        </is>
+      </c>
+      <c r="B5068" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10975.psd</t>
+        </is>
+      </c>
+      <c r="C5068" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNobVNGV1RiRm5IS1lKOWREZ3lnRFE9PSIsInZhbHVlIjoiTVE0TldRcUxQbjBKZmNoZzl2NDE5dz09IiwibWFjIjoiOWU5Zjc2Zjk4YTdiNmNjZTVmNWZiYjVmMGZiNmIwMTQ0NTE3ZjFhZjhjMDMzNzZhMDJlZWM4ZGQ2OTQxMTc3NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5069">
+      <c r="A5069" t="inlineStr">
+        <is>
+          <t>1695.PSD</t>
+        </is>
+      </c>
+      <c r="B5069" t="inlineStr">
+        <is>
+          <t>tamilpsd-10976.psd</t>
+        </is>
+      </c>
+      <c r="C5069" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImI1Yjg2QjNab1llVVc1bkM2d1c1U3c9PSIsInZhbHVlIjoiY00yK1FzZ2pBZCt4ZE53WWlvbFA5dz09IiwibWFjIjoiMTM2YThkOTk1ZDEyZWRjMDgwM2Y0NDk5MzMyNmNkZjBhNzFjZGM1M2VjY2IyMTY1MjQ1MDBmZGFiY2IyYjUzMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5070">
+      <c r="A5070" s="3" t="inlineStr">
+        <is>
+          <t>1694.psd</t>
+        </is>
+      </c>
+      <c r="B5070" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10977.psd</t>
+        </is>
+      </c>
+      <c r="C5070" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBDVTBpS2s2dFRHYUc0RURNOGlSWVE9PSIsInZhbHVlIjoiSFQ4VHRrcWpYd0F0WGpubW55ZkJaQT09IiwibWFjIjoiYmJkMzJkYjhlMDY5Zjg5YjhjODMzZjM3ODk4ODM0NTZjYTUyYjUyODZkNDYzOTJmNzFkYmM5NzVlMmM1MWFhNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5071">
+      <c r="A5071" t="inlineStr">
+        <is>
+          <t>1693.psd</t>
+        </is>
+      </c>
+      <c r="B5071" t="inlineStr">
+        <is>
+          <t>tamilpsd-10978.psd</t>
+        </is>
+      </c>
+      <c r="C5071" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFTdXZWdmZjb0N1bzZXeEZNY1Z2QVE9PSIsInZhbHVlIjoicTI0MzZqWVJFZ1VuekM4MXBrNFNHZz09IiwibWFjIjoiMmEwNTRjNzg2NDdhMWU3ZGQ4NDE0NjU1NmE3Yjk0NWRmZmQzODM2MGYzZjcxOTc2OWFlYTViODNhYzQ5ODNlMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5072">
+      <c r="A5072" s="3" t="inlineStr">
+        <is>
+          <t>1691.psd</t>
+        </is>
+      </c>
+      <c r="B5072" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10979.psd</t>
+        </is>
+      </c>
+      <c r="C5072" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFCYy9hdytLV2o2eUFYcEduRDhyV2c9PSIsInZhbHVlIjoiOE5MOGwwN21pc0ZadFR2OW5Sa01ydz09IiwibWFjIjoiMTNjNWIyOGU2MTZjMzZkY2Y2ZWM5MmU3YjBiM2VlM2Y0YjFkYzg4ODgzNDljZjQ0ODBjMjBlMGQwZDE3NmNlOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5073">
+      <c r="A5073" t="inlineStr">
+        <is>
+          <t>1690.psd</t>
+        </is>
+      </c>
+      <c r="B5073" t="inlineStr">
+        <is>
+          <t>tamilpsd-10980.psd</t>
+        </is>
+      </c>
+      <c r="C5073" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFhR29DeGV0STErVTlLRlo3MGZJSGc9PSIsInZhbHVlIjoiR1dHU0VZUythK2VvT3hhRjVPYk5Odz09IiwibWFjIjoiNTQyMjFhNWI2MTlhY2I2YTRhNDhlZjkzZjcxZTZkYWU2MGM0MzZhOWEwNjEwMTFjMjQ5MjkyMWQ1ZmJiYjRhNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5074">
+      <c r="A5074" s="3" t="inlineStr">
+        <is>
+          <t>1689.psd</t>
+        </is>
+      </c>
+      <c r="B5074" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10981.psd</t>
+        </is>
+      </c>
+      <c r="C5074" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZ4YmtxYXBrOTRQdHFzUEMrTGJhYVE9PSIsInZhbHVlIjoiZ201TG9jK3hQdEU1L2w2MDF6dmE4dz09IiwibWFjIjoiYWZlM2UzZTY4Zjk2MzA3NGE0YmYzMzlmYzdjNDdiOGIwZDQ5MzZiYjgyY2MxNDkyMmNiNTIxZmM4M2M2YjVhZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5075">
+      <c r="A5075" t="inlineStr">
+        <is>
+          <t>1598.PSD</t>
+        </is>
+      </c>
+      <c r="B5075" t="inlineStr">
+        <is>
+          <t>tamilpsd-10982.psd</t>
+        </is>
+      </c>
+      <c r="C5075" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklqVTFVTlFtVHRneTQ0K1V5a1o4UEE9PSIsInZhbHVlIjoidTFVaXY2Mk80bUQrK0FwcU1aWmh6Zz09IiwibWFjIjoiMjIxYjhmZTU4NWIzYjkzMDAyOWJmMzBmNTZkNmQ5NDk5MDQzZDMwYmQ3MDZkZDFkMjAyNjJiNzY0MDlkNjcwNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5076">
+      <c r="A5076" s="3" t="inlineStr">
+        <is>
+          <t>1688.psd</t>
+        </is>
+      </c>
+      <c r="B5076" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10983.psd</t>
+        </is>
+      </c>
+      <c r="C5076" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZtS3FJOE5yRXdNYjl1WXVycnNlT0E9PSIsInZhbHVlIjoiMTIyNzRhdDh3VlpuNkxZWTBrVDZUdz09IiwibWFjIjoiM2ExN2RlOGJiZTg2YjRiN2ZjNWFkN2I2YWJjNzA3MDRmZjQ0NWNmOWRjODBjMWI1MjM4MGEzZjQ5OTVkYjZjOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5077">
+      <c r="A5077" t="inlineStr">
+        <is>
+          <t>1687.psd</t>
+        </is>
+      </c>
+      <c r="B5077" t="inlineStr">
+        <is>
+          <t>tamilpsd-10984.psd</t>
+        </is>
+      </c>
+      <c r="C5077" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlWWEd4Yjk4NVFzbUxKOURRMVdOeWc9PSIsInZhbHVlIjoiTmpQYlBmZHFlMEgwNlQ1WEIyK3I3QT09IiwibWFjIjoiYzVhNjZhYTYwZDc3OTZjNDE3MDQ2OWFkZDA5OGM2YTY3ZGYzMmI4MzE3NzJiMzllMGE5ZTMyNjNlZTU2MjgxMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5078">
+      <c r="A5078" s="3" t="inlineStr">
+        <is>
+          <t>1597.PSD</t>
+        </is>
+      </c>
+      <c r="B5078" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10985.psd</t>
+        </is>
+      </c>
+      <c r="C5078" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9LMTVpN3Q1cEZoRkI2eFZxc29sVUE9PSIsInZhbHVlIjoiNVgxYkYwd3FvSzJUd2NNQ0xFR1Aydz09IiwibWFjIjoiNDg0ZmEzZjM2MzE0NzM4OWM4NTM1OTQyZTRlYjdiYjU4NzcxZDMwM2NlM2I5NWQ0YmI5NTM3ZDc1ODY1YjRlMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5079">
+      <c r="A5079" t="inlineStr">
+        <is>
+          <t>1686.psd</t>
+        </is>
+      </c>
+      <c r="B5079" t="inlineStr">
+        <is>
+          <t>tamilpsd-10986.psd</t>
+        </is>
+      </c>
+      <c r="C5079" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRFdG5MRHlRdFdrNEY1a055TDN6dnc9PSIsInZhbHVlIjoiVm1hbUh3QzdJVmY2VVFuYm1qS2FyUT09IiwibWFjIjoiODBlNDBlNTlmMjA4ZjJhM2JhOWViMjg2NzE1MzlhOTc4MDQyOWNhYWYxMTg0ZjQwNmRjNmYwZTU4ODE5OTVjYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5080">
+      <c r="A5080" s="3" t="inlineStr">
+        <is>
+          <t>1685.psd</t>
+        </is>
+      </c>
+      <c r="B5080" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10987.psd</t>
+        </is>
+      </c>
+      <c r="C5080" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlgxazNhQ0JzS09LMzg3NGZQd2hsOGc9PSIsInZhbHVlIjoiVFNUcUlQMDQzNlRKR2tpVzNOQk9Ddz09IiwibWFjIjoiZTY1YmRmYWRhMzY0ZGI0NTdkOWFlZjUwMzEyYmIyMzliNTRmYjI3Y2RjMzQ1NjE4YTE4M2FlMmY1NTZlY2YxNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5081">
+      <c r="A5081" t="inlineStr">
+        <is>
+          <t>1684.psd</t>
+        </is>
+      </c>
+      <c r="B5081" t="inlineStr">
+        <is>
+          <t>tamilpsd-10988.psd</t>
+        </is>
+      </c>
+      <c r="C5081" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZMQTRWQVlyZzR1TWlJaG9Dem93Q2c9PSIsInZhbHVlIjoicjFUaHUrallqUFhaMUJBSWI3K2xtUT09IiwibWFjIjoiMzY3ZGNjZGUzMDBiMDEwMzY5MzE5MTZhZTA2NDJmOWVkYTk0ZmNiMjIxNjIyMjE2YmQxMzlhZDQzMDhkMmNiNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5082">
+      <c r="A5082" s="3" t="inlineStr">
+        <is>
+          <t>1683.psd</t>
+        </is>
+      </c>
+      <c r="B5082" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10989.psd</t>
+        </is>
+      </c>
+      <c r="C5082" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjkzV0FHRDVOZ3N2SkpRVVJtTUJJY0E9PSIsInZhbHVlIjoiQ1RTL2dYSDc2R1doT09ERWNQNTMxdz09IiwibWFjIjoiMTkyYzBlZGQ0NDM0OWY3NDUyZGRlNmE2OTcyNjc3M2FiMjJiZWZmMzRiY2NhOGExNzEyOTkxNDcxYzZiMDk0OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5083">
+      <c r="A5083" t="inlineStr">
+        <is>
+          <t>1596.psd</t>
+        </is>
+      </c>
+      <c r="B5083" t="inlineStr">
+        <is>
+          <t>tamilpsd-10990.psd</t>
+        </is>
+      </c>
+      <c r="C5083" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik4waTQ0MmRBRFM4M0VDYWl0V3ZXUXc9PSIsInZhbHVlIjoiTFpDcUFrbmd0azFjc0VMd1RPdDNyUT09IiwibWFjIjoiN2JjZTVhZjdhOTA4NTNhMjFhZTU4ZTkyM2E0NDUwYmRkNjIwOGU4Y2FlOTZjYzYwMzFkYWMxYjc5OGY5NTM4ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5084">
+      <c r="A5084" s="3" t="inlineStr">
+        <is>
+          <t>1682.psd</t>
+        </is>
+      </c>
+      <c r="B5084" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10991.psd</t>
+        </is>
+      </c>
+      <c r="C5084" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFKS0kzdjFnbVFISGkzQVc4WmEyQmc9PSIsInZhbHVlIjoialJpRllrakpIUHFlR0dpODkxTEs3Zz09IiwibWFjIjoiMmNhNTQwMTZmZGJlMDc4NjAwYTg5YWM1NTVhOTY5YmNlMjExNjBjNTliZmNhNmQ2MTM1MmE4NTgzNzc2NzJlNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5085">
+      <c r="A5085" t="inlineStr">
+        <is>
+          <t>1681.psd</t>
+        </is>
+      </c>
+      <c r="B5085" t="inlineStr">
+        <is>
+          <t>tamilpsd-10992.psd</t>
+        </is>
+      </c>
+      <c r="C5085" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1OV0lFSC83dHVPclJ5NlF0bzFxRHc9PSIsInZhbHVlIjoiKzZTbkdJQzV3bTVyR0pIQ1RRK1lVdz09IiwibWFjIjoiM2Q3YTMxMmY2Njc2NDYyNzU3MzNlYjJkNjQ4NzRmMTI1MjYyZjU5ZTQ0MGYwMmRmZjQzZjNkNThhN2Q1OTI3MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5086">
+      <c r="A5086" s="3" t="inlineStr">
+        <is>
+          <t>1595.psd</t>
+        </is>
+      </c>
+      <c r="B5086" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10993.psd</t>
+        </is>
+      </c>
+      <c r="C5086" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZicHlmeFJ2UmlyT2hvNzRVNnV3YVE9PSIsInZhbHVlIjoiaVdVYTRGQ0daWHh5bG5wcGlCaStpdz09IiwibWFjIjoiMzM4YWY4YjI5YTZhMzIyZDQ1NWYyYWU4Mzc3NjMyNmFiNTMzZTk0ZmI4NzMwNmFiNzlmZDljNWZjMTcxMWE2MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5087">
+      <c r="A5087" t="inlineStr">
+        <is>
+          <t>1680.psd</t>
+        </is>
+      </c>
+      <c r="B5087" t="inlineStr">
+        <is>
+          <t>tamilpsd-10994.psd</t>
+        </is>
+      </c>
+      <c r="C5087" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktiZlc4cittbUovaEM1enIzaklyRmc9PSIsInZhbHVlIjoiWUhPdmkxc1BFU3FsT2R0TUYrYU1WUT09IiwibWFjIjoiNGNlYzQyNWQyZWE5NzdkYzkyNGVlYWZiODVjZjUxOGZlZTg0YjcwNmQxODNlN2M5YmJhZjA5YWYzOTJjZDgyMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5088">
+      <c r="A5088" s="3" t="inlineStr">
+        <is>
+          <t>1594.PSD</t>
+        </is>
+      </c>
+      <c r="B5088" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10995.psd</t>
+        </is>
+      </c>
+      <c r="C5088" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVJNXM2Tm5xVGZQb3lPQTl4clVIcmc9PSIsInZhbHVlIjoiUnBSdFR6VTBaN0RNMkxyczduN05Idz09IiwibWFjIjoiNDJmNzFjNDZjMDczNGUwMWFhYWU2ODU5MjgyYTUwNWFlMWM5ZDczMzE3ZmVlYzk2NmUyMTMxNGRhOTFkZTU5OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5089">
+      <c r="A5089" t="inlineStr">
+        <is>
+          <t>1679.psd</t>
+        </is>
+      </c>
+      <c r="B5089" t="inlineStr">
+        <is>
+          <t>tamilpsd-10996.psd</t>
+        </is>
+      </c>
+      <c r="C5089" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJ5UzFFcnBZb1VKT2t3dzNRbC80R0E9PSIsInZhbHVlIjoidG80VFdKSnVGd1ovYzhFQUd4Q040UT09IiwibWFjIjoiYzU4NjQ4ZDQ3Mjc1NWIzNGQxYzkzYzU4YTllMDAzODMyNDAyYmI4NWI5ZGI0MzE0MzFhMDI1YTNkM2I1OGNjNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5090">
+      <c r="A5090" s="3" t="inlineStr">
+        <is>
+          <t>1678.psd</t>
+        </is>
+      </c>
+      <c r="B5090" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10997.psd</t>
+        </is>
+      </c>
+      <c r="C5090" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpheTBrcDNxd1EyYlhVMDg4VjBJakE9PSIsInZhbHVlIjoiYnYwSTJ5Y2NSQVVtZkQwSm1CU0orQT09IiwibWFjIjoiMDFhNDFkNDRjZjMzY2E5ZGRjMTg0OTY0NGJjODJiNTEyZjBlNjRjNmViZTI2ZmUwNzQzMzQxZDBhNzU1ODI1YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5091">
+      <c r="A5091" t="inlineStr">
+        <is>
+          <t>1592.PSD</t>
+        </is>
+      </c>
+      <c r="B5091" t="inlineStr">
+        <is>
+          <t>tamilpsd-10998.psd</t>
+        </is>
+      </c>
+      <c r="C5091" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJHeE5sTDNOTHh2cjhUeHo3NjVXc1E9PSIsInZhbHVlIjoiRTRDRXB2NlZDU0Q1OWY5K2l4YzhTZz09IiwibWFjIjoiMWNmMWJiZjFjMmQ4OTU2ZGYzOWMxMzU4MDVhNGExOGYzMjYwNjM4N2VlYWE1ODdlYzljZTUzNWIxNjgyZGRhYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5092">
+      <c r="A5092" s="3" t="inlineStr">
+        <is>
+          <t>1677.psd</t>
+        </is>
+      </c>
+      <c r="B5092" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-10999.psd</t>
+        </is>
+      </c>
+      <c r="C5092" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJFK1hUc3hSUU85NGkzVElsd0oxZkE9PSIsInZhbHVlIjoiODRBcUw4MlV2WXdSU2psN1hnRVNlUT09IiwibWFjIjoiYTcwMDhjM2Y5ZGJlNzczOTQ0NDE5OWJjNmZhZDczY2JlZGQzZmQ3ZGY5ZWNhNjJmYzk5MmIyNTgzNzJmMGM5ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5093">
+      <c r="A5093" t="inlineStr">
+        <is>
+          <t>1676.psd</t>
+        </is>
+      </c>
+      <c r="B5093" t="inlineStr">
+        <is>
+          <t>tamilpsd-11000.psd</t>
+        </is>
+      </c>
+      <c r="C5093" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjB6UnNEMnRqbk13dlVVb01FRzRYY0E9PSIsInZhbHVlIjoiMHpzekpZWDJYVk5aTFlDYlJQV2dZUT09IiwibWFjIjoiNGM4OTJmYjU5M2ZmMDM5ZDcyZTQ0MjUyYmNiMTU4ZmZjYzNlM2ViMWQ1MGQ3NzkyYWQ5MGI0YWYxNDA4ZTcxMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5094">
+      <c r="A5094" s="3" t="inlineStr">
+        <is>
+          <t>1591.PSD</t>
+        </is>
+      </c>
+      <c r="B5094" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11001.psd</t>
+        </is>
+      </c>
+      <c r="C5094" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImQ1RWVpNEg1aWVDMGs4Y2JHNTlZYXc9PSIsInZhbHVlIjoiMmxadjZNZmo1YzFQWXRuTElOK3dOdz09IiwibWFjIjoiMWI5MDkyMzA5NDRhODlhMTIwZGIzNDJiZTM3NmU3YTZiODAwOWFmNTZmYjBjOTU5N2ZlY2JkMjMyNjZjNzcwYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5095">
+      <c r="A5095" t="inlineStr">
+        <is>
+          <t>1675.psd</t>
+        </is>
+      </c>
+      <c r="B5095" t="inlineStr">
+        <is>
+          <t>tamilpsd-11002.psd</t>
+        </is>
+      </c>
+      <c r="C5095" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlEyaEc2eEV0dmtBK3FSc2J6UjVHbWc9PSIsInZhbHVlIjoiV2wzMkthWUlhc0xtUU80Qkp0OTVjdz09IiwibWFjIjoiYmE3NDQ0ODlkNzFmNmJlMzhmMGU1ZWM0ZmRhYjY2Y2Y0MDAzMGJjNDcxMmNhY2NjNzEzNDIwNjdhNDljNWFmMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5096">
+      <c r="A5096" s="3" t="inlineStr">
+        <is>
+          <t>1674.psd</t>
+        </is>
+      </c>
+      <c r="B5096" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11003.psd</t>
+        </is>
+      </c>
+      <c r="C5096" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImIxeGQ4aksvT0JMb291WTBLRnNqTVE9PSIsInZhbHVlIjoiamNNaFNscURtekN4bzVkdFljQjA5QT09IiwibWFjIjoiYjJkZWMxYjNlMjg5NmQ3NzNiOWI4MjA2YmQ0MDRjNzc4ZDc2YzU4MzAwZWY1MGViNDAzYjJjMGMyMTYyOWI1MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5097">
+      <c r="A5097" t="inlineStr">
+        <is>
+          <t>1673.psd</t>
+        </is>
+      </c>
+      <c r="B5097" t="inlineStr">
+        <is>
+          <t>tamilpsd-11004.psd</t>
+        </is>
+      </c>
+      <c r="C5097" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii84d1c5SitSSFdraWRZZ0ZFekJHb3c9PSIsInZhbHVlIjoiQW4xaHpyQWlwYXR0c2hoakVHWWhoZz09IiwibWFjIjoiMzg3MGJiMGQ2NGEwYzdmZWYyNzRiODdiOGRjZDVmOTFmZGU1ZTc2MTA1OGI3ZjM2YzM3NWRiMGIzNTA1ZjljOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5098">
+      <c r="A5098" s="3" t="inlineStr">
+        <is>
+          <t>1672.psd</t>
+        </is>
+      </c>
+      <c r="B5098" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11005.psd</t>
+        </is>
+      </c>
+      <c r="C5098" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhTbVpvaXdhUkl5cXczNGJ6MmJLcEE9PSIsInZhbHVlIjoiZUt2RUZUZFZuYTdHamdSR20wTnV0dz09IiwibWFjIjoiZTkzYjFjNjU2YjVmOGI5NWQxYTg5NDg5NDg1NjAwNzFmMjFlNGQ0ZWFlMWVhOTkzNTFhM2YzYzk4YjdiYTI5NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5099">
+      <c r="A5099" t="inlineStr">
+        <is>
+          <t>1590.PSD</t>
+        </is>
+      </c>
+      <c r="B5099" t="inlineStr">
+        <is>
+          <t>tamilpsd-11006.psd</t>
+        </is>
+      </c>
+      <c r="C5099" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5WbXM2UFZxY0Z5VFVFekkxRWNlaHc9PSIsInZhbHVlIjoiaXNoQkVtRmlaelYwK3V5SCtFOVJXdz09IiwibWFjIjoiODBkOGY1ODNhZDVkNDUxY2NlMGEzMGZiZWUwZTlhYjdiZTkwZGU2Y2JmYTM4ODFmNGMyY2FlNzQxZDZhMzRmNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5100">
+      <c r="A5100" s="3" t="inlineStr">
+        <is>
+          <t>1671.psd</t>
+        </is>
+      </c>
+      <c r="B5100" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11007.psd</t>
+        </is>
+      </c>
+      <c r="C5100" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5Gbm9YN3BmcGZadlZwSjNkQ0lUK0E9PSIsInZhbHVlIjoiQ0x6YTgrSXRtblpVTEVkUDVNTVBDZz09IiwibWFjIjoiYzA3YmE5N2Q4YzE0YzU3Nzk3NGUwMWJlOGVlYTlkODMzNGZmZmYyYjk4Y2ZiMWFlYzk0YjgzMDE3MWYzMjQwNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5101">
+      <c r="A5101" t="inlineStr">
+        <is>
+          <t>1670.psd</t>
+        </is>
+      </c>
+      <c r="B5101" t="inlineStr">
+        <is>
+          <t>tamilpsd-11008.psd</t>
+        </is>
+      </c>
+      <c r="C5101" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhxTnRRN3czMndnaDdsa2xKWEJwYnc9PSIsInZhbHVlIjoidk50c3d2RlRaTHVxaE5YZDFmZ3ZzQT09IiwibWFjIjoiYmU2OTRjNDZmNmZhYmU4ZGYxNjg0MzZhNzUwMTdlMjkyZDdkMTU0M2M4NjQwMjMyODdhNTVmZDg3NTUwNTNkMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5102">
+      <c r="A5102" s="3" t="inlineStr">
+        <is>
+          <t>1669.psd</t>
+        </is>
+      </c>
+      <c r="B5102" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11009.psd</t>
+        </is>
+      </c>
+      <c r="C5102" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlmOWNxWlJzN2xQc3VnUnkra3M1cFE9PSIsInZhbHVlIjoiSmRoT3R2N29ZU0VEb0lmdTNJcmxNZz09IiwibWFjIjoiZGUyYmE1M2ZmOTBkZjViOTJmM2ZjNzIxNDQyNDMzZGQ5MWQ3ZjYzMzY1M2IyNGY2NjRkMjcyZTViZTI1NDg5ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5103">
+      <c r="A5103" t="inlineStr">
+        <is>
+          <t>1668.psd</t>
+        </is>
+      </c>
+      <c r="B5103" t="inlineStr">
+        <is>
+          <t>tamilpsd-11010.psd</t>
+        </is>
+      </c>
+      <c r="C5103" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZnbUhIbkkyQ1gwM0hjeUpDbTBwcnc9PSIsInZhbHVlIjoiTzFiOXF1dzJLQXZWbXVlQ3hkM08vdz09IiwibWFjIjoiODMyMjhhYTFlM2RiYzBkYTUwYmVhNDZmYjlkY2I3NGQzOWEzOWI5MjdlODdiZGZhZmM2ZGUzMDJiZGYxMGM5ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5104">
+      <c r="A5104" s="3" t="inlineStr">
+        <is>
+          <t>1589.psd</t>
+        </is>
+      </c>
+      <c r="B5104" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11011.psd</t>
+        </is>
+      </c>
+      <c r="C5104" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpOT3o4RU1QQ0tVSCtJTS9zWE90cWc9PSIsInZhbHVlIjoiYmlRenZCVTVqYWtYcUVWN1V0RnJpZz09IiwibWFjIjoiODQ4ODU0YzQzY2ZiMTk4ODYyMzI3NjFiNmFjMzczMmIyYzI2NGY2YmExNWQxMGEzZjU5ODVlMzQ2MDFiYTAyMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5105">
+      <c r="A5105" t="inlineStr">
+        <is>
+          <t>1667.psd</t>
+        </is>
+      </c>
+      <c r="B5105" t="inlineStr">
+        <is>
+          <t>tamilpsd-11012.psd</t>
+        </is>
+      </c>
+      <c r="C5105" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik50S1gvK0xTelg3M2FkSlhwSkxKQnc9PSIsInZhbHVlIjoiUGJuWWdVN0ROemhwTjZHeG1WWGpMZz09IiwibWFjIjoiMzdiZjFmZWViZWE4ZDNlMTVmOTMzMzk5NTY2OTEyNTJhNTQxNWViODVlM2MxZTE5ODVlZDY1ZDg4ZmYzODA5YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5106">
+      <c r="A5106" s="3" t="inlineStr">
+        <is>
+          <t>1666.psd</t>
+        </is>
+      </c>
+      <c r="B5106" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11013.psd</t>
+        </is>
+      </c>
+      <c r="C5106" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkQ2MFBXU2FwbjFKckpmUVltak9IVmc9PSIsInZhbHVlIjoiaXVxWlNJdHFad205VUlhTWpETlRhZz09IiwibWFjIjoiODEwYzk1NTRmMWQzMGMyZWQ0MGI2ZGQ0MjNjYTliNzM0NWVjZjVlNzRhNGVjYmFmMmU0NzdhZTA5YjMwMTc5MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5107">
+      <c r="A5107" t="inlineStr">
+        <is>
+          <t>1588.psd</t>
+        </is>
+      </c>
+      <c r="B5107" t="inlineStr">
+        <is>
+          <t>tamilpsd-11014.psd</t>
+        </is>
+      </c>
+      <c r="C5107" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im4xbUNCV2FGLzVmL2tDdWZrcmdHWHc9PSIsInZhbHVlIjoiZFR5aFZ4bmpUS0JaY2xqK01yNlZNdz09IiwibWFjIjoiMGVkODcxMDE1NjExNmZmNTFjYmU2ZWU1YzQ1ODM4NjlmMDQyYjZmMjc4NzdlN2ZlYTQzNzc3ZGQ3Y2FmNGIwNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5108">
+      <c r="A5108" s="3" t="inlineStr">
+        <is>
+          <t>1665.psd</t>
+        </is>
+      </c>
+      <c r="B5108" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11015.psd</t>
+        </is>
+      </c>
+      <c r="C5108" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVJcUhDL2t6VWJwaGhldmxnc1pSTEE9PSIsInZhbHVlIjoiWnMrZVB0VE0ydk5BWTlBUUpjOXorZz09IiwibWFjIjoiYjcxMDU5NjJkZGI2NzhhYTg4ZDlkNzlhYTk4ZjIwZWIxY2M0NTI5OTkwNDQzZTUxOWZhOGVjZjE4NGQ5ZDIzZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5109">
+      <c r="A5109" t="inlineStr">
+        <is>
+          <t>1664.psd</t>
+        </is>
+      </c>
+      <c r="B5109" t="inlineStr">
+        <is>
+          <t>tamilpsd-11016.psd</t>
+        </is>
+      </c>
+      <c r="C5109" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZCOUhOeFFWTzVZWGd4NWRQK3dtSVE9PSIsInZhbHVlIjoiUXVtNFZ2aHNwek4xelVuaFF1bTJFZz09IiwibWFjIjoiZjU2ZDFiMzkzMmM0OTllZWI1YmIzN2YwYzcxYjVmZDZkM2IxM2VhYTAwZWM0YmZhMGE3NjBlMzFlNDlkNDQ0ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5110">
+      <c r="A5110" s="3" t="inlineStr">
+        <is>
+          <t>1663.psd</t>
+        </is>
+      </c>
+      <c r="B5110" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11017.psd</t>
+        </is>
+      </c>
+      <c r="C5110" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjF5S2FES1EwQ2FDTSs4Y2FNaDlUbXc9PSIsInZhbHVlIjoiZ2haRU15aytVUURxQm9hbHJYM3NoZz09IiwibWFjIjoiODcyYjJiMWI1N2I5ZmMwYmRlZWRjNmVjYzIzMjliM2I1MzA4NDJkYTE4ZmUwMjUwOWM2Y2RkZGUxZGJlMjFjNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5111">
+      <c r="A5111" t="inlineStr">
+        <is>
+          <t>1662.psd</t>
+        </is>
+      </c>
+      <c r="B5111" t="inlineStr">
+        <is>
+          <t>tamilpsd-11018.psd</t>
+        </is>
+      </c>
+      <c r="C5111" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJXS1U0QUtuZTlVdjBXa0k4QWVmQXc9PSIsInZhbHVlIjoiRGFwUVM2bGZBT21MSHBxRE9VdEZhQT09IiwibWFjIjoiZTE4Zjg0OTgzY2ZjMzYzZmJmODZhZDZiM2IzOTFjYjhkODAxOTE3NWM4YTJmMmQxNTQzZTQ5YWYyYjRiNWY2NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5112">
+      <c r="A5112" s="3" t="inlineStr">
+        <is>
+          <t>1587.PSD</t>
+        </is>
+      </c>
+      <c r="B5112" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11019.psd</t>
+        </is>
+      </c>
+      <c r="C5112" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBIR1dlUnp4SmVDMVZaSURMSjZuL3c9PSIsInZhbHVlIjoiL0NsS0dpYXU1ODFqOTF6YzNreGF1QT09IiwibWFjIjoiZjYyNmVhYzQwZmM1NTdkOGY1ZGE4MDIzNzkzNjJlZTNmMTZmMWIxOTFiM2I1NzgxNWRmNDRkOGI0ZmRlOGM3NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5113">
+      <c r="A5113" t="inlineStr">
+        <is>
+          <t>1661.psd</t>
+        </is>
+      </c>
+      <c r="B5113" t="inlineStr">
+        <is>
+          <t>tamilpsd-11020.psd</t>
+        </is>
+      </c>
+      <c r="C5113" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdDV1U5c2MxTi81eVRtVms4akRTU1E9PSIsInZhbHVlIjoicVZIRjd2U2QzS3F2ZzdWOFV2Lyt3dz09IiwibWFjIjoiYjc5ZDViNjU3ZmVkOTU4MzQ5N2RkN2NhY2FjMWE1NzMyYTlkY2MxNmRhYWNhMGM1ZjM3NDAxYmE2ZGMzMjc2YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5114">
+      <c r="A5114" s="3" t="inlineStr">
+        <is>
+          <t>1586.PSD</t>
+        </is>
+      </c>
+      <c r="B5114" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11021.psd</t>
+        </is>
+      </c>
+      <c r="C5114" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklncDFwQWhDN3ZtbzNDT1YvK0NwTkE9PSIsInZhbHVlIjoiMU1jMENGTXFoTG4wQndBTVVtU2g5UT09IiwibWFjIjoiZWFkZGNlYjFlYjBkODU2MWUyOWYzZTE0ZTdkMTJkZDlkOGJjYzk2NGU3NWRhZTQ0YTQ5NTlmODA0MTNjNDE1NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5115">
+      <c r="A5115" t="inlineStr">
+        <is>
+          <t>1585.PSD</t>
+        </is>
+      </c>
+      <c r="B5115" t="inlineStr">
+        <is>
+          <t>tamilpsd-11022.psd</t>
+        </is>
+      </c>
+      <c r="C5115" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklpN3o0R05sOEQwZ21Bbm1vbEY4OGc9PSIsInZhbHVlIjoicnAyYkVieFpCckpZN1YvT2QxcXJZQT09IiwibWFjIjoiZmZkMmVkNTU1YTcxZjdhNDI5ZWFjMzVjZjFiNjFlMTE4YmMzODkwNmUxYzMxOTVhYTAyY2VmNTgwOTQ3OWNkNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5116">
+      <c r="A5116" s="3" t="inlineStr">
+        <is>
+          <t>1584.psd</t>
+        </is>
+      </c>
+      <c r="B5116" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11023.psd</t>
+        </is>
+      </c>
+      <c r="C5116" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVjTVIrY2FISEFCcEVPZVZxZk5EaVE9PSIsInZhbHVlIjoiV2pmajZxTVYzNEllOEhpb081TWUydz09IiwibWFjIjoiMDM4OTQwOWFmMmEwYmM0NWZlYTdjYzE0Njc5ZmEwOGVhOTViNGVhOTA3ZmI4MzRhOGU1ZDBmMDU3YWVlZGVhZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5117">
+      <c r="A5117" t="inlineStr">
+        <is>
+          <t>1583.psd</t>
+        </is>
+      </c>
+      <c r="B5117" t="inlineStr">
+        <is>
+          <t>tamilpsd-11024.psd</t>
+        </is>
+      </c>
+      <c r="C5117" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkVpeE9lSWZrNUMvRFdaajY5WlZQQUE9PSIsInZhbHVlIjoiVHFXVHR6RnBCenY1UkxnZXd1djlMQT09IiwibWFjIjoiN2NlNTk0OWY0MzRlODlhMTE4ZTlmNjJhZmQ1ZTI4ZTU3NTQyNGEwN2I0NTliNjAzMzJlZDhjMmQyYTY1NTNlOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5118">
+      <c r="A5118" s="3" t="inlineStr">
+        <is>
+          <t>1582.PSD</t>
+        </is>
+      </c>
+      <c r="B5118" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11025.psd</t>
+        </is>
+      </c>
+      <c r="C5118" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhuTlg3QlcxQnZmaCtjR0ZCYUh2b1E9PSIsInZhbHVlIjoia3hod2thSGk3elVnNExLdVBWb2wzdz09IiwibWFjIjoiZjRmYTllMmNjMmM5MjZlM2QwM2EyZmQzYzY2MDUxNzYxMmUzMjk2NWYzZjE4ZGZhMDBkNDQyZTMzNDliNzg1OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5119">
+      <c r="A5119" t="inlineStr">
+        <is>
+          <t>1581.PSD</t>
+        </is>
+      </c>
+      <c r="B5119" t="inlineStr">
+        <is>
+          <t>tamilpsd-11026.psd</t>
+        </is>
+      </c>
+      <c r="C5119" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ink5WkxtRzVRUVFsRjhYODBETFhoMHc9PSIsInZhbHVlIjoidG9kaE5hWk9iT2s4ZU84ay93Q0d0dz09IiwibWFjIjoiNTkwZThiMmU3NjJhZTY4YTBlNzg5M2U4MTkwZGE1MGUyNzg5OWRkYzFhMzEyY2RiY2UxZmQxMGFkMjhkNmFlNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5120">
+      <c r="A5120" s="3" t="inlineStr">
+        <is>
+          <t>1580.PSD</t>
+        </is>
+      </c>
+      <c r="B5120" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11027.psd</t>
+        </is>
+      </c>
+      <c r="C5120" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iml4Y3o4VlNEMkNqdTg4L2pyWERqNnc9PSIsInZhbHVlIjoiQ3B6VUZlTjFqT2FST1dkVE1pZWgwdz09IiwibWFjIjoiYzAzMTk4ODVkMDhiZWEyMzkxOTZkMGI4NTZhMWEwODJkYTUwNjc2NDA4ZWEwNTAxNmVmNjY1M2M4YzdiY2QyZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5121">
+      <c r="A5121" t="inlineStr">
+        <is>
+          <t>1579.PSD</t>
+        </is>
+      </c>
+      <c r="B5121" t="inlineStr">
+        <is>
+          <t>tamilpsd-11028.psd</t>
+        </is>
+      </c>
+      <c r="C5121" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFpblZiRGl3TUJQM2h2a3lKY2lTQ0E9PSIsInZhbHVlIjoiRWFROVpyVTFHZlhaR0hOSThWMXRuZz09IiwibWFjIjoiNTFkOWUyN2FiOGJjMDMwNTA0MGNhMzk3MDhmYzEwZjJlOTlhMDZjNmQ0OTM0ZmJiNGU3NmY5Y2MwM2Y0NTE0YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5122">
+      <c r="A5122" s="3" t="inlineStr">
+        <is>
+          <t>1578.PSD</t>
+        </is>
+      </c>
+      <c r="B5122" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11029.psd</t>
+        </is>
+      </c>
+      <c r="C5122" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZzZzFLN1NEZFN3alFKVWd3aHdZV2c9PSIsInZhbHVlIjoiWUFoeGNKd0JLbVB2TFlaamcyQUVjUT09IiwibWFjIjoiMzZmYWE2M2Q0NDhjOWUyOTkyNWM3Y2MzNzMyMjMyMzNjNmIxOWFmOWI1N2U0YjEyNjcwYzExMDhlNzEyYTA5ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5123">
+      <c r="A5123" t="inlineStr">
+        <is>
+          <t>1577.PSD</t>
+        </is>
+      </c>
+      <c r="B5123" t="inlineStr">
+        <is>
+          <t>tamilpsd-11030.psd</t>
+        </is>
+      </c>
+      <c r="C5123" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhvVGxkYmh2dWFTU0VMeDFMUnJWcWc9PSIsInZhbHVlIjoiU2dpZnBLNnFnbXNTekJ4WTltSkZVdz09IiwibWFjIjoiOWI1MGZjNTA1NjJjM2E0NTE1OWY3Mzk5ZjMxM2I3NTkyOWE4NDkwOTVjOTcwZjY2OGE0N2IwMjFmMGU4Yzg3MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5124">
+      <c r="A5124" s="3" t="inlineStr">
+        <is>
+          <t>1576.PSD</t>
+        </is>
+      </c>
+      <c r="B5124" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11031.psd</t>
+        </is>
+      </c>
+      <c r="C5124" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZybmttSG5wVlc3T05zSWFGVWJJT1E9PSIsInZhbHVlIjoiSFRwYTFDWTF1UUVXelNjSjlYd2svdz09IiwibWFjIjoiNjVjODE5M2I2MjQxOTZlYmZjYzg0MDUxYmI3ZDk0MDkwOGFjY2ZlMjM5M2Q5OTIxOTRhNjUwNDgzZWZlMWQ4NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5125">
+      <c r="A5125" t="inlineStr">
+        <is>
+          <t>1575.PSD</t>
+        </is>
+      </c>
+      <c r="B5125" t="inlineStr">
+        <is>
+          <t>tamilpsd-11032.psd</t>
+        </is>
+      </c>
+      <c r="C5125" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlZM2NTdFpuTUxoVXM0NGEzaVFhK0E9PSIsInZhbHVlIjoiQlRYVFBwRkFSVGxlUHB3Y01VcTFGZz09IiwibWFjIjoiY2NlZTJlODcwZjY4NjJhNjVjNmQyZGY4NjE4ZTZmYjJiOWMxYzIzOWU2NWQ2NzNmZjRmMTBiMDJkYjYwMzFhMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5126">
+      <c r="A5126" s="3" t="inlineStr">
+        <is>
+          <t>1574.psd</t>
+        </is>
+      </c>
+      <c r="B5126" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11033.psd</t>
+        </is>
+      </c>
+      <c r="C5126" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNqTmNVZklNZDUvTUJPUGZsQ0Y3N2c9PSIsInZhbHVlIjoiL051TkhnYTg0c1JYUW8rR3hkbG9DZz09IiwibWFjIjoiYmI0M2EyNGEwYjM0NWVhMmM1NjNjZGIwYmQ1ODk0NTI1MjJmNjc3ZDQzZmQ4M2NkYmVmZWJjNjk2MmYxYjZlNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5127">
+      <c r="A5127" t="inlineStr">
+        <is>
+          <t>1573.psd</t>
+        </is>
+      </c>
+      <c r="B5127" t="inlineStr">
+        <is>
+          <t>tamilpsd-11034.psd</t>
+        </is>
+      </c>
+      <c r="C5127" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imk2TE1xQU82WVRlK29SQ0tuOHhUUEE9PSIsInZhbHVlIjoicUxqTUlma0w1THEwL0ZoVE8wV0hzdz09IiwibWFjIjoiYjk1YTc3ZTJhYmEzMTc4Mjk4ZTI1NjZjNzNhYTM0OGQ2NWFlY2NkMWJkZThiYjI0ODYzNjM3ZGY0MDZlNmQ4NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5128">
+      <c r="A5128" s="3" t="inlineStr">
+        <is>
+          <t>1572.psd</t>
+        </is>
+      </c>
+      <c r="B5128" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11035.psd</t>
+        </is>
+      </c>
+      <c r="C5128" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjZ4azdIVzhocjg0K1hvYjRoUFBISFE9PSIsInZhbHVlIjoiY2VjUGwweGZOaWk1aitpb01FTG1WZz09IiwibWFjIjoiZDJjMGIxNjZlYmM1MjMyYmEyNjNhZWQ4MjI1ZDYyZmU1Mjk1MzM3Y2U5MDc2MzQyZmViMDQxZmQwNzUyYzY0YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5129">
+      <c r="A5129" t="inlineStr">
+        <is>
+          <t>1571.psd</t>
+        </is>
+      </c>
+      <c r="B5129" t="inlineStr">
+        <is>
+          <t>tamilpsd-11036.psd</t>
+        </is>
+      </c>
+      <c r="C5129" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVPdGhXellwNCttRlJ0N2FDYTRVYWc9PSIsInZhbHVlIjoiVDBRVnlSL3ZnR2JpUnJCSFV0YnNiQT09IiwibWFjIjoiMDA3ODE1Mjc3ODcwZjE4ZTA0YWNmM2EzNzMyMmRhMGRkNTlhM2YxZDY1Njc0MjljM2QzOWU3MWIwYWFiZWI5YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5130">
+      <c r="A5130" s="3" t="inlineStr">
+        <is>
+          <t>1570.PSD</t>
+        </is>
+      </c>
+      <c r="B5130" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11037.psd</t>
+        </is>
+      </c>
+      <c r="C5130" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImE5NCtlbXkwRWdkdU9TSUJWdk5hZ1E9PSIsInZhbHVlIjoiTFVDYWlvd1RaRUo4eHpxYUhTaDV4dz09IiwibWFjIjoiMzY1ZGY5NGY4MWNjZTljMzhiYzZjYWU1YjkxMDE4OGVmMGEzMTQ1NDJkZDlhNTRiZWMyMTZiNzY1MGE0NjUyOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5131">
+      <c r="A5131" t="inlineStr">
+        <is>
+          <t>1569.psd</t>
+        </is>
+      </c>
+      <c r="B5131" t="inlineStr">
+        <is>
+          <t>tamilpsd-11038.psd</t>
+        </is>
+      </c>
+      <c r="C5131" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVjenBjRlZTQnZtZTJTblVkcmZ4VEE9PSIsInZhbHVlIjoidkZDRncrSldpcS80bFFBTE51eUFzUT09IiwibWFjIjoiOTI3Njc2YWMyZDhkYzkzYzNjNDgzY2JiYzJkMmEwODdmZTQxY2FhYWQ2YzY2YTRlOTkzZDFjNTgzNGNlYjQxMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5132">
+      <c r="A5132" s="3" t="inlineStr">
+        <is>
+          <t>1568.PSD</t>
+        </is>
+      </c>
+      <c r="B5132" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11039.psd</t>
+        </is>
+      </c>
+      <c r="C5132" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkhOVVR3aTNGZGlSdWY2cWJXdzJTWFE9PSIsInZhbHVlIjoiSVJ4bnRCeUg5bWVraE5ISG12dGF2QT09IiwibWFjIjoiNGVkMTEzYjI0MzljNjNhOGUwZjVjYzQ5ZTJjMDBhMzVlZDVjZGVjNTdmZWMwOTI2MmUyMWNlZjU2NDc2ZThmMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5133">
+      <c r="A5133" t="inlineStr">
+        <is>
+          <t>1567.PSD</t>
+        </is>
+      </c>
+      <c r="B5133" t="inlineStr">
+        <is>
+          <t>tamilpsd-11040.psd</t>
+        </is>
+      </c>
+      <c r="C5133" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNlWkZzQldwTHFsQjFhbjh5WjgxU1E9PSIsInZhbHVlIjoiMmxLamd1aHN4cVJWUGs0V1NXdWMrdz09IiwibWFjIjoiOTU1MGJiOTQxMDQxMWVmMzY2YzU1NzNlMjNkYjkwNmE3N2M3MGJjMTgxNjY5YzI4ZWIyNzVlMjI1ZWMyMWY5YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5134">
+      <c r="A5134" s="3" t="inlineStr">
+        <is>
+          <t>1566.psd</t>
+        </is>
+      </c>
+      <c r="B5134" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11041.psd</t>
+        </is>
+      </c>
+      <c r="C5134" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpTYXYzVWloZ1pJbzJNN05aM3RxeEE9PSIsInZhbHVlIjoiMFZ0VnMra3h5b0hlcHc0d0FTT1dxZz09IiwibWFjIjoiNjRmYjE2OWY0ZDE4ZjhiMzlkMjhkZTEwZDlmMDc4OGFkODgwNDhiZDIxNWVlMzc2Mjk0ZWMxOWI1ODZiODU2YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5135">
+      <c r="A5135" t="inlineStr">
+        <is>
+          <t>1564.psd</t>
+        </is>
+      </c>
+      <c r="B5135" t="inlineStr">
+        <is>
+          <t>tamilpsd-11042.psd</t>
+        </is>
+      </c>
+      <c r="C5135" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhuL2JsRldTSmZ1UmFEazdOcC9XalE9PSIsInZhbHVlIjoiQXVGMWFpQzFRT3czZWNNR1lnUFdkUT09IiwibWFjIjoiOTQzYmJmYjdlY2Q4MzhhOGFlZDQ4NmMyZTJlNWFhNjIxMDM4YTA2ZTU5YWNhYTQ5OTRmZTIyN2I0OTg4MGVhZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5136">
+      <c r="A5136" s="3" t="inlineStr">
+        <is>
+          <t>1563.PSD</t>
+        </is>
+      </c>
+      <c r="B5136" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11043.psd</t>
+        </is>
+      </c>
+      <c r="C5136" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik0rRDlRa1FvWmVCMkpjamJRbGpzQlE9PSIsInZhbHVlIjoiNmpySDlSTllsK0s4WFBuYTBXdHZOUT09IiwibWFjIjoiZmRmZDUwYzA2ZjVkZTQyZGU4ZTZlMGVlN2NlMzA5MTg1YzJiMjM2NDg1YzI5OWEzZGE4MzI0M2I4MDdlYzQzMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5137">
+      <c r="A5137" t="inlineStr">
+        <is>
+          <t>1562.psd</t>
+        </is>
+      </c>
+      <c r="B5137" t="inlineStr">
+        <is>
+          <t>tamilpsd-11044.psd</t>
+        </is>
+      </c>
+      <c r="C5137" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImkyZ3N2eUFQYTVzUGc3cDlGZ2ZWNEE9PSIsInZhbHVlIjoiQkV4L041d1FiT3F3MHlzL2RGSEdtZz09IiwibWFjIjoiOTM2MDA0M2RiMTc3MmIzOTU2YzJmOTY5OWFiNGJmNTY5NTQxM2E4ZDYwOTA5MjM1ZGZhM2JjMjU5NDk4Mjk3ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5138">
+      <c r="A5138" s="3" t="inlineStr">
+        <is>
+          <t>1561.psd</t>
+        </is>
+      </c>
+      <c r="B5138" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11045.psd</t>
+        </is>
+      </c>
+      <c r="C5138" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNWRmQyWU02cnRNY3FTNndpcHQraHc9PSIsInZhbHVlIjoiTFIrUEtpa1dYSHhTMFU3Z1RVcWx5QT09IiwibWFjIjoiMTNlZTQ3YmZkZWY5MzA4OTA5YTBmOWUzOTFlZjY1M2E2MTY5MzUyZmQxNDk0MTFhYjY4ODE1ZjgxOGUyZjFkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5139">
+      <c r="A5139" t="inlineStr">
+        <is>
+          <t>1560.PSD</t>
+        </is>
+      </c>
+      <c r="B5139" t="inlineStr">
+        <is>
+          <t>tamilpsd-11046.psd</t>
+        </is>
+      </c>
+      <c r="C5139" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRLbjZkZ240YmtoRjlYbUtvaGxmRHc9PSIsInZhbHVlIjoibVBrU2VITkp2emhHcHd0Q1hPMmh4QT09IiwibWFjIjoiMDUzNjlmZTQ3OTliZjczYjI3ZDQ5OTA3YzZmNWVkNjE2YjIzYWI4MDNkNGFjNjIxZDU4YzA1MDAzMmRmMTQwZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5140">
+      <c r="A5140" s="3" t="inlineStr">
+        <is>
+          <t>1559.psd</t>
+        </is>
+      </c>
+      <c r="B5140" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11047.psd</t>
+        </is>
+      </c>
+      <c r="C5140" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhpL0hRZHNjNTJDa2dKLzVKVitBakE9PSIsInZhbHVlIjoiVUNLSG4ydFlZNGV5b0ZRcFo5ck1iZz09IiwibWFjIjoiZjM0NWUwM2ZiYmFhOTg3YjQ4NmJhODVmNGJlOTkzOWM3MDY1MjFmYzFiNmViZDg0Nzc2MWM2NTQyOTE0YWVjOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5141">
+      <c r="A5141" t="inlineStr">
+        <is>
+          <t>1558.PSD</t>
+        </is>
+      </c>
+      <c r="B5141" t="inlineStr">
+        <is>
+          <t>tamilpsd-11048.psd</t>
+        </is>
+      </c>
+      <c r="C5141" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVzcjZTRzg4N0hjR1NnT1VudFZXQVE9PSIsInZhbHVlIjoiU0djeVp5dkxYamgyNmlkVk40NkpSdz09IiwibWFjIjoiYWZiNjBlNWRhYWMxNjMyMTc0NmY4ZjY1ZTg2OTQ3M2NiMDczNzVjMjg3YTA5OTBmMjczMmI3MzBiYzNmYWNkYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5142">
+      <c r="A5142" s="3" t="inlineStr">
+        <is>
+          <t>1557.PSD</t>
+        </is>
+      </c>
+      <c r="B5142" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11049.psd</t>
+        </is>
+      </c>
+      <c r="C5142" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRZQmVZUW5DVkVvSHJjeW8wU0dhc2c9PSIsInZhbHVlIjoiREFPVGRCU3Y0bDhKRHRMa1pBcEVnZz09IiwibWFjIjoiZTQ1MzhlOGQ0Zjk3OGQ2MzhjNmY5MzU0ZWMzNTBhNjVlODljMjQ4MWIxMzQ5ZGZjZjdmZTBmY2MyM2FmYmU2MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5143">
+      <c r="A5143" t="inlineStr">
+        <is>
+          <t>1556.PSD</t>
+        </is>
+      </c>
+      <c r="B5143" t="inlineStr">
+        <is>
+          <t>tamilpsd-11050.psd</t>
+        </is>
+      </c>
+      <c r="C5143" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5JK2xVZERlMjA4Q2pPZkM2am9Gc0E9PSIsInZhbHVlIjoiMFErZ3VUbDkrc21wRVhnYWE3L1ZaUT09IiwibWFjIjoiZjU5MWNiMmExZTQ5Njc0ZGNhYjliZTdhYTEzZTU2YzYwNGI0NjA0YTFiMzg5OWExYTdjNmFiMGVmNTk1ZGM3OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5144">
+      <c r="A5144" s="3" t="inlineStr">
+        <is>
+          <t>1555.PSD</t>
+        </is>
+      </c>
+      <c r="B5144" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11051.psd</t>
+        </is>
+      </c>
+      <c r="C5144" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijk0cVBYZ3lrU2hCSHFEUk5oanIvanc9PSIsInZhbHVlIjoiYnlxNElybmFWWVQybzRvWWlHVE9DZz09IiwibWFjIjoiYTdkYzMxMWQyNDRhNjZiZTQyNmNhOTUwM2E5MjFlMDRmY2JiN2E1YjU2NWQxYTczZmI4YzEwMjBjZTYzOWMyOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5145">
+      <c r="A5145" t="inlineStr">
+        <is>
+          <t>1554.PSD</t>
+        </is>
+      </c>
+      <c r="B5145" t="inlineStr">
+        <is>
+          <t>tamilpsd-11052.psd</t>
+        </is>
+      </c>
+      <c r="C5145" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InpRRkNLRG9Yc0ZVMk1NZmVIUVpTcWc9PSIsInZhbHVlIjoiYVBlM3F5cm9HZFlzd2tzVmxXUDI5UT09IiwibWFjIjoiYTMzNWQ5MWQxODI4YTQ3ZTNkMmFhYWM1YjQyM2E4MTRjY2RmYzM0ODdjMTY1ZDllODBhNTYwOTY0NDc0YzRiZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5146">
+      <c r="A5146" s="3" t="inlineStr">
+        <is>
+          <t>1553.psd</t>
+        </is>
+      </c>
+      <c r="B5146" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11053.psd</t>
+        </is>
+      </c>
+      <c r="C5146" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImQyMmgxb0NpUVR5M0xVNlJMVVJ1MkE9PSIsInZhbHVlIjoidnVndGFKWFdKVXdBM3pUV3NzNFNuZz09IiwibWFjIjoiM2ZkOGZjZjc0YTRlYWVjMWEzNDViMWU2ZTdiZjVmMDQwYTZmZjg0YTc2MTZjMzg2ODFjNTI1OTUyZTk2MzUyNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5147">
+      <c r="A5147" t="inlineStr">
+        <is>
+          <t>1552.PSD</t>
+        </is>
+      </c>
+      <c r="B5147" t="inlineStr">
+        <is>
+          <t>tamilpsd-11054.psd</t>
+        </is>
+      </c>
+      <c r="C5147" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImV6cndnUFpjOUtsOC9wd0h6QTM2b2c9PSIsInZhbHVlIjoiRVFhRDA4S1B3VGxleTY4aFo5VjRTUT09IiwibWFjIjoiZTNkZDM2MzRlYjU1MTIzOWZhMjEwODEyOTNiZjEyNjU3YTRlMzM2NGE5ZWI2MTRlYTFmMGQ2MTIyNjcwNWUwYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5148">
+      <c r="A5148" s="3" t="inlineStr">
+        <is>
+          <t>1551.psd</t>
+        </is>
+      </c>
+      <c r="B5148" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11055.psd</t>
+        </is>
+      </c>
+      <c r="C5148" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlqaXZVMnVoUzQ3d0JoTmZGbGF2WVE9PSIsInZhbHVlIjoidzlNOXN4ZmowS3FWMzVtZnJvQnJaZz09IiwibWFjIjoiOWRkMjIzNTAxYjVkNDgzOWQ4ZDgxYzY1NzAyNzQ3OGE1M2EyNzU2MjMwMzZmOWRjN2RkNWVkYmZkYjE3NmY3MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5149">
+      <c r="A5149" t="inlineStr">
+        <is>
+          <t>1550.PSD</t>
+        </is>
+      </c>
+      <c r="B5149" t="inlineStr">
+        <is>
+          <t>tamilpsd-11056.psd</t>
+        </is>
+      </c>
+      <c r="C5149" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iko5RVpBSFNseDRmTnJYZWxXbllHekE9PSIsInZhbHVlIjoiaVV3NDkzQUV5alpaNHlSVHFLc0xYdz09IiwibWFjIjoiZmU3OWJlYjY3OGU1MTk5OGFjZmRhMzEzZWVkNWNjZWIzNWRiMTNjYmRkODg3ODU0YWNkYTA1ZDRhNjQzMjljOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5150">
+      <c r="A5150" s="3" t="inlineStr">
+        <is>
+          <t>1549.PSD</t>
+        </is>
+      </c>
+      <c r="B5150" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11057.psd</t>
+        </is>
+      </c>
+      <c r="C5150" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNISzg0U2o3S1R1Tmg2cDdmek5jeHc9PSIsInZhbHVlIjoiZmpmdEx6aEZ4dGsyU0JUdHdwdkoyUT09IiwibWFjIjoiZTFhMWQwYmYzNDVmNDJmMDY0NzMyMjc1ZjgyZmE5MjEwMTQ2YTJmYzkzNDA4ODBlMjVlNjg4ODQ4ZjI4NzA3NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5151">
+      <c r="A5151" t="inlineStr">
+        <is>
+          <t>1548.psd</t>
+        </is>
+      </c>
+      <c r="B5151" t="inlineStr">
+        <is>
+          <t>tamilpsd-11058.psd</t>
+        </is>
+      </c>
+      <c r="C5151" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjV1RjdKZE5zays1T3d2b0pYNHBGTlE9PSIsInZhbHVlIjoiRGR6b3llRTRJVFM2SWZhaUN1MHFxQT09IiwibWFjIjoiNGFmODY4NGQyNGRjM2I5OWUwZmVmMWJjOGExYzY3Zjc2YWY3Mzc3MzVjYjAzMTljMTAyN2E1MzVhNjA5M2U2ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5152">
+      <c r="A5152" s="3" t="inlineStr">
+        <is>
+          <t>1547.psd</t>
+        </is>
+      </c>
+      <c r="B5152" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11059.psd</t>
+        </is>
+      </c>
+      <c r="C5152" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iks2NGQ0Mm9Qdm9DOFczWFE1MkdKY0E9PSIsInZhbHVlIjoiWEJScmxLTzYrR0tKTEFSSDJqZUwwUT09IiwibWFjIjoiNjYzYjA3ZmZjMmY5YjhjZjI1YzgxMDEyMTUyOWY1ZTNkZmRkYzU0MGQwYTk5MjZhNDc5MmNlNzUxNTJmZTkxNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5153">
+      <c r="A5153" t="inlineStr">
+        <is>
+          <t>1546.psd</t>
+        </is>
+      </c>
+      <c r="B5153" t="inlineStr">
+        <is>
+          <t>tamilpsd-11060.psd</t>
+        </is>
+      </c>
+      <c r="C5153" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZiNmIveVp3OWxlVkd5akRGVjZGSnc9PSIsInZhbHVlIjoiNDNxVjdCSGwrWFFsLzVPOWtaa28rZz09IiwibWFjIjoiODk2NzdmYjAyNWJjYjY5ZjMzYjE5ZTVkZjg1NmVlMWI1ZTMwY2NhM2EzZGFmYTA0Nzk5ZGRjYTdjYTA5MDZmNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5154">
+      <c r="A5154" s="3" t="inlineStr">
+        <is>
+          <t>1545.psd</t>
+        </is>
+      </c>
+      <c r="B5154" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11061.psd</t>
+        </is>
+      </c>
+      <c r="C5154" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdGVWdVSzl5RkZNSU9kZ2xvbnhGNHc9PSIsInZhbHVlIjoiYytnUTJkRmhoTU1Sa0k2MXZseVk0dz09IiwibWFjIjoiNjdkNWFjODc4ZjRlMDBmZTM5OGM2NmM3NDE0ZDkxZjlhNTA1YjQ1N2Y5N2JhMWUxOTQ3NDNiZWVmZmFlNzQ5MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5155">
+      <c r="A5155" t="inlineStr">
+        <is>
+          <t>1544.PSD</t>
+        </is>
+      </c>
+      <c r="B5155" t="inlineStr">
+        <is>
+          <t>tamilpsd-11062.psd</t>
+        </is>
+      </c>
+      <c r="C5155" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InRUSXBLRFNlUHk1YzM2U0dJTmljaWc9PSIsInZhbHVlIjoiT2RtRnZrbUhDTjB3MUo4UFo5ZmpOUT09IiwibWFjIjoiOTAyNjFkNjgzZDFkYjE0YzRkYmI1ZWExYzdmNmE2YzgzZTFjNWM2ODI3YjQ4MzdjNGMzZmUxMmRkYWI5YjY0MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5156">
+      <c r="A5156" s="3" t="inlineStr">
+        <is>
+          <t>1543.PSD</t>
+        </is>
+      </c>
+      <c r="B5156" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11063.psd</t>
+        </is>
+      </c>
+      <c r="C5156" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InE0QWJ5dzJFTzVjMmdBTC9nYTFkMnc9PSIsInZhbHVlIjoicmQxWHNKRHNIaUVHa2UwQkd1cmhEdz09IiwibWFjIjoiNDY1YzljMmY4ZTNhM2I5NmUzZDUyNGIyNzg0MTVlZWYxMWY4ZDZkMGQxYWFjYWQ0YzI1Y2E1ODQ1MDIyYTU2YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5157">
+      <c r="A5157" t="inlineStr">
+        <is>
+          <t>1542.psd</t>
+        </is>
+      </c>
+      <c r="B5157" t="inlineStr">
+        <is>
+          <t>tamilpsd-11064.psd</t>
+        </is>
+      </c>
+      <c r="C5157" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InpXZWRXUjBJK1ExLzJMWWpTdmlJdnc9PSIsInZhbHVlIjoiamg5Zk1ZdDRnVStTUytMeTJEbUJTUT09IiwibWFjIjoiYmY5YmQwNThkOWJmNjBiMDBlMzE0YTFlNjIwZjc0OWM2M2U1Y2M1NDUwNzg1NjRkMzkzNzU0YzU0MjM4ZDRkNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5158">
+      <c r="A5158" s="3" t="inlineStr">
+        <is>
+          <t>1541.PSD</t>
+        </is>
+      </c>
+      <c r="B5158" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11065.psd</t>
+        </is>
+      </c>
+      <c r="C5158" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IitSMlErMmRkRjYxZHpEZWRrY0tiWlE9PSIsInZhbHVlIjoicktKUFZ1MXd6bEJPT05TbDFTQVhPUT09IiwibWFjIjoiZDNjOGQ3ZDQyODExYjNkNWQyODgyOTVlYzdkMmJiOTJlNzBmMTFkMTkzMTMwOGU0YjViMDY3ZGNlMTM1MjkwYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5159">
+      <c r="A5159" t="inlineStr">
+        <is>
+          <t>1540.PSD</t>
+        </is>
+      </c>
+      <c r="B5159" t="inlineStr">
+        <is>
+          <t>tamilpsd-11066.psd</t>
+        </is>
+      </c>
+      <c r="C5159" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlMOWNrU0dhSGNOaEh1bDZvZS92OFE9PSIsInZhbHVlIjoiRDdVT3BBKyt0RmxpaWVUaEdoUVVJQT09IiwibWFjIjoiZTQ4YzY2NzE4M2ZhYjQwZDZhMmM1M2JiODk2Y2ExOTUxYzMwYjIwZmIxZTE5MDhlMjQ3MGVlYWZmZTlhMDhmZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5160">
+      <c r="A5160" s="3" t="inlineStr">
+        <is>
+          <t>1539.PSD</t>
+        </is>
+      </c>
+      <c r="B5160" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11067.psd</t>
+        </is>
+      </c>
+      <c r="C5160" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik04VzRqRmFjTVR5Z3RFVGREeHM0Q2c9PSIsInZhbHVlIjoiTGRSYzMxblZMa1dRZFZsME51aHE3UT09IiwibWFjIjoiNThmYTZmYzIwM2Q5ZTY0YmRhODcwY2RmZjAzOTQ5YzU0YWQwZTYzZGY5YzliYWYyNmVlYmYxNThjNjk5YWUxZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5161">
+      <c r="A5161" t="inlineStr">
+        <is>
+          <t>1538.PSD</t>
+        </is>
+      </c>
+      <c r="B5161" t="inlineStr">
+        <is>
+          <t>tamilpsd-11068.psd</t>
+        </is>
+      </c>
+      <c r="C5161" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpPalh2WkltQW5ZS3NpY2ZzeksrcUE9PSIsInZhbHVlIjoiN2xLRnVZMGVyRyt4NWRhdjlqSVY0UT09IiwibWFjIjoiOTExOTM3NWM2ODRhNjkwYjVkMGFmNGJmNzg2ODBjZDY5NzMzOGNhNjMzMjhhOTg2NTgwNjNiN2RhYjdhZDEyZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5162">
+      <c r="A5162" s="3" t="inlineStr">
+        <is>
+          <t>1537.PSD</t>
+        </is>
+      </c>
+      <c r="B5162" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11069.psd</t>
+        </is>
+      </c>
+      <c r="C5162" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxJTm9NTXlPYTY1SHBKeHFBRXZuSUE9PSIsInZhbHVlIjoiVWlwb21hVEg3MUMxVEdlQVRmUW8wdz09IiwibWFjIjoiNjkwYTc2OTgwOGRhNDExZWRmMmZjNzkwOTIyYjVmZGU3MDhjMjcxMjYwNTFhYTUwYzIwNzI3OTVlODVlZmZiNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5163">
+      <c r="A5163" t="inlineStr">
+        <is>
+          <t>1536.PSD</t>
+        </is>
+      </c>
+      <c r="B5163" t="inlineStr">
+        <is>
+          <t>tamilpsd-11070.psd</t>
+        </is>
+      </c>
+      <c r="C5163" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNYZ3RQbE9tdmVCVDVRcFZlNWhrWEE9PSIsInZhbHVlIjoiRUhycmJzM0NRVDMzaXZub2FDaGVudz09IiwibWFjIjoiMjQxOTY3YmVlOGFhZTdlYjlmYzFjMDBlZTc0NjdiOGY4YTY2NDk1NjQ4Mjk4MTJiMjMyYmZiYjc5YTk0ZGM2NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5164">
+      <c r="A5164" s="3" t="inlineStr">
+        <is>
+          <t>1535.PSD</t>
+        </is>
+      </c>
+      <c r="B5164" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11071.psd</t>
+        </is>
+      </c>
+      <c r="C5164" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjRYd1JydGVHdDZ5Zm1KdDI0b0lyQmc9PSIsInZhbHVlIjoic1c0elU5Y1hDZGZSZGlxKzVCWW8wQT09IiwibWFjIjoiMWJmMGIwMjdkNTNkNjEzMWZkMThiOWVmMmE4OGRjYjZiMDFmMWIwNDE5MmNkODJiZWUxYTQxYTQ2Mzg5MjVlOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5165">
+      <c r="A5165" t="inlineStr">
+        <is>
+          <t>1534.PSD</t>
+        </is>
+      </c>
+      <c r="B5165" t="inlineStr">
+        <is>
+          <t>tamilpsd-11072.psd</t>
+        </is>
+      </c>
+      <c r="C5165" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9FNUxSUmFUMjRLYkNrd0o4eWtyWEE9PSIsInZhbHVlIjoiN01uWC9RaWk5VFRiZ20xaVVIZFIxUT09IiwibWFjIjoiZGM4MTQ4ZjYzZTQxYTExN2Q1NjAwZWQ2YTY4YThhM2YwN2QzMTVlM2E2MWVmMDJhY2M3ZDFjYzk1MjUyODk0OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5166">
+      <c r="A5166" s="3" t="inlineStr">
+        <is>
+          <t>1533.PSD</t>
+        </is>
+      </c>
+      <c r="B5166" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11073.psd</t>
+        </is>
+      </c>
+      <c r="C5166" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBsSXJXU0lCeFlhbmR5VG04TjdES1E9PSIsInZhbHVlIjoiOEFoTzBZSkpwK1hpbERKWnppM1BHdz09IiwibWFjIjoiYzQyMDljM2JmODg5MTJmMjUwNmIwZmVhYjNkYzk1MTAxMGE4NzJiMTE4NzZmYTM2MDI4ZjJlMjdkOGQxN2Q2MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5167">
+      <c r="A5167" t="inlineStr">
+        <is>
+          <t>1532.PSD</t>
+        </is>
+      </c>
+      <c r="B5167" t="inlineStr">
+        <is>
+          <t>tamilpsd-11074.psd</t>
+        </is>
+      </c>
+      <c r="C5167" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlErNGFmVGRFVE9Qc3Z2eU1FMTdvOUE9PSIsInZhbHVlIjoiQjhpQ2tzcW9sYi90MytXd2RLVENMZz09IiwibWFjIjoiZDYwYWY1NjJiMmVkNjY1MDE2ZjE4NjhlOWU4MGEyYzI3NmJiMWE2YWFlNGJmMGQ3ZGZmZDdmYTk5NWMxNWJkMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5168">
+      <c r="A5168" s="3" t="inlineStr">
+        <is>
+          <t>1531.PSD</t>
+        </is>
+      </c>
+      <c r="B5168" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11075.psd</t>
+        </is>
+      </c>
+      <c r="C5168" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik51eHpOUFRjbGd6dUNyRndpZkhJeGc9PSIsInZhbHVlIjoiZnZDWFNZZW4rTXZ3OEV2emYvcWhyQT09IiwibWFjIjoiNDY0NGIyNTNkZjEwMDk0Y2RiYjI2Y2I3MzFiZmY5Y2NjN2NmZjg1NzY4MTcxYzNjN2JjYTYxYTczMmRkODU3MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5169">
+      <c r="A5169" t="inlineStr">
+        <is>
+          <t>1530.PSD</t>
+        </is>
+      </c>
+      <c r="B5169" t="inlineStr">
+        <is>
+          <t>tamilpsd-11076.psd</t>
+        </is>
+      </c>
+      <c r="C5169" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkR4a1UwZ1ByWGJGQ1cvL1JoVTlMclE9PSIsInZhbHVlIjoidEErcHVZOVFISGxUQ25JWmV4OTEwZz09IiwibWFjIjoiYjc5NTViNTAyZDNjOWNiMTFiZmUzNDA2YzJiNTU0MTQyYmQzZmIxMDA3Zjg5ZjMxZTViNDM2Y2I2Y2I4NzdhYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5170">
+      <c r="A5170" s="3" t="inlineStr">
+        <is>
+          <t>1529.PSD</t>
+        </is>
+      </c>
+      <c r="B5170" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11077.psd</t>
+        </is>
+      </c>
+      <c r="C5170" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktyaXdBS0ZOWWY5WHVtRzZGUnVDVEE9PSIsInZhbHVlIjoiWVdsT0hZUzd0REI0SXY4eTRKRFhNQT09IiwibWFjIjoiOWQxMTc3MmFmMzUxZjExMDMwYmE2MjM0ODUxODM2YTk1NDVjYTc4YjY4NjU1NWUwYzNlMDczYWQ4YjQwNTFmNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5171">
+      <c r="A5171" t="inlineStr">
+        <is>
+          <t>1528.PSD</t>
+        </is>
+      </c>
+      <c r="B5171" t="inlineStr">
+        <is>
+          <t>tamilpsd-11078.psd</t>
+        </is>
+      </c>
+      <c r="C5171" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNjNGFIY0x2S1dqaTRHQzZUSGtuMVE9PSIsInZhbHVlIjoiNVpJT3BpY0phTmpySWhOY0M5QVE5Zz09IiwibWFjIjoiYTJkNDJlZWU1ZDk5NDJiZTJkMDI4ZDc5MjM4ZWVjODFiZjFiYzdmY2Q4N2FhOWZjNWE4M2VhNzMxNmI0NDI1NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5172">
+      <c r="A5172" s="3" t="inlineStr">
+        <is>
+          <t>1527.PSD</t>
+        </is>
+      </c>
+      <c r="B5172" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11079.psd</t>
+        </is>
+      </c>
+      <c r="C5172" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkErdUVGL25lcTk5c0d1eEgxOGxEelE9PSIsInZhbHVlIjoidStVUDRHanNzOC90ZU45dEZYWHBiZz09IiwibWFjIjoiZTNiODQxMDY0Y2Q2ODgzYzRhMTcyOWZiNDViMGZlNjdhNjI0YzFkNWI1NGM4MTdjNzBmMjRmNjc5Y2U3YjNlZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5173">
+      <c r="A5173" t="inlineStr">
+        <is>
+          <t>1526.PSD</t>
+        </is>
+      </c>
+      <c r="B5173" t="inlineStr">
+        <is>
+          <t>tamilpsd-11080.psd</t>
+        </is>
+      </c>
+      <c r="C5173" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlvbUllK2NuVVlYamg5amIvdGlzVGc9PSIsInZhbHVlIjoiV3hNay8wTWxaN2s4ZzJBZjE1S0tidz09IiwibWFjIjoiMzFlNTM0NGZjNGMzNjQ1NTUyODEwYWNhZTI0ZjZkYzM2MDIyOGFkYWFkZTU4ODE2ODM5YWM3ZGU4OGNhZDhhMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5174">
+      <c r="A5174" s="3" t="inlineStr">
+        <is>
+          <t>1525.psd</t>
+        </is>
+      </c>
+      <c r="B5174" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11081.psd</t>
+        </is>
+      </c>
+      <c r="C5174" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlQ3T2VFY2dTc094eU85bi9Iek1TM0E9PSIsInZhbHVlIjoickswZkcydjFCeEx5RWt3d0VmMjhTZz09IiwibWFjIjoiODBhZTRiOTZmZWFiZDBlYThlYTRmZTg3MzdkYWY0YjNiNGRmMDAwM2NlYmNkZjUwZDljOTM2ODliYjQ5Mzg4ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5175">
+      <c r="A5175" t="inlineStr">
+        <is>
+          <t>1524.PSD</t>
+        </is>
+      </c>
+      <c r="B5175" t="inlineStr">
+        <is>
+          <t>tamilpsd-11082.psd</t>
+        </is>
+      </c>
+      <c r="C5175" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtWYktqdm9xU1cxdTFUbXgvb0FlNGc9PSIsInZhbHVlIjoiemp5cDdVS0tUSk1LWjJmSmJzaE5hQT09IiwibWFjIjoiYzA5ODM1Mzk1MWE3YjliMjEwYjhkODg2OWM2MGQ2NjVkZDI5ZjA4ODc2ZTNmOGM1ZDRjZGQ1NzViNjZiYzBhYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5176">
+      <c r="A5176" s="3" t="inlineStr">
+        <is>
+          <t>1523.PSD</t>
+        </is>
+      </c>
+      <c r="B5176" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11083.psd</t>
+        </is>
+      </c>
+      <c r="C5176" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik90dERVSEpIK2NXMjkvY2Nxb1JuRGc9PSIsInZhbHVlIjoiTERJVGx0bGc4Z0tyTVhNOCtVTHN5dz09IiwibWFjIjoiZDc4Y2M4MTgyMDM5NjU0MTdkM2E2NzU4OGI5MjE5ODg3ZDRlZTgyN2RiZDkwMmU3NTYwNzRhMmJjY2NlNDhhYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5177">
+      <c r="A5177" t="inlineStr">
+        <is>
+          <t>1522.psd</t>
+        </is>
+      </c>
+      <c r="B5177" t="inlineStr">
+        <is>
+          <t>tamilpsd-11084.psd</t>
+        </is>
+      </c>
+      <c r="C5177" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklBQXNaVC9ZbDd4aTNBVW1xdm9UdVE9PSIsInZhbHVlIjoiSHZHcEdEMzEzdjMxSGk0QlQ2KzVPZz09IiwibWFjIjoiYTExNGY5MGJhMGU1ZTA0M2EzNWIxNDViYTY0N2QxOTI4YmU0OTczOTZhNjcwN2QyYWE2NWE2ZmQ3NzUwZTU3ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5178">
+      <c r="A5178" s="3" t="inlineStr">
+        <is>
+          <t>1521.psd</t>
+        </is>
+      </c>
+      <c r="B5178" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11085.psd</t>
+        </is>
+      </c>
+      <c r="C5178" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1sZERobVRyYnYvbGkyUlhFNXFRMkE9PSIsInZhbHVlIjoid1V6VCswc0JodUF1YVJKRkNoSnkzZz09IiwibWFjIjoiYjllOTkyOTMxYThiNzdhNjI1OTk4MDkzNzViNzkxMzk0MTI4ODZhMjJjMjZkOGQwMWU1ZDNlNGYzMjFhZDY5MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5179">
+      <c r="A5179" t="inlineStr">
+        <is>
+          <t>1520.psd</t>
+        </is>
+      </c>
+      <c r="B5179" t="inlineStr">
+        <is>
+          <t>tamilpsd-11086.psd</t>
+        </is>
+      </c>
+      <c r="C5179" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImszWmFzQnI0dHN3Z2ZHaHhVVThlcnc9PSIsInZhbHVlIjoiNlNheFl1U1B5eEhvOTV5NjZHd3BJdz09IiwibWFjIjoiMGIwMzI3N2VhZTUyODJkMGE1MmM1MTUxNGRjZDEyNzcyMTJhMWZiOGY5NjI5Y2E4YTZhOWUzZTU0ZmFhMGRiNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5180">
+      <c r="A5180" s="3" t="inlineStr">
+        <is>
+          <t>1519.PSD</t>
+        </is>
+      </c>
+      <c r="B5180" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11087.psd</t>
+        </is>
+      </c>
+      <c r="C5180" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpnUWVDdFJMQ1RCSDdrZGNrUHFIdXc9PSIsInZhbHVlIjoiSVU0VXAveXp3dUs4RWdYNGN0U2E1QT09IiwibWFjIjoiOWRjNzAxY2NhYzVjOGE5ZWMzZmViMWUzZjhmMjE5NjQ1N2U0ZjdjNjU1NTZkZGEwZDMzN2FkOGU0YzAwZjAxZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5181">
+      <c r="A5181" t="inlineStr">
+        <is>
+          <t>1518.psd</t>
+        </is>
+      </c>
+      <c r="B5181" t="inlineStr">
+        <is>
+          <t>tamilpsd-11088.psd</t>
+        </is>
+      </c>
+      <c r="C5181" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhtTlRIVXJHeVB6SXc1eUlMd05mcUE9PSIsInZhbHVlIjoibG1YZjF0SVVrRm0ySGFQNGZHOWRFZz09IiwibWFjIjoiOGZjZDBlOWYxNDc1OGNjODFiODY5MTc5YmZjZjNhNDYzNzI5ZmRhNjU1ZDEwYTQ2ZDRlMjkzZmJlZDhlYzAyZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5182">
+      <c r="A5182" s="3" t="inlineStr">
+        <is>
+          <t>1517.psd</t>
+        </is>
+      </c>
+      <c r="B5182" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11089.psd</t>
+        </is>
+      </c>
+      <c r="C5182" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFEN280Tm5UYmkzakQ4dXhnRGdLVHc9PSIsInZhbHVlIjoiTVU5eGNXMS8wWm4vQm1BVExZWXo1UT09IiwibWFjIjoiYTQ1ZGI2ZjAzN2I1MzMyZGVhMGEzODJhNTQ1ZDlhNTQ3YWU3MGU0MjNlNTUwYTQ0Zjc5ZDk4Mjc2N2Y1ZDYzMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5183">
+      <c r="A5183" t="inlineStr">
+        <is>
+          <t>1516.psd</t>
+        </is>
+      </c>
+      <c r="B5183" t="inlineStr">
+        <is>
+          <t>tamilpsd-11090.psd</t>
+        </is>
+      </c>
+      <c r="C5183" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjZEMWVTZjVNRGh2b3dKVmtFVXVjMHc9PSIsInZhbHVlIjoiMnFIdXRqQUhMUzhXcmx4WkhPUjNKZz09IiwibWFjIjoiYTkxMjJjY2M1ZThjOTMxM2JiMWEyNGUxOTExMzQxYzAyZmFhZmRmMDZmODA5MzJmNjE1OGYyM2E2OGMyNjMyMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5184">
+      <c r="A5184" s="3" t="inlineStr">
+        <is>
+          <t>1515.psd</t>
+        </is>
+      </c>
+      <c r="B5184" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11091.psd</t>
+        </is>
+      </c>
+      <c r="C5184" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjRWdFk4cUVQVnViaWZjVUVnYWxTbHc9PSIsInZhbHVlIjoiVklMdElPSEVVa2N4VE5QQ3dWWGcwQT09IiwibWFjIjoiNTk1NDM4MjBhYmE2ODM1ODk1MzdmNmU2NGVhMDM5MjIxNjNlMGQzMjc2YTk5ZWRlMzdmNGMzYzA4MDgzMmYyNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5185">
+      <c r="A5185" t="inlineStr">
+        <is>
+          <t>1514.psd</t>
+        </is>
+      </c>
+      <c r="B5185" t="inlineStr">
+        <is>
+          <t>tamilpsd-11092.psd</t>
+        </is>
+      </c>
+      <c r="C5185" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFuSis5d1VubUJ6c2pLMi9oWWMxMVE9PSIsInZhbHVlIjoiTW5RZTVFcE9yZVR5RWNLRzBaSkpMZz09IiwibWFjIjoiN2MxZGIwNjI4MjFhNWEzODNkNWM5NjczOTY4M2NmYzQ0NjhiYmExMjk2OGRiNDZlNTljMmI1ZjUyYTY1ZDE2ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5186">
+      <c r="A5186" s="3" t="inlineStr">
+        <is>
+          <t>1513.PSD</t>
+        </is>
+      </c>
+      <c r="B5186" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11093.psd</t>
+        </is>
+      </c>
+      <c r="C5186" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZEOXgxalpSRTk5ZzNDc1RZWDR1eGc9PSIsInZhbHVlIjoibDFlUTdjemVyWnBvMDBMNzc1eTJYQT09IiwibWFjIjoiMWJkMzljMzhjYThkYjRmZWQ1NjE1NTc4MzlkMTRiYzI4NzZmOGJkMzg4NTRkMmFmOTFkNTAxNzZiZjU0OWVjNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5187">
+      <c r="A5187" t="inlineStr">
+        <is>
+          <t>1512.psd</t>
+        </is>
+      </c>
+      <c r="B5187" t="inlineStr">
+        <is>
+          <t>tamilpsd-11094.psd</t>
+        </is>
+      </c>
+      <c r="C5187" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZINFNnMStYR1hxNnNqeFBQMHFWOEE9PSIsInZhbHVlIjoieUZRUjhqM1hNV0RpeGpwVVpPREhFdz09IiwibWFjIjoiOGRmZTM5MmM0ZWFhZjU3MjgyNjAwZjk4MTFiZDI5MzRlZDQyMWQ2NzNmMmEzNTNhN2Q5MGMxNDBiY2UyNGQ2OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5188">
+      <c r="A5188" s="3" t="inlineStr">
+        <is>
+          <t>1511.psd</t>
+        </is>
+      </c>
+      <c r="B5188" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11095.psd</t>
+        </is>
+      </c>
+      <c r="C5188" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhzUkZ5WEVlbm8vTmZybk1ycHloNnc9PSIsInZhbHVlIjoiMkd1bnVHa09xOGx1VlYzUSsxQnhPUT09IiwibWFjIjoiNmFmYWU2ZWE2ZmU5ZGFhYWUwNGFjMTgxYzU0MmFiOWYwM2ZlMDI2YjBiMDQ3Y2JlM2Q2NzU5YTk4ODkxMDFhYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5189">
+      <c r="A5189" t="inlineStr">
+        <is>
+          <t>1510.psd</t>
+        </is>
+      </c>
+      <c r="B5189" t="inlineStr">
+        <is>
+          <t>tamilpsd-11096.psd</t>
+        </is>
+      </c>
+      <c r="C5189" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5Zd09hVEZ5a1pIeWRqZmFXODRZTXc9PSIsInZhbHVlIjoiai80RFIrSGpVWm51cW52SUZyaGNCdz09IiwibWFjIjoiMjZmMzNhMDUzNThkZDliMzJiYWZiYmE3YTU1ODAwZWNiYTlkYTVjMGM4MjlmMjNlMzQ0YzZjYjYxN2JjOGU5NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5190">
+      <c r="A5190" s="3" t="inlineStr">
+        <is>
+          <t>1509.psd</t>
+        </is>
+      </c>
+      <c r="B5190" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11097.psd</t>
+        </is>
+      </c>
+      <c r="C5190" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtnQXFrWE9UZEJCWUw1eGVpNnZSWVE9PSIsInZhbHVlIjoiVXNCdVF3K21aQ0pmV0h3d3FSOG9odz09IiwibWFjIjoiMTEwZmIzNTE1MDUyYTEyZjVhYjRjYjAwYjU5ZGZiY2NkYjlhZjQ0ZTIxMzI3YmZjOWQ2MDI0YjgzNjBkMDY1YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5191">
+      <c r="A5191" t="inlineStr">
+        <is>
+          <t>1508.psd</t>
+        </is>
+      </c>
+      <c r="B5191" t="inlineStr">
+        <is>
+          <t>tamilpsd-11098.psd</t>
+        </is>
+      </c>
+      <c r="C5191" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IitBT014R1BFUHBVUWlKdTU1eldtcUE9PSIsInZhbHVlIjoiSkozRkUxVm1pMC8rRFNhdUl2RHpVdz09IiwibWFjIjoiZWY1MjQzODVkNDJjYmExZGI1YTgzZjFkOTYxNDI1NWY5NGNkYzA2MjczNjJkN2Y5ODY0MmI5NzAxMDU4ZWI1MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5192">
+      <c r="A5192" s="3" t="inlineStr">
+        <is>
+          <t>1507.psd</t>
+        </is>
+      </c>
+      <c r="B5192" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11099.psd</t>
+        </is>
+      </c>
+      <c r="C5192" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im43N2xmRG9vaUMxbXdadE5uMnE1L1E9PSIsInZhbHVlIjoibTY1aHcxVWFNTGJuZXJhV245dDhndz09IiwibWFjIjoiM2NiMjNmYjc2NWIzMWU2OTVlYjVhYjY1YmFlMmRjMzg1YmJjZDk4ZTE0M2E2ZjM4MmU1NmU1MWNlNTg1YTI5YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5193">
+      <c r="A5193" t="inlineStr">
+        <is>
+          <t>1506.psd</t>
+        </is>
+      </c>
+      <c r="B5193" t="inlineStr">
+        <is>
+          <t>tamilpsd-11100.psd</t>
+        </is>
+      </c>
+      <c r="C5193" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Inc5RlVjSldzejNEbjRBamVsQlVJWXc9PSIsInZhbHVlIjoiU1lZOWU2Z1dnNlV0UDBNbGIwWUtOUT09IiwibWFjIjoiMTU4ZDFjNmYyZTkxZWM5YmNkYzg5OTU4MWQ2OGJkNmZlNTBlZjA2Yjk3YmY5NDkzMzJmYjI5MTA2ZDZiYmVlYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5194">
+      <c r="A5194" s="3" t="inlineStr">
+        <is>
+          <t>1505.psd</t>
+        </is>
+      </c>
+      <c r="B5194" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11101.psd</t>
+        </is>
+      </c>
+      <c r="C5194" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndmTk9jdVN3d0FEdC9ib2Q3ek9yQkE9PSIsInZhbHVlIjoiTTlCemQ5eHNrcUdpdTZZSW9lMmNEQT09IiwibWFjIjoiYjA4N2M2MjU2Y2VmODkyMDk5NTQyNDRjZWRlZGQ2Mjc3MGU5ZjZmNWVkZDY2N2U0MDU2M2U0ZDU5ZmYyYjU4NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5195">
+      <c r="A5195" t="inlineStr">
+        <is>
+          <t>1504.psd</t>
+        </is>
+      </c>
+      <c r="B5195" t="inlineStr">
+        <is>
+          <t>tamilpsd-11102.psd</t>
+        </is>
+      </c>
+      <c r="C5195" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5jNVBEZzRIN2xPZzgvYnZMTW1nWUE9PSIsInZhbHVlIjoiSVRnMldkaVlpd0RKZlZQam1HcGFnZz09IiwibWFjIjoiYzllNjc3OWNlYzY2NDY0ODNhYmU1NzRlY2VmZTVlMjhjMzUyMDBlN2MwMDY1NTQyNTQ4ODk1ZGRmZTVkY2I4NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5196">
+      <c r="A5196" s="3" t="inlineStr">
+        <is>
+          <t>1503.psd</t>
+        </is>
+      </c>
+      <c r="B5196" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11103.psd</t>
+        </is>
+      </c>
+      <c r="C5196" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikwxc0JXcGFKaGFYT256K0xyanpjcEE9PSIsInZhbHVlIjoiclFCR2N6REQyWEFoNGxNaStxVDZZdz09IiwibWFjIjoiNTgyOWE2N2NkMzE0ZjI2OGVmZDcwYWU0MjBlYzg4NjBiY2UzZDNjZTY4ZTQ5NzE1OGMyN2E2ZTA4NzEwNjkwYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5197">
+      <c r="A5197" t="inlineStr">
+        <is>
+          <t>1502.psd</t>
+        </is>
+      </c>
+      <c r="B5197" t="inlineStr">
+        <is>
+          <t>tamilpsd-11104.psd</t>
+        </is>
+      </c>
+      <c r="C5197" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNVZXFuaXI3WEtWakJobHUwTm82b0E9PSIsInZhbHVlIjoiTWswU0V5c0Npa2htQy9YTStnVkl5QT09IiwibWFjIjoiMWFkYzRmMTI5OGE4MmVhYjkzMTYxNzg2ZmFiOGNmMjBiZTQ2ZjA5YWJkNmIwYTE1MjkzMTQ4MWRkNDA2NmJmMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5198">
+      <c r="A5198" s="3" t="inlineStr">
+        <is>
+          <t>1501.psd</t>
+        </is>
+      </c>
+      <c r="B5198" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11105.psd</t>
+        </is>
+      </c>
+      <c r="C5198" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRCRmovRkh0UkJDVGpaMU0rQldFRHc9PSIsInZhbHVlIjoiNDRyN3E2M1Z4dk1oOUNhYTArdWcvZz09IiwibWFjIjoiYWM2OTAyZDRiN2UzZWM1YzY4MjZmODQ3N2QwYjllMTRhNTc4MGFjNmIzMjU2YzE0NWQ5NmEyMDlhMzBiNmZkNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5199">
+      <c r="A5199" t="inlineStr">
+        <is>
+          <t>1500.psd</t>
+        </is>
+      </c>
+      <c r="B5199" t="inlineStr">
+        <is>
+          <t>tamilpsd-11106.psd</t>
+        </is>
+      </c>
+      <c r="C5199" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZRMHN4ZXQ3VGFickY4eHdNTVo2dHc9PSIsInZhbHVlIjoiUFVUd3ZDaCtvTkh5WkZkWSthZjFCUT09IiwibWFjIjoiZWIwZTVhOTNmYTY0MDEyNGE2ZTlkNDM3YWQxN2NlZDUwNjFmMWQwMWRjYzQ1YjM5YzdhYjMxZjdiMDUzYjNlNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5200">
+      <c r="A5200" s="3" t="inlineStr">
+        <is>
+          <t>1498.psd</t>
+        </is>
+      </c>
+      <c r="B5200" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11107.psd</t>
+        </is>
+      </c>
+      <c r="C5200" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNlZ1JOYWE4ZUk5ZWVpQVUxVW5Wemc9PSIsInZhbHVlIjoidmRxVS9ybG1aZG5KNGNGdjAwVmc5dz09IiwibWFjIjoiZDIxNTY2ODQwNGQyYjBlNzdiYzMzNTUyZTI0YWQyN2EyMGYxYzExMTViMGE0YjFiYTc1ZmI1ZjljZmU1NWIzNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5201">
+      <c r="A5201" t="inlineStr">
+        <is>
+          <t>1496.psd</t>
+        </is>
+      </c>
+      <c r="B5201" t="inlineStr">
+        <is>
+          <t>tamilpsd-11108.psd</t>
+        </is>
+      </c>
+      <c r="C5201" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZhZ2N4bmNndU56RDYzbTRIamN2anc9PSIsInZhbHVlIjoiNGRBQzRtQk9meUUrYy9sa3pGMnZIdz09IiwibWFjIjoiOWU2M2QwNTkxZDJiOGFmMDdjOTU4YzU1ZWFhYWI4MDFlZTYyMDhmMGNkNWVmOGNkYTA2ZjJmOTdiMDkxMGYyMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5202">
+      <c r="A5202" s="3" t="inlineStr">
+        <is>
+          <t>1494.psd</t>
+        </is>
+      </c>
+      <c r="B5202" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11109.psd</t>
+        </is>
+      </c>
+      <c r="C5202" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktZKzNOR2JiK0FMTXZFLzhRallqMHc9PSIsInZhbHVlIjoiejlzbjE0VHlOY1EwSkEzSHhYeU1lZz09IiwibWFjIjoiYTY1Nzg3OTEwMTQyNGMwMGM4OTU3MjY5YTJhOTBiZjhiM2NkNDU3NDM0YTIzNzc5Y2NmYjFiMzExNmFlMjQ5YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5203">
+      <c r="A5203" t="inlineStr">
+        <is>
+          <t>1493.psd</t>
+        </is>
+      </c>
+      <c r="B5203" t="inlineStr">
+        <is>
+          <t>tamilpsd-11110.psd</t>
+        </is>
+      </c>
+      <c r="C5203" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhUa2JLOGV0SXBndm9wZ21DVjVza1E9PSIsInZhbHVlIjoiUjhpaGY3Y2trdzZ1bWNKME0vc3lCUT09IiwibWFjIjoiZWEzZjY0NTk3ZDcxODg0NGViMTQ5NmQzMTgxMmZmZmI3ZDRkZGI4Nzc0NmQyN2MwMzQxYjIyZGI1ZjM1NTYyNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5204">
+      <c r="A5204" s="3" t="inlineStr">
+        <is>
+          <t>1492.psd</t>
+        </is>
+      </c>
+      <c r="B5204" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11111.psd</t>
+        </is>
+      </c>
+      <c r="C5204" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhBT3M1VmhaaTZwbzg5UzZYdnkrV1E9PSIsInZhbHVlIjoiSDBlSW83a0FzRkxJdUNSUTBXT3pmZz09IiwibWFjIjoiMTE3YTUyMWNiOTg5Mjg1NGRhZTRhZjkwMDkyZjBiYjA0MjAwMTY3ZGNlOGQzNmE0MGY3MzhlZjZmYTY4MWM5YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5205">
+      <c r="A5205" t="inlineStr">
+        <is>
+          <t>1491.psd</t>
+        </is>
+      </c>
+      <c r="B5205" t="inlineStr">
+        <is>
+          <t>tamilpsd-11112.psd</t>
+        </is>
+      </c>
+      <c r="C5205" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBvcTFqNk5mcWdSSWVUSzB1bnNjRkE9PSIsInZhbHVlIjoiOFNjSEExZ2dyOTBYOElIMWVlOTdGZz09IiwibWFjIjoiZmI2NDcxMDkwNjM3OTFjNTdjNTk5OGI1ZmEzMzQyYTJiYjBmNGJiZjU2M2ZhOTE2ZmM1YzcxZWNhZjc0OGI1ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5206">
+      <c r="A5206" s="3" t="inlineStr">
+        <is>
+          <t>1490.psd</t>
+        </is>
+      </c>
+      <c r="B5206" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11113.psd</t>
+        </is>
+      </c>
+      <c r="C5206" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijg1dUY2ZjdEYkxUS2hST3l0ckRUZVE9PSIsInZhbHVlIjoiNUNObkhJV003YU1Scm0zdHNZUElVQT09IiwibWFjIjoiOTE0OGRmMTE1MTAwZTg4NTZlZGUyN2NjMmRlN2JjZjlhODJmN2RhZDk3MjIzYmQ5MWI2Njk2MTY3Yzc2N2JhNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5207">
+      <c r="A5207" t="inlineStr">
+        <is>
+          <t>1489.psd</t>
+        </is>
+      </c>
+      <c r="B5207" t="inlineStr">
+        <is>
+          <t>tamilpsd-11114.psd</t>
+        </is>
+      </c>
+      <c r="C5207" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlJSStmaUNHOGZqemVLeHBqcldhU0E9PSIsInZhbHVlIjoiR2FzSnBodmFEdW9JbVY5YnFnU2puZz09IiwibWFjIjoiOWUwOWU4NTIxMzRkZTc2OGVkOThiMzE5OWRkNmViNTU1MDY3OTg1YmQzMzQ4NTY4MmFkOTVhNjJmMGMxZjQwZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5208">
+      <c r="A5208" s="3" t="inlineStr">
+        <is>
+          <t>1488.psd</t>
+        </is>
+      </c>
+      <c r="B5208" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11115.psd</t>
+        </is>
+      </c>
+      <c r="C5208" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imh0bW02WlBWaTk4T1FDL0xRZ1FHTlE9PSIsInZhbHVlIjoiZUorWlR6L2ZjMTNXaEZPOE5Yb1B0QT09IiwibWFjIjoiZTM3MjNlZDkwN2ViNmI3MzhlYTE4MjI2NjMxOWI4NGRlYzRjNjczNWIzYWFkOWYwOTE1YmU5MzUyNzc2NDc0NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5209">
+      <c r="A5209" t="inlineStr">
+        <is>
+          <t>1487.psd</t>
+        </is>
+      </c>
+      <c r="B5209" t="inlineStr">
+        <is>
+          <t>tamilpsd-11116.psd</t>
+        </is>
+      </c>
+      <c r="C5209" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFKb0d4ZVAvTmJHeXZuRTJabFlhZ1E9PSIsInZhbHVlIjoiZHhzdlJUdUNzT1lDcTBsTUhJVm5hZz09IiwibWFjIjoiY2VlNjQ4MzU1MDg3MDZlYWVjNjBiZmY3ZTA2OWUyMzM4MTU3NWM5MGFiODIxNmUxYzQ5OGE4MWFiZmViNjY5ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5210">
+      <c r="A5210" s="3" t="inlineStr">
+        <is>
+          <t>1486.psd</t>
+        </is>
+      </c>
+      <c r="B5210" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11117.psd</t>
+        </is>
+      </c>
+      <c r="C5210" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVhaXRqOXJTNUFIdUVUNUs4MUtLcFE9PSIsInZhbHVlIjoicnkzc3I1emVHTndhNzYvQW4rZ2oxZz09IiwibWFjIjoiMGM2ZjQ4ZTQxMDU1NjgwYTYwZTlhZTJmYmNhZWViMzQyOGNkZDcxNGVmOTQ4ZjczYjY2OWNmMjMzYjNkNzcyZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5211">
+      <c r="A5211" t="inlineStr">
+        <is>
+          <t>1485.psd</t>
+        </is>
+      </c>
+      <c r="B5211" t="inlineStr">
+        <is>
+          <t>tamilpsd-11118.psd</t>
+        </is>
+      </c>
+      <c r="C5211" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjIyZDcrdTFmUjFkeS96SXRCWFhpRnc9PSIsInZhbHVlIjoiQnhEdnhxeWFFTkMyTUFJMEo1MjlFUT09IiwibWFjIjoiMjRkNzAwYWFmOWFhMmMyMzFkYWI0ZTJkYjFiOWZlOGU4YzM5ZGYzMDlmYzczYjI1MzY0YWZiN2YxNGMxNDM5NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5212">
+      <c r="A5212" s="3" t="inlineStr">
+        <is>
+          <t>1484.psd</t>
+        </is>
+      </c>
+      <c r="B5212" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11119.psd</t>
+        </is>
+      </c>
+      <c r="C5212" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVxdXFwYlo5RVQzUTc3SVhVNHNIK2c9PSIsInZhbHVlIjoiNXVWNDhCTlI4dWFlcnVhMWErS1E0QT09IiwibWFjIjoiOTZlM2JmMzE1MTMwY2FmNTNkYjg0OGRhNGUyNzZkMTdmYTY5MmMyZWZkYTBjYjAxYzU4MDRiMjBkOWIwM2Y2NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5213">
+      <c r="A5213" t="inlineStr">
+        <is>
+          <t>1483.psd</t>
+        </is>
+      </c>
+      <c r="B5213" t="inlineStr">
+        <is>
+          <t>tamilpsd-11120.psd</t>
+        </is>
+      </c>
+      <c r="C5213" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im95VkZaV1NmVlJKMUNCcTJJZVhPOXc9PSIsInZhbHVlIjoiVjBCMExBS1NBRXIwYU1NZ05vdnpCdz09IiwibWFjIjoiNTY1MTQ3MjUyOWZjOGUwNjQ2MjFjNDI4ZTk4YzNhNTllZjc4YTNkY2M1NGY5ZThlMzg0MTgwOTQxMWUyNjcyYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5214">
+      <c r="A5214" s="3" t="inlineStr">
+        <is>
+          <t>1482.psd</t>
+        </is>
+      </c>
+      <c r="B5214" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11121.psd</t>
+        </is>
+      </c>
+      <c r="C5214" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNXWHltSkY1SDY4ZlI5YkJ0TnhESlE9PSIsInZhbHVlIjoiYkpjYnc5TmtIRi9mbjR2eWx2ZjJiQT09IiwibWFjIjoiZDM1ODQxOGFiOTBmNWM2NzVlZTM2MDc2Mzk5ODhlMmM4NGFkODY4OWVlMGVhZDE1ZDdkNGYzODFlNjdmMzY3MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5215">
+      <c r="A5215" t="inlineStr">
+        <is>
+          <t>1481.psd</t>
+        </is>
+      </c>
+      <c r="B5215" t="inlineStr">
+        <is>
+          <t>tamilpsd-11122.psd</t>
+        </is>
+      </c>
+      <c r="C5215" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlkyOUtmMTFaTmtwTjJUMWYySDNHM2c9PSIsInZhbHVlIjoidVBLRkZ2ZzIxNDJVZjliejBCSjc0dz09IiwibWFjIjoiMTAxZWU1YTMwOTc2ZmY0OGQ3MzhjNDQ2NDc5N2FkOWQzODY0YTZmYzllNjMyMWY0NjZhMjQ3ZTc2Y2RjZmRkYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5216">
+      <c r="A5216" s="3" t="inlineStr">
+        <is>
+          <t>1480.psd</t>
+        </is>
+      </c>
+      <c r="B5216" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11123.psd</t>
+        </is>
+      </c>
+      <c r="C5216" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlxTTRqOVRkbWhmYlFjVldEaWpuNlE9PSIsInZhbHVlIjoiUHFnQld5MXlSU1hERkc0NWRkanZGQT09IiwibWFjIjoiY2VmNTYwMTA0ZmE0ZWY3ZGE1NTQ5NmU0YmY0YzI2NmViZjc5YzEyNGFmMTg2ODljMGM5NDg1OGY0Yzk2ZTZhNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5217">
+      <c r="A5217" t="inlineStr">
+        <is>
+          <t>1479.psd</t>
+        </is>
+      </c>
+      <c r="B5217" t="inlineStr">
+        <is>
+          <t>tamilpsd-11124.psd</t>
+        </is>
+      </c>
+      <c r="C5217" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhDZHBGNTRhTkZvV1VVMy9uekFpQXc9PSIsInZhbHVlIjoiMzg4ZWY3UjBLRFVMQk9iV1NhQnBFZz09IiwibWFjIjoiZDZmMzU2NzBkZTZjZTQ2MDRkNjBmMzZmNDg4Y2JiYzc2MzU5MjhmNGRiODcyMzA1ZjVlZTU4MjVjZjNjZGJlYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5218">
+      <c r="A5218" s="3" t="inlineStr">
+        <is>
+          <t>1478.psd</t>
+        </is>
+      </c>
+      <c r="B5218" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11125.psd</t>
+        </is>
+      </c>
+      <c r="C5218" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im91eTFaRE9PREdvWEo3TnNpdTJwS1E9PSIsInZhbHVlIjoidjdzZFo0YS9tajNqemVCaUtLSUc4dz09IiwibWFjIjoiY2ZjMmRhNDJmZjI2YTI1ZDlkZjhkMGFhNzAwZGExODcwNWNkM2QzODk2ODQ4N2NmMzVmMDcyZGI1YTNlMWNhNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5219">
+      <c r="A5219" t="inlineStr">
+        <is>
+          <t>1477.psd</t>
+        </is>
+      </c>
+      <c r="B5219" t="inlineStr">
+        <is>
+          <t>tamilpsd-11126.psd</t>
+        </is>
+      </c>
+      <c r="C5219" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjRSSTlkK1pweW5hOFVKb2lOcXJ4OWc9PSIsInZhbHVlIjoiV0Iva2o0VzRWcENGZTlzeDFzcnZKQT09IiwibWFjIjoiMGUxNGU0ZDJjZjU1YjEyN2NlNTQ5OGRhNDlkNjcyMTRiY2Q0NTA0OWFlMzE3YjA0N2I4MTA3YWMyNTI5NWQ3YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5220">
+      <c r="A5220" s="3" t="inlineStr">
+        <is>
+          <t>1476.psd</t>
+        </is>
+      </c>
+      <c r="B5220" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11127.psd</t>
+        </is>
+      </c>
+      <c r="C5220" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijc1NExudkJBczA5em5LcndsL29yMUE9PSIsInZhbHVlIjoiaFlocWcwcGp2bHRyVTY4dFpxdjYzQT09IiwibWFjIjoiZjc5ZjY0Y2Q3MjdlYWY1ZDQwZjNkMWRlOTdiMzhjMmRiYmI1ZDExODRkNWE4Y2YyMTk4OTRlMTUzMWRmMGI0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5221">
+      <c r="A5221" t="inlineStr">
+        <is>
+          <t>1475.psd</t>
+        </is>
+      </c>
+      <c r="B5221" t="inlineStr">
+        <is>
+          <t>tamilpsd-11128.psd</t>
+        </is>
+      </c>
+      <c r="C5221" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFnN0NpeUtEQ2dlMkUxd0poV3VQQkE9PSIsInZhbHVlIjoiOGp2dW1MMjFtVFZYMnhmajBMMFJsZz09IiwibWFjIjoiZjMxZWM4ZmY0MGRiODcxMjZiMWEzNDM4YjE2YjZiNjU3YmViZTQyODJiMmY4ZTA4M2UyODhiNmYzNjk4NmY5YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5222">
+      <c r="A5222" s="3" t="inlineStr">
+        <is>
+          <t>1474.psd</t>
+        </is>
+      </c>
+      <c r="B5222" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11129.psd</t>
+        </is>
+      </c>
+      <c r="C5222" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InBmSjRIdmhBMmNzRmRndTlTVEhjZlE9PSIsInZhbHVlIjoidTV1alUxSVhsTm5ranlXK09FZElrQT09IiwibWFjIjoiOTkwN2YyNjBjZjMzMTQ3OGI4YjBkYjllYmI0ZTFlNzNkMTA2Y2QzY2E2ZGNlMTUyN2FkNDBlZTExMGRjMGY0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5223">
+      <c r="A5223" t="inlineStr">
+        <is>
+          <t>1499.psd</t>
+        </is>
+      </c>
+      <c r="B5223" t="inlineStr">
+        <is>
+          <t>tamilpsd-11130.psd</t>
+        </is>
+      </c>
+      <c r="C5223" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFlWndKSWducXFmOG0xWVdMTnpwU1E9PSIsInZhbHVlIjoiRzhKZk9iRmF3WFFMZGVDZlVBRzVHUT09IiwibWFjIjoiNjc3ZDg0MmZmZGYzOGY3YzRhYmJmZjgwNzEyY2Q1MmRjOTBkNDUxNDU5MjhlNjAyNjc4YmNjZTM1YmI2MDQ1ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5224">
+      <c r="A5224" s="3" t="inlineStr">
+        <is>
+          <t>1472.psd</t>
+        </is>
+      </c>
+      <c r="B5224" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11131.psd</t>
+        </is>
+      </c>
+      <c r="C5224" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNNdjdmbk9FVlBmd05lNSs4TVJjT0E9PSIsInZhbHVlIjoiMUFXMVpvcDJjcWFHUHlUQ2R0bVViQT09IiwibWFjIjoiMzQxYzY5N2VlNzdmNDllYjE0MDcyZDU1ZjUwZGFmYzRhNDk4YTA2NTAyZjIwNjIwNzE1ZDAzZWRkYzhlOTQ0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5225">
+      <c r="A5225" t="inlineStr">
+        <is>
+          <t>1471.psd</t>
+        </is>
+      </c>
+      <c r="B5225" t="inlineStr">
+        <is>
+          <t>tamilpsd-11132.psd</t>
+        </is>
+      </c>
+      <c r="C5225" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilk0aTNCVmxyZ0k2VWNhVEFkL2xwUnc9PSIsInZhbHVlIjoick9pbUJyQTN3WitVQndYaDNOOUZSZz09IiwibWFjIjoiMmQ2MzczM2U1ZWQwZTczM2E4ZmMwYjQ4NjlmNDUwZDBkYTM4ZGViZjUwNDllYWFiNGI1OWQxNjFiYjYzM2ZlYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5226">
+      <c r="A5226" s="3" t="inlineStr">
+        <is>
+          <t>1470.psd</t>
+        </is>
+      </c>
+      <c r="B5226" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11133.psd</t>
+        </is>
+      </c>
+      <c r="C5226" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkswSWt3YXhqYXR2QWRsanRpTzcxdGc9PSIsInZhbHVlIjoiS0Vydlg1bXdPRnVMYndQaTJGSU4rZz09IiwibWFjIjoiN2Q4NTExYmQxYjg1ZmFmM2FkNTYzZDBmOWI0NGZlM2Q2NjY3MmJlNjg4OTRjOWM2M2YwYzZiY2IxNjMzYzIxYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5227">
+      <c r="A5227" t="inlineStr">
+        <is>
+          <t>1469.psd</t>
+        </is>
+      </c>
+      <c r="B5227" t="inlineStr">
+        <is>
+          <t>tamilpsd-11134.psd</t>
+        </is>
+      </c>
+      <c r="C5227" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkUwWTBUL0cvNDJhMnFJRm5nSHQxYVE9PSIsInZhbHVlIjoiM05QcUw4SDBRS2hMQ1lma0NYWTdBZz09IiwibWFjIjoiYzM1ZTEwOTI1MDhjZDBjYTFhYTcwNGE5ODRiNjcyNDAxNDRlYTExNTE3MTQxYmE2NDkyMWVjYmRmZWJiZjdmMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5228">
+      <c r="A5228" s="3" t="inlineStr">
+        <is>
+          <t>1468.psd</t>
+        </is>
+      </c>
+      <c r="B5228" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11135.psd</t>
+        </is>
+      </c>
+      <c r="C5228" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktLSktwNDMrZ2dEZjMySXJUNG9DWGc9PSIsInZhbHVlIjoiK0x2ZUdLQ1BkUWhHS2htU2FDWTMyQT09IiwibWFjIjoiZDA3MGNiYTVjNmU5NmEyOGU2NzAzYzI0OGM0MmYxNzUxZWQ1ZWRhZmNkY2JiM2MyNzJlNDJlNDA1Yjg4NzY1MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5229">
+      <c r="A5229" t="inlineStr">
+        <is>
+          <t>1467.psd</t>
+        </is>
+      </c>
+      <c r="B5229" t="inlineStr">
+        <is>
+          <t>tamilpsd-11136.psd</t>
+        </is>
+      </c>
+      <c r="C5229" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktFMm9PdGJIaVBGaFJYVzJENHRZWGc9PSIsInZhbHVlIjoiWUhIZDU2WFM3emMrenlhcHpjcjZadz09IiwibWFjIjoiNWJiOGJjZjQ0MDg2YmY0YjZlODMyMzMyM2NjOTZkMTQxNGU2YzhkZDZhM2EzMjc4Y2ZkMjYyODRlOGFjOGYxZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5230">
+      <c r="A5230" s="3" t="inlineStr">
+        <is>
+          <t>1466.psd</t>
+        </is>
+      </c>
+      <c r="B5230" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11137.psd</t>
+        </is>
+      </c>
+      <c r="C5230" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpSU2pJR0pmRkdmOHg5aTF3em1Bd3c9PSIsInZhbHVlIjoicWhibFpKN20rMEVWVDVGdXd5ZkxVUT09IiwibWFjIjoiZGNlNjUxNTA4YTIxODE2ZTZiMGRmZTE4NWU2YWUwZDlkNGVhZmUyMDBmOWQ4OWRhMmRkZGJiNmEyYWYwNmM3MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5231">
+      <c r="A5231" t="inlineStr">
+        <is>
+          <t>1465.psd</t>
+        </is>
+      </c>
+      <c r="B5231" t="inlineStr">
+        <is>
+          <t>tamilpsd-11138.psd</t>
+        </is>
+      </c>
+      <c r="C5231" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InV2TWFWK2tZNHBPL05BeEJaajdxYlE9PSIsInZhbHVlIjoicHFHQWxaWG82eHVmQk5KUXRWQWJMQT09IiwibWFjIjoiMjM0ZmY3MzdiZjBjOTQ0OGU3NTc5NTBjOTY4ODE1OTg1MjFlNTY2NWM1MGYxMGU1ZjY2MjA3MDM0ZWQxNzJmYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5232">
+      <c r="A5232" s="3" t="inlineStr">
+        <is>
+          <t>1464.psd</t>
+        </is>
+      </c>
+      <c r="B5232" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11139.psd</t>
+        </is>
+      </c>
+      <c r="C5232" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBoVURTMmtEamNyeTJJNHRkTCt2RUE9PSIsInZhbHVlIjoiRUxXM3VvQnJlTEtvZ1NLTXVIaENYdz09IiwibWFjIjoiMDkxOWNhNzQyMGJhNzE0MWY4ZjUyNjFhMmUyNjQ2NjgxY2E2ZjI3ODRjYjQ2Y2ZlMzM5NzY5Y2E2NTc3NDQxMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5233">
+      <c r="A5233" t="inlineStr">
+        <is>
+          <t>1463.psd</t>
+        </is>
+      </c>
+      <c r="B5233" t="inlineStr">
+        <is>
+          <t>tamilpsd-11140.psd</t>
+        </is>
+      </c>
+      <c r="C5233" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5ZbTNDVTBsNmNXT0NvaXJwTDE0TkE9PSIsInZhbHVlIjoibzUyekhYZFpRTS9tc3JFNGR5MGxNQT09IiwibWFjIjoiYjBmZWQ4YzJjMjViNjYxYTRjODRiYzQ1NTFhOTBhMTIwNjc0ZmFlMTUwMzg1ZjYwYWQxZWFjYTllNmI0ZjI5NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5234">
+      <c r="A5234" s="3" t="inlineStr">
+        <is>
+          <t>1462.psd</t>
+        </is>
+      </c>
+      <c r="B5234" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11141.psd</t>
+        </is>
+      </c>
+      <c r="C5234" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVBRVY2WS9SdUtjZ3JkT09zK2tmMXc9PSIsInZhbHVlIjoidDY2aG1xTjZvTUx3eStJYmh3N09ZZz09IiwibWFjIjoiYTk0OTVlZDc0MGZlMGYyNGIyNzNmMThhZTRjYTk2NjI1OThkNjcxZmQ2ODliYWExOGEyZGU0MDdkMTRkNDY1NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5235">
+      <c r="A5235" t="inlineStr">
+        <is>
+          <t>1461.psd</t>
+        </is>
+      </c>
+      <c r="B5235" t="inlineStr">
+        <is>
+          <t>tamilpsd-11142.psd</t>
+        </is>
+      </c>
+      <c r="C5235" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFoV2JUNGRWcjdpaWNSM0JNRGg4N3c9PSIsInZhbHVlIjoiOVVIV2F1cHowTEVERkU5eGxMMDNtdz09IiwibWFjIjoiODJiY2M1M2UxMzViMzA0YzY5OWU0NmU5NTBhMjcyYjMwNGZkYTE4YjQxNDU1Mjg0MDM4ZWYxNjNhN2ZiOWZiNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5236">
+      <c r="A5236" s="3" t="inlineStr">
+        <is>
+          <t>1460.psd</t>
+        </is>
+      </c>
+      <c r="B5236" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11143.psd</t>
+        </is>
+      </c>
+      <c r="C5236" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdWcGs4QmpTQllxZUdHZVA5R2hqK2c9PSIsInZhbHVlIjoiU09yR1c2M1ZKeklPRnhvQ0hsUEtrdz09IiwibWFjIjoiMWUwODMwYzc3ODAyZTViYjc3NDVhNWJhZDQ3OTg3OGI2Y2Y2NzhlOGZlMDA4ZWUxOGUyNGVmZmRmMjkxYTUwYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5237">
+      <c r="A5237" t="inlineStr">
+        <is>
+          <t>1459.psd</t>
+        </is>
+      </c>
+      <c r="B5237" t="inlineStr">
+        <is>
+          <t>tamilpsd-11144.psd</t>
+        </is>
+      </c>
+      <c r="C5237" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxlRm40blR6NzJKRTBGS1luRCs5dlE9PSIsInZhbHVlIjoiODV5UjN0SVhUZjZEaWlTdkFzNVljZz09IiwibWFjIjoiNTkwNzdhYzI4YjY0MjhmNjQ5N2ZmYmY0YmE0OGEzMzFlN2NlMzhlMzlkMWM2NGE2ZWQ0YjY2YzM2M2ZiMTdiMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5238">
+      <c r="A5238" s="3" t="inlineStr">
+        <is>
+          <t>1458.psd</t>
+        </is>
+      </c>
+      <c r="B5238" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11145.psd</t>
+        </is>
+      </c>
+      <c r="C5238" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJTdTkrbWpFWEY3d3I0TThwbFBTNEE9PSIsInZhbHVlIjoiY2lPNWVYSWd6Z2RyOWNtMFMrOEVVZz09IiwibWFjIjoiZmZhNmM2YmZmM2QyNTQwNjlmYTYxOWZkNmQ1ODFlZWIwY2NhM2Q4Zjc4YjcyNWRmMGZiNTgyMDczZDE2NGUxMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5239">
+      <c r="A5239" t="inlineStr">
+        <is>
+          <t>1457.psd</t>
+        </is>
+      </c>
+      <c r="B5239" t="inlineStr">
+        <is>
+          <t>tamilpsd-11146.psd</t>
+        </is>
+      </c>
+      <c r="C5239" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjZGWGtOZUhBS2RvMkdOakV6V2EwWVE9PSIsInZhbHVlIjoiTFU1anJHODllRU5ydW5RSEJRVFEwZz09IiwibWFjIjoiMmQ1NjUzZDU4ZDA5NzUzZTkwYTg3ZTFlZGM3ZTJkZjA3YzJlZmE0M2VmYjhkM2Y4YTc0NGI3NDVhZjlmNDJiYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5240">
+      <c r="A5240" s="3" t="inlineStr">
+        <is>
+          <t>1456.psd</t>
+        </is>
+      </c>
+      <c r="B5240" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11147.psd</t>
+        </is>
+      </c>
+      <c r="C5240" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1xNnR2SWttcDFCYmpyb1pkOWs2Zmc9PSIsInZhbHVlIjoiUnhZdXBDT1ZiL1V0RzVBU3p2eDlaUT09IiwibWFjIjoiMWE4NTgxYjkwYjVhYzQ3NjgwZGY1NTViMTAxMjljNGI5ZGY5MjA0NzczMDZmMTAzZTljZmZmZmM3Mjg3NmJmOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5241">
+      <c r="A5241" t="inlineStr">
+        <is>
+          <t>1455.psd</t>
+        </is>
+      </c>
+      <c r="B5241" t="inlineStr">
+        <is>
+          <t>tamilpsd-11148.psd</t>
+        </is>
+      </c>
+      <c r="C5241" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhaUE1lQUlBWXJNOWlUOVlNRU9rRXc9PSIsInZhbHVlIjoiODBLVnErRGEvVUZaMVdkbUgrZCtUQT09IiwibWFjIjoiYTE0NjUwMmM1ZjdhZDBiNGNjZTJlYjk5M2NmMTYzNTU1OGZkOTQ4NGUyYTdhY2RkOTMyZmU5ZTc2ZTNhMDliMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5242">
+      <c r="A5242" s="3" t="inlineStr">
+        <is>
+          <t>1454.psd</t>
+        </is>
+      </c>
+      <c r="B5242" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11149.psd</t>
+        </is>
+      </c>
+      <c r="C5242" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilk5d0VRM0pacVAwcStHRzF2bThUcGc9PSIsInZhbHVlIjoiQWhJMm9HeFVjbUZ4bmpGWXBwalE3Zz09IiwibWFjIjoiMTk1ZDYwMDc2YWI3ZmU2NmFkZjFlYzk1NDQ3MTYxNTA3Y2EwNTA2ZGEzZWRhNDE3YjE5MmViODUzN2RmNTE0MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5243">
+      <c r="A5243" t="inlineStr">
+        <is>
+          <t>1453.psd</t>
+        </is>
+      </c>
+      <c r="B5243" t="inlineStr">
+        <is>
+          <t>tamilpsd-11150.psd</t>
+        </is>
+      </c>
+      <c r="C5243" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhVbFNPZFdubC9HTm4yRURwSU00Y1E9PSIsInZhbHVlIjoiZ2g1Q2ZVNGN0L0dFbDhLZlFkam5TQT09IiwibWFjIjoiNjkyMjE2ZWRlMTgxYzk3OGI4Y2Q3OTBiNjEzZDg5MjRiNGU4NjI1NDk1NWM4NjBlZGE1ODBkYmJjZmYxNDRkMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5244">
+      <c r="A5244" s="3" t="inlineStr">
+        <is>
+          <t>1452.psd</t>
+        </is>
+      </c>
+      <c r="B5244" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11151.psd</t>
+        </is>
+      </c>
+      <c r="C5244" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii91dHRsWXh3N004dVU5aTRwTUVOREE9PSIsInZhbHVlIjoiSEd5TGhEZEQwMkhTdG5iNTdNV2NOQT09IiwibWFjIjoiYzljNDAwYzAwODNiMzY3MGU3YWU3MDYxYWEwMjgxYjg4MWJmZDZmMTZlZmViODhlMzQyNmVhZTRhMDJkZjI1ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5245">
+      <c r="A5245" t="inlineStr">
+        <is>
+          <t>1451.psd</t>
+        </is>
+      </c>
+      <c r="B5245" t="inlineStr">
+        <is>
+          <t>tamilpsd-11152.psd</t>
+        </is>
+      </c>
+      <c r="C5245" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNBU0VtcUZNTktuRGNUR1ZqTTNJeEE9PSIsInZhbHVlIjoibXFFQnZmU25kN1dqT2hUYS9yR1dKZz09IiwibWFjIjoiYTk0NDNiMTdhMTY5YjczODE0MWU5NWFjNWI0YzU1NDg2ZDZiZmI2MzYxZDM1ZGU2NjlhMzAwMDlmODhjNGU5MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5246">
+      <c r="A5246" s="3" t="inlineStr">
+        <is>
+          <t>1450.psd</t>
+        </is>
+      </c>
+      <c r="B5246" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11153.psd</t>
+        </is>
+      </c>
+      <c r="C5246" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZNL1dFd1NwUi90WkQwRG5MSytrR0E9PSIsInZhbHVlIjoiZkVIR3RBQklnd3VCY1lsU0w1NVdvQT09IiwibWFjIjoiMTIyNTQ2YTViNDBmMWJiMTkwMWQwNGNiNWMxNjEyZWI1YzJjOGU4N2I1ZmJkYWQ4YWM0YjU1NmIxNzcyMTk5YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5247">
+      <c r="A5247" t="inlineStr">
+        <is>
+          <t>1449.psd</t>
+        </is>
+      </c>
+      <c r="B5247" t="inlineStr">
+        <is>
+          <t>tamilpsd-11154.psd</t>
+        </is>
+      </c>
+      <c r="C5247" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZWWlE0MXhXUnpKWkRyWFJ1WHRrclE9PSIsInZhbHVlIjoiMTA2amRRa3QxVjhGKzBKdCsrK0xGZz09IiwibWFjIjoiMTVkNGNmNDI2NTdiODRjMDFhMTk1ZGU4NzQ2YTkxZWM3NDdiYzAxOWY3MDZkMWRiNTUwMWQ3ZjZlMDFjMmQxMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5248">
+      <c r="A5248" s="3" t="inlineStr">
+        <is>
+          <t>1448.psd</t>
+        </is>
+      </c>
+      <c r="B5248" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11155.psd</t>
+        </is>
+      </c>
+      <c r="C5248" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imh3a1F3Vmo5OElUT3lDZVB4UW5rSFE9PSIsInZhbHVlIjoiOEdVdkRVZGJUNTF1by9ETUhPdjdmUT09IiwibWFjIjoiZTFiOGEyNzU1YTYzYmQwNDU1NTBmYzRiOWI2NDRiMzZkMDI0MzZlOWQ5YWVhOGM3OTBhZjdhMDQxNDdlZjQxOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5249">
+      <c r="A5249" t="inlineStr">
+        <is>
+          <t>1447.psd</t>
+        </is>
+      </c>
+      <c r="B5249" t="inlineStr">
+        <is>
+          <t>tamilpsd-11156.psd</t>
+        </is>
+      </c>
+      <c r="C5249" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRZWnZBK2FSMFJhdFR5R2wxQm5RK0E9PSIsInZhbHVlIjoiOWMyYVFsYXcyUXM1U1JySWRvNFlmdz09IiwibWFjIjoiYzhmNGVlZTkyYzVmYWJhZjBmMjdiNDM0MWMxYzg2ZGM1ZjM3ZGRjZGEyMWE2ZmNjMDlhN2UwZjBiZDRmOTY4MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5250">
+      <c r="A5250" s="3" t="inlineStr">
+        <is>
+          <t>1446.psd</t>
+        </is>
+      </c>
+      <c r="B5250" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11157.psd</t>
+        </is>
+      </c>
+      <c r="C5250" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhIaGpyQUY2cU8yUVNFU1BEa2QrOGc9PSIsInZhbHVlIjoiUHNFU3dOT2lVSnowdStSdmVnbDZZUT09IiwibWFjIjoiMWNmNjgwZWI3Y2JhNzM3MTdiNGZjZGM5OGNlZGY4YjM5YWM3OGNhNjJkYzQ2ZGE2MDJmYzg5ZjA4ZjlhMzU2YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5251">
+      <c r="A5251" t="inlineStr">
+        <is>
+          <t>1445.psd</t>
+        </is>
+      </c>
+      <c r="B5251" t="inlineStr">
+        <is>
+          <t>tamilpsd-11158.psd</t>
+        </is>
+      </c>
+      <c r="C5251" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNWdXgzR3JuZk11OURSWWx2NE0yRVE9PSIsInZhbHVlIjoiRUl5VG9yNGhWUzh5WXBqS1lGRENjZz09IiwibWFjIjoiYTIwYzUzYmFiYzllZTcwMzllM2IwMTFiZjZlMTllOTE5Yzc2YTU2MTk1MWExYTNmNzQwZTVkNjNiOWFmYjk4ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5252">
+      <c r="A5252" s="3" t="inlineStr">
+        <is>
+          <t>1444.psd</t>
+        </is>
+      </c>
+      <c r="B5252" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11159.psd</t>
+        </is>
+      </c>
+      <c r="C5252" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjduSERDUjRWYnA4azRaVHFaSEJNRVE9PSIsInZhbHVlIjoia2EvZkZqd0wrSnRYVGdFUHgwN1ZRZz09IiwibWFjIjoiNzZjNmRhZGE4ODNhODNkNDhjMTViZDE4OGRkMDcxNTM2YTVhMjg4Yzg2ZjkyODAxMmEwMjdlNzdkZmYyOGU5NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5253">
+      <c r="A5253" t="inlineStr">
+        <is>
+          <t>1442.psd</t>
+        </is>
+      </c>
+      <c r="B5253" t="inlineStr">
+        <is>
+          <t>tamilpsd-11160.psd</t>
+        </is>
+      </c>
+      <c r="C5253" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikg1c2YvQit2emtJSFBKWjFTVUdjVXc9PSIsInZhbHVlIjoiajFNcVM0Z0ZIWnZIM0xSdXIyUWFtUT09IiwibWFjIjoiYjVjNmVmMjE1ZTYyYjZjMmFkY2QzYWE4ZjViMWExMTk2MTAwNTc3MDgxNGFjNzQxYjZiYmI5ZjhiNjgwYWU0OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5254">
+      <c r="A5254" s="3" t="inlineStr">
+        <is>
+          <t>1441.psd</t>
+        </is>
+      </c>
+      <c r="B5254" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11161.psd</t>
+        </is>
+      </c>
+      <c r="C5254" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5PeG9sbVUwVXlRVGw4MEh2ZmtLaHc9PSIsInZhbHVlIjoiSTJzYWpUVTVTWUVDc04zNGlCL2xBQT09IiwibWFjIjoiYjc5YWQ1MzNiMThlZDA0ZTkxZDIwZDBjYWNhZGMyNzhhNTgwN2RjODgyNWU5NzZlMmJiYTVmMDdkNDIyN2VmMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5255">
+      <c r="A5255" t="inlineStr">
+        <is>
+          <t>1440.psd</t>
+        </is>
+      </c>
+      <c r="B5255" t="inlineStr">
+        <is>
+          <t>tamilpsd-11162.psd</t>
+        </is>
+      </c>
+      <c r="C5255" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNjTUJHMmc4enZXTE4vdGQzSHlkeXc9PSIsInZhbHVlIjoiZnVTek8wQnp4VCtEREQ3MXJqUEM1dz09IiwibWFjIjoiMTcyNWVmODQ2ZGZlYTQxMDczYmJiZjBkZWIzZmI0ODU4MWVmZjE0Njc0YjE2ZjdhMDhkNWU4NjQ1NDkwYTQxOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5256">
+      <c r="A5256" s="3" t="inlineStr">
+        <is>
+          <t>1439.psd</t>
+        </is>
+      </c>
+      <c r="B5256" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11163.psd</t>
+        </is>
+      </c>
+      <c r="C5256" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktUUGUweU1ZQVZSUC9RREFFOEtSRFE9PSIsInZhbHVlIjoic3htbWxPamxJb2h3UmI5M0F4UnJldz09IiwibWFjIjoiYzI1ZDAyN2NlYWQxZGI3YjE5ZTE3NzVjMjlkNmYzNjEwYTMzMTI5MWM3MDI0ZmVlMjM4YzkxOTY2YjUzNDdmOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5257">
+      <c r="A5257" t="inlineStr">
+        <is>
+          <t>1438.psd</t>
+        </is>
+      </c>
+      <c r="B5257" t="inlineStr">
+        <is>
+          <t>tamilpsd-11164.psd</t>
+        </is>
+      </c>
+      <c r="C5257" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVlS2NxTHFoQ3RNWS9IR3ZvWHlXY1E9PSIsInZhbHVlIjoiV2FpQ1FkdGE2WEFGVFFPb25pYi9nQT09IiwibWFjIjoiZTA2NWI1OWQzNzQ5ZjYxYzBkN2I4MjU4MTQwZmYyMzRhZjgxYTUxYmFiODRkNmQ0NGJlM2IzYjE0NTJjYTdlZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5258">
+      <c r="A5258" s="3" t="inlineStr">
+        <is>
+          <t>1437.psd</t>
+        </is>
+      </c>
+      <c r="B5258" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11165.psd</t>
+        </is>
+      </c>
+      <c r="C5258" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktxbndTd0liZGtKV2lLYTJYQ3k2eEE9PSIsInZhbHVlIjoiVWZlc0RDdXpkOGcySXdnYWV2U3Ewdz09IiwibWFjIjoiN2MzMjAyNzliZGU0YTZiNWEzMTZkODFhOThlMGY4Y2NhMTJkNzkyYzAyNmY0NzE3MWM0M2RmMDE5OTg4NTFiOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5259">
+      <c r="A5259" t="inlineStr">
+        <is>
+          <t>1436.psd</t>
+        </is>
+      </c>
+      <c r="B5259" t="inlineStr">
+        <is>
+          <t>tamilpsd-11166.psd</t>
+        </is>
+      </c>
+      <c r="C5259" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InIwSWxGNXpNZUxEUVltc25xZVlIVHc9PSIsInZhbHVlIjoiclIxSGljcmp1SHZTeVRuRDhxbHI0Zz09IiwibWFjIjoiNTg0YzBjMDJhZjdkMjg0MzU0N2RkZmM5MzIyZDFlYzI0ODUwN2I1MmIwMmJmZWUyNjFhNWMyMTg4OWE5MmE5NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5260">
+      <c r="A5260" s="3" t="inlineStr">
+        <is>
+          <t>1435.psd</t>
+        </is>
+      </c>
+      <c r="B5260" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11167.psd</t>
+        </is>
+      </c>
+      <c r="C5260" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1JdWhRcXlBeGJxeCtXMk9MMjhYekE9PSIsInZhbHVlIjoidlRndXNtY0FlVk93c1Y5K2lHUk9vUT09IiwibWFjIjoiNGI5ZmQxYWM4MTM2MjYxY2E5ZGZiNTdiZDhiMzgwY2ZmNTkwZTM2NjMyZjQ5NDQ1MGI0OTNiNzJiZjgwM2ZmOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5261">
+      <c r="A5261" t="inlineStr">
+        <is>
+          <t>1434.psd</t>
+        </is>
+      </c>
+      <c r="B5261" t="inlineStr">
+        <is>
+          <t>tamilpsd-11168.psd</t>
+        </is>
+      </c>
+      <c r="C5261" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNTay9SN2ovcXVBVlR2UG00SnBtcFE9PSIsInZhbHVlIjoiaUpvaGVoTzhXV2kzd0RDc2ozSGk5UT09IiwibWFjIjoiY2RlMTUyZGE1MTVmNDI1MTkxNDFlMTEzMmRiMWQ2YzI0ZGFkMmI3Y2RiZTVhYjMzNmM3NjNmNWExZmVhOTJlNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5262">
+      <c r="A5262" s="3" t="inlineStr">
+        <is>
+          <t>1433.psd</t>
+        </is>
+      </c>
+      <c r="B5262" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11169.psd</t>
+        </is>
+      </c>
+      <c r="C5262" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imp5cTFwN0NRMEIrYzh6eWF0Mm4vd0E9PSIsInZhbHVlIjoiVlRZbThhcFhjUU4vclQzNXBTUVI0Zz09IiwibWFjIjoiOTQ5ZjEzMmU0MDk2YmNkMDAyNDgyMjExOWVmZWJmNDQ3Yjg2NTJlNGE0ZGYyYjkxZTRjMjFmNzEzYjY3NTc3NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5263">
+      <c r="A5263" t="inlineStr">
+        <is>
+          <t>1432.psd</t>
+        </is>
+      </c>
+      <c r="B5263" t="inlineStr">
+        <is>
+          <t>tamilpsd-11170.psd</t>
+        </is>
+      </c>
+      <c r="C5263" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBvREpVVkVydWM5UExVWFYyUlRMa3c9PSIsInZhbHVlIjoieDVVWngrMXBGVFJzRlpZaVV1STBvUT09IiwibWFjIjoiYTYzYTY1ZmMwMGZmMWIzZjg2NDI0MTZlYjNiOTYwNGEyY2RhNzhiNGQ5MDJhOGE4NzRhM2ZhNTEwNmZiMDY3ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5264">
+      <c r="A5264" s="3" t="inlineStr">
+        <is>
+          <t>1431.psd</t>
+        </is>
+      </c>
+      <c r="B5264" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11171.psd</t>
+        </is>
+      </c>
+      <c r="C5264" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlYyMDFhR3gyTXNkMHJMc2R3NmppM1E9PSIsInZhbHVlIjoiaDFUYkwxY1ErWEVIQ1NmcUFTVFh6Zz09IiwibWFjIjoiNjRhNmQ5YTIxNGQ0NzY4MGI2ZDk2MzFlMjFmMGEyOTc5YmNjZTgzM2MwZGUzNGUxYTdjNTc1YjMyMzU1MThjYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5265">
+      <c r="A5265" t="inlineStr">
+        <is>
+          <t>1430.psd</t>
+        </is>
+      </c>
+      <c r="B5265" t="inlineStr">
+        <is>
+          <t>tamilpsd-11172.psd</t>
+        </is>
+      </c>
+      <c r="C5265" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhGR2JDd1VCemJpdXM2NjUwTEovVFE9PSIsInZhbHVlIjoiT2JFajc3SjMvK0xTTHRqRDc1bzNmdz09IiwibWFjIjoiMTFlZGZjNmE1NTdkNmQ4ODllNTg4ZjJlNDU1N2FmOTkyNWM1MjE3MTJlNmQ0NDRlMThkNjczYjRjMTRhN2RjMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5266">
+      <c r="A5266" s="3" t="inlineStr">
+        <is>
+          <t>1429.psd</t>
+        </is>
+      </c>
+      <c r="B5266" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11173.psd</t>
+        </is>
+      </c>
+      <c r="C5266" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRhTWVXdE51a0dHV2dEdFEvczBIS0E9PSIsInZhbHVlIjoiZ3RiT1pUbHI0QnRXRWpBbEg5Q0tBQT09IiwibWFjIjoiMjRhYjJlZTA5N2Q1OGM0Nzg1NmU0NTE0MmZmMTNiZDE0NDM1ZjZmZjhhNzNlNDAxODZjOTUwZWQ2YTExNjZhMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5267">
+      <c r="A5267" t="inlineStr">
+        <is>
+          <t>1428.psd</t>
+        </is>
+      </c>
+      <c r="B5267" t="inlineStr">
+        <is>
+          <t>tamilpsd-11174.psd</t>
+        </is>
+      </c>
+      <c r="C5267" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRSRDYyYTNlSHRiZ2tyaEVmL2VENnc9PSIsInZhbHVlIjoiTE1MZlBGSmNhTDhHYVRYcFB1VVFxUT09IiwibWFjIjoiYTczMGJmOTY5ZThhMDgxYTQxMmQ4MzdiYjdlZjI4YmY0NmNmMGJmOWFhNzVhNzdhNWRlY2NhNGQyNWFiZWI4OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5268">
+      <c r="A5268" s="3" t="inlineStr">
+        <is>
+          <t>1427.psd</t>
+        </is>
+      </c>
+      <c r="B5268" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11175.psd</t>
+        </is>
+      </c>
+      <c r="C5268" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjM1OXVkRHJJS0E4RGNiMWtNSnJLSFE9PSIsInZhbHVlIjoiN3U2TzlUM3cwOFRKYjhMSVd6d1RFZz09IiwibWFjIjoiNjkyY2NhNThlNGQ5ZTc4ODc5NTZjY2YyZTZmODBjNjY4NGNmYTYzMDc2NTQ5MDcyMmY0ODBhNDJhNDZkM2U0ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5269">
+      <c r="A5269" t="inlineStr">
+        <is>
+          <t>1426.psd</t>
+        </is>
+      </c>
+      <c r="B5269" t="inlineStr">
+        <is>
+          <t>tamilpsd-11176.psd</t>
+        </is>
+      </c>
+      <c r="C5269" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVtNjN5RTZpa1BoVm1TeTNLd1NOWVE9PSIsInZhbHVlIjoiQURmM2xwcVNrQ2RneXArWmdOd20zQT09IiwibWFjIjoiNTQ2OGVmMzBiOWIxYTM4N2E3YTRlZDY5MDViNDBkOWRjM2I1NzVjY2RlMjc3Y2QwZWViMmQ1NjU1MmZmMTFjMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5270">
+      <c r="A5270" s="3" t="inlineStr">
+        <is>
+          <t>1425.psd</t>
+        </is>
+      </c>
+      <c r="B5270" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11177.psd</t>
+        </is>
+      </c>
+      <c r="C5270" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZLN2RKWmtLWldocGVQVFdpVWk5bWc9PSIsInZhbHVlIjoiUFJnU2t0WnZDVkJqZGxGdlhCR3l2QT09IiwibWFjIjoiMmQxMzJkOTA0ZGY2N2UzODlhZGY5ZGE3YzdhMDU1MmNhOGQyMDc5OWRmM2MzYTVkY2MzMDVkYzI3Y2RhNDA3OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5271">
+      <c r="A5271" t="inlineStr">
+        <is>
+          <t>1423.psd</t>
+        </is>
+      </c>
+      <c r="B5271" t="inlineStr">
+        <is>
+          <t>tamilpsd-11178.psd</t>
+        </is>
+      </c>
+      <c r="C5271" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImFqSXplci8razYvWkZaMGFManEzWmc9PSIsInZhbHVlIjoiTHl4V0N4b01Ba2Q0cW5aQ2ZEVmRPdz09IiwibWFjIjoiMzFhNGM0ZGIyYjYxMzc1MDJhMDc5ZmY2MjMyNzM5ZjNkOTc0YWRlMmFjMThjZDcxZGI3ZThlY2M4N2VmMTdjYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5272">
+      <c r="A5272" s="3" t="inlineStr">
+        <is>
+          <t>1422.psd</t>
+        </is>
+      </c>
+      <c r="B5272" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11179.psd</t>
+        </is>
+      </c>
+      <c r="C5272" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik83YloxNUVNMEZOdjVuN09WZk01QkE9PSIsInZhbHVlIjoiYkRiN3I0U2lySm5TSHVCUkszeGc1QT09IiwibWFjIjoiOWEwNTA3YzE2NWRhMzZhNzhjNzM1YjFjYWRmMmU0Njg2MWE2MjkzZTgyYTgwMzg2NTI0NWEwZTI3ZDNmNjg3OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5273">
+      <c r="A5273" t="inlineStr">
+        <is>
+          <t>1421.psd</t>
+        </is>
+      </c>
+      <c r="B5273" t="inlineStr">
+        <is>
+          <t>tamilpsd-11180.psd</t>
+        </is>
+      </c>
+      <c r="C5273" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllobTBXRDNlZHFsV0p3TFhHM0JZdWc9PSIsInZhbHVlIjoiUTMwL2VZTkdTUk5aT0ZndklZbEhRZz09IiwibWFjIjoiY2UzNGJhNDRkY2FmNmYyYWNlYzc5ZDNkMWU4MzUzMjgwNjk2MWU3OTM2NDlkMzllNjU5Y2I3NGRhMTU1ZTUwNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5274">
+      <c r="A5274" s="3" t="inlineStr">
+        <is>
+          <t>1420.psd</t>
+        </is>
+      </c>
+      <c r="B5274" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11181.psd</t>
+        </is>
+      </c>
+      <c r="C5274" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZhdlVORjYrNCtnTjFPamYrZkpmQVE9PSIsInZhbHVlIjoiNVJQY2k4cVBRT3hmZGJnNkJmTlZEUT09IiwibWFjIjoiMmY0MWMzOWE4NzdjMzVmNjYxMjQ2NDVlYzE3MGJkOWI0ZmNmYTBmYjMwYzZkYjZmMjJjMGEyNzczYTBmN2EwMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5275">
+      <c r="A5275" t="inlineStr">
+        <is>
+          <t>1419.psd</t>
+        </is>
+      </c>
+      <c r="B5275" t="inlineStr">
+        <is>
+          <t>tamilpsd-11182.psd</t>
+        </is>
+      </c>
+      <c r="C5275" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpTZVNzR3hld2QwTGhISHc3eXhkY0E9PSIsInZhbHVlIjoiditvajhiWXRuTUJwRWJKMC9aRDhPUT09IiwibWFjIjoiZjhkYTZmYzcxYTU3MTc1NTI3YWRjNjA2NjQ1ZTAwYjM2MzQ0ZjAyM2Q5ODI4ODExMDA3NzY4YWQwOTI5YjQzZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5276">
+      <c r="A5276" s="3" t="inlineStr">
+        <is>
+          <t>1418.psd</t>
+        </is>
+      </c>
+      <c r="B5276" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11183.psd</t>
+        </is>
+      </c>
+      <c r="C5276" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlQ1NEFvQWNMYml0ZlJ2WG9Da045eXc9PSIsInZhbHVlIjoiWTAyTFcyaUFUdkVlNW1TY2tibzdwUT09IiwibWFjIjoiNzBkYTI5Mzk5MDI0ODRjYzVhYTJkNDQzNDA5YzU1YzUyMTkyOWI2M2JjOGZlNDk5MWIxODI5YWUyNGNlNWQ1ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5277">
+      <c r="A5277" t="inlineStr">
+        <is>
+          <t>1417.psd</t>
+        </is>
+      </c>
+      <c r="B5277" t="inlineStr">
+        <is>
+          <t>tamilpsd-11184.psd</t>
+        </is>
+      </c>
+      <c r="C5277" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InpwNDVnQmNYdFcxcG1DSi82TGhwR0E9PSIsInZhbHVlIjoiY1FibTJDVzRsdXRDVEJKdEZGdEt4QT09IiwibWFjIjoiODM5YzU0MjBhMmI3N2EyOTRmNDY5OGQ4ZDg4N2U0MzBkZGVhNTNmZmZmMWQwNzdkZTliYzJmNjgyNGYxYjA3ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5278">
+      <c r="A5278" s="3" t="inlineStr">
+        <is>
+          <t>1416.psd</t>
+        </is>
+      </c>
+      <c r="B5278" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11185.psd</t>
+        </is>
+      </c>
+      <c r="C5278" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9vcDk5UE1GcEQxV1EvdERrZnRNSVE9PSIsInZhbHVlIjoiN0l2enNOS3FqUVl4TWxqekJHOXZRUT09IiwibWFjIjoiOGIwNTVlNjQ3NzczOTc0ZDgxZWI2ODk2MDE4OTY4ODQxN2Y2YzUzMWIyY2Y2YzY0NTc1YmU2NGVjOWI1NjBkMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5279">
+      <c r="A5279" t="inlineStr">
+        <is>
+          <t>1415.psd</t>
+        </is>
+      </c>
+      <c r="B5279" t="inlineStr">
+        <is>
+          <t>tamilpsd-11186.psd</t>
+        </is>
+      </c>
+      <c r="C5279" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZLbWlidEtLdFdZak1FNlkycHFsc2c9PSIsInZhbHVlIjoibndnZlRTTU9xZkhleDFaSXlSbUI4UT09IiwibWFjIjoiOWFkNjBjNGVkNDE5Y2M2YTcxYjhiN2IzNGNjYzRlZTU2MTcxYWM3MWFjYzc4ZWFkMGIzNDdjMjQxZGYzMjZmZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5280">
+      <c r="A5280" s="3" t="inlineStr">
+        <is>
+          <t>1414.psd</t>
+        </is>
+      </c>
+      <c r="B5280" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11187.psd</t>
+        </is>
+      </c>
+      <c r="C5280" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijlmck4xZ0c0ZzNwZmZGamdndTdlZHc9PSIsInZhbHVlIjoiaHFCUCtUNHRZN3dvNXpCZ0ttWVRKUT09IiwibWFjIjoiYjUyOTE4YjU2MGVhYjk2ZDgyYTUwOTdjZTg4YzU0MDIxODBiMjBlN2RiZmU0OTU0NGUyNzUyNThhNTNjYzdjMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5281">
+      <c r="A5281" t="inlineStr">
+        <is>
+          <t>1413.psd</t>
+        </is>
+      </c>
+      <c r="B5281" t="inlineStr">
+        <is>
+          <t>tamilpsd-11188.psd</t>
+        </is>
+      </c>
+      <c r="C5281" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkdoaFVYeHZPSVZOeVpOMHhiaUdCQUE9PSIsInZhbHVlIjoiYjVGQnNQc2srYnNBbE1TV2djYmhudz09IiwibWFjIjoiNDI4Zjc2YTk5OTliNDA5ZDUzNDAyYjE0MDk4N2IyZGYxMmMwM2MwN2VhODI5NGJlMGZmNzUzYTBlZDc5ODJiYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5282">
+      <c r="A5282" s="3" t="inlineStr">
+        <is>
+          <t>1412.psd</t>
+        </is>
+      </c>
+      <c r="B5282" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11189.psd</t>
+        </is>
+      </c>
+      <c r="C5282" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJrU0ZKcGt4cUpvV1ZGS1BUSStYd3c9PSIsInZhbHVlIjoiSTI3K2tTS0lHeS9Yb3FQVHNHWVd4Zz09IiwibWFjIjoiMTc1ODgzNTA0YjM4ZjVjNThmNjY5ZDQzMTc4OWUzNjhjODcyYjFkNjFlMDVjYmJkMGQzODY0ODA2MTQwYjVmNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5283">
+      <c r="A5283" t="inlineStr">
+        <is>
+          <t>1411.psd</t>
+        </is>
+      </c>
+      <c r="B5283" t="inlineStr">
+        <is>
+          <t>tamilpsd-11190.psd</t>
+        </is>
+      </c>
+      <c r="C5283" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Img5TUtQTTNqTWk2Mm1mS3h4UFJKcEE9PSIsInZhbHVlIjoiRjNKVVh4N2k0S0VyNXBERWlkeVIvQT09IiwibWFjIjoiYmQ2NDM5YjI5OGY2ZTRkYjIxNTIwMDJmZjMzMzdiYTI3MzA5ZThiNTFmMzFjNGE3MDBlMjE4ZTlkNjU3NjM2ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5284">
+      <c r="A5284" s="3" t="inlineStr">
+        <is>
+          <t>1410.psd</t>
+        </is>
+      </c>
+      <c r="B5284" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11191.psd</t>
+        </is>
+      </c>
+      <c r="C5284" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJDeFdXNHVrSHdtZVlDbCsraUZ5Snc9PSIsInZhbHVlIjoiSXpXTWU1SzQrazZkVDZxdWNpdjFSZz09IiwibWFjIjoiMjc3MGNlYmU4ZTBlY2VkNmQ2MGJmNDEzNTI3MTBhYTVlMWI1ZTM5Y2YwNjYyNTI3ZmM5MDU1NzgyZDQwYjk5NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5285">
+      <c r="A5285" t="inlineStr">
+        <is>
+          <t>1409.psd</t>
+        </is>
+      </c>
+      <c r="B5285" t="inlineStr">
+        <is>
+          <t>tamilpsd-11192.psd</t>
+        </is>
+      </c>
+      <c r="C5285" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InYyR0V6Lys1azlCRU1mcUlFQ25FZXc9PSIsInZhbHVlIjoiTUV4QUd5c2o4cUpoeGEzdzUyQ2FUQT09IiwibWFjIjoiMTJlNWUxZDEwNTNiZDQzMzQ5MDZkMjAwNTMxNzJiYTNlMjkzY2Y0NTM2ZjFhMTkyOWFhNzc5MzI3ZGZiNGFjZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5286">
+      <c r="A5286" s="3" t="inlineStr">
+        <is>
+          <t>1408.psd</t>
+        </is>
+      </c>
+      <c r="B5286" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11193.psd</t>
+        </is>
+      </c>
+      <c r="C5286" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjRUUythMXFiY25lTU4xQ1JUWnpZQ3c9PSIsInZhbHVlIjoidWUvdUVOZ0JJODhDNlg4cWRITGRrZz09IiwibWFjIjoiNjdkNjBiMDUzYjljYzAyMDYyYjgzN2ExYzI5MDI3N2EwNGY4ZGI0NWJlZGQ5YThmZTQwM2QwNTEwMzc2ODc0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5287">
+      <c r="A5287" t="inlineStr">
+        <is>
+          <t>1406.psd</t>
+        </is>
+      </c>
+      <c r="B5287" t="inlineStr">
+        <is>
+          <t>tamilpsd-11194.psd</t>
+        </is>
+      </c>
+      <c r="C5287" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InpZUS8rV0h2ZzVaWU5DQ0hycTBBMnc9PSIsInZhbHVlIjoiaTZYb3J4dTBNMGJPM2YvbmN5MDBVZz09IiwibWFjIjoiNTZlNzFhYjY5YzdhYmQzNmMxNzdkMDViMjUwNWVkOTg2MDE5MmU4ZDA0NDM1N2RkYjc4YTg1Yjk4YWIxYjkwYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5288">
+      <c r="A5288" s="3" t="inlineStr">
+        <is>
+          <t>1405.psd</t>
+        </is>
+      </c>
+      <c r="B5288" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11195.psd</t>
+        </is>
+      </c>
+      <c r="C5288" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVGdmo0Q0R1REwxQXJ5OWNaRS94OVE9PSIsInZhbHVlIjoiZHNTUjlGTTdaNllRajVDVVQ4UzNqdz09IiwibWFjIjoiOWVkYTM4Y2IzNDFlNGRhOTc2YjYwNjMyNTJiNWViMmU1YjkwOWVhZTZmODIyNzgxOWRhZTQ5MjhhMzdjMzY4MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5289">
+      <c r="A5289" t="inlineStr">
+        <is>
+          <t>1404.psd</t>
+        </is>
+      </c>
+      <c r="B5289" t="inlineStr">
+        <is>
+          <t>tamilpsd-11196.psd</t>
+        </is>
+      </c>
+      <c r="C5289" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJwNTZ0TU9HMU1kWXk2NVplUUNOTWc9PSIsInZhbHVlIjoiMVVuS2gxUzdiYkxMeEM4dTJVQzR5QT09IiwibWFjIjoiYWY4ZDE2NzVhNDljMTZjYzk3NGVjNjFkOWY2ZmI1NjU0ODAwN2RhZWNjN2ZmNWViMGQ0MTBkYjhiZWQ1ZTZkZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5290">
+      <c r="A5290" s="3" t="inlineStr">
+        <is>
+          <t>1403.psd</t>
+        </is>
+      </c>
+      <c r="B5290" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11197.psd</t>
+        </is>
+      </c>
+      <c r="C5290" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InU3bW8vRWluQ3RBUFJyQmg1b0pyRUE9PSIsInZhbHVlIjoiWUxrMGVScUNoWFdBeWlQd25yNGNsdz09IiwibWFjIjoiMmEzNTRlOWI5MWJmNDI0OWNiOGJhZTYwZTA1YTAyODI3NGZhNTBkM2NkZDRhY2U3NjIwNmVkYWQ0OWI1YjY4ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5291">
+      <c r="A5291" t="inlineStr">
+        <is>
+          <t>1402.psd</t>
+        </is>
+      </c>
+      <c r="B5291" t="inlineStr">
+        <is>
+          <t>tamilpsd-11198.psd</t>
+        </is>
+      </c>
+      <c r="C5291" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InozNEJRZEpDeW04cnNyUkMyczdValE9PSIsInZhbHVlIjoiMFo0WElEQitzMUxyNTg2L3dzVzJvUT09IiwibWFjIjoiNDhlZjcyNzk5OGYzZTgyYTNkNjA5NzdjYjg0YzMzMDc3MTQ0MjQ5YWQzYTAxY2UwN2QyZWM1Zjk1MmNjZjAzZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5292">
+      <c r="A5292" s="3" t="inlineStr">
+        <is>
+          <t>1401.psd</t>
+        </is>
+      </c>
+      <c r="B5292" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11199.psd</t>
+        </is>
+      </c>
+      <c r="C5292" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhUM0N4a1VkWXU4eXpBc0NxSjNHMWc9PSIsInZhbHVlIjoidzJuVXhEdkdFeE1PbWhNM0lnYXA0UT09IiwibWFjIjoiMmZmMGU2N2RiMjZiOTQzYzY5ZWY4NWZhNzAyNmNhN2ViMTMwMmM1YWEzMTYzYzE5NDY3MWM1NzA3NGMxYjVmMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5293">
+      <c r="A5293" t="inlineStr">
+        <is>
+          <t>1424.psd</t>
+        </is>
+      </c>
+      <c r="B5293" t="inlineStr">
+        <is>
+          <t>tamilpsd-11200.psd</t>
+        </is>
+      </c>
+      <c r="C5293" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikw3THRtcmZuY2hNbDZrMVRjdWtHdFE9PSIsInZhbHVlIjoiVlhzdUJFYTQxRzJZanJLeTFMUzFTUT09IiwibWFjIjoiMTNiZTljZDhhZjQzMGU4M2Y3MjU1MDgzYjI1OWI0YmM4YTA1OGRhZTJlN2ViOWEwYzRjMTcwMWMxYTkyMGVlOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5294">
+      <c r="A5294" s="3" t="inlineStr">
+        <is>
+          <t>1400.psd</t>
+        </is>
+      </c>
+      <c r="B5294" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11201.psd</t>
+        </is>
+      </c>
+      <c r="C5294" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJDa0RJSW9Gb2MzQ1M1bG53SjY4VUE9PSIsInZhbHVlIjoiaTZPa3kybEQyYjdDS0hFamVwZ2w5dz09IiwibWFjIjoiOTQ0MmI2YzQxZWU3ZDNhNTc5ODk5MTA3MTA4Yzg5ZGJkODQ3NGVjYmE5ZGFhNmMyOWM5ZWE5YjJhYzA0MWYxZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5295">
+      <c r="A5295" t="inlineStr">
+        <is>
+          <t>1098.psd</t>
+        </is>
+      </c>
+      <c r="B5295" t="inlineStr">
+        <is>
+          <t>tamilpsd-11202.psd</t>
+        </is>
+      </c>
+      <c r="C5295" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFXSFZjRWpvbGtCN2dWNzdYRjhHM2c9PSIsInZhbHVlIjoiN1VVeG1mMmxXdityTnU0Vm5yeUZFdz09IiwibWFjIjoiMzRkMTNlOTYxOTQ5ZWVjN2UzMWQzNDg3Y2I2ZWMzY2IxNWI5MjYwMDBlMGYwMDRlNjRjNGZhM2IyMzIxMTEyNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5296">
+      <c r="A5296" s="3" t="inlineStr">
+        <is>
+          <t>1097.psd</t>
+        </is>
+      </c>
+      <c r="B5296" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11203.psd</t>
+        </is>
+      </c>
+      <c r="C5296" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNOMHVMajFCSVEwQWhyWVJRT2hrRlE9PSIsInZhbHVlIjoidTd0d3RmczZKblB5V3RJb2dIZmM2QT09IiwibWFjIjoiMjljZTA0MzZlYzU4ZGU5MzBiOGM3YWM3ODhjMGVjYTk2ZDM3N2Q2MDkyMjU0NWU2NjQ1NjJjMmUyN2U5MWMyOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5297">
+      <c r="A5297" t="inlineStr">
+        <is>
+          <t>1096.psd</t>
+        </is>
+      </c>
+      <c r="B5297" t="inlineStr">
+        <is>
+          <t>tamilpsd-11204.psd</t>
+        </is>
+      </c>
+      <c r="C5297" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJyY3k4YkxJU3hobHFrdktRUmRFZFE9PSIsInZhbHVlIjoibUJlTnBXeXVBandzUTFwU25yMUtJQT09IiwibWFjIjoiZmEzYWQ3ZTc0OGU4NjAzMzdiNTg3Yjg2MTU5MGNhYmU0NDlmMjg1YTNkMTc4NDcyZTkyNzFhZWFmNGUyOTdiYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5298">
+      <c r="A5298" s="3" t="inlineStr">
+        <is>
+          <t>1095.psd</t>
+        </is>
+      </c>
+      <c r="B5298" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11205.psd</t>
+        </is>
+      </c>
+      <c r="C5298" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhGOWhvZzN5cjRLZzVHOGwwV0l3ZGc9PSIsInZhbHVlIjoibXJQUFVubjhSSytJbjVPZlg5NTFyZz09IiwibWFjIjoiMjU4N2YwZGM0ZGQxYWM5ODE0OGM1YjRjNDc3YzljOTkzMjM2N2Y2NzM5YWE0ZTMxMDE3YWQ1OTRjYzI5MGVhOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5299">
+      <c r="A5299" t="inlineStr">
+        <is>
+          <t>1094.psd</t>
+        </is>
+      </c>
+      <c r="B5299" t="inlineStr">
+        <is>
+          <t>tamilpsd-11206.psd</t>
+        </is>
+      </c>
+      <c r="C5299" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZ4eStHUjV1ZDJYOWUzM0FGallONHc9PSIsInZhbHVlIjoiWTI1NGNXMGc1MjE3S0U2WldoeEcvdz09IiwibWFjIjoiMDQzZDE5MWE4ZWU1YzQzOWFmNDY3ZjlkNmY0MjNjZDI5MjY4Y2Y5MGM4M2ExZmFmMjg3MmU2OTZkNTU2NjZiMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5300">
+      <c r="A5300" s="3" t="inlineStr">
+        <is>
+          <t>1093.psd</t>
+        </is>
+      </c>
+      <c r="B5300" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11207.psd</t>
+        </is>
+      </c>
+      <c r="C5300" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRoL21nYitIRHlCdnlWOEdEdGd4QWc9PSIsInZhbHVlIjoicUdSR0I3Q1BEK29TamFmL0QrZ1oyQT09IiwibWFjIjoiYTg4YWE1YThjNzc5ZDgwNzBiNGU0ZThlZGVlN2M5YjE3ZTM4NTY1MjczYjI4NDliMTQ4M2VlNWMyZDkzNjgxMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5301">
+      <c r="A5301" t="inlineStr">
+        <is>
+          <t>1092.psd</t>
+        </is>
+      </c>
+      <c r="B5301" t="inlineStr">
+        <is>
+          <t>tamilpsd-11208.psd</t>
+        </is>
+      </c>
+      <c r="C5301" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlIzSUN2NXhsREs1NnhKMXJIc1BGYWc9PSIsInZhbHVlIjoicGdrRlJ2OTBSc3RGdE9lbmI3NnFhQT09IiwibWFjIjoiNWQ4NTIxYjI3MWQ1M2U2NWY5OTNkMjk1MmRlNjM3MDU2MzZhMTdlYmQyZjFjNjZhY2NmY2IwZTc2ZmQ1ODdlZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5302">
+      <c r="A5302" s="3" t="inlineStr">
+        <is>
+          <t>1091.psd</t>
+        </is>
+      </c>
+      <c r="B5302" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11209.psd</t>
+        </is>
+      </c>
+      <c r="C5302" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNTcDFHRndoMmtDcGt5VUU5dVpQM0E9PSIsInZhbHVlIjoicVlQMjNrd3VFT3hhME1jMlpUSnk3UT09IiwibWFjIjoiZGI3NzUyNzgxZTFjNmExZmE2YzU4YTc5MzRiNzg0YWZmYmI3ZGI2M2MyNWMxOWRkNTYwMDc3MjgxZDI3Mzg5MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5303">
+      <c r="A5303" t="inlineStr">
+        <is>
+          <t>1090.psd</t>
+        </is>
+      </c>
+      <c r="B5303" t="inlineStr">
+        <is>
+          <t>tamilpsd-11210.psd</t>
+        </is>
+      </c>
+      <c r="C5303" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJBTUJCekduazdtR1BhdTczMStWTVE9PSIsInZhbHVlIjoiS0U1RlA2ZHpKdk5zY3B1RVZ1OVUxQT09IiwibWFjIjoiOWIwN2Q2YTEyNGEzOTRkMjIzOWIwYWYyMzIyODgyNjdlNDUxZGI1OWE2MmQ4OWRlODI5NzJhNzEzOTZlN2IwMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5304">
+      <c r="A5304" s="3" t="inlineStr">
+        <is>
+          <t>1089.psd</t>
+        </is>
+      </c>
+      <c r="B5304" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11211.psd</t>
+        </is>
+      </c>
+      <c r="C5304" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InN1YnZUREdWV1ZxVGVmNjZmTWJxNlE9PSIsInZhbHVlIjoiVjliRnZxeThqRXJPaWFZWGlJdy9CQT09IiwibWFjIjoiMWQ2YzMyOTUzZTVjYjg0ZjdiNjg0Y2EyMWQxYWIxYjQxZjEzYjMyYWNkODU1NWJlMWJmNzI5YjlhOWQzNWM2OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5305">
+      <c r="A5305" t="inlineStr">
+        <is>
+          <t>1088.psd</t>
+        </is>
+      </c>
+      <c r="B5305" t="inlineStr">
+        <is>
+          <t>tamilpsd-11212.psd</t>
+        </is>
+      </c>
+      <c r="C5305" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNUclNtcTVFN293WmZYV3E3emM0elE9PSIsInZhbHVlIjoiUHJNZ0JsbFZDM1lKUzFVWkN6Sllvdz09IiwibWFjIjoiNTEwZjEyY2YzMDY0MjFiOWFkYmEyMWI0MDFkNjQxYTlkMDA5OTE0OGU1NGYwMWI0NjEzNTA5ZjQ1MzZiOTIwZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5306">
+      <c r="A5306" s="3" t="inlineStr">
+        <is>
+          <t>1087.psd</t>
+        </is>
+      </c>
+      <c r="B5306" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11213.psd</t>
+        </is>
+      </c>
+      <c r="C5306" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkVWd21GdDFrNHhJQW0xZFQ3NUVqY2c9PSIsInZhbHVlIjoiMlhEOU5TbXRuQ1VEWWFabGdYR2tUZz09IiwibWFjIjoiMzI2OTdmM2QwNzhlNzZkNGU3OTZhMjc0MjZhNDVjZGJlNjFjMTQ4MzE3ZWVlMjdiYzA1ZTQ5Zjg1NjhiMjMyNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5307">
+      <c r="A5307" t="inlineStr">
+        <is>
+          <t>1086.psd</t>
+        </is>
+      </c>
+      <c r="B5307" t="inlineStr">
+        <is>
+          <t>tamilpsd-11214.psd</t>
+        </is>
+      </c>
+      <c r="C5307" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5SczgwMG1uT2h3eUtTcEZFWXVtWVE9PSIsInZhbHVlIjoiUUpBSXZiaFFSU0xhQzhkMCtncjJ4UT09IiwibWFjIjoiMjA3Y2Y3N2RhMWNmMThlZDlhMmJhYWFjMDc2ZjEzY2ZiODRkNDUxMGE2ZmI3MGY1ODFhNDAwNTg1NWJlY2Q1MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5308">
+      <c r="A5308" s="3" t="inlineStr">
+        <is>
+          <t>1085.psd</t>
+        </is>
+      </c>
+      <c r="B5308" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11215.psd</t>
+        </is>
+      </c>
+      <c r="C5308" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5yOGl0K21aMTduYVVPRUFSWnhjZlE9PSIsInZhbHVlIjoiMWRhbk15KzFVQVFiVFRDT056SXpRdz09IiwibWFjIjoiMDVlODljZTFjZDA4ZDQ1MWMwYjg0NzgyMzEzMjU1MmE4MDMzNWRjZjE0ODYyNzhmMzlkMGQ0OGE5NTJmMDMwNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5309">
+      <c r="A5309" t="inlineStr">
+        <is>
+          <t>1084.psd</t>
+        </is>
+      </c>
+      <c r="B5309" t="inlineStr">
+        <is>
+          <t>tamilpsd-11216.psd</t>
+        </is>
+      </c>
+      <c r="C5309" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik9sazNKSisvZXBaZithOStJRUxFZkE9PSIsInZhbHVlIjoiTGRqR3NBNWR5RlZpK1RUSHFBNlNnUT09IiwibWFjIjoiYzQ2N2Q4NjFlMTIwYzg0MTJkODY5Yzk0NmU2ZTdkMjc0M2M0MWFhMmYxMjZiNDJlNTA0MGZlOTAwZTQzMWZhNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5310">
+      <c r="A5310" s="3" t="inlineStr">
+        <is>
+          <t>1083.psd</t>
+        </is>
+      </c>
+      <c r="B5310" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11217.psd</t>
+        </is>
+      </c>
+      <c r="C5310" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFmMm4xTjd4UGhzbEFieHhOblU4UXc9PSIsInZhbHVlIjoiWlVQSUlMTWFkenErT0ExOEM0VC9Fdz09IiwibWFjIjoiYTExM2M5YjhkNjAzNWQxZTM3MDY5NGUwNTcyOWUxZmQzYTYxYjVjOTg4YjllNmRhOTNlOWE4NDI1YzhhNTIyNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5311">
+      <c r="A5311" t="inlineStr">
+        <is>
+          <t>1082.psd</t>
+        </is>
+      </c>
+      <c r="B5311" t="inlineStr">
+        <is>
+          <t>tamilpsd-11218.psd</t>
+        </is>
+      </c>
+      <c r="C5311" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImN2azhqbGVpc3JnMXpaQlRuS25FZmc9PSIsInZhbHVlIjoicmZhREZaVVJXT1RPRFhUN2RPbzNsQT09IiwibWFjIjoiOWQ5MTdjMmM4ZTM0ODc3NjA4NjY3NzJlYjVlZmJkMDcwYThkODRjNTE0NmJlNjM5OTJlODJlYmNhYmNmN2JjYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5312">
+      <c r="A5312" s="3" t="inlineStr">
+        <is>
+          <t>1081.psd</t>
+        </is>
+      </c>
+      <c r="B5312" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11219.psd</t>
+        </is>
+      </c>
+      <c r="C5312" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IksvNURrbitVbTRNdzRCdmE1QUZVMWc9PSIsInZhbHVlIjoiNXlGejkyQ3AvaktNOHp3ZEZGR0xMdz09IiwibWFjIjoiNTkwOGQ3NjE3YjFjY2ZiOGI4ZTA2MWEyOGE0YzcxNjIwOWVjYzlkMzQ4ODhkNjg0YjRjYWNiN2NkZDljYWQ2NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5313">
+      <c r="A5313" t="inlineStr">
+        <is>
+          <t>1080.psd</t>
+        </is>
+      </c>
+      <c r="B5313" t="inlineStr">
+        <is>
+          <t>tamilpsd-11220.psd</t>
+        </is>
+      </c>
+      <c r="C5313" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5XRkFseDZSTGNKNG1wRUtlUk9OMHc9PSIsInZhbHVlIjoiRysycGtaRjJ2MmZHUUYzY2NSeFRBZz09IiwibWFjIjoiMGZiYmZjMTJhYTFjZWRjZGM0Y2MyMjI1ODE2MmVjNzBkNGI5YzIzOThjNTJmYjJmYjkyYmQzMDQzOGY0NDE3MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5314">
+      <c r="A5314" s="3" t="inlineStr">
+        <is>
+          <t>1079.psd</t>
+        </is>
+      </c>
+      <c r="B5314" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11221.psd</t>
+        </is>
+      </c>
+      <c r="C5314" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik81K0pxdGwzM0hTV1crbXpPY212K3c9PSIsInZhbHVlIjoiYTA2elJSQ21BQ2FvR1NLRy9oQWVjUT09IiwibWFjIjoiZTdhMWUzY2E5OTlmOWI5MTVkMDU2NjA4MTkwMTEyZjUyODUyZDU4NTc3ZTdjYTYwY2NhZGYxYzlkN2M2ZTE3YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5315">
+      <c r="A5315" t="inlineStr">
+        <is>
+          <t>1078.psd</t>
+        </is>
+      </c>
+      <c r="B5315" t="inlineStr">
+        <is>
+          <t>tamilpsd-11222.psd</t>
+        </is>
+      </c>
+      <c r="C5315" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlLcmVvejZMZVl1MFJEN0hVV2pwRlE9PSIsInZhbHVlIjoibFVmOWxTMjJWVE05TUtmS0pldk16QT09IiwibWFjIjoiZjdlNmVkMjkxMGIxMjdiYjkyM2E0ZTJjMzFlMDA4NDZmZThmNjFkMTVkNjIxN2JhMjRkOGUzYmZmNDk3NWFiMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5316">
+      <c r="A5316" s="3" t="inlineStr">
+        <is>
+          <t>1077.psd</t>
+        </is>
+      </c>
+      <c r="B5316" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11223.psd</t>
+        </is>
+      </c>
+      <c r="C5316" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikx4M1R3QUF3NWN0KzUrVDQ2L3FrRlE9PSIsInZhbHVlIjoiM3hudmNkRzRqMTBSdGxWNE9QN2lXQT09IiwibWFjIjoiNmU2ODIyNWZjOGZlYWQ3YWFmYWFkZGJkMWQyNzE3ZTI3YjQyOTE0NTZkOTRmOWQxZjNmOTkyMmZlZTkwODIzNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5317">
+      <c r="A5317" t="inlineStr">
+        <is>
+          <t>1076.psd</t>
+        </is>
+      </c>
+      <c r="B5317" t="inlineStr">
+        <is>
+          <t>tamilpsd-11224.psd</t>
+        </is>
+      </c>
+      <c r="C5317" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imo1WjUvV0xwNUhvZWZ2K1RVY1lCL3c9PSIsInZhbHVlIjoiSEdzTU9scVc3K1Z3VUx2TnFYdzdtZz09IiwibWFjIjoiNDY0MDAzM2QwMTQ0NjlkYTdkODQ0Yjk2MWVlMzA4ZjFhZjgwYTJlY2IwZDRlMWJiMWJhNzI1MTI4YzVlYjMwNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5318">
+      <c r="A5318" s="3" t="inlineStr">
+        <is>
+          <t>1075.psd</t>
+        </is>
+      </c>
+      <c r="B5318" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11225.psd</t>
+        </is>
+      </c>
+      <c r="C5318" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFhcUdTVzVvOHNyVzFrNG1LTnoxT3c9PSIsInZhbHVlIjoiZEVITFdiT3B1L3oydlhGSUpkYWd0Zz09IiwibWFjIjoiYzQyZjU1YzAyNGMwYzllYzg3OWQzMTE0Y2NjMzA4OWI5ZWNhYzIwNDAwNzdmNzhhODE0MjUzZjVjM2IzZTY1ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5319">
+      <c r="A5319" t="inlineStr">
+        <is>
+          <t>1099.psd</t>
+        </is>
+      </c>
+      <c r="B5319" t="inlineStr">
+        <is>
+          <t>tamilpsd-11226.psd</t>
+        </is>
+      </c>
+      <c r="C5319" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpqRnRoVWV2M1piNDBJVTEya1k4THc9PSIsInZhbHVlIjoiWXRqcVdtaFZMZHhxeHN5T0t2ZW9hQT09IiwibWFjIjoiNmNlYzBkMDc4ZDU4MGZjMTA4YzdmNDYyOTU3MTJhOTY4YTRlYjZhODA2OTRhZWY4YjMxMzZjMWZlZDliZjk5ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5320">
+      <c r="A5320" s="3" t="inlineStr">
+        <is>
+          <t>1184.psd</t>
+        </is>
+      </c>
+      <c r="B5320" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11227.psd</t>
+        </is>
+      </c>
+      <c r="C5320" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IldwaEM3QVJhRmh5M1E1bzBkWmN5dEE9PSIsInZhbHVlIjoiNC9IQUVZTEtlU3RSZnE2eTEyUVJKdz09IiwibWFjIjoiNDJkZGMwMGZlMzM4NGRmZGQ0ODM4MzcxOTBmMGZjOTAyZjhkYzFmN2ExMmU3ZDRkMDAyY2M0NmEwNzgxNDJmZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5321">
+      <c r="A5321" t="inlineStr">
+        <is>
+          <t>1183.psd</t>
+        </is>
+      </c>
+      <c r="B5321" t="inlineStr">
+        <is>
+          <t>tamilpsd-11228.psd</t>
+        </is>
+      </c>
+      <c r="C5321" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkVMZ1ZsVGhzWEV0R0tZV1ZXZTRNeVE9PSIsInZhbHVlIjoiUDdTTHI2UVZIWFVITlpDUTNLYld4QT09IiwibWFjIjoiMzYyMTUyNmIxZjFlODEzMDczYWQ5YmE0YWVhZTg5NmU1ZGNmNmY5MzViYTAyY2Y2NzlhNzViMmIyNzQxMWIzZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5322">
+      <c r="A5322" s="3" t="inlineStr">
+        <is>
+          <t>1182.psd</t>
+        </is>
+      </c>
+      <c r="B5322" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11229.psd</t>
+        </is>
+      </c>
+      <c r="C5322" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkdRYU5SLy9JT3BCRHNHSEd0TFRsQ3c9PSIsInZhbHVlIjoiSnVwOWxmTDZIQnlIc3NrSTlkZGh2UT09IiwibWFjIjoiNjU5MjVmMDU3YjNkODFjNWYyZDE2ZWNjYWEyODY0MmVmNTIzOGQxZmM5NDJkOWMzZjE0Mzk0ZmViMTUzNTg1YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5323">
+      <c r="A5323" t="inlineStr">
+        <is>
+          <t>1181.psd</t>
+        </is>
+      </c>
+      <c r="B5323" t="inlineStr">
+        <is>
+          <t>tamilpsd-11230.psd</t>
+        </is>
+      </c>
+      <c r="C5323" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFFTGN3N1RyZHZ4S0RYMnFMeVR6U2c9PSIsInZhbHVlIjoiWlJ4NVhyQkF1WFVORTJ0TE5qaS9NQT09IiwibWFjIjoiMzA4M2Y5ZmFkZjE4NmM5N2MwNmI1YzJhYTA3MGQ4ODhiZTMxNTBjZmI1ZjgzODJmZGU0YmExNzQ1YjBiNzBhYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5324">
+      <c r="A5324" s="3" t="inlineStr">
+        <is>
+          <t>1180.psd</t>
+        </is>
+      </c>
+      <c r="B5324" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11231.psd</t>
+        </is>
+      </c>
+      <c r="C5324" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhXRTVhRlpZQ3hVWHQvVFBNc1NYL3c9PSIsInZhbHVlIjoiN0VCcFhCUlRpL08rWUowaTl1Wnc0QT09IiwibWFjIjoiZTkzNzJiNDExZDEwNWNkZmViODgzMzJhZDEwOTM5ODA2YmJjMDNmNzYxYThiMWU3M2VkZTgwZmVkMzA0MjhmOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5325">
+      <c r="A5325" t="inlineStr">
+        <is>
+          <t>1179.psd</t>
+        </is>
+      </c>
+      <c r="B5325" t="inlineStr">
+        <is>
+          <t>tamilpsd-11232.psd</t>
+        </is>
+      </c>
+      <c r="C5325" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdYbEwzaVI4UVllTC8rdFBoeVpETHc9PSIsInZhbHVlIjoiVHNQY2pRZ0V0UVhMZWJsZjhFRUsxUT09IiwibWFjIjoiZThhYTU1OTY4MTJiZmE5NmYyNTA2YmYwNGQ5NzI2ZjUwMGQ1YTMxZDBhMzNlNWI1ZTI2Yjc0Mjc3MTY3MjhlZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5326">
+      <c r="A5326" s="3" t="inlineStr">
+        <is>
+          <t>1178.psd</t>
+        </is>
+      </c>
+      <c r="B5326" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11233.psd</t>
+        </is>
+      </c>
+      <c r="C5326" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFWOG9ORFhWRk4wdVl5VFB6V1VrTFE9PSIsInZhbHVlIjoiWVhjbVJEVDJ2WmRqT1RwNzZ1SWl1dz09IiwibWFjIjoiYjZlYzlmZDE4NTNkYjk2MTZjOWFlNWMyYTBlZWFlZWFiMjAwZmJmY2M1NDc5ZGJlMmRmMjFjYjlhYjNmOTczMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5327">
+      <c r="A5327" t="inlineStr">
+        <is>
+          <t>1177.psd</t>
+        </is>
+      </c>
+      <c r="B5327" t="inlineStr">
+        <is>
+          <t>tamilpsd-11234.psd</t>
+        </is>
+      </c>
+      <c r="C5327" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFiRDJpbmNCdVJIa2prR2tWNWNJRmc9PSIsInZhbHVlIjoibks0TWVXWmM5YktWWVBnTDRUNC9iQT09IiwibWFjIjoiMjAzODY1NzAyODY1OGRiM2M0MGZkNDY4M2JhODM4OTQwZjczODZmZDlmMmNhNzAxMmExZjc2NzNlYjY3OWFmZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5328">
+      <c r="A5328" s="3" t="inlineStr">
+        <is>
+          <t>1176.psd</t>
+        </is>
+      </c>
+      <c r="B5328" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11235.psd</t>
+        </is>
+      </c>
+      <c r="C5328" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNoam43Zm0yemVnSGc2NVlubUU2Q2c9PSIsInZhbHVlIjoiTEUvbnQzODcvSTNXRmcyVjZxUVF4dz09IiwibWFjIjoiNDE4NmEyMGJjNzVmZjE2MjI1YmQ3NTc5NTdjZWI1N2RhMjc1ZTM3OWE3MzIyMmMyMWZhODUwMDIxZTk0NmNlNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5329">
+      <c r="A5329" t="inlineStr">
+        <is>
+          <t>1175.psd</t>
+        </is>
+      </c>
+      <c r="B5329" t="inlineStr">
+        <is>
+          <t>tamilpsd-11236.psd</t>
+        </is>
+      </c>
+      <c r="C5329" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBGQ3RQdGdwVHcxemtzVjVCU1Z1cVE9PSIsInZhbHVlIjoiQzJEb0VDdTYwRE5nak5VSU5wakh6UT09IiwibWFjIjoiOGJiNDk2MmExZDQ5NmUwNGE3NjlmOTRlYzJiYjZkOGRiYmIxNGQzOGYxZDRlOTY1YzAxZjE2ODc1NmJjNDgwNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5330">
+      <c r="A5330" s="3" t="inlineStr">
+        <is>
+          <t>1174.psd</t>
+        </is>
+      </c>
+      <c r="B5330" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11237.psd</t>
+        </is>
+      </c>
+      <c r="C5330" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijc4eTZXNGQxeHRWa2VjREpORklIZUE9PSIsInZhbHVlIjoiU0hFRm5VWEVtS0taV0Vkb2pWUWswQT09IiwibWFjIjoiMDhhMTNjOTc0NzMxNTU3YTZkOWVlMWYyZWU3YjM5NjNlODA4ZDhiZDE0NzFjZTQ0ZmViYzdmOTBmZjFjMzA4MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5331">
+      <c r="A5331" t="inlineStr">
+        <is>
+          <t>1173.psd</t>
+        </is>
+      </c>
+      <c r="B5331" t="inlineStr">
+        <is>
+          <t>tamilpsd-11238.psd</t>
+        </is>
+      </c>
+      <c r="C5331" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhzbEEvVjNPUkpnakZ0ZHRvV0hmVGc9PSIsInZhbHVlIjoiZnpvdkczNmsydjQ4eWprVDZ0WHpvZz09IiwibWFjIjoiNWY5M2I1ZDg2NzMzMDJlOWVjYWQzYTViMGVkNWJhZWI0MzVlNGIyYTc0YWQyYzE1ZTdmNzBkY2U3N2Q5MDhjZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5332">
+      <c r="A5332" s="3" t="inlineStr">
+        <is>
+          <t>1172.psd</t>
+        </is>
+      </c>
+      <c r="B5332" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11239.psd</t>
+        </is>
+      </c>
+      <c r="C5332" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZmRUtEZTVBUlJ5Z0UzODU5TVNUN1E9PSIsInZhbHVlIjoiSUV2elMxVkZaNEhzQitOMVk1QzQ0UT09IiwibWFjIjoiYWE4OTI5MTA2MTI4ZGY0NTJlMDhiZDIzNmVhMGU0YzA4NWI4MmMxOGIwMDhiNjhlMGUyN2Y0NDQyMTIzY2UxZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5333">
+      <c r="A5333" t="inlineStr">
+        <is>
+          <t>1171.psd</t>
+        </is>
+      </c>
+      <c r="B5333" t="inlineStr">
+        <is>
+          <t>tamilpsd-11240.psd</t>
+        </is>
+      </c>
+      <c r="C5333" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRnbUxQMFlDd3o2ZVViQWIrUENIUkE9PSIsInZhbHVlIjoiYVl2azVWN2MyeUMvdHQzV2JaL3BMdz09IiwibWFjIjoiMmFlZTk4MWRiNmQzNzU2ZTk5YjNmNzc2YzE0NDExZGY3OWMyMmJiNDgzODZiZjE2ZjZlMTIwYzQyNGNjOWQ4ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5334">
+      <c r="A5334" s="3" t="inlineStr">
+        <is>
+          <t>1170.psd</t>
+        </is>
+      </c>
+      <c r="B5334" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11241.psd</t>
+        </is>
+      </c>
+      <c r="C5334" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVUclNhSnRhNWg1RUtIUmc3OUdqeEE9PSIsInZhbHVlIjoiYWNHbHdmUTNvT0MyaUtranFPNWtOUT09IiwibWFjIjoiNGRlOTI0MzMzYWY1ZjA3NGFlY2E5Zjc4ZDE0MzgzZGI1NzI1YjQ3YTVhOTI1NmFlM2EwOWI0ZjVkOWI4YTdiOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5335">
+      <c r="A5335" t="inlineStr">
+        <is>
+          <t>1169.psd</t>
+        </is>
+      </c>
+      <c r="B5335" t="inlineStr">
+        <is>
+          <t>tamilpsd-11242.psd</t>
+        </is>
+      </c>
+      <c r="C5335" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllWZ0tVY0J3U0FwdHVxMG5vZmtTUlE9PSIsInZhbHVlIjoiWi9XUEVlaTRzTzNpTnBpM2IwZTd3dz09IiwibWFjIjoiNjNhNDI4MDk0NjNhOTdkMzQ5NTMyMzJmNTI1Yjg3Mzg1ODY4YmZjNzhiODA2YmIzODcwZDlkYzUwNDc4YzhiNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5336">
+      <c r="A5336" s="3" t="inlineStr">
+        <is>
+          <t>1168.psd</t>
+        </is>
+      </c>
+      <c r="B5336" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11243.psd</t>
+        </is>
+      </c>
+      <c r="C5336" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBhdGRIdnVBZjlLYmhXTlB6T1prVmc9PSIsInZhbHVlIjoiRHA4bjBGeHlHcE5lVzkrcFpiQ0xaUT09IiwibWFjIjoiM2UyZGNjOTRkNjEzZDIwNDYwZjkyZWVhOWYyZThiMGI5ODM3Zjc5NWIyMmI1YTZlOGEwZWIzZTIzZjJjN2FiNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5337">
+      <c r="A5337" t="inlineStr">
+        <is>
+          <t>1166.psd</t>
+        </is>
+      </c>
+      <c r="B5337" t="inlineStr">
+        <is>
+          <t>tamilpsd-11244.psd</t>
+        </is>
+      </c>
+      <c r="C5337" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1adTA3SEYxR1A2Z3BTMWxDTzVOMHc9PSIsInZhbHVlIjoidFprb0V6UU84STVZeHJwMCtiYjNXQT09IiwibWFjIjoiOThkMzhmY2Y5NTgxYjQ4OWQ1YTczOTFkNjlhODUyODhhOTZjMGMwZWEyNjRkMWUzZDVkY2I3YzU1MDA1YzkyZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5338">
+      <c r="A5338" s="3" t="inlineStr">
+        <is>
+          <t>1165.psd</t>
+        </is>
+      </c>
+      <c r="B5338" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11245.psd</t>
+        </is>
+      </c>
+      <c r="C5338" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJ6REFKOXA0L1BhUnVqV0lpSmhzaWc9PSIsInZhbHVlIjoibEl5cG1QUnc3dUFxSnZzM09Xb21VQT09IiwibWFjIjoiYjY4Y2ZkNGQyYmNjZDY0ODQxMjU2NDdjNmZiMWNmOTc5YTM0MDVkNjc0OTBjNzNiY2JkNTRlNDdmODhiMzBiNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5339">
+      <c r="A5339" t="inlineStr">
+        <is>
+          <t>1372.psd</t>
+        </is>
+      </c>
+      <c r="B5339" t="inlineStr">
+        <is>
+          <t>tamilpsd-11246.psd</t>
+        </is>
+      </c>
+      <c r="C5339" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im82VjZNaWpGQVdXQzJTb3JvY3ZPTGc9PSIsInZhbHVlIjoiQjQ0Q1lsMjROM1dXbC8xSDVvaXVCZz09IiwibWFjIjoiYmUwM2JmZDc4NDY5OTFiMTIzYzI3NTRhMGQ5NWQ4NmFjYjRmMWJmY2VmZWE4ODI5Yzc4M2UxNDg2M2RlNjBlNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rename_log.xlsx
+++ b/rename_log.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5339"/>
+  <dimension ref="A1:C5809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -67130,6 +67130,7996 @@
         </is>
       </c>
     </row>
+    <row r="5340">
+      <c r="A5340" s="3" t="inlineStr">
+        <is>
+          <t>1371.psd</t>
+        </is>
+      </c>
+      <c r="B5340" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11247.psd</t>
+        </is>
+      </c>
+      <c r="C5340" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNDUFpHb2VaM2d3bWtQakhCeUdnMXc9PSIsInZhbHVlIjoiekVJNmthS21iL0xDd2pZUmRMV1Z0UT09IiwibWFjIjoiOGM2NTZkMzk1MTkwNjJkZGYyODc0MjI3ZmQyOWUwNDM5Y2IxMDI4MzJkMmI2NjJlMDJmNjJkYjAzNmQ0MWRkMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5341">
+      <c r="A5341" t="inlineStr">
+        <is>
+          <t>1370.psd</t>
+        </is>
+      </c>
+      <c r="B5341" t="inlineStr">
+        <is>
+          <t>tamilpsd-11248.psd</t>
+        </is>
+      </c>
+      <c r="C5341" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpkTDBLZTBLcVpqT3JqRFpwSks1bUE9PSIsInZhbHVlIjoiNmM0cUdTN092WmJwVmc5bHdOcTY2Zz09IiwibWFjIjoiNWY4Y2MxZTU3N2FiNWNiZjAzOGFmY2ZhYzRhZWYzNTllM2IzNmI1MWFmZTJjMzFkN2I5OTNmMWEzMTQ5YTMzZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5342">
+      <c r="A5342" s="3" t="inlineStr">
+        <is>
+          <t>1369.psd</t>
+        </is>
+      </c>
+      <c r="B5342" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11249.psd</t>
+        </is>
+      </c>
+      <c r="C5342" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJJZEdTbGlHa1BBcFdWTmNZTWYyVXc9PSIsInZhbHVlIjoiY3FNZ2M4a0lRaGExLzdnS3R2clc5Zz09IiwibWFjIjoiZTg5MDMzODBjYzBjODY4OTAzOWMwYTJiYTZhMTUxNzVjOTA0MGYwZWM4NTg4Mjc4YWY4OTMyYTAwMGZkY2YzNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5343">
+      <c r="A5343" t="inlineStr">
+        <is>
+          <t>1368.psd</t>
+        </is>
+      </c>
+      <c r="B5343" t="inlineStr">
+        <is>
+          <t>tamilpsd-11250.psd</t>
+        </is>
+      </c>
+      <c r="C5343" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhkTlpUbUxKMnNzLzRpNnZ0bXhQUUE9PSIsInZhbHVlIjoiUmFVZ0JHaEJsTElxcXhiMFYxY0liQT09IiwibWFjIjoiOGZkMmMzNThiZGUwZjhiZTNhMzJhZjM2MTViMjJhYTdlYzhhNWNhY2I3Y2E4YWQwMTgzYTQwMDA4YzQ4MDdjOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5344">
+      <c r="A5344" s="3" t="inlineStr">
+        <is>
+          <t>1367.psd</t>
+        </is>
+      </c>
+      <c r="B5344" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11251.psd</t>
+        </is>
+      </c>
+      <c r="C5344" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ink1N1dSbzNuT0RGZmdpZWRLUjJJN3c9PSIsInZhbHVlIjoidkEwV28rQUVocHJpd0lOU2tlWEVBdz09IiwibWFjIjoiYTI2YTY2Zjc5YTdlNmZhZTAxMTFlYWEzYzQ1NmIzMDE1NDg1YjRmNzYwOGFlOGFhYjI0MTg5NTRkYmE2ZmE3NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5345">
+      <c r="A5345" t="inlineStr">
+        <is>
+          <t>1365.psd</t>
+        </is>
+      </c>
+      <c r="B5345" t="inlineStr">
+        <is>
+          <t>tamilpsd-11252.psd</t>
+        </is>
+      </c>
+      <c r="C5345" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InprRHBiMmpkMHFsalZaWDVnRGFtVXc9PSIsInZhbHVlIjoiZXh6UDBGN2RnVjJGZlJHdmhIOEZMdz09IiwibWFjIjoiN2U2NDA3ZDQzOGQxYzNhNWYxOWJhYWZjODBjZmE0NGU1MzRmNWU3OGQ2NjIyZTFiZmNjZDlkZmEwNjRkMzE0NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5346">
+      <c r="A5346" s="3" t="inlineStr">
+        <is>
+          <t>1366.psd</t>
+        </is>
+      </c>
+      <c r="B5346" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11253.psd</t>
+        </is>
+      </c>
+      <c r="C5346" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlJdUJSUWNCek5ZbnpCcG10TTByTkE9PSIsInZhbHVlIjoicjViVzZXM2oxUGpxeDI5T3BobkdYQT09IiwibWFjIjoiZWFiM2Y3MzY5NWE0ZjQ4ZjhmZWIwOGRlZmY3YjBkNTI3MjJhODA0NTFjMTg0Yzk5NWNkYTY5YjYyOWExOTM4ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5347">
+      <c r="A5347" t="inlineStr">
+        <is>
+          <t>1364.psd</t>
+        </is>
+      </c>
+      <c r="B5347" t="inlineStr">
+        <is>
+          <t>tamilpsd-11254.psd</t>
+        </is>
+      </c>
+      <c r="C5347" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im8wbktERm9rS1dmYjJhSHROYW1oN3c9PSIsInZhbHVlIjoiQW81c01rcFFmdi9pK25sMWF6bHcwUT09IiwibWFjIjoiYzAwZWMyYjcwZDc1MjE2ODI5N2IyZTY3ZGUzOTgyMTU2YzU1MDQ4NTQ0ZjlhMmRkMzA5YTljNWM0MWU3OTAzOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5348">
+      <c r="A5348" s="3" t="inlineStr">
+        <is>
+          <t>1363.psd</t>
+        </is>
+      </c>
+      <c r="B5348" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11255.psd</t>
+        </is>
+      </c>
+      <c r="C5348" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpJb1kxQUl6bXN3eHpNaEwrdzl2Y1E9PSIsInZhbHVlIjoiY21PU05nYWNzVFRYYUJBeVpHNWRLZz09IiwibWFjIjoiOGFkYTYyNzU1ZDNkYTUyOGI4NjNkMmVhODA3YjlkZGViZGJiZDViYzgxMzg5N2FhZTQ4NzVlNGI1MjY2NTEyYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5349">
+      <c r="A5349" t="inlineStr">
+        <is>
+          <t>1362.psd</t>
+        </is>
+      </c>
+      <c r="B5349" t="inlineStr">
+        <is>
+          <t>tamilpsd-11256.psd</t>
+        </is>
+      </c>
+      <c r="C5349" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlUvM3RXYTdYcDFBbFAvZm1UbElLS0E9PSIsInZhbHVlIjoiekNobEVwRnZRU1RiTmh6cWUxNGwwdz09IiwibWFjIjoiZTRkMzFmNDBjY2Q5MGIyMjhiNTljZDQyNGEyNzRhOTg4ZmZiYjE0OWEyNmE1MjAzMjYxZTUxMjhmNjJiNzk1OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5350">
+      <c r="A5350" s="3" t="inlineStr">
+        <is>
+          <t>1361.psd</t>
+        </is>
+      </c>
+      <c r="B5350" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11257.psd</t>
+        </is>
+      </c>
+      <c r="C5350" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktLNTlaYStZZHFMTFMySWIvMEk2MkE9PSIsInZhbHVlIjoiZXk4RVFLUHNtbU15KzRqb3FvaVRRUT09IiwibWFjIjoiMDg2YjhjZDJlNzg3ZmZiMjJkZGY1NWRmODI2OGM3ZGI5MDA0ZTYyZmZhMjgyMWI4N2M5Y2U5NDc2YTg1MjEyMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5351">
+      <c r="A5351" t="inlineStr">
+        <is>
+          <t>1360.psd</t>
+        </is>
+      </c>
+      <c r="B5351" t="inlineStr">
+        <is>
+          <t>tamilpsd-11258.psd</t>
+        </is>
+      </c>
+      <c r="C5351" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5FR0R3dHpGQXJWZVF6dlVEUmZQV2c9PSIsInZhbHVlIjoicXJGQUhXTHVWMUJ6MzVzM2ZFSmhqdz09IiwibWFjIjoiZGM5ODE1NTc5MDM5MGUwODQ4ZjlhYzYzOGFmNzA3MTgzOTg4MTUwYzdiMjRkOTgxMjZkMjkzMWQyNTUwNTJkNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5352">
+      <c r="A5352" s="3" t="inlineStr">
+        <is>
+          <t>1359.psd</t>
+        </is>
+      </c>
+      <c r="B5352" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11259.psd</t>
+        </is>
+      </c>
+      <c r="C5352" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpiOGpwWEJkWGhDSlNRckxHcGtYTWc9PSIsInZhbHVlIjoibWtYckZiT29jUExuRGZIWWNnbCtnUT09IiwibWFjIjoiOGY0Y2NkNjdjY2VkYWI3MGQwODViMzA0MDY5M2EyNmY2MDFiMDY1ZjJiOTM5YWY4NmExZjg0OTE0YWQ5NzViYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5353">
+      <c r="A5353" t="inlineStr">
+        <is>
+          <t>1358.psd</t>
+        </is>
+      </c>
+      <c r="B5353" t="inlineStr">
+        <is>
+          <t>tamilpsd-11260.psd</t>
+        </is>
+      </c>
+      <c r="C5353" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpxclozSWdVVUVSUzNFbVU1MlFzZmc9PSIsInZhbHVlIjoiVzFPWlQyTXhRR3NPdjU5S1BpVDBIUT09IiwibWFjIjoiMTcxMDY4Y2Y2OGMzY2E3Y2U4ZjcyZGYwZTJlOGU0ZDdmNDgzMDhkZWYzMDQ1MTEwNjAyODgyYjljZGJjM2Y3NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5354">
+      <c r="A5354" s="3" t="inlineStr">
+        <is>
+          <t>1357.psd</t>
+        </is>
+      </c>
+      <c r="B5354" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11261.psd</t>
+        </is>
+      </c>
+      <c r="C5354" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlYxbEpQTjR5NEpiRnhDVzJHbWt0TUE9PSIsInZhbHVlIjoiZmhYVXhmcmdMa1BBVnNscVlZYlE5dz09IiwibWFjIjoiZGQxM2ZhYzZkYmQyZmIzMWMzZWM4OGYxNzE4M2YxMmY5ZWIwZTE0MzFlMTdkMTRhMTZmNjc0YzhhZDIyN2M4YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5355">
+      <c r="A5355" t="inlineStr">
+        <is>
+          <t>1356.psd</t>
+        </is>
+      </c>
+      <c r="B5355" t="inlineStr">
+        <is>
+          <t>tamilpsd-11262.psd</t>
+        </is>
+      </c>
+      <c r="C5355" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1QVHBCRTg0V2pITHk3N3hEbEZqMXc9PSIsInZhbHVlIjoiSWRKYUpWY1ZlejUrbCtPckRsNVUrUT09IiwibWFjIjoiOTJkZDRhMzIwNTgyNDMwYzdjYzgzZDg1ODJjY2U5NGFjNDU4ODU3ZjJmYmQ2NDA4Y2JhNjkwZmViOWYwNDVmMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5356">
+      <c r="A5356" s="3" t="inlineStr">
+        <is>
+          <t>1355.psd</t>
+        </is>
+      </c>
+      <c r="B5356" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11263.psd</t>
+        </is>
+      </c>
+      <c r="C5356" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im01TUd6MWl4TGdWVGExTkJFRzdmaFE9PSIsInZhbHVlIjoidW1LOTRGU0NORjdGLzg5YWNaS3lzZz09IiwibWFjIjoiM2Y2YTQ1Y2QxMDUwMWUwZjEwMGNhMzA1ODI4ZjkwNjUzZjFjMTcxNmRmMDlmNjZkYjc2ODNiODJiYWMxZjU0ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5357">
+      <c r="A5357" t="inlineStr">
+        <is>
+          <t>1354.psd</t>
+        </is>
+      </c>
+      <c r="B5357" t="inlineStr">
+        <is>
+          <t>tamilpsd-11264.psd</t>
+        </is>
+      </c>
+      <c r="C5357" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImF5NEhPRGFaaVM0R0U0b3BDUW9ZY1E9PSIsInZhbHVlIjoiaUVkYnJaWCsrai95akpBTWMvRlRTQT09IiwibWFjIjoiNzcxZWVlNjkwNTIwODA0MTc1NWU5NTg1ZGQ3YzBjODQ0OGQzZTdkZmM2YWY3ZGM3YjU5ZjEyYzk2YTg3OWFhNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5358">
+      <c r="A5358" s="3" t="inlineStr">
+        <is>
+          <t>1353.psd</t>
+        </is>
+      </c>
+      <c r="B5358" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11265.psd</t>
+        </is>
+      </c>
+      <c r="C5358" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpWR0UrTjMrcVZkL21Qd1FpdlYybkE9PSIsInZhbHVlIjoiSmt6QmFHWG5kbzIzcTh4Rm1hNzYwUT09IiwibWFjIjoiNDMxMTQ4MjU5NDU0NmY4Yzc0YTc0ZGEyMzE3YzQ0NDEzNTc4ZmQyNjQ4ZmRiMTlmMGQ3ZmUwYjIxNzgxNWI3YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5359">
+      <c r="A5359" t="inlineStr">
+        <is>
+          <t>1352.psd</t>
+        </is>
+      </c>
+      <c r="B5359" t="inlineStr">
+        <is>
+          <t>tamilpsd-11266.psd</t>
+        </is>
+      </c>
+      <c r="C5359" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9iSWx6Ymt2S1ZEY2dMSDNFazJJcUE9PSIsInZhbHVlIjoiZE1naVMzckxlY2xXWEpwaFJ0bE5HUT09IiwibWFjIjoiYzJmOGVhYmU4MGJmNTVlNjE3MjAxNDgzMmM2OGJjNjkwM2Y3NTkyZDcyZjJhZDI5OTdiN2I5OTcyNzQ2N2ZmNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5360">
+      <c r="A5360" s="3" t="inlineStr">
+        <is>
+          <t>1351.psd</t>
+        </is>
+      </c>
+      <c r="B5360" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11267.psd</t>
+        </is>
+      </c>
+      <c r="C5360" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklKcjIwVGpVZUZLRm05ZHhOckJVNlE9PSIsInZhbHVlIjoiNjNETDUwL0QyQW5Fc3FQUXpucGhLUT09IiwibWFjIjoiY2M5NTQzOWZkN2E5NmIzM2U4MWRjOTFhNjM0NGVjNGRjN2ZkYmVjOTIwMGQ3ODRmN2Q3OWYyZWY3YmY1ZjI0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5361">
+      <c r="A5361" t="inlineStr">
+        <is>
+          <t>1350.psd</t>
+        </is>
+      </c>
+      <c r="B5361" t="inlineStr">
+        <is>
+          <t>tamilpsd-11268.psd</t>
+        </is>
+      </c>
+      <c r="C5361" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjM2VldqaGlrQk93bXNyeHdjeVEzVlE9PSIsInZhbHVlIjoiLzJCL0lzV0xtMDEyRnhnMkpGN3hmZz09IiwibWFjIjoiODFhNzIxYjk3YjE5Yjc2Zjk3ZjFjMjZmZDlhYjNmNTRiYjhmOGRmY2VlNzcwY2RmODQ0NmQxOWZlYzY3MzkzNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5362">
+      <c r="A5362" s="3" t="inlineStr">
+        <is>
+          <t>1348.psd</t>
+        </is>
+      </c>
+      <c r="B5362" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11269.psd</t>
+        </is>
+      </c>
+      <c r="C5362" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iit2WGRDVWh3NDdRZkVESHpocFVIMGc9PSIsInZhbHVlIjoiVTZMMzJraitGWEFtQ25QUklWZEZIQT09IiwibWFjIjoiNzE4ODY4MTlmMzQ3NmFmYzNmZmY5ZjcwMWY1NTIyMGE0ODk5MjRiNTRlZGZhMTk4M2FkMzVkNzNhNDJjM2VlZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5363">
+      <c r="A5363" t="inlineStr">
+        <is>
+          <t>1349.psd</t>
+        </is>
+      </c>
+      <c r="B5363" t="inlineStr">
+        <is>
+          <t>tamilpsd-11270.psd</t>
+        </is>
+      </c>
+      <c r="C5363" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InM3R0FMb3Z3SGVWYlBWZE52aTFNdEE9PSIsInZhbHVlIjoiVUlMT2ZWTHE3TFZpdnhrOWVUSWw3QT09IiwibWFjIjoiZTk2NjcwOGI5ZTM0MTM2ZDc4N2Y5NTZhYzg3NDRiM2RkNzdjMzZjODdkNjJkNTZkZGQ1MTYwN2UwOTc0YzYxZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5364">
+      <c r="A5364" s="3" t="inlineStr">
+        <is>
+          <t>1347.psd</t>
+        </is>
+      </c>
+      <c r="B5364" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11271.psd</t>
+        </is>
+      </c>
+      <c r="C5364" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRVWTlMRnd6Z05obHlBWFdTUEs2cGc9PSIsInZhbHVlIjoibWs3SU9qMDdjNUVJaXlOSjVRTnZVQT09IiwibWFjIjoiYWFlMDVlNmY1OGQ2YzZiMjE5OGQ4MTQzZGUxMWIwNjFhZjc2M2U1ZDg2MGJmYmMyZTczNmNjZTQ5MTFlMDllMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5365">
+      <c r="A5365" t="inlineStr">
+        <is>
+          <t>1346.psd</t>
+        </is>
+      </c>
+      <c r="B5365" t="inlineStr">
+        <is>
+          <t>tamilpsd-11272.psd</t>
+        </is>
+      </c>
+      <c r="C5365" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5pbGhibUl4V29IMSsxaW93eGFWeHc9PSIsInZhbHVlIjoiWmhzZldZbmdkdjUrSTVPb0hpaEdvdz09IiwibWFjIjoiMzBkMmNmOWY3NmM2M2MwZmExOWJhMGI0ZTA2ZjU5MzZkMWRlNGZjZGFkZDhjODM0Y2Y4NjdlNDFlNjEyZGNkMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5366">
+      <c r="A5366" s="3" t="inlineStr">
+        <is>
+          <t>1345.psd</t>
+        </is>
+      </c>
+      <c r="B5366" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11273.psd</t>
+        </is>
+      </c>
+      <c r="C5366" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNBMlRsb1Vka3V3T0xhYlNXbjJVb1E9PSIsInZhbHVlIjoiMEM5bzJqQkhvQS8zcENGUCtiV2J3UT09IiwibWFjIjoiYTExNWNkNGNiNDQ4ODNjZTE2N2E4YjllMjg5Njc0YzQ0NGE5NzY4YTUxMzEyYTE1NjdmMjFiNTI5MzcyZjNjMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5367">
+      <c r="A5367" t="inlineStr">
+        <is>
+          <t>1344.psd</t>
+        </is>
+      </c>
+      <c r="B5367" t="inlineStr">
+        <is>
+          <t>tamilpsd-11274.psd</t>
+        </is>
+      </c>
+      <c r="C5367" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVaczVNSlN1ZjJ1dkpHVExVVnNuUXc9PSIsInZhbHVlIjoiZ1pGZmhhT2tqZVd2R3RpekJJTHFQZz09IiwibWFjIjoiOTU3YzVmYjgyMGU3YTg0MDZiZTc5ZTI4ZThjNTYzYzk4YjhiMmI3NzE0OTQ2NjQ1NjZlZGMzOGQ2MDEwNjgwZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5368">
+      <c r="A5368" s="3" t="inlineStr">
+        <is>
+          <t>1343.psd</t>
+        </is>
+      </c>
+      <c r="B5368" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11275.psd</t>
+        </is>
+      </c>
+      <c r="C5368" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxGMnhyK0F4cjFrZXo3Nm5WK3lva3c9PSIsInZhbHVlIjoiYnZWdHAzcFdEZ2RRZDJsck5OQmZGUT09IiwibWFjIjoiYWFlYTg5OGU0ZGNmNzZlMjI0OWJmZDFhNjIzMDk3ZDJmZWFlYTgxNWEzZjk1MjY5N2I5NGE0MjNiMDkwMDMyYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5369">
+      <c r="A5369" t="inlineStr">
+        <is>
+          <t>1342.psd</t>
+        </is>
+      </c>
+      <c r="B5369" t="inlineStr">
+        <is>
+          <t>tamilpsd-11276.psd</t>
+        </is>
+      </c>
+      <c r="C5369" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJKcy9FclRQSUtjUk1MWG9iK3pPZGc9PSIsInZhbHVlIjoiek8yNlBYejdXQ001VVpJU1dnWUoyQT09IiwibWFjIjoiNzk0ZjA4YjA1MjYyOTI4YjVmZTQ2YzE5NTg3NzE2ZDVmODA5MDAzNmRhZTUwYTAzZWZhNmVjNmM5OTgzNzY3ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5370">
+      <c r="A5370" s="3" t="inlineStr">
+        <is>
+          <t>1341.psd</t>
+        </is>
+      </c>
+      <c r="B5370" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11277.psd</t>
+        </is>
+      </c>
+      <c r="C5370" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlmQmw1M0hzQ3l1U2pCR0ZnOGVkVFE9PSIsInZhbHVlIjoiUllLN3VIb3drZnYyMHpicW94Z0Y3UT09IiwibWFjIjoiYjYyNmVkOWNhNjM0NjA5ZGQ3MTRhZTllYjFjZDhmYmRlYmJlMThlZWNkOWJmZDg3NjkyMjY2YzUxYjE3OWNkZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5371">
+      <c r="A5371" t="inlineStr">
+        <is>
+          <t>1339.psd</t>
+        </is>
+      </c>
+      <c r="B5371" t="inlineStr">
+        <is>
+          <t>tamilpsd-11278.psd</t>
+        </is>
+      </c>
+      <c r="C5371" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikh6SE9uV0RRaUVPVkg0TFQrbHJYYnc9PSIsInZhbHVlIjoieHA0S3hqdHYrSlBPOXBuWm9abHFCZz09IiwibWFjIjoiMjgzOTZhZmMxOTM4MGEyNjhmZGU5ZWQ4YzA2NjEyNGMzNDc0ZTZkNWVkOWRkNDhhOWFjZmY4MGIzYWFiZTZlMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5372">
+      <c r="A5372" s="3" t="inlineStr">
+        <is>
+          <t>1338.psd</t>
+        </is>
+      </c>
+      <c r="B5372" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11279.psd</t>
+        </is>
+      </c>
+      <c r="C5372" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjE5dE1GMC8zR1p2azZJM1lTV3FNcmc9PSIsInZhbHVlIjoiUVJtVEtaWUk0dGIyME9jV1g2b29oUT09IiwibWFjIjoiZDM4NTQyMzU1MmY5MDcxZDJiMmFiMjRkZGFlMzIwNWVhNzQwZjk0NzNjMDU4YmE2NzE4MjRjZDY0N2I5MTAzYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5373">
+      <c r="A5373" t="inlineStr">
+        <is>
+          <t>1337.psd</t>
+        </is>
+      </c>
+      <c r="B5373" t="inlineStr">
+        <is>
+          <t>tamilpsd-11280.psd</t>
+        </is>
+      </c>
+      <c r="C5373" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNlcHdnZ3plRHpMREtvTGFkZTVkNnc9PSIsInZhbHVlIjoidnhzZmQvTWZjbkZMR2JKNDdOU3dhQT09IiwibWFjIjoiN2M4N2NkNjE2MTA3NTlmZmVkNzg4Mjc3Zjc0ZDk3MjhiNjZkYjM2ZGMxYzJiNjNkYjFhZmE0ZTY4MTM0MzQ5MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5374">
+      <c r="A5374" s="3" t="inlineStr">
+        <is>
+          <t>1336.psd</t>
+        </is>
+      </c>
+      <c r="B5374" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11281.psd</t>
+        </is>
+      </c>
+      <c r="C5374" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxWaHBKTlZUSVVEbUpaNy8wcGtaMlE9PSIsInZhbHVlIjoiOHBSeFhuY3pHN0NHckM5TlQzT0N5dz09IiwibWFjIjoiZDc5ZDU0MzIxZDI1ODYzYjA1YTc3ZmQ1NTA1Y2U4OWY3YjE1NzFlNjA5YTRkOTZiNTYwNDg2MjQxOWViZWE0NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5375">
+      <c r="A5375" t="inlineStr">
+        <is>
+          <t>1334.psd</t>
+        </is>
+      </c>
+      <c r="B5375" t="inlineStr">
+        <is>
+          <t>tamilpsd-11282.psd</t>
+        </is>
+      </c>
+      <c r="C5375" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdjRGJibXR5aGVkaWVIb1c0dEZWcEE9PSIsInZhbHVlIjoiU0kxemp1aWZtSXhlS1duVkVTcy9zUT09IiwibWFjIjoiMWFhOTdhNzRiNjVkMDUwZDcyZjRkZTUxMjdmZTVjMWJkOWExNDhiZDFlNWFmZTFjM2ExZWNjZDdlOWQ2Mjc5YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5376">
+      <c r="A5376" s="3" t="inlineStr">
+        <is>
+          <t>1335.psd</t>
+        </is>
+      </c>
+      <c r="B5376" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11283.psd</t>
+        </is>
+      </c>
+      <c r="C5376" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlM2aUp2V1QveXpGUjFCS0lIRGJsY0E9PSIsInZhbHVlIjoiOUVaM3pWV2RzYWZqd2syQ2Z0MkJTQT09IiwibWFjIjoiYjM5NGVkODZjZmU4YTYyYjRjYzk3ZDhiYTU5MjNmMWQ1MmZhZDIwNTM2MGYxNjUxNTg2ODVhZDBlMzVkNTc0OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5377">
+      <c r="A5377" t="inlineStr">
+        <is>
+          <t>1332.psd</t>
+        </is>
+      </c>
+      <c r="B5377" t="inlineStr">
+        <is>
+          <t>tamilpsd-11284.psd</t>
+        </is>
+      </c>
+      <c r="C5377" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjdRREZzVFR2N1BYOEo3WTNTYWVrQlE9PSIsInZhbHVlIjoiR25mU3poaTFhc0ZpVHdyMW5NVGlwQT09IiwibWFjIjoiMmQ4YWJlMDhjMTk1NGU3ZDQ0YTVlMzdiNTQ2YmZjZGI2NTA3MWJiMGVkOWRlMzMzOGFmMDdiM2U3YzAzYzJlZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5378">
+      <c r="A5378" s="3" t="inlineStr">
+        <is>
+          <t>1331.psd</t>
+        </is>
+      </c>
+      <c r="B5378" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11285.psd</t>
+        </is>
+      </c>
+      <c r="C5378" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9DbCtESGJLYjJvYlFPb2gzTVhsZFE9PSIsInZhbHVlIjoieXJwMVM0WTNibWc1cjBXTDA1eVN4QT09IiwibWFjIjoiZmI2ODgxZDllMDc5MTIwMTg0MzZlYjhhNjNhZDRlYjg0YzkyNjlhZGY1OTkyMjJmYmQxOTE0ZWM0M2FlNGEzMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5379">
+      <c r="A5379" t="inlineStr">
+        <is>
+          <t>1330.psd</t>
+        </is>
+      </c>
+      <c r="B5379" t="inlineStr">
+        <is>
+          <t>tamilpsd-11286.psd</t>
+        </is>
+      </c>
+      <c r="C5379" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpmRUljTXJHRWVETzVvUmFRTGNZMFE9PSIsInZhbHVlIjoiRlYwVzlNQ1ZNUnFXRXoyMXRscmJ2Zz09IiwibWFjIjoiMDExZTZlNjMzM2JmNWQxYmJhOTZkZjM3NDNiMjAyNzIwOWI0YjNhY2Y5MGIxYjYzOTcwMmViZjQ3YjZkYjEwYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5380">
+      <c r="A5380" s="3" t="inlineStr">
+        <is>
+          <t>1329.psd</t>
+        </is>
+      </c>
+      <c r="B5380" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11287.psd</t>
+        </is>
+      </c>
+      <c r="C5380" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktuYzFybTVUS0Rhb2Fpa3dGd1Evcmc9PSIsInZhbHVlIjoiOGNlSEdDWWcwN0sxcktvQ1FES2NrQT09IiwibWFjIjoiNjJjNzE4MDVlYWMwYjllMjdlYzYxOTcxMjJmMDlkYjM3NGJhZDEzNTUyMzk0Mzk4ZjNiZDcxZGJlYzBmNjY1NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5381">
+      <c r="A5381" t="inlineStr">
+        <is>
+          <t>1328.psd</t>
+        </is>
+      </c>
+      <c r="B5381" t="inlineStr">
+        <is>
+          <t>tamilpsd-11288.psd</t>
+        </is>
+      </c>
+      <c r="C5381" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtUcUQvNkovREtna3pBdUJHdmxhOXc9PSIsInZhbHVlIjoiWlQyL3VQWDB1UStVdUdLRXpqZWxhZz09IiwibWFjIjoiMjcwMGNhZjA0OGRmNzA0YjhlNjEwZGRiZjkwYjZlMWVmODA1YmY0YzgyYmU5NjljNDdlYjdmODkzODgzOTA1YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5382">
+      <c r="A5382" s="3" t="inlineStr">
+        <is>
+          <t>1327.psd</t>
+        </is>
+      </c>
+      <c r="B5382" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11289.psd</t>
+        </is>
+      </c>
+      <c r="C5382" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhCMkxzNml0dVZ6OGxZRXdJa0xvc3c9PSIsInZhbHVlIjoiUnUvR2Jzb3ZXazBwc3pZSFRSQngrQT09IiwibWFjIjoiMjliOTVmM2VkYTI4NDlkOTgzMDg5OGU2MWFmZjRkN2Y1NmU2ZTZkODhmNWRmOGE2NmMzYjUwMzM3OTM2YmI1NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5383">
+      <c r="A5383" t="inlineStr">
+        <is>
+          <t>1326.psd</t>
+        </is>
+      </c>
+      <c r="B5383" t="inlineStr">
+        <is>
+          <t>tamilpsd-11290.psd</t>
+        </is>
+      </c>
+      <c r="C5383" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZXclo2WlJIV2cyNjZCUEpFWk9NYlE9PSIsInZhbHVlIjoiYno0dUdVOTJzUzFNWm05ekdudUdVZz09IiwibWFjIjoiNzVmNWE2YjNjNjA5NmMwZjlkZjUwMTY0OGVjODQwNjIwODg0YzEyZjVjNzFkOGIwNjA2OGJhMWFkZDZhOTc2NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5384">
+      <c r="A5384" s="3" t="inlineStr">
+        <is>
+          <t>1325.psd</t>
+        </is>
+      </c>
+      <c r="B5384" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11291.psd</t>
+        </is>
+      </c>
+      <c r="C5384" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InpRbjN3dkNEQlcvMDVXNDNYcnhQeFE9PSIsInZhbHVlIjoieUdCdS8rSlNSYkJmRyt5RDlCYWprUT09IiwibWFjIjoiMGZmYWRmMGJkMzQ5ZjU0YWYwM2M5Y2JiYTk3ZmJhM2Q5ODE2ZmYyZTFjNDJmOTg0NWQyNjUwZDk0YzRiN2U1OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5385">
+      <c r="A5385" t="inlineStr">
+        <is>
+          <t>1324.psd</t>
+        </is>
+      </c>
+      <c r="B5385" t="inlineStr">
+        <is>
+          <t>tamilpsd-11292.psd</t>
+        </is>
+      </c>
+      <c r="C5385" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkovdnJHbmVTZjVtNDhQR1dMOERPTEE9PSIsInZhbHVlIjoiTk5IeTg0L3ZwQWZheXdET2FDcklYdz09IiwibWFjIjoiMWNmYmRjMmY4ODYyZmE2OTBiYjQ2ZTg3NzU3NDBkMDAzZDBiYTQwMGYxNGJmYTM0YmJmYjI2ZDZjMjlkNGRiNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5386">
+      <c r="A5386" s="3" t="inlineStr">
+        <is>
+          <t>1323.psd</t>
+        </is>
+      </c>
+      <c r="B5386" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11293.psd</t>
+        </is>
+      </c>
+      <c r="C5386" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZMbHRHazhnWmxXWkV2L3hqS1NzSlE9PSIsInZhbHVlIjoiV2YyNTUwOU1nc0EvWkU5U3k5czlzQT09IiwibWFjIjoiZTY5OGYxM2JmMmUwZmQ4YTBiMDAwNDUwYzljYWFkOGRjMTA2ODNhZjZjMjlmNDcwNjkzZGYxNjQ0MjQ2NTU4OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5387">
+      <c r="A5387" t="inlineStr">
+        <is>
+          <t>1322.psd</t>
+        </is>
+      </c>
+      <c r="B5387" t="inlineStr">
+        <is>
+          <t>tamilpsd-11294.psd</t>
+        </is>
+      </c>
+      <c r="C5387" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InJEa2ZQcytjUUtIQzFqem5Kd1JNL0E9PSIsInZhbHVlIjoiVUtPdFFrUFZVM1FEbnpTYXpWem52QT09IiwibWFjIjoiM2E4MDRhNTRiZTUwNDJmMjUwN2M1M2NlZGFkYjAyZjAyZTRlZjY1NGUzZjZjMjNhNWE0MTM2MDlhNzJjNTFmZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5388">
+      <c r="A5388" s="3" t="inlineStr">
+        <is>
+          <t>1321.psd</t>
+        </is>
+      </c>
+      <c r="B5388" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11295.psd</t>
+        </is>
+      </c>
+      <c r="C5388" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllzcFRTa2dvOUJJOHh5MFl2bHdwdWc9PSIsInZhbHVlIjoiejlVRmlTSmpmWDVBVXJJcDZjTEJPUT09IiwibWFjIjoiNzQxMDI3ODQ1ZTM1ZTdjNjY4MWQzNDE0YjMzYTM4MWNmMjNlNDc4YTllOGU3NWNiYjBkMGI4YmU5NmFkNzNhMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5389">
+      <c r="A5389" t="inlineStr">
+        <is>
+          <t>1320.psd</t>
+        </is>
+      </c>
+      <c r="B5389" t="inlineStr">
+        <is>
+          <t>tamilpsd-11296.psd</t>
+        </is>
+      </c>
+      <c r="C5389" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InB1ODdsSEU4VzZNdm9HSUZkdVZRR1E9PSIsInZhbHVlIjoiUjBBaTUzM2NqaWtkTEprNVFOMlBtdz09IiwibWFjIjoiODBhNDNkYWE4OGM1ODgxNTMzZmIzMWU3NjY1ZGZhNDljMzk1MDQ0YmUyZDU5NmE1YzU3NWI1MTU0ZTE3NDc5MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5390">
+      <c r="A5390" s="3" t="inlineStr">
+        <is>
+          <t>1319.psd</t>
+        </is>
+      </c>
+      <c r="B5390" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11297.psd</t>
+        </is>
+      </c>
+      <c r="C5390" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlLVGErWG82VFF6QUMrVHJNSG9sckE9PSIsInZhbHVlIjoiZEJ5U3ZvZGgrdHdiVDlzN0ZYaTlKdz09IiwibWFjIjoiMWUyNWMwY2E0MDRmZTI2M2ZhMTAyZmRiNmYxODE1YThlMTJmZWMwNDg1NzI0YjgxN2FlOGRhYzhmN2UyOTAwZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5391">
+      <c r="A5391" t="inlineStr">
+        <is>
+          <t>1318.psd</t>
+        </is>
+      </c>
+      <c r="B5391" t="inlineStr">
+        <is>
+          <t>tamilpsd-11298.psd</t>
+        </is>
+      </c>
+      <c r="C5391" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5wNTlEWHdKZDBLWDZTZklURUtUK1E9PSIsInZhbHVlIjoieUIyYkN5MUVzQjRYWitCUXM2d09IZz09IiwibWFjIjoiZmNlNDNhMWIwNjliYTgxMjY5ZGJjZmU2ZjU0ZWJkOWEyZTc1MDFhMGZiODI3NDlhZjUxMTk3YjkzY2E2YjJkYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5392">
+      <c r="A5392" s="3" t="inlineStr">
+        <is>
+          <t>1317.psd</t>
+        </is>
+      </c>
+      <c r="B5392" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11299.psd</t>
+        </is>
+      </c>
+      <c r="C5392" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9yWFBBa1ZOcVJIWHRwZU1hcis2K3c9PSIsInZhbHVlIjoiK0llTTEzaEFwNElvSGk2TnBXUVZLQT09IiwibWFjIjoiYTlmY2ZjNDNkODVjNGI0YTAxNTlhZmMxZTZiMGQ2MDYzNGM0OThmZDMyNDkwZjM2OGYwNTFlMTQ5NjQyMzA1MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5393">
+      <c r="A5393" t="inlineStr">
+        <is>
+          <t>1316.psd</t>
+        </is>
+      </c>
+      <c r="B5393" t="inlineStr">
+        <is>
+          <t>tamilpsd-11300.psd</t>
+        </is>
+      </c>
+      <c r="C5393" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlzeUZxNWtGbzU5eDVJN2w3QnFrQVE9PSIsInZhbHVlIjoidGxWNzB0YjVtQU9WNTV6S25hUnZWQT09IiwibWFjIjoiMWQxYjdhZjQ4NzIzZGZkYmJiN2ViNTlmNGNkYzRhYmM0YWMzZmFkNDM5ZDdlOWFlNjc3Y2ZkYTYxNDI1NTRjYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5394">
+      <c r="A5394" s="3" t="inlineStr">
+        <is>
+          <t>133.psd</t>
+        </is>
+      </c>
+      <c r="B5394" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11301.psd</t>
+        </is>
+      </c>
+      <c r="C5394" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9yalVOQ1luOGtBZUZaUVF3cDBlVFE9PSIsInZhbHVlIjoiQnFxdXpjZjFjYzNLeVY2WEQ2WCtzZz09IiwibWFjIjoiZmNkOWZiOGUzMzQ4Y2JkZWIwZDU3MGQyODI0Yzg4OTAwYjgxYzA4OGM1NTI5ZWUxZGYxYjI1N2M3ZTk0ZTE1NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5395">
+      <c r="A5395" t="inlineStr">
+        <is>
+          <t>1340.psd</t>
+        </is>
+      </c>
+      <c r="B5395" t="inlineStr">
+        <is>
+          <t>tamilpsd-11302.psd</t>
+        </is>
+      </c>
+      <c r="C5395" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktDblcyYUl5ZVlXeXY3RVZ5bGU5UGc9PSIsInZhbHVlIjoiYjVWZWVRdDdsUVo0LzFzaGQrOGVMQT09IiwibWFjIjoiMzA0ZDY3MDhmYzhhZmViODI3OTJjOGY4NDQ4MTJmMGEwNmZkMTYzNzU4OTdmZWE0ODJjMTA4YTUxMDRhOTdiZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5396">
+      <c r="A5396" s="3" t="inlineStr">
+        <is>
+          <t>1.psd</t>
+        </is>
+      </c>
+      <c r="B5396" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11303.psd</t>
+        </is>
+      </c>
+      <c r="C5396" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktyY2Njc3l6OTBhZ3IxVmd6d01BbkE9PSIsInZhbHVlIjoiOGs0R0pKMGJGMkpIRmJkWngvZFQ4Zz09IiwibWFjIjoiNjU0ZGQwNjRkOTA0ODM1YTg3MjM5OWNiMDNjODBkZTE2NTNkYzc0OWYzZGE1MTc3NmJiZDBiMzUzZTg0MGFkZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5397">
+      <c r="A5397" t="inlineStr">
+        <is>
+          <t>01 (18).psd</t>
+        </is>
+      </c>
+      <c r="B5397" t="inlineStr">
+        <is>
+          <t>tamilpsd-11307.psd</t>
+        </is>
+      </c>
+      <c r="C5397" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9mL1BHUmQvdUh6eTFIZERUcXRNS2c9PSIsInZhbHVlIjoiME8rd2ljSnExTGxidWl6YWcwTXIxUT09IiwibWFjIjoiZDg3N2FmZjJhMDY1MTIxMzkxOTBhZTkzM2MzYTU2ZDViY2M3ZDkyMmIxYTVhMjY0NTYyNWY0NmFkYmQzNDBhZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5398">
+      <c r="A5398" s="3" t="inlineStr">
+        <is>
+          <t>01 (17).psd</t>
+        </is>
+      </c>
+      <c r="B5398" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11309.psd</t>
+        </is>
+      </c>
+      <c r="C5398" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFnMW5RYjM4Y1RIc3dmM2hoUzQ1ZlE9PSIsInZhbHVlIjoiZ2oxWm5BTGFEMTFOczJ5cjN3UUlzUT09IiwibWFjIjoiZTNmMjk1OTc2ODIwODYwM2IyOTE3MDJkZTQ0ZTljMjFhODcwMWViMDcxMjljYmFmYjBkODBhOTlmMTBkMDA2ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5399">
+      <c r="A5399" t="inlineStr">
+        <is>
+          <t>01 (14).psd</t>
+        </is>
+      </c>
+      <c r="B5399" t="inlineStr">
+        <is>
+          <t>tamilpsd-11311.psd</t>
+        </is>
+      </c>
+      <c r="C5399" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkE3RDRSc3RpMWZsZ1d3b1psUUhBUWc9PSIsInZhbHVlIjoieFVHTC82ZjdTcjZLeXJwTFFIVHlJdz09IiwibWFjIjoiNDZhZjU3Yjk2Y2U3ODI5NTY1NjdiYTMzNmNhYzU3NTUwOGQ4N2Q1NDVmNmEwNmI3OTZmZGM1NTU1OWRkNzE4MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5400">
+      <c r="A5400" s="3" t="inlineStr">
+        <is>
+          <t>01 (13).psd</t>
+        </is>
+      </c>
+      <c r="B5400" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11312.psd</t>
+        </is>
+      </c>
+      <c r="C5400" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFpZklXRlhGaExxNGFPUmFDdXhqbkE9PSIsInZhbHVlIjoiQWh3cTd6SVJaZmM5WTBVempCOGFLdz09IiwibWFjIjoiOGRhNjJmN2MwYjQyMjY3YjhmYzcyMmNhYzNmMWRhMTNmMGVjZTA4ZDE2ZjE4MTc0ZjlkOTViMzMxNTU2NzBmZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5401">
+      <c r="A5401" t="inlineStr">
+        <is>
+          <t>01 (12).psd</t>
+        </is>
+      </c>
+      <c r="B5401" t="inlineStr">
+        <is>
+          <t>tamilpsd-11313.psd</t>
+        </is>
+      </c>
+      <c r="C5401" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpsL2RjeTA2bTNGUnU3ZURaZ0VUcVE9PSIsInZhbHVlIjoiSmVNRDR6Z05kUjdRM2Y4RzcrRW44UT09IiwibWFjIjoiYWY0ZDJjZTU5ZWQxYjBmYjAwOWY0ODlkOWRiMDM3MTUwNDc0MGY2OTE4NTg1MGQ5MDk0NGMyYWM5MGNmOWM5ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5402">
+      <c r="A5402" s="3" t="inlineStr">
+        <is>
+          <t>01 (11).psd</t>
+        </is>
+      </c>
+      <c r="B5402" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11316.psd</t>
+        </is>
+      </c>
+      <c r="C5402" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlMTHpDNWl1V3hIcWtwcklZQm9VQUE9PSIsInZhbHVlIjoieXBDRy9LU2FHQzlOazFaZzJxbHRlQT09IiwibWFjIjoiYzNjZGI2NDJiMzE2MGYwMmRmYTVkYTgwZWNlYmUyZjU0ZmNjOTlhNjA4ZWY4MDcxNTQ2ZWUwOGY2NjhiMGU2NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5403">
+      <c r="A5403" t="inlineStr">
+        <is>
+          <t>01 (9).psd</t>
+        </is>
+      </c>
+      <c r="B5403" t="inlineStr">
+        <is>
+          <t>tamilpsd-11319.psd</t>
+        </is>
+      </c>
+      <c r="C5403" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkY0NU1MQnNEeG5mMjJGemkra2I2bkE9PSIsInZhbHVlIjoiZ1l6OUNPZlZFcTQ5alhXUWpmaGg5UT09IiwibWFjIjoiZWE4ZTZkMDg3YjdmNjU5NTNjN2ViZTQ2NjI4ZTFjZWE5MDAzOGI0YjMzNGNlYzU3OTk1MjRlM2RlNWY3ZmFjYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5404">
+      <c r="A5404" s="3" t="inlineStr">
+        <is>
+          <t>01 (8).psd</t>
+        </is>
+      </c>
+      <c r="B5404" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11322.psd</t>
+        </is>
+      </c>
+      <c r="C5404" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IityMjRiaS9GZFdiSlFqVDQxbDFXOHc9PSIsInZhbHVlIjoiYmwwaHF0Zkl3Z3VUTW02TDlLV3Fidz09IiwibWFjIjoiMzRlNDI5NTE2ODZkZmZhZWI5ZjY5MzE3NmNiYTJhMTAyOGUwOTExMmQ5Nzk3ODU4ZjNjOWIwZGVmNzFjMGNjZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5405">
+      <c r="A5405" t="inlineStr">
+        <is>
+          <t>01 (7).psd</t>
+        </is>
+      </c>
+      <c r="B5405" t="inlineStr">
+        <is>
+          <t>tamilpsd-11325.psd</t>
+        </is>
+      </c>
+      <c r="C5405" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktWNTg0K2hwcFNkbFc0YjZHM1BZRnc9PSIsInZhbHVlIjoiamRYbjkyVEROaEtXSWRWYzFVMXlFZz09IiwibWFjIjoiMmQ1MDk4N2ViMjBhOWQ4NWMzYjQwZjZlNzdhOWRhNDc5M2IwM2UyNDNiMGI2ZDcxYmNjOTQwMGYzMjNjNmNiMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5406">
+      <c r="A5406" s="3" t="inlineStr">
+        <is>
+          <t>01 (3).psd</t>
+        </is>
+      </c>
+      <c r="B5406" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11327.psd</t>
+        </is>
+      </c>
+      <c r="C5406" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImUrR3dHa0R4OGdIV3dCSUxSenRzS2c9PSIsInZhbHVlIjoiK3B0Z0lHWnVJeG0rVVpjZzk5K0w5UT09IiwibWFjIjoiNmIyNGNkZWRiZTk4YWIzNGMzZTY1OGYyNTQzZmI1YjdkZDhjZTUxYWE5NDlkZTUxNzczYmQxMjEyYWExMTY2NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5407">
+      <c r="A5407" t="inlineStr">
+        <is>
+          <t>001.psd</t>
+        </is>
+      </c>
+      <c r="B5407" t="inlineStr">
+        <is>
+          <t>tamilpsd-11330.psd</t>
+        </is>
+      </c>
+      <c r="C5407" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNlVk1GK1dvZUZ6c1hEVEQwS2VIQWc9PSIsInZhbHVlIjoiVUtIM3lCRUo5bGZKdllDNE83cHJHUT09IiwibWFjIjoiMjIzZTJiZTlmNjM5NDUzMWY0OGFmMDQzOTgwZjg2MzJhNGI0MjY4YWJiOTM0MDg0NGFjOTVhMWMwMmY1NmI2NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5408">
+      <c r="A5408" s="3" t="inlineStr">
+        <is>
+          <t>01 (2).psd</t>
+        </is>
+      </c>
+      <c r="B5408" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11334.psd</t>
+        </is>
+      </c>
+      <c r="C5408" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkdiTkJ1cm5aVTlNTERXclFNQkZjU3c9PSIsInZhbHVlIjoiRjVGa1Y1RXltMHpjWC9LcnYxdm01Zz09IiwibWFjIjoiODYxZTQzZTVlY2YwY2NlYjhhYTQwY2U4YWRlMmE0MGFiMTBiZDk3NDkyYjBmOGY4ZWY5ZDc3YzU3ZjBmNjQwMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5409">
+      <c r="A5409" t="inlineStr">
+        <is>
+          <t>1300.psd</t>
+        </is>
+      </c>
+      <c r="B5409" t="inlineStr">
+        <is>
+          <t>tamilpsd-11337.psd</t>
+        </is>
+      </c>
+      <c r="C5409" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktjeWcxVHhSUUZaN2RDcHFqQzQ1K2c9PSIsInZhbHVlIjoiQ2VCYmpuQTI0cUprYnlzOXE2bjlSQT09IiwibWFjIjoiZjAyYmNlMTJlNTlkNjlhMTZiZjZlZTg1ZTdlYWRhZDAzY2M0MjVlNGFhNWQwNjE5MDI1YTUwN2ZmNTU1Nzg5MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5410">
+      <c r="A5410" s="3" t="inlineStr">
+        <is>
+          <t>1299.psd</t>
+        </is>
+      </c>
+      <c r="B5410" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11338.psd</t>
+        </is>
+      </c>
+      <c r="C5410" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlYzL2dnNFN3dEt6QUczcmZlMGRMK2c9PSIsInZhbHVlIjoidEJLdllsUkZmRy9nMFZFSk9WaS8zdz09IiwibWFjIjoiYjA4YzRiM2NjMWZlYzk1MjkzODBmMzg3ODY1MDliNDgxYjMwYzcxNmViMzQzYTE5OTJjNzU0ZGViN2U0YmYwZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5411">
+      <c r="A5411" t="inlineStr">
+        <is>
+          <t>1298.psd</t>
+        </is>
+      </c>
+      <c r="B5411" t="inlineStr">
+        <is>
+          <t>tamilpsd-11339.psd</t>
+        </is>
+      </c>
+      <c r="C5411" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNnaTJaWFArU2cxQkpkK2NySzN4YkE9PSIsInZhbHVlIjoiMWYvMHpuT1dJa2R2SUd2dGFCZmNIZz09IiwibWFjIjoiYmMxMDdlM2I1OTJjYjgzZDlkMzg1YzU2MzY1MDY4ODM4YzgxZTFmYzM3YmI0YjQ0ZjI0NWQ5ZjI5Y2JiZDZmMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5412">
+      <c r="A5412" s="3" t="inlineStr">
+        <is>
+          <t>1297.psd</t>
+        </is>
+      </c>
+      <c r="B5412" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11340.psd</t>
+        </is>
+      </c>
+      <c r="C5412" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZvb1l2OXEwK2Z6RWxJVHVuUG8vWEE9PSIsInZhbHVlIjoiUnRQeDlxalpsY1V5VjNCZStMbUdTQT09IiwibWFjIjoiNDYzOWZjMjkyN2MzMzc2Njk2YWEyNTVlYTNkMzY4OTgxZTI0ZTYxODlkNDcwYTNiMzRlN2QwYzMwNzQ2NjE1OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5413">
+      <c r="A5413" t="inlineStr">
+        <is>
+          <t>1296.psd</t>
+        </is>
+      </c>
+      <c r="B5413" t="inlineStr">
+        <is>
+          <t>tamilpsd-11341.psd</t>
+        </is>
+      </c>
+      <c r="C5413" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFFTGlUUVZiTGcvMlJpQm9vL2ZacGc9PSIsInZhbHVlIjoibFBPdjR0VjRwUXNsWVVUdFVvb0tlQT09IiwibWFjIjoiYjVlODNmNDc0YjMzNGJiM2VjMDJhZTY1ODMyNGExZGQxMjg3MTVmZjI0M2UxMWJjMjJiMjVkZjM2ZTYyNTEwMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5414">
+      <c r="A5414" s="3" t="inlineStr">
+        <is>
+          <t>1295.psd</t>
+        </is>
+      </c>
+      <c r="B5414" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11342.psd</t>
+        </is>
+      </c>
+      <c r="C5414" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InJxQnpXTEdpcldzL2UyaGZ5Z2oraGc9PSIsInZhbHVlIjoiVXZ1RkNta3hPbSt4WDF6NzgvbGNaZz09IiwibWFjIjoiNTBmZDY4ZWI1NzZkZGQ5ZDIyYzRkY2Q3MTlkNDYxNmVhMzE0MzkwMmU5MTI5ZmRhMTQyNDI3ZDYyMWMyZDM2ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5415">
+      <c r="A5415" t="inlineStr">
+        <is>
+          <t>1294.psd</t>
+        </is>
+      </c>
+      <c r="B5415" t="inlineStr">
+        <is>
+          <t>tamilpsd-11343.psd</t>
+        </is>
+      </c>
+      <c r="C5415" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjU5NzhmYzVEbGpVOHR2SFZvRnJXd1E9PSIsInZhbHVlIjoiMExUMzVieWh2UnRoRFkyNkpTbkZSZz09IiwibWFjIjoiYzA5ODBjZjZmMmNmOGFiYTJkYzk5NTRmNTllYTUyYzE4NjdiNmY5OTI5ZjU2MDNiZGM0ODc1MDA5YjllYjVmMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5416">
+      <c r="A5416" s="3" t="inlineStr">
+        <is>
+          <t>1293.psd</t>
+        </is>
+      </c>
+      <c r="B5416" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11344.psd</t>
+        </is>
+      </c>
+      <c r="C5416" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZHQlJEZ05jMjVBdlg3d0JKai8yVVE9PSIsInZhbHVlIjoiS3ZBZnAwOXFETlAwUmRRVGZpTFVmQT09IiwibWFjIjoiZDg4NmM3ZGVjNmM3NGJjODViOWM2MjlmZTJiMjQwNzZmMjg3NjdmODRkZjczNGYzMDIwNmU4MDg4ODgwM2YzZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5417">
+      <c r="A5417" t="inlineStr">
+        <is>
+          <t>1292.psd</t>
+        </is>
+      </c>
+      <c r="B5417" t="inlineStr">
+        <is>
+          <t>tamilpsd-11345.psd</t>
+        </is>
+      </c>
+      <c r="C5417" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVrNW1lclh6b2p4YW9pdDZLcE4vcXc9PSIsInZhbHVlIjoiRE00elNKU1cwUUIrOHd1ZWpPbUNEZz09IiwibWFjIjoiMGQ2ZTQ4MDM4MjAxZWU4MWYyYmVmMzgyN2M0ZDE5OWI0M2RjMjdjMThjNTU2Mjg0MDhhOTk4MTQ3ZDY2M2JlYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5418">
+      <c r="A5418" s="3" t="inlineStr">
+        <is>
+          <t>1291.psd</t>
+        </is>
+      </c>
+      <c r="B5418" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11346.psd</t>
+        </is>
+      </c>
+      <c r="C5418" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNJckF5TzVZY3l6VkdqZkJQVllSQ2c9PSIsInZhbHVlIjoiVTd4VVZjV2NCckJ3WVB3REF1SVV2UT09IiwibWFjIjoiNzllMDM0Njg4ZjE4NzNlOWViYzBmYzFjNDZlNDdmMDNhMDAyOGNlZjEzMzU1OGI0NWRiMjAwM2NkMGViZmExZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5419">
+      <c r="A5419" t="inlineStr">
+        <is>
+          <t>1290.psd</t>
+        </is>
+      </c>
+      <c r="B5419" t="inlineStr">
+        <is>
+          <t>tamilpsd-11347.psd</t>
+        </is>
+      </c>
+      <c r="C5419" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9iTTFwcHU0RXRIbXd3WXhrT29TM2c9PSIsInZhbHVlIjoiZVQ5dVFycSs2dU9EYkkrWFNvSjl5QT09IiwibWFjIjoiNDkzYmY5MjVlNTE5OGRjMWUxMTFjODI1N2I2ZGViMDYwNjkyODU4YmU3MThhNjVlNTExMjc5ZjdmNjM3ZTk0MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5420">
+      <c r="A5420" s="3" t="inlineStr">
+        <is>
+          <t>1289.psd</t>
+        </is>
+      </c>
+      <c r="B5420" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11348.psd</t>
+        </is>
+      </c>
+      <c r="C5420" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhnQmFyZDBqOFlSWTZ1Zno3RXkrWmc9PSIsInZhbHVlIjoiT3VaRXJBb2NzcmV3cjZkZFNBL2ZKdz09IiwibWFjIjoiZWI3ZTRhMTU0ZDIwNGRlNTM3OThmMjk2YjYyZTRmNTRiMWJjNDJiMjFjNTc2Y2Q2MzJmNGNmMDI4NmY1MDAwMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5421">
+      <c r="A5421" t="inlineStr">
+        <is>
+          <t>1288.psd</t>
+        </is>
+      </c>
+      <c r="B5421" t="inlineStr">
+        <is>
+          <t>tamilpsd-11349.psd</t>
+        </is>
+      </c>
+      <c r="C5421" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InJLbVRjTk04ZHo1N0lBR3BnV0J6MGc9PSIsInZhbHVlIjoiTVZUMHhqRmFybzdjMmY4WENra05Idz09IiwibWFjIjoiNGE3ZjU0YTBjYTA3ZTQxMDhkYzVmNWJlNGIxOGE5ZTQ5NmNmMzIwMjIxZjBhM2MxMGE2NjFkMjVhMTlkMjM2MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5422">
+      <c r="A5422" s="3" t="inlineStr">
+        <is>
+          <t>1287.psd</t>
+        </is>
+      </c>
+      <c r="B5422" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11350.psd</t>
+        </is>
+      </c>
+      <c r="C5422" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhOdFErdCs2WFFDb1NaMmlDdy9jcXc9PSIsInZhbHVlIjoibHpRNmx0Y3BtRldPaUJ5ck53ZjNEQT09IiwibWFjIjoiODQ3ZDUwZjk0YTg2Y2Y1YWY0NzhlMjUxNzVlMGExOWUyNGM5NDQ3YTBmYWUxNjdlMzYzMzlhMjc2ZDgzZTc4OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5423">
+      <c r="A5423" t="inlineStr">
+        <is>
+          <t>1286.psd</t>
+        </is>
+      </c>
+      <c r="B5423" t="inlineStr">
+        <is>
+          <t>tamilpsd-11351.psd</t>
+        </is>
+      </c>
+      <c r="C5423" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikg3K254TzUwcnhsRktMOUFZNWNEWnc9PSIsInZhbHVlIjoidUtsMVRJN0hJbVI0dmdaYkJUaVcxQT09IiwibWFjIjoiMWJhMGY3M2M4NWU1YzA4NjFmOGJiNTcwNzljY2JiYTJiNTFlZDEwYmU2NmFhZjkzODBkYjM2ZDk4YzZmYjQ1OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5424">
+      <c r="A5424" s="3" t="inlineStr">
+        <is>
+          <t>1285.psd</t>
+        </is>
+      </c>
+      <c r="B5424" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11352.psd</t>
+        </is>
+      </c>
+      <c r="C5424" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpqWU1lOEQ3UjNEQWgwWU1WWjFFZ1E9PSIsInZhbHVlIjoiQTNJejVQdHNlQ1Arc3NRNmFCUmdxZz09IiwibWFjIjoiODAxM2U1NTc1NWQxMzEwMjViNjMxMjVmMTEzMDU5YjczNWQ5ZTY0ZGIwNzkzN2JmZGZlZWNmNzY5YjJlNjFjYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5425">
+      <c r="A5425" t="inlineStr">
+        <is>
+          <t>1284.psd</t>
+        </is>
+      </c>
+      <c r="B5425" t="inlineStr">
+        <is>
+          <t>tamilpsd-11353.psd</t>
+        </is>
+      </c>
+      <c r="C5425" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFsOEozR1F6cHFrUkhBRitiWkpXOGc9PSIsInZhbHVlIjoicTV1NzBOc3JaeHZuSEgvMkNzcTNhUT09IiwibWFjIjoiMTcwMDQ0MzY1NWMyMDc4ZTg0MjBkMmI0MzM4MGZlNTgzZDU0MjQxNjM3ZTc2MWRmYWQyN2IwNWU5NjdiYWE3NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5426">
+      <c r="A5426" s="3" t="inlineStr">
+        <is>
+          <t>1283.psd</t>
+        </is>
+      </c>
+      <c r="B5426" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11354.psd</t>
+        </is>
+      </c>
+      <c r="C5426" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZjNCtJUmdrWUhLQUp4bS8vc0JLT1E9PSIsInZhbHVlIjoiUlZFZzczVHNpcFJiYjNjZlkrVk5LQT09IiwibWFjIjoiYmIxNTJhNzIyODAzNDcyNDlhOGQ2NTM1N2M2MjIzNjc4ZTFiODg0ZmI0ZmI2M2Y3Zjg1YTZjYTA1YjI5NDAxYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5427">
+      <c r="A5427" t="inlineStr">
+        <is>
+          <t>1282.psd</t>
+        </is>
+      </c>
+      <c r="B5427" t="inlineStr">
+        <is>
+          <t>tamilpsd-11355.psd</t>
+        </is>
+      </c>
+      <c r="C5427" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ind6cXArNU9EMFFiY2NLazNNVG1iY2c9PSIsInZhbHVlIjoid0gvQ1A2TTladDV0cllWb1dTcFdvZz09IiwibWFjIjoiMjM0YmVjMDU5NDE5NTU1MzM0MTJmYTRkMTY5Y2YyMmVhMjM5MDk3N2JmNjZkM2MzNzZjMWI0ZjczOGE2NjY5OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5428">
+      <c r="A5428" s="3" t="inlineStr">
+        <is>
+          <t>1281.psd</t>
+        </is>
+      </c>
+      <c r="B5428" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11356.psd</t>
+        </is>
+      </c>
+      <c r="C5428" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkpvcnlZcDNKVHBMaTBuSmJmci90SEE9PSIsInZhbHVlIjoidVVDVjlTRFRnMWJYdzEvNFdjRWNTdz09IiwibWFjIjoiZjg2NDlkOTQxODE2NTkxMjZkZjQ0OWZiNmYzYjNkNzcxYTJmYWNhMWEwNDMwMDI3ZjExMzIyNDMxYTc4NDdkZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5429">
+      <c r="A5429" t="inlineStr">
+        <is>
+          <t>1280.psd</t>
+        </is>
+      </c>
+      <c r="B5429" t="inlineStr">
+        <is>
+          <t>tamilpsd-11357.psd</t>
+        </is>
+      </c>
+      <c r="C5429" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJxQW5ZZU45Z0lGMEVJWEZKL1JsZ3c9PSIsInZhbHVlIjoiTjd4VStVUXdtY2JUN1ZaS2djMDg2Zz09IiwibWFjIjoiNDE3NDYzMzY4NzcyMGRjYjA1NGRhMDE1MTNmZjEzZDgwMDdhNWU5ZGNhMjJjNDNjMWYwNWZkZGJkNGVmOGNlZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5430">
+      <c r="A5430" s="3" t="inlineStr">
+        <is>
+          <t>1279.psd</t>
+        </is>
+      </c>
+      <c r="B5430" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11358.psd</t>
+        </is>
+      </c>
+      <c r="C5430" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9IWU56WXNOL3I5VkNsb2M4dDJNN2c9PSIsInZhbHVlIjoiSzRURkt4LzdadEVzNTdPcUQybEZFdz09IiwibWFjIjoiYWFkNzNmYmFkOGJmNDMzZDExYjk5ODE0NWMxNjRhNjRlNWYyNjBmZjA3NzYwMDk5MGViYzcxYTJlNzY3NGQ1MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5431">
+      <c r="A5431" t="inlineStr">
+        <is>
+          <t>1278.psd</t>
+        </is>
+      </c>
+      <c r="B5431" t="inlineStr">
+        <is>
+          <t>tamilpsd-11359.psd</t>
+        </is>
+      </c>
+      <c r="C5431" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InMybXJZN2FTMkUvRHBZZ3F1T2NwRkE9PSIsInZhbHVlIjoicTJMQnNOSEJLRXR1Y3Z5bTIwbjZVdz09IiwibWFjIjoiMjgxNjJjMDNiNzNmODlkZGU5OGUwMjVlZjNkY2NmNmQxNDhmMDFiODBiNDBlYzBhM2Y3YmY5N2ExMDBiNTFiNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5432">
+      <c r="A5432" s="3" t="inlineStr">
+        <is>
+          <t>1277.psd</t>
+        </is>
+      </c>
+      <c r="B5432" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11360.psd</t>
+        </is>
+      </c>
+      <c r="C5432" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5RSmYwOGhvbnRSREVIeGFKODBMaHc9PSIsInZhbHVlIjoiZU5xa3Nzd3BuWGJvZlVxVkNlTWUvZz09IiwibWFjIjoiNmY3ZDNkMDdkZjBiZGZjM2FjM2IyNmMzMTgzYzIxYWVjY2RhNTEyMTk4MmE2MjA1MzE0NzgwYWJiZTI1YTMwMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5433">
+      <c r="A5433" t="inlineStr">
+        <is>
+          <t>1301.psd</t>
+        </is>
+      </c>
+      <c r="B5433" t="inlineStr">
+        <is>
+          <t>tamilpsd-11361.psd</t>
+        </is>
+      </c>
+      <c r="C5433" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlcvWUdhMHdlMFUyS1JOVmd3ME44L2c9PSIsInZhbHVlIjoiTzQ4S0pQVkhENkF4U1ZOUFVnUTBWUT09IiwibWFjIjoiOGM4NmY0ODlkMDk2NzRjOTc2ZTExNDZiMjc2MDk1YjQzOThkMGIxMmUzNzk2ZTZiNjU1ZmQwNTA0NmRkMTdlYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5434">
+      <c r="A5434" s="3" t="inlineStr">
+        <is>
+          <t>good - 1_098.psd</t>
+        </is>
+      </c>
+      <c r="B5434" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11362.psd</t>
+        </is>
+      </c>
+      <c r="C5434" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijgram9RR3hIemhnWU5sNE9xWGo4Ymc9PSIsInZhbHVlIjoiOFNkM2taMVpqMldWS05YN2xCYkVTdz09IiwibWFjIjoiZjRjMzA0YjY5YjM1OWIyYjI4YTc4YjU0NmU3ZWJiZTg2OWE0MDM2OGY5Y2ExOWVhOTlmYWNiNDUxNDcwZDg3NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5435">
+      <c r="A5435" t="inlineStr">
+        <is>
+          <t>good - 1_093.psd</t>
+        </is>
+      </c>
+      <c r="B5435" t="inlineStr">
+        <is>
+          <t>tamilpsd-11365.psd</t>
+        </is>
+      </c>
+      <c r="C5435" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZlSFY0NHI0a1M1N1JBUW5OdXJYTGc9PSIsInZhbHVlIjoiRkRmdEFsc3NvK3ZEYXhHU0VsakdpUT09IiwibWFjIjoiYzVmNDA2ZjYyMGIwMmRjYWRjYTQ2ZDZlODNmN2YzNjBmNGZmYTk2NDNkZTM1ZjNkZjZlMTI2ZjZkZTZkOWEzYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5436">
+      <c r="A5436" s="3" t="inlineStr">
+        <is>
+          <t>good - 1_083.psd</t>
+        </is>
+      </c>
+      <c r="B5436" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11368.psd</t>
+        </is>
+      </c>
+      <c r="C5436" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRmUnlDdmJIMkhQdWltTVdhMmN0YVE9PSIsInZhbHVlIjoiSWNpc2VXNVRXOThtTitPa2NkcHp1dz09IiwibWFjIjoiNTllYTIxODc5ZGU3OTNkZmQ1N2ZlN2MwYmQwYTY1ZjAxOTk0OWQ0ZjFiYmU5NDU5ZDg4NGU2NjEzMDNlMTQzZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5437">
+      <c r="A5437" t="inlineStr">
+        <is>
+          <t>good - 1_081.psd</t>
+        </is>
+      </c>
+      <c r="B5437" t="inlineStr">
+        <is>
+          <t>tamilpsd-11370.psd</t>
+        </is>
+      </c>
+      <c r="C5437" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhHTHlPcTZCUlR6ZUxJOVo2TFJ2Wmc9PSIsInZhbHVlIjoiMTE3eFpIeVhlODlxWFBtUTNJRGlBZz09IiwibWFjIjoiYzAwMDE1MGE1NjU5NDdjMzIwMzFlNmI3ZjIzNTlkYjRkYTRmZTg0ZjBlMWQ4MDk2NWI4NDYyZTYyMjNhMDBjMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5438">
+      <c r="A5438" s="3" t="inlineStr">
+        <is>
+          <t>good - 1_079.psd</t>
+        </is>
+      </c>
+      <c r="B5438" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11372.psd</t>
+        </is>
+      </c>
+      <c r="C5438" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1uUFIzQ2dhWVRZR1d5Tlc2U09Eanc9PSIsInZhbHVlIjoiYXFyUXU2WTFiZXllVGh6NkFIbGtldz09IiwibWFjIjoiYjY0NGJkMDQ2MDNjNjE4ZmEzY2IwZWRkZDg5ZGZlYzcwOWQ4OTM0NzM0MDQ3YWRhYmNlZTcwNTJhZDliZmVkZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5439">
+      <c r="A5439" t="inlineStr">
+        <is>
+          <t>good - 1_077.psd</t>
+        </is>
+      </c>
+      <c r="B5439" t="inlineStr">
+        <is>
+          <t>tamilpsd-11374.psd</t>
+        </is>
+      </c>
+      <c r="C5439" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZsNjZVM0t6YXJCY0FqVFhWd0R3cFE9PSIsInZhbHVlIjoiYlJaVHNwQklKNW0wUlJzN3RBcnpxdz09IiwibWFjIjoiZWJhMzc0YTk4NzZhZjcxZGNkMGUwMTU0ZjAxOWViNjYxMzkyMTBlNzRkYzFlMDQwMTlmZmI0ZmZhYzA2NjRmZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5440">
+      <c r="A5440" s="3" t="inlineStr">
+        <is>
+          <t>good - 1_051.psd</t>
+        </is>
+      </c>
+      <c r="B5440" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11376.psd</t>
+        </is>
+      </c>
+      <c r="C5440" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklyNmp4bUhsQWxUV0dRclI4YkljV3c9PSIsInZhbHVlIjoiRlVWWGF5V0QxbkVUT21VU01ycVJmZz09IiwibWFjIjoiYjJkM2YwOTA2Y2FkZTY1MjdjMjVhMzdlZDAxZGI3Nzg2ZWFmYTU1NTlkNjk3ODE2MDQwMmYwMDMyNThlMjMzZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5441">
+      <c r="A5441" t="inlineStr">
+        <is>
+          <t>good - 1_047.psd</t>
+        </is>
+      </c>
+      <c r="B5441" t="inlineStr">
+        <is>
+          <t>tamilpsd-11378.psd</t>
+        </is>
+      </c>
+      <c r="C5441" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNsb0Z2SDdIbFVldjFqc0dQRk9WS0E9PSIsInZhbHVlIjoiaEwxL1lhcjFCRnZ6MHJ4SlpvVXIxQT09IiwibWFjIjoiM2JlMzMzYmNiYTI1ODQ4YTkyNWRjMzU5YjQ1Zjg3MTNjMDVlMzY4NmY2ZDg3NmZjYzNmNGQ4Nzg1MGQxZjI3ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5442">
+      <c r="A5442" s="3" t="inlineStr">
+        <is>
+          <t>good - 1_034.psd</t>
+        </is>
+      </c>
+      <c r="B5442" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11380.psd</t>
+        </is>
+      </c>
+      <c r="C5442" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNuVGllYVZRSkpSV1hGcEtXMFl4OUE9PSIsInZhbHVlIjoibkNCV1p0bDhpbndPRHZIYmdBNG8yUT09IiwibWFjIjoiM2I5YTM1YWUzOTg0MDFkYmFjNzE0OWIwMmU1NTI3ZGI4NDdiY2IyOTI2MDBkZDAxNDUyZmI4Njc3NzcwMjJlNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5443">
+      <c r="A5443" t="inlineStr">
+        <is>
+          <t>good - 1_033.psd</t>
+        </is>
+      </c>
+      <c r="B5443" t="inlineStr">
+        <is>
+          <t>tamilpsd-11382.psd</t>
+        </is>
+      </c>
+      <c r="C5443" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5LZjEvR0NVUktibjZVQXh4d2RtOEE9PSIsInZhbHVlIjoiMWVYdVlIOERBUUs3QmI5UlRFUDB3UT09IiwibWFjIjoiYWQwNjgzODQzNmJiMjM2OTZiYzIwZTAzMDQxNDU5MDIwNjZlNjk4M2JmM2U4OTIzOTY0NmNkMzZlZjBlYWUyOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5444">
+      <c r="A5444" s="3" t="inlineStr">
+        <is>
+          <t>good - 1_032.psd</t>
+        </is>
+      </c>
+      <c r="B5444" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11384.psd</t>
+        </is>
+      </c>
+      <c r="C5444" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpYTTBqbnNmZXUrZzBJcWRtZUxYb0E9PSIsInZhbHVlIjoiL1ZEaFQ2QWVqZDN6VnZrR0FEQmhFZz09IiwibWFjIjoiMjdlNjZjNmZjZWU2MGM1ZTEzYTYxZTgwMzcxNjNkMGJkY2Q3NWM5ZTBhMWE2N2ZiNzI4NTA5YzNiMDllMmI1ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5445">
+      <c r="A5445" t="inlineStr">
+        <is>
+          <t>good - 1_028.psd</t>
+        </is>
+      </c>
+      <c r="B5445" t="inlineStr">
+        <is>
+          <t>tamilpsd-11387.psd</t>
+        </is>
+      </c>
+      <c r="C5445" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkkwWWJtVW5BRjlZUHY3cHNBeCtGa1E9PSIsInZhbHVlIjoiYjJWUE5XVDBLYmtWeTVVZlczZ3BrQT09IiwibWFjIjoiYzVjZmZiMWIyOTdkNzNjM2JlNTI1Nzk5YTEyZGEwMWU5YWYwMGQyZDY4ZjQ3ZDU4ZGIwM2JhMDMyYmNjMWQ3YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5446">
+      <c r="A5446" s="3" t="inlineStr">
+        <is>
+          <t>1a.psd</t>
+        </is>
+      </c>
+      <c r="B5446" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11391.psd</t>
+        </is>
+      </c>
+      <c r="C5446" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhXOFBOcFJzRGwweGRNMEF2YmRQd1E9PSIsInZhbHVlIjoiaWRWYUlnOTE4QmFIUWdaMk5UWVhNZz09IiwibWFjIjoiYjBmZWI1NDAyMDRhNDFlOTFmNjFjZjZkYzE2ZjNlYTkxNzNjNzZmZTE1NTE0OTQ3OWFlNzQ5ZGNlYzliNTYwOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5447">
+      <c r="A5447" t="inlineStr">
+        <is>
+          <t>good - 1_115.psd</t>
+        </is>
+      </c>
+      <c r="B5447" t="inlineStr">
+        <is>
+          <t>tamilpsd-11392.psd</t>
+        </is>
+      </c>
+      <c r="C5447" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklOcmE2aUVvRXRNSzRjU3JnTWd6Mmc9PSIsInZhbHVlIjoiaVo2SFBXRk5lTlhIN1A0dEVEVnBKUT09IiwibWFjIjoiZDE1MGE3YzkzMGIyZDUxNTkyODhkZmFiOTU4OTMwOGM3MDgwYWFmYzk1N2M3NmZhYjY2MmY3N2JhYjc0N2RhMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5448">
+      <c r="A5448" s="3" t="inlineStr">
+        <is>
+          <t>1164.psd</t>
+        </is>
+      </c>
+      <c r="B5448" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11395.psd</t>
+        </is>
+      </c>
+      <c r="C5448" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVFZXRHUzFUYnFpS0c2RWxnbjZuSnc9PSIsInZhbHVlIjoiTzVJT25aVjd4TXQrczhMdlNmZ25LQT09IiwibWFjIjoiZjU4MmFlMmFiZDQ4OWYxODE0Y2VkODE0NGFjZDY3N2ViNzllMDM5YTdmMWIxYjU2Njg2NjE5N2ZmMzczOWNkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5449">
+      <c r="A5449" t="inlineStr">
+        <is>
+          <t>1163.psd</t>
+        </is>
+      </c>
+      <c r="B5449" t="inlineStr">
+        <is>
+          <t>tamilpsd-11396.psd</t>
+        </is>
+      </c>
+      <c r="C5449" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNWd1JVdlM0MzI0TFc1MFVIMUl0cGc9PSIsInZhbHVlIjoiYWlZNElVOW8vZ3FZNHhtQk5md2FNUT09IiwibWFjIjoiNjMzMWQ0ZDQ4MGJmMmNhZDA2YWUyMjg2MzFjZTBlYTlmMjlhMjU0ZGQ4YWU0ZTZiOGZlYzg5MTIxYmUwOGUzMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5450">
+      <c r="A5450" s="3" t="inlineStr">
+        <is>
+          <t>1162.psd</t>
+        </is>
+      </c>
+      <c r="B5450" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11397.psd</t>
+        </is>
+      </c>
+      <c r="C5450" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InU5eG5zSmVudXYyQkFuUWJRUmJ0eVE9PSIsInZhbHVlIjoiUnJZRWFCSW1mTFgxY0VTd1F3NFJHQT09IiwibWFjIjoiMmE0ZGU0ZTQ3NWU1ZDE3MjYwMTZhNjIxZGViMTBjNGQxZjk1MjIyNzM4ZGNmNGMwY2M5MzJiM2NlZDQ3MmI0YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5451">
+      <c r="A5451" t="inlineStr">
+        <is>
+          <t>1161.psd</t>
+        </is>
+      </c>
+      <c r="B5451" t="inlineStr">
+        <is>
+          <t>tamilpsd-11398.psd</t>
+        </is>
+      </c>
+      <c r="C5451" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVkVDZYajdRVENNUitGaFNTQXNvWFE9PSIsInZhbHVlIjoiRHBGWjdBZkM3NHFKdHNiakFyb1k2Zz09IiwibWFjIjoiNjQwZjQ4MmY2M2YyYWJmY2ZjNDM1MTQzYzQyYTA4MWRiMDQ1NjZiMGExYjBkYzBiZjkwYWRmZGE2N2JkZTc4YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5452">
+      <c r="A5452" s="3" t="inlineStr">
+        <is>
+          <t>1259.psd</t>
+        </is>
+      </c>
+      <c r="B5452" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11399.psd</t>
+        </is>
+      </c>
+      <c r="C5452" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJMTVpWMnVhRkljRWVxR01qRWE2Vmc9PSIsInZhbHVlIjoiZCtrL3loaEluQ0ZRY1NkZ0Myc0xwdz09IiwibWFjIjoiNGU0NjcwMTJlMTRmOGY1NTMxNTRhZjA3YmIzNTM2MGQ1MjcxNjBhZDdiZThlZWRjMGE3M2I1MWM5ZWI0NWRmMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5453">
+      <c r="A5453" t="inlineStr">
+        <is>
+          <t>1258.psd</t>
+        </is>
+      </c>
+      <c r="B5453" t="inlineStr">
+        <is>
+          <t>tamilpsd-11400.psd</t>
+        </is>
+      </c>
+      <c r="C5453" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iko3NTVKWndMVEJ4UEg2YW4rblRWZkE9PSIsInZhbHVlIjoiSFVTeTV3UHRReENJR2RvN1VEVnRzQT09IiwibWFjIjoiMThmZTFjYmI2NDBmYzZmNjI3ZmZlZWViNzdkMGZhMDZlOGM3MWJkMTZjZGMzMWQ1MmQ0ODQ0NjA1ZmFiNzM2NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5454">
+      <c r="A5454" s="3" t="inlineStr">
+        <is>
+          <t>1159.psd</t>
+        </is>
+      </c>
+      <c r="B5454" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11401.psd</t>
+        </is>
+      </c>
+      <c r="C5454" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhEenp5cE4rT3RLUXVUVTNvejlJNmc9PSIsInZhbHVlIjoiM1FUVkpqKzhDYTN2VVN5OEt0OUR5Zz09IiwibWFjIjoiZGNmMWEzZmRjYjYxMDg0YmI1NGYzYzY3ZDBmMGIxNDY0NTgxNTlkM2M1YmIzYzg4MzBjMDk2NDQ0YjAzMDQ2YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5455">
+      <c r="A5455" t="inlineStr">
+        <is>
+          <t>1257.psd</t>
+        </is>
+      </c>
+      <c r="B5455" t="inlineStr">
+        <is>
+          <t>tamilpsd-11402.psd</t>
+        </is>
+      </c>
+      <c r="C5455" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1uRUxnQmQ5NWlBTkRxeFNja0tsYXc9PSIsInZhbHVlIjoiVkViUDJOdXhZN1h1eTIzUTFMdG5jQT09IiwibWFjIjoiYWZhN2U1MWEwNzJhOTE0YzlkYzFhMWQzNGY1YjE0ODhiMzUyNDNkYmYwOGJkOTcwNzMzMzhkYTM1NDIzYzM5MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5456">
+      <c r="A5456" s="3" t="inlineStr">
+        <is>
+          <t>1256.psd</t>
+        </is>
+      </c>
+      <c r="B5456" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11403.psd</t>
+        </is>
+      </c>
+      <c r="C5456" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik9FSlBkeC84eTFXaG84QjlBVDd1cGc9PSIsInZhbHVlIjoiMXJpTlJaQ2RoRmw5ZDl3NCtvMElpQT09IiwibWFjIjoiNzRkYjVmMjY4YTNmMGYxZDBmN2ZjY2IxY2VmNzNhOTdhMWJjNTliOTc1ZmIwMTI0Y2I0NDk5OGRjZDI1NDBkNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5457">
+      <c r="A5457" t="inlineStr">
+        <is>
+          <t>1157.psd</t>
+        </is>
+      </c>
+      <c r="B5457" t="inlineStr">
+        <is>
+          <t>tamilpsd-11404.psd</t>
+        </is>
+      </c>
+      <c r="C5457" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9mOGhXN2lQN0xkSEVDTGJUc2txQWc9PSIsInZhbHVlIjoiMHExRFA1SWd2SlZjeGZrN3crYUxZZz09IiwibWFjIjoiYmQyMTI5NGY0YjA0MmMxNjgxZmVkZDA1MDQ5ZTE1NGNhNzRhZTViOTlhYjg4ZDgwMDNkNmI0YjRhMDc3NTY1MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5458">
+      <c r="A5458" s="3" t="inlineStr">
+        <is>
+          <t>1255.psd</t>
+        </is>
+      </c>
+      <c r="B5458" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11405.psd</t>
+        </is>
+      </c>
+      <c r="C5458" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjZPVjVxOE5kMU9lVzExUlFENzJaNkE9PSIsInZhbHVlIjoiUG9leThNYitzUjlaaFlDRGJzTGgydz09IiwibWFjIjoiNWI0NmYxOTZiZjg0NzgyNzFhOWFlM2VmMWMwZGY1NzVlZTUwNTJiYjk0MzEyOTYzN2VhNjU5ZWFkNDIxZWQ4ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5459">
+      <c r="A5459" t="inlineStr">
+        <is>
+          <t>1254.psd</t>
+        </is>
+      </c>
+      <c r="B5459" t="inlineStr">
+        <is>
+          <t>tamilpsd-11406.psd</t>
+        </is>
+      </c>
+      <c r="C5459" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImgwWHVNZWlRRktlQ0NMdlRUcXNha2c9PSIsInZhbHVlIjoiTGNhampqbnAzeXJBVURRankrTThwUT09IiwibWFjIjoiMTdlYTc0NzUyYzlkNjEzYzgwOGYxY2E4NThkY2ZhNGE1Y2MyYTk4YjJhMzNkMzk3YzEzNjQ1MDBkZWZiOThhNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5460">
+      <c r="A5460" s="3" t="inlineStr">
+        <is>
+          <t>1253.psd</t>
+        </is>
+      </c>
+      <c r="B5460" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11407.psd</t>
+        </is>
+      </c>
+      <c r="C5460" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRhMjZta0ZUVjBlZ2Zta2RaRDExRVE9PSIsInZhbHVlIjoiWHA2TDlKM0phTVl4eXdxdWd3S2xpdz09IiwibWFjIjoiYjkwYmI0MTZmOWJjZDExNmNlMzc0MWQ3ZjM4NGNlMWJlMmY3ZDg1ZjJmZDUwZTYwNTIyNmFjY2Q4N2QzZmNkZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5461">
+      <c r="A5461" t="inlineStr">
+        <is>
+          <t>1156.psd</t>
+        </is>
+      </c>
+      <c r="B5461" t="inlineStr">
+        <is>
+          <t>tamilpsd-11408.psd</t>
+        </is>
+      </c>
+      <c r="C5461" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlI1Zy9LZ2lVVllXK3Q2cWFUZDFzNmc9PSIsInZhbHVlIjoiazRpTGlqU1hORzUvdGVWWUJoUFd1QT09IiwibWFjIjoiODQ1ZTQ4MjNjMTBlOWUyNjg5OTdhNTMwZjg3ZGIyMjNiZjQxNDJiMTVmNTIzNzg0OWQ3MzQ2OTVlZmM5MWQ3MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5462">
+      <c r="A5462" s="3" t="inlineStr">
+        <is>
+          <t>1252.psd</t>
+        </is>
+      </c>
+      <c r="B5462" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11409.psd</t>
+        </is>
+      </c>
+      <c r="C5462" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikp0aXRpYmUwNE9IdUlxQkt0SkNrTlE9PSIsInZhbHVlIjoiWFdwOEc3WlU0WmR2YjNucC9rVUZUUT09IiwibWFjIjoiMzQ0MDhiOWRkNzZlYzBiZGU3ODgwYTcyMDM0MTgzNjFjYWNiYWQyYzA2MTBlYzI3NDlkOGUwMWFhODhkNmFmNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5463">
+      <c r="A5463" t="inlineStr">
+        <is>
+          <t>1251.psd</t>
+        </is>
+      </c>
+      <c r="B5463" t="inlineStr">
+        <is>
+          <t>tamilpsd-11410.psd</t>
+        </is>
+      </c>
+      <c r="C5463" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJ3dXJycitzY24wbXlpM1kxOHliNmc9PSIsInZhbHVlIjoiS1ZvQjJ6ekcvWEdzbmNlai9aelBJZz09IiwibWFjIjoiOGI2Yjc0ODgzMjkxZDgxYWRkM2QxNjg1NGNiNTAwY2I5ODhjMDMyMjFmODg3YTc1NjJmY2IzYWE0ZGIzNjA3YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5464">
+      <c r="A5464" s="3" t="inlineStr">
+        <is>
+          <t>1155.psd</t>
+        </is>
+      </c>
+      <c r="B5464" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11411.psd</t>
+        </is>
+      </c>
+      <c r="C5464" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjN2ZElqSTJnQys2K2RNWlhBTWhRWGc9PSIsInZhbHVlIjoiMmEwK3JnSmxFWHNTY3dkV3gxaUF5Zz09IiwibWFjIjoiNDNlYTk3YTc5NzY5M2I4MDZhNzlhM2RlMjI1NzgyNTZkZTA3NTVkZjhmNjFkYzgzMWY3N2QzNGUxNTE1NDZlMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5465">
+      <c r="A5465" t="inlineStr">
+        <is>
+          <t>1250.psd</t>
+        </is>
+      </c>
+      <c r="B5465" t="inlineStr">
+        <is>
+          <t>tamilpsd-11412.psd</t>
+        </is>
+      </c>
+      <c r="C5465" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImFYeC9lK1JmOWIzaWZpdmJUZjk5R0E9PSIsInZhbHVlIjoiclZJSXhxWnVrOXhtSFJZeGxBNzh6QT09IiwibWFjIjoiOTFlYzgyNGEzNTRlNmJiOTU4ZGI1ODQ5Y2ZjZjIwZWYxNjhhYWFiMWZiYzU1MDZjOTNhOGMyOTFiYjUxMjZkMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5466">
+      <c r="A5466" s="3" t="inlineStr">
+        <is>
+          <t>1249.psd</t>
+        </is>
+      </c>
+      <c r="B5466" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11413.psd</t>
+        </is>
+      </c>
+      <c r="C5466" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilg5TEJ3ejZwTWFLTjRSK1o2U0RJRFE9PSIsInZhbHVlIjoiRzlmSllYSk5OMmUweEFzTlYrSnAvUT09IiwibWFjIjoiNjRiZjQ5NDRiMGRlMzY5OTViM2E3M2NiODdhY2VhNjhmYjJiY2QwMDRjMGRiNjA3YjcyYTQxZjhhZDE2NGM4YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5467">
+      <c r="A5467" t="inlineStr">
+        <is>
+          <t>1248.psd</t>
+        </is>
+      </c>
+      <c r="B5467" t="inlineStr">
+        <is>
+          <t>tamilpsd-11414.psd</t>
+        </is>
+      </c>
+      <c r="C5467" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklrN0hDSmJSaVJlYnNvYjFoZ0ZKV3c9PSIsInZhbHVlIjoiS0UzME1aT21IdlhXdWloUG9XVFlaUT09IiwibWFjIjoiZDFkYmI5MTI0ZDJlZjk1ZmNjMzU2YjdhMmVlZjFmYWYzZjVlOGMxNzljNzlkMjgyYzE0YTc3ZTY2NGM2YmNmNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5468">
+      <c r="A5468" s="3" t="inlineStr">
+        <is>
+          <t>1247.psd</t>
+        </is>
+      </c>
+      <c r="B5468" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11415.psd</t>
+        </is>
+      </c>
+      <c r="C5468" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlqZ0ZGUXBWbHRpcDRGTWxKOS9qa2c9PSIsInZhbHVlIjoiU1JpOTFJZnlBdEpGN09hQlNoTUFYdz09IiwibWFjIjoiM2FjNzRkM2VhOTg1YTVlZjVkM2ZkMWMwOGY5MWI5NDhmMzAwY2JlNDMyNjk2ZjMxN2NmN2Y2OWJmMWNmYTJmYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5469">
+      <c r="A5469" t="inlineStr">
+        <is>
+          <t>1154.psd</t>
+        </is>
+      </c>
+      <c r="B5469" t="inlineStr">
+        <is>
+          <t>tamilpsd-11416.psd</t>
+        </is>
+      </c>
+      <c r="C5469" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InRqOE9QczdLNHhKQXpRSkg2QjdNcFE9PSIsInZhbHVlIjoiaEdmcXR0RUZVL2x0T1NKWjNrMm9sZz09IiwibWFjIjoiODE5NDAzYzI4MTc0YjJiM2Y2MzA3YjA1YzczMjdlY2ViNjQ4OTE2OTQ5ZGJkNGI3ZTAzYThkMWJlZTY2MjMwZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5470">
+      <c r="A5470" s="3" t="inlineStr">
+        <is>
+          <t>1246.psd</t>
+        </is>
+      </c>
+      <c r="B5470" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11417.psd</t>
+        </is>
+      </c>
+      <c r="C5470" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InB4K3UrMTVCM2wzR1FhNzgrcXhuL3c9PSIsInZhbHVlIjoiZFJqeE0ySGhNckZ0SE13TUpaTXFuUT09IiwibWFjIjoiZTc4ODI1ZjRkYjc5MWE1MGFlNDAzNDYwZWRhMTgyNGMxZDZhNWY5MmQ3YmJkNzQ2MmMwN2Y3ZWY4YTc1ZDRlZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5471">
+      <c r="A5471" t="inlineStr">
+        <is>
+          <t>1245.psd</t>
+        </is>
+      </c>
+      <c r="B5471" t="inlineStr">
+        <is>
+          <t>tamilpsd-11418.psd</t>
+        </is>
+      </c>
+      <c r="C5471" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5NU3NEcHk1MGJwdGY4Z3BJUS9YaVE9PSIsInZhbHVlIjoiZWNoVUU2V3IwL1ltWUV5dkJWUWZ1QT09IiwibWFjIjoiY2M0ZTc1YTUwZGI1M2QwYTMwZTdkODhhMmEyYzVjOTAyMTkwNTNmNTc0Yzk1MWVkNzI5YTNmYTcwYjUxMTViNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5472">
+      <c r="A5472" s="3" t="inlineStr">
+        <is>
+          <t>1153.psd</t>
+        </is>
+      </c>
+      <c r="B5472" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11419.psd</t>
+        </is>
+      </c>
+      <c r="C5472" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5yMXVwaHZheUVYcWZXNGdWNFJ5OGc9PSIsInZhbHVlIjoiYnZJVVR5UjhBcExTREU4WTRGaDJOQT09IiwibWFjIjoiMDQ5YTExYTY3ZjY5MjIxMDkxZWQ0YTk5YTNmMjE2NjM3Zjc4MGMxMjUyNGUwNTAzZmE1YWUxNDUwMjMzYmY5OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5473">
+      <c r="A5473" t="inlineStr">
+        <is>
+          <t>1149.psd</t>
+        </is>
+      </c>
+      <c r="B5473" t="inlineStr">
+        <is>
+          <t>tamilpsd-11420.psd</t>
+        </is>
+      </c>
+      <c r="C5473" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRFM0wxbStGSWV4dmhqbWVDWWo1THc9PSIsInZhbHVlIjoicllMMS8yU1p4SzR4SHhzVzg4T0lDZz09IiwibWFjIjoiYzQxNjlkYzU4ZTAzNmFlNzNhZDg2YTBkMDcwZjliNGZhYjlmZjY4YTI0OTRjZTdjYTJmZjFhNjdhYzAyODU5NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5474">
+      <c r="A5474" s="3" t="inlineStr">
+        <is>
+          <t>1244.psd</t>
+        </is>
+      </c>
+      <c r="B5474" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11421.psd</t>
+        </is>
+      </c>
+      <c r="C5474" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjdJb0hJeE5iMktlVmVER291QkVIRFE9PSIsInZhbHVlIjoicWxzZm5ySTVsejVrMUk2eU0yZUpLUT09IiwibWFjIjoiYmZmOWUyMmZmMmYwZjYyZDQ1NmYxNTBkOGMxM2JkYWNlY2FiZTgxOGQ5MzdlMzkzNWRmZDA0MmFhOTU2OWE4YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5475">
+      <c r="A5475" t="inlineStr">
+        <is>
+          <t>1243.psd</t>
+        </is>
+      </c>
+      <c r="B5475" t="inlineStr">
+        <is>
+          <t>tamilpsd-11422.psd</t>
+        </is>
+      </c>
+      <c r="C5475" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndhL2pydkRpWXFvNGRTZEVyMk96WGc9PSIsInZhbHVlIjoiYmw5QlNpQjRDNFlPdldHQWgrTXErQT09IiwibWFjIjoiOTdiYWZkOGEwMGRiMWJjMDg2YTI0ZDU2MzNjZWRiM2JkOTgyODVlNmUzYWVmNTM1OTcyMjAxNzFiNTlmNzJkZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5476">
+      <c r="A5476" s="3" t="inlineStr">
+        <is>
+          <t>1242.psd</t>
+        </is>
+      </c>
+      <c r="B5476" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11423.psd</t>
+        </is>
+      </c>
+      <c r="C5476" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJsMTZ6Ri8zb2tNbDhJY3lMTXBLbnc9PSIsInZhbHVlIjoiZVFKSFE0NXVRSnRHZS9JWVhiK3V4UT09IiwibWFjIjoiZWNkYTUyZmE5ZDVjOTNjZmM2YjdkODM2ZGQxZGU1NmI5ZjJlZDM2YjdkMWJmMWFmNzRiMWM0MWJkZWE3YzkwNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5477">
+      <c r="A5477" t="inlineStr">
+        <is>
+          <t>1241.psd</t>
+        </is>
+      </c>
+      <c r="B5477" t="inlineStr">
+        <is>
+          <t>tamilpsd-11424.psd</t>
+        </is>
+      </c>
+      <c r="C5477" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNjSmNOQ2gwR0J5YlpJTEc3OEJnVnc9PSIsInZhbHVlIjoib3QxSXZpOTRtOEpQTEJVOXVEc0lQdz09IiwibWFjIjoiMzU4ZDNlYTA2MTdkMDhiZmFlYWNiNzY5MjE0ODA5MDIwMGU2MWZlMjQ3ZGYyOTJkMTBiNjRmMzc1NmY4OGUwOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5478">
+      <c r="A5478" s="3" t="inlineStr">
+        <is>
+          <t>1240.psd</t>
+        </is>
+      </c>
+      <c r="B5478" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11425.psd</t>
+        </is>
+      </c>
+      <c r="C5478" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndVWXlOL0c3SnNZS2g0QU11QUhycEE9PSIsInZhbHVlIjoiSVNMMUVKWWYxTHBsWEFROERneG4xQT09IiwibWFjIjoiOGVmZTdkZWZkMTEwZTFmMmRlNTMwNmEyN2M5NTE2ZjljYjgzNjRmNmIyYjRmZDNhMTQ3ZDIwYTdjOWFkYWUzMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5479">
+      <c r="A5479" t="inlineStr">
+        <is>
+          <t>1239.psd</t>
+        </is>
+      </c>
+      <c r="B5479" t="inlineStr">
+        <is>
+          <t>tamilpsd-11426.psd</t>
+        </is>
+      </c>
+      <c r="C5479" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5YdkJKbmVCUFlOR252Q2daUllPYmc9PSIsInZhbHVlIjoiclJTa3p2Tkp4WEhtNldzL2ptSzNKQT09IiwibWFjIjoiNjdkNTc0NGZkZjliYjVjNWYzNGY5Y2RiMmIwNDI2OGUzNTcwZmRjOTExYmE4YzcyYjAyZDhiMWIwNjkxYTRmMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5480">
+      <c r="A5480" s="3" t="inlineStr">
+        <is>
+          <t>1238.psd</t>
+        </is>
+      </c>
+      <c r="B5480" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11427.psd</t>
+        </is>
+      </c>
+      <c r="C5480" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikxkc05oV0pEc3FWTExEVTFZcU5Nbnc9PSIsInZhbHVlIjoiMXpRQ2dDajZCVDZZMGlwK0xhSFE0QT09IiwibWFjIjoiNGE0OTcwMGZmYTM5MzkxZjg0YjNhZGRiNTFlMGQ1M2QyNDI5ZDY0MjliN2QwNjQyZTAyZTQ3NGNkZjk2NzgyMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5481">
+      <c r="A5481" t="inlineStr">
+        <is>
+          <t>1237.psd</t>
+        </is>
+      </c>
+      <c r="B5481" t="inlineStr">
+        <is>
+          <t>tamilpsd-11428.psd</t>
+        </is>
+      </c>
+      <c r="C5481" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlWbG9SSEMwVlA5YUpkN0NxMFdsWnc9PSIsInZhbHVlIjoid3ZJVHNsSXJPTWdSMHBDMlJQb1FIZz09IiwibWFjIjoiNTI3ZTI2YzQ3N2UwNmZlYmQ0MGFjNmU5MjI1MjM0YWEzNGQyNGQwNWZmMmM3ZjVlZGUzNjY0NmM0ZjMyYWYyNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5482">
+      <c r="A5482" s="3" t="inlineStr">
+        <is>
+          <t>1260.psd</t>
+        </is>
+      </c>
+      <c r="B5482" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11429.psd</t>
+        </is>
+      </c>
+      <c r="C5482" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRnRTVpQ0FIWlVzS3NpaWxaVi8wWnc9PSIsInZhbHVlIjoiQjY3aHhQeE1VYnhxdTJPMWNIVS9rQT09IiwibWFjIjoiZGFjMWU0ZmZjMWNhMjI5YzBhMDMwMjc3ZWM4ZmEzZWQ3ZGU2NGM1Mjk4ZTMxODgxY2U3NGE4NmQ5ODI2YjkwYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5483">
+      <c r="A5483" t="inlineStr">
+        <is>
+          <t>1148.psd</t>
+        </is>
+      </c>
+      <c r="B5483" t="inlineStr">
+        <is>
+          <t>tamilpsd-11430.psd</t>
+        </is>
+      </c>
+      <c r="C5483" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhabFNMYU9UYWZkVGFiU2JVUGpwS3c9PSIsInZhbHVlIjoib0FnN3B4cytjNDArditZQ2VNTFRGUT09IiwibWFjIjoiMTVlZTRhZWE2NjYwZTI0NmNmYzEyYzgxMzY0N2I2Njc1ZTA5NTFhYmQ0NzIwNTRjYjMwOTNhYjI3N2JkODY5MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5484">
+      <c r="A5484" s="3" t="inlineStr">
+        <is>
+          <t>1147.psd</t>
+        </is>
+      </c>
+      <c r="B5484" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11431.psd</t>
+        </is>
+      </c>
+      <c r="C5484" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFjczJiMTY5Wi90QmRMYVNUZWxQVlE9PSIsInZhbHVlIjoiQXd6MmRBTW0vWEhWbU9uT2FKTjhkZz09IiwibWFjIjoiOGRhYjU3NTE5NzgwZmMyNTg4NjcxNTU5NTMzZGQ5YjBmZGIwMDRiZGEyNWU4NzJhMWUyN2NhNWJhOTQyNWEyYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5485">
+      <c r="A5485" t="inlineStr">
+        <is>
+          <t>1146.psd</t>
+        </is>
+      </c>
+      <c r="B5485" t="inlineStr">
+        <is>
+          <t>tamilpsd-11432.psd</t>
+        </is>
+      </c>
+      <c r="C5485" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhRY2VjVHZQRDRBTkhvL1QrTUxXYWc9PSIsInZhbHVlIjoiaEJETndXYnVzMVA1VzhQbW9rWXlEQT09IiwibWFjIjoiYTA1ZDMxMzI2ZDQ0ZDUwMjY2NDkyZmIwMDZkYTU3MDcyZTc4Yjk1MWEyZWFmMzhiMjY3YjdmNjI1N2UzY2Q3MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5486">
+      <c r="A5486" s="3" t="inlineStr">
+        <is>
+          <t>1234.psd</t>
+        </is>
+      </c>
+      <c r="B5486" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11433.psd</t>
+        </is>
+      </c>
+      <c r="C5486" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVvTlhHdlhxMUNUakVpRCtoNmdBRnc9PSIsInZhbHVlIjoiN0IvdTl4YUhXRXlOaXJ1eTNJS0k2UT09IiwibWFjIjoiNmYwZjJhMzc2YjEyNDc3NTY1NjA5MDQzN2JmODQyYzkyNTcwZGViNGRjZTMwNDMzYmY5N2M2MTEwZTBkOGY4YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5487">
+      <c r="A5487" t="inlineStr">
+        <is>
+          <t>1233.PSD</t>
+        </is>
+      </c>
+      <c r="B5487" t="inlineStr">
+        <is>
+          <t>tamilpsd-11434.psd</t>
+        </is>
+      </c>
+      <c r="C5487" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRlQlBDdnEvV1krYWgwbCtLenh3Wnc9PSIsInZhbHVlIjoiTXR1N1RnV1YzcWNoT0trdEUveHZ2QT09IiwibWFjIjoiZmIzNTYyMGJkMTExMDRlYzVlYzRiZmVlMTI2YzIyM2M1M2MwMDViYTYzOWZlMWRkMmYwYzM4ZTYyNmEyMTFjNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5488">
+      <c r="A5488" s="3" t="inlineStr">
+        <is>
+          <t>1232.psd</t>
+        </is>
+      </c>
+      <c r="B5488" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11435.psd</t>
+        </is>
+      </c>
+      <c r="C5488" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkorVlp4eWFPakg1NldFM3VFUjV0QVE9PSIsInZhbHVlIjoiMXFkQUNUOUJCZUVEWW8wdFpRdFBWZz09IiwibWFjIjoiYmI3ODdlZDM3OWI0ZjM5M2E0Yjk5MzIwODY1ZTU2ZDFkZjk1Y2Q1N2U2MzdhMWFlNTFmYmE1Mzg3NzM3NTE5YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5489">
+      <c r="A5489" t="inlineStr">
+        <is>
+          <t>1231.psd</t>
+        </is>
+      </c>
+      <c r="B5489" t="inlineStr">
+        <is>
+          <t>tamilpsd-11436.psd</t>
+        </is>
+      </c>
+      <c r="C5489" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRCMHBaSkMrRTZxWlcySVROUnkyOWc9PSIsInZhbHVlIjoieEVNRDcwTlNVQTVNRFNubVluSnFqdz09IiwibWFjIjoiNTZjZDc3YjM4NTYxZGVlNjQzNDFmNjgyODJjZGIwNTc2YjlkY2VkMWEyZDQwYjNiZWJjYTlmZDU0ODRjYTFiZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5490">
+      <c r="A5490" s="3" t="inlineStr">
+        <is>
+          <t>1230.psd</t>
+        </is>
+      </c>
+      <c r="B5490" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11437.psd</t>
+        </is>
+      </c>
+      <c r="C5490" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZjTnpOWGtzTWRTZEtIeHN0aVpHWWc9PSIsInZhbHVlIjoiNHBFUHBGSnhPWFU2a2c1MFBZem8wQT09IiwibWFjIjoiZDU2MDcxY2VlNzMxZmVhYWQyZGE0YTUwNmFkOWY5ZDI1MjM5ODliMjdlMzljM2Y5MjZhN2JhZjdhOGNlODk5MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5491">
+      <c r="A5491" t="inlineStr">
+        <is>
+          <t>1229.psd</t>
+        </is>
+      </c>
+      <c r="B5491" t="inlineStr">
+        <is>
+          <t>tamilpsd-11438.psd</t>
+        </is>
+      </c>
+      <c r="C5491" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRXMTExSGxBSjRFbC9DcGhzaXZJQUE9PSIsInZhbHVlIjoiNEdUaUNUVml2VHZlRlVRSFFCYnhVZz09IiwibWFjIjoiZWQ2NTYwOGU5MWZhMGQzZWRjYWFlM2U1ZmZjYmMzNGZlZTE1Y2M5NTBmZDhlY2JjMmRjZWI1OGMwYjMwNTBmZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5492">
+      <c r="A5492" s="3" t="inlineStr">
+        <is>
+          <t>1228.psd</t>
+        </is>
+      </c>
+      <c r="B5492" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11439.psd</t>
+        </is>
+      </c>
+      <c r="C5492" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikh3Z2pONkVRTm9aeVZzY29hazBjRHc9PSIsInZhbHVlIjoiT051eW9hOWNkWTU1K3NyUkpZTG13Zz09IiwibWFjIjoiNDNhY2Q4MjgwOGNkNzFkODdlZjE2NWYzYzMyNjM4NGFiOGQ0YWIxMTM0ZDVlMTIzNWI3MWE1ZGEwMDRhODI0NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5493">
+      <c r="A5493" t="inlineStr">
+        <is>
+          <t>1227.psd</t>
+        </is>
+      </c>
+      <c r="B5493" t="inlineStr">
+        <is>
+          <t>tamilpsd-11440.psd</t>
+        </is>
+      </c>
+      <c r="C5493" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVyRDVIeUJwQWRwOWRNRitEb1VGZ0E9PSIsInZhbHVlIjoiWkxNUFpFQk16d2F6akFac292Y2hqQT09IiwibWFjIjoiMTljMzllZmQ2YzJjZjBkMjBiZGE2NWNmODZiOWE2NDMwMTEzYTYxZGQ1Yzg3MmRhODVlOGM0ZDE5N2MzMzlkNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5494">
+      <c r="A5494" s="3" t="inlineStr">
+        <is>
+          <t>1226.psd</t>
+        </is>
+      </c>
+      <c r="B5494" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11441.psd</t>
+        </is>
+      </c>
+      <c r="C5494" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii85S2xmYjBwY0xQRlcrNFplbmowU1E9PSIsInZhbHVlIjoiaFJubm1BNUNNWElzbGFFT0x4RkJRdz09IiwibWFjIjoiYzZmMDVhOGMzNmFkOWZmYzlmODYxOTg0ZDRlNGM3N2VhM2NkMTI0ZDFiOTQzM2VkMmY2MzM4YjkwYzYyYjNkNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5495">
+      <c r="A5495" t="inlineStr">
+        <is>
+          <t>1225.psd</t>
+        </is>
+      </c>
+      <c r="B5495" t="inlineStr">
+        <is>
+          <t>tamilpsd-11442.psd</t>
+        </is>
+      </c>
+      <c r="C5495" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkowWmNnYUJvbk84NE16dTRCSzRYUFE9PSIsInZhbHVlIjoiQVZJQkhHZjFXRGJtZldWclhCdTQxQT09IiwibWFjIjoiMGFhNWVhMDM5YTczMGRiOWEzOGQ2Y2ZmMDlhYjkyN2YyZjFmODY4M2U5ZmZjNWZjZWViYzRlZTgzMjY2MzUzOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5496">
+      <c r="A5496" s="3" t="inlineStr">
+        <is>
+          <t>1224.psd</t>
+        </is>
+      </c>
+      <c r="B5496" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11443.psd</t>
+        </is>
+      </c>
+      <c r="C5496" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InpleDY1WUNFdnoxYWg2bVJsMmh1SHc9PSIsInZhbHVlIjoiakUrUVp5djU3U0lIZ3NDdHFCWDdVQT09IiwibWFjIjoiZjRmNDAxOGM5ZGI2YjI1NmZkNWJjM2M2NDc0M2UxOWE4ZDMxMWE5NmZhNzQwYzQ5OThmYThlZjdjM2IwYTIzMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5497">
+      <c r="A5497" t="inlineStr">
+        <is>
+          <t>1223.psd</t>
+        </is>
+      </c>
+      <c r="B5497" t="inlineStr">
+        <is>
+          <t>tamilpsd-11444.psd</t>
+        </is>
+      </c>
+      <c r="C5497" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBRcUYvM1JhWkR1aWdGanNUOHhBTUE9PSIsInZhbHVlIjoia3ErcnlldHlKVXlkNGxreHEvdFBWQT09IiwibWFjIjoiNjRkZThlYTdkMDdiOGI1NzBhZTk4MjY3NTUyNDQxYTg1ZmIzZDhiYWZkMzY0ZmVlYTM0NWZiNzJjMmQ1ZWYwMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5498">
+      <c r="A5498" s="3" t="inlineStr">
+        <is>
+          <t>1222.psd</t>
+        </is>
+      </c>
+      <c r="B5498" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11445.psd</t>
+        </is>
+      </c>
+      <c r="C5498" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVadDg3ZTFBUEJaZWkvYzZpRTdKWHc9PSIsInZhbHVlIjoiamI0Z1gyT01wV3NPT1p0dDl5c0p4dz09IiwibWFjIjoiNDI3M2I2YjA3ZjBlNTc4OWI4M2IyYzA1ZWYxYmJkYWQ1MTA5Zjc3YWMzNGZmMjY3MmViNGQ2OTc5YzJiZmYxMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5499">
+      <c r="A5499" t="inlineStr">
+        <is>
+          <t>1221.PSD</t>
+        </is>
+      </c>
+      <c r="B5499" t="inlineStr">
+        <is>
+          <t>tamilpsd-11446.psd</t>
+        </is>
+      </c>
+      <c r="C5499" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRxdmt2ZW9TMGJmV2hSOFV4Yy9nZWc9PSIsInZhbHVlIjoiQjFhVzhyKzI3NmFZcTl6cC95S1RjQT09IiwibWFjIjoiZWJlZThhZWViZGFjMGU5NzQwYjQ4OWYxYjM3NWEyMzYyNDY4MDk4MWUzYTRhMDc3ZTZlMGM3ZDY1NjI3YmY3MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5500">
+      <c r="A5500" s="3" t="inlineStr">
+        <is>
+          <t>1220.psd</t>
+        </is>
+      </c>
+      <c r="B5500" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11447.psd</t>
+        </is>
+      </c>
+      <c r="C5500" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkE3bCsveVZiTXFwZVlOLzE0WnpwbUE9PSIsInZhbHVlIjoiNk5oVkR3MThJenhvWENsSkNBN0VrQT09IiwibWFjIjoiOGY1ZjY2ZGMwMjFhZmQ3NjU5MjM5ZmZiMTU2OGI1YjQzNDkwYzM4ZWQxZWQ4ZjM4N2RmYWQxZjhmYWUyNDAyZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5501">
+      <c r="A5501" t="inlineStr">
+        <is>
+          <t>1219.psd</t>
+        </is>
+      </c>
+      <c r="B5501" t="inlineStr">
+        <is>
+          <t>tamilpsd-11448.psd</t>
+        </is>
+      </c>
+      <c r="C5501" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9pVzkyVWlEUzZnUi9wcWdjK3NqeXc9PSIsInZhbHVlIjoiaWkxa01PM3ZHYXBBa0tscFlVSjNhdz09IiwibWFjIjoiYzFiYzkzNGE1ZTkzZTk2M2NjMjVhNDU4NDMzNDBiYTM1MjE0NDNkOTEyN2FmNmRiNWViNjQ5NjAyNGJiMDliNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5502">
+      <c r="A5502" s="3" t="inlineStr">
+        <is>
+          <t>1218.psd</t>
+        </is>
+      </c>
+      <c r="B5502" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11449.psd</t>
+        </is>
+      </c>
+      <c r="C5502" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVybVdUcDEwY3UzWFF5SXVZaFYvZkE9PSIsInZhbHVlIjoiaE9NWjRMeFFIWHMvZkxWQ1BrQWdXUT09IiwibWFjIjoiOWI5OWUyZDg3NzcyZGM4ODZhYzdiNjdkMTE1ZDI2Y2ZhMzE4ZjZhMThkY2U0OTg4MGZhMjk5MTFkODlkZWFiOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5503">
+      <c r="A5503" t="inlineStr">
+        <is>
+          <t>1217.psd</t>
+        </is>
+      </c>
+      <c r="B5503" t="inlineStr">
+        <is>
+          <t>tamilpsd-11450.psd</t>
+        </is>
+      </c>
+      <c r="C5503" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktzcGJzWjR4SXRmbWlEc1BhM3cvalE9PSIsInZhbHVlIjoiY2sycGVGQy9MOGVYN0c0SGxwWTZEQT09IiwibWFjIjoiNjIyYjczMGFhZWQ4YzZlODA2Zjc0Y2IzYTgyOTM2MmQ3NDg3OWQ3YzkxZDAyZjUyNDRjMmMyY2U4YzY0MWU3NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5504">
+      <c r="A5504" s="3" t="inlineStr">
+        <is>
+          <t>1216.psd</t>
+        </is>
+      </c>
+      <c r="B5504" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11451.psd</t>
+        </is>
+      </c>
+      <c r="C5504" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlYYUZBNFg0WExORnF2eFJPSDVZaUE9PSIsInZhbHVlIjoiYXAwT3drS0drL0J5SjBEYzFqM0NwZz09IiwibWFjIjoiZjFjYjhkZTdhYmYxMmYyZjViNGZmNjI3MGI1OGI2M2QxNTY0NGM2YTNiOWFkOWZiNjAzYTE1MWJjZTVhN2UxYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5505">
+      <c r="A5505" t="inlineStr">
+        <is>
+          <t>1215.psd</t>
+        </is>
+      </c>
+      <c r="B5505" t="inlineStr">
+        <is>
+          <t>tamilpsd-11452.psd</t>
+        </is>
+      </c>
+      <c r="C5505" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpROStHdXpLS3Z1dDRMck0vdFpPa1E9PSIsInZhbHVlIjoiamMwZlVJOWszaVlUVjV3OWF2VG0yQT09IiwibWFjIjoiZmQ5YzIyZDA5OGYzMDlhYTkwYmMzZmI4MzIwZDVkN2QyNzZhOWIyNzIyMmUxMzc4ZTAxMzIzYzY2YWEzMGIwNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5506">
+      <c r="A5506" s="3" t="inlineStr">
+        <is>
+          <t>1214.psd</t>
+        </is>
+      </c>
+      <c r="B5506" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11453.psd</t>
+        </is>
+      </c>
+      <c r="C5506" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNveFlaeC9vbFJqYi8yRmk4Z055a0E9PSIsInZhbHVlIjoiMXdOOE1iamRQRXZWVDQyMmJjWDVjZz09IiwibWFjIjoiZDE4ZDE1ZmFlZjI2ZDNmYzA2YTk5M2FjZDczYmVhMGFhOGI2MTIyY2E3Nzk1NmQ5YTI2NzZmMTBmYmQyMWZhMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5507">
+      <c r="A5507" t="inlineStr">
+        <is>
+          <t>1145.psd</t>
+        </is>
+      </c>
+      <c r="B5507" t="inlineStr">
+        <is>
+          <t>tamilpsd-11454.psd</t>
+        </is>
+      </c>
+      <c r="C5507" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjdJSVRLYTJPTWhDaHpjTU5YSkM3UFE9PSIsInZhbHVlIjoid25HSWpxMVZwdHRpcVo2ZDM2YmJUUT09IiwibWFjIjoiNmJmMTBkM2IyMzI4NGM3MjhhM2ZiNDcxNTc3ZjZlZDFiZWJiNzc1ZTc2N2U2OWI1MTA2YWRhYmYzN2MzMWQ5NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5508">
+      <c r="A5508" s="3" t="inlineStr">
+        <is>
+          <t>1213.psd</t>
+        </is>
+      </c>
+      <c r="B5508" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11455.psd</t>
+        </is>
+      </c>
+      <c r="C5508" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFJV2taT1l4OS8weXJtY0Fqd3YxdEE9PSIsInZhbHVlIjoiK2ZKK3o4UXhiOWJ0djJXMjVLWlFuUT09IiwibWFjIjoiODI2NDE2ZGRkMmI2ZDM3NTUzZWFlNWMxNTQyN2RkM2RkMjQzMmIzMjhkNzQzOTMzNzA1ZTI5ZDVmMWY5MWVmNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5509">
+      <c r="A5509" t="inlineStr">
+        <is>
+          <t>1212.psd</t>
+        </is>
+      </c>
+      <c r="B5509" t="inlineStr">
+        <is>
+          <t>tamilpsd-11456.psd</t>
+        </is>
+      </c>
+      <c r="C5509" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFOQ3pENlcySlVmZEcrUVZKWmtLU1E9PSIsInZhbHVlIjoiY1JucWM3cE10TFRlNnRoOS9FcWhjUT09IiwibWFjIjoiOGYwODRhZmYwYzRlZmE1Yjg3MjI3ZDQ5NGU1M2Y3NjljNzA1ZTUyMTZkZmRmODc3MWE2MjBjMGQ5YjliMDM1YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5510">
+      <c r="A5510" s="3" t="inlineStr">
+        <is>
+          <t>1144.psd</t>
+        </is>
+      </c>
+      <c r="B5510" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11457.psd</t>
+        </is>
+      </c>
+      <c r="C5510" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZqTENNWnVXRUhQMUJ2VUEyRU5vVVE9PSIsInZhbHVlIjoia1F6cnU0UFYwYlVkZTZiL05aejVhZz09IiwibWFjIjoiZTFjODcxNjI2NTc3YzM5ZDc3OWU5ZWVkMTdlZjg0YWY1MGQ4MDcxZGU0NmMzNjUxZjdkZWU1ZjA1NjRjZDg0MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5511">
+      <c r="A5511" t="inlineStr">
+        <is>
+          <t>1211.psd</t>
+        </is>
+      </c>
+      <c r="B5511" t="inlineStr">
+        <is>
+          <t>tamilpsd-11458.psd</t>
+        </is>
+      </c>
+      <c r="C5511" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik8zNHdOQW5KRmRaczF1OFdYWk03SEE9PSIsInZhbHVlIjoiU0xadGlGYTNneHZocXRiNExNMmh4QT09IiwibWFjIjoiNGIxYmZiMmVmMDU0M2ZjMDk0NDNkOTU4YmM1ZGY0MTM5ZjU1NzU4MTI0ZWM2MWFhMmRlN2QyNGFiYmRjNWVmMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5512">
+      <c r="A5512" s="3" t="inlineStr">
+        <is>
+          <t>1210.psd</t>
+        </is>
+      </c>
+      <c r="B5512" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11459.psd</t>
+        </is>
+      </c>
+      <c r="C5512" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtYZ1laK1Z3MGFwelhBVXplNWVLY2c9PSIsInZhbHVlIjoiZitVdVNzUmdIbXQwT0tMaE5qQXRqUT09IiwibWFjIjoiY2NmZmYxZWQ1N2FlMzIxOGViMzkwYTBiN2U5YTVlNTg0MDRmNjZjODEwZTg2YTI4ZDUyZDZjNzVjMzQ2Yzg0NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5513">
+      <c r="A5513" t="inlineStr">
+        <is>
+          <t>1209.psd</t>
+        </is>
+      </c>
+      <c r="B5513" t="inlineStr">
+        <is>
+          <t>tamilpsd-11460.psd</t>
+        </is>
+      </c>
+      <c r="C5513" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBTS0IvemtsNmx6cVBkZlduNUtrZUE9PSIsInZhbHVlIjoiS1c0T25SNjQveEt6ZkpPVzhYcklLdz09IiwibWFjIjoiMDBiODU4ZTkyOGJkYzgwMmQxN2UwMGRkYjVkNTQ5NDExZmQ4NzZlZTJlNjQ2MjIxZjVmNGYzYzNlYjlkYmFmYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5514">
+      <c r="A5514" s="3" t="inlineStr">
+        <is>
+          <t>1208.psd</t>
+        </is>
+      </c>
+      <c r="B5514" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11461.psd</t>
+        </is>
+      </c>
+      <c r="C5514" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjdnZldNdkhGRTVNKzQ2Tkl0VUZocHc9PSIsInZhbHVlIjoiSW1jVVRyVllmbkRyM1pVbUlqVUppUT09IiwibWFjIjoiOWVkZWMzNWNiZmMzN2YwMmQ0YWZkMjU4MjIyMmZkMTVhZDJkZWM1ZjQ2MTMyMWU1OTBjNTlkMWI2NmIzMDcwMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5515">
+      <c r="A5515" t="inlineStr">
+        <is>
+          <t>1207.psd</t>
+        </is>
+      </c>
+      <c r="B5515" t="inlineStr">
+        <is>
+          <t>tamilpsd-11462.psd</t>
+        </is>
+      </c>
+      <c r="C5515" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZWdHhqYVpvVFB6Tm5mSE50TTFvK0E9PSIsInZhbHVlIjoibUt2SEY3T2hUV0thVzluazdDVWJIQT09IiwibWFjIjoiYjE0NDYzOWUyODQxMWE1YjVkODFkYTA3YzY2NDhlNDBhZmE2YzhmZGRlYjcxOTU1ZWU2Mzc2M2M1YWMwNDkzMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5516">
+      <c r="A5516" s="3" t="inlineStr">
+        <is>
+          <t>1206.psd</t>
+        </is>
+      </c>
+      <c r="B5516" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11463.psd</t>
+        </is>
+      </c>
+      <c r="C5516" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlR2NUZ0ajQveGNTc2JrVzJ1K3Jyc1E9PSIsInZhbHVlIjoiVHV4RWVLWmF5UDJDb1FuRXRoSjVFZz09IiwibWFjIjoiZTFiNzZmODIwNmM2OGE5NjI5YTQ0YmZkNTE1M2ZmYTQ2M2IzMmRlYzNhYTViZjJhZTI0ZDg1ZjgyMGIyZDFkNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5517">
+      <c r="A5517" t="inlineStr">
+        <is>
+          <t>1205.psd</t>
+        </is>
+      </c>
+      <c r="B5517" t="inlineStr">
+        <is>
+          <t>tamilpsd-11464.psd</t>
+        </is>
+      </c>
+      <c r="C5517" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJlcEhwclB5ZWRpODYxUHdoYUE1a2c9PSIsInZhbHVlIjoiYThYaDRJTnZCU0ZKdDc1RGNiMmZmZz09IiwibWFjIjoiZDFmNTg2NGY1NDBmYThjZjFmZmY5NDAxNDdhOWFmNGI4MTkyMzFhNDgwY2JjOWY4OTQ2YzQwNGQ4YzY2MjFjMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5518">
+      <c r="A5518" s="3" t="inlineStr">
+        <is>
+          <t>1204.psd</t>
+        </is>
+      </c>
+      <c r="B5518" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11465.psd</t>
+        </is>
+      </c>
+      <c r="C5518" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InY2aU11ZHJqUFNIUnUvVEt0ck55UHc9PSIsInZhbHVlIjoiSG5hbWUrcnhyVERBV3FscDVrMG5xZz09IiwibWFjIjoiNGIyN2FiMWI4NWRhZmE4NGQ2MzUzYmY5NjExNjEwM2FjZDBjZjdhYWQ0NTAyODFjNDQ3NWM2NjAzZjcxMTc5YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5519">
+      <c r="A5519" t="inlineStr">
+        <is>
+          <t>1203.psd</t>
+        </is>
+      </c>
+      <c r="B5519" t="inlineStr">
+        <is>
+          <t>tamilpsd-11466.psd</t>
+        </is>
+      </c>
+      <c r="C5519" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhkaTJySlluZ2hWWEVpOFYreGFJeUE9PSIsInZhbHVlIjoiZGlRc2tHTzFKNG9DdGNvZGxBMkc4UT09IiwibWFjIjoiODlhYjQ5OTE1ODBkMTlkNTY4NmNmOGFlY2ZjZTY2OGE0YzdmN2ZhOGY2YjE4NGE0Y2MxZDliOTEyZWViZGI2NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5520">
+      <c r="A5520" s="3" t="inlineStr">
+        <is>
+          <t>1202.psd</t>
+        </is>
+      </c>
+      <c r="B5520" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11467.psd</t>
+        </is>
+      </c>
+      <c r="C5520" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxmeWhUUzBQTWw0WUFJZ29kaCtPL2c9PSIsInZhbHVlIjoidFgxT0xFMDkxdFF0WGdVY00rOHBsZz09IiwibWFjIjoiOTZlN2E5MTgzNjU2YWE5Y2ZlNjlkMDZhYjZhMjk1YmE3YWFlZTUzYTViNGIyYWRlY2E5NTRhM2I0NDkyZGJhYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5521">
+      <c r="A5521" t="inlineStr">
+        <is>
+          <t>1201.psd</t>
+        </is>
+      </c>
+      <c r="B5521" t="inlineStr">
+        <is>
+          <t>tamilpsd-11468.psd</t>
+        </is>
+      </c>
+      <c r="C5521" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InJiV0JNK3VDazlvY1BqVk1mSjJKU1E9PSIsInZhbHVlIjoieVBvajhONkNtcjNLSHBZaEh4bFVYUT09IiwibWFjIjoiY2UwZWQ5NmU0MmRmNmFhNDBmMGNhMjI3NGMyMzFlMDQyZGJiMDg5Yjk3YTg1MjA1MDFkNDZlOGUyY2JmNDc2YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5522">
+      <c r="A5522" s="3" t="inlineStr">
+        <is>
+          <t>1200.psd</t>
+        </is>
+      </c>
+      <c r="B5522" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11469.psd</t>
+        </is>
+      </c>
+      <c r="C5522" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ill4TndmdURaaGdKZ0VhOXY0TUZPcWc9PSIsInZhbHVlIjoiSzhjNWNsaGpXdFRnZEVsOWlPUnpKdz09IiwibWFjIjoiZTY4ZjljNWQ4ZjU0YjI4NTc3ZGQ1NDkxN2E1MjMzZjI2NjA1ZDgzNzRhY2QwMjNmNGIxNDVjZDMzNzAyYTJiZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5523">
+      <c r="A5523" t="inlineStr">
+        <is>
+          <t>1199.psd</t>
+        </is>
+      </c>
+      <c r="B5523" t="inlineStr">
+        <is>
+          <t>tamilpsd-11470.psd</t>
+        </is>
+      </c>
+      <c r="C5523" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkVPVS9CVXA4UFoyL2FGWlRGWVd2TUE9PSIsInZhbHVlIjoiVUxrUUlLeTN6K2NDUEFPSUFOQXBpUT09IiwibWFjIjoiMGI4Y2Y3ZWI2YzJjZTRjNWUzOGVlYjRjZGVjN2E5ZjQ2MzFjODg5YTJkZTljMmVhNTJlNmM5MjU3NTE3MDMxOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5524">
+      <c r="A5524" s="3" t="inlineStr">
+        <is>
+          <t>1198.psd</t>
+        </is>
+      </c>
+      <c r="B5524" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11471.psd</t>
+        </is>
+      </c>
+      <c r="C5524" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNoN3JZNUpUSmZiSDBvc1VYYU9uQ2c9PSIsInZhbHVlIjoiSm5aMkt4OFpDQ2oxQ2R0ZTlGT0hhZz09IiwibWFjIjoiMjE5MWQ2YTM5NjU2Y2UxOTJlNWUyNjE3OWYyMGU4ZjU5ZmIzN2RlYzc4MTc4ODlhN2U5ZjAzNWI2ZDU4ZmMzNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5525">
+      <c r="A5525" t="inlineStr">
+        <is>
+          <t>1197.psd</t>
+        </is>
+      </c>
+      <c r="B5525" t="inlineStr">
+        <is>
+          <t>tamilpsd-11472.psd</t>
+        </is>
+      </c>
+      <c r="C5525" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InJ3TTVCdzJUVWxBL01ONXRzUldQWGc9PSIsInZhbHVlIjoiNjNJYVhSS2FpTXdTYjAxeGlYOWQ1Zz09IiwibWFjIjoiMTg4OTg0ZmIzZjMyM2ZmMmE0MTk4NDI4NTMwYmFmNmEyMmU4ZjYyYmQ5ZjQ3MDVlNTEzM2M0NDZmNmJiZGI0OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5526">
+      <c r="A5526" s="3" t="inlineStr">
+        <is>
+          <t>1196.psd</t>
+        </is>
+      </c>
+      <c r="B5526" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11473.psd</t>
+        </is>
+      </c>
+      <c r="C5526" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5qVW52RnFkRUN5UHJmNElpc0xyUFE9PSIsInZhbHVlIjoiWXgyb2U2RFpSVmtnR1RXcllxdC81dz09IiwibWFjIjoiMWFiYzIyOWI2ZDI5NTQ2YzUwYzIwMGFhMzMyZWZkM2E3ZTViZDQyODJlNDUzOGQyZmU3YjU4YTkwNjFjNTBmZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5527">
+      <c r="A5527" t="inlineStr">
+        <is>
+          <t>1195.psd</t>
+        </is>
+      </c>
+      <c r="B5527" t="inlineStr">
+        <is>
+          <t>tamilpsd-11474.psd</t>
+        </is>
+      </c>
+      <c r="C5527" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFaL2JJKy9BdFM5WU05enlMT3labXc9PSIsInZhbHVlIjoiemx0aStNd0VnRzRyVFc4ME52VjJLUT09IiwibWFjIjoiMWY2OWY1OTM3NDJlMDM3YWYwZDNkYzU5MjI4N2JhYTRiNGQ2NTY5NjYzMTNkNzQyZTg3ZTM3OGJlY2I1NGUxZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5528">
+      <c r="A5528" s="3" t="inlineStr">
+        <is>
+          <t>1194.psd</t>
+        </is>
+      </c>
+      <c r="B5528" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11475.psd</t>
+        </is>
+      </c>
+      <c r="C5528" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhadElnQWlYcG1iUVA2ZFhIZlMzYlE9PSIsInZhbHVlIjoiaVZmZUFlMnpRUExPOFNDUlBQb2FTZz09IiwibWFjIjoiNTNhNmE4MzEwOGUwNTliMTY0MjliMjA2YTBlYjRjNzQyNTQ4YmQ3MGI3Y2NlYjk5ZTE5YzJmNGE5Y2I5YjUyNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5529">
+      <c r="A5529" t="inlineStr">
+        <is>
+          <t>1193.psd</t>
+        </is>
+      </c>
+      <c r="B5529" t="inlineStr">
+        <is>
+          <t>tamilpsd-11476.psd</t>
+        </is>
+      </c>
+      <c r="C5529" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InEyelhnNE1SU2N0bnh3ZEZkQ1loM2c9PSIsInZhbHVlIjoieWVQYWk4bHRRVHJPVGI5U0Q5REZaZz09IiwibWFjIjoiYTM2NmViMzUyYjcyMDVjOTgzMmNjN2NhN2YxODM5Y2RkOGE1MDFiOGIwYWRlYjkwNTQ4NzkxYTI1NTdhYWYwMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5530">
+      <c r="A5530" s="3" t="inlineStr">
+        <is>
+          <t>1192.psd</t>
+        </is>
+      </c>
+      <c r="B5530" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11477.psd</t>
+        </is>
+      </c>
+      <c r="C5530" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlQeXU3Z0tnV3JKVnRxamY1MkdveUE9PSIsInZhbHVlIjoiMitrY0NTb2JSWlZ2aVdrcno4Q3p0QT09IiwibWFjIjoiNGViYzUwZDgyODZhZTdlNWM5MmQxNWJlNmM2ZGZjM2I4NGFjYWViYjU2NTk1YjBiMjMwMGVkNGU5ZDZjNTNkYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5531">
+      <c r="A5531" t="inlineStr">
+        <is>
+          <t>1191.psd</t>
+        </is>
+      </c>
+      <c r="B5531" t="inlineStr">
+        <is>
+          <t>tamilpsd-11478.psd</t>
+        </is>
+      </c>
+      <c r="C5531" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndlUUN3SiswWC9qZ2NtSERNZjBabHc9PSIsInZhbHVlIjoiTHZFeUNKcUNHU2lnb1BydE9iMWI1Zz09IiwibWFjIjoiZmQwZTcwNTk5YTNmMjY4OTU5NGY3NzE2NGYzNjJiYmM0ZGEwZTczNjNiYTliNjQ2ZWEyYzM2N2Q4ZWQxODRkOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5532">
+      <c r="A5532" s="3" t="inlineStr">
+        <is>
+          <t>1190.psd</t>
+        </is>
+      </c>
+      <c r="B5532" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11479.psd</t>
+        </is>
+      </c>
+      <c r="C5532" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImY3SXB2NG5OMnpFSkdoa1FwV1Z6YlE9PSIsInZhbHVlIjoibmdzRktFMXFJNUYwSm00NXRjRFdMUT09IiwibWFjIjoiY2Q5OTA0Nzc4NTcyNmUxOTM3OGFkMTNkNzJiZGMxZmNhOWU4NDY4NGFjOTRjZGJhNDY4NWM5ZTQyN2JkMGM0MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5533">
+      <c r="A5533" t="inlineStr">
+        <is>
+          <t>1189.psd</t>
+        </is>
+      </c>
+      <c r="B5533" t="inlineStr">
+        <is>
+          <t>tamilpsd-11480.psd</t>
+        </is>
+      </c>
+      <c r="C5533" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRFMHI1UndVYWw1bDNGWGF6VllhRUE9PSIsInZhbHVlIjoibE42WTBORFh2cjVBN0txWExoNDJYUT09IiwibWFjIjoiYmM0MDJkYjg5N2I2N2Y0NDAyZjJkMzg2ZDliMTUyOTg0ZjJlZDljNjQzZTAzZmE3MDRjNzkyMDJkYzZkNDQzYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5534">
+      <c r="A5534" s="3" t="inlineStr">
+        <is>
+          <t>1188.psd</t>
+        </is>
+      </c>
+      <c r="B5534" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11481.psd</t>
+        </is>
+      </c>
+      <c r="C5534" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImQwWjJ0TmFyWWwrSS8xOWJ4ZVg2YVE9PSIsInZhbHVlIjoiVHdxNUR6alNTUE5DQzcweWt4VE1oUT09IiwibWFjIjoiMTA1OTE1Yzk4YzQ2MjAxZDBmNzYxMGU1NjIwZDA5Y2E1ZGZlMDEyNGQ5YjEyNDRhZjczZDVlNmU5YjM3ZjlmNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5535">
+      <c r="A5535" t="inlineStr">
+        <is>
+          <t>1187.psd</t>
+        </is>
+      </c>
+      <c r="B5535" t="inlineStr">
+        <is>
+          <t>tamilpsd-11482.psd</t>
+        </is>
+      </c>
+      <c r="C5535" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IngrY3ZLcFRreDNqUWdnWEE2cElKRnc9PSIsInZhbHVlIjoiZjNFNlJvMithOTNvRlRrdVcvM3NpUT09IiwibWFjIjoiZTNjNTdiMTJiOTE0NjEzM2E0YmNmZjBkMzc2N2M1YzU0MzBhZmNmMTA5NzJiMWFmMzM1ZTAzZWIzODljZTc3MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5536">
+      <c r="A5536" s="3" t="inlineStr">
+        <is>
+          <t>1143.psd</t>
+        </is>
+      </c>
+      <c r="B5536" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11483.psd</t>
+        </is>
+      </c>
+      <c r="C5536" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjY0U0JpYVh5d1NialBKUElvWkhaMXc9PSIsInZhbHVlIjoib0R5SWhLREhpUDkxVFB1OFlLc0hsQT09IiwibWFjIjoiMzQ4NDEwNjMxNDA5MGE2MjIwMmQzZDI1YjMxYzlhMzA5Mjg1YTA5MzMyMDgyNTc0Y2Q3NTJiZGFjYjY5ZTZkNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5537">
+      <c r="A5537" t="inlineStr">
+        <is>
+          <t>1186.psd</t>
+        </is>
+      </c>
+      <c r="B5537" t="inlineStr">
+        <is>
+          <t>tamilpsd-11484.psd</t>
+        </is>
+      </c>
+      <c r="C5537" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllLRnZXL21MSzlkS2FhQnIxSzFvT1E9PSIsInZhbHVlIjoiMzUyeWRONFVHUTJZZk9ObXEwdHA3dz09IiwibWFjIjoiN2FkNjZkZTM5Zjg1ODJiNmZjYjRjZjU2YTQ1OTMwNDQzZDQ3ZDQwZTM4M2Y0NDZmMTczYTY4MTBkM2YwMzNkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5538">
+      <c r="A5538" s="3" t="inlineStr">
+        <is>
+          <t>1235.psd</t>
+        </is>
+      </c>
+      <c r="B5538" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11485.psd</t>
+        </is>
+      </c>
+      <c r="C5538" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InA0OVpzZVE0bUdybEhQcmc1WG8rS2c9PSIsInZhbHVlIjoiUWh1UnhtWUt4OHNIV1RVOWJJajQ2dz09IiwibWFjIjoiNTAxMWIwOWE0ZmUxZjg3MDlhMTA3NjBiN2Y5ZmRkM2RkY2EyNjU4NjVmZGQzZGMzNzA0MGQ4MGM1NTlmMDE1OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5539">
+      <c r="A5539" t="inlineStr">
+        <is>
+          <t>1142.psd</t>
+        </is>
+      </c>
+      <c r="B5539" t="inlineStr">
+        <is>
+          <t>tamilpsd-11486.psd</t>
+        </is>
+      </c>
+      <c r="C5539" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJpd05OeGYxTHdUYm5IUTlxcGdtZlE9PSIsInZhbHVlIjoiRE0xMGJwZ0JPd2dLaVYxcE5vSWlPUT09IiwibWFjIjoiOGJmNjhhZWU0ZmVmYjcyZGZiYzkyYTEwMjEyYTQxMDkwNTNkZjIwZmIxNmYzMjIzNmYyNDE2MDFiM2NiNTI5YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5540">
+      <c r="A5540" s="3" t="inlineStr">
+        <is>
+          <t>1141.psd</t>
+        </is>
+      </c>
+      <c r="B5540" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11487.psd</t>
+        </is>
+      </c>
+      <c r="C5540" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhWZ0IwTG9FTXdnek5MTjJYaWdYb2c9PSIsInZhbHVlIjoiQkhCa3pkeXdPYWVZT201K24yTlk2UT09IiwibWFjIjoiOTQzYmE1OWZkOWYwMDZjMjg4YzRjODg0OTI4MDJkZGI4MThkZTY0OGY5Yzc5MDliYjY5NWFhMWY0MDUzZTgyNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5541">
+      <c r="A5541" t="inlineStr">
+        <is>
+          <t>1140.psd</t>
+        </is>
+      </c>
+      <c r="B5541" t="inlineStr">
+        <is>
+          <t>tamilpsd-11488.psd</t>
+        </is>
+      </c>
+      <c r="C5541" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlyZ2xobjltZGdONmdwMjl3QkgwcEE9PSIsInZhbHVlIjoic3I0VDJsV2tWeVlUWlRPdC9EWjBvdz09IiwibWFjIjoiOWFkNzEwOWExMWZhMjJmNDg0MmM3M2QxZTRiYTMyM2Q1ZDRkNzg3MGE3MGQwMzdlZjEyZjUzYjJjM2UwY2U5YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5542">
+      <c r="A5542" s="3" t="inlineStr">
+        <is>
+          <t>1139.psd</t>
+        </is>
+      </c>
+      <c r="B5542" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11489.psd</t>
+        </is>
+      </c>
+      <c r="C5542" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNQdGc5MkxlcjJCa1ZlVStzTzRUaEE9PSIsInZhbHVlIjoiaWhXQXNmYmVIa1hJRmVNSDVCUHVsUT09IiwibWFjIjoiNzJiY2YwZDY5ZWI1NzE4ZGFiOThmNTg1Nzg1NjM0YWQ0ODkxOTRkMzI1NzhmMjYwYjAyMTEyMjg4M2MwZjY0MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5543">
+      <c r="A5543" t="inlineStr">
+        <is>
+          <t>1138.psd</t>
+        </is>
+      </c>
+      <c r="B5543" t="inlineStr">
+        <is>
+          <t>tamilpsd-11490.psd</t>
+        </is>
+      </c>
+      <c r="C5543" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InUxRGdGMzM5RHNPNkVWb0xSbW5wUmc9PSIsInZhbHVlIjoiSWV6bnRxN2Q4U25XQWQxREI4dzRFQT09IiwibWFjIjoiZWRmZGVhNWEyYmJkNjk0MWE4ZDc2MTYyMjczYmQ4NGY5MWQwMzU5Njg3YzNjNjY4Mjg3ZDg1MmE2OTAyZWNmNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5544">
+      <c r="A5544" s="3" t="inlineStr">
+        <is>
+          <t>1137.psd</t>
+        </is>
+      </c>
+      <c r="B5544" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11491.psd</t>
+        </is>
+      </c>
+      <c r="C5544" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IisyTW96NnNhYzNGQWZZenlNMGI5b3c9PSIsInZhbHVlIjoiNVFMWlpoRmJyYUtOaTh1Zk1IWUExUT09IiwibWFjIjoiMmEwNTI1MWQ5Yzg0ZTAwMTkyNTQyY2JkNGMxNjBmNDIxZThiZjVjYTE3NTcwYjJkYmMwOTVhNmYzNGE2ZmY2NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5545">
+      <c r="A5545" t="inlineStr">
+        <is>
+          <t>1134.psd</t>
+        </is>
+      </c>
+      <c r="B5545" t="inlineStr">
+        <is>
+          <t>tamilpsd-11492.psd</t>
+        </is>
+      </c>
+      <c r="C5545" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJjc2I5YXRCWmNPeDR4SlRPVzNnbXc9PSIsInZhbHVlIjoiNzl3VXY2bU5XSHlzZW96bzBPdTFqUT09IiwibWFjIjoiYTIwMTZhNjk1YWFiYTE3Nzc5OWY1YmZhODExNzZmNzQ0MzRhOTlmY2FhNjI4MzE3ZDA1MDQyMjIxM2U3Y2RlYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5546">
+      <c r="A5546" s="3" t="inlineStr">
+        <is>
+          <t>1133.psd</t>
+        </is>
+      </c>
+      <c r="B5546" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11493.psd</t>
+        </is>
+      </c>
+      <c r="C5546" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndoRFJKQ3FaM3JPYWdkY0ExeTV3Z3c9PSIsInZhbHVlIjoiSmRQRmEyV1Z1aG5SSHNSZHNLSlRodz09IiwibWFjIjoiMDBlZGNhNjNmYmQyNjhhZTJjMDRlMTc5ZjE5Yjk2M2QyMTQ3OTE2ZjE0ODBlYTM5MDJhNjNjN2IxMDY1ZmI3ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5547">
+      <c r="A5547" t="inlineStr">
+        <is>
+          <t>1132.psd</t>
+        </is>
+      </c>
+      <c r="B5547" t="inlineStr">
+        <is>
+          <t>tamilpsd-11494.psd</t>
+        </is>
+      </c>
+      <c r="C5547" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjY3TVJKSEF3ZjNpVzNBSE10M1RML2c9PSIsInZhbHVlIjoidWpieFNxNWx5YXBRQUsvQ1A5N0J1Zz09IiwibWFjIjoiMWYwYjM3MWZlMzQ3Yzk2NmY3MDZkMjRiMjE5MTdjYzZiYzFiNmEyY2VlODVlNjVlYzNmNmVjZTdiNGY1ZGI1NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5548">
+      <c r="A5548" s="3" t="inlineStr">
+        <is>
+          <t>1131.psd</t>
+        </is>
+      </c>
+      <c r="B5548" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11495.psd</t>
+        </is>
+      </c>
+      <c r="C5548" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilg5ODdOY1k1SElSM3FxWnJMNGpLK1E9PSIsInZhbHVlIjoiZnZjZmY2M0dzVnp5b1lRZHQ4cXROUT09IiwibWFjIjoiZmRjNmZkZGY2MmMyY2QzMWYyNGU4YjhlZDMzZWFlNzJhMTYyMjY3MzVkYTc5YjJjNmQ4OWJjZjM1ZjE2ZTU2ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5549">
+      <c r="A5549" t="inlineStr">
+        <is>
+          <t>1130.psd</t>
+        </is>
+      </c>
+      <c r="B5549" t="inlineStr">
+        <is>
+          <t>tamilpsd-11496.psd</t>
+        </is>
+      </c>
+      <c r="C5549" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InM3elkxZVJyWHI4WTAwSk4zSGxvc0E9PSIsInZhbHVlIjoiK3BxOFV0UDlpSm8xV1RnNXhhWk82QT09IiwibWFjIjoiOGM3NjA1MDAzYTI4Y2ZhMWJmNmEzNzhhZmJjZTMzZDhmMjIwYmM0YWE3ZjllOGNmZTc2MjJjMDg0ZjVhZTc5MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5550">
+      <c r="A5550" s="3" t="inlineStr">
+        <is>
+          <t>1129.psd</t>
+        </is>
+      </c>
+      <c r="B5550" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11497.psd</t>
+        </is>
+      </c>
+      <c r="C5550" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNUMkE5UTFjK0t0dWZSRzJUTWhWQkE9PSIsInZhbHVlIjoiZTEyUEUzT1luUmJ5Sm83NlFyRmNBZz09IiwibWFjIjoiZmMyMzk1OWZjZmJlM2Q5N2MwYWRhMmU4ZjhkMmU5N2M1N2VmOGY2MWI5ZjA2YzYwYjk2ODM4ZmU4ZjVhMDBkYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5551">
+      <c r="A5551" t="inlineStr">
+        <is>
+          <t>1124.psd</t>
+        </is>
+      </c>
+      <c r="B5551" t="inlineStr">
+        <is>
+          <t>tamilpsd-11498.psd</t>
+        </is>
+      </c>
+      <c r="C5551" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InJLNmt0cmNWT00va2FUa1ZYMU8yaHc9PSIsInZhbHVlIjoicko5UURSYTl3RWVPbDJ5enJaelFkUT09IiwibWFjIjoiYjg3YzE0NGEwOGMwZjA0NzVmMWM0MTA5YWFkOTMyMWFjMjc4ZTMyZGIxOTg1MmU5YTcxYTQ1NDA2ODZjMzRmYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5552">
+      <c r="A5552" s="3" t="inlineStr">
+        <is>
+          <t>1123.psd</t>
+        </is>
+      </c>
+      <c r="B5552" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11499.psd</t>
+        </is>
+      </c>
+      <c r="C5552" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRLTHU4eGlNSDRJYzhnYmtHMzEzakE9PSIsInZhbHVlIjoiTmVvSkJoMWlBZmY4QWdHV0ZWekFiUT09IiwibWFjIjoiZTY1NzRiZjNlYTU0ZTcwOGRhOTg3M2M4MjQ3YjFjNDk2NmUzNjM3OTI2YTY4ZDVlYzZhNGYwNzhjOTc0M2QyMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5553">
+      <c r="A5553" t="inlineStr">
+        <is>
+          <t>1122.psd</t>
+        </is>
+      </c>
+      <c r="B5553" t="inlineStr">
+        <is>
+          <t>tamilpsd-11500.psd</t>
+        </is>
+      </c>
+      <c r="C5553" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktmM3lXK2psVjQ2TlorbGgvNUpBTUE9PSIsInZhbHVlIjoicTNqZ0lZTzMraGlkQmhwcnBQNjI4QT09IiwibWFjIjoiZTAzNDM1YWQxNzJiMTAzNDYzNzQ1YzA2NjkyZjJmMWNiY2U3ODE1MjRiYWFiNDNjMzgwMjFmZjdmYTJhY2Q2NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5554">
+      <c r="A5554" s="3" t="inlineStr">
+        <is>
+          <t>1121.psd</t>
+        </is>
+      </c>
+      <c r="B5554" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11501.psd</t>
+        </is>
+      </c>
+      <c r="C5554" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkdiU2NNQmRMeW1XZk92ZDBoMnVRc3c9PSIsInZhbHVlIjoiRUhtbm1JcnMyeURoc1pPaE8xczBXdz09IiwibWFjIjoiYTA1YzJlZTUwYmMyZmM4OTQyMDlhMzVmYWNhMjcyZjVhMTdlZGIzY2I1MTM4Yjg0MGQxYzJmNjViYjM1ODAwMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5555">
+      <c r="A5555" t="inlineStr">
+        <is>
+          <t>1120.psd</t>
+        </is>
+      </c>
+      <c r="B5555" t="inlineStr">
+        <is>
+          <t>tamilpsd-11502.psd</t>
+        </is>
+      </c>
+      <c r="C5555" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkhXS0RaZ2VHcVpOVjN5VzEzaEtvNnc9PSIsInZhbHVlIjoibjduaTR6Z1k2aHgvaFUzUHRBRWhydz09IiwibWFjIjoiZTg4OWM2MGIyZDRkOTE4YTZkYjk5NmY4MWU3NzBlMDc3NTkyMTZmZTBiODIzMWE5MDA1MjUwNGRjYjg1NThhNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5556">
+      <c r="A5556" s="3" t="inlineStr">
+        <is>
+          <t>1119.psd</t>
+        </is>
+      </c>
+      <c r="B5556" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11503.psd</t>
+        </is>
+      </c>
+      <c r="C5556" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklWOGE3MVpvQkFKYWJPcDYrbWtxWmc9PSIsInZhbHVlIjoiMVhRQk1PdXhyUnJ5V3FYeVNpZXpmUT09IiwibWFjIjoiNWQyYWE5ZWNhMTRiOWEzYTJjM2Q5MjY1NjBkMzliYzJiNzBjNTc4MTk1NThkMTNlMTk5ZTBhYmUxZThlYzhhMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5557">
+      <c r="A5557" t="inlineStr">
+        <is>
+          <t>1118.psd</t>
+        </is>
+      </c>
+      <c r="B5557" t="inlineStr">
+        <is>
+          <t>tamilpsd-11504.psd</t>
+        </is>
+      </c>
+      <c r="C5557" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkE0UVV2NHloWDhLQVhLeFhoTHZHOVE9PSIsInZhbHVlIjoiOERMeHBqZW1xRndXc0RVbG1UdHp4Zz09IiwibWFjIjoiZGMwOTY5MmIzNWZlOTc5NmVhZDJlMDNiNmE5OTk5NTM0ZDI0ZTZhN2NmZjgwNmZlZDEzYjA1NzE2YzU1NTE2OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5558">
+      <c r="A5558" s="3" t="inlineStr">
+        <is>
+          <t>1117.psd</t>
+        </is>
+      </c>
+      <c r="B5558" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11505.psd</t>
+        </is>
+      </c>
+      <c r="C5558" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjRPaThNd3lNRy9rWWU2UlFqYU12cXc9PSIsInZhbHVlIjoiRVo1eU05WmYxNXVlVXIxMXNyd1IrZz09IiwibWFjIjoiOGNlYWUxMzJmYzg0ZWQ3MTNlMWU4NmY3MTZjNzUyMmFmZDgxNWI5OTE4ZGJlOTMyYWQxNmQ4MDhjZTc1NjM3MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5559">
+      <c r="A5559" t="inlineStr">
+        <is>
+          <t>1116.psd</t>
+        </is>
+      </c>
+      <c r="B5559" t="inlineStr">
+        <is>
+          <t>tamilpsd-11506.psd</t>
+        </is>
+      </c>
+      <c r="C5559" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlEvMmRCVjFhdHNhMDJ6ODlVTHUyclE9PSIsInZhbHVlIjoiU2ZndFVraXZXRGhZQjhUTDVOeTd3QT09IiwibWFjIjoiYjcyNjk2YTAxZjU2N2I4NzBkMzhjNjRkNWM4NjAxNDk4YzNjNTk2YTRmNDQzNjU4MjU2MDNhNzE2NzhhMmZmNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5560">
+      <c r="A5560" s="3" t="inlineStr">
+        <is>
+          <t>1114.psd</t>
+        </is>
+      </c>
+      <c r="B5560" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11507.psd</t>
+        </is>
+      </c>
+      <c r="C5560" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlYyTDNURVJKQjFjbTh2bTZ1U1UxV1E9PSIsInZhbHVlIjoibG9XcGVkOG41dHB1ZDgrT2dhVFNPZz09IiwibWFjIjoiN2M1OTI4MTE0N2MxNmE4NDZhN2NkYmE4OTU2OWZkZGRlZTBlOGU1ZWIxMmJmMDcxYWU0MTZkZWVkOTU0ODBhOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5561">
+      <c r="A5561" t="inlineStr">
+        <is>
+          <t>1113.psd</t>
+        </is>
+      </c>
+      <c r="B5561" t="inlineStr">
+        <is>
+          <t>tamilpsd-11508.psd</t>
+        </is>
+      </c>
+      <c r="C5561" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpSZ1N4ZWFTeHBaRkNOUUZ2SHVNdEE9PSIsInZhbHVlIjoiYm9lNkhmbncxbEFROGtwYUNra0l0Zz09IiwibWFjIjoiZmNiMzE4MWY4MDA2ZDA4NmEzMmE5ZjJhZmQ5MzgxMDgyYTMyYTM5YzQ4NDY3ZTJmMjM3NjZhNzdhMWU1NGFkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5562">
+      <c r="A5562" s="3" t="inlineStr">
+        <is>
+          <t>1112.psd</t>
+        </is>
+      </c>
+      <c r="B5562" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11509.psd</t>
+        </is>
+      </c>
+      <c r="C5562" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjRDSlpLVjQxZ3JZM0dmNENrWG5EcEE9PSIsInZhbHVlIjoiMTdJNUVKcUc4N05lckNDY1h3ck0yQT09IiwibWFjIjoiYjhlZWI0ODE0ZjYyOTkzNTAyNDczNDI2ZmUxYWNjNDYxNTMwZWIwZGQyNTkzZjkzY2Y4MmZkMjgxZTQ1MTdlNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5563">
+      <c r="A5563" t="inlineStr">
+        <is>
+          <t>1111.psd</t>
+        </is>
+      </c>
+      <c r="B5563" t="inlineStr">
+        <is>
+          <t>tamilpsd-11510.psd</t>
+        </is>
+      </c>
+      <c r="C5563" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImsweXpGWjkyK09yaklmYk80TmMwcXc9PSIsInZhbHVlIjoiWUhtbUNqODVaSWlUUi8vSU1Nb0ZPZz09IiwibWFjIjoiZjlhMWEwNWNiMTAyMTM5MzdjMzIwNDVhZTdhZTY0NjczNDgzNDVlMWI1MjljODM2N2E3NmQwZmU3MDY5ZmI4NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5564">
+      <c r="A5564" s="3" t="inlineStr">
+        <is>
+          <t>1110.psd</t>
+        </is>
+      </c>
+      <c r="B5564" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11511.psd</t>
+        </is>
+      </c>
+      <c r="C5564" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndDMkVDQmdETFVYTlpVKzBsdSt2L0E9PSIsInZhbHVlIjoicXRQTzEwYlpUeld2aW5EVnVWK3VJZz09IiwibWFjIjoiYWQ1ODM4M2RmYmI5YjRiNGJhMDg0ODMwNjAxMmY1NjVmZDEyNjhjMDY5NzhlYjFkOTcwZGYxMTk4Y2Y1NTRjYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5565">
+      <c r="A5565" t="inlineStr">
+        <is>
+          <t>1109.psd</t>
+        </is>
+      </c>
+      <c r="B5565" t="inlineStr">
+        <is>
+          <t>tamilpsd-11512.psd</t>
+        </is>
+      </c>
+      <c r="C5565" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImVhTHJkc255ZDlMVVdzcStWWXpnWXc9PSIsInZhbHVlIjoiN3BRZkkveERob3o5bCt1NlBYYU1udz09IiwibWFjIjoiMGI4NmQxOTY1OTg5MmNlNGJmYzI3NTZkYjg4N2FkOWFjYWQ5ZWI3YjM2ZDdiMjJjM2MwNTQwNmZmN2EzNTM1ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5566">
+      <c r="A5566" s="3" t="inlineStr">
+        <is>
+          <t>1106.psd</t>
+        </is>
+      </c>
+      <c r="B5566" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11513.psd</t>
+        </is>
+      </c>
+      <c r="C5566" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImI4RzFSWk5pV0t0TjVsRDlRNUNiRWc9PSIsInZhbHVlIjoiUlFXN2syZTFXcU5UNWNBQ1MyT1pJdz09IiwibWFjIjoiYjhhZTQwYWFiOGJjY2QwNjQxNmI5Zjg2NzNiMmMxMjE3ODM2MmU4N2E2OWMwZGMxNTU5ZjI5NjE4MGMyYzY3MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5567">
+      <c r="A5567" t="inlineStr">
+        <is>
+          <t>1105.psd</t>
+        </is>
+      </c>
+      <c r="B5567" t="inlineStr">
+        <is>
+          <t>tamilpsd-11514.psd</t>
+        </is>
+      </c>
+      <c r="C5567" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktlSVc5dDFOWGV5Vm9DSm9wMWlITlE9PSIsInZhbHVlIjoiczJKcFdJOXdjUC9VWUkvbGh3aHU3Zz09IiwibWFjIjoiOWYxODBiMzU0YWJlM2Y0M2M2YjM0MmMwZjZhMDBjMmFhNGIxOGI5NDdjOWQ5NjkyNzMyN2E0ODhiNTcyMWVkMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5568">
+      <c r="A5568" s="3" t="inlineStr">
+        <is>
+          <t>1104.psd</t>
+        </is>
+      </c>
+      <c r="B5568" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11515.psd</t>
+        </is>
+      </c>
+      <c r="C5568" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImovOVp6UGFJQ1I5QldHNG5SbCtHYlE9PSIsInZhbHVlIjoiMGF1YUZGeW5WY2JJNEhjNW41T2MxUT09IiwibWFjIjoiOTZjZTBjYjJkNmJiNDkzMGYyZWYxMDEwZWYwNzVlMjQ1MWRkZWE5NmZkYzlhMzAxOTJlMTE2ZDcyN2RlOGZjOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5569">
+      <c r="A5569" t="inlineStr">
+        <is>
+          <t>1103.psd</t>
+        </is>
+      </c>
+      <c r="B5569" t="inlineStr">
+        <is>
+          <t>tamilpsd-11516.psd</t>
+        </is>
+      </c>
+      <c r="C5569" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkVHSVZtK1ViL1JuK3JjMno4aExTSkE9PSIsInZhbHVlIjoieHh0UkdZc1FJMm05aXQ5QWVCVmJzZz09IiwibWFjIjoiZWZlYWFlNWNhZDZjMDI4NzgxMjQyZWIyOGU3NDE0NzNmN2MwMGQxYzdhNTYxN2QyY2QwZTQ4M2Q5OGEzM2E0MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5570">
+      <c r="A5570" s="3" t="inlineStr">
+        <is>
+          <t>1102.psd</t>
+        </is>
+      </c>
+      <c r="B5570" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11517.psd</t>
+        </is>
+      </c>
+      <c r="C5570" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJJS3N5VGtoVVRSYVI0WXhiY3grclE9PSIsInZhbHVlIjoiUDhxMGdxSHlrUDlaWjhxNlV4dmExQT09IiwibWFjIjoiOGU4MTkxNzRiN2IxNjEyNTA2NTY1MjZmMGExNDdkMjNjMzg1OTBkZTE0MjIzMGVhZTQ3YjFiNWVhMjhkZThiOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5571">
+      <c r="A5571" t="inlineStr">
+        <is>
+          <t>1101.psd</t>
+        </is>
+      </c>
+      <c r="B5571" t="inlineStr">
+        <is>
+          <t>tamilpsd-11518.psd</t>
+        </is>
+      </c>
+      <c r="C5571" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkYxNWZieWxqTHNEWFEvbmtjaXdiQUE9PSIsInZhbHVlIjoiR1BydlJNelYwbFhJdFpXZ2s3emdvQT09IiwibWFjIjoiOGZkOWQzMjdmMWJmMGEyNmE3ZDI0ZWQ4OWUxNWMxZTVlMzFkODE1ZTY0MTM3YmZlY2Y5OTliOGMxNWUzYWIxMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5572">
+      <c r="A5572" s="3" t="inlineStr">
+        <is>
+          <t>1100.psd</t>
+        </is>
+      </c>
+      <c r="B5572" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11519.psd</t>
+        </is>
+      </c>
+      <c r="C5572" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFiUDgrdGtvd1NJWTRxb29POFh1b1E9PSIsInZhbHVlIjoiOVRQeFB5U2ExTjNrVGk4aU1ydS9ZUT09IiwibWFjIjoiZmY5YTAxYTJhN2UxMTA2YmNlMjNiYjkwZDgwMmIzY2M1NDlhY2RhYTM1NDIyNzUzYTc2ZjFmOTkxZDk4M2NmMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5573">
+      <c r="A5573" t="inlineStr">
+        <is>
+          <t>1073.psd</t>
+        </is>
+      </c>
+      <c r="B5573" t="inlineStr">
+        <is>
+          <t>tamilpsd-11520.psd</t>
+        </is>
+      </c>
+      <c r="C5573" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFaWEhUVXE3WHFTK3kwS1N5S2krY3c9PSIsInZhbHVlIjoiMHMxdW9zVGdpSTV0VU12Q0M0VXBnUT09IiwibWFjIjoiYTQzMWJmYzUyNzEyOTAxZmQyNGJjNmU0ZmMwOTU4NThmMWFjNjFlY2I3MTRmYjFjMGI4OGNhZTFmNmRkMWFiZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5574">
+      <c r="A5574" s="3" t="inlineStr">
+        <is>
+          <t>1072.psd</t>
+        </is>
+      </c>
+      <c r="B5574" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11521.psd</t>
+        </is>
+      </c>
+      <c r="C5574" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxSMFNCcjhxZ2Z4cjVnYWVpaHdPc3c9PSIsInZhbHVlIjoiSUhlaCtKQ2NzNTBseGlXRTU4Q3ZyUT09IiwibWFjIjoiNDE2YzE3NzZhYTFmM2UxYTYwNDFjMWY5MTBmYjJmMGZhMTk5MzBlY2FlNGMzYjdjM2NiYzZmNmQ1MjNlMzMwOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5575">
+      <c r="A5575" t="inlineStr">
+        <is>
+          <t>1070.psd</t>
+        </is>
+      </c>
+      <c r="B5575" t="inlineStr">
+        <is>
+          <t>tamilpsd-11522.psd</t>
+        </is>
+      </c>
+      <c r="C5575" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxoRHJwL1dzZjZIQ0pJcFFmbHdnc0E9PSIsInZhbHVlIjoiUUc4WkZQeU13Q0REZUVuMVJCVkZKUT09IiwibWFjIjoiYmZmOGQyYWUwM2I5YjcwZDMzNGJlMDBjY2M4OTdhMzI3ZjEyNjI1YjgwMmFmMWZlZTgyODUwZGIyMDhhNzY2OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5576">
+      <c r="A5576" s="3" t="inlineStr">
+        <is>
+          <t>1069.psd</t>
+        </is>
+      </c>
+      <c r="B5576" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11523.psd</t>
+        </is>
+      </c>
+      <c r="C5576" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjNRYjJIb1grQkZLYWFRVld0a0Y0UFE9PSIsInZhbHVlIjoiWWFDaXZxS0Z4ckI2Z3Q5VDA0blZoUT09IiwibWFjIjoiNTU3NDAzMTExZWM5YmU1YjE0Y2NhMDg4NzZhODljYTM4ZWFkNDViZDBjOGRlY2U1YWU4ZjkwYzM2ZWExZDBkZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5577">
+      <c r="A5577" t="inlineStr">
+        <is>
+          <t>1068.psd</t>
+        </is>
+      </c>
+      <c r="B5577" t="inlineStr">
+        <is>
+          <t>tamilpsd-11524.psd</t>
+        </is>
+      </c>
+      <c r="C5577" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijg4aWg2TG9mdFFEMEgwaGNPbFhYdEE9PSIsInZhbHVlIjoiSWRsZzdNNVkzZWE3NG5SK1pTL1pYdz09IiwibWFjIjoiZTAyZDlhODFhZWZjZjUyNDU3ODdhZjIwMTgyNzFjOWQ1NjMzNDYzMmNiY2M3NmZkMzFhMTQzZjU5MGJiYTA3MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5578">
+      <c r="A5578" s="3" t="inlineStr">
+        <is>
+          <t>1066.psd</t>
+        </is>
+      </c>
+      <c r="B5578" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11525.psd</t>
+        </is>
+      </c>
+      <c r="C5578" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkN6dDAvb0FzWmFibExqbDBsN0IxSnc9PSIsInZhbHVlIjoiQ2NzRnhHbytxYjcvUHZ5NDFhaTVOdz09IiwibWFjIjoiMjMyNjBhMTc3OWY5NjY4NGJmZTZhNTk1NzFiNmNhZDE3ZTNjYWQ5YWZkNDhjMTVjZTNiOTkyMTY0ODA5YWE0YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5579">
+      <c r="A5579" t="inlineStr">
+        <is>
+          <t>1064.psd</t>
+        </is>
+      </c>
+      <c r="B5579" t="inlineStr">
+        <is>
+          <t>tamilpsd-11526.psd</t>
+        </is>
+      </c>
+      <c r="C5579" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJvS1FkdjdISU5KaFlCN1htNVhreWc9PSIsInZhbHVlIjoibzFJNjV6YlRkeVFpWWFTZWRUSzZhdz09IiwibWFjIjoiZmU1MDNjMjdkZTYyMWQ2ZTMyYTIyOWRmMjg5ZjQ4MWQ1YmE5M2I2MGViZGE0OTFiZDE0ZmE0YmUzNjllNjExNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5580">
+      <c r="A5580" s="3" t="inlineStr">
+        <is>
+          <t>1063.psd</t>
+        </is>
+      </c>
+      <c r="B5580" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11527.psd</t>
+        </is>
+      </c>
+      <c r="C5580" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxKQ2NPMGtqQkNHVE5sN3N1Q25rWGc9PSIsInZhbHVlIjoialpCbUtIM2tiMGhMVVpRNWhEbWh5Zz09IiwibWFjIjoiZTUyMDYyZTgwOTMzYTUxMmMzYjg1ZDBhOWQ1YTJjMzkyMGZhZTU2YTg4ZjNlYTQ0MzgzNjlkMmExMjNjNDU5OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5581">
+      <c r="A5581" t="inlineStr">
+        <is>
+          <t>1061.psd</t>
+        </is>
+      </c>
+      <c r="B5581" t="inlineStr">
+        <is>
+          <t>tamilpsd-11528.psd</t>
+        </is>
+      </c>
+      <c r="C5581" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZLMTZITXE5NGdFa3pXT1ZCWnFYb3c9PSIsInZhbHVlIjoiamFNWnhzb3p0U05HY0VtTEhhZGdwZz09IiwibWFjIjoiYTFkOWQ3OWY2MGUxOTIyMjYyYzZjNjNkN2Y4YTY0ZDA2OWFkOTgwYTBlNzlmNTYyOTdjMWI2MjI4NzkyNjBkYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5582">
+      <c r="A5582" s="3" t="inlineStr">
+        <is>
+          <t>1060.psd</t>
+        </is>
+      </c>
+      <c r="B5582" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11529.psd</t>
+        </is>
+      </c>
+      <c r="C5582" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImUxTHR3L0pKQlE2STdzWW1FY0NEQ1E9PSIsInZhbHVlIjoiNkZMa3IyRHFZZWlmMFFlaWV4MUxydz09IiwibWFjIjoiMDIyY2ZlMWEyY2UwZWRiNDhkMTc4ODNmMTk1ZTQxYzQ1YzI3MGMzYmY4OGU3MGJmOTg0NDRiMmM5ZTA3MWQzNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5583">
+      <c r="A5583" t="inlineStr">
+        <is>
+          <t>1059.psd</t>
+        </is>
+      </c>
+      <c r="B5583" t="inlineStr">
+        <is>
+          <t>tamilpsd-11530.psd</t>
+        </is>
+      </c>
+      <c r="C5583" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iks2bE1yRmdSZi9hdE0xdjhkOTlISmc9PSIsInZhbHVlIjoidDdXWmFQMXprZFZESjZ0MlorSmFPQT09IiwibWFjIjoiOTg0MWI1NzQxOGJiZGNmNDE3MGMxYjAzM2E0ZmJmODY1OGM5YTI5YzM0Yjc0OWI5MGMxMmU2ZTI0NmQ5ZjlkYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5584">
+      <c r="A5584" s="3" t="inlineStr">
+        <is>
+          <t>1185.psd</t>
+        </is>
+      </c>
+      <c r="B5584" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11531.psd</t>
+        </is>
+      </c>
+      <c r="C5584" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlzcHptL3RuK2owVjVucytQZy91R0E9PSIsInZhbHVlIjoiMk4rYmRESFJYakFrdVBmLzhQemQrUT09IiwibWFjIjoiMjg5Mjg5YWI0ODlkM2ZhZGM1OGU2ZTNjZmI4ZWU0ZGFkMGJiZjkyNjFlMjM2ZWY0ZDFjMzUyYmJhNzBmZTUwZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5585">
+      <c r="A5585" t="inlineStr">
+        <is>
+          <t>1057.psd</t>
+        </is>
+      </c>
+      <c r="B5585" t="inlineStr">
+        <is>
+          <t>tamilpsd-11532.psd</t>
+        </is>
+      </c>
+      <c r="C5585" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImEwRWZhS3o3Wklnc1ZBVzZsRUNIVUE9PSIsInZhbHVlIjoicXhsQVpVTGRmUEcvWGxQZ0dDMi9Vdz09IiwibWFjIjoiZmVjYzU0ZDYzY2Q5M2EwNTE5OGRhNDUyOWE5NTM1NDJhZjAwY2JlMzA3YmJiZjA2NDJmNGEwNmQ3YmQ4MmQzZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5586">
+      <c r="A5586" s="3" t="inlineStr">
+        <is>
+          <t>1056.psd</t>
+        </is>
+      </c>
+      <c r="B5586" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11533.psd</t>
+        </is>
+      </c>
+      <c r="C5586" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVSTXhBZUZqNU9PYXpoYk9pZGgwdFE9PSIsInZhbHVlIjoiR21QZWxrN0ZyMXhiZC9CUW9oV1dGUT09IiwibWFjIjoiNWE5MGMyMDkzNzc5N2EwOTQ3ZmQ4NTlhMTA0NzhhZTkyODQwNTQ4YTQ4NDYyNDNkNDI5ZWM2MWQ4YmRkMjU4YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5587">
+      <c r="A5587" t="inlineStr">
+        <is>
+          <t>1055.psd</t>
+        </is>
+      </c>
+      <c r="B5587" t="inlineStr">
+        <is>
+          <t>tamilpsd-11534.psd</t>
+        </is>
+      </c>
+      <c r="C5587" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRvd2ROZlFub2hCV3JDSHNjeTdCcVE9PSIsInZhbHVlIjoiODQySDFHQ2kvVzBTdlpHSXRaZmpoZz09IiwibWFjIjoiOTYyYzJjYmU0OTQwYjdjOWM2ZGQ1NTAwMWNjYzlhYjEwNmE0MzRkNzNlYTg2Y2ZiZDQzZjZkNWUxYzRjNGYwZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5588">
+      <c r="A5588" s="3" t="inlineStr">
+        <is>
+          <t>1054.psd</t>
+        </is>
+      </c>
+      <c r="B5588" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11535.psd</t>
+        </is>
+      </c>
+      <c r="C5588" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZDY3hJMmNaT1Y3RFNOSjR2elZGSlE9PSIsInZhbHVlIjoiMmxxVGVHSHNzSE5sTWFnUExzeWdSdz09IiwibWFjIjoiZGI1ZDg1NGZjMDA5NWRhNTQyMDAwMzJiNTM4YjM2ZDEzOTQxM2VjYmU1NjY5N2EyZDUwYjliYjk1OTA1MmE3YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5589">
+      <c r="A5589" t="inlineStr">
+        <is>
+          <t>1053.psd</t>
+        </is>
+      </c>
+      <c r="B5589" t="inlineStr">
+        <is>
+          <t>tamilpsd-11536.psd</t>
+        </is>
+      </c>
+      <c r="C5589" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJsYUFiUVMzWWQvK1RQSDhaMHJtT0E9PSIsInZhbHVlIjoieDdqaC9TSWZGZHhTQno2Qmh2Z1FQZz09IiwibWFjIjoiNjIyZGQ4YmU3NThiNDYzMmJkY2VhZjIyYzkzNWVhMmMzZjFlY2Y0MzBjZDQ5ZjljYWM1OTYxNjg1NmUyN2IyMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5590">
+      <c r="A5590" s="3" t="inlineStr">
+        <is>
+          <t>1052.psd</t>
+        </is>
+      </c>
+      <c r="B5590" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11537.psd</t>
+        </is>
+      </c>
+      <c r="C5590" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkcrVXpHdVFhN2xuSmZKcWxYdEI0eUE9PSIsInZhbHVlIjoiNVdVS1lrK2doM2Ztd05VVGQ4a09VQT09IiwibWFjIjoiMjk0YzVlNzM1OGQzMjA0ZWE5ZjczNjYwZWQ1OWMzMzgwNTM3ZjczMTgzOTU2NjY0MTM5NjFhYTZkMzRmNmE0NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5591">
+      <c r="A5591" t="inlineStr">
+        <is>
+          <t>1051.psd</t>
+        </is>
+      </c>
+      <c r="B5591" t="inlineStr">
+        <is>
+          <t>tamilpsd-11538.psd</t>
+        </is>
+      </c>
+      <c r="C5591" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9TNE5hbHJ3YkUwMXlQWHpJUFgvWEE9PSIsInZhbHVlIjoiTm5Kcjh1bmRPbThIS2xxTklpNzgxdz09IiwibWFjIjoiYTNmYzA5ZWY4NTYwOWU3NWI5YTkzZWM0MzAyYzYyODRjNDc3OTJkMWRiMTdhMGEwMjYzYTkxNGYzZTcyMDg3MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5592">
+      <c r="A5592" s="3" t="inlineStr">
+        <is>
+          <t>1050.psd</t>
+        </is>
+      </c>
+      <c r="B5592" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11539.psd</t>
+        </is>
+      </c>
+      <c r="C5592" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJLRVhvQkdIWURZUlNJYzNrQVJFNFE9PSIsInZhbHVlIjoiL09pbHRqTkF6SGR6SWdjbk5CSGJnZz09IiwibWFjIjoiMWQ5YmZiZTg1Njc1NGIwMWZkMTRlYWE3ZmJkZTZkNTQ5NDUyMGYzZTYyYjdjNWI2NGJkZDdkZjY3N2QyZWFmNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5593">
+      <c r="A5593" t="inlineStr">
+        <is>
+          <t>1049.psd</t>
+        </is>
+      </c>
+      <c r="B5593" t="inlineStr">
+        <is>
+          <t>tamilpsd-11540.psd</t>
+        </is>
+      </c>
+      <c r="C5593" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJPZldoTFFZdDY0UHNBMTAyenZoaFE9PSIsInZhbHVlIjoiTlJZUDl5WmlyenErdjBjL0JXZ0RQUT09IiwibWFjIjoiZTkzOWIxMTU4MzNhMTMwYjY5YmY0NmM4N2M3ZTM2YzM4ZmIzYTFlMWY3YWE2ZWJmNDIyMDU0OTVjY2QyMTcxNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5594">
+      <c r="A5594" s="3" t="inlineStr">
+        <is>
+          <t>1048.psd</t>
+        </is>
+      </c>
+      <c r="B5594" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11541.psd</t>
+        </is>
+      </c>
+      <c r="C5594" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFQVkt4eWplWWhES0QzTUZReDRzaGc9PSIsInZhbHVlIjoiVmREVDBnd0liRVpxMDFhVXgrc2R2UT09IiwibWFjIjoiNmIyYWMwMzRmNGUwNDNkOWE3ZGNiZDA1ZGRhZDQ0ZDlkOGE4YjBmNDA4MDdhMGVjNTcyY2I0OWQ5YmQzZDAzOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5595">
+      <c r="A5595" t="inlineStr">
+        <is>
+          <t>1047.psd</t>
+        </is>
+      </c>
+      <c r="B5595" t="inlineStr">
+        <is>
+          <t>tamilpsd-11542.psd</t>
+        </is>
+      </c>
+      <c r="C5595" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InR0VFMxTlVscmVKK093NHJ4dDJFL2c9PSIsInZhbHVlIjoiL0V2MlU0YUkrUDJwMjNWNnJMbFJ6Zz09IiwibWFjIjoiOGVhMTU2YmQxMGQ2ZTBlYzY0ZDljYzEwMjVkNDMxNmYxOGRmODU3NzBjYzJiNTBhZjU4MGZhMDNiZWYzODMwNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5596">
+      <c r="A5596" s="3" t="inlineStr">
+        <is>
+          <t>1046.psd</t>
+        </is>
+      </c>
+      <c r="B5596" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11543.psd</t>
+        </is>
+      </c>
+      <c r="C5596" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imk3VmkwNkM1VDJwUDA2MHJjWVAxK0E9PSIsInZhbHVlIjoiZUtXOHltM2JQcjlEZWF0NVdjVW14UT09IiwibWFjIjoiMGIwN2U2N2NmMzEzNzU3YThkMmRjYjBiOTA0ZDY4MmE4MTQwODk2MjU2NTEwNDcwYmUzNDI5Y2VhZDcxNGMxYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5597">
+      <c r="A5597" t="inlineStr">
+        <is>
+          <t>1045.psd</t>
+        </is>
+      </c>
+      <c r="B5597" t="inlineStr">
+        <is>
+          <t>tamilpsd-11544.psd</t>
+        </is>
+      </c>
+      <c r="C5597" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdIMGdnK0YrMlduZlNNYm43bzFnQlE9PSIsInZhbHVlIjoicWFWbFJ4aDNtTHZsRkVaWHhob09rdz09IiwibWFjIjoiMDQ3YWYwYjgwMmJiYzYyYTA1ZjgyMjljNjEwNzg2OWMxZGY5ZThiYTA5NjFmNTI5OGE1NjAxYTA1YjVlMTgzYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5598">
+      <c r="A5598" s="3" t="inlineStr">
+        <is>
+          <t>1044.psd</t>
+        </is>
+      </c>
+      <c r="B5598" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11545.psd</t>
+        </is>
+      </c>
+      <c r="C5598" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InEwQkdsU2JQWm44RFI4RVpaZHZ4b0E9PSIsInZhbHVlIjoiajNrNWl6ZHp5THRYL1FKUDdIa0ZJQT09IiwibWFjIjoiNWE5YzM3YmU3NzBhNzBlOWFjZDBlNzcwZWZkYmFlNjA0MmZlNmVhYTQxNDU2N2MzYmY5MWVlYWUyMWQxNGI5MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5599">
+      <c r="A5599" t="inlineStr">
+        <is>
+          <t>1043.psd</t>
+        </is>
+      </c>
+      <c r="B5599" t="inlineStr">
+        <is>
+          <t>tamilpsd-11546.psd</t>
+        </is>
+      </c>
+      <c r="C5599" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imo1cWEzRDFxNFMzMXNtR1FkY2VHNlE9PSIsInZhbHVlIjoicnhGUnozZWszQVVxNjd5Q0ZNcnVPdz09IiwibWFjIjoiMzUzY2IyYWM2MTE5MjJjNzlmZTU2ZDQ4ZmVkNDhmMTMxNDQ5ODIyNWNkZjI5N2UzM2FmZjc2NmJmYWRiMzNmYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5600">
+      <c r="A5600" s="3" t="inlineStr">
+        <is>
+          <t>1042.psd</t>
+        </is>
+      </c>
+      <c r="B5600" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11547.psd</t>
+        </is>
+      </c>
+      <c r="C5600" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImE1c2g3SEdQUzFNM0RUK1hzNDVTZGc9PSIsInZhbHVlIjoiV3daUWl0NU5maFNoWUxmK1dGc1VsZz09IiwibWFjIjoiZWNkNmU5MjEzNDU5MGZjYjg2MjcwZDk4YWRjZjEwMGFiZjY3MWUxMzJlNzBkMDBkMjMyNjQ5NDU3ZGZlNmRlNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5601">
+      <c r="A5601" t="inlineStr">
+        <is>
+          <t>1041.psd</t>
+        </is>
+      </c>
+      <c r="B5601" t="inlineStr">
+        <is>
+          <t>tamilpsd-11548.psd</t>
+        </is>
+      </c>
+      <c r="C5601" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRGcTBrcDFJY1pnMFlMUzN2Yis0UkE9PSIsInZhbHVlIjoiNVNLQnRnTUovdVptMmVNQ2U1ZTd5Zz09IiwibWFjIjoiMzhmMGIyYjcwMDBlMDAyOTFiYTg2NmFmZjM5ODM0NGE1MjRlNDRjMDQ4YTQxZjQ0NWM3OTRjN2MzMDA5MDNmOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5602">
+      <c r="A5602" s="3" t="inlineStr">
+        <is>
+          <t>1040.psd</t>
+        </is>
+      </c>
+      <c r="B5602" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11549.psd</t>
+        </is>
+      </c>
+      <c r="C5602" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRjVlVYNUxpRWZ2eHhnd2RXZ0R4MlE9PSIsInZhbHVlIjoiWXhhUGlCSWdqL1VSY2hsM3NqY2d0QT09IiwibWFjIjoiNDBhNTU5NjNjM2E0YTYzZDIzMWE0N2Q3YmEwNWIwYzBlOWVkMTQ2ZTdkZGRjOTNkZWY4YWRhN2I3NGMzOTBmOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5603">
+      <c r="A5603" t="inlineStr">
+        <is>
+          <t>1039.psd</t>
+        </is>
+      </c>
+      <c r="B5603" t="inlineStr">
+        <is>
+          <t>tamilpsd-11550.psd</t>
+        </is>
+      </c>
+      <c r="C5603" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZlUUgyR0RoMFFGeGhJczFlVldzM1E9PSIsInZhbHVlIjoiVWV6blloUVB3ZjJxWE90NkE3ZE1kQT09IiwibWFjIjoiMzkxNzNjNjVkZDg3OTNhN2JiNWRiNmI5ZjExYjUwNjU1MWRkM2JmN2Q1ODJmZDI0YmE4MzU0MmQwZjc4YjA4ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5604">
+      <c r="A5604" s="3" t="inlineStr">
+        <is>
+          <t>1038.psd</t>
+        </is>
+      </c>
+      <c r="B5604" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11551.psd</t>
+        </is>
+      </c>
+      <c r="C5604" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJJVG8ybHV5U21DTG05SUdDeXhKTXc9PSIsInZhbHVlIjoiaDdUZXJwQ3B4MnJ0MWtVYSt5VVZUdz09IiwibWFjIjoiYWU4YWUzOTI2ZDI1MzVmMjBhNTlkNzk5YzY3ZDQ1ODIzOTFmMDA5MmU1Njg2MDMyMDFhNjYzYWU5Zjk4OTUwZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5605">
+      <c r="A5605" t="inlineStr">
+        <is>
+          <t>1037.psd</t>
+        </is>
+      </c>
+      <c r="B5605" t="inlineStr">
+        <is>
+          <t>tamilpsd-11552.psd</t>
+        </is>
+      </c>
+      <c r="C5605" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxRaEIveVloWWpCNE1EVGFDZ0RLS0E9PSIsInZhbHVlIjoiTHJsT2s5UGo2VFZsaExScitGakdRUT09IiwibWFjIjoiMWQzMDc5OTU2OGU5ZjcyNjEyNWUwNGVlMjgxNDg1ZmYwZjExYTY1YzZjNzQwYWQ2MGUyM2VkNjE4ODk2ZDBhNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5606">
+      <c r="A5606" s="3" t="inlineStr">
+        <is>
+          <t>1036.psd</t>
+        </is>
+      </c>
+      <c r="B5606" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11553.psd</t>
+        </is>
+      </c>
+      <c r="C5606" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlR2dmFaUnkrRDFhKzVOYnRmVGJROGc9PSIsInZhbHVlIjoieWRKSjM5QmVUSGg0enkvVjFtTVJZQT09IiwibWFjIjoiY2NkZjc1NzU3M2JjZDQ4NGNlZDEyNDk4OGI3MTU2NzUxMGE4YjJmMTRmOTQ4MGRlYWY5N2MwNDU5NmRjODQ1MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5607">
+      <c r="A5607" t="inlineStr">
+        <is>
+          <t>1035.psd</t>
+        </is>
+      </c>
+      <c r="B5607" t="inlineStr">
+        <is>
+          <t>tamilpsd-11554.psd</t>
+        </is>
+      </c>
+      <c r="C5607" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im00OUlBc1NLY3NaSGszL3orbjV5aXc9PSIsInZhbHVlIjoiUUpPN0N3QUs2RmxadzhlVnoycXlodz09IiwibWFjIjoiYmFkNDRkZThhNTUxOTYyYTFjNWIxZThmOGU5NGFkODlmNTdkNDAzMDI1YmIwN2U2MmFmNDk4ZjFiMDkyMTZkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5608">
+      <c r="A5608" s="3" t="inlineStr">
+        <is>
+          <t>1034.psd</t>
+        </is>
+      </c>
+      <c r="B5608" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11555.psd</t>
+        </is>
+      </c>
+      <c r="C5608" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikp6bjZ3MmJhMHhTc0IvcWhlS2p5NGc9PSIsInZhbHVlIjoielY2TlQ3V2I5dzlnMTU1b0VmcHFIUT09IiwibWFjIjoiZGZlYTNhMmQzODg1YmM5NGViZjVhY2E2MzgwNzE4MzY1ZGFjZmIyYzQzZWM5MDQ0OGE4YmI0YjI0M2M2Y2E5NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5609">
+      <c r="A5609" t="inlineStr">
+        <is>
+          <t>1033.psd</t>
+        </is>
+      </c>
+      <c r="B5609" t="inlineStr">
+        <is>
+          <t>tamilpsd-11556.psd</t>
+        </is>
+      </c>
+      <c r="C5609" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjdpMUprOGNPNzBkUWk4Ull2ZHNHWGc9PSIsInZhbHVlIjoiVE9meW5NK2xHMDIrZ1FkT0Y4TVk0QT09IiwibWFjIjoiMDA1NjgzNGZmYmE2YTQ2YjM3ZmQxZGRiMGQ1OWM2MTMzY2Y1MzQ5Mzc1NDg0ZDllNTQ4ZDViYjdiM2E3ZjIzMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5610">
+      <c r="A5610" s="3" t="inlineStr">
+        <is>
+          <t>1032.psd</t>
+        </is>
+      </c>
+      <c r="B5610" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11557.psd</t>
+        </is>
+      </c>
+      <c r="C5610" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndNazhneEdvczVqelJ0Wm5FQVRMSXc9PSIsInZhbHVlIjoicTVNUXZRNlQvdGpjSjlNOW9kSldxUT09IiwibWFjIjoiMDJiYWI3ZDhlNWFmMjcyZGRkYjU5NDM3MDkxMmQ1ZjEwYzk4YjZhZmIzZWFlMDYwYWYzY2JiMDZmMGI5NGQ3NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5611">
+      <c r="A5611" t="inlineStr">
+        <is>
+          <t>1031.psd</t>
+        </is>
+      </c>
+      <c r="B5611" t="inlineStr">
+        <is>
+          <t>tamilpsd-11558.psd</t>
+        </is>
+      </c>
+      <c r="C5611" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlQZjU0cnkzUU5HOXk1KzRyWmxWaHc9PSIsInZhbHVlIjoieCt3ZVNaVUE5ejJobVlLTWROa2NWZz09IiwibWFjIjoiYjE2ODdmZTM2NDU0Y2Y2YmUyMTQ5MmVhNGYyMzAxZWE2NGQwMDU4ODZkNGM1ZTc2ZTNhN2Q5MjE3MzYzYzhiZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5612">
+      <c r="A5612" s="3" t="inlineStr">
+        <is>
+          <t>1030.psd</t>
+        </is>
+      </c>
+      <c r="B5612" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11559.psd</t>
+        </is>
+      </c>
+      <c r="C5612" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpkVUNnaGN0UGVDbDM4aHlqSzVQTFE9PSIsInZhbHVlIjoiNDhDTmFWTlZ3cWVWYlp2dU1aRDFtUT09IiwibWFjIjoiNDIyODRhMmI4OWNjOGEwMjViZTRiNzIxMTExZTFlMTE4YjcxY2IyNDQ1YTAzZjVjNmQxZjAwNTI0ZGYzYTc2NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5613">
+      <c r="A5613" t="inlineStr">
+        <is>
+          <t>1029.psd</t>
+        </is>
+      </c>
+      <c r="B5613" t="inlineStr">
+        <is>
+          <t>tamilpsd-11560.psd</t>
+        </is>
+      </c>
+      <c r="C5613" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRZdDh1T25CcVRxZUlKcWt6MnpiOUE9PSIsInZhbHVlIjoiNStia3ZUN3NnZ1IrVDBYNnNjYkpSQT09IiwibWFjIjoiZTdmOThiYWFlYWFiMjRjMDkzY2I4OGQ2Y2Q4ZWVkMjU5NWU3MmNmMDM3ZDZkOWUxMzA0ZThmZDc4MGViZWUxZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5614">
+      <c r="A5614" s="3" t="inlineStr">
+        <is>
+          <t>1028.psd</t>
+        </is>
+      </c>
+      <c r="B5614" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11561.psd</t>
+        </is>
+      </c>
+      <c r="C5614" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InM5V3J6bjBTYzR2NTRER05UOHNWRVE9PSIsInZhbHVlIjoiTmYxZktMam1DaHJFWUNxa3AvWTMxUT09IiwibWFjIjoiZTdlOWE2N2EzMGIzZjFhMTUxNjBmMjAyZjRhNDM0MWQ3NTQ4NzE3MjkxMTQ5OTY4NmY2ZjM5MDRlYmZkNjI1NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5615">
+      <c r="A5615" t="inlineStr">
+        <is>
+          <t>1027.psd</t>
+        </is>
+      </c>
+      <c r="B5615" t="inlineStr">
+        <is>
+          <t>tamilpsd-11562.psd</t>
+        </is>
+      </c>
+      <c r="C5615" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImROOEF3NGQ4Qmc4d1UxZENVRGVuRHc9PSIsInZhbHVlIjoiS2ZaOWpSYzdkbTQ3cWRBdWM2U1dRQT09IiwibWFjIjoiY2FmMTdiZWE3ZGUwODhiNjZjNDQwZmIyYjk3ZGNiMTdmOWE5MjAwMTJkZTIxMzhjODczNDNlYjM1ODNiNDI2MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5616">
+      <c r="A5616" s="3" t="inlineStr">
+        <is>
+          <t>1026.psd</t>
+        </is>
+      </c>
+      <c r="B5616" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11563.psd</t>
+        </is>
+      </c>
+      <c r="C5616" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJGMVFxZlo0alpTZFJvKzZxeG9kWmc9PSIsInZhbHVlIjoieElLclpZVXdnemlkZTgxcVJ1VmNVUT09IiwibWFjIjoiY2I5MzlkNTJkOTFkMGQ0YWU1N2FhMmM0NjQ1NzZhZDI5ZWJkZWU2MTBiZmUyMDBjZTI0ZDdmMTJlYmRhMGY1MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5617">
+      <c r="A5617" t="inlineStr">
+        <is>
+          <t>1025.psd</t>
+        </is>
+      </c>
+      <c r="B5617" t="inlineStr">
+        <is>
+          <t>tamilpsd-11564.psd</t>
+        </is>
+      </c>
+      <c r="C5617" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNEajFuRXlGTndhc1lkWU9Cc2RFUmc9PSIsInZhbHVlIjoiVGZEdFhxMVUvcU9NTUVkeDJJRTA3UT09IiwibWFjIjoiN2NiZWU3MjFkMzkzODFjMGRjNTRhMWI4NDU3YTEyZmJjNWU3NDlmYjU1ODBjMjQ0YTIyMzc1YmI5YjZiZGYzNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5618">
+      <c r="A5618" s="3" t="inlineStr">
+        <is>
+          <t>1024.psd</t>
+        </is>
+      </c>
+      <c r="B5618" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11565.psd</t>
+        </is>
+      </c>
+      <c r="C5618" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InowRG5UbkdJb0xua2hvNVJFUkFob0E9PSIsInZhbHVlIjoicTJ4SHNJRjZxUjNtUVJNWTlmakI5Zz09IiwibWFjIjoiYjRmOGIyMGUxYWJmMGNmMTMxOWUyYmYwMWIzMjEzM2I1NTBmYWQ3NzMyMTEzNjY4MWEyNzUyYTkwZWZiMDM3ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5619">
+      <c r="A5619" t="inlineStr">
+        <is>
+          <t>1023.psd</t>
+        </is>
+      </c>
+      <c r="B5619" t="inlineStr">
+        <is>
+          <t>tamilpsd-11566.psd</t>
+        </is>
+      </c>
+      <c r="C5619" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFtNk53NGpPQkJ1WXRiMmlMQkZuZ1E9PSIsInZhbHVlIjoiNEV2UHQzM29CRzhINERtUXlwRmI1Zz09IiwibWFjIjoiZDUwODE0YmEwMTQ0MGY1OGNmZjNmZGFmYjVmZGQ5OGFlNmVmYzgwYmJhZDZkYWU2NWYyYjcwYTIzODU2YTM1YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5620">
+      <c r="A5620" s="3" t="inlineStr">
+        <is>
+          <t>1022.psd</t>
+        </is>
+      </c>
+      <c r="B5620" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11567.psd</t>
+        </is>
+      </c>
+      <c r="C5620" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpFa0NiSU56N1hkQjExeTkvVDVJYmc9PSIsInZhbHVlIjoiajdoZzZKaVUyMW0xYjVHS0Jmeit5UT09IiwibWFjIjoiYzM1YzNmNzk1YjA0YzNjYmI3YThiNjNlYzk5OTkzNDlkNWE0OTE2NDQ1ZThjMTZlYTgyODQzYjg2MzZhMDExNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5621">
+      <c r="A5621" t="inlineStr">
+        <is>
+          <t>1021.psd</t>
+        </is>
+      </c>
+      <c r="B5621" t="inlineStr">
+        <is>
+          <t>tamilpsd-11568.psd</t>
+        </is>
+      </c>
+      <c r="C5621" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik93ZXJsQ1o0MHkwR0gxRFFCZmJWanc9PSIsInZhbHVlIjoidGJ3ZmsrTTJUQmZBZGZ0SmJ3b3FHZz09IiwibWFjIjoiMDE5M2NkNDRhYTg2OTM4ODJlYzk1ZWMwZjE2NzdiZTcwYTllNGE1MjdlNmQzYzViOTkwNGEyOTBkZjBiY2U5YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5622">
+      <c r="A5622" s="3" t="inlineStr">
+        <is>
+          <t>1020.psd</t>
+        </is>
+      </c>
+      <c r="B5622" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11569.psd</t>
+        </is>
+      </c>
+      <c r="C5622" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjB5aG5CTVN5YWdCWXFkYlhIS3laYkE9PSIsInZhbHVlIjoieHd0cXFtVy94ZjdGRGZ2MVlNeWxhdz09IiwibWFjIjoiZDRhMTVmY2M4NmIwNTFhOGIwZjdkYjZmOGRkYTM3Yzg4ZDgwYTkwOTUwZjYzNzZmMDAxYjY5ZTcyYzU2YzQ5OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5623">
+      <c r="A5623" t="inlineStr">
+        <is>
+          <t>1019.psd</t>
+        </is>
+      </c>
+      <c r="B5623" t="inlineStr">
+        <is>
+          <t>tamilpsd-11570.psd</t>
+        </is>
+      </c>
+      <c r="C5623" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ind3elFMVyt1WHp4bk1UeUZoUStWaFE9PSIsInZhbHVlIjoic0REMkRMWEJMb3ZkeGF2UlZFWWxUQT09IiwibWFjIjoiOGViZTljMzZmYTI1MzcyNWFhM2I4NDU3M2JjZjMyZGY0M2NjODViZDA3ZGI1MDg5OGI2MDJhMmEzMTQ2ZDA0MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5624">
+      <c r="A5624" s="3" t="inlineStr">
+        <is>
+          <t>1018.psd</t>
+        </is>
+      </c>
+      <c r="B5624" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11571.psd</t>
+        </is>
+      </c>
+      <c r="C5624" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1OK1RFVjlUZDdYWXdtZHk5bmFGNEE9PSIsInZhbHVlIjoia01QRnNZSWpucUVHQndUa0k2Q2Rvdz09IiwibWFjIjoiMmE2MzBmODViOGI0MGY1Y2FmMGZkODE3Y2U1YmUyMTViYTRhNGY2MTdjZjdhMmU1OWU4NGY1YjE3MWRmZjU1MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5625">
+      <c r="A5625" t="inlineStr">
+        <is>
+          <t>1017.psd</t>
+        </is>
+      </c>
+      <c r="B5625" t="inlineStr">
+        <is>
+          <t>tamilpsd-11572.psd</t>
+        </is>
+      </c>
+      <c r="C5625" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpGU2ZKblorcG1SMWVBRU1JQXBqU0E9PSIsInZhbHVlIjoiSldwQkZQUHBpNkFEcHg2MUtlZUsyQT09IiwibWFjIjoiOTEzZThlYTA3YTZlZDNlNWMyY2RjMDYzNDJjYTAxYTk5NDA5ZTNlMWE4NGM3ZTBjODc0ZmVmOWIxMGJkMDQ3MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5626">
+      <c r="A5626" s="3" t="inlineStr">
+        <is>
+          <t>1016.psd</t>
+        </is>
+      </c>
+      <c r="B5626" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11573.psd</t>
+        </is>
+      </c>
+      <c r="C5626" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im0xSkdHb2YrUHJWMVptZzdNQVVGV0E9PSIsInZhbHVlIjoiQ2NSL2hiSVFBYmlkVDlDV1RCN00yUT09IiwibWFjIjoiNjBmNjQ2ZmQzZWEwM2NhMjRiYzQyMzI3M2Y5OTUwN2RmZTFmNmM0MDI2OGE0MmMzOTA4YTdiYzk1MjY3OTM5MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5627">
+      <c r="A5627" t="inlineStr">
+        <is>
+          <t>1015.psd</t>
+        </is>
+      </c>
+      <c r="B5627" t="inlineStr">
+        <is>
+          <t>tamilpsd-11574.psd</t>
+        </is>
+      </c>
+      <c r="C5627" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlkzaWJmQWVnSkdXaFdBYjdYRzliRkE9PSIsInZhbHVlIjoiMC9vM0Vxcit3NDRQUWh3YjF1WnR2dz09IiwibWFjIjoiM2Q4MTgyYTgyMTU2NmQyNDhiYTJkOGIxZWM0NDE4OWNmZmNkNGEwNWM2MjU3ZTg2NDA1ZWNjODgxNTVlMDMxOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5628">
+      <c r="A5628" s="3" t="inlineStr">
+        <is>
+          <t>1014.psd</t>
+        </is>
+      </c>
+      <c r="B5628" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11575.psd</t>
+        </is>
+      </c>
+      <c r="C5628" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilp0eVd4U1VJRDE1YTJrd3Era25BY2c9PSIsInZhbHVlIjoiVDhkNmJSRWRWMFIzam1LMURoSUpaQT09IiwibWFjIjoiZjc3MDk1N2RlMDNiZGEwMmI0ZWY5NzMwOTc1YzE4YzI5Mzc1NDYwZDM4MWE2M2U3ZDg5NGZiNWQ2ODk4N2E4OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5629">
+      <c r="A5629" t="inlineStr">
+        <is>
+          <t>1058.psd</t>
+        </is>
+      </c>
+      <c r="B5629" t="inlineStr">
+        <is>
+          <t>tamilpsd-11576.psd</t>
+        </is>
+      </c>
+      <c r="C5629" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtpSTNRMHhqNnIzQjJGUE1EN1B6M1E9PSIsInZhbHVlIjoiKzZCWFVQWXBwWjJVSGZrcEVqMTdMdz09IiwibWFjIjoiNmU0OTg1NDMxNWY5YjA3N2UzNGNiZGFhMDQ2OWUxY2RiZTFlOWUwZGFmOWM5MmRkYTczYjk0ZDU5ZGY0MGU5MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5630">
+      <c r="A5630" s="3" t="inlineStr">
+        <is>
+          <t>1012.psd</t>
+        </is>
+      </c>
+      <c r="B5630" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11577.psd</t>
+        </is>
+      </c>
+      <c r="C5630" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9ZT0VmOHFYbTlwenNsMThsN1F0OVE9PSIsInZhbHVlIjoid210akJvYnI5UjB4cGcrcmJFSUthUT09IiwibWFjIjoiNzZlNWUzNDMzYzY5MmFiNGE2OTFkNGRhMzA5ZWVkZDgyZTczMTI3YmNlOTM3ODJlMGE4ZGE4OGZjYzg3YmVhZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5631">
+      <c r="A5631" t="inlineStr">
+        <is>
+          <t>1011.psd</t>
+        </is>
+      </c>
+      <c r="B5631" t="inlineStr">
+        <is>
+          <t>tamilpsd-11578.psd</t>
+        </is>
+      </c>
+      <c r="C5631" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklnWkJua2lLcmprMFhtaTBLNDU5UEE9PSIsInZhbHVlIjoiYUt6SGU0eEtWSElaL0hacStHVTk5UT09IiwibWFjIjoiOTM5NDQ4OGQ1ZDAzYjRlZDZjODRkNWI2ZDlmNTNkOWYyY2NmMTI4NjViOTllNjIxMzZlZTE0NGM1NDBhNGQyMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5632">
+      <c r="A5632" s="3" t="inlineStr">
+        <is>
+          <t>1010.psd</t>
+        </is>
+      </c>
+      <c r="B5632" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11579.psd</t>
+        </is>
+      </c>
+      <c r="C5632" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik5NTHp1T0U4NW1QVTlTVWNyM0hZZGc9PSIsInZhbHVlIjoiWG5nbUh4bzFGUjNoNFdISUJrMVc3dz09IiwibWFjIjoiYTQ1OGViMDY4MDVjNDQ4NGMxZmI2ZTU0NzczOWFjNTI1YzI0MmQ5YzY1MzIzYjZjODJkNzNiZTk4MWRjMWM5MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5633">
+      <c r="A5633" t="inlineStr">
+        <is>
+          <t>1009.psd</t>
+        </is>
+      </c>
+      <c r="B5633" t="inlineStr">
+        <is>
+          <t>tamilpsd-11580.psd</t>
+        </is>
+      </c>
+      <c r="C5633" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNDWmFoOGl5c3ZyQnFtdUlLUXE4dFE9PSIsInZhbHVlIjoiTjVBYno5MzY1WW15ZkxYcW9ubFd2dz09IiwibWFjIjoiYTY1OTU1YmVjYzk4Mjg3MDhjZmIyNTU5MjM3MDE3ZTM5ZDBlYmY2ZmRjZjViMWRhZTZjOGNiMDhiMWJkNzdjNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5634">
+      <c r="A5634" s="3" t="inlineStr">
+        <is>
+          <t>1008.psd</t>
+        </is>
+      </c>
+      <c r="B5634" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11581.psd</t>
+        </is>
+      </c>
+      <c r="C5634" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikduak04djJzWmtlUWoyLzVxRFZPdlE9PSIsInZhbHVlIjoiL01LM2pxZ2t3ZTA5TnNOTlFxck5Tdz09IiwibWFjIjoiNDEwYjg4MWE2MTAyZjAwMzIxMzI2MTQ3NzU5YzBlZjVlMzA4M2M4YjcwYWYyMDkwYTU3YzRhNGVhNmQ0ZjkyZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5635">
+      <c r="A5635" t="inlineStr">
+        <is>
+          <t>1007.psd</t>
+        </is>
+      </c>
+      <c r="B5635" t="inlineStr">
+        <is>
+          <t>tamilpsd-11582.psd</t>
+        </is>
+      </c>
+      <c r="C5635" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRTSndDblFzNmJuS0hLTklZK2V4QUE9PSIsInZhbHVlIjoicXMzekxxdXNBOWF4MVhRQkJiREJrUT09IiwibWFjIjoiMDZlYjlmY2U4ZGRiNTQwZGZlNGRmZGFiMWIwMmMwMmI2Yjc3MGY0YWY1MjY2MTA1MGU1M2MyNGMxNThkOWZmNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5636">
+      <c r="A5636" s="3" t="inlineStr">
+        <is>
+          <t>1006.psd</t>
+        </is>
+      </c>
+      <c r="B5636" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11583.psd</t>
+        </is>
+      </c>
+      <c r="C5636" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpLbnlrYzJjOWY0L2FaMndOT3g4K1E9PSIsInZhbHVlIjoiaTBXYWJiZ2RlbldYZjB5Q2RvWHVLZz09IiwibWFjIjoiZWRkZTQzODA1ODIxYjRiOGEwODkwYTc1Y2Q1Mzc5NTU1ZGU3NWM2MDBkY2JhZjI4OTBhOTM5ODU1ZDI1MDNlYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5637">
+      <c r="A5637" t="inlineStr">
+        <is>
+          <t>1005.psd</t>
+        </is>
+      </c>
+      <c r="B5637" t="inlineStr">
+        <is>
+          <t>tamilpsd-11584.psd</t>
+        </is>
+      </c>
+      <c r="C5637" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJRektBM0NhNGpxNm54dFJPZ1I0L1E9PSIsInZhbHVlIjoiK01NUkN0NVBrdU1lYXFKZzdpSzdvdz09IiwibWFjIjoiOGM2ZmRhMjM1NDgyZTU1MTBhZmM2YjMxNzQ0ZTE3YTAzZDViOGMzNGNjOGNkZGE4MGVmMzAxZjJlMmMxNGQ0MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5638">
+      <c r="A5638" s="3" t="inlineStr">
+        <is>
+          <t>1004.psd</t>
+        </is>
+      </c>
+      <c r="B5638" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11585.psd</t>
+        </is>
+      </c>
+      <c r="C5638" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjI2cGpZdDkwODFZZkp4VXlvek04OEE9PSIsInZhbHVlIjoiK09mUEFtN3JOZWxuNnE2Y014eXJhUT09IiwibWFjIjoiNmFmNWJhNGM1NzkwZTVmNjNlYTVhNDMzNTk3MjA0NzViYTZmZWU2YzU4OTFjZjM5ZTlmODA0NzUyMDY5MDJkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5639">
+      <c r="A5639" t="inlineStr">
+        <is>
+          <t>1003.psd</t>
+        </is>
+      </c>
+      <c r="B5639" t="inlineStr">
+        <is>
+          <t>tamilpsd-11586.psd</t>
+        </is>
+      </c>
+      <c r="C5639" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikl6SWVSOExWb0F3cVB6WEpOc1oxNkE9PSIsInZhbHVlIjoiMHRCMEtZUkQyOU9Tc0p1SnJSYkhKdz09IiwibWFjIjoiN2E1OGZjMjQ2MWFkYmQ2YzJjMzhmM2U2OWRhNzY3YjU3Y2UzNTE0Yzk0NjFhZWNhYWJjYmMxYzhkZWFlNTE1YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5640">
+      <c r="A5640" s="3" t="inlineStr">
+        <is>
+          <t>1002.psd</t>
+        </is>
+      </c>
+      <c r="B5640" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11587.psd</t>
+        </is>
+      </c>
+      <c r="C5640" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InBzRUNNbTRzMGFUYk4wOVYxNzJlU2c9PSIsInZhbHVlIjoiaVg1Sjk0c3ZDMnZFdmlKV1diaEtuQT09IiwibWFjIjoiNWJlNjAyNGY4N2I3Y2M0OTkyMjhkMTliMGViYjI4YmUzODIwNTYyN2M2ZDNkNmMwZGM3OGFlYTJiZjFkNzljNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5641">
+      <c r="A5641" t="inlineStr">
+        <is>
+          <t>1001.psd</t>
+        </is>
+      </c>
+      <c r="B5641" t="inlineStr">
+        <is>
+          <t>tamilpsd-11588.psd</t>
+        </is>
+      </c>
+      <c r="C5641" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndZMjhOdXh3WXlHQ2RlWFVaOFEvMmc9PSIsInZhbHVlIjoidWtqQmppcjcxd0RkU2thSVp2ZzhWZz09IiwibWFjIjoiOWNjMTA5OWFkODdiZmM2NGM0NTc1NDUzMGQ5Yjk2NzcwODZlOWQwODFmNTNiMzIzZDk1NDAzMWJjNzM5NTBmZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5642">
+      <c r="A5642" s="3" t="inlineStr">
+        <is>
+          <t>1000.psd</t>
+        </is>
+      </c>
+      <c r="B5642" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11589.psd</t>
+        </is>
+      </c>
+      <c r="C5642" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpGOUZGbTE2d2c1REJCdWtXR25GTUE9PSIsInZhbHVlIjoiektvZ1kvZmJ2Nm1zaVZuMm5hdXYwUT09IiwibWFjIjoiNWQwZjJjMjViOGQ4Y2EzNTI2ZTBhYWNiODgxNmYwNWIyOGVjYzYxZDM0ZGNjNmJmNjFhYjAyMDQ2ZTQ3MzA4ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5643">
+      <c r="A5643" t="inlineStr">
+        <is>
+          <t>999.psd</t>
+        </is>
+      </c>
+      <c r="B5643" t="inlineStr">
+        <is>
+          <t>tamilpsd-11590.psd</t>
+        </is>
+      </c>
+      <c r="C5643" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlJIWGtkK1R6eU0xWWU4V0Q3M29FL1E9PSIsInZhbHVlIjoiRTJZVE9Ic1k0MWNRcDJrYXhjaitsdz09IiwibWFjIjoiMGMyOWRjNmJmOWU3YTczMDkwYjJmYzU3MzdlZWMwNGUyOTBiNzk4MDc1M2YxOTkzYWU3M2M1YWNmNTBmOTUwNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5644">
+      <c r="A5644" s="3" t="inlineStr">
+        <is>
+          <t>998.psd</t>
+        </is>
+      </c>
+      <c r="B5644" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11591.psd</t>
+        </is>
+      </c>
+      <c r="C5644" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InJEbDNxRWMwT2FJTFZ6WG1FcjRDaXc9PSIsInZhbHVlIjoiL3NYTHFEMWVZaVhsMVhKVldqVEQzdz09IiwibWFjIjoiZjFiM2M4MmYyNTE3ZGU0YzU0MWRjZDc2NDAwMGVhZDdlZjczOTg0MGE5ZTY3MjcwYjhkZDJjNjY4ZWU5NGNjNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5645">
+      <c r="A5645" t="inlineStr">
+        <is>
+          <t>997.psd</t>
+        </is>
+      </c>
+      <c r="B5645" t="inlineStr">
+        <is>
+          <t>tamilpsd-11592.psd</t>
+        </is>
+      </c>
+      <c r="C5645" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVYay9qUm11bHlhOWVEUnZFOGU0YlE9PSIsInZhbHVlIjoiZ0ZEaUVwckVhYklZUXdUNEhpWnRHZz09IiwibWFjIjoiZmQ4ODgwOWJiYTg4NDA4MGRjNDNiZGFjNjc0ZDFlM2U5NTMzZDI4YTIwMTRkYzE3YzA0MmY4NjNiMmMyNTI5NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5646">
+      <c r="A5646" s="3" t="inlineStr">
+        <is>
+          <t>996.psd</t>
+        </is>
+      </c>
+      <c r="B5646" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11593.psd</t>
+        </is>
+      </c>
+      <c r="C5646" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImorRlJrWWJ4L1NQY2tPdHFySmQ4WEE9PSIsInZhbHVlIjoiSm8wUVlSZWdZQlVWc3RTb241aG54UT09IiwibWFjIjoiNTRkMzYyNGIwYzc1MGY0ZjI4M2ZlN2FmOWY0NTI1NjU3NTE1MWU5ZThmNzc3NDdhMzNhMTI5NTY5ZTNkY2MxNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5647">
+      <c r="A5647" t="inlineStr">
+        <is>
+          <t>995.psd</t>
+        </is>
+      </c>
+      <c r="B5647" t="inlineStr">
+        <is>
+          <t>tamilpsd-11594.psd</t>
+        </is>
+      </c>
+      <c r="C5647" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InZJRlBsNEdObENwZElLYVR1NS9weUE9PSIsInZhbHVlIjoiNEV5RTRzQTRudnZBUUdoM1ppNHhHQT09IiwibWFjIjoiMTRmNDE4NWEyYTYxN2NhNDg1ZmE2NGFhN2UyYTkyMmQzNjVmZTE0ZjA5ZjdiMzA0NGFhMGMyOTEzMGIzMWJiMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5648">
+      <c r="A5648" s="3" t="inlineStr">
+        <is>
+          <t>994.psd</t>
+        </is>
+      </c>
+      <c r="B5648" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11595.psd</t>
+        </is>
+      </c>
+      <c r="C5648" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InRwWi9yZkN0Q3BkOUJoTkxWNmEzM2c9PSIsInZhbHVlIjoiV1cwVzM4T0Zxb1R2ZFZHVmFaU0VKQT09IiwibWFjIjoiZmJkYjJmM2MzYzJhMDBhNTA3NjQ2OWU3OGRhNzAxMGRkMGU1NmI3NWZlZmE4NTQzNzIxZDA3NmE3NjhiNGMyZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5649">
+      <c r="A5649" t="inlineStr">
+        <is>
+          <t>993.psd</t>
+        </is>
+      </c>
+      <c r="B5649" t="inlineStr">
+        <is>
+          <t>tamilpsd-11596.psd</t>
+        </is>
+      </c>
+      <c r="C5649" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBOTjRsQnkzY2g2T2IzRGpqTE5Ld3c9PSIsInZhbHVlIjoiQlNSNlFydHRHWmc2dHhHcFRaZ0ZCUT09IiwibWFjIjoiNzAwZWFmODk3ZWJkOWNiNjY0ZDJmMzYzNzk3YzI1YzZkN2UyODFjNmI1MDUwOTA5YWUwOGUxNDdhNDM2OWM0NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5650">
+      <c r="A5650" s="3" t="inlineStr">
+        <is>
+          <t>992.psd</t>
+        </is>
+      </c>
+      <c r="B5650" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11597.psd</t>
+        </is>
+      </c>
+      <c r="C5650" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlTVHRvNGhJT3RSWjVwTUFIRHhiVXc9PSIsInZhbHVlIjoiTXZQSjZYSFM5S1ZjTVNLL1o2eUlIdz09IiwibWFjIjoiMWYwYjUzYmE4OTQwNTc4NzhhODA1YzNiMWMxM2I4MTQ2OTIwZDM1ZTIxNjg2ZmU5Nzk5YzFmNTU5Y2E2ZTEwZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5651">
+      <c r="A5651" t="inlineStr">
+        <is>
+          <t>991.psd</t>
+        </is>
+      </c>
+      <c r="B5651" t="inlineStr">
+        <is>
+          <t>tamilpsd-11598.psd</t>
+        </is>
+      </c>
+      <c r="C5651" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtUdGZKSW5GbU1PREo5cW5Fc2dIUkE9PSIsInZhbHVlIjoicTA5WlgvZU1vaFptTmtLb3FlUnhJdz09IiwibWFjIjoiZDZjODA1NWRiYTgwZDE0YTU2YWM3YjgzNWI1ZGZiZDlhNDMxYjZhNDk1YzcwYWVmMzc5ZDU4YzQ5NDZjNGFlOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5652">
+      <c r="A5652" s="3" t="inlineStr">
+        <is>
+          <t>990.psd</t>
+        </is>
+      </c>
+      <c r="B5652" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11599.psd</t>
+        </is>
+      </c>
+      <c r="C5652" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilhma1lNemRPQi84RHNnVm41THMwNlE9PSIsInZhbHVlIjoidnNkbTlqOFIvWm5TN25PNjQxWDN5QT09IiwibWFjIjoiNjcwZDVmMGYxNzk0MGVlMDE2NzZmYzAwYTVlNmY3Y2M2NTJkOGU5MGY2YWE4NmRmZTBmYTM3MGVmZmY5Y2FlOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5653">
+      <c r="A5653" t="inlineStr">
+        <is>
+          <t>989.psd</t>
+        </is>
+      </c>
+      <c r="B5653" t="inlineStr">
+        <is>
+          <t>tamilpsd-11600.psd</t>
+        </is>
+      </c>
+      <c r="C5653" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlmUkd0bmR4SVJzK3ZnVFhoWjhMWEE9PSIsInZhbHVlIjoiSktBQnR5VmJKSHVpbjl2a0VLUjEzUT09IiwibWFjIjoiYjc2OGU0MzUxM2NjNDk1ODlkODhjZGMxM2IyZWY3YThlN2U4ODVkYmRiZWZkNDQzNGJjNDkzZDRkMzQ4MTRiOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5654">
+      <c r="A5654" s="3" t="inlineStr">
+        <is>
+          <t>988.psd</t>
+        </is>
+      </c>
+      <c r="B5654" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11601.psd</t>
+        </is>
+      </c>
+      <c r="C5654" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkExb3haZXgzMTN1aGR5NTY0aHBwTFE9PSIsInZhbHVlIjoiU2V2dVFQM1l1NkdLZldickYvS3kvdz09IiwibWFjIjoiMjc5MzE4OTlhMTRlYzJhMjkzZjcwNzkxYTcwMzMyOTM2MjExOTQwNTEzYzFhOGMxNjhmNzllMTljNzU2MzU5NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5655">
+      <c r="A5655" t="inlineStr">
+        <is>
+          <t>986.psd</t>
+        </is>
+      </c>
+      <c r="B5655" t="inlineStr">
+        <is>
+          <t>tamilpsd-11602.psd</t>
+        </is>
+      </c>
+      <c r="C5655" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRnbTJ5d1BLRHo2K2VNRGxWNzJ2S1E9PSIsInZhbHVlIjoiTVQ4Q2t5R1BpN0RNWlMrMUt0RmlXQT09IiwibWFjIjoiNTFjZjQ2OTlkNTMxYzliYThkMjYwNzZiMDc5YWQ0NjMxODAxNDBhMjg3YzQ3YmFkOWVjZjgxYjM1NTc5NTQzZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5656">
+      <c r="A5656" s="3" t="inlineStr">
+        <is>
+          <t>985.psd</t>
+        </is>
+      </c>
+      <c r="B5656" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11603.psd</t>
+        </is>
+      </c>
+      <c r="C5656" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9hR2NWVG9temlPWkVKb0hhaVRmZFE9PSIsInZhbHVlIjoiaGJ5ZGpsTktMSjZETFZYVWdvS3pmZz09IiwibWFjIjoiODBlYzUzNjQ1MDVlMDU2MzE3YzNjODc2MTAzYmIwODg1YjRkNTMzNTg2MGYxNDg2N2IxYTAyYTI3ZGRjYjYzYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5657">
+      <c r="A5657" t="inlineStr">
+        <is>
+          <t>984.psd</t>
+        </is>
+      </c>
+      <c r="B5657" t="inlineStr">
+        <is>
+          <t>tamilpsd-11604.psd</t>
+        </is>
+      </c>
+      <c r="C5657" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhIRjl6QnNJSHRBblkzZGUxeWNnVWc9PSIsInZhbHVlIjoia1diOVBKb1poekRUWWh5VzJnOGJudz09IiwibWFjIjoiODczMWMzNjMxMDk5ZjEwNDI1MjdkNjY1MWYzODI5MDlhZTM4YjNhNWMyODc4MDQ2ZTY4YzU5ZWFmNTE2ZTgyMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5658">
+      <c r="A5658" s="3" t="inlineStr">
+        <is>
+          <t>983.psd</t>
+        </is>
+      </c>
+      <c r="B5658" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11605.psd</t>
+        </is>
+      </c>
+      <c r="C5658" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1MRzlxSjc3dnljZW9PQTlmQ05za0E9PSIsInZhbHVlIjoiT1F1MDlVOHU0a0lqZmpnd3hDbURwQT09IiwibWFjIjoiZjc5NTkwNzg5Mjk5NjIyMTdhNWI2NzIyZjM2NTg5MTkzMzE3NWFkY2NhYWNjYTk2NmI0ZWZiMzVkNGY4ZmQyMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5659">
+      <c r="A5659" t="inlineStr">
+        <is>
+          <t>982.psd</t>
+        </is>
+      </c>
+      <c r="B5659" t="inlineStr">
+        <is>
+          <t>tamilpsd-11606.psd</t>
+        </is>
+      </c>
+      <c r="C5659" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imx6ek1ib29jREJZYlo4Vkd0MzFodmc9PSIsInZhbHVlIjoiRkh3VWh5a0J5eU5ISnk2Z29TQ1ljdz09IiwibWFjIjoiNDZhNmFhMDJhOTc1MTYzNDVlMGMyZjdlYjdhYzcxYjZhZDQ1YzU2ZGQwOGU1MzcxYjQwMGQxM2IzMTgxMjVkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5660">
+      <c r="A5660" s="3" t="inlineStr">
+        <is>
+          <t>981.psd</t>
+        </is>
+      </c>
+      <c r="B5660" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11607.psd</t>
+        </is>
+      </c>
+      <c r="C5660" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikg0cG16OTRnbFpTRzZvN0pYNUNEV2c9PSIsInZhbHVlIjoicGgwcEdOd2plcEVMVzJFUGhXcWJUZz09IiwibWFjIjoiNjdhMzRjYjg2NjNjMGFhN2Y3MzNkYjE5NzRiZGQwNjFmYzgwODk0NGE4NmU3ZTRkYmZmMzRlNWJhYjgzNTUxYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5661">
+      <c r="A5661" t="inlineStr">
+        <is>
+          <t>980.psd</t>
+        </is>
+      </c>
+      <c r="B5661" t="inlineStr">
+        <is>
+          <t>tamilpsd-11608.psd</t>
+        </is>
+      </c>
+      <c r="C5661" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlTWkhTdTQzaEJkT0UvZ3RNYVRxU1E9PSIsInZhbHVlIjoiVlAvZTMwS0o3M29UL2tuaHNVNkJSdz09IiwibWFjIjoiMGRlMWE5YWY2YTlmMWM2OGU2MDA5NjIwNDZiNTYxNDBkOGY0OWFjNDIwNTZiYzJiNGI3MWY4ZDVmODVmZWNlNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5662">
+      <c r="A5662" s="3" t="inlineStr">
+        <is>
+          <t>979.psd</t>
+        </is>
+      </c>
+      <c r="B5662" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11609.psd</t>
+        </is>
+      </c>
+      <c r="C5662" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImxPT0dvL2VGNm5INUxnVkprdVVPbUE9PSIsInZhbHVlIjoiS3JzcGZ0TmdSNW1Sa3N2WHNHMWZFZz09IiwibWFjIjoiMzcyZWZhMTQ0MzgzNGFkNmM0YTFkZjAwNDliOGI1MWVjYjJlMjg3MjI5OTkzMjVkMWYxYWE5NTc4ZjEwOTU0NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5663">
+      <c r="A5663" t="inlineStr">
+        <is>
+          <t>978.psd</t>
+        </is>
+      </c>
+      <c r="B5663" t="inlineStr">
+        <is>
+          <t>tamilpsd-11610.psd</t>
+        </is>
+      </c>
+      <c r="C5663" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtNbkk4WmVEOEdmdGdVLzFxbEM5Rnc9PSIsInZhbHVlIjoiNU5KM01leXI3VCtpTUxHNjc5VEo5QT09IiwibWFjIjoiZmExN2I3MzgwOWQ2ZTkyZGJmNGJhMzI5YmNiOWM4ZGEwMzM5YjM2Nzk5ZTg5ZTgyZTI3YTcwYzU4NzcyMmRiYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5664">
+      <c r="A5664" s="3" t="inlineStr">
+        <is>
+          <t>977.psd</t>
+        </is>
+      </c>
+      <c r="B5664" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11611.psd</t>
+        </is>
+      </c>
+      <c r="C5664" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImlKaVlOZU9NM09lazkwcUl6b3NVSkE9PSIsInZhbHVlIjoicFVCVndrcVd5L0J1M0xyUWMvTGRIZz09IiwibWFjIjoiMTIwNDg3YzQ5MTlkZDI0Y2E1MjRkYjNkZjBhNjAzNjhhYjhmMDJjYTgzZmQ5MzMzYmJmN2NlNjRmNzRhNzhhMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5665">
+      <c r="A5665" t="inlineStr">
+        <is>
+          <t>976.psd</t>
+        </is>
+      </c>
+      <c r="B5665" t="inlineStr">
+        <is>
+          <t>tamilpsd-11612.psd</t>
+        </is>
+      </c>
+      <c r="C5665" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImQvQ1ZjN1haT3RuZnZwSkMyUlM5SlE9PSIsInZhbHVlIjoiVHdsZUNTY2pHRTFqWUxzUE1YWVFNQT09IiwibWFjIjoiZDU2YWViZTY1NzE3Mjk4N2U5MmJmNTNlZjY4YTU1MmE3MDJjNmU2NmQ0YzQ2ODc4NDZhZmE3ODc0NWUzZmYxNSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5666">
+      <c r="A5666" s="3" t="inlineStr">
+        <is>
+          <t>975.psd</t>
+        </is>
+      </c>
+      <c r="B5666" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11613.psd</t>
+        </is>
+      </c>
+      <c r="C5666" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFWUzZjc1hhZ2xSNkhKbTdHblZXVkE9PSIsInZhbHVlIjoiRTFZbGtvUjV0aFpLM0R1czl2NXBzQT09IiwibWFjIjoiYWQ4ZDM5MWE1YWVjNThkZGFhN2JhYTBkNWMyMGNiNTVmYzVhYWI2NzcwZTNiZjk3ZmJlMzg5MTcxOGIxMDhmNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5667">
+      <c r="A5667" t="inlineStr">
+        <is>
+          <t>974.psd</t>
+        </is>
+      </c>
+      <c r="B5667" t="inlineStr">
+        <is>
+          <t>tamilpsd-11614.psd</t>
+        </is>
+      </c>
+      <c r="C5667" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJnQUZpY0gzNmp6TzNhVFF5aTVva1E9PSIsInZhbHVlIjoia0lLVlFQVGh3NUllUHdhV0J0dXpRZz09IiwibWFjIjoiOTQzZDQ0YTM3OWNhNmVlZDVkYmE0Yzg4YmM2MjRjMDY4NGY5MDI4ZTI2ZDU1YzkxNGVhZjM5ZTg5YjA5YWZlOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5668">
+      <c r="A5668" s="3" t="inlineStr">
+        <is>
+          <t>973.psd</t>
+        </is>
+      </c>
+      <c r="B5668" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11615.psd</t>
+        </is>
+      </c>
+      <c r="C5668" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNRU0M1cmZVZGFvVmFkV2tBc2lDMEE9PSIsInZhbHVlIjoieUthbXhTRVJNbGd1ZlBHR2JKMk5ldz09IiwibWFjIjoiZjFiMzc0NjAyZWJiZmUxZmY4NzI4OTczMTBmYzFlNDBhM2M5NjhlYTE0ZmNhMTA2NjYyNmZmNDBiNzYzYzdjMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5669">
+      <c r="A5669" t="inlineStr">
+        <is>
+          <t>972.psd</t>
+        </is>
+      </c>
+      <c r="B5669" t="inlineStr">
+        <is>
+          <t>tamilpsd-11616.psd</t>
+        </is>
+      </c>
+      <c r="C5669" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik9rcFNaOWt3UXdqWWE1NEpQZUhGakE9PSIsInZhbHVlIjoidmw0SXozQ3BQVFVkNk81YXVJY0haQT09IiwibWFjIjoiNDEyY2ZlYzZiYzQ5YzhmYmZhOTI3MWY2ZGI2ZGJhMGU1MzBmMjlkYWQxZDE2ODBlNGIyYTAxNDViOGM4MDA5OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5670">
+      <c r="A5670" s="3" t="inlineStr">
+        <is>
+          <t>970.psd</t>
+        </is>
+      </c>
+      <c r="B5670" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11617.psd</t>
+        </is>
+      </c>
+      <c r="C5670" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikt5dUloYzdjdEh6KzlBRGQ1QkpuWmc9PSIsInZhbHVlIjoiQUNKZ1V4czAyaEthcXhYUzdhMzUvdz09IiwibWFjIjoiOTQxOWM4ZmFiNDcwYzcwZjY2MTY4ZmI1NGI1MGU1NjYzZjcwZDMwOWMzNDdjN2Q4ZTBmZjI4MGI0M2U4MWY0NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5671">
+      <c r="A5671" t="inlineStr">
+        <is>
+          <t>969.psd</t>
+        </is>
+      </c>
+      <c r="B5671" t="inlineStr">
+        <is>
+          <t>tamilpsd-11618.psd</t>
+        </is>
+      </c>
+      <c r="C5671" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVZUkQwVk9KZlkxbzRSUm1TcmRtclE9PSIsInZhbHVlIjoiSXVuOWRyRHFSVmlzU2lvYk5HQWZHUT09IiwibWFjIjoiMDIyMmJmMGYwMzJlNmI5Yzk0ZGRmZTBiOWQyZDIxZjU5ZjdjMDViMzMzYzgyYTdmODgyODMzMTZhZDRkYmIzZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5672">
+      <c r="A5672" s="3" t="inlineStr">
+        <is>
+          <t>968.psd</t>
+        </is>
+      </c>
+      <c r="B5672" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11619.psd</t>
+        </is>
+      </c>
+      <c r="C5672" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVLQ21McmFadDNpRGg2dEpGZVh2V2c9PSIsInZhbHVlIjoiaHVoZmUwY243R2dTQ2xET1BsVjNPZz09IiwibWFjIjoiMTdhMzE2NWFhMjZhZmJmOTZkYmE4Yjk1MzJhZmFlN2EwMWMxY2U0MWMxYzIwZjhmYjBkYWY3YTY0OGY0Y2I5NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5673">
+      <c r="A5673" t="inlineStr">
+        <is>
+          <t>966.psd</t>
+        </is>
+      </c>
+      <c r="B5673" t="inlineStr">
+        <is>
+          <t>tamilpsd-11620.psd</t>
+        </is>
+      </c>
+      <c r="C5673" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InRzSW5DeUJEekFtZytyQjE4eXZvMnc9PSIsInZhbHVlIjoiZ0tjRTRrZlVBWEJicjF2OHg3SkhMUT09IiwibWFjIjoiMThhOTM4YTRlY2ExY2Y4ZTgyNWU4NGRkNDUzNGRjZWM0Njc3MDc3N2FiMzQyYjcxMTYwNjY1Mjg3ZWFiYWRmMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5674">
+      <c r="A5674" s="3" t="inlineStr">
+        <is>
+          <t>965.psd</t>
+        </is>
+      </c>
+      <c r="B5674" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11621.psd</t>
+        </is>
+      </c>
+      <c r="C5674" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBoZ1J3RlBVNlIyZTB2UHk4ZDJNUUE9PSIsInZhbHVlIjoiZkYxWUVuTTJIcEdCSmJCYUJqSmtOZz09IiwibWFjIjoiZmQzZjhhY2NhOGUxZTc3NDJlYjY2MzdmZDhjZWI1NjIxNDE0ZTYxYzdkN2RmYjM3MTUzY2Q3MjI0Mjk4ODQ4ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5675">
+      <c r="A5675" t="inlineStr">
+        <is>
+          <t>964.psd</t>
+        </is>
+      </c>
+      <c r="B5675" t="inlineStr">
+        <is>
+          <t>tamilpsd-11622.psd</t>
+        </is>
+      </c>
+      <c r="C5675" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxLYUVDZFJXWTNuSlhmRVpYUTErWnc9PSIsInZhbHVlIjoiRFpxRjcyYm56NHVFVm5QeUY4dDVXUT09IiwibWFjIjoiMWRiYmNkMDgwNDUwYmM4NGVmYTQ5NDViYmJjY2M1YWY0Zjg3M2RkYmY1YTQwZmNmYWI0ZjIwMDFjOGM5MWQwZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5676">
+      <c r="A5676" s="3" t="inlineStr">
+        <is>
+          <t>1013.psd</t>
+        </is>
+      </c>
+      <c r="B5676" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11623.psd</t>
+        </is>
+      </c>
+      <c r="C5676" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ii9rdEFsTjh3WXQ5ekhDZXhPbGZ4T3c9PSIsInZhbHVlIjoiU1ZPMkRieGNKeWVQV1dVMVpFWDBFZz09IiwibWFjIjoiNjQyOTVmNzE4OWU2OGM1YzJhM2FmN2EyMjQ1NWMwM2FiOTM2ODJkYzYzMzBiMjI1ZTEzZGZhZmY1NzQ3YjdkYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5677">
+      <c r="A5677" t="inlineStr">
+        <is>
+          <t>916.psd</t>
+        </is>
+      </c>
+      <c r="B5677" t="inlineStr">
+        <is>
+          <t>tamilpsd-11624.psd</t>
+        </is>
+      </c>
+      <c r="C5677" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkQ1OVA4MEpkSVlrVUFud2RnN2pVcUE9PSIsInZhbHVlIjoiSmxjOEdCdzNnTzkrU0g5b0ljTExYdz09IiwibWFjIjoiODUzZTFlYTc0MDI4ZjIxNzY3YWE5YzFhZDdmMDkyMzcwNjc1NDZiMDE2ZDZhODczYWIzYmYzNjc2ZTU5YzljOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5678">
+      <c r="A5678" s="3" t="inlineStr">
+        <is>
+          <t>915.psd</t>
+        </is>
+      </c>
+      <c r="B5678" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11625.psd</t>
+        </is>
+      </c>
+      <c r="C5678" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllIVHBsVllxVXhZazJraUpzVEhpa3c9PSIsInZhbHVlIjoiNjdLUGxuYUNvWW5zdE00empFZndUUT09IiwibWFjIjoiY2ExODVkNjAyNjM5ODIzMjgzOWY5MzRhYWQ4YTMzYmMxNjVkOWI5NDc1NDYxNzZkMDI1MTk5YTIzMmE3OGUxMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5679">
+      <c r="A5679" t="inlineStr">
+        <is>
+          <t>963.psd</t>
+        </is>
+      </c>
+      <c r="B5679" t="inlineStr">
+        <is>
+          <t>tamilpsd-11626.psd</t>
+        </is>
+      </c>
+      <c r="C5679" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZ6NTh1MmJidkNqbjRQU09mU0VPTWc9PSIsInZhbHVlIjoiSFNWM3NwUHB3ZFdjeG1NS3ZZQTdzQT09IiwibWFjIjoiNjdmZjk1ZTk0M2EyZmY2YmViNGUyZDFiYzRiMjRmNmI5ZGQ5NGEyOWExZjdjN2IyZTcyOWNkMDYxYThkNzQxMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5680">
+      <c r="A5680" s="3" t="inlineStr">
+        <is>
+          <t>962.psd</t>
+        </is>
+      </c>
+      <c r="B5680" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11627.psd</t>
+        </is>
+      </c>
+      <c r="C5680" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhETmF3OE1LK2VXSFl4Tk4yMlVQbGc9PSIsInZhbHVlIjoibGp5LzVvc3VBZFFGc29KLyt0aEt5UT09IiwibWFjIjoiNzExY2EzNjA4M2RhNmZjMTIyNGNjMzk1ZmNmMmFhYTA4YWIyZmY2MjI5YTIzMzhhMzg1MTE4Y2JlMWRkY2Y4YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5681">
+      <c r="A5681" t="inlineStr">
+        <is>
+          <t>961.psd</t>
+        </is>
+      </c>
+      <c r="B5681" t="inlineStr">
+        <is>
+          <t>tamilpsd-11628.psd</t>
+        </is>
+      </c>
+      <c r="C5681" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjRMQzhGV1BQODFnb2FScUt6MHlEd0E9PSIsInZhbHVlIjoiWUdKV0lqbnFEM01EejVRTkxocUJ0dz09IiwibWFjIjoiMmE5NDYyYWU3ZGEyNjJhZjM0ZDZlMjM1N2U5YmJjMTdhMTE5YmY2NTMzZDZkY2Y3ODBjYTY0ZWVmYmE0NGExYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5682">
+      <c r="A5682" s="3" t="inlineStr">
+        <is>
+          <t>960.psd</t>
+        </is>
+      </c>
+      <c r="B5682" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11629.psd</t>
+        </is>
+      </c>
+      <c r="C5682" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlliMHRIdE9iczFpcTMvaEk5NGI2dEE9PSIsInZhbHVlIjoiUDNWanRpV2tEV3ZscWVjUFk5T25TUT09IiwibWFjIjoiNzMzZTRiODcwYmNlOGJkMjIyMDYyNWFiOTQxMDdiYzUzOGJhMGUzM2RiYWFhNjI5NmRkOThkODgwNzhjY2M5NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5683">
+      <c r="A5683" t="inlineStr">
+        <is>
+          <t>959.psd</t>
+        </is>
+      </c>
+      <c r="B5683" t="inlineStr">
+        <is>
+          <t>tamilpsd-11630.psd</t>
+        </is>
+      </c>
+      <c r="C5683" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJQdXRRNy9CSVM3eld0STJMRjJFdFE9PSIsInZhbHVlIjoiM2p2VXJMSjhrUkVnSWFsSy9qNW56QT09IiwibWFjIjoiYTFmZGMyZDA4YTU5OWE2NzY5N2JlMjViN2QyM2QwOTkxNDY5ZWI2MGRjNjRiYzNiOGE0MWU1MWUxNzMwZGZlMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5684">
+      <c r="A5684" s="3" t="inlineStr">
+        <is>
+          <t>958.psd</t>
+        </is>
+      </c>
+      <c r="B5684" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11631.psd</t>
+        </is>
+      </c>
+      <c r="C5684" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikt4ZDNvd0kwYVNiK3lMSUR2ck1RS1E9PSIsInZhbHVlIjoiYzQ0RmQ0a1liaStNYTIyeW43ZkpOQT09IiwibWFjIjoiNjM5ZmEwNmM2Mzk0YTM2ZGY1M2U1OWMyNTViZTU3YjIwMTNhMDdkZDZkZDU3MWE5MDBhZTI3ZDBkYzczODNiYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5685">
+      <c r="A5685" t="inlineStr">
+        <is>
+          <t>957.psd</t>
+        </is>
+      </c>
+      <c r="B5685" t="inlineStr">
+        <is>
+          <t>tamilpsd-11632.psd</t>
+        </is>
+      </c>
+      <c r="C5685" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNOemcvcHFkRzJtTnM0eURldmdXY0E9PSIsInZhbHVlIjoiTU1weW5hSTNabjZYOVViOHBNSExvQT09IiwibWFjIjoiMzAzOGUxMjU3ZDY4ZGEyYzIyYjg4ODI5ODZmOGM0NGVmNTAzYzI2OTczNDA3ZTllNmU3MTNiNGI3ZTUxNDM5ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5686">
+      <c r="A5686" s="3" t="inlineStr">
+        <is>
+          <t>956.psd</t>
+        </is>
+      </c>
+      <c r="B5686" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11633.psd</t>
+        </is>
+      </c>
+      <c r="C5686" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNxT0dUUFdPdVpLQlV6dEtJUEUzbGc9PSIsInZhbHVlIjoiSjFPdWZqYnpCazIySWI2ckk4eFFBUT09IiwibWFjIjoiMmNlN2FjZTdkN2MyMDA4M2M4YmEzNTkxYWIwZjdkNjQzMGRkZmRmZGVlZmRlZTZhZmM3ZjA0NWYxZmNkNTE1ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5687">
+      <c r="A5687" t="inlineStr">
+        <is>
+          <t>955.psd</t>
+        </is>
+      </c>
+      <c r="B5687" t="inlineStr">
+        <is>
+          <t>tamilpsd-11634.psd</t>
+        </is>
+      </c>
+      <c r="C5687" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktlK1JUUmZZSFFxWmVXcGJIb0FWSHc9PSIsInZhbHVlIjoiS2NjYkI3bk1kUlQwN1VyTlRlOXNhQT09IiwibWFjIjoiMzI3MGMxMzk4ZjYxZGIyNTBlZjBmYTg5NDI0NWFkZGUyNzA2MjUxMGM5YzRjNjYxODIyOTZjMWQwMzdlNTBlMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5688">
+      <c r="A5688" s="3" t="inlineStr">
+        <is>
+          <t>954.psd</t>
+        </is>
+      </c>
+      <c r="B5688" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11635.psd</t>
+        </is>
+      </c>
+      <c r="C5688" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikg3T3ZRVjJXMGJ2TEIwenU2TEZkNlE9PSIsInZhbHVlIjoiNEVSc1hxVGNiU20rTXdOeG43MEZBdz09IiwibWFjIjoiZThhYjcwZWViOWM4ODkxMDdkZTBmMGFkYTU2MzAwZmZhZmRhMTRiOGRhYzljMTcwZTViMjc4MzM3ZTFhMmRlNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5689">
+      <c r="A5689" t="inlineStr">
+        <is>
+          <t>951.psd</t>
+        </is>
+      </c>
+      <c r="B5689" t="inlineStr">
+        <is>
+          <t>tamilpsd-11636.psd</t>
+        </is>
+      </c>
+      <c r="C5689" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFkMWdVZk9pQ0g4V29uWlhoanJ5dHc9PSIsInZhbHVlIjoiREkrekJZeE5GZFlZYll5aEx2Z2QrQT09IiwibWFjIjoiOTU5ZWYzNjg0NWQxZThkMDliNGJjNGU2ODQwYjU0MDYzZTg0NWNkM2M4ODFlM2I2YmY3ZDJjYzExMzJiMmJkNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5690">
+      <c r="A5690" s="3" t="inlineStr">
+        <is>
+          <t>952.psd</t>
+        </is>
+      </c>
+      <c r="B5690" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11637.psd</t>
+        </is>
+      </c>
+      <c r="C5690" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNHbDl1MDB1ekdIa3labCtyQzZ6a2c9PSIsInZhbHVlIjoieXY3NHVIRG05ak1DYmpuSm9icktNUT09IiwibWFjIjoiODc5NDE0ZjViOWNiYjFmYTYxN2EyZDA2ZGE4YmZlODIxODdiYzlmN2M5MDk5ZDJmYjU0ODQyOGIxNTI2ZTljMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5691">
+      <c r="A5691" t="inlineStr">
+        <is>
+          <t>950.psd</t>
+        </is>
+      </c>
+      <c r="B5691" t="inlineStr">
+        <is>
+          <t>tamilpsd-11638.psd</t>
+        </is>
+      </c>
+      <c r="C5691" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilc0T2duQmh3VHZyWjFyL3NEUWU0MUE9PSIsInZhbHVlIjoia3E2UVVHTTZmeVlONWthM0t0RU9rZz09IiwibWFjIjoiODg5NmY3MjIxZDBiN2MwMjcwOWVkNmVhYmIzNzQxZTViMTY3MjU3NDViMjVkZmM2NzM0OTE1Yjk4NTEwZTM5MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5692">
+      <c r="A5692" s="3" t="inlineStr">
+        <is>
+          <t>949.psd</t>
+        </is>
+      </c>
+      <c r="B5692" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11639.psd</t>
+        </is>
+      </c>
+      <c r="C5692" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im0vZVE4UWd3aitRUzA4dHNGd3hDK2c9PSIsInZhbHVlIjoib29Oc0JRWHovNXVRMGo2V0hBMlU5dz09IiwibWFjIjoiOTI0MGRhNzA3NjIyMTIzZWIyMTczYmQ0NTMxYmZhNzUxZDhiNjE0NDczOTM1OTcxMjc5Mjc1ZDQxY2E0NDRiYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5693">
+      <c r="A5693" t="inlineStr">
+        <is>
+          <t>948.psd</t>
+        </is>
+      </c>
+      <c r="B5693" t="inlineStr">
+        <is>
+          <t>tamilpsd-11640.psd</t>
+        </is>
+      </c>
+      <c r="C5693" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Inc4NjFLSFZDcTB6M0lYb1ZpanRQcUE9PSIsInZhbHVlIjoicVI5dTZWTkFXQ2EwSnhlSVJGMlh1UT09IiwibWFjIjoiMWRjZTM2MDg5NTI5ZmFmNzg2MmI1ZDE1ODJjZWVlYjBhODY5OTFlNWNjNjdiODRiY2I1ZTIwZmRlODk1YTZkOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5694">
+      <c r="A5694" s="3" t="inlineStr">
+        <is>
+          <t>947.psd</t>
+        </is>
+      </c>
+      <c r="B5694" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11641.psd</t>
+        </is>
+      </c>
+      <c r="C5694" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjBnK3FJZ0FZa3E0ZUhlejAwZTg4aHc9PSIsInZhbHVlIjoiV2JGMGN5L1ovVWhlYW41aVpzbTA4dz09IiwibWFjIjoiZmVmMDM2ZmM0YzUwYzUzN2UzNDE3NTU3ZWQxY2YzOWEwOTUxMjY5MzlmN2E5MmZlNWIwNTc5ZGZhZDRiNDc5NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5695">
+      <c r="A5695" t="inlineStr">
+        <is>
+          <t>946.psd</t>
+        </is>
+      </c>
+      <c r="B5695" t="inlineStr">
+        <is>
+          <t>tamilpsd-11642.psd</t>
+        </is>
+      </c>
+      <c r="C5695" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imk2b2NERG1UL1NoSVZtNld1b0xlS1E9PSIsInZhbHVlIjoieUZHOVJqTjFxbTFMaWhnNU9UbitvQT09IiwibWFjIjoiY2Q4ODhkYjVhNDRlMjJkZmQ3MzM1NmRiODI3NDhmNjljN2Y1ZTk5ODc4YTk2YTllMDJjODBkNDk4OWJiODQ2YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5696">
+      <c r="A5696" s="3" t="inlineStr">
+        <is>
+          <t>945.psd</t>
+        </is>
+      </c>
+      <c r="B5696" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11643.psd</t>
+        </is>
+      </c>
+      <c r="C5696" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtsdkpYcWh3NzhaN0NFQ1ZvQ2xpNWc9PSIsInZhbHVlIjoiUlpzOW5yQnE0WCtuNlpubDZhamZHZz09IiwibWFjIjoiOTkwNTU0YjU3MzhjN2YyZTg2YmE3Y2I1OTljYjNlYTBiZmY5M2FlY2NlODEwMmNjMDg1NGQ2YWQ3ZjZjZjE1ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5697">
+      <c r="A5697" t="inlineStr">
+        <is>
+          <t>944.psd</t>
+        </is>
+      </c>
+      <c r="B5697" t="inlineStr">
+        <is>
+          <t>tamilpsd-11644.psd</t>
+        </is>
+      </c>
+      <c r="C5697" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZmNlptK1FVWFJFRlNEQUpwU3VBMEE9PSIsInZhbHVlIjoiMUkwZUhMNE0vVDlRbW1yRFhUSXVFQT09IiwibWFjIjoiYzQwYzRjMmZhNTU1ZDAyNDgwMzQ1NTI4YWIyMGRhNzhjMWVhY2NmMGM2N2QxZWYxN2NkZjQzNjkzZTRmOWUyNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5698">
+      <c r="A5698" s="3" t="inlineStr">
+        <is>
+          <t>943.psd</t>
+        </is>
+      </c>
+      <c r="B5698" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11645.psd</t>
+        </is>
+      </c>
+      <c r="C5698" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklTa2FjRTg4enV4elZlV0lmaEMrQ2c9PSIsInZhbHVlIjoiRTJNNmRoUEV6NzI0bVVvVUx1WGNaZz09IiwibWFjIjoiYTI2ODNmYWRkOWQwYzI0NjU4NjliNmQ4NWViMTAwNWQzMjk3Y2NmNjAyYWEyM2E0MTYyODExNjhiN2U1MDQ1MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5699">
+      <c r="A5699" t="inlineStr">
+        <is>
+          <t>942.psd</t>
+        </is>
+      </c>
+      <c r="B5699" t="inlineStr">
+        <is>
+          <t>tamilpsd-11646.psd</t>
+        </is>
+      </c>
+      <c r="C5699" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRWdU5XOVI1MlozQVN2WisyOVpZTlE9PSIsInZhbHVlIjoidWtmdldaYlBKN2FYYlU2REtLVkhidz09IiwibWFjIjoiZGMxZWU5YWI4MjhlMjAyNjRkM2ViMGNjMGMyNDcxYjRiNDI2NWU0MWQ0OTAzY2UyNzhiYzRiYmZlYzUzYWMxYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5700">
+      <c r="A5700" s="3" t="inlineStr">
+        <is>
+          <t>941.psd</t>
+        </is>
+      </c>
+      <c r="B5700" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11647.psd</t>
+        </is>
+      </c>
+      <c r="C5700" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imt3NUtOMzZBZjV4OHNtZXAxM0szMlE9PSIsInZhbHVlIjoiQktrbHVDUG4vZVBKZStUZXM3Tk5zdz09IiwibWFjIjoiM2ZiZDI2OTQxMjY5OWE1MDdhYmYwZjFmM2VlMjYzNjgwNjlhMTZiYzY3OGYxNDMwODFhNzAwMzAzMTdiYjRiOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5701">
+      <c r="A5701" t="inlineStr">
+        <is>
+          <t>940.psd</t>
+        </is>
+      </c>
+      <c r="B5701" t="inlineStr">
+        <is>
+          <t>tamilpsd-11648.psd</t>
+        </is>
+      </c>
+      <c r="C5701" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im1RMlBIQ2dLdnYwNUtDZGRpVyt4L2c9PSIsInZhbHVlIjoid2tXWVRCekJVTnpYcUNVWkVMVDl2dz09IiwibWFjIjoiOGEyOTc1ZWM2MTY0OGZlNTFkZmM0ZjNhM2Y4ODY0NDhiNTQzNDUyNGEyZGM4MGIzMmMzZmJhMGU2N2Q0NmVjZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5702">
+      <c r="A5702" s="3" t="inlineStr">
+        <is>
+          <t>939.psd</t>
+        </is>
+      </c>
+      <c r="B5702" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11649.psd</t>
+        </is>
+      </c>
+      <c r="C5702" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRrU2d6YmRaOG5RTXRjdUdrdU5YWGc9PSIsInZhbHVlIjoiR09BTGFQcWRGK1Q0b3Bzb0tRM2pmZz09IiwibWFjIjoiNTRmOGI5OGQ3OWNkZWJjMDVkMDEwYjljYTM2ODNlNDk3NGJjZDE4MDk4MzMzMjViNzY5NTI1MWJjZmYyNDZmYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5703">
+      <c r="A5703" t="inlineStr">
+        <is>
+          <t>938.psd</t>
+        </is>
+      </c>
+      <c r="B5703" t="inlineStr">
+        <is>
+          <t>tamilpsd-11650.psd</t>
+        </is>
+      </c>
+      <c r="C5703" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjQ0cEdra2NFNy92dG5EZU5qWjgxQkE9PSIsInZhbHVlIjoiODZhakhadG91cTJqcVlLczczcnZFUT09IiwibWFjIjoiNWUzMWEzN2E5MzE5OTcwODZkZTY3YjgzZjA5NjhkZTZlMzY3ZmVkM2I2MGQzZWYwOWQ5YTIzYzBlMTU1OWUwYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5704">
+      <c r="A5704" s="3" t="inlineStr">
+        <is>
+          <t>937.psd</t>
+        </is>
+      </c>
+      <c r="B5704" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11651.psd</t>
+        </is>
+      </c>
+      <c r="C5704" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZaQUxURzFQMzdJYWY3dFNINzNMVGc9PSIsInZhbHVlIjoic0tQZ01FbUJTZDdROEpIWTlwY1Jpdz09IiwibWFjIjoiOWExNWQ0OTgwYTg3OTVlZjFhNmVkNjE5Yzc3MmEyMGNjMzk2ZjJmYTUzODZlNjVjNWJkOTNmYjYyZGZjOTI2NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5705">
+      <c r="A5705" t="inlineStr">
+        <is>
+          <t>936.psd</t>
+        </is>
+      </c>
+      <c r="B5705" t="inlineStr">
+        <is>
+          <t>tamilpsd-11652.psd</t>
+        </is>
+      </c>
+      <c r="C5705" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikd5VVdxNW1Oc1ptcW9tQUlGNE9yVUE9PSIsInZhbHVlIjoiZml4ZUNnNE55SjgzKzNZakhadktlZz09IiwibWFjIjoiMzk1YjcxMjhmNThhNGNkNGM5ZDE3ZTg2YmQxYWI2NDVhNzYzNTNjYTVjYWNmODQzMDQ0ZmU2MWQ5MjUzZjcyOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5706">
+      <c r="A5706" s="3" t="inlineStr">
+        <is>
+          <t>935.psd</t>
+        </is>
+      </c>
+      <c r="B5706" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11653.psd</t>
+        </is>
+      </c>
+      <c r="C5706" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhKaFZ3bVNFb0VOcHg1UnhUSWRQTlE9PSIsInZhbHVlIjoib3o5bFE2ajBkbytKN1FKcmU1eFBRQT09IiwibWFjIjoiN2Y5MTQ3NDY4NzRjNzQ1MWE1ZDVkN2EyN2YxMDhmYzM2NWQwZTU2YTJmZTVkNmM2ZWU1MDc5N2E4ZTQyN2U1NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5707">
+      <c r="A5707" t="inlineStr">
+        <is>
+          <t>934.psd</t>
+        </is>
+      </c>
+      <c r="B5707" t="inlineStr">
+        <is>
+          <t>tamilpsd-11654.psd</t>
+        </is>
+      </c>
+      <c r="C5707" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVHc1NwTU1rMXFLT1k0T3V2YUJxZlE9PSIsInZhbHVlIjoiSmZZck4wMWZONzlaRzFJeHYydG43dz09IiwibWFjIjoiOTFiNTA0ZjIxNTJkYjI4ZjE5ODRiOWI3OTRjNGQ1M2NjNmRlZDJmNWRhNTMwMjViZjFiZGMzZDZhOGNlOWNhNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5708">
+      <c r="A5708" s="3" t="inlineStr">
+        <is>
+          <t>933.psd</t>
+        </is>
+      </c>
+      <c r="B5708" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11655.psd</t>
+        </is>
+      </c>
+      <c r="C5708" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhvZFZNOHJWb2lOK3BBZVdLTW1KK0E9PSIsInZhbHVlIjoiWTdTSkZrOCtmM29oSGV5V2xsa1BKUT09IiwibWFjIjoiNWJlMDU3NTY1OGM3ZGEzNWQ3ZDEwZjY2YjhmNWIxYzA0ZDBlMGZjZmU3NmUyYmJlNTY3NDA4M2IxN2U0MzE0MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5709">
+      <c r="A5709" t="inlineStr">
+        <is>
+          <t>932.psd</t>
+        </is>
+      </c>
+      <c r="B5709" t="inlineStr">
+        <is>
+          <t>tamilpsd-11656.psd</t>
+        </is>
+      </c>
+      <c r="C5709" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNzcEo2UlBvdjVZUThSVlVEMk5LUFE9PSIsInZhbHVlIjoiMm5kd29mdHRnckhURmFBZC9TSTA3QT09IiwibWFjIjoiODYyMjA1NzAyMWQwMTE4YzVmZTJjMDVkZDIzODI1YzgxZDI2YzUzOGIzNDg2YTQwODI1YmFjODRlNTZmOTQyZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5710">
+      <c r="A5710" s="3" t="inlineStr">
+        <is>
+          <t>931.psd</t>
+        </is>
+      </c>
+      <c r="B5710" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11657.psd</t>
+        </is>
+      </c>
+      <c r="C5710" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhCV3FlU2hTTXZxNFVnUHFNR2R3RFE9PSIsInZhbHVlIjoiR3FuK1ArdzI3TlY5ditKN0oyc0J0QT09IiwibWFjIjoiODYzNGM4NjBkZDYzNjBiMjU1Njk1MTg3YWExNDEyNzNjZjk2ZDE1NTlmYWI3Y2VjZTY2Nzk4OTBhZmJjYWJhNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5711">
+      <c r="A5711" t="inlineStr">
+        <is>
+          <t>930.psd</t>
+        </is>
+      </c>
+      <c r="B5711" t="inlineStr">
+        <is>
+          <t>tamilpsd-11658.psd</t>
+        </is>
+      </c>
+      <c r="C5711" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im40R240bVhlZ2dVMFFDT1NvcHc2aXc9PSIsInZhbHVlIjoiSjUrU2preko2czRRUTBFYi8yT25FUT09IiwibWFjIjoiZDQ4ZjZmNDE3YmM2ZjRjYTZiM2Q2ZDVhMjQyY2JmMDE5NjNjOGUyMGVlOGE4ODg3YmFkMjAwMTg3ODg2OTYwMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5712">
+      <c r="A5712" s="3" t="inlineStr">
+        <is>
+          <t>929.psd</t>
+        </is>
+      </c>
+      <c r="B5712" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11659.psd</t>
+        </is>
+      </c>
+      <c r="C5712" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ilg5ZWc1MkpyNG9VeGNYaVNrcHUxdFE9PSIsInZhbHVlIjoiQko1N2h5UDFLeXRFMkNhNFdEdE9ldz09IiwibWFjIjoiMzdmMDEyYmJkYmI0MzYwOWU0MTY5ODlmY2Q5NjM1YzEzM2E1YWMyMjAwNDE4NDUzODdlMzg2M2ZiMDcyYTI2ZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5713">
+      <c r="A5713" t="inlineStr">
+        <is>
+          <t>928.psd</t>
+        </is>
+      </c>
+      <c r="B5713" t="inlineStr">
+        <is>
+          <t>tamilpsd-11660.psd</t>
+        </is>
+      </c>
+      <c r="C5713" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InBXc1NVeExoZFhCTGEwT0pzNzg0cFE9PSIsInZhbHVlIjoid1p6d2NaMktiZEk2ek9yU1hkZk1rdz09IiwibWFjIjoiMTg5ODY0MzAwYzc5NTkwMDNhY2VkOWMyNGVmN2VkYWMzYjExODdkMjFkMzg3MjJjMDU5Njg1OTkzMzY5ZjIyYiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5714">
+      <c r="A5714" s="3" t="inlineStr">
+        <is>
+          <t>927.psd</t>
+        </is>
+      </c>
+      <c r="B5714" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11661.psd</t>
+        </is>
+      </c>
+      <c r="C5714" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InRWYlZiZnBOU2phcGFxU3I1R1hscHc9PSIsInZhbHVlIjoiYmx6c09jdFkyc3Y1TnBiUjNjZVBkdz09IiwibWFjIjoiZGJlZmIxMGI4ZDc4OTNjZTU0YTQ3MzdlYTliOGVkNWQ0N2IyYmQzZDkwODBkOTU0ZTM5ODU3YmVlYTQwZmQ0NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5715">
+      <c r="A5715" t="inlineStr">
+        <is>
+          <t>926.psd</t>
+        </is>
+      </c>
+      <c r="B5715" t="inlineStr">
+        <is>
+          <t>tamilpsd-11662.psd</t>
+        </is>
+      </c>
+      <c r="C5715" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImNrTGZjOWhqU0RZNTB6VFk3ZXhVN0E9PSIsInZhbHVlIjoielBQNVprc09iZDRYbW5RQndKN0pUUT09IiwibWFjIjoiYzRjYjdmOTY5OTA3NDlkOTNiYWY5YzU2MThmNTQzMjM3YWU0NThiMzAwZjA4OTNlM2JkNGI0NTAwY2Y2YjNmMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5716">
+      <c r="A5716" s="3" t="inlineStr">
+        <is>
+          <t>925.psd</t>
+        </is>
+      </c>
+      <c r="B5716" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11663.psd</t>
+        </is>
+      </c>
+      <c r="C5716" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhuZW8wblkyME5yVDJBckVCMzRVa0E9PSIsInZhbHVlIjoiWjdsMXNPcHdkWWhaZ2FzbGl4RlNPZz09IiwibWFjIjoiZmEyZGE5YzU4MTYzNzVhM2ZkNDcwNzkxNzc1MDgwMmE3MmU4ZjNiZTIxMTg2ZDExYzU0MDczOGYwYTAxMjU4MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5717">
+      <c r="A5717" t="inlineStr">
+        <is>
+          <t>923.psd</t>
+        </is>
+      </c>
+      <c r="B5717" t="inlineStr">
+        <is>
+          <t>tamilpsd-11664.psd</t>
+        </is>
+      </c>
+      <c r="C5717" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Inl6SWI5cGNyVkU3Y3JmaGZMd0hHcmc9PSIsInZhbHVlIjoiMndrMElQVjFMckl6U0pjVGgxYXhidz09IiwibWFjIjoiNjU4MjM3M2YwMjQ2ZDZkYTQ5ODY3OTE1MTQ1MGZkMjExMTU4M2Y2ZjVjYThlZmZjY2M2ZjlmYjNhZWFjNmQ2ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5718">
+      <c r="A5718" s="3" t="inlineStr">
+        <is>
+          <t>922.psd</t>
+        </is>
+      </c>
+      <c r="B5718" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11665.psd</t>
+        </is>
+      </c>
+      <c r="C5718" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhQVEVyNUUweHFFMWhwelM3SVR3NkE9PSIsInZhbHVlIjoiWjJaK2gvR1duVFYwTWN5bG1hV0pYQT09IiwibWFjIjoiOGRkZTc2NTE0ZjZhNThiODFhMTM1Mzg4ZmJkOGE3MTNiYmFmYjFmNGFkZWQ5ZmJlZWQ0NzEwY2U1YmI2N2FkZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5719">
+      <c r="A5719" t="inlineStr">
+        <is>
+          <t>921.psd</t>
+        </is>
+      </c>
+      <c r="B5719" t="inlineStr">
+        <is>
+          <t>tamilpsd-11666.psd</t>
+        </is>
+      </c>
+      <c r="C5719" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllNc3ZtTURsUFVwclZmUURGWS91S0E9PSIsInZhbHVlIjoiUTYxZW84aEdqdnFER2t3S3JScHM5dz09IiwibWFjIjoiZWI4Y2MxY2VjMmJkZDQ1MWE0NTZlZDA0MGM5MzcwZTcyNjgxYjQxOTY1NmI1YjdjOTFlMzBiNzBiYjBlMTdkMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5720">
+      <c r="A5720" s="3" t="inlineStr">
+        <is>
+          <t>920.psd</t>
+        </is>
+      </c>
+      <c r="B5720" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11667.psd</t>
+        </is>
+      </c>
+      <c r="C5720" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRaMnE2K3FTekhrYm9HcE91YmVHUlE9PSIsInZhbHVlIjoiREdqY0FUeHdFQzZ6N1UvTG1TSnM0UT09IiwibWFjIjoiNGNiNWQ1ZTE2ZjZmZDA0YWFjYjBmY2E5MDUzZDcxMDU5ZjVjN2Q3ZjliZGMyZmFhMTM4YTVkNjUwZDgyMDQ0NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5721">
+      <c r="A5721" t="inlineStr">
+        <is>
+          <t>919.psd</t>
+        </is>
+      </c>
+      <c r="B5721" t="inlineStr">
+        <is>
+          <t>tamilpsd-11668.psd</t>
+        </is>
+      </c>
+      <c r="C5721" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkNpYTFGRzRxWXhwZXdsZmt4b1hrclE9PSIsInZhbHVlIjoiS3RJb0c0dEFmMkU3MHNNK2pWNzIxZz09IiwibWFjIjoiYjkyODJlODE0MzMxODNiNmY2NDAzZWJhNjQxNjA4NmJiYzk4Y2ZmNjk2NTUxNzg0YWIxYTIzMGVhYmI5YjAzZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5722">
+      <c r="A5722" s="3" t="inlineStr">
+        <is>
+          <t>918.psd</t>
+        </is>
+      </c>
+      <c r="B5722" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11669.psd</t>
+        </is>
+      </c>
+      <c r="C5722" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlZsb0xraDQ2aGluUlpNMUJ3K3VBN3c9PSIsInZhbHVlIjoiMWhXTEpvdzlBR2JNN1llT2R3WVE1UT09IiwibWFjIjoiZWNhM2Y5MTNmNzcyMmM3MDcyOTExNTJhY2NhMGQ0MjJiMTM1MTI1MGZlODAyODg3Y2QyMDRiYmQxOTNlYjM3OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5723">
+      <c r="A5723" t="inlineStr">
+        <is>
+          <t>917.psd</t>
+        </is>
+      </c>
+      <c r="B5723" t="inlineStr">
+        <is>
+          <t>tamilpsd-11670.psd</t>
+        </is>
+      </c>
+      <c r="C5723" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVKbkNLSTlaSzNjWGRtMTZzNlFqU0E9PSIsInZhbHVlIjoiRDY1cWQ3RHJ2aUpKS0lWOFUwMDJxUT09IiwibWFjIjoiODA4Y2U3NTMzYTQ4ZDM0OTgwYThjZmY5ZGZhNjU2OTUwZTA1OGNiZWM3OTczYmZhNWEyN2IwOTBhYmU1MzM4YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5724">
+      <c r="A5724" s="3" t="inlineStr">
+        <is>
+          <t>909.psd</t>
+        </is>
+      </c>
+      <c r="B5724" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11671.psd</t>
+        </is>
+      </c>
+      <c r="C5724" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFQMStQb2R2c1JlcnphZEZpRXJlZEE9PSIsInZhbHVlIjoiMWNEdGhBUEluakdkNTJqU21nQmlOUT09IiwibWFjIjoiMzgwMzhiM2QzMjVmOTM1YmE4MGFiNjRmOWNiMmJhNWJhMDJjYTRhNTBlNWQ0NjA5NjZiOWYyOTIyYjM3N2FhNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5725">
+      <c r="A5725" t="inlineStr">
+        <is>
+          <t>908.psd</t>
+        </is>
+      </c>
+      <c r="B5725" t="inlineStr">
+        <is>
+          <t>tamilpsd-11672.psd</t>
+        </is>
+      </c>
+      <c r="C5725" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFZNVlZWElGbHhSYm04em9GNVVFQWc9PSIsInZhbHVlIjoiT2FlZXczb1A0NFRlbll5cTdBZGRHQT09IiwibWFjIjoiYWNmYjIzMzk1MzY1ODA3NWM5YWExMDA1NDdiNDM2NDFkZGMzYTUyNmVkNGEzNjQxZGUyMDQ3YmFhZWE2ZjFlMyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5726">
+      <c r="A5726" s="3" t="inlineStr">
+        <is>
+          <t>907.psd</t>
+        </is>
+      </c>
+      <c r="B5726" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11673.psd</t>
+        </is>
+      </c>
+      <c r="C5726" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlBRYmJRYTNxZTVCL21QcmRSY29XTVE9PSIsInZhbHVlIjoiaEp2UFp2M3lzaTBkQ0EwL3lDR1JhZz09IiwibWFjIjoiN2JmZjI5MWM1NjA3NmU2NjQ4OTMzM2RkNDQ5NTQyOWRmN2QwMjQ3Njk4Yzc3YzdkNjc0NDIwNmQ0NjA3MmE1NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5727">
+      <c r="A5727" t="inlineStr">
+        <is>
+          <t>906.psd</t>
+        </is>
+      </c>
+      <c r="B5727" t="inlineStr">
+        <is>
+          <t>tamilpsd-11674.psd</t>
+        </is>
+      </c>
+      <c r="C5727" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkhUQlBIejltVU0yQlZyOFpCSTRyYmc9PSIsInZhbHVlIjoieW1IMXpuMWUwdFhCeXJpNlh5eDJaUT09IiwibWFjIjoiYzYyMzM5ZWE0YWI4OGQ5OWFiZTk5N2UxNjc4ZmIwZDc4MThmNzI5MTVjMmRhMDJmMTFlM2FkZGJhNzRkNTM0OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5728">
+      <c r="A5728" s="3" t="inlineStr">
+        <is>
+          <t>905.psd</t>
+        </is>
+      </c>
+      <c r="B5728" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11675.psd</t>
+        </is>
+      </c>
+      <c r="C5728" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im0rTlo5NGFaczFXaGpJYkxaaENhVEE9PSIsInZhbHVlIjoibVNlRlFZZDRhc0ExS3kzMUhMYTZuZz09IiwibWFjIjoiNmFlYmMyMDA5ZTQ4OWYyNDFkNmJiN2E4NTY4NjRiNjQxN2JjNjQ5YWQzNDMzZjA0ZDEyZWVmOTUxODgzOGEwNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5729">
+      <c r="A5729" t="inlineStr">
+        <is>
+          <t>904.psd</t>
+        </is>
+      </c>
+      <c r="B5729" t="inlineStr">
+        <is>
+          <t>tamilpsd-11676.psd</t>
+        </is>
+      </c>
+      <c r="C5729" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImdQN2dRSEZRTDAvayt2bURBVWs5cmc9PSIsInZhbHVlIjoiLzZxUWI4a01jWHJSbnNMSjY4VVhrdz09IiwibWFjIjoiNTMwMDQ0ZTllZjE1NDM2NjJiN2Q4MzY0N2M2NDA3MTJiMmY1NjcyZWNiNGY5ZjE4MzkzODEyZjc1YzNmM2Q5NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5730">
+      <c r="A5730" s="3" t="inlineStr">
+        <is>
+          <t>903.psd</t>
+        </is>
+      </c>
+      <c r="B5730" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11677.psd</t>
+        </is>
+      </c>
+      <c r="C5730" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlDdjJnMEtRMHdYSlhmQ0ZCbHk3Rnc9PSIsInZhbHVlIjoic0JaV1ptdmNVMGFlTHh4SHBhNGRJZz09IiwibWFjIjoiN2E3MjM0ZjMxMDdiZmE3YjA4ZGQ4NjM5MzllNjNmNWQ4NDUyNTYxOGJlMDhlMGJjNmZlNmQ1MjZiZGVhOWJjMSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5731">
+      <c r="A5731" t="inlineStr">
+        <is>
+          <t>902.psd</t>
+        </is>
+      </c>
+      <c r="B5731" t="inlineStr">
+        <is>
+          <t>tamilpsd-11678.psd</t>
+        </is>
+      </c>
+      <c r="C5731" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IklMbHNyRHRNQk9tV1pmbzFNdCtmeHc9PSIsInZhbHVlIjoiOGxhRkNlcWpPN1pxQURROXV0VTVoUT09IiwibWFjIjoiNzNlNzA1Njg5N2IwZDY5NTk3MmE5M2M0ODEwYWFjMTY3YWQ1YmZmYmE0MjkzNWI0YTgyMjdkNDZkYmUwMTAwZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5732">
+      <c r="A5732" s="3" t="inlineStr">
+        <is>
+          <t>901.psd</t>
+        </is>
+      </c>
+      <c r="B5732" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11679.psd</t>
+        </is>
+      </c>
+      <c r="C5732" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkhnYlR5S1QwaXVOeVMyZm1iTGsxMkE9PSIsInZhbHVlIjoidk5iNWhUcVdqd3FhM2NqeEwyL2YzZz09IiwibWFjIjoiYThmOTgzN2U4NDhmNzZiY2I0NDIwMzZkMGI0ZWM3OTI1MGVmZWM1ZDMxZTQ3ZWFjOThjZjdkMjRiZWE0YWUzOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5733">
+      <c r="A5733" t="inlineStr">
+        <is>
+          <t>900.psd</t>
+        </is>
+      </c>
+      <c r="B5733" t="inlineStr">
+        <is>
+          <t>tamilpsd-11680.psd</t>
+        </is>
+      </c>
+      <c r="C5733" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlhOTJZYUZYbWxZWmlUb2dqeWRJR2c9PSIsInZhbHVlIjoieVJyOG1iSzk2MStFK3k0RHAyYjRSQT09IiwibWFjIjoiYzA5MDUyNDFjNWI4NGVhMGU5NTU0Y2EyNzQwMWQwZDNhZDNmM2MzNWY1ODQ3ZDkyMTc2OGY4NzUxOTRjOTJkOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5734">
+      <c r="A5734" s="3" t="inlineStr">
+        <is>
+          <t>899.psd</t>
+        </is>
+      </c>
+      <c r="B5734" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11681.psd</t>
+        </is>
+      </c>
+      <c r="C5734" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhaaFFuaytFL3hZTXdoNjF1aGFXakE9PSIsInZhbHVlIjoid09vVFI0MlE5UW5LMXIxa240V2lTdz09IiwibWFjIjoiYmJhMTI2M2IxNzQ0NzliYjFlMjJjMjNiYzQwMmUzMTkzMmUwMmI0NjI3ZjZiOGUwZDg5NGY1MDAxOGE1Y2JhYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5735">
+      <c r="A5735" t="inlineStr">
+        <is>
+          <t>898.psd</t>
+        </is>
+      </c>
+      <c r="B5735" t="inlineStr">
+        <is>
+          <t>tamilpsd-11682.psd</t>
+        </is>
+      </c>
+      <c r="C5735" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlRJMEdTWmlZQURWTUlwa29sa1lqdUE9PSIsInZhbHVlIjoiZFEvbDExNnVzY2wxbVBBNEFBblNSZz09IiwibWFjIjoiOGVlNjE5ZDNhOTM4MzE3ZTAzMzA3MzYyOWFlODViYmQ0YzNkYWU0NGM1Mzg4MGVmNDIwNGMyOTVhNzNkNWY1OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5736">
+      <c r="A5736" s="3" t="inlineStr">
+        <is>
+          <t>897.psd</t>
+        </is>
+      </c>
+      <c r="B5736" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11683.psd</t>
+        </is>
+      </c>
+      <c r="C5736" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IldSSDVuREFBUUJBbkVRRzFYUjhXSHc9PSIsInZhbHVlIjoieFFOTDlTM3hqY1N0dFkwTUFnZ09Rdz09IiwibWFjIjoiODVlN2NmY2MzODE4YTA1ODFkNzEzNDZjM2MzODk3MDMyZWUxZjM3ZWYyNTVjYjMxYTBlNDkxM2U4YTdhZDdiYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5737">
+      <c r="A5737" t="inlineStr">
+        <is>
+          <t>896.psd</t>
+        </is>
+      </c>
+      <c r="B5737" t="inlineStr">
+        <is>
+          <t>tamilpsd-11684.psd</t>
+        </is>
+      </c>
+      <c r="C5737" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImQvQWFjZkJ4R3hUSGtvU0dsNWdsdHc9PSIsInZhbHVlIjoiMGN2dUQxRStYUWhGOFF5N25DY2dlQT09IiwibWFjIjoiOGY4MTI4Y2UzYWE0MDJmYzQ1YTA4ZTRmNzA5Y2VjY2U2YzkwOWRlZmMxNDYwODRkYjQ0NmQyMGI0ZjY5YTg2MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5738">
+      <c r="A5738" s="3" t="inlineStr">
+        <is>
+          <t>895.psd</t>
+        </is>
+      </c>
+      <c r="B5738" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11685.psd</t>
+        </is>
+      </c>
+      <c r="C5738" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImZJYTRFTHBjOXRZbmRuY081eWZra1E9PSIsInZhbHVlIjoiZ1ZBU3BuS2ZOT1ozT0dQLy9mNk5ZZz09IiwibWFjIjoiYmI0MDlkZThmODYwNjBlZTM0YjI1ZmY0NGYzMjA5MWRiMWQyZTcyNTE4MTY3OGQyMTBjYjM1YTA3ZjU0NGY1MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5739">
+      <c r="A5739" t="inlineStr">
+        <is>
+          <t>894.psd</t>
+        </is>
+      </c>
+      <c r="B5739" t="inlineStr">
+        <is>
+          <t>tamilpsd-11686.psd</t>
+        </is>
+      </c>
+      <c r="C5739" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVyTjBOMUFiVTg0OWZENXVJTUNLc3c9PSIsInZhbHVlIjoiUnNQVUZyNDNIK1NJOWNtTit1WUpQUT09IiwibWFjIjoiYzAyMDU1MDNjMjFhNWQ3NjI5YWZkYzNiMjVkYTc2MWQwNDM3MDNlNmQ4MDMxYTc5NzNjNjQxOGJiMjA3Y2M0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5740">
+      <c r="A5740" s="3" t="inlineStr">
+        <is>
+          <t>893.psd</t>
+        </is>
+      </c>
+      <c r="B5740" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11687.psd</t>
+        </is>
+      </c>
+      <c r="C5740" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVoQng5dlJmVmJPKzZMU0pIc3RtZXc9PSIsInZhbHVlIjoiVStkZllCenZsaWk1dVZDdzRTRXUwZz09IiwibWFjIjoiODZlODc2Nzg5MWI5YjViZWJhYjgyNTU0YzY2NDVkYTYzYjU5OWZjYTZjNTg0NmMyNzY1Y2NhZTBiZmJmZDUzMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5741">
+      <c r="A5741" t="inlineStr">
+        <is>
+          <t>892.psd</t>
+        </is>
+      </c>
+      <c r="B5741" t="inlineStr">
+        <is>
+          <t>tamilpsd-11688.psd</t>
+        </is>
+      </c>
+      <c r="C5741" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkVGMnE0eFlSekJSWVpTNjBUZzFVSEE9PSIsInZhbHVlIjoiOXZ5cEFOZFpXNEFFMzFXd0g5ZVBsdz09IiwibWFjIjoiYjZiYTA4MGYzMmRjNjRhNzcwOTRkYjU0ZDg2MWQ0NDFkYTU3YjQzNjE2ZDU0ZTA3ZWYwNDU1YjdiMzU3YzkwZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5742">
+      <c r="A5742" s="3" t="inlineStr">
+        <is>
+          <t>890.psd</t>
+        </is>
+      </c>
+      <c r="B5742" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11689.psd</t>
+        </is>
+      </c>
+      <c r="C5742" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhUc1ZTSS92WXFZR0wzRnJ2eTBoanc9PSIsInZhbHVlIjoiRXVtMjNhOVpReFJWaFRvTUtnaDVVdz09IiwibWFjIjoiMGNjNDhjZTYzNzhhZDI0ZTgwMjczN2Q5MzE2YmZmZmUwOWEzYjIwOWU3N2UzMDNmZTZkNjZmMTY5OTNjYTQzZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5743">
+      <c r="A5743" t="inlineStr">
+        <is>
+          <t>891.psd</t>
+        </is>
+      </c>
+      <c r="B5743" t="inlineStr">
+        <is>
+          <t>tamilpsd-11690.psd</t>
+        </is>
+      </c>
+      <c r="C5743" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IngzcnpxVGlwdjhCNHRXUmliOWQwMWc9PSIsInZhbHVlIjoiV3ViZjVIR2FBY2F4V0NlUTdWNm5UZz09IiwibWFjIjoiNTIxNzA1NDRiODIwMDhiNTcyZWFkNjYyNGVmOWEzNTA0Y2M1YjBmNjgzMzBlNjcyMjgxNzFiNThjYmNhODQ0NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5744">
+      <c r="A5744" s="3" t="inlineStr">
+        <is>
+          <t>889.psd</t>
+        </is>
+      </c>
+      <c r="B5744" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11691.psd</t>
+        </is>
+      </c>
+      <c r="C5744" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImJmdGYraXJCUkZsekowbEFHZUdPYWc9PSIsInZhbHVlIjoiayt2dzM1bEtXdUZraFFIZHN0aW9kQT09IiwibWFjIjoiN2IwYjBhZTdhZDAyZjAwNjZjZTk2OTBiMDgwMjlhMDlmNjE5N2E3Mjc5ZGY3YTllOTAwY2VkNjMwYzhkMzk1OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5745">
+      <c r="A5745" t="inlineStr">
+        <is>
+          <t>887.psd</t>
+        </is>
+      </c>
+      <c r="B5745" t="inlineStr">
+        <is>
+          <t>tamilpsd-11692.psd</t>
+        </is>
+      </c>
+      <c r="C5745" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imw4TGM5cC9oNWNKNFFSeERzOEV2cFE9PSIsInZhbHVlIjoiMzNGM21zb2xyTVdFZHZaSGlGaDNGUT09IiwibWFjIjoiMTNkYzg3YjEwOGY4ZTZmOGM5M2YwNTE5NjhlZGFmOTI2MzAwOGQ3NzJjMDBhNjY0YTlmZmNiYjBjZjkyZmU1MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5746">
+      <c r="A5746" s="3" t="inlineStr">
+        <is>
+          <t>886.psd</t>
+        </is>
+      </c>
+      <c r="B5746" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11693.psd</t>
+        </is>
+      </c>
+      <c r="C5746" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImtjbjUwaEthdXJkNUdWZVgwZHRiWHc9PSIsInZhbHVlIjoiZWppcXZVdXQ5blBPS2s4Wm4zVEl0Zz09IiwibWFjIjoiOGRjYjc5M2I4ZWNkODNiMzhiNzhiYWYyYzc5YzU1ZGFlMTZiZTAxMDg2MjYyMjMxMWYyNTA2YWNlYTE4NDcwNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5747">
+      <c r="A5747" t="inlineStr">
+        <is>
+          <t>885.psd</t>
+        </is>
+      </c>
+      <c r="B5747" t="inlineStr">
+        <is>
+          <t>tamilpsd-11694.psd</t>
+        </is>
+      </c>
+      <c r="C5747" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImpKOGdCaDU1dmFOY0QwRk9ycWVmOXc9PSIsInZhbHVlIjoiWXFKRXhjaXczTnpyeDQzUklubGsxdz09IiwibWFjIjoiNDYzODQ1NDE0MjUxMmUwZGNlNDlmY2UzYzgxOTI3ZmY4OTJmODY1MGQ5MzJkMjFhZDA4Y2VhMjJiM2MwYjgxZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5748">
+      <c r="A5748" s="3" t="inlineStr">
+        <is>
+          <t>884.psd</t>
+        </is>
+      </c>
+      <c r="B5748" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11695.psd</t>
+        </is>
+      </c>
+      <c r="C5748" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im44K1BjdkU5cnBUN3B3VVFXUnR0eVE9PSIsInZhbHVlIjoidDU1RXZjVFFCNkl1VUIyQURQTytsdz09IiwibWFjIjoiYzgyZGM4MzBlM2ZiNDZkMTBhMjViZWVlMWFiZTU3NzkzMTdlMzk0ODYyYWJjMjQwMDA4OWE5ODNhZjY0MTk4YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5749">
+      <c r="A5749" t="inlineStr">
+        <is>
+          <t>883.psd</t>
+        </is>
+      </c>
+      <c r="B5749" t="inlineStr">
+        <is>
+          <t>tamilpsd-11696.psd</t>
+        </is>
+      </c>
+      <c r="C5749" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjRDTm9rRjFuNHNwNUFlbVM0MUtFYUE9PSIsInZhbHVlIjoiQXNPWVRKakVBckFqVTAzcVpPbDJjZz09IiwibWFjIjoiMmQ4ZDExMTZhZDQ2YTc5YTMwNzc4YjQ0OTg0MjU4NDcwZDliYjg2ZWFiOTg1ZTE1MzllMTE5MmE1MTRlODI5NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5750">
+      <c r="A5750" s="3" t="inlineStr">
+        <is>
+          <t>882.psd</t>
+        </is>
+      </c>
+      <c r="B5750" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11697.psd</t>
+        </is>
+      </c>
+      <c r="C5750" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZZL1J2Z3VNRzdETmp5N2pqRE9UUkE9PSIsInZhbHVlIjoiT21TTDNIdTloWXNQN0o3Y2tKemxxdz09IiwibWFjIjoiOTk1MDQ5YmQ1ZTAxNmM0MzdmNzkzMjhlMzI5Njk1ZTUwMWU1OGVlYjMxNWY0ZjA2NDUwOWMxMDVlYzBiODRjYSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5751">
+      <c r="A5751" t="inlineStr">
+        <is>
+          <t>881.psd</t>
+        </is>
+      </c>
+      <c r="B5751" t="inlineStr">
+        <is>
+          <t>tamilpsd-11698.psd</t>
+        </is>
+      </c>
+      <c r="C5751" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikg5MGtsN21pc3BPd2FSdDFyeGRWOUE9PSIsInZhbHVlIjoiTHo4dGhEbElSMklPS1VtUWJMQ3FaQT09IiwibWFjIjoiNTFhZTNkODBkZjc5ODEwYzZlMGQ1Mzc0NTc5NDNlZGQyZWZjY2U1MzA4NmU5ZTI3YjE1MzFiYzNmNWIyODUwZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5752">
+      <c r="A5752" s="3" t="inlineStr">
+        <is>
+          <t>880.psd</t>
+        </is>
+      </c>
+      <c r="B5752" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11699.psd</t>
+        </is>
+      </c>
+      <c r="C5752" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InE3VC9BQ0w1d3R3SkRpV0NUc21MRHc9PSIsInZhbHVlIjoid2RUOEx0Mjdqc1dpTkVEOHBnaGNBdz09IiwibWFjIjoiMzFlYjJiNThkODNiYmZlMzU5ZTE0MjYzNDQwNjI2NzQ2OWJhYTU2YjcxMGNjNjk2MWFlMjNkYjhhMDM5NjlhNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5753">
+      <c r="A5753" t="inlineStr">
+        <is>
+          <t>879.psd</t>
+        </is>
+      </c>
+      <c r="B5753" t="inlineStr">
+        <is>
+          <t>tamilpsd-11700.psd</t>
+        </is>
+      </c>
+      <c r="C5753" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkFITlI0OE8wMnVlU2NRbmhsa00za0E9PSIsInZhbHVlIjoiOHZDUHJ1UW0xam81ZUhKSEdJVHB0QT09IiwibWFjIjoiZjAwZjc0NDM2Y2ZlNDA0MjUwYTYwYWVjZGNiZGUxZTQzMzJiOGQ0YmU1MDk0MGJlMmJhYTIzM2Q2MmViMGI1NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5754">
+      <c r="A5754" s="3" t="inlineStr">
+        <is>
+          <t>878.psd</t>
+        </is>
+      </c>
+      <c r="B5754" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11701.psd</t>
+        </is>
+      </c>
+      <c r="C5754" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InFhbis2SFNJZGRBREozS2paOC9nSEE9PSIsInZhbHVlIjoiOWxrdDZoYjV3L1AxaHgrZ3VkUXFQUT09IiwibWFjIjoiY2I1MmFjZjJlMTg5MGZiMDdhYzdiZjc0ZThkNWI4NmVlN2VhZWNmNGQ3MWVkYjljNTI0MzU0NTBkZmQ0YTk4MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5755">
+      <c r="A5755" t="inlineStr">
+        <is>
+          <t>877.psd</t>
+        </is>
+      </c>
+      <c r="B5755" t="inlineStr">
+        <is>
+          <t>tamilpsd-11702.psd</t>
+        </is>
+      </c>
+      <c r="C5755" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjZIR2RQUnBweWhlZ21NYzN6S3VyblE9PSIsInZhbHVlIjoiT2Q1bzl4bEhUZkU5V2hiVFJ1Rldrdz09IiwibWFjIjoiMDk4ZGNiOGU4NDY1ZGI5YjdlYmJiMmQ4NzQ3Y2NkZDUzNDNlMjA2ZDI5ZDgzYjA4MmM3OTE2ZDVlZGRkMzJmZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5756">
+      <c r="A5756" s="3" t="inlineStr">
+        <is>
+          <t>876.psd</t>
+        </is>
+      </c>
+      <c r="B5756" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11703.psd</t>
+        </is>
+      </c>
+      <c r="C5756" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InVFK3duQnRzZC9XdVJWNDhrd3ZONUE9PSIsInZhbHVlIjoieW1lTGloTDEwWVJROW8yNThkOE81Zz09IiwibWFjIjoiN2YwYzZmYjdiNjQ4YzQ2MThmYWVkMDMwNTAyMDliZGE3MmUyOTRiZWY2YzlkNTBmODZmNGNjODhjNzkyMDc1YSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5757">
+      <c r="A5757" t="inlineStr">
+        <is>
+          <t>875.psd</t>
+        </is>
+      </c>
+      <c r="B5757" t="inlineStr">
+        <is>
+          <t>tamilpsd-11704.psd</t>
+        </is>
+      </c>
+      <c r="C5757" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im9UODRKRGRkT244YVc4bXNlUWg1Q2c9PSIsInZhbHVlIjoieW9QUEJSNU4raDBGQ0RWK1lVTndzdz09IiwibWFjIjoiMDA5N2U3ZjBmNjk5ODc1N2Q2NDQyOTdkOTJmNzZlZmY1Njg1ZWI5N2Q2YTkyOGNhOWI3MmY2ODczZWM0MDg3NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5758">
+      <c r="A5758" s="3" t="inlineStr">
+        <is>
+          <t>874.psd</t>
+        </is>
+      </c>
+      <c r="B5758" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11705.psd</t>
+        </is>
+      </c>
+      <c r="C5758" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImhuNnA0ZXNLQ21BZjdERmpaZVFLOUE9PSIsInZhbHVlIjoiYVBmS3hlRitiNFJNZSt0ZDMrMFRqUT09IiwibWFjIjoiNmYyNjVhMzYzNWIxMDQ4N2IxMDdmMzg1YjRlMzcxZmY3ZWIzNzc3YmIxOTIxN2NjYjVhZmM2MjA5ZGFkMTg5YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5759">
+      <c r="A5759" t="inlineStr">
+        <is>
+          <t>873.psd</t>
+        </is>
+      </c>
+      <c r="B5759" t="inlineStr">
+        <is>
+          <t>tamilpsd-11706.psd</t>
+        </is>
+      </c>
+      <c r="C5759" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkxqZ2FtaVlPVGk0dnoyRXB1Ylc0UGc9PSIsInZhbHVlIjoianZnb05BaW9YK2h1NVhRUFRab2xCQT09IiwibWFjIjoiMDk0YmQzYjQyZTQyNjIwYjliZmMzZTc5NjM5YjdlMmY1MGJkMmNjN2YyZGZhYzdkZTdmMWJmZjljYWVlOTY3MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5760">
+      <c r="A5760" s="3" t="inlineStr">
+        <is>
+          <t>872.psd</t>
+        </is>
+      </c>
+      <c r="B5760" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11707.psd</t>
+        </is>
+      </c>
+      <c r="C5760" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjZQU3ExRGNINHVwVTAvSDJBY1kvWGc9PSIsInZhbHVlIjoiZ1ZVUTFzdFRKZHRlOHBiWlM0YVVGQT09IiwibWFjIjoiOTM0ODQ2NDM1MmQ5Njg4Y2Y2MmI5MDkwNjU1MjkzNzQxYmZlODhkZDVhMmY0ZDE3N2U0MTI4M2I3YWYyZjUxNCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5761">
+      <c r="A5761" t="inlineStr">
+        <is>
+          <t>871.psd</t>
+        </is>
+      </c>
+      <c r="B5761" t="inlineStr">
+        <is>
+          <t>tamilpsd-11708.psd</t>
+        </is>
+      </c>
+      <c r="C5761" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Im5wcmQ2aFNpdkhPTjkyb0RWbkRZSVE9PSIsInZhbHVlIjoiS1FyNFZzRUUzTU16aXRXSnJqZGdkdz09IiwibWFjIjoiYWZhYmQ0NTY2ZmZiMjk3N2M4MDcxOTAxMjA5MDc4NDUxZjZlMTUzMzcyOGZlZjIxNGFmNGE4NTgzMzIzN2U2OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5762">
+      <c r="A5762" s="3" t="inlineStr">
+        <is>
+          <t>870.psd</t>
+        </is>
+      </c>
+      <c r="B5762" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11709.psd</t>
+        </is>
+      </c>
+      <c r="C5762" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktVNCtVRGdTOHBjeHlXSForNHNiT3c9PSIsInZhbHVlIjoidFpsSFhqOGh4MUVLdjJlVHhnYlAyQT09IiwibWFjIjoiZTQ2MmJjNjk0OTViOWE4NGI0NzJkODQ4NDdiNjI5MTk1NTc5MDQwMzcxNDZkOTZlNDhmMzkwOGFjODQzNmZlMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5763">
+      <c r="A5763" t="inlineStr">
+        <is>
+          <t>869.psd</t>
+        </is>
+      </c>
+      <c r="B5763" t="inlineStr">
+        <is>
+          <t>tamilpsd-11710.psd</t>
+        </is>
+      </c>
+      <c r="C5763" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkdlMHpkcitiT0J4YWtjeVhQS0hxMnc9PSIsInZhbHVlIjoicDBxcklGNEkxZnZPZm1qdU5SMWp3Zz09IiwibWFjIjoiNmFkMWRiOTBlMjNkMzgyMTJiMzUwNDIwNzgyZGQyMTFiNDMwOWYxYWU0ZTMxMGQ4YmM2MzFkYTMwZmE1ZTA3MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5764">
+      <c r="A5764" s="3" t="inlineStr">
+        <is>
+          <t>868.psd</t>
+        </is>
+      </c>
+      <c r="B5764" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11711.psd</t>
+        </is>
+      </c>
+      <c r="C5764" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InNzQ3NEMng1NVdwV3kzbE0yVjhyMXc9PSIsInZhbHVlIjoiYlNmNG9aeHRkQXJ0UHhHbG9pTGlCQT09IiwibWFjIjoiZmMyNmU2MTk0YTNjYjZlNjRhMTg5MDM5ZWU0MjBjOWE0MjM4MWZmNGQ4YTI3ZGVjOGY1NzY5OTA0NTUzZGRhMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5765">
+      <c r="A5765" t="inlineStr">
+        <is>
+          <t>867.psd</t>
+        </is>
+      </c>
+      <c r="B5765" t="inlineStr">
+        <is>
+          <t>tamilpsd-11712.psd</t>
+        </is>
+      </c>
+      <c r="C5765" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZub2dTbVZ1NVNhemkvbFVWb2xHMFE9PSIsInZhbHVlIjoiTktRN1MrVnNFZWFyT2I1TUY5OVNaUT09IiwibWFjIjoiOWEwZGFlOTFlNzUxYTQ3NzVmMzMyZDI2OTQyZGVkOGQ3ZDNlZjA2YTM0ZGRiNzlmOTlmZTQ1M2I2ZTJlOGVjMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5766">
+      <c r="A5766" s="3" t="inlineStr">
+        <is>
+          <t>866.psd</t>
+        </is>
+      </c>
+      <c r="B5766" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11713.psd</t>
+        </is>
+      </c>
+      <c r="C5766" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhuelJUMURTYjNCTzZyMVdDZ09qV1E9PSIsInZhbHVlIjoiSUxNV1B1MWQranRvYkkwY05DSWF0UT09IiwibWFjIjoiNDMwODAxZWE5ZWU2YjQ5ZjhmZTVhODBkYTI3M2VmNWM1ZDNiZWU4NjdjOTZiNjhiMDY3ZTc4ODMyOTRiNWMyOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5767">
+      <c r="A5767" t="inlineStr">
+        <is>
+          <t>865.psd</t>
+        </is>
+      </c>
+      <c r="B5767" t="inlineStr">
+        <is>
+          <t>tamilpsd-11714.psd</t>
+        </is>
+      </c>
+      <c r="C5767" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkF0Q2tZYXMwaG5jaW5zNGVoTGpUTXc9PSIsInZhbHVlIjoiRzE1S2RqTVZpaTFVcGlraWVIK25nUT09IiwibWFjIjoiMDNkYWZkMDAxMmQ4Mzk0YWQ5MmEyZjc4ZTY2MDUxYjFmYTQ2ZDZjYzExOWJlYjdhMDlmYmQ0M2JhZDhhNTYxZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5768">
+      <c r="A5768" s="3" t="inlineStr">
+        <is>
+          <t>864.psd</t>
+        </is>
+      </c>
+      <c r="B5768" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11715.psd</t>
+        </is>
+      </c>
+      <c r="C5768" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IllsN3NOY1N1WjluVlFZdVJlcDY5dnc9PSIsInZhbHVlIjoiQ0tUT3dSRDZqWFpkNGhXRXNjQ1pGZz09IiwibWFjIjoiOGY2ZDczODNkNmMzOWE0ZTM3OTg0ZjMxNWZiYjU1MTc1ZDFlYjkwYTA1YmNiNzg0NTE5OGJmMTk2ZWRhOTUwOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5769">
+      <c r="A5769" t="inlineStr">
+        <is>
+          <t>863.psd</t>
+        </is>
+      </c>
+      <c r="B5769" t="inlineStr">
+        <is>
+          <t>tamilpsd-11716.psd</t>
+        </is>
+      </c>
+      <c r="C5769" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjhOS2FNNzdGb2c0TFRMdWhtTlVwSmc9PSIsInZhbHVlIjoiWmRvYUtXWWRLMlN1VnlGY2t0WFF5Zz09IiwibWFjIjoiZmFlYTE1NjZlZDE4ZjEzMjVjMTRiMTc1MTQwYWZkNmEwMzJjMGJmODUyZGY0NWUwMDJkMWNmMTZjMmFmM2Q1MiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5770">
+      <c r="A5770" s="3" t="inlineStr">
+        <is>
+          <t>862.psd</t>
+        </is>
+      </c>
+      <c r="B5770" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11717.psd</t>
+        </is>
+      </c>
+      <c r="C5770" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjZMWkJERFY5dGU2aEt5eHVqUTZHMUE9PSIsInZhbHVlIjoibU45QXpONkwzUWdkUktHSXhxREtpZz09IiwibWFjIjoiODg4NWYzMGI4YTA2MDZlOWEzNWU5YmQzNjg1MzM4NTQ1YzQ2M2VjZTg5ZTBmMjM0MjQ2OTEzNDA0OGQyZmEzZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5771">
+      <c r="A5771" t="inlineStr">
+        <is>
+          <t>861.psd</t>
+        </is>
+      </c>
+      <c r="B5771" t="inlineStr">
+        <is>
+          <t>tamilpsd-11718.psd</t>
+        </is>
+      </c>
+      <c r="C5771" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkJrSG9iUlY0Q1Rpa255blpJN2ZuTWc9PSIsInZhbHVlIjoiMnVZTHFOR3l6RjBMelkrd2tYTEZTUT09IiwibWFjIjoiOTNjN2FhZjk4ZjQ1NTUyNzQ4MGFhOGI3MjFmYjczY2YxNWNkMWQ0NDYwOGYwNDNhNDY5MmFlYWQ4MGE3ZjZjOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5772">
+      <c r="A5772" s="3" t="inlineStr">
+        <is>
+          <t>860.psd</t>
+        </is>
+      </c>
+      <c r="B5772" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11719.psd</t>
+        </is>
+      </c>
+      <c r="C5772" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImgveHRZQmJpazF4eFhENmw4TFo3aGc9PSIsInZhbHVlIjoiZERCWm5mSXZCdXFHODhWWmlZTDVpQT09IiwibWFjIjoiNWM0NzVjYzY0ZmY0NmVmODkwNzU4MzlkMWQyYzEyZjJhZjE0ODBjMzg5NDdjZTM4ZmI0ZTliNjI3OGM4MjE4OSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5773">
+      <c r="A5773" t="inlineStr">
+        <is>
+          <t>859.psd</t>
+        </is>
+      </c>
+      <c r="B5773" t="inlineStr">
+        <is>
+          <t>tamilpsd-11720.psd</t>
+        </is>
+      </c>
+      <c r="C5773" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRCUVlEaWlhT2N4ck1MZWdJUjQwanc9PSIsInZhbHVlIjoiSTBMNGJhdHp3L0l1cW9WUTdLeGtGUT09IiwibWFjIjoiOTQ2YWMxYTJiZDY0N2U3ZjI2ZWRmYTYzZDBmOGE4YThkYTRiNjQyYTBhOTI5Njk5ZjhmNjBkNDFlMTBjYWU3NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5774">
+      <c r="A5774" s="3" t="inlineStr">
+        <is>
+          <t>858.psd</t>
+        </is>
+      </c>
+      <c r="B5774" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11721.psd</t>
+        </is>
+      </c>
+      <c r="C5774" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjVCV0NXalNWbXJuamRzS214WUdWUGc9PSIsInZhbHVlIjoiTkl2c1hxd2U3VnpGdTF1MThOeGxWdz09IiwibWFjIjoiZDE3YmZmYjU1Y2YxYTliMzYxYzJhZTdiMzM4ODA0NWZjZjc2N2ZmZjJhMTE5NjFmNjhiOWQwMzQzYTE1ZDVhZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5775">
+      <c r="A5775" t="inlineStr">
+        <is>
+          <t>857.psd</t>
+        </is>
+      </c>
+      <c r="B5775" t="inlineStr">
+        <is>
+          <t>tamilpsd-11722.psd</t>
+        </is>
+      </c>
+      <c r="C5775" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjFyRGlvYlFQQk1IRVJoSk16Sk1TTmc9PSIsInZhbHVlIjoiZmU2NUpvUEVtWVphNjJqWGRxVDIvdz09IiwibWFjIjoiNWU1ZDIyNGZhOTAwNWY0NTEzMWI2MWEwYmEwMDNhNjM2NjQyZTQ0MmIwYmE4YTJmZWIzM2MwMDYxMzVhMTg1MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5776">
+      <c r="A5776" s="3" t="inlineStr">
+        <is>
+          <t>856.psd</t>
+        </is>
+      </c>
+      <c r="B5776" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11723.psd</t>
+        </is>
+      </c>
+      <c r="C5776" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjIybkdzcUpoZThzV0g5OHQvcWZicWc9PSIsInZhbHVlIjoidG5PYkEyZmUyVlY3QjFpY3BNMnREdz09IiwibWFjIjoiZmI0N2M2ODlkZmYyMmI5MmFiMDU2NmUwODUxNTFhNGRlNDE5M2UxMGFjMDk2MGMyMmJjYjBlNTRkZGI1MmNhZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5777">
+      <c r="A5777" t="inlineStr">
+        <is>
+          <t>855.psd</t>
+        </is>
+      </c>
+      <c r="B5777" t="inlineStr">
+        <is>
+          <t>tamilpsd-11724.psd</t>
+        </is>
+      </c>
+      <c r="C5777" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlFBTWQrT1p2T2lPcm5kNW9MRW9Hcmc9PSIsInZhbHVlIjoiejR5QU8rKzdwUWQyKzJpRk82Q2RUUT09IiwibWFjIjoiNGVhYjM3NGVmNTVhMDNhZjVlMDRjOGVmYzRhYjM4NTMxMWUwOWZkOTM3NGU0ZDMxMTAyMTU5NmE0MDA4NTU1NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5778">
+      <c r="A5778" s="3" t="inlineStr">
+        <is>
+          <t>854.psd</t>
+        </is>
+      </c>
+      <c r="B5778" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11725.psd</t>
+        </is>
+      </c>
+      <c r="C5778" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik1xNjAxZWp2Slc1WHhNYUo0SU1Gcmc9PSIsInZhbHVlIjoiUnVrNEMrR2tvZEpqdGVBcExOVU12Zz09IiwibWFjIjoiZmM5MWNkZWIzOTU0ODFlNjNlZjA2OWUzMjY3MWE5YjYwYTY5ODM0ZTc0Nzc4ODlhNjlkODNlMTk2OWQ5ZDBmYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5779">
+      <c r="A5779" t="inlineStr">
+        <is>
+          <t>853.psd</t>
+        </is>
+      </c>
+      <c r="B5779" t="inlineStr">
+        <is>
+          <t>tamilpsd-11726.psd</t>
+        </is>
+      </c>
+      <c r="C5779" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlNkeGw3WDRJSkdObGdWWXRiZndzNnc9PSIsInZhbHVlIjoiZUF4NFhrSm9pa0hVRWlZbVFCSE5yUT09IiwibWFjIjoiYzY1NWIzNmU3MDAwOTg1YjVhYjRlYjMxMTVkMTgzYTVmNWQzZjQ4ZTJjODFiODNiMGM1ODdkNDhjZDEyYTRkZSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5780">
+      <c r="A5780" s="3" t="inlineStr">
+        <is>
+          <t>852.psd</t>
+        </is>
+      </c>
+      <c r="B5780" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11727.psd</t>
+        </is>
+      </c>
+      <c r="C5780" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Iko1U1pLajBFV1I0RGY5N1NCcnJBN1E9PSIsInZhbHVlIjoiSFJiQXhuWksxUndKelEyTEZ5VUhKZz09IiwibWFjIjoiODQwNTUzZDJkNDQ0YWRjYjE5MTNhZTcxNjE2MmIzYzZjOWZmMTczMzBkNmFhYjRiMDVkNWQ1ZDg3YThkNTJhNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5781">
+      <c r="A5781" t="inlineStr">
+        <is>
+          <t>851.psd</t>
+        </is>
+      </c>
+      <c r="B5781" t="inlineStr">
+        <is>
+          <t>tamilpsd-11728.psd</t>
+        </is>
+      </c>
+      <c r="C5781" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImI0dkRlanFKRVJMTWpZeTROdW1kc0E9PSIsInZhbHVlIjoiNElSb3dzTFZjazFXK0xVUXRITnJvQT09IiwibWFjIjoiOGRmZjA4MTIxNjdkYWQzMWNiNWJiYWJkNzgxZWViODNhNzY3MDU3MGM4MTNjMmQyMTA5ZThjOTE4YmY2N2MxYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5782">
+      <c r="A5782" s="3" t="inlineStr">
+        <is>
+          <t>850.psd</t>
+        </is>
+      </c>
+      <c r="B5782" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11729.psd</t>
+        </is>
+      </c>
+      <c r="C5782" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InY1S1NpcEZyRythL0tZM2l3am5CRGc9PSIsInZhbHVlIjoiUlFRYnJYeFJxcFRHZHNzcFlIbktRdz09IiwibWFjIjoiZGZiZmJhMTkwZDM0YWUxMGMwMWVhYWIwNzM4ZmNhNGUzOGJhMjdlYzEwZTZjMGMwNWNmNWI0NjQ4MGRiNWRmMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5783">
+      <c r="A5783" t="inlineStr">
+        <is>
+          <t>849.psd</t>
+        </is>
+      </c>
+      <c r="B5783" t="inlineStr">
+        <is>
+          <t>tamilpsd-11730.psd</t>
+        </is>
+      </c>
+      <c r="C5783" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlpEZDNrS21pT0gyay84eEF0dWQzM3c9PSIsInZhbHVlIjoielkrZ2dhN1R2eXV4TUk2RWJDc2xxZz09IiwibWFjIjoiN2RjZjQ0ZWM4YWY5Yjc0ODUyODg1MTBlOTFkZWE2ZWYxMjBhZGQ3ZWJiYmRlZmY1NzZmNzA4NGE0MDcxYTA2NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5784">
+      <c r="A5784" s="3" t="inlineStr">
+        <is>
+          <t>848.psd</t>
+        </is>
+      </c>
+      <c r="B5784" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11731.psd</t>
+        </is>
+      </c>
+      <c r="C5784" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjcxWjhPWkNMZFZ0S1hqaTExR21HMlE9PSIsInZhbHVlIjoicFV0dzE5NEU5VG15OERCazZJcFRDQT09IiwibWFjIjoiYzcwYTM2NDlmNTg5MDZkNmZmOGQxYjIwZjdjZmVmMzBhZWRkMzVlM2ZkYmM2OGI4NTJlNzFmNWJiMWViYjRjMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5785">
+      <c r="A5785" t="inlineStr">
+        <is>
+          <t>846.psd</t>
+        </is>
+      </c>
+      <c r="B5785" t="inlineStr">
+        <is>
+          <t>tamilpsd-11732.psd</t>
+        </is>
+      </c>
+      <c r="C5785" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjM2ZjVvcEN4dkVHVkJWa1IvSHNCZGc9PSIsInZhbHVlIjoiaEI3UjY3YktHcWFxZ0xUVGFjbkV1dz09IiwibWFjIjoiY2M3YzdjYjZlYjZjNzM5YjBjZTRiM2Y0ZjBkYWQ0NzFlOTY4YzdkMzE1MzAyNmI2YWFmYWVhZTNhNzI0YTM0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5786">
+      <c r="A5786" s="3" t="inlineStr">
+        <is>
+          <t>847.psd</t>
+        </is>
+      </c>
+      <c r="B5786" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11733.psd</t>
+        </is>
+      </c>
+      <c r="C5786" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjlyTlJiRGtLVkJ2Sm5yYW1lU3c4REE9PSIsInZhbHVlIjoiNHRZbXBCeDF1dVl3QVpQK2xrQzByUT09IiwibWFjIjoiZGQ3ZWFlZGFjZjI5NDE3MGIwYmVkZmE1ZWZmOWE0ZjllYTlmYWExZWY2YTFjNTk3YjZjODhiNDUzYTQ5MjBhZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5787">
+      <c r="A5787" t="inlineStr">
+        <is>
+          <t>845.psd</t>
+        </is>
+      </c>
+      <c r="B5787" t="inlineStr">
+        <is>
+          <t>tamilpsd-11734.psd</t>
+        </is>
+      </c>
+      <c r="C5787" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IldRbnJ0bmI3NnZ5aG03YUhXV1hvQWc9PSIsInZhbHVlIjoiUW84SERhZE50SkVFaXRqWkdxUXVjUT09IiwibWFjIjoiYzc1YzZhNDRlNThiNDg5YjdmY2UzNWYwMjRhMTc2YzVkYWJlZTQzZGZmN2JiOGZiYjEyYTI2N2U2MDAyYjgwYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5788">
+      <c r="A5788" s="3" t="inlineStr">
+        <is>
+          <t>844.psd</t>
+        </is>
+      </c>
+      <c r="B5788" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11735.psd</t>
+        </is>
+      </c>
+      <c r="C5788" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlQ1QkRNdVBvUmdIdWNUTDUrb1B3MWc9PSIsInZhbHVlIjoicFBKSDhsUlFwd0t4L041VlkxSTdCQT09IiwibWFjIjoiOTMwYmMxZTRkNjdkZjQ1NjllOTExNjQyYWUzYjA0NmNlZjQ5NTg2NWU1YTE3YjhiODdkY2E4MzIwZWExNTVjMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5789">
+      <c r="A5789" t="inlineStr">
+        <is>
+          <t>843.psd</t>
+        </is>
+      </c>
+      <c r="B5789" t="inlineStr">
+        <is>
+          <t>tamilpsd-11736.psd</t>
+        </is>
+      </c>
+      <c r="C5789" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IktnZHZCK1lFbEFPZzZrcXlrYXA3eHc9PSIsInZhbHVlIjoiZXM4MjlrbUlZaW1Mam1QK1RmMUoxdz09IiwibWFjIjoiYzhlYWRjYzY5MmM0NzQxNWJlY2Q3YmU4Y2MzYmUxNTkzNDY5MjlmNWJhNWQ4NjRiNjg4YWRiMDY1ODQwOTg0YyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5790">
+      <c r="A5790" s="3" t="inlineStr">
+        <is>
+          <t>841.psd</t>
+        </is>
+      </c>
+      <c r="B5790" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11737.psd</t>
+        </is>
+      </c>
+      <c r="C5790" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlhRS3BvaU9ZcUxxU0JUdkJOMk53dnc9PSIsInZhbHVlIjoiYUJDWXBIMEhubVN0eFBLTzRBRVhGdz09IiwibWFjIjoiYjc1NWEyNjYwYzdlMzYyZDYzNjk4NWM2NzgyMWMyZGU4NDA2NWJlYmUzZjRkZmU0NWI1MmYxNjAwMTA3YjNhYyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5791">
+      <c r="A5791" t="inlineStr">
+        <is>
+          <t>840.psd</t>
+        </is>
+      </c>
+      <c r="B5791" t="inlineStr">
+        <is>
+          <t>tamilpsd-11738.psd</t>
+        </is>
+      </c>
+      <c r="C5791" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Imp3OThyVSsvM0o0NkRXSkc4VGcxbVE9PSIsInZhbHVlIjoiVU9zQ0hLOVJUeEJxLzdCZEhmTzdNZz09IiwibWFjIjoiZmUxYjM2MGM2YzdjMmJhNWU0OTU3NDcxNDZlNTkxZTBlMTljOTlmMTM4NDhiMjgzZTlmYjdkY2M3OTg2NGMxMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5792">
+      <c r="A5792" s="3" t="inlineStr">
+        <is>
+          <t>839.psd</t>
+        </is>
+      </c>
+      <c r="B5792" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11739.psd</t>
+        </is>
+      </c>
+      <c r="C5792" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Inl5SW9iTVdBNm9Lek5oUnBsbXhnUkE9PSIsInZhbHVlIjoicEhmNHM4dnhmQmxPVHdNd3lIOWJaQT09IiwibWFjIjoiZWEyMGE1YzhmMzA0OWMyZTNkZDA2NDY1ZGM1ZDBlM2VlYTM4ODM0ZjYwMWNlMzUzNGU5YWU3OTc2NmYyNTdlOCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5793">
+      <c r="A5793" t="inlineStr">
+        <is>
+          <t>838.psd</t>
+        </is>
+      </c>
+      <c r="B5793" t="inlineStr">
+        <is>
+          <t>tamilpsd-11740.psd</t>
+        </is>
+      </c>
+      <c r="C5793" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRyZndDdkhXZ2dDYXNVVzhoRGpQakE9PSIsInZhbHVlIjoiZWVEbzFZN3h6cEhMbTFTQThkamdyUT09IiwibWFjIjoiNGRmY2UyZjUyYzgxMDM3MTAyNTc5YTBjMGNlM2EyMjFjNTA1ZjljZjhhYjI3Y2Y2NzlhYjE4NzY2YjQ4NTNjMiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5794">
+      <c r="A5794" s="3" t="inlineStr">
+        <is>
+          <t>837.psd</t>
+        </is>
+      </c>
+      <c r="B5794" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11741.psd</t>
+        </is>
+      </c>
+      <c r="C5794" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IndZdTVPZWNEVERtMFlqV0oyNGJkSGc9PSIsInZhbHVlIjoib244SnVzelpVQzNkaWQ4bkRsRGYxQT09IiwibWFjIjoiZTJjNmJiMWVjOTE3NDkyNTgyNjRmMmQzN2ZmY2Q2ZDdlMDY5ZTFkOGI5NmE1ODc2NTMyMDMwZTRiMjRhNWE5NCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5795">
+      <c r="A5795" t="inlineStr">
+        <is>
+          <t>835.psd</t>
+        </is>
+      </c>
+      <c r="B5795" t="inlineStr">
+        <is>
+          <t>tamilpsd-11742.psd</t>
+        </is>
+      </c>
+      <c r="C5795" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkZlcG1pMVVTQVk3bkVxMU9TWVIyelE9PSIsInZhbHVlIjoiQ3dBWVR0ZzFzVi9qekJ6Z1BQNGVqUT09IiwibWFjIjoiNGI5ZTA5NDZkYjhlNGNhZDUzMjU2ODk4OWQxNDRhYjczNmRlZGIzZTNmNzFiNjFlMzE1YzQwYmM2ZDYwNGU2MyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5796">
+      <c r="A5796" s="3" t="inlineStr">
+        <is>
+          <t>834.psd</t>
+        </is>
+      </c>
+      <c r="B5796" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11743.psd</t>
+        </is>
+      </c>
+      <c r="C5796" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ik51SXJXeERPaGRkUVpvWjc0ckpkRWc9PSIsInZhbHVlIjoiaFdTM2pySjVLdDlRQ0M4cE9GUHhSQT09IiwibWFjIjoiY2M3MTg0M2ZlZjMxYTcyZTY4NmJlYzZiNGE3ZDc5N2FkNDljNGZlZjBhMDcwYzczOWUyOGVhNjFkZjkyMGRmOSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5797">
+      <c r="A5797" t="inlineStr">
+        <is>
+          <t>833.psd</t>
+        </is>
+      </c>
+      <c r="B5797" t="inlineStr">
+        <is>
+          <t>tamilpsd-11744.psd</t>
+        </is>
+      </c>
+      <c r="C5797" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InhEd2lHSFVpTEFNL05RNDdSTmF6V2c9PSIsInZhbHVlIjoiTDVmMUxLSlA4aEFqR1BuMmVhK1R3Zz09IiwibWFjIjoiMjNiODNjNjY4OWUzMmMwODI0NWUzYjUwZDlkMDQ5NDRiODI0MDkxOWE3ZDRjMDcxYWFmOTJiNDM4YzBkNDQ4NSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5798">
+      <c r="A5798" s="3" t="inlineStr">
+        <is>
+          <t>832.psd</t>
+        </is>
+      </c>
+      <c r="B5798" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11745.psd</t>
+        </is>
+      </c>
+      <c r="C5798" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikd1Yjl4Z0VtYTFlRkY1QXVvUUJHZ2c9PSIsInZhbHVlIjoiTEtjSFBXaU1Eb1lzby9yUGRSTTBqQT09IiwibWFjIjoiMjExMGI3MTNlNTNhYmMwM2U5ZDk3YzhhNzY1MmJkZjYyMDM4NGJmMDUzN2VhMTg2MzU0OWE4ZDcyZTk3NzFhMCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5799">
+      <c r="A5799" t="inlineStr">
+        <is>
+          <t>831.psd</t>
+        </is>
+      </c>
+      <c r="B5799" t="inlineStr">
+        <is>
+          <t>tamilpsd-11746.psd</t>
+        </is>
+      </c>
+      <c r="C5799" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjB0d012Zys3RnYvMUVsMkE2cmp6M3c9PSIsInZhbHVlIjoibkdtSEJ1WWQwZVA2V2VQbEpuMWEyQT09IiwibWFjIjoiMDgwZDA3MGQ4OTQyNWRmODRhYTVlMDliNzJjNjA0MDg0MzA1NDQ1YzA3OWVhODE5MmEwMjNhODBmNzAxZDk1NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5800">
+      <c r="A5800" s="3" t="inlineStr">
+        <is>
+          <t>830.psd</t>
+        </is>
+      </c>
+      <c r="B5800" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11747.psd</t>
+        </is>
+      </c>
+      <c r="C5800" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IitwU2p6V1EyQVhwVjdYa0ltVnliWEE9PSIsInZhbHVlIjoicnloa0RmelBxazJwZzd3ZVZMYnJIQT09IiwibWFjIjoiMzE3YTg4YmZlOGUwOWM5MTQ1M2ZjNTgyOWNmMzY5NWI2MzMxNjAzZDdmY2E0ZGY5NWI5Mjg4ZTg0OGRiZWY2NiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5801">
+      <c r="A5801" t="inlineStr">
+        <is>
+          <t>829.psd</t>
+        </is>
+      </c>
+      <c r="B5801" t="inlineStr">
+        <is>
+          <t>tamilpsd-11748.psd</t>
+        </is>
+      </c>
+      <c r="C5801" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IjJoSGc5bG9uUGpDZjhaenJwWi9xdEE9PSIsInZhbHVlIjoiTU1Qejd3dVc4RGZKa2lsbDJBc09sUT09IiwibWFjIjoiODI5MTU4NjMwYzg4NTE4ZmY5NTY2MzY4ZjY3ZTkyY2RjMGYzMmNmNjIyMDYxZDBiYjBiNmNhMTAxODQ3MGU0ZiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5802">
+      <c r="A5802" s="3" t="inlineStr">
+        <is>
+          <t>828.psd</t>
+        </is>
+      </c>
+      <c r="B5802" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11749.psd</t>
+        </is>
+      </c>
+      <c r="C5802" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ijh3dTVQZDRsbGVkTWFqeStqZDdaaGc9PSIsInZhbHVlIjoiTVFvM2NEMkFRZTZDQ01RTVVTNlk5QT09IiwibWFjIjoiNDIzZmUyNTFmYzNlMTA3NGI4MTcwZTlmNTE2YmUxNWQzZjFlMjU1OTA4MTFlMjc0YjhlNTA3M2NkM2RkZWYxNyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5803">
+      <c r="A5803" t="inlineStr">
+        <is>
+          <t>826.psd</t>
+        </is>
+      </c>
+      <c r="B5803" t="inlineStr">
+        <is>
+          <t>tamilpsd-11750.psd</t>
+        </is>
+      </c>
+      <c r="C5803" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IkRVOEw2UmFCUGIrU3Vrd2ZmVkFrWWc9PSIsInZhbHVlIjoiWFRkYkY2dm9mRzV6RkVRWTRpRUhMZz09IiwibWFjIjoiOWVkMWYyNjQwOTMzYWRkNDdkYjliYWM1ZDY5NzU5MmM1Y2Y4M2Y2MzQ0OWFkZGI2NmQxYTMyNTgwYjU2NmY4OCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5804">
+      <c r="A5804" s="3" t="inlineStr">
+        <is>
+          <t>825.psd</t>
+        </is>
+      </c>
+      <c r="B5804" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11751.psd</t>
+        </is>
+      </c>
+      <c r="C5804" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImRCa3FPSjc3L1FvQk44ZGpCYklrQlE9PSIsInZhbHVlIjoiT1JsYzNURHM3aU5LSFlJNkJuZGd4QT09IiwibWFjIjoiODBiMDkxNWM5MWVhYWFjZDA4ZmU5NTFmMjY1NGVmZGU4NDhiMTU5YWY2YjNjMmQyZTY5NGJiNjNkMDhmM2Y3MCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5805">
+      <c r="A5805" t="inlineStr">
+        <is>
+          <t>824.psd</t>
+        </is>
+      </c>
+      <c r="B5805" t="inlineStr">
+        <is>
+          <t>tamilpsd-11752.psd</t>
+        </is>
+      </c>
+      <c r="C5805" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6ImFYclBqU2xGU3dGNlh5Nys5ZTUrTHc9PSIsInZhbHVlIjoib3dEZk9lMEd2N21EZExMTjFGME9zdz09IiwibWFjIjoiOTU5ZjVlZjY1N2RkNWYyNDk3NGRlYjA2NDRkMDAyNDc1Mjk1ZjU3ZTU2Y2RlNzYwOWJjZjRkMWI0NzNmNDVlNiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5806">
+      <c r="A5806" s="3" t="inlineStr">
+        <is>
+          <t>823.psd</t>
+        </is>
+      </c>
+      <c r="B5806" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11753.psd</t>
+        </is>
+      </c>
+      <c r="C5806" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InltRVFSRnR3RFhzT0RPZGZ1S1I4Q0E9PSIsInZhbHVlIjoiSW15aG81OXplQWx6bkVBd3RYTldKdz09IiwibWFjIjoiNjMzZmQyODRlZDM4YzQ0N2I0Y2Q3MzAyYTUyNmZmNjQxYjFjNzY5OWM3MWU2MGRlZTZhY2U2ZjIxMzFiNGI0ZCIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5807">
+      <c r="A5807" t="inlineStr">
+        <is>
+          <t>822.psd</t>
+        </is>
+      </c>
+      <c r="B5807" t="inlineStr">
+        <is>
+          <t>tamilpsd-11754.psd</t>
+        </is>
+      </c>
+      <c r="C5807" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6InlPUWU2NWlBOGVnMXhpSFN0OU56aUE9PSIsInZhbHVlIjoiYVlDRnBsTW9BQTdaZjcya3UwQkt3dz09IiwibWFjIjoiODRkNDUyNzAzZDU5NTg1NzkwMmJmM2UyZDI1YTc4MTliNmYzZDVmZjBiNzZjZmRkOWRjNDRjYzVmYWJiNDY5NyIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5808">
+      <c r="A5808" s="3" t="inlineStr">
+        <is>
+          <t>821.psd</t>
+        </is>
+      </c>
+      <c r="B5808" s="3" t="inlineStr">
+        <is>
+          <t>tamilpsd-11755.psd</t>
+        </is>
+      </c>
+      <c r="C5808" s="3" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6IlVBMlhsbmR6Vm9mT1UreVdxTWErbFE9PSIsInZhbHVlIjoiQmtnaEZhc1htMTVsb2FVaUcxR1FyQT09IiwibWFjIjoiMWY4Y2RmM2VkYzRhMWYzYTY2YWQ4MTI5NDM5ZTEwYTY2YjY3ZGQxMTcwODc5M2RiZWQ5OWU5NjQ2YmYzMzE0YiIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5809">
+      <c r="A5809" t="inlineStr">
+        <is>
+          <t>820.psd</t>
+        </is>
+      </c>
+      <c r="B5809" t="inlineStr">
+        <is>
+          <t>tamilpsd-11756.psd</t>
+        </is>
+      </c>
+      <c r="C5809" t="inlineStr">
+        <is>
+          <t>https://forpsd.com/download/eyJpdiI6Ikk0WFRGTWlDU0Q1WGJiYzkzaUliOVE9PSIsInZhbHVlIjoiK3cvb244Y2Fyb1FibDhvaDIwaWdDUT09IiwibWFjIjoiOTFlYjAzYjk0Y2IyMDI0Njg3ZjZjZjk3NDAxMTVkOGU1ZDZjNmEyOTNmM2I0OGY3MzExMWE4N2M1ODhiNDA5MSIsInRhZyI6IiJ9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
